--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -719,13 +719,13 @@
         <v>11.76</v>
       </c>
       <c r="S2" t="n">
-        <v>61.1</v>
+        <v>61.6</v>
       </c>
       <c r="T2" t="n">
         <v>0.32</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="V2" t="n">
         <v>60</v>
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1461.04</v>
+        <v>1463.1</v>
       </c>
       <c r="AO2" t="n">
-        <v>1409.93</v>
+        <v>1409.05</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="T3" t="n">
         <v>0.39</v>
@@ -951,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>8039.51</v>
+        <v>8057.14</v>
       </c>
       <c r="AO3" t="n">
-        <v>7636.76</v>
+        <v>7648.5</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>11.76</v>
       </c>
       <c r="S4" t="n">
-        <v>58.6</v>
+        <v>58.8</v>
       </c>
       <c r="T4" t="n">
         <v>0.29</v>
@@ -1118,10 +1118,10 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>115.79</v>
+        <v>116.18</v>
       </c>
       <c r="AO4" t="n">
-        <v>109.46</v>
+        <v>109.62</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>11.76</v>
       </c>
       <c r="S5" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="T5" t="n">
         <v>0.29</v>
@@ -1285,10 +1285,10 @@
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12178.66</v>
+        <v>12177.9</v>
       </c>
       <c r="AO5" t="n">
-        <v>11640.57</v>
+        <v>11645.22</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>58.3</v>
+        <v>57.7</v>
       </c>
       <c r="T6" t="n">
         <v>0.25</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.86</v>
+        <v>-0.88</v>
       </c>
       <c r="V6" t="n">
         <v>55</v>
@@ -1405,10 +1405,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>2707.04</v>
+        <v>2707.02</v>
       </c>
       <c r="Z6" t="n">
-        <v>2803.2</v>
+        <v>2803.18</v>
       </c>
       <c r="AA6" t="n">
         <v>2769.28</v>
@@ -1452,10 +1452,10 @@
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>2814.38</v>
+        <v>2816.91</v>
       </c>
       <c r="AO6" t="n">
-        <v>2686.78</v>
+        <v>2683.26</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1554,13 +1554,13 @@
         <v>11.76</v>
       </c>
       <c r="S7" t="n">
-        <v>56.3</v>
+        <v>55.5</v>
       </c>
       <c r="T7" t="n">
         <v>0.25</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.96</v>
+        <v>-0.99</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -1619,10 +1619,10 @@
         <v>11.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>2268.06</v>
+        <v>2264.99</v>
       </c>
       <c r="AO7" t="n">
-        <v>2144.03</v>
+        <v>2137.47</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105127.58</v>
+        <v>98206.09</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,145 +1680,145 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>738.55</v>
+        <v>372.95</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹735.6 - ₹742.98</t>
+          <t>₹371.41 - ₹375.26</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>750.37</v>
+        <v>379.11</v>
       </c>
       <c r="I8" t="n">
-        <v>225</v>
+        <v>432</v>
       </c>
       <c r="J8" t="n">
-        <v>729.51</v>
+        <v>357.21</v>
       </c>
       <c r="K8" t="n">
-        <v>703.6799999999999</v>
+        <v>349.78</v>
       </c>
       <c r="L8" t="n">
-        <v>686.09</v>
+        <v>347.56</v>
       </c>
       <c r="M8" t="n">
-        <v>9.210000000000001</v>
+        <v>6.64</v>
       </c>
       <c r="N8" t="n">
-        <v>8.49</v>
+        <v>4.07</v>
       </c>
       <c r="O8" t="n">
-        <v>9.380000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.77</v>
+        <v>7.7</v>
       </c>
       <c r="R8" t="n">
         <v>11.76</v>
       </c>
       <c r="S8" t="n">
-        <v>51.9</v>
+        <v>53</v>
       </c>
       <c r="T8" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="U8" t="n">
         <v>-1.03</v>
       </c>
       <c r="V8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="W8" t="n">
-        <v>5.75</v>
+        <v>2.81</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>720.8200000000001</v>
+        <v>366.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>725.27</v>
+        <v>379.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>744.46</v>
+        <v>375.93</v>
       </c>
       <c r="AB8" t="n">
-        <v>716.39</v>
+        <v>361.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>744.27</v>
+        <v>372.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>751.6900000000001</v>
+        <v>374.64</v>
       </c>
       <c r="AE8" t="n">
-        <v>764.8200000000001</v>
+        <v>376.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>48.2</v>
+        <v>78.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76)</t>
+          <t>Low VIX (11.76)</t>
         </is>
       </c>
       <c r="AI8" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>49</v>
+        <v>6.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>15.1</v>
+        <v>25.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>20.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AM8" t="n">
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>756.42</v>
+        <v>382.62</v>
       </c>
       <c r="AO8" t="n">
-        <v>720.72</v>
+        <v>363.2</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
+          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
+          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
+          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
         </is>
       </c>
     </row>
@@ -1830,16 +1830,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>98206.09</v>
+        <v>105127.58</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,145 +1847,145 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>372.95</v>
+        <v>738.55</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹371.41 - ₹375.26</t>
+          <t>₹735.6 - ₹742.98</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>379.11</v>
+        <v>750.37</v>
       </c>
       <c r="I9" t="n">
-        <v>432</v>
+        <v>225</v>
       </c>
       <c r="J9" t="n">
-        <v>357.21</v>
+        <v>729.51</v>
       </c>
       <c r="K9" t="n">
-        <v>349.78</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>347.56</v>
+        <v>686.09</v>
       </c>
       <c r="M9" t="n">
-        <v>6.64</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>4.07</v>
+        <v>8.49</v>
       </c>
       <c r="O9" t="n">
-        <v>2.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>-0.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.7</v>
+        <v>14.77</v>
       </c>
       <c r="R9" t="n">
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>52.6</v>
+        <v>51.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.05</v>
+        <v>-1.04</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="W9" t="n">
-        <v>2.81</v>
+        <v>5.74</v>
       </c>
       <c r="X9" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>366.16</v>
+        <v>720.8200000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>379.22</v>
+        <v>725.26</v>
       </c>
       <c r="AA9" t="n">
-        <v>375.93</v>
+        <v>744.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>361.4</v>
+        <v>716.39</v>
       </c>
       <c r="AC9" t="n">
-        <v>372.32</v>
+        <v>744.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>374.64</v>
+        <v>751.6900000000001</v>
       </c>
       <c r="AE9" t="n">
-        <v>376.32</v>
+        <v>764.8200000000001</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.3</v>
+        <v>48.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Low VIX (11.76)</t>
+          <t>TTM Squeeze | Low VIX (11.76)</t>
         </is>
       </c>
       <c r="AI9" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>6.1</v>
+        <v>49</v>
       </c>
       <c r="AK9" t="n">
-        <v>25.2</v>
+        <v>15.1</v>
       </c>
       <c r="AL9" t="n">
-        <v>68.90000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="AM9" t="n">
         <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>383.31</v>
+        <v>757.85</v>
       </c>
       <c r="AO9" t="n">
-        <v>363.07</v>
+        <v>720.36</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
+          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
+          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
+          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
         </is>
       </c>
     </row>
@@ -2055,13 +2055,13 @@
         <v>11.76</v>
       </c>
       <c r="S10" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="T10" t="n">
         <v>0.3</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.08</v>
+        <v>-1.07</v>
       </c>
       <c r="V10" t="n">
         <v>41.7</v>
@@ -2073,10 +2073,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>4548.57</v>
+        <v>4548.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>4711.2</v>
+        <v>4711.24</v>
       </c>
       <c r="AA10" t="n">
         <v>4683.67</v>
@@ -2120,10 +2120,10 @@
         <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>4766.04</v>
+        <v>4769.63</v>
       </c>
       <c r="AO10" t="n">
-        <v>4524.12</v>
+        <v>4515.61</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         <v>17.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>5882.83</v>
+        <v>5880.76</v>
       </c>
       <c r="AO11" t="n">
-        <v>5618.25</v>
+        <v>5625.04</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2389,13 +2389,13 @@
         <v>11.76</v>
       </c>
       <c r="S12" t="n">
-        <v>56.4</v>
+        <v>56.6</v>
       </c>
       <c r="T12" t="n">
         <v>0.21</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.24</v>
+        <v>-1.23</v>
       </c>
       <c r="V12" t="n">
         <v>53.3</v>
@@ -2454,10 +2454,10 @@
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>3878.18</v>
+        <v>3866.75</v>
       </c>
       <c r="AO12" t="n">
-        <v>3649.2</v>
+        <v>3645.21</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2556,13 +2556,13 @@
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
       <c r="T13" t="n">
         <v>0.23</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.26</v>
+        <v>-1.28</v>
       </c>
       <c r="V13" t="n">
         <v>45</v>
@@ -2621,10 +2621,10 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>1504.82</v>
+        <v>1504.41</v>
       </c>
       <c r="AO13" t="n">
-        <v>1443.14</v>
+        <v>1443.16</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2723,13 +2723,13 @@
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>56.5</v>
+        <v>56</v>
       </c>
       <c r="T14" t="n">
         <v>0.18</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.52</v>
+        <v>-1.54</v>
       </c>
       <c r="V14" t="n">
         <v>55</v>
@@ -2741,10 +2741,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>1019.37</v>
+        <v>1019.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>1056.01</v>
+        <v>1055.98</v>
       </c>
       <c r="AA14" t="n">
         <v>1055.07</v>
@@ -2788,10 +2788,10 @@
         <v>18.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>1086.02</v>
+        <v>1086.01</v>
       </c>
       <c r="AO14" t="n">
-        <v>1011.32</v>
+        <v>1011.5</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>146280.27</v>
+        <v>85420.58</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2849,145 +2849,145 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1651.3</v>
+        <v>14049</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹1641.81 - ₹1665.54</t>
+          <t>₹13965.8 - ₹14173.8</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1689.26</v>
+        <v>14381.8</v>
       </c>
       <c r="I15" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>1478.49</v>
+        <v>13190.57</v>
       </c>
       <c r="K15" t="n">
-        <v>1460.44</v>
+        <v>12605.68</v>
       </c>
       <c r="L15" t="n">
-        <v>1458.79</v>
+        <v>12333.95</v>
       </c>
       <c r="M15" t="n">
-        <v>14.41</v>
+        <v>16.25</v>
       </c>
       <c r="N15" t="n">
-        <v>56.22</v>
+        <v>477.1</v>
       </c>
       <c r="O15" t="n">
-        <v>42.84</v>
+        <v>503.84</v>
       </c>
       <c r="P15" t="n">
-        <v>13.38</v>
+        <v>-26.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>47.45</v>
+        <v>416</v>
       </c>
       <c r="R15" t="n">
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>49.7</v>
+        <v>51.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.77</v>
+        <v>-1.76</v>
       </c>
       <c r="V15" t="n">
-        <v>48.3</v>
+        <v>46.7</v>
       </c>
       <c r="W15" t="n">
-        <v>8.69</v>
+        <v>6.67</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>1625.39</v>
+        <v>13634.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>1683.18</v>
+        <v>14126.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1664.51</v>
+        <v>14161.39</v>
       </c>
       <c r="AB15" t="n">
-        <v>1580.13</v>
+        <v>13425</v>
       </c>
       <c r="AC15" t="n">
-        <v>1641.1</v>
+        <v>14079.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1671.7</v>
+        <v>14558.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>1692.1</v>
+        <v>15067.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>86.2</v>
+        <v>64.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Low VIX (11.76)</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76)</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>28.6</v>
+        <v>41.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>17.7</v>
+        <v>21.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>8.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AM15" t="n">
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>1694.41</v>
+        <v>14572.92</v>
       </c>
       <c r="AO15" t="n">
-        <v>1604.92</v>
+        <v>13548.3</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
+          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
+          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
+          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>85420.58</v>
+        <v>146280.27</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3016,145 +3016,145 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>14049</v>
+        <v>1651.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹13965.8 - ₹14173.8</t>
+          <t>₹1641.81 - ₹1665.54</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14381.8</v>
+        <v>1689.26</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="J16" t="n">
-        <v>13190.57</v>
+        <v>1478.49</v>
       </c>
       <c r="K16" t="n">
-        <v>12605.68</v>
+        <v>1460.44</v>
       </c>
       <c r="L16" t="n">
-        <v>12333.95</v>
+        <v>1458.79</v>
       </c>
       <c r="M16" t="n">
-        <v>16.25</v>
+        <v>14.41</v>
       </c>
       <c r="N16" t="n">
-        <v>477.1</v>
+        <v>56.22</v>
       </c>
       <c r="O16" t="n">
-        <v>503.84</v>
+        <v>42.84</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.74</v>
+        <v>13.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>416</v>
+        <v>47.45</v>
       </c>
       <c r="R16" t="n">
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>50.8</v>
+        <v>49.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.78</v>
+        <v>-1.77</v>
       </c>
       <c r="V16" t="n">
-        <v>46.7</v>
+        <v>48.3</v>
       </c>
       <c r="W16" t="n">
-        <v>6.67</v>
+        <v>8.69</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>13634.58</v>
+        <v>1625.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>14126.3</v>
+        <v>1683.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>14161.39</v>
+        <v>1664.51</v>
       </c>
       <c r="AB16" t="n">
-        <v>13425</v>
+        <v>1580.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>14079.67</v>
+        <v>1641.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>14558.34</v>
+        <v>1671.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>15067.67</v>
+        <v>1692.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>64.7</v>
+        <v>86.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76)</t>
+          <t>Low VIX (11.76)</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>41.2</v>
+        <v>28.6</v>
       </c>
       <c r="AK16" t="n">
-        <v>21.1</v>
+        <v>17.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM16" t="n">
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>14626.35</v>
+        <v>1696.86</v>
       </c>
       <c r="AO16" t="n">
-        <v>13484.26</v>
+        <v>1606.63</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
+          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
+          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
+          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
         </is>
       </c>
     </row>
@@ -3224,13 +3224,13 @@
         <v>11.76</v>
       </c>
       <c r="S17" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
       <c r="T17" t="n">
         <v>0.15</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.88</v>
+        <v>-1.89</v>
       </c>
       <c r="V17" t="n">
         <v>53.3</v>
@@ -3245,7 +3245,7 @@
         <v>590.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>611.72</v>
+        <v>611.73</v>
       </c>
       <c r="AA17" t="n">
         <v>618.26</v>
@@ -3289,10 +3289,10 @@
         <v>6.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>643.89</v>
+        <v>646.59</v>
       </c>
       <c r="AO17" t="n">
-        <v>582.86</v>
+        <v>581.54</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -3391,13 +3391,13 @@
         <v>11.76</v>
       </c>
       <c r="S18" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="T18" t="n">
         <v>0.17</v>
       </c>
       <c r="U18" t="n">
-        <v>-2</v>
+        <v>-2.01</v>
       </c>
       <c r="V18" t="n">
         <v>51.7</v>
@@ -3456,10 +3456,10 @@
         <v>10</v>
       </c>
       <c r="AN18" t="n">
-        <v>2178.31</v>
+        <v>2178.06</v>
       </c>
       <c r="AO18" t="n">
-        <v>2030.62</v>
+        <v>2031.95</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3576,10 +3576,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1114.02</v>
+        <v>1114.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>1153.76</v>
+        <v>1153.79</v>
       </c>
       <c r="AA19" t="n">
         <v>1144.38</v>
@@ -3623,10 +3623,10 @@
         <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>1168.76</v>
+        <v>1170.05</v>
       </c>
       <c r="AO19" t="n">
-        <v>1101.06</v>
+        <v>1102.98</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3725,13 +3725,13 @@
         <v>11.76</v>
       </c>
       <c r="S20" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="T20" t="n">
         <v>0.16</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.2</v>
+        <v>-2.23</v>
       </c>
       <c r="V20" t="n">
         <v>50</v>
@@ -3790,10 +3790,10 @@
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>313.79</v>
+        <v>313.19</v>
       </c>
       <c r="AO20" t="n">
-        <v>291.94</v>
+        <v>291.63</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3892,13 +3892,13 @@
         <v>11.76</v>
       </c>
       <c r="S21" t="n">
-        <v>45.9</v>
+        <v>45.3</v>
       </c>
       <c r="T21" t="n">
         <v>0.15</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.43</v>
+        <v>-2.47</v>
       </c>
       <c r="V21" t="n">
         <v>48.3</v>
@@ -3910,10 +3910,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>1705.12</v>
+        <v>1705.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>1765.36</v>
+        <v>1765.39</v>
       </c>
       <c r="AA21" t="n">
         <v>1734.77</v>
@@ -3957,10 +3957,10 @@
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>1789.43</v>
+        <v>1786.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>1656.08</v>
+        <v>1655.68</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -3979,17 +3979,17 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
+          <t>[1721.0, 1730.97, 1740.93, 1750.9, 1760.86, 1770.83]</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.21, 1823.74]</t>
+          <t>[1721.0, 1754.7, 1774.49, 1792.0, 1808.32, 1823.89]</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
+          <t>[1721.0, 1713.17, 1715.76, 1720.07, 1725.26, 1731.03]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -719,13 +719,13 @@
         <v>11.76</v>
       </c>
       <c r="S2" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
       <c r="T2" t="n">
         <v>0.32</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="V2" t="n">
         <v>60</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76)</t>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI2" t="n">
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1463.1</v>
+        <v>1463.47</v>
       </c>
       <c r="AO2" t="n">
-        <v>1409.05</v>
+        <v>1408.82</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="T3" t="n">
         <v>0.39</v>
@@ -904,13 +904,13 @@
         <v>-0.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>7803.37</v>
+        <v>7803.14</v>
       </c>
       <c r="Z3" t="n">
         <v>8059.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>7920.87</v>
+        <v>7920.64</v>
       </c>
       <c r="AB3" t="n">
         <v>7607.65</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76)</t>
+          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI3" t="n">
@@ -951,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>8057.14</v>
+        <v>8042.82</v>
       </c>
       <c r="AO3" t="n">
-        <v>7648.5</v>
+        <v>7643.3</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -973,17 +973,17 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[7833.5, 7920.87, 8008.25, 8095.62, 8183.0, 8270.37]</t>
+          <t>[7833.5, 7920.64, 8007.78, 8094.92, 8182.07, 8269.21]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[7833.5, 7981.1, 8093.42, 8199.94, 8303.45, 8405.04]</t>
+          <t>[7833.5, 7980.87, 8092.96, 8199.24, 8302.52, 8403.88]</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>[7833.5, 7875.7, 7944.37, 8017.39, 8092.66, 8169.37]</t>
+          <t>[7833.5, 7875.47, 7943.9, 8016.69, 8091.73, 8168.2]</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76)</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI4" t="n">
@@ -1118,10 +1118,10 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>116.18</v>
+        <v>115.9</v>
       </c>
       <c r="AO4" t="n">
-        <v>109.62</v>
+        <v>109.77</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>11.76</v>
       </c>
       <c r="S5" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
       <c r="T5" t="n">
         <v>0.29</v>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76)</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI5" t="n">
@@ -1285,10 +1285,10 @@
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12177.9</v>
+        <v>12175.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>11645.22</v>
+        <v>11620.15</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>57.7</v>
+        <v>57.1</v>
       </c>
       <c r="T6" t="n">
         <v>0.25</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="V6" t="n">
         <v>55</v>
@@ -1405,10 +1405,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>2707.02</v>
+        <v>2707.04</v>
       </c>
       <c r="Z6" t="n">
-        <v>2803.18</v>
+        <v>2803.2</v>
       </c>
       <c r="AA6" t="n">
         <v>2769.28</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (11.76)</t>
+          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI6" t="n">
@@ -1452,10 +1452,10 @@
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>2816.91</v>
+        <v>2810.31</v>
       </c>
       <c r="AO6" t="n">
-        <v>2683.26</v>
+        <v>2684.26</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>11.76</v>
       </c>
       <c r="S7" t="n">
-        <v>55.5</v>
+        <v>55.7</v>
       </c>
       <c r="T7" t="n">
         <v>0.25</v>
@@ -1572,7 +1572,7 @@
         <v>-0.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>2184.76</v>
+        <v>2184.77</v>
       </c>
       <c r="Z7" t="n">
         <v>2261.76</v>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76)</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI7" t="n">
@@ -1619,10 +1619,10 @@
         <v>11.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>2264.99</v>
+        <v>2264.08</v>
       </c>
       <c r="AO7" t="n">
-        <v>2137.47</v>
+        <v>2141.36</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -1641,17 +1641,17 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2199.8, 2217.76, 2235.72, 2253.68, 2271.64, 2289.6]</t>
+          <t>[2199.8, 2217.76, 2235.73, 2253.69, 2271.66, 2289.62]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2199.8, 2236.84, 2262.71, 2286.73, 2309.8, 2332.27]</t>
+          <t>[2199.8, 2236.85, 2262.72, 2286.74, 2309.82, 2332.29]</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>[2199.8, 2203.45, 2215.48, 2228.89, 2243.01, 2257.59]</t>
+          <t>[2199.8, 2203.45, 2215.49, 2228.9, 2243.03, 2257.62]</t>
         </is>
       </c>
     </row>
@@ -1663,16 +1663,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>98206.09</v>
+        <v>105127.58</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,145 +1680,145 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>372.95</v>
+        <v>738.55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹371.41 - ₹375.26</t>
+          <t>₹735.6 - ₹742.98</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>379.11</v>
+        <v>750.37</v>
       </c>
       <c r="I8" t="n">
-        <v>432</v>
+        <v>225</v>
       </c>
       <c r="J8" t="n">
-        <v>357.21</v>
+        <v>729.51</v>
       </c>
       <c r="K8" t="n">
-        <v>349.78</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>347.56</v>
+        <v>686.09</v>
       </c>
       <c r="M8" t="n">
-        <v>6.64</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>4.07</v>
+        <v>8.49</v>
       </c>
       <c r="O8" t="n">
-        <v>2.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>-0.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.7</v>
+        <v>14.77</v>
       </c>
       <c r="R8" t="n">
         <v>11.76</v>
       </c>
       <c r="S8" t="n">
-        <v>53</v>
+        <v>51.8</v>
       </c>
       <c r="T8" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="U8" t="n">
         <v>-1.03</v>
       </c>
       <c r="V8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="W8" t="n">
-        <v>2.81</v>
+        <v>5.75</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>366.16</v>
+        <v>720.8200000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>379.22</v>
+        <v>725.27</v>
       </c>
       <c r="AA8" t="n">
-        <v>375.93</v>
+        <v>744.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>361.4</v>
+        <v>716.39</v>
       </c>
       <c r="AC8" t="n">
-        <v>372.32</v>
+        <v>744.27</v>
       </c>
       <c r="AD8" t="n">
-        <v>374.64</v>
+        <v>751.6900000000001</v>
       </c>
       <c r="AE8" t="n">
-        <v>376.32</v>
+        <v>764.8200000000001</v>
       </c>
       <c r="AF8" t="n">
-        <v>78.3</v>
+        <v>48.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Low VIX (11.76)</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI8" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6.1</v>
+        <v>49</v>
       </c>
       <c r="AK8" t="n">
-        <v>25.2</v>
+        <v>15.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>68.90000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="AM8" t="n">
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>382.62</v>
+        <v>757.39</v>
       </c>
       <c r="AO8" t="n">
-        <v>363.2</v>
+        <v>720.78</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
+          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
+          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
+          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
         </is>
       </c>
     </row>
@@ -1830,16 +1830,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>105127.58</v>
+        <v>25000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,145 +1847,145 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>738.55</v>
+        <v>372.95</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹735.6 - ₹742.98</t>
+          <t>₹371.41 - ₹375.26</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>750.37</v>
+        <v>379.11</v>
       </c>
       <c r="I9" t="n">
-        <v>225</v>
+        <v>432</v>
       </c>
       <c r="J9" t="n">
-        <v>729.51</v>
+        <v>357.21</v>
       </c>
       <c r="K9" t="n">
-        <v>703.6799999999999</v>
+        <v>349.78</v>
       </c>
       <c r="L9" t="n">
-        <v>686.09</v>
+        <v>347.56</v>
       </c>
       <c r="M9" t="n">
-        <v>9.210000000000001</v>
+        <v>6.64</v>
       </c>
       <c r="N9" t="n">
-        <v>8.49</v>
+        <v>4.07</v>
       </c>
       <c r="O9" t="n">
-        <v>9.380000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.77</v>
+        <v>7.7</v>
       </c>
       <c r="R9" t="n">
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>51.5</v>
+        <v>52.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="U9" t="n">
         <v>-1.04</v>
       </c>
       <c r="V9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="W9" t="n">
-        <v>5.74</v>
+        <v>2.81</v>
       </c>
       <c r="X9" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>720.8200000000001</v>
+        <v>366.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>725.26</v>
+        <v>379.22</v>
       </c>
       <c r="AA9" t="n">
-        <v>744.46</v>
+        <v>375.93</v>
       </c>
       <c r="AB9" t="n">
-        <v>716.39</v>
+        <v>361.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>744.27</v>
+        <v>372.32</v>
       </c>
       <c r="AD9" t="n">
-        <v>751.6900000000001</v>
+        <v>374.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>764.8200000000001</v>
+        <v>376.32</v>
       </c>
       <c r="AF9" t="n">
-        <v>48.2</v>
+        <v>78.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76)</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI9" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>49</v>
+        <v>6.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>15.1</v>
+        <v>25.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>20.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AM9" t="n">
         <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>757.85</v>
+        <v>382.71</v>
       </c>
       <c r="AO9" t="n">
-        <v>720.36</v>
+        <v>363.7</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
+          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
+          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
+          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
         </is>
       </c>
     </row>
@@ -2055,13 +2055,13 @@
         <v>11.76</v>
       </c>
       <c r="S10" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="T10" t="n">
         <v>0.3</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.07</v>
+        <v>-1.08</v>
       </c>
       <c r="V10" t="n">
         <v>41.7</v>
@@ -2073,10 +2073,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>4548.62</v>
+        <v>4548.64</v>
       </c>
       <c r="Z10" t="n">
-        <v>4711.24</v>
+        <v>4711.27</v>
       </c>
       <c r="AA10" t="n">
         <v>4683.67</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76)</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI10" t="n">
@@ -2120,10 +2120,10 @@
         <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>4769.63</v>
+        <v>4766.05</v>
       </c>
       <c r="AO10" t="n">
-        <v>4515.61</v>
+        <v>4517.83</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2222,19 +2222,19 @@
         <v>11.76</v>
       </c>
       <c r="S11" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
       <c r="T11" t="n">
         <v>0.25</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.12</v>
+        <v>-1.14</v>
       </c>
       <c r="V11" t="n">
         <v>53.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="X11" t="n">
         <v>-0.77</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76)</t>
+          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI11" t="n">
@@ -2287,10 +2287,10 @@
         <v>17.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>5880.76</v>
+        <v>5884.47</v>
       </c>
       <c r="AO11" t="n">
-        <v>5625.04</v>
+        <v>5620.69</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2389,13 +2389,13 @@
         <v>11.76</v>
       </c>
       <c r="S12" t="n">
-        <v>56.6</v>
+        <v>56</v>
       </c>
       <c r="T12" t="n">
         <v>0.21</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.23</v>
+        <v>-1.26</v>
       </c>
       <c r="V12" t="n">
         <v>53.3</v>
@@ -2407,10 +2407,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>3684.03</v>
+        <v>3683.99</v>
       </c>
       <c r="Z12" t="n">
-        <v>3815.63</v>
+        <v>3815.59</v>
       </c>
       <c r="AA12" t="n">
         <v>3790.08</v>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76)</t>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI12" t="n">
@@ -2454,10 +2454,10 @@
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>3866.75</v>
+        <v>3871.66</v>
       </c>
       <c r="AO12" t="n">
-        <v>3645.21</v>
+        <v>3648.3</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2556,13 +2556,13 @@
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="T13" t="n">
         <v>0.23</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.28</v>
+        <v>-1.27</v>
       </c>
       <c r="V13" t="n">
         <v>45</v>
@@ -2577,7 +2577,7 @@
         <v>1431.86</v>
       </c>
       <c r="Z13" t="n">
-        <v>1388.25</v>
+        <v>1388.21</v>
       </c>
       <c r="AA13" t="n">
         <v>1484.99</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76)</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI13" t="n">
@@ -2621,10 +2621,10 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>1504.41</v>
+        <v>1506.89</v>
       </c>
       <c r="AO13" t="n">
-        <v>1443.16</v>
+        <v>1441.95</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2723,13 +2723,13 @@
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>56</v>
+        <v>56.4</v>
       </c>
       <c r="T14" t="n">
         <v>0.18</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.54</v>
+        <v>-1.52</v>
       </c>
       <c r="V14" t="n">
         <v>55</v>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76)</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI14" t="n">
@@ -2788,10 +2788,10 @@
         <v>18.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>1086.01</v>
+        <v>1087.61</v>
       </c>
       <c r="AO14" t="n">
-        <v>1011.5</v>
+        <v>1010.99</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2890,13 +2890,13 @@
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="T15" t="n">
         <v>0.18</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.76</v>
+        <v>-1.77</v>
       </c>
       <c r="V15" t="n">
         <v>46.7</v>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76)</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
@@ -2955,10 +2955,10 @@
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>14572.92</v>
+        <v>14591.79</v>
       </c>
       <c r="AO15" t="n">
-        <v>13548.3</v>
+        <v>13479.71</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -3057,13 +3057,13 @@
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="T16" t="n">
         <v>0.19</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.77</v>
+        <v>-1.78</v>
       </c>
       <c r="V16" t="n">
         <v>48.3</v>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Low VIX (11.76)</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
@@ -3122,10 +3122,10 @@
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>1696.86</v>
+        <v>1697.55</v>
       </c>
       <c r="AO16" t="n">
-        <v>1606.63</v>
+        <v>1608.28</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>590.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>611.73</v>
+        <v>611.72</v>
       </c>
       <c r="AA17" t="n">
         <v>618.26</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76)</t>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI17" t="n">
@@ -3289,10 +3289,10 @@
         <v>6.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>646.59</v>
+        <v>643.3200000000001</v>
       </c>
       <c r="AO17" t="n">
-        <v>581.54</v>
+        <v>582.9400000000001</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -3391,13 +3391,13 @@
         <v>11.76</v>
       </c>
       <c r="S18" t="n">
-        <v>48.4</v>
+        <v>47.9</v>
       </c>
       <c r="T18" t="n">
         <v>0.17</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.01</v>
+        <v>-2.04</v>
       </c>
       <c r="V18" t="n">
         <v>51.7</v>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76)</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI18" t="n">
@@ -3456,10 +3456,10 @@
         <v>10</v>
       </c>
       <c r="AN18" t="n">
-        <v>2178.06</v>
+        <v>2180.45</v>
       </c>
       <c r="AO18" t="n">
-        <v>2031.95</v>
+        <v>2028.26</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3558,13 +3558,13 @@
         <v>11.76</v>
       </c>
       <c r="S19" t="n">
-        <v>44.5</v>
+        <v>44.9</v>
       </c>
       <c r="T19" t="n">
         <v>0.18</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.18</v>
+        <v>-2.16</v>
       </c>
       <c r="V19" t="n">
         <v>46.7</v>
@@ -3576,10 +3576,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1114.05</v>
+        <v>1113.98</v>
       </c>
       <c r="Z19" t="n">
-        <v>1153.79</v>
+        <v>1153.71</v>
       </c>
       <c r="AA19" t="n">
         <v>1144.38</v>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76)</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI19" t="n">
@@ -3623,10 +3623,10 @@
         <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>1170.05</v>
+        <v>1169.2</v>
       </c>
       <c r="AO19" t="n">
-        <v>1102.98</v>
+        <v>1104.97</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3725,13 +3725,13 @@
         <v>11.76</v>
       </c>
       <c r="S20" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="T20" t="n">
         <v>0.16</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.23</v>
+        <v>-2.25</v>
       </c>
       <c r="V20" t="n">
         <v>50</v>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76)</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI20" t="n">
@@ -3790,10 +3790,10 @@
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>313.19</v>
+        <v>313.63</v>
       </c>
       <c r="AO20" t="n">
-        <v>291.63</v>
+        <v>291.75</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3892,13 +3892,13 @@
         <v>11.76</v>
       </c>
       <c r="S21" t="n">
-        <v>45.3</v>
+        <v>45.7</v>
       </c>
       <c r="T21" t="n">
         <v>0.15</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.47</v>
+        <v>-2.44</v>
       </c>
       <c r="V21" t="n">
         <v>48.3</v>
@@ -3910,10 +3910,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>1705.15</v>
+        <v>1705.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>1765.39</v>
+        <v>1765.36</v>
       </c>
       <c r="AA21" t="n">
         <v>1734.77</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76)</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI21" t="n">
@@ -3957,10 +3957,10 @@
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>1786.25</v>
+        <v>1785.58</v>
       </c>
       <c r="AO21" t="n">
-        <v>1655.68</v>
+        <v>1658.16</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -3979,17 +3979,17 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>[1721.0, 1730.97, 1740.93, 1750.9, 1760.86, 1770.83]</t>
+          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[1721.0, 1754.7, 1774.49, 1792.0, 1808.32, 1823.89]</t>
+          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.21, 1823.74]</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>[1721.0, 1713.17, 1715.76, 1720.07, 1725.26, 1731.03]</t>
+          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -719,13 +719,13 @@
         <v>11.76</v>
       </c>
       <c r="S2" t="n">
-        <v>61.8</v>
+        <v>61.5</v>
       </c>
       <c r="T2" t="n">
         <v>0.32</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
       <c r="V2" t="n">
         <v>60</v>
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1463.47</v>
+        <v>1463.97</v>
       </c>
       <c r="AO2" t="n">
-        <v>1408.82</v>
+        <v>1409.74</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
       <c r="T3" t="n">
         <v>0.39</v>
@@ -904,13 +904,13 @@
         <v>-0.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>7803.14</v>
+        <v>7803.37</v>
       </c>
       <c r="Z3" t="n">
         <v>8059.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>7920.64</v>
+        <v>7920.87</v>
       </c>
       <c r="AB3" t="n">
         <v>7607.65</v>
@@ -951,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>8042.82</v>
+        <v>8061.63</v>
       </c>
       <c r="AO3" t="n">
-        <v>7643.3</v>
+        <v>7640.14</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -973,17 +973,17 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[7833.5, 7920.64, 8007.78, 8094.92, 8182.07, 8269.21]</t>
+          <t>[7833.5, 7920.87, 8008.25, 8095.62, 8183.0, 8270.37]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[7833.5, 7980.87, 8092.96, 8199.24, 8302.52, 8403.88]</t>
+          <t>[7833.5, 7981.1, 8093.42, 8199.94, 8303.45, 8405.04]</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>[7833.5, 7875.47, 7943.9, 8016.69, 8091.73, 8168.2]</t>
+          <t>[7833.5, 7875.7, 7944.37, 8017.39, 8092.66, 8169.37]</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
         <v>11.76</v>
       </c>
       <c r="S4" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="T4" t="n">
         <v>0.29</v>
@@ -1118,10 +1118,10 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>115.9</v>
+        <v>115.88</v>
       </c>
       <c r="AO4" t="n">
-        <v>109.77</v>
+        <v>109.57</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>11.76</v>
       </c>
       <c r="S5" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="T5" t="n">
         <v>0.29</v>
@@ -1238,10 +1238,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>11732.12</v>
+        <v>11731.98</v>
       </c>
       <c r="Z5" t="n">
-        <v>12148.72</v>
+        <v>12148.58</v>
       </c>
       <c r="AA5" t="n">
         <v>11998.22</v>
@@ -1285,10 +1285,10 @@
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12175.8</v>
+        <v>12182.37</v>
       </c>
       <c r="AO5" t="n">
-        <v>11620.15</v>
+        <v>11626.21</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>57.1</v>
+        <v>57.9</v>
       </c>
       <c r="T6" t="n">
         <v>0.25</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9</v>
+        <v>-0.87</v>
       </c>
       <c r="V6" t="n">
         <v>55</v>
@@ -1405,10 +1405,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>2707.04</v>
+        <v>2707.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2803.2</v>
+        <v>2803.25</v>
       </c>
       <c r="AA6" t="n">
         <v>2769.28</v>
@@ -1452,10 +1452,10 @@
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>2810.31</v>
+        <v>2813.86</v>
       </c>
       <c r="AO6" t="n">
-        <v>2684.26</v>
+        <v>2683.28</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>-0.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>2184.77</v>
+        <v>2184.76</v>
       </c>
       <c r="Z7" t="n">
         <v>2261.76</v>
@@ -1619,10 +1619,10 @@
         <v>11.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>2264.08</v>
+        <v>2268.44</v>
       </c>
       <c r="AO7" t="n">
-        <v>2141.36</v>
+        <v>2141.15</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -1641,17 +1641,17 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2199.8, 2217.76, 2235.73, 2253.69, 2271.66, 2289.62]</t>
+          <t>[2199.8, 2217.76, 2235.72, 2253.68, 2271.64, 2289.6]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2199.8, 2236.85, 2262.72, 2286.74, 2309.82, 2332.29]</t>
+          <t>[2199.8, 2236.84, 2262.71, 2286.73, 2309.8, 2332.27]</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>[2199.8, 2203.45, 2215.49, 2228.9, 2243.03, 2257.62]</t>
+          <t>[2199.8, 2203.45, 2215.48, 2228.89, 2243.01, 2257.59]</t>
         </is>
       </c>
     </row>
@@ -1721,19 +1721,19 @@
         <v>11.76</v>
       </c>
       <c r="S8" t="n">
-        <v>51.8</v>
+        <v>52.1</v>
       </c>
       <c r="T8" t="n">
         <v>0.27</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.03</v>
+        <v>-1.02</v>
       </c>
       <c r="V8" t="n">
         <v>55</v>
       </c>
       <c r="W8" t="n">
-        <v>5.75</v>
+        <v>5.74</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
@@ -1742,7 +1742,7 @@
         <v>720.8200000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>725.27</v>
+        <v>725.26</v>
       </c>
       <c r="AA8" t="n">
         <v>744.46</v>
@@ -1786,10 +1786,10 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>757.39</v>
+        <v>757.77</v>
       </c>
       <c r="AO8" t="n">
-        <v>720.78</v>
+        <v>720.14</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25000</v>
+        <v>98206.09</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="T9" t="n">
         <v>0.26</v>
@@ -1953,14 +1953,14 @@
         <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>382.71</v>
+        <v>382.86</v>
       </c>
       <c r="AO9" t="n">
-        <v>363.7</v>
+        <v>363.5</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2055,13 +2055,13 @@
         <v>11.76</v>
       </c>
       <c r="S10" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="T10" t="n">
         <v>0.3</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.08</v>
+        <v>-1.06</v>
       </c>
       <c r="V10" t="n">
         <v>41.7</v>
@@ -2073,10 +2073,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>4548.64</v>
+        <v>4548.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>4711.27</v>
+        <v>4711.2</v>
       </c>
       <c r="AA10" t="n">
         <v>4683.67</v>
@@ -2120,10 +2120,10 @@
         <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>4766.05</v>
+        <v>4770.98</v>
       </c>
       <c r="AO10" t="n">
-        <v>4517.83</v>
+        <v>4523.28</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2222,19 +2222,19 @@
         <v>11.76</v>
       </c>
       <c r="S11" t="n">
-        <v>51.4</v>
+        <v>52</v>
       </c>
       <c r="T11" t="n">
         <v>0.25</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.14</v>
+        <v>-1.12</v>
       </c>
       <c r="V11" t="n">
         <v>53.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="X11" t="n">
         <v>-0.77</v>
@@ -2287,10 +2287,10 @@
         <v>17.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>5884.47</v>
+        <v>5875.25</v>
       </c>
       <c r="AO11" t="n">
-        <v>5620.69</v>
+        <v>5631.46</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2389,13 +2389,13 @@
         <v>11.76</v>
       </c>
       <c r="S12" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="T12" t="n">
         <v>0.21</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.26</v>
+        <v>-1.25</v>
       </c>
       <c r="V12" t="n">
         <v>53.3</v>
@@ -2454,10 +2454,10 @@
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>3871.66</v>
+        <v>3873.35</v>
       </c>
       <c r="AO12" t="n">
-        <v>3648.3</v>
+        <v>3649.96</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2556,13 +2556,13 @@
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="T13" t="n">
         <v>0.23</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.27</v>
+        <v>-1.28</v>
       </c>
       <c r="V13" t="n">
         <v>45</v>
@@ -2577,7 +2577,7 @@
         <v>1431.86</v>
       </c>
       <c r="Z13" t="n">
-        <v>1388.21</v>
+        <v>1388.25</v>
       </c>
       <c r="AA13" t="n">
         <v>1484.99</v>
@@ -2621,10 +2621,10 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>1506.89</v>
+        <v>1504.35</v>
       </c>
       <c r="AO13" t="n">
-        <v>1441.95</v>
+        <v>1441.16</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
       <c r="T14" t="n">
         <v>0.18</v>
@@ -2741,10 +2741,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>1019.35</v>
+        <v>1019.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>1055.98</v>
+        <v>1056.01</v>
       </c>
       <c r="AA14" t="n">
         <v>1055.07</v>
@@ -2788,10 +2788,10 @@
         <v>18.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>1087.61</v>
+        <v>1084.67</v>
       </c>
       <c r="AO14" t="n">
-        <v>1010.99</v>
+        <v>1009.83</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85420.58</v>
+        <v>146280.27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2849,145 +2849,145 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14049</v>
+        <v>1651.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹13965.8 - ₹14173.8</t>
+          <t>₹1641.81 - ₹1665.54</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14381.8</v>
+        <v>1689.26</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="J15" t="n">
-        <v>13190.57</v>
+        <v>1478.49</v>
       </c>
       <c r="K15" t="n">
-        <v>12605.68</v>
+        <v>1460.44</v>
       </c>
       <c r="L15" t="n">
-        <v>12333.95</v>
+        <v>1458.79</v>
       </c>
       <c r="M15" t="n">
-        <v>16.25</v>
+        <v>14.41</v>
       </c>
       <c r="N15" t="n">
-        <v>477.1</v>
+        <v>56.22</v>
       </c>
       <c r="O15" t="n">
-        <v>503.84</v>
+        <v>42.84</v>
       </c>
       <c r="P15" t="n">
-        <v>-26.74</v>
+        <v>13.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>416</v>
+        <v>47.45</v>
       </c>
       <c r="R15" t="n">
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>50.9</v>
+        <v>49.9</v>
       </c>
       <c r="T15" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.77</v>
+        <v>-1.76</v>
       </c>
       <c r="V15" t="n">
-        <v>46.7</v>
+        <v>48.3</v>
       </c>
       <c r="W15" t="n">
-        <v>6.67</v>
+        <v>8.69</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>13634.58</v>
+        <v>1625.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>14126.3</v>
+        <v>1683.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>14161.39</v>
+        <v>1664.51</v>
       </c>
       <c r="AB15" t="n">
-        <v>13425</v>
+        <v>1580.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>14079.67</v>
+        <v>1641.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>14558.34</v>
+        <v>1671.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>15067.67</v>
+        <v>1692.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>64.7</v>
+        <v>86.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>41.2</v>
+        <v>28.6</v>
       </c>
       <c r="AK15" t="n">
-        <v>21.1</v>
+        <v>17.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM15" t="n">
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>14591.79</v>
+        <v>1698.14</v>
       </c>
       <c r="AO15" t="n">
-        <v>13479.71</v>
+        <v>1608.41</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
+          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
+          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
+          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>146280.27</v>
+        <v>85420.58</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3016,145 +3016,145 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1651.3</v>
+        <v>14049</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹1641.81 - ₹1665.54</t>
+          <t>₹13965.8 - ₹14173.8</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1689.26</v>
+        <v>14381.8</v>
       </c>
       <c r="I16" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>1478.49</v>
+        <v>13190.57</v>
       </c>
       <c r="K16" t="n">
-        <v>1460.44</v>
+        <v>12605.68</v>
       </c>
       <c r="L16" t="n">
-        <v>1458.79</v>
+        <v>12333.95</v>
       </c>
       <c r="M16" t="n">
-        <v>14.41</v>
+        <v>16.25</v>
       </c>
       <c r="N16" t="n">
-        <v>56.22</v>
+        <v>477.1</v>
       </c>
       <c r="O16" t="n">
-        <v>42.84</v>
+        <v>503.84</v>
       </c>
       <c r="P16" t="n">
-        <v>13.38</v>
+        <v>-26.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.45</v>
+        <v>416</v>
       </c>
       <c r="R16" t="n">
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>49.6</v>
+        <v>50.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.78</v>
+        <v>-1.79</v>
       </c>
       <c r="V16" t="n">
-        <v>48.3</v>
+        <v>46.7</v>
       </c>
       <c r="W16" t="n">
-        <v>8.69</v>
+        <v>6.67</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>1625.39</v>
+        <v>13634.81</v>
       </c>
       <c r="Z16" t="n">
-        <v>1683.18</v>
+        <v>14126.52</v>
       </c>
       <c r="AA16" t="n">
-        <v>1664.51</v>
+        <v>14161.39</v>
       </c>
       <c r="AB16" t="n">
-        <v>1580.13</v>
+        <v>13425</v>
       </c>
       <c r="AC16" t="n">
-        <v>1641.1</v>
+        <v>14079.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>1671.7</v>
+        <v>14558.34</v>
       </c>
       <c r="AE16" t="n">
-        <v>1692.1</v>
+        <v>15067.67</v>
       </c>
       <c r="AF16" t="n">
-        <v>86.2</v>
+        <v>64.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28.6</v>
+        <v>41.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>17.7</v>
+        <v>21.1</v>
       </c>
       <c r="AL16" t="n">
-        <v>8.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AM16" t="n">
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>1697.55</v>
+        <v>14604.59</v>
       </c>
       <c r="AO16" t="n">
-        <v>1608.28</v>
+        <v>13490.97</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
+          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
+          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
+          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
         </is>
       </c>
     </row>
@@ -3224,13 +3224,13 @@
         <v>11.76</v>
       </c>
       <c r="S17" t="n">
-        <v>57.1</v>
+        <v>57.4</v>
       </c>
       <c r="T17" t="n">
         <v>0.15</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.89</v>
+        <v>-1.87</v>
       </c>
       <c r="V17" t="n">
         <v>53.3</v>
@@ -3289,10 +3289,10 @@
         <v>6.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>643.3200000000001</v>
+        <v>643.62</v>
       </c>
       <c r="AO17" t="n">
-        <v>582.9400000000001</v>
+        <v>583.84</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -3391,13 +3391,13 @@
         <v>11.76</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>49</v>
       </c>
       <c r="T18" t="n">
         <v>0.17</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.04</v>
+        <v>-1.98</v>
       </c>
       <c r="V18" t="n">
         <v>51.7</v>
@@ -3456,10 +3456,10 @@
         <v>10</v>
       </c>
       <c r="AN18" t="n">
-        <v>2180.45</v>
+        <v>2182.37</v>
       </c>
       <c r="AO18" t="n">
-        <v>2028.26</v>
+        <v>2033.12</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3558,13 +3558,13 @@
         <v>11.76</v>
       </c>
       <c r="S19" t="n">
-        <v>44.9</v>
+        <v>44.3</v>
       </c>
       <c r="T19" t="n">
         <v>0.18</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.16</v>
+        <v>-2.19</v>
       </c>
       <c r="V19" t="n">
         <v>46.7</v>
@@ -3576,10 +3576,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1113.98</v>
+        <v>1114.03</v>
       </c>
       <c r="Z19" t="n">
-        <v>1153.71</v>
+        <v>1153.77</v>
       </c>
       <c r="AA19" t="n">
         <v>1144.38</v>
@@ -3623,10 +3623,10 @@
         <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>1169.2</v>
+        <v>1168.55</v>
       </c>
       <c r="AO19" t="n">
-        <v>1104.97</v>
+        <v>1100.62</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3725,13 +3725,13 @@
         <v>11.76</v>
       </c>
       <c r="S20" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="T20" t="n">
         <v>0.16</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.25</v>
+        <v>-2.23</v>
       </c>
       <c r="V20" t="n">
         <v>50</v>
@@ -3790,10 +3790,10 @@
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>313.63</v>
+        <v>313.35</v>
       </c>
       <c r="AO20" t="n">
-        <v>291.75</v>
+        <v>291.86</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3892,13 +3892,13 @@
         <v>11.76</v>
       </c>
       <c r="S21" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
       <c r="T21" t="n">
         <v>0.15</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.44</v>
+        <v>-2.41</v>
       </c>
       <c r="V21" t="n">
         <v>48.3</v>
@@ -3957,10 +3957,10 @@
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>1785.58</v>
+        <v>1790.43</v>
       </c>
       <c r="AO21" t="n">
-        <v>1658.16</v>
+        <v>1655.98</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.21, 1823.74]</t>
+          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.2, 1823.74]</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1463.97</v>
+        <v>1461.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>1409.74</v>
+        <v>1407.88</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -886,13 +886,13 @@
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>55.9</v>
+        <v>55.7</v>
       </c>
       <c r="T3" t="n">
         <v>0.39</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="V3" t="n">
         <v>48.3</v>
@@ -951,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>8061.63</v>
+        <v>8045.56</v>
       </c>
       <c r="AO3" t="n">
-        <v>7640.14</v>
+        <v>7627.74</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1053,13 +1053,13 @@
         <v>11.76</v>
       </c>
       <c r="S4" t="n">
-        <v>58.7</v>
+        <v>58.4</v>
       </c>
       <c r="T4" t="n">
         <v>0.29</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.67</v>
+        <v>-0.68</v>
       </c>
       <c r="V4" t="n">
         <v>51.7</v>
@@ -1118,10 +1118,10 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>115.88</v>
+        <v>115.75</v>
       </c>
       <c r="AO4" t="n">
-        <v>109.57</v>
+        <v>109.83</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>11.76</v>
       </c>
       <c r="S5" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="T5" t="n">
         <v>0.29</v>
@@ -1285,10 +1285,10 @@
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12182.37</v>
+        <v>12158.36</v>
       </c>
       <c r="AO5" t="n">
-        <v>11626.21</v>
+        <v>11626.15</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
       <c r="T6" t="n">
         <v>0.25</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.87</v>
+        <v>-0.88</v>
       </c>
       <c r="V6" t="n">
         <v>55</v>
@@ -1405,10 +1405,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>2707.09</v>
+        <v>2707.04</v>
       </c>
       <c r="Z6" t="n">
-        <v>2803.25</v>
+        <v>2803.2</v>
       </c>
       <c r="AA6" t="n">
         <v>2769.28</v>
@@ -1452,10 +1452,10 @@
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>2813.86</v>
+        <v>2813.46</v>
       </c>
       <c r="AO6" t="n">
-        <v>2683.28</v>
+        <v>2683.65</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1554,13 +1554,13 @@
         <v>11.76</v>
       </c>
       <c r="S7" t="n">
-        <v>55.7</v>
+        <v>56.1</v>
       </c>
       <c r="T7" t="n">
         <v>0.25</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.99</v>
+        <v>-0.97</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -1619,10 +1619,10 @@
         <v>11.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>2268.44</v>
+        <v>2267.91</v>
       </c>
       <c r="AO7" t="n">
-        <v>2141.15</v>
+        <v>2141.66</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>11.76</v>
       </c>
       <c r="S8" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="T8" t="n">
         <v>0.27</v>
@@ -1733,7 +1733,7 @@
         <v>55</v>
       </c>
       <c r="W8" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
@@ -1742,7 +1742,7 @@
         <v>720.8200000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>725.26</v>
+        <v>725.27</v>
       </c>
       <c r="AA8" t="n">
         <v>744.46</v>
@@ -1786,10 +1786,10 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>757.77</v>
+        <v>756.16</v>
       </c>
       <c r="AO8" t="n">
-        <v>720.14</v>
+        <v>720.1900000000001</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>52.7</v>
+        <v>52.9</v>
       </c>
       <c r="T9" t="n">
         <v>0.26</v>
@@ -1953,10 +1953,10 @@
         <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>382.86</v>
+        <v>382.62</v>
       </c>
       <c r="AO9" t="n">
-        <v>363.5</v>
+        <v>362.41</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -2055,13 +2055,13 @@
         <v>11.76</v>
       </c>
       <c r="S10" t="n">
-        <v>46.7</v>
+        <v>47.1</v>
       </c>
       <c r="T10" t="n">
         <v>0.3</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.06</v>
+        <v>-1.04</v>
       </c>
       <c r="V10" t="n">
         <v>41.7</v>
@@ -2120,10 +2120,10 @@
         <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>4770.98</v>
+        <v>4769.22</v>
       </c>
       <c r="AO10" t="n">
-        <v>4523.28</v>
+        <v>4523.4</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2222,13 +2222,13 @@
         <v>11.76</v>
       </c>
       <c r="S11" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="T11" t="n">
         <v>0.25</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.12</v>
+        <v>-1.13</v>
       </c>
       <c r="V11" t="n">
         <v>53.3</v>
@@ -2287,10 +2287,10 @@
         <v>17.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>5875.25</v>
+        <v>5880.41</v>
       </c>
       <c r="AO11" t="n">
-        <v>5631.46</v>
+        <v>5626</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2389,13 +2389,13 @@
         <v>11.76</v>
       </c>
       <c r="S12" t="n">
-        <v>56.1</v>
+        <v>55.9</v>
       </c>
       <c r="T12" t="n">
         <v>0.21</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.25</v>
+        <v>-1.26</v>
       </c>
       <c r="V12" t="n">
         <v>53.3</v>
@@ -2407,10 +2407,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>3683.99</v>
+        <v>3684.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>3815.59</v>
+        <v>3815.63</v>
       </c>
       <c r="AA12" t="n">
         <v>3790.08</v>
@@ -2454,10 +2454,10 @@
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>3873.35</v>
+        <v>3870.75</v>
       </c>
       <c r="AO12" t="n">
-        <v>3649.96</v>
+        <v>3639.78</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2556,13 +2556,13 @@
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>51.8</v>
+        <v>52</v>
       </c>
       <c r="T13" t="n">
         <v>0.23</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.28</v>
+        <v>-1.27</v>
       </c>
       <c r="V13" t="n">
         <v>45</v>
@@ -2621,10 +2621,10 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>1504.35</v>
+        <v>1504.69</v>
       </c>
       <c r="AO13" t="n">
-        <v>1441.16</v>
+        <v>1442.77</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>56.5</v>
+        <v>56.4</v>
       </c>
       <c r="T14" t="n">
         <v>0.18</v>
@@ -2741,10 +2741,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>1019.37</v>
+        <v>1019.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>1056.01</v>
+        <v>1055.98</v>
       </c>
       <c r="AA14" t="n">
         <v>1055.07</v>
@@ -2788,10 +2788,10 @@
         <v>18.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>1084.67</v>
+        <v>1084.1</v>
       </c>
       <c r="AO14" t="n">
-        <v>1009.83</v>
+        <v>1009.87</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>146280.27</v>
+        <v>85420.58</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2849,145 +2849,145 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1651.3</v>
+        <v>14049</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹1641.81 - ₹1665.54</t>
+          <t>₹13965.8 - ₹14173.8</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1689.26</v>
+        <v>14381.8</v>
       </c>
       <c r="I15" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>1478.49</v>
+        <v>13190.57</v>
       </c>
       <c r="K15" t="n">
-        <v>1460.44</v>
+        <v>12605.68</v>
       </c>
       <c r="L15" t="n">
-        <v>1458.79</v>
+        <v>12333.95</v>
       </c>
       <c r="M15" t="n">
-        <v>14.41</v>
+        <v>16.25</v>
       </c>
       <c r="N15" t="n">
-        <v>56.22</v>
+        <v>477.1</v>
       </c>
       <c r="O15" t="n">
-        <v>42.84</v>
+        <v>503.84</v>
       </c>
       <c r="P15" t="n">
-        <v>13.38</v>
+        <v>-26.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>47.45</v>
+        <v>416</v>
       </c>
       <c r="R15" t="n">
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>49.9</v>
+        <v>51.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="U15" t="n">
         <v>-1.76</v>
       </c>
       <c r="V15" t="n">
-        <v>48.3</v>
+        <v>46.7</v>
       </c>
       <c r="W15" t="n">
-        <v>8.69</v>
+        <v>6.67</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>1625.35</v>
+        <v>13634.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>1683.14</v>
+        <v>14126.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1664.51</v>
+        <v>14161.39</v>
       </c>
       <c r="AB15" t="n">
-        <v>1580.13</v>
+        <v>13425</v>
       </c>
       <c r="AC15" t="n">
-        <v>1641.1</v>
+        <v>14079.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1671.7</v>
+        <v>14558.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>1692.1</v>
+        <v>15067.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>86.2</v>
+        <v>64.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>28.6</v>
+        <v>41.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>17.7</v>
+        <v>21.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>8.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AM15" t="n">
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>1698.14</v>
+        <v>14605.78</v>
       </c>
       <c r="AO15" t="n">
-        <v>1608.41</v>
+        <v>13527.81</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
+          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
+          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
+          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>85420.58</v>
+        <v>146280.27</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3016,145 +3016,145 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>14049</v>
+        <v>1651.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹13965.8 - ₹14173.8</t>
+          <t>₹1641.81 - ₹1665.54</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14381.8</v>
+        <v>1689.26</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="J16" t="n">
-        <v>13190.57</v>
+        <v>1478.49</v>
       </c>
       <c r="K16" t="n">
-        <v>12605.68</v>
+        <v>1460.44</v>
       </c>
       <c r="L16" t="n">
-        <v>12333.95</v>
+        <v>1458.79</v>
       </c>
       <c r="M16" t="n">
-        <v>16.25</v>
+        <v>14.41</v>
       </c>
       <c r="N16" t="n">
-        <v>477.1</v>
+        <v>56.22</v>
       </c>
       <c r="O16" t="n">
-        <v>503.84</v>
+        <v>42.84</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.74</v>
+        <v>13.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>416</v>
+        <v>47.45</v>
       </c>
       <c r="R16" t="n">
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>50.5</v>
+        <v>49.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.79</v>
+        <v>-1.78</v>
       </c>
       <c r="V16" t="n">
-        <v>46.7</v>
+        <v>48.3</v>
       </c>
       <c r="W16" t="n">
-        <v>6.67</v>
+        <v>8.69</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>13634.81</v>
+        <v>1625.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>14126.52</v>
+        <v>1683.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>14161.39</v>
+        <v>1664.51</v>
       </c>
       <c r="AB16" t="n">
-        <v>13425</v>
+        <v>1580.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>14079.67</v>
+        <v>1641.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>14558.34</v>
+        <v>1671.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>15067.67</v>
+        <v>1692.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>64.7</v>
+        <v>86.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>41.2</v>
+        <v>28.6</v>
       </c>
       <c r="AK16" t="n">
-        <v>21.1</v>
+        <v>17.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM16" t="n">
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>14604.59</v>
+        <v>1697.96</v>
       </c>
       <c r="AO16" t="n">
-        <v>13490.97</v>
+        <v>1608.69</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
+          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
+          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
+          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
         </is>
       </c>
     </row>
@@ -3224,13 +3224,13 @@
         <v>11.76</v>
       </c>
       <c r="S17" t="n">
-        <v>57.4</v>
+        <v>56.8</v>
       </c>
       <c r="T17" t="n">
         <v>0.15</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="V17" t="n">
         <v>53.3</v>
@@ -3245,7 +3245,7 @@
         <v>590.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>611.72</v>
+        <v>611.73</v>
       </c>
       <c r="AA17" t="n">
         <v>618.26</v>
@@ -3289,10 +3289,10 @@
         <v>6.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>643.62</v>
+        <v>642.47</v>
       </c>
       <c r="AO17" t="n">
-        <v>583.84</v>
+        <v>581.6</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -3391,13 +3391,13 @@
         <v>11.76</v>
       </c>
       <c r="S18" t="n">
-        <v>49</v>
+        <v>48.2</v>
       </c>
       <c r="T18" t="n">
         <v>0.17</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.98</v>
+        <v>-2.02</v>
       </c>
       <c r="V18" t="n">
         <v>51.7</v>
@@ -3456,10 +3456,10 @@
         <v>10</v>
       </c>
       <c r="AN18" t="n">
-        <v>2182.37</v>
+        <v>2185.04</v>
       </c>
       <c r="AO18" t="n">
-        <v>2033.12</v>
+        <v>2028.32</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3558,13 +3558,13 @@
         <v>11.76</v>
       </c>
       <c r="S19" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="T19" t="n">
         <v>0.18</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.19</v>
+        <v>-2.18</v>
       </c>
       <c r="V19" t="n">
         <v>46.7</v>
@@ -3576,10 +3576,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1114.03</v>
+        <v>1114.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>1153.77</v>
+        <v>1153.79</v>
       </c>
       <c r="AA19" t="n">
         <v>1144.38</v>
@@ -3623,10 +3623,10 @@
         <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>1168.55</v>
+        <v>1169.58</v>
       </c>
       <c r="AO19" t="n">
-        <v>1100.62</v>
+        <v>1102.69</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3725,13 +3725,13 @@
         <v>11.76</v>
       </c>
       <c r="S20" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="T20" t="n">
         <v>0.16</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.23</v>
+        <v>-2.21</v>
       </c>
       <c r="V20" t="n">
         <v>50</v>
@@ -3790,10 +3790,10 @@
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>313.35</v>
+        <v>313.56</v>
       </c>
       <c r="AO20" t="n">
-        <v>291.86</v>
+        <v>292.1</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3892,13 +3892,13 @@
         <v>11.76</v>
       </c>
       <c r="S21" t="n">
-        <v>46.3</v>
+        <v>45.7</v>
       </c>
       <c r="T21" t="n">
         <v>0.15</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.41</v>
+        <v>-2.44</v>
       </c>
       <c r="V21" t="n">
         <v>48.3</v>
@@ -3910,10 +3910,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>1705.12</v>
+        <v>1705.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>1765.36</v>
+        <v>1765.4</v>
       </c>
       <c r="AA21" t="n">
         <v>1734.77</v>
@@ -3957,10 +3957,10 @@
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>1790.43</v>
+        <v>1787.32</v>
       </c>
       <c r="AO21" t="n">
-        <v>1655.98</v>
+        <v>1656.89</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -3979,17 +3979,17 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
+          <t>[1721.0, 1730.98, 1740.97, 1750.95, 1760.93, 1770.91]</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.2, 1823.74]</t>
+          <t>[1721.0, 1754.71, 1774.53, 1792.05, 1808.39, 1823.98]</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
+          <t>[1721.0, 1713.18, 1715.79, 1720.12, 1725.33, 1731.11]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -719,7 +719,7 @@
         <v>11.76</v>
       </c>
       <c r="S2" t="n">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
       <c r="T2" t="n">
         <v>0.32</v>
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1461.7</v>
+        <v>1461.91</v>
       </c>
       <c r="AO2" t="n">
-        <v>1407.88</v>
+        <v>1409.62</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -886,13 +886,13 @@
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>55.7</v>
+        <v>56</v>
       </c>
       <c r="T3" t="n">
         <v>0.39</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.66</v>
+        <v>-0.65</v>
       </c>
       <c r="V3" t="n">
         <v>48.3</v>
@@ -904,13 +904,13 @@
         <v>-0.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>7803.37</v>
+        <v>7803.14</v>
       </c>
       <c r="Z3" t="n">
         <v>8059.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>7920.87</v>
+        <v>7920.64</v>
       </c>
       <c r="AB3" t="n">
         <v>7607.65</v>
@@ -951,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>8045.56</v>
+        <v>8050.52</v>
       </c>
       <c r="AO3" t="n">
-        <v>7627.74</v>
+        <v>7641</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -973,17 +973,17 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[7833.5, 7920.87, 8008.25, 8095.62, 8183.0, 8270.37]</t>
+          <t>[7833.5, 7920.64, 8007.78, 8094.92, 8182.07, 8269.21]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[7833.5, 7981.1, 8093.42, 8199.94, 8303.45, 8405.04]</t>
+          <t>[7833.5, 7980.87, 8092.96, 8199.24, 8302.52, 8403.88]</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>[7833.5, 7875.7, 7944.37, 8017.39, 8092.66, 8169.37]</t>
+          <t>[7833.5, 7875.47, 7943.9, 8016.69, 8091.73, 8168.2]</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
         <v>11.76</v>
       </c>
       <c r="S4" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="T4" t="n">
         <v>0.29</v>
@@ -1118,10 +1118,10 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>115.75</v>
+        <v>115.77</v>
       </c>
       <c r="AO4" t="n">
-        <v>109.83</v>
+        <v>109.52</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1220,13 +1220,13 @@
         <v>11.76</v>
       </c>
       <c r="S5" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
       <c r="T5" t="n">
         <v>0.29</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>48.3</v>
@@ -1238,10 +1238,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>11731.98</v>
+        <v>11732.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>12148.58</v>
+        <v>12148.72</v>
       </c>
       <c r="AA5" t="n">
         <v>11998.22</v>
@@ -1285,10 +1285,10 @@
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12158.36</v>
+        <v>12158.3</v>
       </c>
       <c r="AO5" t="n">
-        <v>11626.15</v>
+        <v>11651.1</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1329,16 +1329,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>263368.34</v>
+        <v>105169.94</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,145 +1346,145 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2747.3</v>
+        <v>2199.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2735.68 - ₹2764.73</t>
+          <t>₹2190.26 - ₹2214.11</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2793.77</v>
+        <v>2237.97</v>
       </c>
       <c r="I6" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="J6" t="n">
-        <v>2687.86</v>
+        <v>2140.62</v>
       </c>
       <c r="K6" t="n">
-        <v>2678.76</v>
+        <v>2061.08</v>
       </c>
       <c r="L6" t="n">
-        <v>2570.71</v>
+        <v>1703.8</v>
       </c>
       <c r="M6" t="n">
-        <v>6.83</v>
+        <v>27.05</v>
       </c>
       <c r="N6" t="n">
-        <v>16.14</v>
+        <v>29.77</v>
       </c>
       <c r="O6" t="n">
-        <v>10.09</v>
+        <v>35.4</v>
       </c>
       <c r="P6" t="n">
-        <v>6.05</v>
+        <v>-5.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>58.09</v>
+        <v>47.71</v>
       </c>
       <c r="R6" t="n">
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>57.8</v>
+        <v>55.9</v>
       </c>
       <c r="T6" t="n">
         <v>0.25</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.88</v>
+        <v>-0.98</v>
       </c>
       <c r="V6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="X6" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>2707.04</v>
+        <v>2184.77</v>
       </c>
       <c r="Z6" t="n">
-        <v>2803.2</v>
+        <v>2261.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>2769.28</v>
+        <v>2217.76</v>
       </c>
       <c r="AB6" t="n">
-        <v>2660.17</v>
+        <v>2128.24</v>
       </c>
       <c r="AC6" t="n">
-        <v>2751.53</v>
+        <v>2191.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>2770.66</v>
+        <v>2221.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2794.03</v>
+        <v>2242.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>62.4</v>
+        <v>57.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI6" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>12.8</v>
+        <v>6.4</v>
       </c>
       <c r="AM6" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AN6" t="n">
-        <v>2813.46</v>
+        <v>2269.42</v>
       </c>
       <c r="AO6" t="n">
-        <v>2683.65</v>
+        <v>2140.59</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹263,368.34 Cr., a P/E ratio of 55.24, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.38 (Bullish Momentum Zone), while MACD Line (16.14) trades above Signal (10.09) with an expanding histogram (+6.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.83% above the 200-day DMA (₹2570.71). Daily volatility envelope is bounded by ATR(14) of ₹58.09.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,747.30) is positioned above the 30-day DMA (₹2,687.86), 50-day DMA (₹2,678.76), and 200-day DMA (₹2,570.71). The price distance from 200 DMA is +6.83%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2747.3, 2755.54, 2763.78, 2772.03, 2780.27, 2788.51]</t>
+          <t>[2199.8, 2217.76, 2235.73, 2253.69, 2271.66, 2289.62]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2747.3, 2778.78, 2796.64, 2812.27, 2826.74, 2840.46]</t>
+          <t>[2199.8, 2236.85, 2262.72, 2286.74, 2309.82, 2332.29]</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>[2747.3, 2738.12, 2739.14, 2741.84, 2745.42, 2749.54]</t>
+          <t>[2199.8, 2203.45, 2215.49, 2228.9, 2243.03, 2257.62]</t>
         </is>
       </c>
     </row>
@@ -1496,162 +1496,162 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>105169.94</v>
+        <v>98206.09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2199.8</v>
+        <v>372.95</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹2190.26 - ₹2214.11</t>
+          <t>₹371.41 - ₹375.26</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2237.97</v>
+        <v>379.11</v>
       </c>
       <c r="I7" t="n">
-        <v>69</v>
+        <v>432</v>
       </c>
       <c r="J7" t="n">
-        <v>2140.62</v>
+        <v>357.21</v>
       </c>
       <c r="K7" t="n">
-        <v>2061.08</v>
+        <v>349.78</v>
       </c>
       <c r="L7" t="n">
-        <v>1703.8</v>
+        <v>347.56</v>
       </c>
       <c r="M7" t="n">
-        <v>27.05</v>
+        <v>6.64</v>
       </c>
       <c r="N7" t="n">
-        <v>29.77</v>
+        <v>4.07</v>
       </c>
       <c r="O7" t="n">
-        <v>35.4</v>
+        <v>2.35</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>47.71</v>
+        <v>7.7</v>
       </c>
       <c r="R7" t="n">
         <v>11.76</v>
       </c>
       <c r="S7" t="n">
-        <v>56.1</v>
+        <v>52.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.97</v>
+        <v>-1.04</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
       </c>
       <c r="W7" t="n">
-        <v>1.78</v>
+        <v>2.81</v>
       </c>
       <c r="X7" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>2184.76</v>
+        <v>366.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>2261.76</v>
+        <v>379.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>2217.76</v>
+        <v>375.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>2128.24</v>
+        <v>361.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>2191.3</v>
+        <v>372.32</v>
       </c>
       <c r="AD7" t="n">
-        <v>2221.1</v>
+        <v>374.64</v>
       </c>
       <c r="AE7" t="n">
-        <v>2242.4</v>
+        <v>376.32</v>
       </c>
       <c r="AF7" t="n">
-        <v>57.9</v>
+        <v>78.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI7" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>97.09999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>17.5</v>
+        <v>25.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AN7" t="n">
-        <v>2267.91</v>
+        <v>383.24</v>
       </c>
       <c r="AO7" t="n">
-        <v>2141.66</v>
+        <v>363.08</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2199.8, 2217.76, 2235.72, 2253.68, 2271.64, 2289.6]</t>
+          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2199.8, 2236.84, 2262.71, 2286.73, 2309.8, 2332.27]</t>
+          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>[2199.8, 2203.45, 2215.48, 2228.89, 2243.01, 2257.59]</t>
+          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
         </is>
       </c>
     </row>
@@ -1721,19 +1721,19 @@
         <v>11.76</v>
       </c>
       <c r="S8" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="T8" t="n">
         <v>0.27</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.02</v>
+        <v>-1.05</v>
       </c>
       <c r="V8" t="n">
         <v>55</v>
       </c>
       <c r="W8" t="n">
-        <v>5.75</v>
+        <v>5.74</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
@@ -1742,7 +1742,7 @@
         <v>720.8200000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>725.27</v>
+        <v>725.26</v>
       </c>
       <c r="AA8" t="n">
         <v>744.46</v>
@@ -1786,10 +1786,10 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>756.16</v>
+        <v>756.83</v>
       </c>
       <c r="AO8" t="n">
-        <v>720.1900000000001</v>
+        <v>720.3099999999999</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -1830,162 +1830,162 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>98206.09</v>
+        <v>310746.28</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>372.95</v>
+        <v>4646.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹371.41 - ₹375.26</t>
+          <t>₹4629.85 - ₹4671.48</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>379.11</v>
+        <v>4713.1</v>
       </c>
       <c r="I9" t="n">
-        <v>432</v>
+        <v>40</v>
       </c>
       <c r="J9" t="n">
-        <v>357.21</v>
+        <v>4471.9</v>
       </c>
       <c r="K9" t="n">
-        <v>349.78</v>
+        <v>4404.23</v>
       </c>
       <c r="L9" t="n">
-        <v>347.56</v>
+        <v>4346.03</v>
       </c>
       <c r="M9" t="n">
-        <v>6.64</v>
+        <v>5.42</v>
       </c>
       <c r="N9" t="n">
-        <v>4.07</v>
+        <v>56.6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.35</v>
+        <v>49.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>6.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.7</v>
+        <v>83.25</v>
       </c>
       <c r="R9" t="n">
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>52.9</v>
+        <v>46.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.04</v>
+        <v>-1.07</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="W9" t="n">
-        <v>2.81</v>
+        <v>2.15</v>
       </c>
       <c r="X9" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>366.16</v>
+        <v>4548.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>379.22</v>
+        <v>4711.39</v>
       </c>
       <c r="AA9" t="n">
-        <v>375.93</v>
+        <v>4683.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>361.4</v>
+        <v>4521.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>372.32</v>
+        <v>4635.53</v>
       </c>
       <c r="AD9" t="n">
-        <v>374.64</v>
+        <v>4679.96</v>
       </c>
       <c r="AE9" t="n">
-        <v>376.32</v>
+        <v>4713.43</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.3</v>
+        <v>59.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI9" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>6.1</v>
+        <v>34.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>25.2</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
-        <v>68.90000000000001</v>
+        <v>27.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AN9" t="n">
-        <v>382.62</v>
+        <v>4772.74</v>
       </c>
       <c r="AO9" t="n">
-        <v>362.41</v>
+        <v>4522.8</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
+          <t>[4646.5, 4660.44, 4674.38, 4688.32, 4702.26, 4716.2]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
+          <t>[4646.5, 4693.74, 4721.47, 4746.0, 4768.86, 4790.66]</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
+          <t>[4646.5, 4635.46, 4639.06, 4645.06, 4652.31, 4660.35]</t>
         </is>
       </c>
     </row>
@@ -1997,162 +1997,162 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>310746.28</v>
+        <v>68767.81</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4646.5</v>
+        <v>5751.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹4629.85 - ₹4671.48</t>
+          <t>₹5727.01 - ₹5788.23</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4713.1</v>
+        <v>5849.44</v>
       </c>
       <c r="I10" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J10" t="n">
-        <v>4471.9</v>
+        <v>5575</v>
       </c>
       <c r="K10" t="n">
-        <v>4404.23</v>
+        <v>5484.08</v>
       </c>
       <c r="L10" t="n">
-        <v>4346.03</v>
+        <v>5521.06</v>
       </c>
       <c r="M10" t="n">
-        <v>5.42</v>
+        <v>5.35</v>
       </c>
       <c r="N10" t="n">
-        <v>56.6</v>
+        <v>57.19</v>
       </c>
       <c r="O10" t="n">
-        <v>49.9</v>
+        <v>51.96</v>
       </c>
       <c r="P10" t="n">
-        <v>6.7</v>
+        <v>5.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>83.25</v>
+        <v>122.43</v>
       </c>
       <c r="R10" t="n">
         <v>11.76</v>
       </c>
       <c r="S10" t="n">
-        <v>47.1</v>
+        <v>52.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.04</v>
+        <v>-1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>41.7</v>
+        <v>53.3</v>
       </c>
       <c r="W10" t="n">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="X10" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>4548.57</v>
+        <v>5710.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>4711.2</v>
+        <v>5912.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>4683.67</v>
+        <v>5797.51</v>
       </c>
       <c r="AB10" t="n">
-        <v>4521.62</v>
+        <v>5567.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>4635.53</v>
+        <v>5773.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>4679.96</v>
+        <v>5811.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>4713.43</v>
+        <v>5871.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>59.3</v>
+        <v>58.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI10" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34.1</v>
+        <v>29.9</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>14.6</v>
       </c>
       <c r="AL10" t="n">
-        <v>27.5</v>
+        <v>15.6</v>
       </c>
       <c r="AM10" t="n">
-        <v>24</v>
+        <v>17.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>4769.22</v>
+        <v>5881.57</v>
       </c>
       <c r="AO10" t="n">
-        <v>4523.4</v>
+        <v>5624.81</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,767.81 Cr., a P/E ratio of 29.85, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,751.50) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[4646.5, 4660.44, 4674.38, 4688.32, 4702.26, 4716.2]</t>
+          <t>[5751.5, 5797.12, 5842.75, 5888.37, 5934.0, 5979.62]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[4646.5, 4693.74, 4721.47, 4746.0, 4768.86, 4790.66]</t>
+          <t>[5751.5, 5846.1, 5912.0, 5973.19, 6031.94, 6089.12]</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>[4646.5, 4635.46, 4639.06, 4645.06, 4652.31, 4660.35]</t>
+          <t>[5751.5, 5760.4, 5790.81, 5824.76, 5860.54, 5897.49]</t>
         </is>
       </c>
     </row>
@@ -2164,16 +2164,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68767.81</v>
+        <v>133901.31</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2181,145 +2181,145 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5751.5</v>
+        <v>3760</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹5727.01 - ₹5788.23</t>
+          <t>₹3740.59 - ₹3789.12</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5849.44</v>
+        <v>3837.66</v>
       </c>
       <c r="I11" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J11" t="n">
-        <v>5575</v>
+        <v>3594.31</v>
       </c>
       <c r="K11" t="n">
-        <v>5484.08</v>
+        <v>3627.85</v>
       </c>
       <c r="L11" t="n">
-        <v>5521.06</v>
+        <v>3330.53</v>
       </c>
       <c r="M11" t="n">
-        <v>5.35</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>57.19</v>
+        <v>22.06</v>
       </c>
       <c r="O11" t="n">
-        <v>51.96</v>
+        <v>10.09</v>
       </c>
       <c r="P11" t="n">
-        <v>5.23</v>
+        <v>11.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>122.43</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="R11" t="n">
         <v>11.76</v>
       </c>
       <c r="S11" t="n">
-        <v>51.7</v>
+        <v>56.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.13</v>
+        <v>-1.22</v>
       </c>
       <c r="V11" t="n">
         <v>53.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.82</v>
+        <v>2.23</v>
       </c>
       <c r="X11" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>5710.85</v>
+        <v>3684.03</v>
       </c>
       <c r="Z11" t="n">
-        <v>5912.15</v>
+        <v>3815.63</v>
       </c>
       <c r="AA11" t="n">
-        <v>5797.51</v>
+        <v>3790.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>5567.86</v>
+        <v>3614.39</v>
       </c>
       <c r="AC11" t="n">
-        <v>5773.17</v>
+        <v>3743.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>5811.34</v>
+        <v>3824.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>5871.17</v>
+        <v>3889.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>58.4</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI11" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>29.9</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AK11" t="n">
         <v>14.6</v>
       </c>
       <c r="AL11" t="n">
-        <v>15.6</v>
+        <v>9.5</v>
       </c>
       <c r="AM11" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="AN11" t="n">
-        <v>5880.41</v>
+        <v>3877.01</v>
       </c>
       <c r="AO11" t="n">
-        <v>5626</v>
+        <v>3657.42</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,767.81 Cr., a P/E ratio of 29.85, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,901.31 Cr., a P/E ratio of 79.36, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,751.50) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,760.00) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[5751.5, 5797.12, 5842.75, 5888.37, 5934.0, 5979.62]</t>
+          <t>[3760.0, 3771.28, 3782.56, 3793.84, 3805.12, 3816.4]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[5751.5, 5846.1, 5912.0, 5973.19, 6031.94, 6089.12]</t>
+          <t>[3760.0, 3810.11, 3837.47, 3861.1, 3882.78, 3903.23]</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>[5751.5, 5760.4, 5790.81, 5824.76, 5860.54, 5897.49]</t>
+          <t>[3760.0, 3742.16, 3741.37, 3743.4, 3746.88, 3751.28]</t>
         </is>
       </c>
     </row>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>133901.31</v>
+        <v>119011.76</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2348,145 +2348,145 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3760</v>
+        <v>1473.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹3740.59 - ₹3789.12</t>
+          <t>₹1466.31 - ₹1483.53</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3837.66</v>
+        <v>1500.76</v>
       </c>
       <c r="I12" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="J12" t="n">
-        <v>3594.31</v>
+        <v>1436.14</v>
       </c>
       <c r="K12" t="n">
-        <v>3627.85</v>
+        <v>1414.83</v>
       </c>
       <c r="L12" t="n">
-        <v>3330.53</v>
+        <v>1396.09</v>
       </c>
       <c r="M12" t="n">
-        <v>9.859999999999999</v>
+        <v>5.04</v>
       </c>
       <c r="N12" t="n">
-        <v>22.06</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>10.09</v>
+        <v>6.31</v>
       </c>
       <c r="P12" t="n">
-        <v>11.97</v>
+        <v>1.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>97.06999999999999</v>
+        <v>34.45</v>
       </c>
       <c r="R12" t="n">
         <v>11.76</v>
       </c>
       <c r="S12" t="n">
-        <v>55.9</v>
+        <v>52</v>
       </c>
       <c r="T12" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.26</v>
+        <v>-1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>53.3</v>
+        <v>45</v>
       </c>
       <c r="W12" t="n">
-        <v>2.23</v>
+        <v>11.03</v>
       </c>
       <c r="X12" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>3684.03</v>
+        <v>1431.86</v>
       </c>
       <c r="Z12" t="n">
-        <v>3815.63</v>
+        <v>1388.21</v>
       </c>
       <c r="AA12" t="n">
-        <v>3790.08</v>
+        <v>1484.99</v>
       </c>
       <c r="AB12" t="n">
-        <v>3614.39</v>
+        <v>1421.52</v>
       </c>
       <c r="AC12" t="n">
-        <v>3743.5</v>
+        <v>1471.43</v>
       </c>
       <c r="AD12" t="n">
-        <v>3824.9</v>
+        <v>1480.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>3889.8</v>
+        <v>1487.93</v>
       </c>
       <c r="AF12" t="n">
-        <v>74.09999999999999</v>
+        <v>56.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.08</v>
+        <v>-0.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI12" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>79.40000000000001</v>
+        <v>35.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>14.6</v>
+        <v>3.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="AM12" t="n">
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>3870.75</v>
+        <v>1504.58</v>
       </c>
       <c r="AO12" t="n">
-        <v>3639.78</v>
+        <v>1443.2</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,901.31 Cr., a P/E ratio of 79.36, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,760.00) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[3760.0, 3771.28, 3782.56, 3793.84, 3805.12, 3816.4]</t>
+          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[3760.0, 3810.11, 3837.47, 3861.1, 3882.78, 3903.23]</t>
+          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>[3760.0, 3742.16, 3741.37, 3743.4, 3746.88, 3751.28]</t>
+          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
         </is>
       </c>
     </row>
@@ -2498,16 +2498,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>119011.76</v>
+        <v>246283.11</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2515,90 +2515,90 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1473.2</v>
+        <v>1046.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1466.31 - ₹1483.53</t>
+          <t>₹1040.39 - ₹1056.17</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1500.76</v>
+        <v>1071.96</v>
       </c>
       <c r="I13" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J13" t="n">
-        <v>1436.14</v>
+        <v>1032.61</v>
       </c>
       <c r="K13" t="n">
-        <v>1414.83</v>
+        <v>994.9400000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>1396.09</v>
+        <v>942.9400000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>5.04</v>
+        <v>8.94</v>
       </c>
       <c r="N13" t="n">
-        <v>8.130000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>6.31</v>
+        <v>12.02</v>
       </c>
       <c r="P13" t="n">
-        <v>1.82</v>
+        <v>-3.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.45</v>
+        <v>31.57</v>
       </c>
       <c r="R13" t="n">
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>52</v>
+        <v>56.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.27</v>
+        <v>-1.52</v>
       </c>
       <c r="V13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="W13" t="n">
-        <v>11.03</v>
+        <v>3.38</v>
       </c>
       <c r="X13" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>1431.86</v>
+        <v>1019.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>1388.25</v>
+        <v>1056.01</v>
       </c>
       <c r="AA13" t="n">
-        <v>1484.99</v>
+        <v>1055.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>1421.52</v>
+        <v>999.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>1471.43</v>
+        <v>1043.47</v>
       </c>
       <c r="AD13" t="n">
-        <v>1480.56</v>
+        <v>1057.84</v>
       </c>
       <c r="AE13" t="n">
-        <v>1487.93</v>
+        <v>1068.97</v>
       </c>
       <c r="AF13" t="n">
-        <v>56.5</v>
+        <v>46.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2609,51 +2609,51 @@
         <v>0.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>35.3</v>
+        <v>18.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.5</v>
+        <v>39.1</v>
       </c>
       <c r="AL13" t="n">
-        <v>12</v>
+        <v>50.1</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>1504.69</v>
+        <v>1087.24</v>
       </c>
       <c r="AO13" t="n">
-        <v>1442.77</v>
+        <v>1010.62</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹246,283.11 Cr., a P/E ratio of 18.48, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,046.70) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
+          <t>[1046.7, 1049.84, 1052.98, 1056.12, 1059.26, 1062.4]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
+          <t>[1046.7, 1062.47, 1070.84, 1077.99, 1084.52, 1090.64]</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
+          <t>[1046.7, 1040.37, 1039.59, 1039.72, 1040.32, 1041.22]</t>
         </is>
       </c>
     </row>
@@ -2665,16 +2665,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>246283.11</v>
+        <v>85420.58</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2682,145 +2682,145 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1046.7</v>
+        <v>14049</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹1040.39 - ₹1056.17</t>
+          <t>₹13965.8 - ₹14173.8</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1071.96</v>
+        <v>14381.8</v>
       </c>
       <c r="I14" t="n">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>1032.61</v>
+        <v>13190.57</v>
       </c>
       <c r="K14" t="n">
-        <v>994.9400000000001</v>
+        <v>12605.68</v>
       </c>
       <c r="L14" t="n">
-        <v>942.9400000000001</v>
+        <v>12333.95</v>
       </c>
       <c r="M14" t="n">
-        <v>8.94</v>
+        <v>16.25</v>
       </c>
       <c r="N14" t="n">
-        <v>8.390000000000001</v>
+        <v>477.1</v>
       </c>
       <c r="O14" t="n">
-        <v>12.02</v>
+        <v>503.84</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.63</v>
+        <v>-26.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>31.57</v>
+        <v>416</v>
       </c>
       <c r="R14" t="n">
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>56.4</v>
+        <v>51.3</v>
       </c>
       <c r="T14" t="n">
         <v>0.18</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.52</v>
+        <v>-1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>55</v>
+        <v>46.7</v>
       </c>
       <c r="W14" t="n">
-        <v>3.38</v>
+        <v>6.67</v>
       </c>
       <c r="X14" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>1019.35</v>
+        <v>13634.58</v>
       </c>
       <c r="Z14" t="n">
-        <v>1055.98</v>
+        <v>14126.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1055.07</v>
+        <v>14161.39</v>
       </c>
       <c r="AB14" t="n">
-        <v>999.34</v>
+        <v>13425</v>
       </c>
       <c r="AC14" t="n">
-        <v>1043.47</v>
+        <v>14079.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>1057.84</v>
+        <v>14558.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>1068.97</v>
+        <v>15067.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>46.1</v>
+        <v>64.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.14</v>
+        <v>0.11</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI14" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>18.5</v>
+        <v>41.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>39.1</v>
+        <v>21.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>50.1</v>
+        <v>3.6</v>
       </c>
       <c r="AM14" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>1084.1</v>
+        <v>14590.27</v>
       </c>
       <c r="AO14" t="n">
-        <v>1009.87</v>
+        <v>13527.74</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹246,283.11 Cr., a P/E ratio of 18.48, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,046.70) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[1046.7, 1049.84, 1052.98, 1056.12, 1059.26, 1062.4]</t>
+          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[1046.7, 1062.47, 1070.84, 1077.99, 1084.52, 1090.64]</t>
+          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>[1046.7, 1040.37, 1039.59, 1039.72, 1040.32, 1041.22]</t>
+          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85420.58</v>
+        <v>146280.27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2849,145 +2849,145 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14049</v>
+        <v>1651.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹13965.8 - ₹14173.8</t>
+          <t>₹1641.81 - ₹1665.54</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14381.8</v>
+        <v>1689.26</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="J15" t="n">
-        <v>13190.57</v>
+        <v>1478.49</v>
       </c>
       <c r="K15" t="n">
-        <v>12605.68</v>
+        <v>1460.44</v>
       </c>
       <c r="L15" t="n">
-        <v>12333.95</v>
+        <v>1458.79</v>
       </c>
       <c r="M15" t="n">
-        <v>16.25</v>
+        <v>14.41</v>
       </c>
       <c r="N15" t="n">
-        <v>477.1</v>
+        <v>56.22</v>
       </c>
       <c r="O15" t="n">
-        <v>503.84</v>
+        <v>42.84</v>
       </c>
       <c r="P15" t="n">
-        <v>-26.74</v>
+        <v>13.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>416</v>
+        <v>47.45</v>
       </c>
       <c r="R15" t="n">
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>51.2</v>
+        <v>49.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.76</v>
+        <v>-1.79</v>
       </c>
       <c r="V15" t="n">
-        <v>46.7</v>
+        <v>48.3</v>
       </c>
       <c r="W15" t="n">
-        <v>6.67</v>
+        <v>8.69</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>13634.58</v>
+        <v>1625.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>14126.3</v>
+        <v>1683.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>14161.39</v>
+        <v>1664.51</v>
       </c>
       <c r="AB15" t="n">
-        <v>13425</v>
+        <v>1580.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>14079.67</v>
+        <v>1641.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>14558.34</v>
+        <v>1671.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>15067.67</v>
+        <v>1692.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>64.7</v>
+        <v>86.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>41.2</v>
+        <v>28.6</v>
       </c>
       <c r="AK15" t="n">
-        <v>21.1</v>
+        <v>17.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM15" t="n">
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>14605.78</v>
+        <v>1695.31</v>
       </c>
       <c r="AO15" t="n">
-        <v>13527.81</v>
+        <v>1605.12</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
+          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
+          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
+          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>146280.27</v>
+        <v>17572.27</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3016,145 +3016,145 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1651.3</v>
+        <v>613.35</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹1641.81 - ₹1665.54</t>
+          <t>₹608.87 - ₹620.07</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1689.26</v>
+        <v>631.27</v>
       </c>
       <c r="I16" t="n">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="J16" t="n">
-        <v>1478.49</v>
+        <v>578.01</v>
       </c>
       <c r="K16" t="n">
-        <v>1460.44</v>
+        <v>541.38</v>
       </c>
       <c r="L16" t="n">
-        <v>1458.79</v>
+        <v>553.54</v>
       </c>
       <c r="M16" t="n">
-        <v>14.41</v>
+        <v>10.74</v>
       </c>
       <c r="N16" t="n">
-        <v>56.22</v>
+        <v>14.56</v>
       </c>
       <c r="O16" t="n">
-        <v>42.84</v>
+        <v>16.43</v>
       </c>
       <c r="P16" t="n">
-        <v>13.38</v>
+        <v>-1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.45</v>
+        <v>22.4</v>
       </c>
       <c r="R16" t="n">
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>49.6</v>
+        <v>57</v>
       </c>
       <c r="T16" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.78</v>
+        <v>-1.9</v>
       </c>
       <c r="V16" t="n">
-        <v>48.3</v>
+        <v>53.3</v>
       </c>
       <c r="W16" t="n">
-        <v>8.69</v>
+        <v>4.8</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>1625.39</v>
+        <v>590.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>1683.18</v>
+        <v>611.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>1664.51</v>
+        <v>618.26</v>
       </c>
       <c r="AB16" t="n">
-        <v>1580.13</v>
+        <v>579.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>1641.1</v>
+        <v>616.27</v>
       </c>
       <c r="AD16" t="n">
-        <v>1671.7</v>
+        <v>624.54</v>
       </c>
       <c r="AE16" t="n">
-        <v>1692.1</v>
+        <v>635.72</v>
       </c>
       <c r="AF16" t="n">
-        <v>86.2</v>
+        <v>60.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28.6</v>
+        <v>88.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>17.7</v>
+        <v>-10.1</v>
       </c>
       <c r="AL16" t="n">
-        <v>8.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AM16" t="n">
-        <v>15</v>
+        <v>6.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>1697.96</v>
+        <v>648.13</v>
       </c>
       <c r="AO16" t="n">
-        <v>1608.69</v>
+        <v>582.21</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
+          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
+          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
+          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
         </is>
       </c>
     </row>
@@ -3166,16 +3166,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17572.27</v>
+        <v>63429.15</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3183,145 +3183,145 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>613.35</v>
+        <v>2105.7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹608.87 - ₹620.07</t>
+          <t>₹2092.64 - ₹2125.3</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>631.27</v>
+        <v>2157.96</v>
       </c>
       <c r="I17" t="n">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="J17" t="n">
-        <v>578.01</v>
+        <v>1999.45</v>
       </c>
       <c r="K17" t="n">
-        <v>541.38</v>
+        <v>1888.17</v>
       </c>
       <c r="L17" t="n">
-        <v>553.54</v>
+        <v>1880.41</v>
       </c>
       <c r="M17" t="n">
-        <v>10.74</v>
+        <v>12.26</v>
       </c>
       <c r="N17" t="n">
-        <v>14.56</v>
+        <v>62.25</v>
       </c>
       <c r="O17" t="n">
-        <v>16.43</v>
+        <v>68.98</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.88</v>
+        <v>-6.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.4</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="R17" t="n">
         <v>11.76</v>
       </c>
       <c r="S17" t="n">
-        <v>56.8</v>
+        <v>48.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.91</v>
+        <v>-2.01</v>
       </c>
       <c r="V17" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="W17" t="n">
-        <v>4.8</v>
+        <v>4.49</v>
       </c>
       <c r="X17" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y17" t="n">
-        <v>590.26</v>
+        <v>2027.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>611.73</v>
+        <v>2032.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>618.26</v>
+        <v>2122.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>579.75</v>
+        <v>2007.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>616.27</v>
+        <v>2111.93</v>
       </c>
       <c r="AD17" t="n">
-        <v>624.54</v>
+        <v>2127.76</v>
       </c>
       <c r="AE17" t="n">
-        <v>635.72</v>
+        <v>2149.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>60.8</v>
+        <v>48.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI17" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ17" t="n">
-        <v>88.5</v>
+        <v>34.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>-10.1</v>
+        <v>63</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.7</v>
+        <v>36.1</v>
       </c>
       <c r="AM17" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="AN17" t="n">
-        <v>642.47</v>
+        <v>2188.81</v>
       </c>
       <c r="AO17" t="n">
-        <v>581.6</v>
+        <v>2028.6</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
+          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
+          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
+          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
         </is>
       </c>
     </row>
@@ -3333,162 +3333,162 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63429.15</v>
+        <v>46194.13</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2105.7</v>
+        <v>1135.3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹2092.64 - ₹2125.3</t>
+          <t>₹1128.39 - ₹1145.67</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2157.96</v>
+        <v>1162.95</v>
       </c>
       <c r="I18" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="J18" t="n">
-        <v>1999.45</v>
+        <v>1109.56</v>
       </c>
       <c r="K18" t="n">
-        <v>1888.17</v>
+        <v>1105.35</v>
       </c>
       <c r="L18" t="n">
-        <v>1880.41</v>
+        <v>1100.33</v>
       </c>
       <c r="M18" t="n">
-        <v>12.26</v>
+        <v>3.87</v>
       </c>
       <c r="N18" t="n">
-        <v>62.25</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>68.98</v>
+        <v>4.71</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.73</v>
+        <v>4.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>65.31999999999999</v>
+        <v>34.56</v>
       </c>
       <c r="R18" t="n">
         <v>11.76</v>
       </c>
       <c r="S18" t="n">
-        <v>48.2</v>
+        <v>44.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.02</v>
+        <v>-2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>51.7</v>
+        <v>46.7</v>
       </c>
       <c r="W18" t="n">
-        <v>4.49</v>
+        <v>2.28</v>
       </c>
       <c r="X18" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y18" t="n">
-        <v>2027.32</v>
+        <v>1114.01</v>
       </c>
       <c r="Z18" t="n">
-        <v>2032.25</v>
+        <v>1153.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>2122.55</v>
+        <v>1144.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>2007.72</v>
+        <v>1083.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>2111.93</v>
+        <v>1144.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>2127.76</v>
+        <v>1156.86</v>
       </c>
       <c r="AE18" t="n">
-        <v>2149.83</v>
+        <v>1178.43</v>
       </c>
       <c r="AF18" t="n">
-        <v>48.8</v>
+        <v>52.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI18" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34.2</v>
+        <v>37.7</v>
       </c>
       <c r="AK18" t="n">
-        <v>63</v>
+        <v>29.9</v>
       </c>
       <c r="AL18" t="n">
-        <v>36.1</v>
+        <v>26.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AN18" t="n">
-        <v>2185.04</v>
+        <v>1168.8</v>
       </c>
       <c r="AO18" t="n">
-        <v>2028.32</v>
+        <v>1101.74</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,194.13 Cr., a P/E ratio of 37.73, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,135.30) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
+          <t>[1135.3, 1138.71, 1142.11, 1145.52, 1148.92, 1152.33]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
+          <t>[1135.3, 1152.53, 1161.66, 1169.46, 1176.58, 1183.24]</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
+          <t>[1135.3, 1128.34, 1127.45, 1127.56, 1128.19, 1129.14]</t>
         </is>
       </c>
     </row>
@@ -3500,162 +3500,162 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>46194.13</v>
+        <v>278417.14</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1135.3</v>
+        <v>302.45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>₹1128.39 - ₹1145.67</t>
+          <t>₹300.39 - ₹305.53</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1162.95</v>
+        <v>310.68</v>
       </c>
       <c r="I19" t="n">
-        <v>96</v>
+        <v>324</v>
       </c>
       <c r="J19" t="n">
-        <v>1109.56</v>
+        <v>281.7</v>
       </c>
       <c r="K19" t="n">
-        <v>1105.35</v>
+        <v>268.93</v>
       </c>
       <c r="L19" t="n">
-        <v>1100.33</v>
+        <v>274.01</v>
       </c>
       <c r="M19" t="n">
-        <v>3.87</v>
+        <v>13.37</v>
       </c>
       <c r="N19" t="n">
-        <v>9.130000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="O19" t="n">
-        <v>4.71</v>
+        <v>8.42</v>
       </c>
       <c r="P19" t="n">
-        <v>4.42</v>
+        <v>1.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>34.56</v>
+        <v>10.28</v>
       </c>
       <c r="R19" t="n">
         <v>11.76</v>
       </c>
       <c r="S19" t="n">
-        <v>44.4</v>
+        <v>48.6</v>
       </c>
       <c r="T19" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.18</v>
+        <v>-2.23</v>
       </c>
       <c r="V19" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="X19" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1114.05</v>
+        <v>299.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>1153.79</v>
+        <v>309.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>1144.38</v>
+        <v>304.87</v>
       </c>
       <c r="AB19" t="n">
-        <v>1083.45</v>
+        <v>287.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1144.43</v>
+        <v>306.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1156.86</v>
+        <v>311.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1178.43</v>
+        <v>320.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>52.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI19" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ19" t="n">
-        <v>37.7</v>
+        <v>672.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>29.9</v>
+        <v>182</v>
       </c>
       <c r="AL19" t="n">
-        <v>26.5</v>
+        <v>0.6</v>
       </c>
       <c r="AM19" t="n">
         <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>1169.58</v>
+        <v>313.15</v>
       </c>
       <c r="AO19" t="n">
-        <v>1102.69</v>
+        <v>291.97</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,194.13 Cr., a P/E ratio of 37.73, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,135.30) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>[1135.3, 1138.71, 1142.11, 1145.52, 1148.92, 1152.33]</t>
+          <t>[302.45, 303.8, 305.15, 306.5, 307.85, 309.19]</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>[1135.3, 1152.53, 1161.66, 1169.46, 1176.58, 1183.24]</t>
+          <t>[302.45, 307.91, 310.96, 313.62, 316.07, 318.39]</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>[1135.3, 1128.34, 1127.45, 1127.56, 1128.19, 1129.14]</t>
+          <t>[302.45, 300.71, 300.79, 301.15, 301.68, 302.3]</t>
         </is>
       </c>
     </row>
@@ -3667,162 +3667,162 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>278417.14</v>
+        <v>76187.09</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>302.45</v>
+        <v>1721</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>₹300.39 - ₹305.53</t>
+          <t>₹1709.13 - ₹1738.8</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>310.68</v>
+        <v>1768.46</v>
       </c>
       <c r="I20" t="n">
-        <v>324</v>
+        <v>56</v>
       </c>
       <c r="J20" t="n">
-        <v>281.7</v>
+        <v>1505.99</v>
       </c>
       <c r="K20" t="n">
-        <v>268.93</v>
+        <v>1472.15</v>
       </c>
       <c r="L20" t="n">
-        <v>274.01</v>
+        <v>1507.99</v>
       </c>
       <c r="M20" t="n">
-        <v>13.37</v>
+        <v>15.58</v>
       </c>
       <c r="N20" t="n">
-        <v>9.93</v>
+        <v>53.48</v>
       </c>
       <c r="O20" t="n">
-        <v>8.42</v>
+        <v>30.14</v>
       </c>
       <c r="P20" t="n">
-        <v>1.51</v>
+        <v>23.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.28</v>
+        <v>59.33</v>
       </c>
       <c r="R20" t="n">
         <v>11.76</v>
       </c>
       <c r="S20" t="n">
-        <v>48.9</v>
+        <v>46.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.21</v>
+        <v>-2.42</v>
       </c>
       <c r="V20" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="W20" t="n">
-        <v>2.44</v>
+        <v>7.48</v>
       </c>
       <c r="X20" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y20" t="n">
-        <v>299.26</v>
+        <v>1705.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>309.85</v>
+        <v>1765.36</v>
       </c>
       <c r="AA20" t="n">
-        <v>304.87</v>
+        <v>1734.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>287.03</v>
+        <v>1632.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>306.75</v>
+        <v>1713.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>311.7</v>
+        <v>1745.96</v>
       </c>
       <c r="AE20" t="n">
-        <v>320.95</v>
+        <v>1770.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>65.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI20" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>672.1</v>
+        <v>35.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>182</v>
+        <v>49.9</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.6</v>
+        <v>9.6</v>
       </c>
       <c r="AM20" t="n">
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>313.56</v>
+        <v>1789.44</v>
       </c>
       <c r="AO20" t="n">
-        <v>292.1</v>
+        <v>1653.38</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,187.09 Cr., a P/E ratio of 35.21, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.48) trades above Signal (30.14) with an expanding histogram (+23.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1507.99). Daily volatility envelope is bounded by ATR(14) of ₹59.33.</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,721.00) is positioned above the 30-day DMA (₹1,505.99), 50-day DMA (₹1,472.15), and 200-day DMA (₹1,507.99). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>[302.45, 303.8, 305.15, 306.5, 307.85, 309.19]</t>
+          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>[302.45, 307.91, 310.96, 313.62, 316.07, 318.39]</t>
+          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.2, 1823.74]</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>[302.45, 300.71, 300.79, 301.15, 301.68, 302.3]</t>
+          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
         </is>
       </c>
     </row>
@@ -3834,162 +3834,136 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>76187.09</v>
+        <v>263368.34</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1721</v>
-      </c>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>₹1709.13 - ₹1738.8</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>1768.46</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>56</v>
+        <v>500</v>
       </c>
       <c r="J21" t="n">
-        <v>1505.99</v>
+        <v>2687.36</v>
       </c>
       <c r="K21" t="n">
-        <v>1472.15</v>
+        <v>2675.37</v>
       </c>
       <c r="L21" t="n">
-        <v>1507.99</v>
+        <v>2568.56</v>
       </c>
       <c r="M21" t="n">
-        <v>15.58</v>
+        <v>7.39</v>
       </c>
       <c r="N21" t="n">
-        <v>53.48</v>
+        <v>13.44</v>
       </c>
       <c r="O21" t="n">
-        <v>30.14</v>
+        <v>8.58</v>
       </c>
       <c r="P21" t="n">
-        <v>23.34</v>
+        <v>4.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.33</v>
+        <v>54.77</v>
       </c>
       <c r="R21" t="n">
         <v>11.76</v>
       </c>
       <c r="S21" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-2.44</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>48.3</v>
+        <v>55</v>
       </c>
       <c r="W21" t="n">
-        <v>7.48</v>
+        <v>1.88</v>
       </c>
       <c r="X21" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1705.17</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1765.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1734.77</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1632.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1713.83</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1745.96</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1770.93</v>
-      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>77.3</v>
+        <v>65.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.16</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Vol Spike 3.9x | TTM Squeeze | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI21" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>35.2</v>
+        <v>55.2</v>
       </c>
       <c r="AK21" t="n">
-        <v>49.9</v>
+        <v>17.9</v>
       </c>
       <c r="AL21" t="n">
-        <v>9.6</v>
+        <v>12.8</v>
       </c>
       <c r="AM21" t="n">
         <v>15</v>
       </c>
-      <c r="AN21" t="n">
-        <v>1787.32</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1656.89</v>
-      </c>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,187.09 Cr., a P/E ratio of 35.21, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹263,368.34 Cr., a P/E ratio of 55.24, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.48) trades above Signal (30.14) with an expanding histogram (+23.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1507.99). Daily volatility envelope is bounded by ATR(14) of ₹59.33.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.78 (Bullish Momentum Zone), while MACD Line (13.44) trades above Signal (8.58) with an expanding histogram (+4.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.39% above the 200-day DMA (₹2568.56). Daily volatility envelope is bounded by ATR(14) of ₹54.77.</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,721.00) is positioned above the 30-day DMA (₹1,505.99), 50-day DMA (₹1,472.15), and 200-day DMA (₹1,507.99). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹nan) is positioned above the 30-day DMA (₹2,687.36), 50-day DMA (₹2,675.37), and 200-day DMA (₹2,568.56). The price distance from 200 DMA is +7.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>[1721.0, 1730.98, 1740.97, 1750.95, 1760.93, 1770.91]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[1721.0, 1754.71, 1774.53, 1792.05, 1808.39, 1823.98]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>[1721.0, 1713.18, 1715.79, 1720.12, 1725.33, 1731.11]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -719,7 +719,7 @@
         <v>11.76</v>
       </c>
       <c r="S2" t="n">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
       <c r="T2" t="n">
         <v>0.32</v>
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1461.91</v>
+        <v>1462.82</v>
       </c>
       <c r="AO2" t="n">
-        <v>1409.62</v>
+        <v>1410.75</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>215046.57</v>
+        <v>129536.96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,145 +845,145 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7833.5</v>
+        <v>112.71</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹7803.39 - ₹7878.67</t>
+          <t>₹112.3 - ₹113.33</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7953.95</v>
+        <v>114.37</v>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>1607</v>
       </c>
       <c r="J3" t="n">
-        <v>7437.81</v>
+        <v>107.66</v>
       </c>
       <c r="K3" t="n">
-        <v>7344.46</v>
+        <v>106.31</v>
       </c>
       <c r="L3" t="n">
-        <v>7171.21</v>
+        <v>112.63</v>
       </c>
       <c r="M3" t="n">
-        <v>9.19</v>
+        <v>-0.88</v>
       </c>
       <c r="N3" t="n">
-        <v>121.41</v>
+        <v>1.59</v>
       </c>
       <c r="O3" t="n">
-        <v>84.98999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>36.42</v>
+        <v>0.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>150.57</v>
+        <v>2.07</v>
       </c>
       <c r="R3" t="n">
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="T3" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="V3" t="n">
-        <v>48.3</v>
+        <v>51.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.92</v>
+        <v>3.29</v>
       </c>
       <c r="X3" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>7803.14</v>
+        <v>111.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>8059.35</v>
+        <v>115.27</v>
       </c>
       <c r="AA3" t="n">
-        <v>7920.64</v>
+        <v>113.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>7607.65</v>
+        <v>109.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>7842.17</v>
+        <v>112.47</v>
       </c>
       <c r="AD3" t="n">
-        <v>7890.34</v>
+        <v>113.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>7947.17</v>
+        <v>113.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>74.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI3" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ3" t="n">
-        <v>37.3</v>
+        <v>5.9</v>
       </c>
       <c r="AK3" t="n">
-        <v>31.5</v>
+        <v>15.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>23.2</v>
+        <v>38.1</v>
       </c>
       <c r="AM3" t="n">
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>8050.52</v>
+        <v>115.94</v>
       </c>
       <c r="AO3" t="n">
-        <v>7641</v>
+        <v>109.65</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹215,046.57 Cr., a P/E ratio of 37.31, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹129,536.96 Cr., a P/E ratio of 5.86, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.10 (Bullish Momentum Zone), while MACD Line (121.41) trades above Signal (84.99) with an expanding histogram (+36.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.19% above the 200-day DMA (₹7171.21). Daily volatility envelope is bounded by ATR(14) of ₹150.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.92 (Bullish Momentum Zone), while MACD Line (1.59) trades above Signal (1.18) with an expanding histogram (+0.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading -0.88% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.07.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,833.50) is positioned above the 30-day DMA (₹7,437.81), 50-day DMA (₹7,344.46), and 200-day DMA (₹7,171.21). The price distance from 200 DMA is +9.19%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹112.71) is positioned above the 30-day DMA (₹107.66), 50-day DMA (₹106.31), and 200-day DMA (₹112.63). The price distance from 200 DMA is -0.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[7833.5, 7920.64, 8007.78, 8094.92, 8182.07, 8269.21]</t>
+          <t>[112.71, 113.05, 113.39, 113.72, 114.06, 114.4]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[7833.5, 7980.87, 8092.96, 8199.24, 8302.52, 8403.88]</t>
+          <t>[112.71, 113.88, 114.56, 115.16, 115.72, 116.26]</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>[7833.5, 7875.47, 7943.9, 8016.69, 8091.73, 8168.2]</t>
+          <t>[112.71, 112.43, 112.51, 112.65, 112.82, 113.01]</t>
         </is>
       </c>
     </row>
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>129536.96</v>
+        <v>215046.57</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,145 +1012,145 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>112.71</v>
+        <v>7833.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹112.3 - ₹113.33</t>
+          <t>₹7803.39 - ₹7878.67</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>114.37</v>
+        <v>7953.95</v>
       </c>
       <c r="I4" t="n">
-        <v>1607</v>
+        <v>22</v>
       </c>
       <c r="J4" t="n">
-        <v>107.66</v>
+        <v>7437.81</v>
       </c>
       <c r="K4" t="n">
-        <v>106.31</v>
+        <v>7344.46</v>
       </c>
       <c r="L4" t="n">
-        <v>112.63</v>
+        <v>7171.21</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.88</v>
+        <v>9.19</v>
       </c>
       <c r="N4" t="n">
-        <v>1.59</v>
+        <v>121.41</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.41</v>
+        <v>36.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.07</v>
+        <v>150.57</v>
       </c>
       <c r="R4" t="n">
         <v>11.76</v>
       </c>
       <c r="S4" t="n">
-        <v>58.5</v>
+        <v>55.6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.68</v>
+        <v>-0.66</v>
       </c>
       <c r="V4" t="n">
-        <v>51.7</v>
+        <v>48.3</v>
       </c>
       <c r="W4" t="n">
-        <v>3.29</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>111.33</v>
+        <v>7803.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>115.27</v>
+        <v>8059.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>113.61</v>
+        <v>7920.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>109.6</v>
+        <v>7607.65</v>
       </c>
       <c r="AC4" t="n">
-        <v>112.47</v>
+        <v>7842.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>113.25</v>
+        <v>7890.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>113.78</v>
+        <v>7947.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI4" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5.9</v>
+        <v>37.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>15.2</v>
+        <v>31.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>38.1</v>
+        <v>23.2</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>115.77</v>
+        <v>8043.65</v>
       </c>
       <c r="AO4" t="n">
-        <v>109.52</v>
+        <v>7643.78</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹129,536.96 Cr., a P/E ratio of 5.86, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹215,046.57 Cr., a P/E ratio of 37.31, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.92 (Bullish Momentum Zone), while MACD Line (1.59) trades above Signal (1.18) with an expanding histogram (+0.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading -0.88% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.10 (Bullish Momentum Zone), while MACD Line (121.41) trades above Signal (84.99) with an expanding histogram (+36.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.19% above the 200-day DMA (₹7171.21). Daily volatility envelope is bounded by ATR(14) of ₹150.57.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹112.71) is positioned above the 30-day DMA (₹107.66), 50-day DMA (₹106.31), and 200-day DMA (₹112.63). The price distance from 200 DMA is -0.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,833.50) is positioned above the 30-day DMA (₹7,437.81), 50-day DMA (₹7,344.46), and 200-day DMA (₹7,171.21). The price distance from 200 DMA is +9.19%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[112.71, 113.05, 113.39, 113.72, 114.06, 114.4]</t>
+          <t>[7833.5, 7920.87, 8008.25, 8095.62, 8183.0, 8270.37]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[112.71, 113.88, 114.56, 115.16, 115.72, 116.26]</t>
+          <t>[7833.5, 7981.1, 8093.42, 8199.94, 8303.45, 8405.04]</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>[112.71, 112.43, 112.51, 112.65, 112.82, 113.01]</t>
+          <t>[7833.5, 7875.7, 7944.37, 8017.39, 8092.66, 8169.37]</t>
         </is>
       </c>
     </row>
@@ -1285,10 +1285,10 @@
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12158.3</v>
+        <v>12169.11</v>
       </c>
       <c r="AO5" t="n">
-        <v>11651.1</v>
+        <v>11641.9</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1329,16 +1329,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>105169.94</v>
+        <v>263368.34</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,145 +1346,145 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2199.8</v>
+        <v>2747.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2190.26 - ₹2214.11</t>
+          <t>₹2735.68 - ₹2764.73</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2237.97</v>
+        <v>2793.77</v>
       </c>
       <c r="I6" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="J6" t="n">
-        <v>2140.62</v>
+        <v>2687.86</v>
       </c>
       <c r="K6" t="n">
-        <v>2061.08</v>
+        <v>2678.76</v>
       </c>
       <c r="L6" t="n">
-        <v>1703.8</v>
+        <v>2570.71</v>
       </c>
       <c r="M6" t="n">
-        <v>27.05</v>
+        <v>6.83</v>
       </c>
       <c r="N6" t="n">
-        <v>29.77</v>
+        <v>16.14</v>
       </c>
       <c r="O6" t="n">
-        <v>35.4</v>
+        <v>10.09</v>
       </c>
       <c r="P6" t="n">
-        <v>-5.63</v>
+        <v>6.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>47.71</v>
+        <v>58.09</v>
       </c>
       <c r="R6" t="n">
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>55.9</v>
+        <v>57.9</v>
       </c>
       <c r="T6" t="n">
         <v>0.25</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.98</v>
+        <v>-0.87</v>
       </c>
       <c r="V6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="X6" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>2184.77</v>
+        <v>2706.99</v>
       </c>
       <c r="Z6" t="n">
-        <v>2261.76</v>
+        <v>2803.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>2217.76</v>
+        <v>2769.28</v>
       </c>
       <c r="AB6" t="n">
-        <v>2128.24</v>
+        <v>2660.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>2191.3</v>
+        <v>2751.53</v>
       </c>
       <c r="AD6" t="n">
-        <v>2221.1</v>
+        <v>2770.66</v>
       </c>
       <c r="AE6" t="n">
-        <v>2242.4</v>
+        <v>2794.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>57.9</v>
+        <v>62.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI6" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>97.09999999999999</v>
+        <v>55.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>6.4</v>
+        <v>12.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>2269.42</v>
+        <v>2811.63</v>
       </c>
       <c r="AO6" t="n">
-        <v>2140.59</v>
+        <v>2688.27</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹263,368.34 Cr., a P/E ratio of 55.24, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.38 (Bullish Momentum Zone), while MACD Line (16.14) trades above Signal (10.09) with an expanding histogram (+6.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.83% above the 200-day DMA (₹2570.71). Daily volatility envelope is bounded by ATR(14) of ₹58.09.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,747.30) is positioned above the 30-day DMA (₹2,687.86), 50-day DMA (₹2,678.76), and 200-day DMA (₹2,570.71). The price distance from 200 DMA is +6.83%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2199.8, 2217.76, 2235.73, 2253.69, 2271.66, 2289.62]</t>
+          <t>[2747.3, 2755.54, 2763.78, 2772.03, 2780.27, 2788.51]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2199.8, 2236.85, 2262.72, 2286.74, 2309.82, 2332.29]</t>
+          <t>[2747.3, 2778.78, 2796.64, 2812.27, 2826.74, 2840.46]</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>[2199.8, 2203.45, 2215.49, 2228.9, 2243.03, 2257.62]</t>
+          <t>[2747.3, 2738.12, 2739.14, 2741.84, 2745.42, 2749.54]</t>
         </is>
       </c>
     </row>
@@ -1496,162 +1496,162 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98206.09</v>
+        <v>105169.94</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🟢 HIGH CONVICTION BUY</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>372.95</v>
+        <v>2199.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹371.41 - ₹375.26</t>
+          <t>₹2190.26 - ₹2214.11</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>379.11</v>
+        <v>2237.97</v>
       </c>
       <c r="I7" t="n">
-        <v>432</v>
+        <v>69</v>
       </c>
       <c r="J7" t="n">
-        <v>357.21</v>
+        <v>2140.62</v>
       </c>
       <c r="K7" t="n">
-        <v>349.78</v>
+        <v>2061.08</v>
       </c>
       <c r="L7" t="n">
-        <v>347.56</v>
+        <v>1703.8</v>
       </c>
       <c r="M7" t="n">
-        <v>6.64</v>
+        <v>27.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.07</v>
+        <v>29.77</v>
       </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>35.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>-5.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.7</v>
+        <v>47.71</v>
       </c>
       <c r="R7" t="n">
         <v>11.76</v>
       </c>
       <c r="S7" t="n">
-        <v>52.9</v>
+        <v>56.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.04</v>
+        <v>-0.97</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
       </c>
       <c r="W7" t="n">
-        <v>2.81</v>
+        <v>1.78</v>
       </c>
       <c r="X7" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>366.16</v>
+        <v>2184.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>379.22</v>
+        <v>2261.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>375.93</v>
+        <v>2217.76</v>
       </c>
       <c r="AB7" t="n">
-        <v>361.4</v>
+        <v>2128.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>372.32</v>
+        <v>2191.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>374.64</v>
+        <v>2221.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>376.32</v>
+        <v>2242.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>78.3</v>
+        <v>57.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI7" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AK7" t="n">
-        <v>25.2</v>
+        <v>17.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>68.90000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AM7" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>383.24</v>
+        <v>2271.94</v>
       </c>
       <c r="AO7" t="n">
-        <v>363.08</v>
+        <v>2138.69</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
+          <t>[2199.8, 2217.76, 2235.72, 2253.68, 2271.64, 2289.6]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
+          <t>[2199.8, 2236.84, 2262.71, 2286.73, 2309.8, 2332.27]</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
+          <t>[2199.8, 2203.45, 2215.48, 2228.89, 2243.01, 2257.59]</t>
         </is>
       </c>
     </row>
@@ -1721,19 +1721,19 @@
         <v>11.76</v>
       </c>
       <c r="S8" t="n">
-        <v>51.4</v>
+        <v>52.2</v>
       </c>
       <c r="T8" t="n">
         <v>0.27</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.05</v>
+        <v>-1.02</v>
       </c>
       <c r="V8" t="n">
         <v>55</v>
       </c>
       <c r="W8" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
@@ -1742,7 +1742,7 @@
         <v>720.8200000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>725.26</v>
+        <v>725.27</v>
       </c>
       <c r="AA8" t="n">
         <v>744.46</v>
@@ -1786,10 +1786,10 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>756.83</v>
+        <v>758.26</v>
       </c>
       <c r="AO8" t="n">
-        <v>720.3099999999999</v>
+        <v>720.29</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -1830,162 +1830,162 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>310746.28</v>
+        <v>25000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4646.5</v>
+        <v>372.95</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹4629.85 - ₹4671.48</t>
+          <t>₹371.41 - ₹375.26</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4713.1</v>
+        <v>379.11</v>
       </c>
       <c r="I9" t="n">
-        <v>40</v>
+        <v>432</v>
       </c>
       <c r="J9" t="n">
-        <v>4471.9</v>
+        <v>357.21</v>
       </c>
       <c r="K9" t="n">
-        <v>4404.23</v>
+        <v>349.78</v>
       </c>
       <c r="L9" t="n">
-        <v>4346.03</v>
+        <v>347.56</v>
       </c>
       <c r="M9" t="n">
-        <v>5.42</v>
+        <v>6.64</v>
       </c>
       <c r="N9" t="n">
-        <v>56.6</v>
+        <v>4.07</v>
       </c>
       <c r="O9" t="n">
-        <v>49.9</v>
+        <v>2.35</v>
       </c>
       <c r="P9" t="n">
-        <v>6.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>83.25</v>
+        <v>7.7</v>
       </c>
       <c r="R9" t="n">
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>46.3</v>
+        <v>53.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.07</v>
+        <v>-1.03</v>
       </c>
       <c r="V9" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="W9" t="n">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="X9" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>4548.77</v>
+        <v>366.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>4711.39</v>
+        <v>379.22</v>
       </c>
       <c r="AA9" t="n">
-        <v>4683.67</v>
+        <v>375.93</v>
       </c>
       <c r="AB9" t="n">
-        <v>4521.62</v>
+        <v>361.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>4635.53</v>
+        <v>372.32</v>
       </c>
       <c r="AD9" t="n">
-        <v>4679.96</v>
+        <v>374.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>4713.43</v>
+        <v>376.32</v>
       </c>
       <c r="AF9" t="n">
-        <v>59.3</v>
+        <v>78.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI9" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34.1</v>
+        <v>6.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>25.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>27.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>4772.74</v>
+        <v>383.76</v>
       </c>
       <c r="AO9" t="n">
-        <v>4522.8</v>
+        <v>363.9</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[4646.5, 4660.44, 4674.38, 4688.32, 4702.26, 4716.2]</t>
+          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[4646.5, 4693.74, 4721.47, 4746.0, 4768.86, 4790.66]</t>
+          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>[4646.5, 4635.46, 4639.06, 4645.06, 4652.31, 4660.35]</t>
+          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
         </is>
       </c>
     </row>
@@ -1997,162 +1997,162 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68767.81</v>
+        <v>310746.28</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5751.5</v>
+        <v>4646.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹5727.01 - ₹5788.23</t>
+          <t>₹4629.85 - ₹4671.48</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5849.44</v>
+        <v>4713.1</v>
       </c>
       <c r="I10" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J10" t="n">
-        <v>5575</v>
+        <v>4471.9</v>
       </c>
       <c r="K10" t="n">
-        <v>5484.08</v>
+        <v>4404.23</v>
       </c>
       <c r="L10" t="n">
-        <v>5521.06</v>
+        <v>4346.03</v>
       </c>
       <c r="M10" t="n">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="N10" t="n">
-        <v>57.19</v>
+        <v>56.6</v>
       </c>
       <c r="O10" t="n">
-        <v>51.96</v>
+        <v>49.9</v>
       </c>
       <c r="P10" t="n">
-        <v>5.23</v>
+        <v>6.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>122.43</v>
+        <v>83.25</v>
       </c>
       <c r="R10" t="n">
         <v>11.76</v>
       </c>
       <c r="S10" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.11</v>
+        <v>-1.07</v>
       </c>
       <c r="V10" t="n">
-        <v>53.3</v>
+        <v>41.7</v>
       </c>
       <c r="W10" t="n">
-        <v>2.81</v>
+        <v>2.15</v>
       </c>
       <c r="X10" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>5710.85</v>
+        <v>4548.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>5912.15</v>
+        <v>4711.06</v>
       </c>
       <c r="AA10" t="n">
-        <v>5797.51</v>
+        <v>4683.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>5567.86</v>
+        <v>4521.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>5773.17</v>
+        <v>4635.53</v>
       </c>
       <c r="AD10" t="n">
-        <v>5811.34</v>
+        <v>4679.96</v>
       </c>
       <c r="AE10" t="n">
-        <v>5871.17</v>
+        <v>4713.43</v>
       </c>
       <c r="AF10" t="n">
-        <v>58.4</v>
+        <v>59.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI10" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>29.9</v>
+        <v>34.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>14.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
-        <v>15.6</v>
+        <v>27.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>17.6</v>
+        <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>5881.57</v>
+        <v>4770.72</v>
       </c>
       <c r="AO10" t="n">
-        <v>5624.81</v>
+        <v>4523.8</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,767.81 Cr., a P/E ratio of 29.85, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,751.50) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[5751.5, 5797.12, 5842.75, 5888.37, 5934.0, 5979.62]</t>
+          <t>[4646.5, 4660.44, 4674.38, 4688.32, 4702.26, 4716.2]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[5751.5, 5846.1, 5912.0, 5973.19, 6031.94, 6089.12]</t>
+          <t>[4646.5, 4693.74, 4721.47, 4746.0, 4768.86, 4790.66]</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>[5751.5, 5760.4, 5790.81, 5824.76, 5860.54, 5897.49]</t>
+          <t>[4646.5, 4635.46, 4639.06, 4645.06, 4652.31, 4660.35]</t>
         </is>
       </c>
     </row>
@@ -2164,16 +2164,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>133901.31</v>
+        <v>68767.81</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2181,145 +2181,145 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3760</v>
+        <v>5751.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹3740.59 - ₹3789.12</t>
+          <t>₹5727.01 - ₹5788.23</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3837.66</v>
+        <v>5849.44</v>
       </c>
       <c r="I11" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J11" t="n">
-        <v>3594.31</v>
+        <v>5575</v>
       </c>
       <c r="K11" t="n">
-        <v>3627.85</v>
+        <v>5484.08</v>
       </c>
       <c r="L11" t="n">
-        <v>3330.53</v>
+        <v>5521.06</v>
       </c>
       <c r="M11" t="n">
-        <v>9.859999999999999</v>
+        <v>5.35</v>
       </c>
       <c r="N11" t="n">
-        <v>22.06</v>
+        <v>57.19</v>
       </c>
       <c r="O11" t="n">
-        <v>10.09</v>
+        <v>51.96</v>
       </c>
       <c r="P11" t="n">
-        <v>11.97</v>
+        <v>5.23</v>
       </c>
       <c r="Q11" t="n">
-        <v>97.06999999999999</v>
+        <v>122.43</v>
       </c>
       <c r="R11" t="n">
         <v>11.76</v>
       </c>
       <c r="S11" t="n">
-        <v>56.7</v>
+        <v>51.8</v>
       </c>
       <c r="T11" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.22</v>
+        <v>-1.12</v>
       </c>
       <c r="V11" t="n">
         <v>53.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.23</v>
+        <v>2.81</v>
       </c>
       <c r="X11" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>3684.03</v>
+        <v>5710.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>3815.63</v>
+        <v>5912.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>3790.08</v>
+        <v>5797.51</v>
       </c>
       <c r="AB11" t="n">
-        <v>3614.39</v>
+        <v>5567.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>3743.5</v>
+        <v>5773.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>3824.9</v>
+        <v>5811.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>3889.8</v>
+        <v>5871.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>74.09999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI11" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>79.40000000000001</v>
+        <v>29.9</v>
       </c>
       <c r="AK11" t="n">
         <v>14.6</v>
       </c>
       <c r="AL11" t="n">
-        <v>9.5</v>
+        <v>15.6</v>
       </c>
       <c r="AM11" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>3877.01</v>
+        <v>5889.8</v>
       </c>
       <c r="AO11" t="n">
-        <v>3657.42</v>
+        <v>5621.92</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,901.31 Cr., a P/E ratio of 79.36, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,767.81 Cr., a P/E ratio of 29.85, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,760.00) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,751.50) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[3760.0, 3771.28, 3782.56, 3793.84, 3805.12, 3816.4]</t>
+          <t>[5751.5, 5797.12, 5842.75, 5888.37, 5934.0, 5979.62]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[3760.0, 3810.11, 3837.47, 3861.1, 3882.78, 3903.23]</t>
+          <t>[5751.5, 5846.1, 5912.0, 5973.19, 6031.94, 6089.12]</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>[3760.0, 3742.16, 3741.37, 3743.4, 3746.88, 3751.28]</t>
+          <t>[5751.5, 5760.4, 5790.81, 5824.76, 5860.54, 5897.49]</t>
         </is>
       </c>
     </row>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>119011.76</v>
+        <v>133901.31</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2348,145 +2348,145 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1473.2</v>
+        <v>3760</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹1466.31 - ₹1483.53</t>
+          <t>₹3740.59 - ₹3789.12</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1500.76</v>
+        <v>3837.66</v>
       </c>
       <c r="I12" t="n">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="J12" t="n">
-        <v>1436.14</v>
+        <v>3594.31</v>
       </c>
       <c r="K12" t="n">
-        <v>1414.83</v>
+        <v>3627.85</v>
       </c>
       <c r="L12" t="n">
-        <v>1396.09</v>
+        <v>3330.53</v>
       </c>
       <c r="M12" t="n">
-        <v>5.04</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.130000000000001</v>
+        <v>22.06</v>
       </c>
       <c r="O12" t="n">
-        <v>6.31</v>
+        <v>10.09</v>
       </c>
       <c r="P12" t="n">
-        <v>1.82</v>
+        <v>11.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>34.45</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>11.76</v>
       </c>
       <c r="S12" t="n">
-        <v>52</v>
+        <v>56.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.27</v>
+        <v>-1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>45</v>
+        <v>53.3</v>
       </c>
       <c r="W12" t="n">
-        <v>11.03</v>
+        <v>2.23</v>
       </c>
       <c r="X12" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>1431.86</v>
+        <v>3684.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>1388.21</v>
+        <v>3815.63</v>
       </c>
       <c r="AA12" t="n">
-        <v>1484.99</v>
+        <v>3790.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1421.52</v>
+        <v>3614.39</v>
       </c>
       <c r="AC12" t="n">
-        <v>1471.43</v>
+        <v>3743.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1480.56</v>
+        <v>3824.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>1487.93</v>
+        <v>3889.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>56.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.08</v>
+        <v>0.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI12" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>35.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.5</v>
+        <v>14.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="AM12" t="n">
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>1504.58</v>
+        <v>3874.11</v>
       </c>
       <c r="AO12" t="n">
-        <v>1443.2</v>
+        <v>3649.9</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,901.31 Cr., a P/E ratio of 79.36, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,760.00) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
+          <t>[3760.0, 3771.28, 3782.56, 3793.84, 3805.12, 3816.4]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
+          <t>[3760.0, 3810.11, 3837.47, 3861.1, 3882.78, 3903.23]</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
+          <t>[3760.0, 3742.16, 3741.37, 3743.4, 3746.88, 3751.28]</t>
         </is>
       </c>
     </row>
@@ -2498,16 +2498,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>246283.11</v>
+        <v>119011.76</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2515,90 +2515,90 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1046.7</v>
+        <v>1473.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1040.39 - ₹1056.17</t>
+          <t>₹1466.31 - ₹1483.53</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1071.96</v>
+        <v>1500.76</v>
       </c>
       <c r="I13" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J13" t="n">
-        <v>1032.61</v>
+        <v>1436.14</v>
       </c>
       <c r="K13" t="n">
-        <v>994.9400000000001</v>
+        <v>1414.83</v>
       </c>
       <c r="L13" t="n">
-        <v>942.9400000000001</v>
+        <v>1396.09</v>
       </c>
       <c r="M13" t="n">
-        <v>8.94</v>
+        <v>5.04</v>
       </c>
       <c r="N13" t="n">
-        <v>8.390000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>12.02</v>
+        <v>6.31</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.63</v>
+        <v>1.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>31.57</v>
+        <v>34.45</v>
       </c>
       <c r="R13" t="n">
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>56.5</v>
+        <v>51.9</v>
       </c>
       <c r="T13" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.52</v>
+        <v>-1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="W13" t="n">
-        <v>3.38</v>
+        <v>11.03</v>
       </c>
       <c r="X13" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>1019.37</v>
+        <v>1431.86</v>
       </c>
       <c r="Z13" t="n">
-        <v>1056.01</v>
+        <v>1388.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1055.07</v>
+        <v>1484.99</v>
       </c>
       <c r="AB13" t="n">
-        <v>999.34</v>
+        <v>1421.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>1043.47</v>
+        <v>1471.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>1057.84</v>
+        <v>1480.56</v>
       </c>
       <c r="AE13" t="n">
-        <v>1068.97</v>
+        <v>1487.93</v>
       </c>
       <c r="AF13" t="n">
-        <v>46.1</v>
+        <v>56.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2609,51 +2609,51 @@
         <v>0.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>18.5</v>
+        <v>35.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>39.1</v>
+        <v>3.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>50.1</v>
+        <v>12</v>
       </c>
       <c r="AM13" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>1087.24</v>
+        <v>1505.91</v>
       </c>
       <c r="AO13" t="n">
-        <v>1010.62</v>
+        <v>1440.51</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹246,283.11 Cr., a P/E ratio of 18.48, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,046.70) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1046.7, 1049.84, 1052.98, 1056.12, 1059.26, 1062.4]</t>
+          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1046.7, 1062.47, 1070.84, 1077.99, 1084.52, 1090.64]</t>
+          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>[1046.7, 1040.37, 1039.59, 1039.72, 1040.32, 1041.22]</t>
+          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
         </is>
       </c>
     </row>
@@ -2665,16 +2665,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>85420.58</v>
+        <v>246283.11</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2682,145 +2682,145 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14049</v>
+        <v>1046.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹13965.8 - ₹14173.8</t>
+          <t>₹1040.39 - ₹1056.17</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>14381.8</v>
+        <v>1071.96</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="J14" t="n">
-        <v>13190.57</v>
+        <v>1032.61</v>
       </c>
       <c r="K14" t="n">
-        <v>12605.68</v>
+        <v>994.9400000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>12333.95</v>
+        <v>942.9400000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>16.25</v>
+        <v>8.94</v>
       </c>
       <c r="N14" t="n">
-        <v>477.1</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>503.84</v>
+        <v>12.02</v>
       </c>
       <c r="P14" t="n">
-        <v>-26.74</v>
+        <v>-3.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>416</v>
+        <v>31.57</v>
       </c>
       <c r="R14" t="n">
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>51.3</v>
+        <v>56.4</v>
       </c>
       <c r="T14" t="n">
         <v>0.18</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.75</v>
+        <v>-1.52</v>
       </c>
       <c r="V14" t="n">
-        <v>46.7</v>
+        <v>55</v>
       </c>
       <c r="W14" t="n">
-        <v>6.67</v>
+        <v>3.38</v>
       </c>
       <c r="X14" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>13634.58</v>
+        <v>1019.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>14126.3</v>
+        <v>1056.01</v>
       </c>
       <c r="AA14" t="n">
-        <v>14161.39</v>
+        <v>1055.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>13425</v>
+        <v>999.34</v>
       </c>
       <c r="AC14" t="n">
-        <v>14079.67</v>
+        <v>1043.47</v>
       </c>
       <c r="AD14" t="n">
-        <v>14558.34</v>
+        <v>1057.84</v>
       </c>
       <c r="AE14" t="n">
-        <v>15067.67</v>
+        <v>1068.97</v>
       </c>
       <c r="AF14" t="n">
-        <v>64.7</v>
+        <v>46.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI14" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>41.2</v>
+        <v>18.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>21.1</v>
+        <v>39.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.6</v>
+        <v>50.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>14590.27</v>
+        <v>1085.79</v>
       </c>
       <c r="AO14" t="n">
-        <v>13527.74</v>
+        <v>1009.74</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹246,283.11 Cr., a P/E ratio of 18.48, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,046.70) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
+          <t>[1046.7, 1049.84, 1052.98, 1056.12, 1059.26, 1062.4]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
+          <t>[1046.7, 1062.47, 1070.84, 1077.99, 1084.52, 1090.64]</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
+          <t>[1046.7, 1040.37, 1039.59, 1039.72, 1040.32, 1041.22]</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>146280.27</v>
+        <v>85420.58</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2849,145 +2849,145 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1651.3</v>
+        <v>14049</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹1641.81 - ₹1665.54</t>
+          <t>₹13965.8 - ₹14173.8</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1689.26</v>
+        <v>14381.8</v>
       </c>
       <c r="I15" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>1478.49</v>
+        <v>13190.57</v>
       </c>
       <c r="K15" t="n">
-        <v>1460.44</v>
+        <v>12605.68</v>
       </c>
       <c r="L15" t="n">
-        <v>1458.79</v>
+        <v>12333.95</v>
       </c>
       <c r="M15" t="n">
-        <v>14.41</v>
+        <v>16.25</v>
       </c>
       <c r="N15" t="n">
-        <v>56.22</v>
+        <v>477.1</v>
       </c>
       <c r="O15" t="n">
-        <v>42.84</v>
+        <v>503.84</v>
       </c>
       <c r="P15" t="n">
-        <v>13.38</v>
+        <v>-26.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>47.45</v>
+        <v>416</v>
       </c>
       <c r="R15" t="n">
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>49.3</v>
+        <v>50.6</v>
       </c>
       <c r="T15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="U15" t="n">
         <v>-1.79</v>
       </c>
       <c r="V15" t="n">
-        <v>48.3</v>
+        <v>46.7</v>
       </c>
       <c r="W15" t="n">
-        <v>8.69</v>
+        <v>6.67</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>1625.35</v>
+        <v>13634.81</v>
       </c>
       <c r="Z15" t="n">
-        <v>1683.14</v>
+        <v>14126.52</v>
       </c>
       <c r="AA15" t="n">
-        <v>1664.51</v>
+        <v>14161.39</v>
       </c>
       <c r="AB15" t="n">
-        <v>1580.13</v>
+        <v>13425</v>
       </c>
       <c r="AC15" t="n">
-        <v>1641.1</v>
+        <v>14079.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1671.7</v>
+        <v>14558.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>1692.1</v>
+        <v>15067.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>86.2</v>
+        <v>64.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>28.6</v>
+        <v>41.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>17.7</v>
+        <v>21.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>8.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AM15" t="n">
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>1695.31</v>
+        <v>14574.67</v>
       </c>
       <c r="AO15" t="n">
-        <v>1605.12</v>
+        <v>13507.87</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
+          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
+          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
+          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17572.27</v>
+        <v>146280.27</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3016,145 +3016,145 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>613.35</v>
+        <v>1651.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹608.87 - ₹620.07</t>
+          <t>₹1641.81 - ₹1665.54</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>631.27</v>
+        <v>1689.26</v>
       </c>
       <c r="I16" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="J16" t="n">
-        <v>578.01</v>
+        <v>1478.49</v>
       </c>
       <c r="K16" t="n">
-        <v>541.38</v>
+        <v>1460.44</v>
       </c>
       <c r="L16" t="n">
-        <v>553.54</v>
+        <v>1458.79</v>
       </c>
       <c r="M16" t="n">
-        <v>10.74</v>
+        <v>14.41</v>
       </c>
       <c r="N16" t="n">
-        <v>14.56</v>
+        <v>56.22</v>
       </c>
       <c r="O16" t="n">
-        <v>16.43</v>
+        <v>42.84</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.88</v>
+        <v>13.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>22.4</v>
+        <v>47.45</v>
       </c>
       <c r="R16" t="n">
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>57</v>
+        <v>49.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>53.3</v>
+        <v>48.3</v>
       </c>
       <c r="W16" t="n">
-        <v>4.8</v>
+        <v>8.69</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>590.26</v>
+        <v>1625.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>611.73</v>
+        <v>1683.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>618.26</v>
+        <v>1664.51</v>
       </c>
       <c r="AB16" t="n">
-        <v>579.75</v>
+        <v>1580.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>616.27</v>
+        <v>1641.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>624.54</v>
+        <v>1671.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>635.72</v>
+        <v>1692.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>60.8</v>
+        <v>86.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>88.5</v>
+        <v>28.6</v>
       </c>
       <c r="AK16" t="n">
-        <v>-10.1</v>
+        <v>17.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM16" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>648.13</v>
+        <v>1697.3</v>
       </c>
       <c r="AO16" t="n">
-        <v>582.21</v>
+        <v>1609.8</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
+          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
+          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
+          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
         </is>
       </c>
     </row>
@@ -3166,16 +3166,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63429.15</v>
+        <v>17572.27</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3183,145 +3183,145 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2105.7</v>
+        <v>613.35</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹2092.64 - ₹2125.3</t>
+          <t>₹608.87 - ₹620.07</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2157.96</v>
+        <v>631.27</v>
       </c>
       <c r="I17" t="n">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="J17" t="n">
-        <v>1999.45</v>
+        <v>578.01</v>
       </c>
       <c r="K17" t="n">
-        <v>1888.17</v>
+        <v>541.38</v>
       </c>
       <c r="L17" t="n">
-        <v>1880.41</v>
+        <v>553.54</v>
       </c>
       <c r="M17" t="n">
-        <v>12.26</v>
+        <v>10.74</v>
       </c>
       <c r="N17" t="n">
-        <v>62.25</v>
+        <v>14.56</v>
       </c>
       <c r="O17" t="n">
-        <v>68.98</v>
+        <v>16.43</v>
       </c>
       <c r="P17" t="n">
-        <v>-6.73</v>
+        <v>-1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>65.31999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="R17" t="n">
         <v>11.76</v>
       </c>
       <c r="S17" t="n">
-        <v>48.5</v>
+        <v>57.4</v>
       </c>
       <c r="T17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.01</v>
+        <v>-1.87</v>
       </c>
       <c r="V17" t="n">
-        <v>51.7</v>
+        <v>53.3</v>
       </c>
       <c r="W17" t="n">
-        <v>4.49</v>
+        <v>4.8</v>
       </c>
       <c r="X17" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y17" t="n">
-        <v>2027.32</v>
+        <v>590.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>2032.25</v>
+        <v>611.72</v>
       </c>
       <c r="AA17" t="n">
-        <v>2122.55</v>
+        <v>618.26</v>
       </c>
       <c r="AB17" t="n">
-        <v>2007.72</v>
+        <v>579.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2111.93</v>
+        <v>616.27</v>
       </c>
       <c r="AD17" t="n">
-        <v>2127.76</v>
+        <v>624.54</v>
       </c>
       <c r="AE17" t="n">
-        <v>2149.83</v>
+        <v>635.72</v>
       </c>
       <c r="AF17" t="n">
-        <v>48.8</v>
+        <v>60.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI17" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34.2</v>
+        <v>88.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>63</v>
+        <v>-10.1</v>
       </c>
       <c r="AL17" t="n">
-        <v>36.1</v>
+        <v>3.7</v>
       </c>
       <c r="AM17" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>2188.81</v>
+        <v>642.6900000000001</v>
       </c>
       <c r="AO17" t="n">
-        <v>2028.6</v>
+        <v>581.9</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
+          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
+          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
+          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
         </is>
       </c>
     </row>
@@ -3333,162 +3333,162 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>46194.13</v>
+        <v>63429.15</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1135.3</v>
+        <v>2105.7</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹1128.39 - ₹1145.67</t>
+          <t>₹2092.64 - ₹2125.3</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1162.95</v>
+        <v>2157.96</v>
       </c>
       <c r="I18" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="J18" t="n">
-        <v>1109.56</v>
+        <v>1999.45</v>
       </c>
       <c r="K18" t="n">
-        <v>1105.35</v>
+        <v>1888.17</v>
       </c>
       <c r="L18" t="n">
-        <v>1100.33</v>
+        <v>1880.41</v>
       </c>
       <c r="M18" t="n">
-        <v>3.87</v>
+        <v>12.26</v>
       </c>
       <c r="N18" t="n">
-        <v>9.130000000000001</v>
+        <v>62.25</v>
       </c>
       <c r="O18" t="n">
-        <v>4.71</v>
+        <v>68.98</v>
       </c>
       <c r="P18" t="n">
-        <v>4.42</v>
+        <v>-6.73</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.56</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="R18" t="n">
         <v>11.76</v>
       </c>
       <c r="S18" t="n">
-        <v>44.4</v>
+        <v>48.6</v>
       </c>
       <c r="T18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.18</v>
+        <v>-2</v>
       </c>
       <c r="V18" t="n">
-        <v>46.7</v>
+        <v>51.7</v>
       </c>
       <c r="W18" t="n">
-        <v>2.28</v>
+        <v>4.49</v>
       </c>
       <c r="X18" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y18" t="n">
-        <v>1114.01</v>
+        <v>2027.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>1153.74</v>
+        <v>2032.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>1144.38</v>
+        <v>2122.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1083.45</v>
+        <v>2007.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>1144.43</v>
+        <v>2111.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1156.86</v>
+        <v>2127.76</v>
       </c>
       <c r="AE18" t="n">
-        <v>1178.43</v>
+        <v>2149.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>52.9</v>
+        <v>48.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI18" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>37.7</v>
+        <v>34.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>29.9</v>
+        <v>63</v>
       </c>
       <c r="AL18" t="n">
-        <v>26.5</v>
+        <v>36.1</v>
       </c>
       <c r="AM18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AN18" t="n">
-        <v>1168.8</v>
+        <v>2181.15</v>
       </c>
       <c r="AO18" t="n">
-        <v>1101.74</v>
+        <v>2035.93</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,194.13 Cr., a P/E ratio of 37.73, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,135.30) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[1135.3, 1138.71, 1142.11, 1145.52, 1148.92, 1152.33]</t>
+          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[1135.3, 1152.53, 1161.66, 1169.46, 1176.58, 1183.24]</t>
+          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>[1135.3, 1128.34, 1127.45, 1127.56, 1128.19, 1129.14]</t>
+          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
         </is>
       </c>
     </row>
@@ -3500,162 +3500,162 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>278417.14</v>
+        <v>46194.13</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>302.45</v>
+        <v>1135.3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>₹300.39 - ₹305.53</t>
+          <t>₹1128.39 - ₹1145.67</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>310.68</v>
+        <v>1162.95</v>
       </c>
       <c r="I19" t="n">
-        <v>324</v>
+        <v>96</v>
       </c>
       <c r="J19" t="n">
-        <v>281.7</v>
+        <v>1109.56</v>
       </c>
       <c r="K19" t="n">
-        <v>268.93</v>
+        <v>1105.35</v>
       </c>
       <c r="L19" t="n">
-        <v>274.01</v>
+        <v>1100.33</v>
       </c>
       <c r="M19" t="n">
-        <v>13.37</v>
+        <v>3.87</v>
       </c>
       <c r="N19" t="n">
-        <v>9.93</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>8.42</v>
+        <v>4.71</v>
       </c>
       <c r="P19" t="n">
-        <v>1.51</v>
+        <v>4.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.28</v>
+        <v>34.56</v>
       </c>
       <c r="R19" t="n">
         <v>11.76</v>
       </c>
       <c r="S19" t="n">
-        <v>48.6</v>
+        <v>44.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.23</v>
+        <v>-2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="W19" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="X19" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>299.26</v>
+        <v>1114</v>
       </c>
       <c r="Z19" t="n">
-        <v>309.85</v>
+        <v>1153.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>304.87</v>
+        <v>1144.38</v>
       </c>
       <c r="AB19" t="n">
-        <v>287.03</v>
+        <v>1083.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>306.75</v>
+        <v>1144.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>311.7</v>
+        <v>1156.86</v>
       </c>
       <c r="AE19" t="n">
-        <v>320.95</v>
+        <v>1178.43</v>
       </c>
       <c r="AF19" t="n">
-        <v>65.40000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI19" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ19" t="n">
-        <v>672.1</v>
+        <v>37.7</v>
       </c>
       <c r="AK19" t="n">
-        <v>182</v>
+        <v>29.9</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.6</v>
+        <v>26.5</v>
       </c>
       <c r="AM19" t="n">
         <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>313.15</v>
+        <v>1171.19</v>
       </c>
       <c r="AO19" t="n">
-        <v>291.97</v>
+        <v>1101.74</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,194.13 Cr., a P/E ratio of 37.73, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,135.30) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>[302.45, 303.8, 305.15, 306.5, 307.85, 309.19]</t>
+          <t>[1135.3, 1138.71, 1142.11, 1145.52, 1148.92, 1152.33]</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>[302.45, 307.91, 310.96, 313.62, 316.07, 318.39]</t>
+          <t>[1135.3, 1152.53, 1161.66, 1169.46, 1176.58, 1183.24]</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>[302.45, 300.71, 300.79, 301.15, 301.68, 302.3]</t>
+          <t>[1135.3, 1128.34, 1127.45, 1127.56, 1128.19, 1129.14]</t>
         </is>
       </c>
     </row>
@@ -3667,162 +3667,162 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>76187.09</v>
+        <v>278417.14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1721</v>
+        <v>302.45</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>₹1709.13 - ₹1738.8</t>
+          <t>₹300.39 - ₹305.53</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1768.46</v>
+        <v>310.68</v>
       </c>
       <c r="I20" t="n">
-        <v>56</v>
+        <v>324</v>
       </c>
       <c r="J20" t="n">
-        <v>1505.99</v>
+        <v>281.7</v>
       </c>
       <c r="K20" t="n">
-        <v>1472.15</v>
+        <v>268.93</v>
       </c>
       <c r="L20" t="n">
-        <v>1507.99</v>
+        <v>274.01</v>
       </c>
       <c r="M20" t="n">
-        <v>15.58</v>
+        <v>13.37</v>
       </c>
       <c r="N20" t="n">
-        <v>53.48</v>
+        <v>9.93</v>
       </c>
       <c r="O20" t="n">
-        <v>30.14</v>
+        <v>8.42</v>
       </c>
       <c r="P20" t="n">
-        <v>23.34</v>
+        <v>1.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>59.33</v>
+        <v>10.28</v>
       </c>
       <c r="R20" t="n">
         <v>11.76</v>
       </c>
       <c r="S20" t="n">
-        <v>46.1</v>
+        <v>48.7</v>
       </c>
       <c r="T20" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.42</v>
+        <v>-2.23</v>
       </c>
       <c r="V20" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
       <c r="W20" t="n">
-        <v>7.48</v>
+        <v>2.44</v>
       </c>
       <c r="X20" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y20" t="n">
-        <v>1705.12</v>
+        <v>299.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>1765.36</v>
+        <v>309.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>1734.77</v>
+        <v>304.87</v>
       </c>
       <c r="AB20" t="n">
-        <v>1632.01</v>
+        <v>287.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1713.83</v>
+        <v>306.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1745.96</v>
+        <v>311.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>1770.93</v>
+        <v>320.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>77.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI20" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>35.2</v>
+        <v>672.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>49.9</v>
+        <v>182</v>
       </c>
       <c r="AL20" t="n">
-        <v>9.6</v>
+        <v>0.6</v>
       </c>
       <c r="AM20" t="n">
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>1789.44</v>
+        <v>313.15</v>
       </c>
       <c r="AO20" t="n">
-        <v>1653.38</v>
+        <v>292.51</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,187.09 Cr., a P/E ratio of 35.21, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.48) trades above Signal (30.14) with an expanding histogram (+23.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1507.99). Daily volatility envelope is bounded by ATR(14) of ₹59.33.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,721.00) is positioned above the 30-day DMA (₹1,505.99), 50-day DMA (₹1,472.15), and 200-day DMA (₹1,507.99). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
+          <t>[302.45, 303.8, 305.15, 306.5, 307.85, 309.19]</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.2, 1823.74]</t>
+          <t>[302.45, 307.91, 310.96, 313.62, 316.07, 318.39]</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
+          <t>[302.45, 300.71, 300.79, 301.15, 301.68, 302.3]</t>
         </is>
       </c>
     </row>
@@ -3834,136 +3834,162 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>263368.34</v>
+        <v>76187.09</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1721</v>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>₹1709.13 - ₹1738.8</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1768.46</v>
+      </c>
       <c r="I21" t="n">
-        <v>500</v>
+        <v>56</v>
       </c>
       <c r="J21" t="n">
-        <v>2687.36</v>
+        <v>1505.99</v>
       </c>
       <c r="K21" t="n">
-        <v>2675.37</v>
+        <v>1472.15</v>
       </c>
       <c r="L21" t="n">
-        <v>2568.56</v>
+        <v>1507.99</v>
       </c>
       <c r="M21" t="n">
-        <v>7.39</v>
+        <v>15.58</v>
       </c>
       <c r="N21" t="n">
-        <v>13.44</v>
+        <v>53.48</v>
       </c>
       <c r="O21" t="n">
-        <v>8.58</v>
+        <v>30.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.86</v>
+        <v>23.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>54.77</v>
+        <v>59.33</v>
       </c>
       <c r="R21" t="n">
         <v>11.76</v>
       </c>
       <c r="S21" t="n">
-        <v>54</v>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+        <v>45.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-2.45</v>
+      </c>
       <c r="V21" t="n">
-        <v>55</v>
+        <v>48.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.88</v>
+        <v>7.48</v>
       </c>
       <c r="X21" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>1705.12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1765.36</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1734.77</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1632.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1713.83</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1745.96</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1770.93</v>
+      </c>
       <c r="AF21" t="n">
-        <v>65.8</v>
+        <v>77.3</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Vol Spike 3.9x | TTM Squeeze | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI21" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>55.2</v>
+        <v>35.2</v>
       </c>
       <c r="AK21" t="n">
-        <v>17.9</v>
+        <v>49.9</v>
       </c>
       <c r="AL21" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="AM21" t="n">
         <v>15</v>
       </c>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
+      <c r="AN21" t="n">
+        <v>1786.32</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1653.57</v>
+      </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹263,368.34 Cr., a P/E ratio of 55.24, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,187.09 Cr., a P/E ratio of 35.21, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.78 (Bullish Momentum Zone), while MACD Line (13.44) trades above Signal (8.58) with an expanding histogram (+4.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.39% above the 200-day DMA (₹2568.56). Daily volatility envelope is bounded by ATR(14) of ₹54.77.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.48) trades above Signal (30.14) with an expanding histogram (+23.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1507.99). Daily volatility envelope is bounded by ATR(14) of ₹59.33.</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹nan) is positioned above the 30-day DMA (₹2,687.36), 50-day DMA (₹2,675.37), and 200-day DMA (₹2,568.56). The price distance from 200 DMA is +7.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,721.00) is positioned above the 30-day DMA (₹1,505.99), 50-day DMA (₹1,472.15), and 200-day DMA (₹1,507.99). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.21, 1823.74]</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU21"/>
+  <dimension ref="A1:AU16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,28 +719,28 @@
         <v>11.76</v>
       </c>
       <c r="S2" t="n">
-        <v>61.7</v>
+        <v>50.2</v>
       </c>
       <c r="T2" t="n">
         <v>0.32</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.48</v>
+        <v>-0.86</v>
       </c>
       <c r="V2" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="W2" t="n">
-        <v>6.24</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y2" t="n">
-        <v>1424.81</v>
+        <v>1415.53</v>
       </c>
       <c r="Z2" t="n">
-        <v>1471.73</v>
+        <v>1465.77</v>
       </c>
       <c r="AA2" t="n">
         <v>1446.88</v>
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1462.82</v>
+        <v>1492.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>1410.75</v>
+        <v>1383.2</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -806,17 +806,17 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[1435.4, 1446.34, 1457.29, 1468.23, 1479.18, 1490.12]</t>
+          <t>[1435.4, 1439.71, 1444.01, 1448.32, 1452.62, 1456.93]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[1435.4, 1456.03, 1470.99, 1485.02, 1498.56, 1511.79]</t>
+          <t>[1435.4, 1449.39, 1457.71, 1465.1, 1472.0, 1478.6]</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>[1435.4, 1439.08, 1447.01, 1455.65, 1464.65, 1473.88]</t>
+          <t>[1435.4, 1432.44, 1433.74, 1435.73, 1438.09, 1440.68]</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -886,28 +886,28 @@
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>59</v>
+        <v>50.4</v>
       </c>
       <c r="T3" t="n">
         <v>0.29</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.66</v>
+        <v>-0.97</v>
       </c>
       <c r="V3" t="n">
-        <v>51.7</v>
+        <v>51.5</v>
       </c>
       <c r="W3" t="n">
-        <v>3.29</v>
+        <v>2.23</v>
       </c>
       <c r="X3" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>111.33</v>
+        <v>111.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>115.27</v>
+        <v>115.19</v>
       </c>
       <c r="AA3" t="n">
         <v>113.61</v>
@@ -951,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>115.94</v>
+        <v>117.69</v>
       </c>
       <c r="AO3" t="n">
-        <v>109.65</v>
+        <v>107.9</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -995,162 +995,162 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>215046.57</v>
+        <v>310746.28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7833.5</v>
+        <v>4646.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹7803.39 - ₹7878.67</t>
+          <t>₹4629.85 - ₹4671.48</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>7953.95</v>
+        <v>4713.1</v>
       </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J4" t="n">
-        <v>7437.81</v>
+        <v>4471.9</v>
       </c>
       <c r="K4" t="n">
-        <v>7344.46</v>
+        <v>4404.23</v>
       </c>
       <c r="L4" t="n">
-        <v>7171.21</v>
+        <v>4346.03</v>
       </c>
       <c r="M4" t="n">
-        <v>9.19</v>
+        <v>5.42</v>
       </c>
       <c r="N4" t="n">
-        <v>121.41</v>
+        <v>56.6</v>
       </c>
       <c r="O4" t="n">
-        <v>84.98999999999999</v>
+        <v>49.9</v>
       </c>
       <c r="P4" t="n">
-        <v>36.42</v>
+        <v>6.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>150.57</v>
+        <v>83.25</v>
       </c>
       <c r="R4" t="n">
         <v>11.76</v>
       </c>
       <c r="S4" t="n">
-        <v>55.6</v>
+        <v>47.6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.66</v>
+        <v>-1.03</v>
       </c>
       <c r="V4" t="n">
-        <v>48.3</v>
+        <v>50.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>7803.37</v>
+        <v>4611.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>8059.35</v>
+        <v>4771.38</v>
       </c>
       <c r="AA4" t="n">
-        <v>7920.87</v>
+        <v>4683.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>7607.65</v>
+        <v>4521.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>7842.17</v>
+        <v>4635.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>7890.34</v>
+        <v>4679.96</v>
       </c>
       <c r="AE4" t="n">
-        <v>7947.17</v>
+        <v>4713.43</v>
       </c>
       <c r="AF4" t="n">
-        <v>74.09999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI4" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>37.3</v>
+        <v>34.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>31.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>23.2</v>
+        <v>27.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AN4" t="n">
-        <v>8043.65</v>
+        <v>4815.85</v>
       </c>
       <c r="AO4" t="n">
-        <v>7643.78</v>
+        <v>4473.38</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹215,046.57 Cr., a P/E ratio of 37.31, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.10 (Bullish Momentum Zone), while MACD Line (121.41) trades above Signal (84.99) with an expanding histogram (+36.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.19% above the 200-day DMA (₹7171.21). Daily volatility envelope is bounded by ATR(14) of ₹150.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,833.50) is positioned above the 30-day DMA (₹7,437.81), 50-day DMA (₹7,344.46), and 200-day DMA (₹7,171.21). The price distance from 200 DMA is +9.19%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[7833.5, 7920.87, 8008.25, 8095.62, 8183.0, 8270.37]</t>
+          <t>[4646.5, 4681.04, 4715.59, 4750.13, 4784.67, 4819.22]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[7833.5, 7981.1, 8093.42, 8199.94, 8303.45, 8405.04]</t>
+          <t>[4646.5, 4714.34, 4762.68, 4807.81, 4851.27, 4893.68]</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>[7833.5, 7875.7, 7944.37, 8017.39, 8092.66, 8169.37]</t>
+          <t>[4646.5, 4656.07, 4680.27, 4706.87, 4734.72, 4763.37]</t>
         </is>
       </c>
     </row>
@@ -1162,162 +1162,162 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>350150.12</v>
+        <v>98206.09</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11903</v>
+        <v>372.95</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹11859.37 - ₹11968.45</t>
+          <t>₹371.41 - ₹375.26</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12077.53</v>
+        <v>379.11</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>432</v>
       </c>
       <c r="J5" t="n">
-        <v>11421.23</v>
+        <v>357.21</v>
       </c>
       <c r="K5" t="n">
-        <v>11269.86</v>
+        <v>349.78</v>
       </c>
       <c r="L5" t="n">
-        <v>11569.69</v>
+        <v>347.56</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4</v>
+        <v>6.64</v>
       </c>
       <c r="N5" t="n">
-        <v>143.27</v>
+        <v>4.07</v>
       </c>
       <c r="O5" t="n">
-        <v>124.24</v>
+        <v>2.35</v>
       </c>
       <c r="P5" t="n">
-        <v>19.02</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>218.17</v>
+        <v>7.7</v>
       </c>
       <c r="R5" t="n">
         <v>11.76</v>
       </c>
       <c r="S5" t="n">
-        <v>57.9</v>
+        <v>52.1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.07</v>
       </c>
       <c r="V5" t="n">
-        <v>48.3</v>
+        <v>53.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.67</v>
+        <v>4.29</v>
       </c>
       <c r="X5" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>11732.12</v>
+        <v>368.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>12148.72</v>
+        <v>381.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>11998.22</v>
+        <v>375.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>11575.75</v>
+        <v>361.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>11903.67</v>
+        <v>372.32</v>
       </c>
       <c r="AD5" t="n">
-        <v>12008.34</v>
+        <v>374.64</v>
       </c>
       <c r="AE5" t="n">
-        <v>12113.67</v>
+        <v>376.32</v>
       </c>
       <c r="AF5" t="n">
-        <v>62.6</v>
+        <v>78.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.23</v>
+        <v>0.08</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI5" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ5" t="n">
-        <v>41</v>
+        <v>6.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>15.9</v>
+        <v>25.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>9.300000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AM5" t="n">
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12169.11</v>
+        <v>388.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>11641.9</v>
+        <v>357.92</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹350,150.12 Cr., a P/E ratio of 40.98, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (143.27) trades above Signal (124.24) with an expanding histogram (+19.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.40% above the 200-day DMA (₹11569.69). Daily volatility envelope is bounded by ATR(14) of ₹218.17.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,903.00) is positioned above the 30-day DMA (₹11,421.23), 50-day DMA (₹11,269.86), and 200-day DMA (₹11,569.69). The price distance from 200 DMA is +2.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[11903.0, 11938.71, 11974.42, 12010.13, 12045.84, 12081.54]</t>
+          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[11903.0, 12025.98, 12097.83, 12161.28, 12220.37, 12276.68]</t>
+          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>[11903.0, 11873.26, 11881.86, 11896.76, 11914.94, 11935.19]</t>
+          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
         </is>
       </c>
     </row>
@@ -1329,162 +1329,162 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>263368.34</v>
+        <v>215046.57</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2747.3</v>
+        <v>7833.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2735.68 - ₹2764.73</t>
+          <t>₹7803.39 - ₹7878.67</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2793.77</v>
+        <v>7953.95</v>
       </c>
       <c r="I6" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>2687.86</v>
+        <v>7437.81</v>
       </c>
       <c r="K6" t="n">
-        <v>2678.76</v>
+        <v>7344.46</v>
       </c>
       <c r="L6" t="n">
-        <v>2570.71</v>
+        <v>7171.21</v>
       </c>
       <c r="M6" t="n">
-        <v>6.83</v>
+        <v>9.19</v>
       </c>
       <c r="N6" t="n">
-        <v>16.14</v>
+        <v>121.41</v>
       </c>
       <c r="O6" t="n">
-        <v>10.09</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>6.05</v>
+        <v>36.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>58.09</v>
+        <v>150.57</v>
       </c>
       <c r="R6" t="n">
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>57.9</v>
+        <v>48.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.87</v>
+        <v>-1.1</v>
       </c>
       <c r="V6" t="n">
-        <v>55</v>
+        <v>50.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>5.13</v>
       </c>
       <c r="X6" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>2706.99</v>
+        <v>7728.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2803.14</v>
+        <v>8002.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>2769.28</v>
+        <v>7896.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>2660.17</v>
+        <v>7607.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>2751.53</v>
+        <v>7842.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>2770.66</v>
+        <v>7890.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>2794.03</v>
+        <v>7947.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>62.4</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.03</v>
+        <v>0.19</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI6" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55.2</v>
+        <v>37.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.9</v>
+        <v>31.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>12.8</v>
+        <v>23.2</v>
       </c>
       <c r="AM6" t="n">
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>2811.63</v>
+        <v>9251.1</v>
       </c>
       <c r="AO6" t="n">
-        <v>2688.27</v>
+        <v>6460.02</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹263,368.34 Cr., a P/E ratio of 55.24, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹215,046.57 Cr., a P/E ratio of 37.31, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.38 (Bullish Momentum Zone), while MACD Line (16.14) trades above Signal (10.09) with an expanding histogram (+6.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.83% above the 200-day DMA (₹2570.71). Daily volatility envelope is bounded by ATR(14) of ₹58.09.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.10 (Bullish Momentum Zone), while MACD Line (121.41) trades above Signal (84.99) with an expanding histogram (+36.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.19% above the 200-day DMA (₹7171.21). Daily volatility envelope is bounded by ATR(14) of ₹150.57.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,747.30) is positioned above the 30-day DMA (₹2,687.86), 50-day DMA (₹2,678.76), and 200-day DMA (₹2,570.71). The price distance from 200 DMA is +6.83%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,833.50) is positioned above the 30-day DMA (₹7,437.81), 50-day DMA (₹7,344.46), and 200-day DMA (₹7,171.21). The price distance from 200 DMA is +9.19%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2747.3, 2755.54, 2763.78, 2772.03, 2780.27, 2788.51]</t>
+          <t>[7833.5, 7857.0, 7880.5, 7904.0, 7927.5, 7951.0]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2747.3, 2778.78, 2796.64, 2812.27, 2826.74, 2840.46]</t>
+          <t>[7833.5, 7917.23, 7965.67, 8008.32, 8047.95, 8085.67]</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>[2747.3, 2738.12, 2739.14, 2741.84, 2745.42, 2749.54]</t>
+          <t>[7833.5, 7811.83, 7816.62, 7825.77, 7837.16, 7850.0]</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,98 +1505,98 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>105169.94</v>
+        <v>105127.58</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2199.8</v>
+        <v>738.55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹2190.26 - ₹2214.11</t>
+          <t>₹735.6 - ₹742.98</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2237.97</v>
+        <v>750.37</v>
       </c>
       <c r="I7" t="n">
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="J7" t="n">
-        <v>2140.62</v>
+        <v>729.51</v>
       </c>
       <c r="K7" t="n">
-        <v>2061.08</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>1703.8</v>
+        <v>686.09</v>
       </c>
       <c r="M7" t="n">
-        <v>27.05</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>29.77</v>
+        <v>8.49</v>
       </c>
       <c r="O7" t="n">
-        <v>35.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.63</v>
+        <v>-0.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>47.71</v>
+        <v>14.77</v>
       </c>
       <c r="R7" t="n">
         <v>11.76</v>
       </c>
       <c r="S7" t="n">
-        <v>56.2</v>
+        <v>49.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.97</v>
+        <v>-1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.78</v>
+        <v>2.84</v>
       </c>
       <c r="X7" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>2184.76</v>
+        <v>727.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>2261.76</v>
+        <v>753.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>2217.76</v>
+        <v>744.46</v>
       </c>
       <c r="AB7" t="n">
-        <v>2128.24</v>
+        <v>716.39</v>
       </c>
       <c r="AC7" t="n">
-        <v>2191.3</v>
+        <v>744.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>2221.1</v>
+        <v>751.6900000000001</v>
       </c>
       <c r="AE7" t="n">
-        <v>2242.4</v>
+        <v>764.8200000000001</v>
       </c>
       <c r="AF7" t="n">
-        <v>57.9</v>
+        <v>48.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         <v>0.15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>97.09999999999999</v>
+        <v>49</v>
       </c>
       <c r="AK7" t="n">
-        <v>17.5</v>
+        <v>15.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.4</v>
+        <v>20.9</v>
       </c>
       <c r="AM7" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AN7" t="n">
-        <v>2271.94</v>
+        <v>767.5700000000001</v>
       </c>
       <c r="AO7" t="n">
-        <v>2138.69</v>
+        <v>710.38</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2199.8, 2217.76, 2235.72, 2253.68, 2271.64, 2289.6]</t>
+          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2199.8, 2236.84, 2262.71, 2286.73, 2309.8, 2332.27]</t>
+          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>[2199.8, 2203.45, 2215.48, 2228.89, 2243.01, 2257.59]</t>
+          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105127.58</v>
+        <v>105169.94</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,90 +1680,90 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>738.55</v>
+        <v>2199.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹735.6 - ₹742.98</t>
+          <t>₹2190.26 - ₹2214.11</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>750.37</v>
+        <v>2237.97</v>
       </c>
       <c r="I8" t="n">
-        <v>225</v>
+        <v>69</v>
       </c>
       <c r="J8" t="n">
-        <v>729.51</v>
+        <v>2140.62</v>
       </c>
       <c r="K8" t="n">
-        <v>703.6799999999999</v>
+        <v>2061.08</v>
       </c>
       <c r="L8" t="n">
-        <v>686.09</v>
+        <v>1703.8</v>
       </c>
       <c r="M8" t="n">
-        <v>9.210000000000001</v>
+        <v>27.05</v>
       </c>
       <c r="N8" t="n">
-        <v>8.49</v>
+        <v>29.77</v>
       </c>
       <c r="O8" t="n">
-        <v>9.380000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9</v>
+        <v>-5.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.77</v>
+        <v>47.71</v>
       </c>
       <c r="R8" t="n">
         <v>11.76</v>
       </c>
       <c r="S8" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="V8" t="n">
         <v>52.2</v>
       </c>
-      <c r="T8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="V8" t="n">
-        <v>55</v>
-      </c>
       <c r="W8" t="n">
-        <v>5.75</v>
+        <v>2.26</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>720.8200000000001</v>
+        <v>2170.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>725.27</v>
+        <v>2247.27</v>
       </c>
       <c r="AA8" t="n">
-        <v>744.46</v>
+        <v>2217.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>716.39</v>
+        <v>2128.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>744.27</v>
+        <v>2191.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>751.6900000000001</v>
+        <v>2221.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>764.8200000000001</v>
+        <v>2242.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>48.2</v>
+        <v>57.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1774,51 +1774,51 @@
         <v>0.15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>49</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AK8" t="n">
-        <v>15.1</v>
+        <v>17.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>20.9</v>
+        <v>6.4</v>
       </c>
       <c r="AM8" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>758.26</v>
+        <v>2307.76</v>
       </c>
       <c r="AO8" t="n">
-        <v>720.29</v>
+        <v>2092.5</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
+          <t>[2199.8, 2206.4, 2213.0, 2219.6, 2226.2, 2232.8]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
+          <t>[2199.8, 2225.48, 2239.99, 2252.65, 2264.36, 2275.47]</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
+          <t>[2199.8, 2192.09, 2192.76, 2194.81, 2197.57, 2200.79]</t>
         </is>
       </c>
     </row>
@@ -1830,16 +1830,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25000</v>
+        <v>119011.76</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,145 +1847,145 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>372.95</v>
+        <v>1473.2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹371.41 - ₹375.26</t>
+          <t>₹1466.31 - ₹1483.53</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>379.11</v>
+        <v>1500.76</v>
       </c>
       <c r="I9" t="n">
-        <v>432</v>
+        <v>96</v>
       </c>
       <c r="J9" t="n">
-        <v>357.21</v>
+        <v>1436.14</v>
       </c>
       <c r="K9" t="n">
-        <v>349.78</v>
+        <v>1414.83</v>
       </c>
       <c r="L9" t="n">
-        <v>347.56</v>
+        <v>1396.09</v>
       </c>
       <c r="M9" t="n">
-        <v>6.64</v>
+        <v>5.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.07</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>2.35</v>
+        <v>6.31</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.7</v>
+        <v>34.45</v>
       </c>
       <c r="R9" t="n">
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>53.1</v>
+        <v>48.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.03</v>
+        <v>-1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="W9" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="X9" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>366.16</v>
+        <v>1442.83</v>
       </c>
       <c r="Z9" t="n">
-        <v>379.22</v>
+        <v>1494.39</v>
       </c>
       <c r="AA9" t="n">
-        <v>375.93</v>
+        <v>1484.99</v>
       </c>
       <c r="AB9" t="n">
-        <v>361.4</v>
+        <v>1421.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>372.32</v>
+        <v>1471.43</v>
       </c>
       <c r="AD9" t="n">
-        <v>374.64</v>
+        <v>1480.56</v>
       </c>
       <c r="AE9" t="n">
-        <v>376.32</v>
+        <v>1487.93</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.3</v>
+        <v>56.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.08</v>
+        <v>-0.08</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI9" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>6.1</v>
+        <v>35.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>25.2</v>
+        <v>3.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>68.90000000000001</v>
+        <v>12</v>
       </c>
       <c r="AM9" t="n">
         <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>383.76</v>
+        <v>2156.84</v>
       </c>
       <c r="AO9" t="n">
-        <v>363.9</v>
+        <v>813.36</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
+          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
+          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
+          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
         </is>
       </c>
     </row>
@@ -1997,162 +1997,162 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>310746.28</v>
+        <v>246283.11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4646.5</v>
+        <v>1046.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹4629.85 - ₹4671.48</t>
+          <t>₹1040.39 - ₹1056.17</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4713.1</v>
+        <v>1071.96</v>
       </c>
       <c r="I10" t="n">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="J10" t="n">
-        <v>4471.9</v>
+        <v>1032.61</v>
       </c>
       <c r="K10" t="n">
-        <v>4404.23</v>
+        <v>994.9400000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>4346.03</v>
+        <v>942.9400000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>5.42</v>
+        <v>8.94</v>
       </c>
       <c r="N10" t="n">
-        <v>56.6</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>49.9</v>
+        <v>12.02</v>
       </c>
       <c r="P10" t="n">
-        <v>6.7</v>
+        <v>-3.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>83.25</v>
+        <v>31.57</v>
       </c>
       <c r="R10" t="n">
         <v>11.76</v>
       </c>
       <c r="S10" t="n">
-        <v>46.4</v>
+        <v>50.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.07</v>
+        <v>-1.85</v>
       </c>
       <c r="V10" t="n">
-        <v>41.7</v>
+        <v>52.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.15</v>
+        <v>2.72</v>
       </c>
       <c r="X10" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>4548.43</v>
+        <v>1033.78</v>
       </c>
       <c r="Z10" t="n">
-        <v>4711.06</v>
+        <v>1070.41</v>
       </c>
       <c r="AA10" t="n">
-        <v>4683.67</v>
+        <v>1055.07</v>
       </c>
       <c r="AB10" t="n">
-        <v>4521.62</v>
+        <v>999.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>4635.53</v>
+        <v>1043.47</v>
       </c>
       <c r="AD10" t="n">
-        <v>4679.96</v>
+        <v>1057.84</v>
       </c>
       <c r="AE10" t="n">
-        <v>4713.43</v>
+        <v>1068.97</v>
       </c>
       <c r="AF10" t="n">
-        <v>59.3</v>
+        <v>46.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI10" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34.1</v>
+        <v>18.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>39.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>27.5</v>
+        <v>50.1</v>
       </c>
       <c r="AM10" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>4770.72</v>
+        <v>1093.82</v>
       </c>
       <c r="AO10" t="n">
-        <v>4523.8</v>
+        <v>1002.87</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹246,283.11 Cr., a P/E ratio of 18.48, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,046.70) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[4646.5, 4660.44, 4674.38, 4688.32, 4702.26, 4716.2]</t>
+          <t>[1046.7, 1049.84, 1052.98, 1056.12, 1059.26, 1062.4]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[4646.5, 4693.74, 4721.47, 4746.0, 4768.86, 4790.66]</t>
+          <t>[1046.7, 1062.47, 1070.84, 1077.99, 1084.52, 1090.64]</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>[4646.5, 4635.46, 4639.06, 4645.06, 4652.31, 4660.35]</t>
+          <t>[1046.7, 1040.37, 1039.59, 1039.72, 1040.32, 1041.22]</t>
         </is>
       </c>
     </row>
@@ -2164,16 +2164,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68767.81</v>
+        <v>85420.58</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2181,145 +2181,145 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5751.5</v>
+        <v>14049</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹5727.01 - ₹5788.23</t>
+          <t>₹13965.8 - ₹14173.8</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5849.44</v>
+        <v>14381.8</v>
       </c>
       <c r="I11" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>5575</v>
+        <v>13190.57</v>
       </c>
       <c r="K11" t="n">
-        <v>5484.08</v>
+        <v>12605.68</v>
       </c>
       <c r="L11" t="n">
-        <v>5521.06</v>
+        <v>12333.95</v>
       </c>
       <c r="M11" t="n">
-        <v>5.35</v>
+        <v>16.25</v>
       </c>
       <c r="N11" t="n">
-        <v>57.19</v>
+        <v>477.1</v>
       </c>
       <c r="O11" t="n">
-        <v>51.96</v>
+        <v>503.84</v>
       </c>
       <c r="P11" t="n">
-        <v>5.23</v>
+        <v>-26.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>122.43</v>
+        <v>416</v>
       </c>
       <c r="R11" t="n">
         <v>11.76</v>
       </c>
       <c r="S11" t="n">
-        <v>51.8</v>
+        <v>49.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.12</v>
+        <v>-1.86</v>
       </c>
       <c r="V11" t="n">
-        <v>53.3</v>
+        <v>48.9</v>
       </c>
       <c r="W11" t="n">
-        <v>2.81</v>
+        <v>3.54</v>
       </c>
       <c r="X11" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>5710.85</v>
+        <v>13933.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>5912.15</v>
+        <v>14425.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>5797.51</v>
+        <v>14161.39</v>
       </c>
       <c r="AB11" t="n">
-        <v>5567.86</v>
+        <v>13425</v>
       </c>
       <c r="AC11" t="n">
-        <v>5773.17</v>
+        <v>14079.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>5811.34</v>
+        <v>14558.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>5871.17</v>
+        <v>15067.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>58.4</v>
+        <v>64.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI11" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>29.9</v>
+        <v>41.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>14.6</v>
+        <v>21.1</v>
       </c>
       <c r="AL11" t="n">
-        <v>15.6</v>
+        <v>3.6</v>
       </c>
       <c r="AM11" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="AN11" t="n">
-        <v>5889.8</v>
+        <v>14691.98</v>
       </c>
       <c r="AO11" t="n">
-        <v>5621.92</v>
+        <v>13511.14</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,767.81 Cr., a P/E ratio of 29.85, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,751.50) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[5751.5, 5797.12, 5842.75, 5888.37, 5934.0, 5979.62]</t>
+          <t>[14049.0, 14144.12, 14239.24, 14334.35, 14429.47, 14524.59]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[5751.5, 5846.1, 5912.0, 5973.19, 6031.94, 6089.12]</t>
+          <t>[14049.0, 14310.52, 14474.56, 14622.57, 14762.27, 14896.67]</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>[5751.5, 5760.4, 5790.81, 5824.76, 5860.54, 5897.49]</t>
+          <t>[14049.0, 14019.32, 14062.74, 14118.19, 14179.87, 14245.53]</t>
         </is>
       </c>
     </row>
@@ -2331,162 +2331,162 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>133901.31</v>
+        <v>146280.27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3760</v>
+        <v>1651.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹3740.59 - ₹3789.12</t>
+          <t>₹1641.81 - ₹1665.54</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3837.66</v>
+        <v>1689.26</v>
       </c>
       <c r="I12" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="J12" t="n">
-        <v>3594.31</v>
+        <v>1478.49</v>
       </c>
       <c r="K12" t="n">
-        <v>3627.85</v>
+        <v>1460.44</v>
       </c>
       <c r="L12" t="n">
-        <v>3330.53</v>
+        <v>1458.79</v>
       </c>
       <c r="M12" t="n">
-        <v>9.859999999999999</v>
+        <v>14.41</v>
       </c>
       <c r="N12" t="n">
-        <v>22.06</v>
+        <v>56.22</v>
       </c>
       <c r="O12" t="n">
-        <v>10.09</v>
+        <v>42.84</v>
       </c>
       <c r="P12" t="n">
-        <v>11.97</v>
+        <v>13.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>97.06999999999999</v>
+        <v>47.45</v>
       </c>
       <c r="R12" t="n">
         <v>11.76</v>
       </c>
       <c r="S12" t="n">
-        <v>56.1</v>
+        <v>47.8</v>
       </c>
       <c r="T12" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.25</v>
+        <v>-1.87</v>
       </c>
       <c r="V12" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="W12" t="n">
-        <v>2.23</v>
+        <v>1.71</v>
       </c>
       <c r="X12" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>3684.03</v>
+        <v>1628.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>3815.63</v>
+        <v>1686.72</v>
       </c>
       <c r="AA12" t="n">
-        <v>3790.08</v>
+        <v>1664.51</v>
       </c>
       <c r="AB12" t="n">
-        <v>3614.39</v>
+        <v>1580.13</v>
       </c>
       <c r="AC12" t="n">
-        <v>3743.5</v>
+        <v>1641.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>3824.9</v>
+        <v>1671.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>3889.8</v>
+        <v>1692.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>74.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI12" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>79.40000000000001</v>
+        <v>28.6</v>
       </c>
       <c r="AK12" t="n">
-        <v>14.6</v>
+        <v>17.7</v>
       </c>
       <c r="AL12" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM12" t="n">
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>3874.11</v>
+        <v>1712.49</v>
       </c>
       <c r="AO12" t="n">
-        <v>3649.9</v>
+        <v>1593.5</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,901.31 Cr., a P/E ratio of 79.36, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,760.00) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[3760.0, 3771.28, 3782.56, 3793.84, 3805.12, 3816.4]</t>
+          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[3760.0, 3810.11, 3837.47, 3861.1, 3882.78, 3903.23]</t>
+          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>[3760.0, 3742.16, 3741.37, 3743.4, 3746.88, 3751.28]</t>
+          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
         </is>
       </c>
     </row>
@@ -2498,16 +2498,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>119011.76</v>
+        <v>63429.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2515,145 +2515,145 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1473.2</v>
+        <v>2105.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1466.31 - ₹1483.53</t>
+          <t>₹2092.64 - ₹2125.3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1500.76</v>
+        <v>2157.96</v>
       </c>
       <c r="I13" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="J13" t="n">
-        <v>1436.14</v>
+        <v>1999.45</v>
       </c>
       <c r="K13" t="n">
-        <v>1414.83</v>
+        <v>1888.17</v>
       </c>
       <c r="L13" t="n">
-        <v>1396.09</v>
+        <v>1880.41</v>
       </c>
       <c r="M13" t="n">
-        <v>5.04</v>
+        <v>12.26</v>
       </c>
       <c r="N13" t="n">
-        <v>8.130000000000001</v>
+        <v>62.25</v>
       </c>
       <c r="O13" t="n">
-        <v>6.31</v>
+        <v>68.98</v>
       </c>
       <c r="P13" t="n">
-        <v>1.82</v>
+        <v>-6.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.45</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="R13" t="n">
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>51.9</v>
+        <v>48.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.27</v>
+        <v>-2.01</v>
       </c>
       <c r="V13" t="n">
-        <v>45</v>
+        <v>52.5</v>
       </c>
       <c r="W13" t="n">
-        <v>11.03</v>
+        <v>2.38</v>
       </c>
       <c r="X13" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>1431.86</v>
+        <v>2079.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>1388.25</v>
+        <v>2153.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1484.99</v>
+        <v>2122.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>1421.52</v>
+        <v>2007.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>1471.43</v>
+        <v>2111.93</v>
       </c>
       <c r="AD13" t="n">
-        <v>1480.56</v>
+        <v>2127.76</v>
       </c>
       <c r="AE13" t="n">
-        <v>1487.93</v>
+        <v>2149.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>56.5</v>
+        <v>48.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI13" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>35.3</v>
+        <v>34.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.5</v>
+        <v>63</v>
       </c>
       <c r="AL13" t="n">
-        <v>12</v>
+        <v>36.1</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AN13" t="n">
-        <v>1505.91</v>
+        <v>2188.09</v>
       </c>
       <c r="AO13" t="n">
-        <v>1440.51</v>
+        <v>2027.94</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
+          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
+          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
+          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
         </is>
       </c>
     </row>
@@ -2665,16 +2665,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>246283.11</v>
+        <v>17572.27</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2682,145 +2682,145 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1046.7</v>
+        <v>613.35</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹1040.39 - ₹1056.17</t>
+          <t>₹608.87 - ₹620.07</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1071.96</v>
+        <v>631.27</v>
       </c>
       <c r="I14" t="n">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="J14" t="n">
-        <v>1032.61</v>
+        <v>578.01</v>
       </c>
       <c r="K14" t="n">
-        <v>994.9400000000001</v>
+        <v>541.38</v>
       </c>
       <c r="L14" t="n">
-        <v>942.9400000000001</v>
+        <v>553.54</v>
       </c>
       <c r="M14" t="n">
-        <v>8.94</v>
+        <v>10.74</v>
       </c>
       <c r="N14" t="n">
-        <v>8.390000000000001</v>
+        <v>14.56</v>
       </c>
       <c r="O14" t="n">
-        <v>12.02</v>
+        <v>16.43</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.63</v>
+        <v>-1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>31.57</v>
+        <v>22.4</v>
       </c>
       <c r="R14" t="n">
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>56.4</v>
+        <v>49</v>
       </c>
       <c r="T14" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.52</v>
+        <v>-2.4</v>
       </c>
       <c r="V14" t="n">
-        <v>55</v>
+        <v>48.1</v>
       </c>
       <c r="W14" t="n">
-        <v>3.38</v>
+        <v>6.55</v>
       </c>
       <c r="X14" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>1019.37</v>
+        <v>605.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1056.01</v>
+        <v>626.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>1055.07</v>
+        <v>618.26</v>
       </c>
       <c r="AB14" t="n">
-        <v>999.34</v>
+        <v>579.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>1043.47</v>
+        <v>616.27</v>
       </c>
       <c r="AD14" t="n">
-        <v>1057.84</v>
+        <v>624.54</v>
       </c>
       <c r="AE14" t="n">
-        <v>1068.97</v>
+        <v>635.72</v>
       </c>
       <c r="AF14" t="n">
-        <v>46.1</v>
+        <v>60.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.14</v>
+        <v>0.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI14" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>18.5</v>
+        <v>88.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>39.1</v>
+        <v>-10.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>50.1</v>
+        <v>3.7</v>
       </c>
       <c r="AM14" t="n">
-        <v>18.5</v>
+        <v>6.7</v>
       </c>
       <c r="AN14" t="n">
-        <v>1085.79</v>
+        <v>658.1900000000001</v>
       </c>
       <c r="AO14" t="n">
-        <v>1009.74</v>
+        <v>571.33</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹246,283.11 Cr., a P/E ratio of 18.48, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,046.70) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[1046.7, 1049.84, 1052.98, 1056.12, 1059.26, 1062.4]</t>
+          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[1046.7, 1062.47, 1070.84, 1077.99, 1084.52, 1090.64]</t>
+          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>[1046.7, 1040.37, 1039.59, 1039.72, 1040.32, 1041.22]</t>
+          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2841,153 +2841,153 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85420.58</v>
+        <v>76187.09</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14049</v>
+        <v>1721</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹13965.8 - ₹14173.8</t>
+          <t>₹1709.13 - ₹1738.8</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14381.8</v>
+        <v>1768.46</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="J15" t="n">
-        <v>13190.57</v>
+        <v>1505.99</v>
       </c>
       <c r="K15" t="n">
-        <v>12605.68</v>
+        <v>1472.15</v>
       </c>
       <c r="L15" t="n">
-        <v>12333.95</v>
+        <v>1507.99</v>
       </c>
       <c r="M15" t="n">
-        <v>16.25</v>
+        <v>15.58</v>
       </c>
       <c r="N15" t="n">
-        <v>477.1</v>
+        <v>53.48</v>
       </c>
       <c r="O15" t="n">
-        <v>503.84</v>
+        <v>30.14</v>
       </c>
       <c r="P15" t="n">
-        <v>-26.74</v>
+        <v>23.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>416</v>
+        <v>59.33</v>
       </c>
       <c r="R15" t="n">
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>50.6</v>
+        <v>43.9</v>
       </c>
       <c r="T15" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.79</v>
+        <v>-2.55</v>
       </c>
       <c r="V15" t="n">
-        <v>46.7</v>
+        <v>51.5</v>
       </c>
       <c r="W15" t="n">
-        <v>6.67</v>
+        <v>2.38</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>13634.81</v>
+        <v>1695.71</v>
       </c>
       <c r="Z15" t="n">
-        <v>14126.52</v>
+        <v>1755.94</v>
       </c>
       <c r="AA15" t="n">
-        <v>14161.39</v>
+        <v>1734.77</v>
       </c>
       <c r="AB15" t="n">
-        <v>13425</v>
+        <v>1632.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>14079.67</v>
+        <v>1713.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>14558.34</v>
+        <v>1745.96</v>
       </c>
       <c r="AE15" t="n">
-        <v>15067.67</v>
+        <v>1770.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>64.7</v>
+        <v>77.3</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>41.2</v>
+        <v>35.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>21.1</v>
+        <v>49.9</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.6</v>
+        <v>9.6</v>
       </c>
       <c r="AM15" t="n">
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>14574.67</v>
+        <v>1810.49</v>
       </c>
       <c r="AO15" t="n">
-        <v>13507.87</v>
+        <v>1644.19</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,187.09 Cr., a P/E ratio of 35.21, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.48) trades above Signal (30.14) with an expanding histogram (+23.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1507.99). Daily volatility envelope is bounded by ATR(14) of ₹59.33.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,721.00) is positioned above the 30-day DMA (₹1,505.99), 50-day DMA (₹1,472.15), and 200-day DMA (₹1,507.99). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
+          <t>[1721.0, 1726.16, 1731.33, 1736.49, 1741.65, 1746.81]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
+          <t>[1721.0, 1749.89, 1764.89, 1777.59, 1789.11, 1799.88]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
+          <t>[1721.0, 1708.36, 1706.16, 1705.66, 1706.06, 1707.02]</t>
         </is>
       </c>
     </row>
@@ -2999,997 +2999,162 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>146280.27</v>
+        <v>278417.14</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1651.3</v>
+        <v>302.45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹1641.81 - ₹1665.54</t>
+          <t>₹300.39 - ₹305.53</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1689.26</v>
+        <v>310.68</v>
       </c>
       <c r="I16" t="n">
-        <v>70</v>
+        <v>324</v>
       </c>
       <c r="J16" t="n">
-        <v>1478.49</v>
+        <v>281.7</v>
       </c>
       <c r="K16" t="n">
-        <v>1460.44</v>
+        <v>268.93</v>
       </c>
       <c r="L16" t="n">
-        <v>1458.79</v>
+        <v>274.01</v>
       </c>
       <c r="M16" t="n">
-        <v>14.41</v>
+        <v>13.37</v>
       </c>
       <c r="N16" t="n">
-        <v>56.22</v>
+        <v>9.93</v>
       </c>
       <c r="O16" t="n">
-        <v>42.84</v>
+        <v>8.42</v>
       </c>
       <c r="P16" t="n">
-        <v>13.38</v>
+        <v>1.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.45</v>
+        <v>10.28</v>
       </c>
       <c r="R16" t="n">
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>49.1</v>
+        <v>42.4</v>
       </c>
       <c r="T16" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.8</v>
+        <v>-2.6</v>
       </c>
       <c r="V16" t="n">
-        <v>48.3</v>
+        <v>46.4</v>
       </c>
       <c r="W16" t="n">
-        <v>8.69</v>
+        <v>2.4</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>1625.39</v>
+        <v>299.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>1683.18</v>
+        <v>309.72</v>
       </c>
       <c r="AA16" t="n">
-        <v>1664.51</v>
+        <v>304.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>1580.13</v>
+        <v>287.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1641.1</v>
+        <v>306.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1671.7</v>
+        <v>311.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>1692.1</v>
+        <v>320.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>86.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28.6</v>
+        <v>672.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>17.7</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="n">
-        <v>8.699999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="AM16" t="n">
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>1697.3</v>
+        <v>317.38</v>
       </c>
       <c r="AO16" t="n">
-        <v>1609.8</v>
+        <v>287.93</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
+          <t>[302.45, 303.67, 304.9, 306.12, 307.35, 308.57]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
+          <t>[302.45, 307.79, 310.72, 313.25, 315.57, 317.77]</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PGEL</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>17572.27</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>613.35</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>₹608.87 - ₹620.07</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>631.27</v>
-      </c>
-      <c r="I17" t="n">
-        <v>148</v>
-      </c>
-      <c r="J17" t="n">
-        <v>578.01</v>
-      </c>
-      <c r="K17" t="n">
-        <v>541.38</v>
-      </c>
-      <c r="L17" t="n">
-        <v>553.54</v>
-      </c>
-      <c r="M17" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="N17" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="O17" t="n">
-        <v>16.43</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="S17" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="V17" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>590.26</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>611.72</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>618.26</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>579.75</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>616.27</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>624.54</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>635.72</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AI17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>-10.1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>642.6900000000001</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>581.9</v>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>63429.15</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2105.7</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>₹2092.64 - ₹2125.3</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>2157.96</v>
-      </c>
-      <c r="I18" t="n">
-        <v>51</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1999.45</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1888.17</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1880.41</v>
-      </c>
-      <c r="M18" t="n">
-        <v>12.26</v>
-      </c>
-      <c r="N18" t="n">
-        <v>62.25</v>
-      </c>
-      <c r="O18" t="n">
-        <v>68.98</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-6.73</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>65.31999999999999</v>
-      </c>
-      <c r="R18" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="S18" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="V18" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="W18" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2027.32</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2032.25</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2122.55</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2007.72</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2111.93</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2127.76</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2149.83</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AI18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>63</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2181.15</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>2035.93</v>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>360ONE</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>46194.13</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1135.3</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>₹1128.39 - ₹1145.67</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>1162.95</v>
-      </c>
-      <c r="I19" t="n">
-        <v>96</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1109.56</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1105.35</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1100.33</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="N19" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>34.56</v>
-      </c>
-      <c r="R19" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="S19" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1114</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1153.74</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1144.38</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1083.45</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1144.43</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1156.86</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1178.43</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AI19" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1171.19</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1101.74</v>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,194.13 Cr., a P/E ratio of 37.73, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,135.30) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>[1135.3, 1138.71, 1142.11, 1145.52, 1148.92, 1152.33]</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>[1135.3, 1152.53, 1161.66, 1169.46, 1176.58, 1183.24]</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>[1135.3, 1128.34, 1127.45, 1127.56, 1128.19, 1129.14]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>278417.14</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>302.45</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>₹300.39 - ₹305.53</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>310.68</v>
-      </c>
-      <c r="I20" t="n">
-        <v>324</v>
-      </c>
-      <c r="J20" t="n">
-        <v>281.7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>268.93</v>
-      </c>
-      <c r="L20" t="n">
-        <v>274.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="N20" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="O20" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="R20" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="S20" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="V20" t="n">
-        <v>50</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>299.26</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>309.85</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>304.87</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>287.03</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>306.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>320.95</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AI20" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>672.1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>182</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>313.15</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>292.51</v>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>[302.45, 303.8, 305.15, 306.5, 307.85, 309.19]</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>[302.45, 307.91, 310.96, 313.62, 316.07, 318.39]</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>[302.45, 300.71, 300.79, 301.15, 301.68, 302.3]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>76187.09</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1721</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>₹1709.13 - ₹1738.8</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>1768.46</v>
-      </c>
-      <c r="I21" t="n">
-        <v>56</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1505.99</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1472.15</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1507.99</v>
-      </c>
-      <c r="M21" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="N21" t="n">
-        <v>53.48</v>
-      </c>
-      <c r="O21" t="n">
-        <v>30.14</v>
-      </c>
-      <c r="P21" t="n">
-        <v>23.34</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="R21" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="S21" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="V21" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1705.12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1765.36</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1734.77</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1632.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1713.83</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1745.96</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1770.93</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AI21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1786.32</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1653.57</v>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,187.09 Cr., a P/E ratio of 35.21, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.48) trades above Signal (30.14) with an expanding histogram (+23.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1507.99). Daily volatility envelope is bounded by ATR(14) of ₹59.33.</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,721.00) is positioned above the 30-day DMA (₹1,505.99), 50-day DMA (₹1,472.15), and 200-day DMA (₹1,507.99). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.21, 1823.74]</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
+          <t>[302.45, 300.59, 300.54, 300.78, 301.18, 301.67]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -719,28 +719,28 @@
         <v>11.76</v>
       </c>
       <c r="S2" t="n">
-        <v>50.2</v>
+        <v>55.2</v>
       </c>
       <c r="T2" t="n">
         <v>0.32</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.86</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>6.24</v>
       </c>
       <c r="X2" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y2" t="n">
-        <v>1415.53</v>
+        <v>1424.81</v>
       </c>
       <c r="Z2" t="n">
-        <v>1465.77</v>
+        <v>1471.73</v>
       </c>
       <c r="AA2" t="n">
         <v>1446.88</v>
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1492.2</v>
+        <v>1462.68</v>
       </c>
       <c r="AO2" t="n">
-        <v>1383.2</v>
+        <v>1407.05</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -806,17 +806,17 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[1435.4, 1439.71, 1444.01, 1448.32, 1452.62, 1456.93]</t>
+          <t>[1435.4, 1446.34, 1457.29, 1468.23, 1479.18, 1490.12]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[1435.4, 1449.39, 1457.71, 1465.1, 1472.0, 1478.6]</t>
+          <t>[1435.4, 1456.03, 1470.99, 1485.02, 1498.56, 1511.79]</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>[1435.4, 1432.44, 1433.74, 1435.73, 1438.09, 1440.68]</t>
+          <t>[1435.4, 1439.08, 1447.01, 1455.65, 1464.65, 1473.88]</t>
         </is>
       </c>
     </row>
@@ -886,28 +886,28 @@
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>50.4</v>
+        <v>52.9</v>
       </c>
       <c r="T3" t="n">
         <v>0.29</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.97</v>
+        <v>-0.88</v>
       </c>
       <c r="V3" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="W3" t="n">
-        <v>2.23</v>
+        <v>3.29</v>
       </c>
       <c r="X3" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>111.24</v>
+        <v>111.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>115.19</v>
+        <v>115.27</v>
       </c>
       <c r="AA3" t="n">
         <v>113.61</v>
@@ -951,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>117.69</v>
+        <v>115.97</v>
       </c>
       <c r="AO3" t="n">
-        <v>107.9</v>
+        <v>109.92</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -995,162 +995,162 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>310746.28</v>
+        <v>215046.57</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4646.5</v>
+        <v>7833.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹4629.85 - ₹4671.48</t>
+          <t>₹7803.39 - ₹7878.67</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4713.1</v>
+        <v>7953.95</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="J4" t="n">
-        <v>4471.9</v>
+        <v>7437.81</v>
       </c>
       <c r="K4" t="n">
-        <v>4404.23</v>
+        <v>7344.46</v>
       </c>
       <c r="L4" t="n">
-        <v>4346.03</v>
+        <v>7171.21</v>
       </c>
       <c r="M4" t="n">
-        <v>5.42</v>
+        <v>9.19</v>
       </c>
       <c r="N4" t="n">
-        <v>56.6</v>
+        <v>121.41</v>
       </c>
       <c r="O4" t="n">
-        <v>49.9</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>6.7</v>
+        <v>36.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>83.25</v>
+        <v>150.57</v>
       </c>
       <c r="R4" t="n">
         <v>11.76</v>
       </c>
       <c r="S4" t="n">
-        <v>47.6</v>
+        <v>49.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.03</v>
+        <v>-0.9</v>
       </c>
       <c r="V4" t="n">
-        <v>50.4</v>
+        <v>48.3</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>4611.35</v>
+        <v>7803.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>4771.38</v>
+        <v>8059.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>4683.67</v>
+        <v>7920.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>4521.62</v>
+        <v>7607.65</v>
       </c>
       <c r="AC4" t="n">
-        <v>4635.53</v>
+        <v>7842.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>4679.96</v>
+        <v>7890.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>4713.43</v>
+        <v>7947.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>59.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI4" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>34.1</v>
+        <v>37.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>31.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>27.5</v>
+        <v>23.2</v>
       </c>
       <c r="AM4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>4815.85</v>
+        <v>8055.52</v>
       </c>
       <c r="AO4" t="n">
-        <v>4473.38</v>
+        <v>7646.07</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹215,046.57 Cr., a P/E ratio of 37.31, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.10 (Bullish Momentum Zone), while MACD Line (121.41) trades above Signal (84.99) with an expanding histogram (+36.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.19% above the 200-day DMA (₹7171.21). Daily volatility envelope is bounded by ATR(14) of ₹150.57.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,833.50) is positioned above the 30-day DMA (₹7,437.81), 50-day DMA (₹7,344.46), and 200-day DMA (₹7,171.21). The price distance from 200 DMA is +9.19%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[4646.5, 4681.04, 4715.59, 4750.13, 4784.67, 4819.22]</t>
+          <t>[7833.5, 7920.87, 8008.25, 8095.62, 8183.0, 8270.37]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[4646.5, 4714.34, 4762.68, 4807.81, 4851.27, 4893.68]</t>
+          <t>[7833.5, 7981.1, 8093.42, 8199.94, 8303.45, 8405.04]</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>[4646.5, 4656.07, 4680.27, 4706.87, 4734.72, 4763.37]</t>
+          <t>[7833.5, 7875.7, 7944.37, 8017.39, 8092.66, 8169.37]</t>
         </is>
       </c>
     </row>
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>98206.09</v>
+        <v>105169.94</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,145 +1179,145 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>372.95</v>
+        <v>2199.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹371.41 - ₹375.26</t>
+          <t>₹2190.26 - ₹2214.11</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>379.11</v>
+        <v>2237.97</v>
       </c>
       <c r="I5" t="n">
-        <v>432</v>
+        <v>69</v>
       </c>
       <c r="J5" t="n">
-        <v>357.21</v>
+        <v>2140.62</v>
       </c>
       <c r="K5" t="n">
-        <v>349.78</v>
+        <v>2061.08</v>
       </c>
       <c r="L5" t="n">
-        <v>347.56</v>
+        <v>1703.8</v>
       </c>
       <c r="M5" t="n">
-        <v>6.64</v>
+        <v>27.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.07</v>
+        <v>29.77</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>35.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>-5.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.7</v>
+        <v>47.71</v>
       </c>
       <c r="R5" t="n">
         <v>11.76</v>
       </c>
       <c r="S5" t="n">
-        <v>52.1</v>
+        <v>49.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.07</v>
+        <v>-1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>53.4</v>
+        <v>50</v>
       </c>
       <c r="W5" t="n">
-        <v>4.29</v>
+        <v>1.78</v>
       </c>
       <c r="X5" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>368.15</v>
+        <v>2184.76</v>
       </c>
       <c r="Z5" t="n">
-        <v>381.21</v>
+        <v>2261.76</v>
       </c>
       <c r="AA5" t="n">
-        <v>375.93</v>
+        <v>2217.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>361.4</v>
+        <v>2128.24</v>
       </c>
       <c r="AC5" t="n">
-        <v>372.32</v>
+        <v>2191.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>374.64</v>
+        <v>2221.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>376.32</v>
+        <v>2242.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>78.3</v>
+        <v>57.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI5" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>25.2</v>
+        <v>17.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>68.90000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AM5" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>388.5</v>
+        <v>2266.77</v>
       </c>
       <c r="AO5" t="n">
-        <v>357.92</v>
+        <v>2139.2</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
+          <t>[2199.8, 2217.76, 2235.72, 2253.68, 2271.64, 2289.6]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
+          <t>[2199.8, 2236.84, 2262.71, 2286.73, 2309.8, 2332.27]</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
+          <t>[2199.8, 2203.45, 2215.48, 2228.89, 2243.01, 2257.59]</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,153 +1338,153 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>215046.57</v>
+        <v>105127.58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7833.5</v>
+        <v>738.55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹7803.39 - ₹7878.67</t>
+          <t>₹735.6 - ₹742.98</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7953.95</v>
+        <v>750.37</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>225</v>
       </c>
       <c r="J6" t="n">
-        <v>7437.81</v>
+        <v>729.51</v>
       </c>
       <c r="K6" t="n">
-        <v>7344.46</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>7171.21</v>
+        <v>686.09</v>
       </c>
       <c r="M6" t="n">
-        <v>9.19</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>121.41</v>
+        <v>8.49</v>
       </c>
       <c r="O6" t="n">
-        <v>84.98999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>36.42</v>
+        <v>-0.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>150.57</v>
+        <v>14.77</v>
       </c>
       <c r="R6" t="n">
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>48.4</v>
+        <v>46.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1</v>
+        <v>-1.23</v>
       </c>
       <c r="V6" t="n">
-        <v>50.2</v>
+        <v>55</v>
       </c>
       <c r="W6" t="n">
-        <v>5.13</v>
+        <v>5.75</v>
       </c>
       <c r="X6" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>7728.5</v>
+        <v>720.8200000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>8002.67</v>
+        <v>725.27</v>
       </c>
       <c r="AA6" t="n">
-        <v>7896.17</v>
+        <v>744.46</v>
       </c>
       <c r="AB6" t="n">
-        <v>7607.65</v>
+        <v>716.39</v>
       </c>
       <c r="AC6" t="n">
-        <v>7842.17</v>
+        <v>744.27</v>
       </c>
       <c r="AD6" t="n">
-        <v>7890.34</v>
+        <v>751.6900000000001</v>
       </c>
       <c r="AE6" t="n">
-        <v>7947.17</v>
+        <v>764.8200000000001</v>
       </c>
       <c r="AF6" t="n">
-        <v>74.09999999999999</v>
+        <v>48.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI6" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37.3</v>
+        <v>49</v>
       </c>
       <c r="AK6" t="n">
-        <v>31.5</v>
+        <v>15.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>23.2</v>
+        <v>20.9</v>
       </c>
       <c r="AM6" t="n">
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>9251.1</v>
+        <v>758.27</v>
       </c>
       <c r="AO6" t="n">
-        <v>6460.02</v>
+        <v>719.9400000000001</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹215,046.57 Cr., a P/E ratio of 37.31, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.10 (Bullish Momentum Zone), while MACD Line (121.41) trades above Signal (84.99) with an expanding histogram (+36.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.19% above the 200-day DMA (₹7171.21). Daily volatility envelope is bounded by ATR(14) of ₹150.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,833.50) is positioned above the 30-day DMA (₹7,437.81), 50-day DMA (₹7,344.46), and 200-day DMA (₹7,171.21). The price distance from 200 DMA is +9.19%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[7833.5, 7857.0, 7880.5, 7904.0, 7927.5, 7951.0]</t>
+          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[7833.5, 7917.23, 7965.67, 8008.32, 8047.95, 8085.67]</t>
+          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>[7833.5, 7811.83, 7816.62, 7825.77, 7837.16, 7850.0]</t>
+          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
         </is>
       </c>
     </row>
@@ -1496,162 +1496,162 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>105127.58</v>
+        <v>310746.28</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>738.55</v>
+        <v>4646.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹735.6 - ₹742.98</t>
+          <t>₹4629.85 - ₹4671.48</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>750.37</v>
+        <v>4713.1</v>
       </c>
       <c r="I7" t="n">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="J7" t="n">
-        <v>729.51</v>
+        <v>4471.9</v>
       </c>
       <c r="K7" t="n">
-        <v>703.6799999999999</v>
+        <v>4404.23</v>
       </c>
       <c r="L7" t="n">
-        <v>686.09</v>
+        <v>4346.03</v>
       </c>
       <c r="M7" t="n">
-        <v>9.210000000000001</v>
+        <v>5.42</v>
       </c>
       <c r="N7" t="n">
-        <v>8.49</v>
+        <v>56.6</v>
       </c>
       <c r="O7" t="n">
-        <v>9.380000000000001</v>
+        <v>49.9</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9</v>
+        <v>6.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.77</v>
+        <v>83.25</v>
       </c>
       <c r="R7" t="n">
         <v>11.76</v>
       </c>
       <c r="S7" t="n">
-        <v>49.3</v>
+        <v>41.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.13</v>
+        <v>-1.23</v>
       </c>
       <c r="V7" t="n">
-        <v>53</v>
+        <v>41.7</v>
       </c>
       <c r="W7" t="n">
-        <v>2.84</v>
+        <v>2.15</v>
       </c>
       <c r="X7" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>727.6</v>
+        <v>4548.57</v>
       </c>
       <c r="Z7" t="n">
-        <v>753.45</v>
+        <v>4711.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>744.46</v>
+        <v>4683.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>716.39</v>
+        <v>4521.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>744.27</v>
+        <v>4635.53</v>
       </c>
       <c r="AD7" t="n">
-        <v>751.6900000000001</v>
+        <v>4679.96</v>
       </c>
       <c r="AE7" t="n">
-        <v>764.8200000000001</v>
+        <v>4713.43</v>
       </c>
       <c r="AF7" t="n">
-        <v>48.2</v>
+        <v>59.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI7" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>49</v>
+        <v>34.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>15.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>20.9</v>
+        <v>27.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AN7" t="n">
-        <v>767.5700000000001</v>
+        <v>4768.55</v>
       </c>
       <c r="AO7" t="n">
-        <v>710.38</v>
+        <v>4526.98</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
+          <t>[4646.5, 4660.44, 4674.38, 4688.32, 4702.26, 4716.2]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
+          <t>[4646.5, 4693.74, 4721.47, 4746.0, 4768.86, 4790.66]</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
+          <t>[4646.5, 4635.46, 4639.06, 4645.06, 4652.31, 4660.35]</t>
         </is>
       </c>
     </row>
@@ -1663,162 +1663,162 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105169.94</v>
+        <v>98206.09</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2199.8</v>
+        <v>372.95</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹2190.26 - ₹2214.11</t>
+          <t>₹371.41 - ₹375.26</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2237.97</v>
+        <v>379.11</v>
       </c>
       <c r="I8" t="n">
-        <v>69</v>
+        <v>432</v>
       </c>
       <c r="J8" t="n">
-        <v>2140.62</v>
+        <v>357.21</v>
       </c>
       <c r="K8" t="n">
-        <v>2061.08</v>
+        <v>349.78</v>
       </c>
       <c r="L8" t="n">
-        <v>1703.8</v>
+        <v>347.56</v>
       </c>
       <c r="M8" t="n">
-        <v>27.05</v>
+        <v>6.64</v>
       </c>
       <c r="N8" t="n">
-        <v>29.77</v>
+        <v>4.07</v>
       </c>
       <c r="O8" t="n">
-        <v>35.4</v>
+        <v>2.35</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>47.71</v>
+        <v>7.7</v>
       </c>
       <c r="R8" t="n">
         <v>11.76</v>
       </c>
       <c r="S8" t="n">
-        <v>50.7</v>
+        <v>47.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2</v>
+        <v>-1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="W8" t="n">
-        <v>2.26</v>
+        <v>2.81</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>2170.27</v>
+        <v>366.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>2247.27</v>
+        <v>379.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>2217.4</v>
+        <v>375.93</v>
       </c>
       <c r="AB8" t="n">
-        <v>2128.24</v>
+        <v>361.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2191.3</v>
+        <v>372.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>2221.1</v>
+        <v>374.64</v>
       </c>
       <c r="AE8" t="n">
-        <v>2242.4</v>
+        <v>376.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>57.9</v>
+        <v>78.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI8" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>97.09999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>17.5</v>
+        <v>25.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>6.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>2307.76</v>
+        <v>383.02</v>
       </c>
       <c r="AO8" t="n">
-        <v>2092.5</v>
+        <v>363.06</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[2199.8, 2206.4, 2213.0, 2219.6, 2226.2, 2232.8]</t>
+          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[2199.8, 2225.48, 2239.99, 2252.65, 2264.36, 2275.47]</t>
+          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>[2199.8, 2192.09, 2192.76, 2194.81, 2197.57, 2200.79]</t>
+          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1888,28 +1888,28 @@
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>48.1</v>
+        <v>47</v>
       </c>
       <c r="T9" t="n">
         <v>0.23</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.44</v>
+        <v>-1.48</v>
       </c>
       <c r="V9" t="n">
-        <v>50.3</v>
+        <v>45</v>
       </c>
       <c r="W9" t="n">
-        <v>3.4</v>
+        <v>11.03</v>
       </c>
       <c r="X9" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>1442.83</v>
+        <v>1431.86</v>
       </c>
       <c r="Z9" t="n">
-        <v>1494.39</v>
+        <v>1388.25</v>
       </c>
       <c r="AA9" t="n">
         <v>1484.99</v>
@@ -1953,10 +1953,10 @@
         <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>2156.84</v>
+        <v>1504.86</v>
       </c>
       <c r="AO9" t="n">
-        <v>813.36</v>
+        <v>1439.62</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -2055,28 +2055,28 @@
         <v>11.76</v>
       </c>
       <c r="S10" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="T10" t="n">
         <v>0.18</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.85</v>
+        <v>-1.82</v>
       </c>
       <c r="V10" t="n">
-        <v>52.2</v>
+        <v>55</v>
       </c>
       <c r="W10" t="n">
-        <v>2.72</v>
+        <v>3.38</v>
       </c>
       <c r="X10" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>1033.78</v>
+        <v>1019.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>1070.41</v>
+        <v>1056.01</v>
       </c>
       <c r="AA10" t="n">
         <v>1055.07</v>
@@ -2120,10 +2120,10 @@
         <v>18.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>1093.82</v>
+        <v>1088.74</v>
       </c>
       <c r="AO10" t="n">
-        <v>1002.87</v>
+        <v>1013.57</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2173,153 +2173,153 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>85420.58</v>
+        <v>146280.27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>14049</v>
+        <v>1651.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹13965.8 - ₹14173.8</t>
+          <t>₹1641.81 - ₹1665.54</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14381.8</v>
+        <v>1689.26</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="J11" t="n">
-        <v>13190.57</v>
+        <v>1478.49</v>
       </c>
       <c r="K11" t="n">
-        <v>12605.68</v>
+        <v>1460.44</v>
       </c>
       <c r="L11" t="n">
-        <v>12333.95</v>
+        <v>1458.79</v>
       </c>
       <c r="M11" t="n">
-        <v>16.25</v>
+        <v>14.41</v>
       </c>
       <c r="N11" t="n">
-        <v>477.1</v>
+        <v>56.22</v>
       </c>
       <c r="O11" t="n">
-        <v>503.84</v>
+        <v>42.84</v>
       </c>
       <c r="P11" t="n">
-        <v>-26.74</v>
+        <v>13.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>416</v>
+        <v>47.45</v>
       </c>
       <c r="R11" t="n">
         <v>11.76</v>
       </c>
       <c r="S11" t="n">
-        <v>49.3</v>
+        <v>44.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.86</v>
+        <v>-2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>48.9</v>
+        <v>48.3</v>
       </c>
       <c r="W11" t="n">
-        <v>3.54</v>
+        <v>8.69</v>
       </c>
       <c r="X11" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>13933.38</v>
+        <v>1625.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>14425.1</v>
+        <v>1683.13</v>
       </c>
       <c r="AA11" t="n">
-        <v>14161.39</v>
+        <v>1664.51</v>
       </c>
       <c r="AB11" t="n">
-        <v>13425</v>
+        <v>1580.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>14079.67</v>
+        <v>1641.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>14558.34</v>
+        <v>1671.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>15067.67</v>
+        <v>1692.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>64.7</v>
+        <v>86.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI11" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>41.2</v>
+        <v>28.6</v>
       </c>
       <c r="AK11" t="n">
-        <v>21.1</v>
+        <v>17.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM11" t="n">
         <v>15</v>
       </c>
       <c r="AN11" t="n">
-        <v>14691.98</v>
+        <v>1700.37</v>
       </c>
       <c r="AO11" t="n">
-        <v>13511.14</v>
+        <v>1608.23</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[14049.0, 14144.12, 14239.24, 14334.35, 14429.47, 14524.59]</t>
+          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[14049.0, 14310.52, 14474.56, 14622.57, 14762.27, 14896.67]</t>
+          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>[14049.0, 14019.32, 14062.74, 14118.19, 14179.87, 14245.53]</t>
+          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>146280.27</v>
+        <v>85420.58</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2348,145 +2348,145 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1651.3</v>
+        <v>14049</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹1641.81 - ₹1665.54</t>
+          <t>₹13965.8 - ₹14173.8</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1689.26</v>
+        <v>14381.8</v>
       </c>
       <c r="I12" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>1478.49</v>
+        <v>13190.57</v>
       </c>
       <c r="K12" t="n">
-        <v>1460.44</v>
+        <v>12605.68</v>
       </c>
       <c r="L12" t="n">
-        <v>1458.79</v>
+        <v>12333.95</v>
       </c>
       <c r="M12" t="n">
-        <v>14.41</v>
+        <v>16.25</v>
       </c>
       <c r="N12" t="n">
-        <v>56.22</v>
+        <v>477.1</v>
       </c>
       <c r="O12" t="n">
-        <v>42.84</v>
+        <v>503.84</v>
       </c>
       <c r="P12" t="n">
-        <v>13.38</v>
+        <v>-26.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>47.45</v>
+        <v>416</v>
       </c>
       <c r="R12" t="n">
         <v>11.76</v>
       </c>
       <c r="S12" t="n">
-        <v>47.8</v>
+        <v>45.7</v>
       </c>
       <c r="T12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.87</v>
+        <v>-2.05</v>
       </c>
       <c r="V12" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.71</v>
+        <v>6.67</v>
       </c>
       <c r="X12" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>1628.92</v>
+        <v>13634.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>1686.72</v>
+        <v>14126.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>1664.51</v>
+        <v>14161.39</v>
       </c>
       <c r="AB12" t="n">
-        <v>1580.13</v>
+        <v>13425</v>
       </c>
       <c r="AC12" t="n">
-        <v>1641.1</v>
+        <v>14079.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>1671.7</v>
+        <v>14558.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>1692.1</v>
+        <v>15067.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>86.2</v>
+        <v>64.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI12" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>28.6</v>
+        <v>41.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>17.7</v>
+        <v>21.1</v>
       </c>
       <c r="AL12" t="n">
-        <v>8.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AM12" t="n">
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>1712.49</v>
+        <v>14625.09</v>
       </c>
       <c r="AO12" t="n">
-        <v>1593.5</v>
+        <v>13525.23</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
+          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
+          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
+          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
         </is>
       </c>
     </row>
@@ -2498,16 +2498,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>63429.15</v>
+        <v>17572.27</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2515,145 +2515,145 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2105.7</v>
+        <v>613.35</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹2092.64 - ₹2125.3</t>
+          <t>₹608.87 - ₹620.07</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2157.96</v>
+        <v>631.27</v>
       </c>
       <c r="I13" t="n">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="J13" t="n">
-        <v>1999.45</v>
+        <v>578.01</v>
       </c>
       <c r="K13" t="n">
-        <v>1888.17</v>
+        <v>541.38</v>
       </c>
       <c r="L13" t="n">
-        <v>1880.41</v>
+        <v>553.54</v>
       </c>
       <c r="M13" t="n">
-        <v>12.26</v>
+        <v>10.74</v>
       </c>
       <c r="N13" t="n">
-        <v>62.25</v>
+        <v>14.56</v>
       </c>
       <c r="O13" t="n">
-        <v>68.98</v>
+        <v>16.43</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.73</v>
+        <v>-1.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.31999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="R13" t="n">
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>48.4</v>
+        <v>51.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.01</v>
+        <v>-2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>52.5</v>
+        <v>53.3</v>
       </c>
       <c r="W13" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="X13" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>2079.55</v>
+        <v>590.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>2153.25</v>
+        <v>611.73</v>
       </c>
       <c r="AA13" t="n">
-        <v>2122.55</v>
+        <v>618.26</v>
       </c>
       <c r="AB13" t="n">
-        <v>2007.72</v>
+        <v>579.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>2111.93</v>
+        <v>616.27</v>
       </c>
       <c r="AD13" t="n">
-        <v>2127.76</v>
+        <v>624.54</v>
       </c>
       <c r="AE13" t="n">
-        <v>2149.83</v>
+        <v>635.72</v>
       </c>
       <c r="AF13" t="n">
-        <v>48.8</v>
+        <v>60.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI13" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>34.2</v>
+        <v>88.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>63</v>
+        <v>-10.1</v>
       </c>
       <c r="AL13" t="n">
-        <v>36.1</v>
+        <v>3.7</v>
       </c>
       <c r="AM13" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="AN13" t="n">
-        <v>2188.09</v>
+        <v>645.35</v>
       </c>
       <c r="AO13" t="n">
-        <v>2027.94</v>
+        <v>584.29</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
+          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
+          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
+          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
         </is>
       </c>
     </row>
@@ -2665,162 +2665,162 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17572.27</v>
+        <v>63429.15</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>613.35</v>
+        <v>2105.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹608.87 - ₹620.07</t>
+          <t>₹2092.64 - ₹2125.3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>631.27</v>
+        <v>2157.96</v>
       </c>
       <c r="I14" t="n">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="J14" t="n">
-        <v>578.01</v>
+        <v>1999.45</v>
       </c>
       <c r="K14" t="n">
-        <v>541.38</v>
+        <v>1888.17</v>
       </c>
       <c r="L14" t="n">
-        <v>553.54</v>
+        <v>1880.41</v>
       </c>
       <c r="M14" t="n">
-        <v>10.74</v>
+        <v>12.26</v>
       </c>
       <c r="N14" t="n">
-        <v>14.56</v>
+        <v>62.25</v>
       </c>
       <c r="O14" t="n">
-        <v>16.43</v>
+        <v>68.98</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.88</v>
+        <v>-6.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.4</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="R14" t="n">
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>49</v>
+        <v>42.9</v>
       </c>
       <c r="T14" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.4</v>
+        <v>-2.31</v>
       </c>
       <c r="V14" t="n">
-        <v>48.1</v>
+        <v>51.7</v>
       </c>
       <c r="W14" t="n">
-        <v>6.55</v>
+        <v>4.49</v>
       </c>
       <c r="X14" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>605.5</v>
+        <v>2027.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>626.97</v>
+        <v>2032.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>618.26</v>
+        <v>2122.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>579.75</v>
+        <v>2007.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>616.27</v>
+        <v>2111.93</v>
       </c>
       <c r="AD14" t="n">
-        <v>624.54</v>
+        <v>2127.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>635.72</v>
+        <v>2149.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>60.8</v>
+        <v>48.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI14" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>88.5</v>
+        <v>34.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>-10.1</v>
+        <v>63</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.7</v>
+        <v>36.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="AN14" t="n">
-        <v>658.1900000000001</v>
+        <v>2174.81</v>
       </c>
       <c r="AO14" t="n">
-        <v>571.33</v>
+        <v>2031.51</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
+          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
+          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
+          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
         </is>
       </c>
     </row>
@@ -2832,16 +2832,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76187.09</v>
+        <v>278417.14</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2849,145 +2849,145 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1721</v>
+        <v>302.45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹1709.13 - ₹1738.8</t>
+          <t>₹300.39 - ₹305.53</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1768.46</v>
+        <v>310.68</v>
       </c>
       <c r="I15" t="n">
-        <v>56</v>
+        <v>324</v>
       </c>
       <c r="J15" t="n">
-        <v>1505.99</v>
+        <v>281.7</v>
       </c>
       <c r="K15" t="n">
-        <v>1472.15</v>
+        <v>268.93</v>
       </c>
       <c r="L15" t="n">
-        <v>1507.99</v>
+        <v>274.01</v>
       </c>
       <c r="M15" t="n">
-        <v>15.58</v>
+        <v>13.37</v>
       </c>
       <c r="N15" t="n">
-        <v>53.48</v>
+        <v>9.93</v>
       </c>
       <c r="O15" t="n">
-        <v>30.14</v>
+        <v>8.42</v>
       </c>
       <c r="P15" t="n">
-        <v>23.34</v>
+        <v>1.51</v>
       </c>
       <c r="Q15" t="n">
-        <v>59.33</v>
+        <v>10.28</v>
       </c>
       <c r="R15" t="n">
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>43.9</v>
+        <v>43.6</v>
       </c>
       <c r="T15" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.55</v>
+        <v>-2.53</v>
       </c>
       <c r="V15" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="W15" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>1695.71</v>
+        <v>299.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>1755.94</v>
+        <v>309.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>1734.77</v>
+        <v>304.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1632.01</v>
+        <v>287.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1713.83</v>
+        <v>306.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1745.96</v>
+        <v>311.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1770.93</v>
+        <v>320.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>77.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>35.2</v>
+        <v>672.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>49.9</v>
+        <v>182</v>
       </c>
       <c r="AL15" t="n">
-        <v>9.6</v>
+        <v>0.6</v>
       </c>
       <c r="AM15" t="n">
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>1810.49</v>
+        <v>313.72</v>
       </c>
       <c r="AO15" t="n">
-        <v>1644.19</v>
+        <v>292.31</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,187.09 Cr., a P/E ratio of 35.21, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.48) trades above Signal (30.14) with an expanding histogram (+23.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1507.99). Daily volatility envelope is bounded by ATR(14) of ₹59.33.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,721.00) is positioned above the 30-day DMA (₹1,505.99), 50-day DMA (₹1,472.15), and 200-day DMA (₹1,507.99). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[1721.0, 1726.16, 1731.33, 1736.49, 1741.65, 1746.81]</t>
+          <t>[302.45, 303.8, 305.15, 306.5, 307.85, 309.19]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[1721.0, 1749.89, 1764.89, 1777.59, 1789.11, 1799.88]</t>
+          <t>[302.45, 307.91, 310.96, 313.62, 316.07, 318.39]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[1721.0, 1708.36, 1706.16, 1705.66, 1706.06, 1707.02]</t>
+          <t>[302.45, 300.71, 300.79, 301.15, 301.68, 302.3]</t>
         </is>
       </c>
     </row>
@@ -2999,16 +2999,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>278417.14</v>
+        <v>76187.09</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3016,145 +3016,145 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>302.45</v>
+        <v>1721</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹300.39 - ₹305.53</t>
+          <t>₹1709.13 - ₹1738.8</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>310.68</v>
+        <v>1768.46</v>
       </c>
       <c r="I16" t="n">
-        <v>324</v>
+        <v>56</v>
       </c>
       <c r="J16" t="n">
-        <v>281.7</v>
+        <v>1505.99</v>
       </c>
       <c r="K16" t="n">
-        <v>268.93</v>
+        <v>1472.15</v>
       </c>
       <c r="L16" t="n">
-        <v>274.01</v>
+        <v>1507.99</v>
       </c>
       <c r="M16" t="n">
-        <v>13.37</v>
+        <v>15.58</v>
       </c>
       <c r="N16" t="n">
-        <v>9.93</v>
+        <v>53.48</v>
       </c>
       <c r="O16" t="n">
-        <v>8.42</v>
+        <v>30.14</v>
       </c>
       <c r="P16" t="n">
-        <v>1.51</v>
+        <v>23.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>10.28</v>
+        <v>59.33</v>
       </c>
       <c r="R16" t="n">
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>42.4</v>
+        <v>41.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="V16" t="n">
-        <v>46.4</v>
+        <v>48.3</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4</v>
+        <v>7.48</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>299.14</v>
+        <v>1705.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>309.72</v>
+        <v>1765.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>304.87</v>
+        <v>1734.77</v>
       </c>
       <c r="AB16" t="n">
-        <v>287.03</v>
+        <v>1632.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>306.75</v>
+        <v>1713.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>311.7</v>
+        <v>1745.96</v>
       </c>
       <c r="AE16" t="n">
-        <v>320.95</v>
+        <v>1770.93</v>
       </c>
       <c r="AF16" t="n">
-        <v>65.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>672.1</v>
+        <v>35.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>182</v>
+        <v>49.9</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.6</v>
+        <v>9.6</v>
       </c>
       <c r="AM16" t="n">
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>317.38</v>
+        <v>1788.88</v>
       </c>
       <c r="AO16" t="n">
-        <v>287.93</v>
+        <v>1658.41</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,187.09 Cr., a P/E ratio of 35.21, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.48) trades above Signal (30.14) with an expanding histogram (+23.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1507.99). Daily volatility envelope is bounded by ATR(14) of ₹59.33.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,721.00) is positioned above the 30-day DMA (₹1,505.99), 50-day DMA (₹1,472.15), and 200-day DMA (₹1,507.99). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[302.45, 303.67, 304.9, 306.12, 307.35, 308.57]</t>
+          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[302.45, 307.79, 310.72, 313.25, 315.57, 317.77]</t>
+          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.21, 1823.74]</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>[302.45, 300.59, 300.54, 300.78, 301.18, 301.67]</t>
+          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU16"/>
+  <dimension ref="A1:AU21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,13 +719,13 @@
         <v>11.76</v>
       </c>
       <c r="S2" t="n">
-        <v>55.2</v>
+        <v>55</v>
       </c>
       <c r="T2" t="n">
         <v>0.32</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="V2" t="n">
         <v>60</v>
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1462.68</v>
+        <v>1461.76</v>
       </c>
       <c r="AO2" t="n">
-        <v>1407.05</v>
+        <v>1408.25</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="T3" t="n">
         <v>0.29</v>
@@ -951,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>115.97</v>
+        <v>115.91</v>
       </c>
       <c r="AO3" t="n">
-        <v>109.92</v>
+        <v>109.56</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1053,13 +1053,13 @@
         <v>11.76</v>
       </c>
       <c r="S4" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="n">
         <v>0.39</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9</v>
+        <v>-0.88</v>
       </c>
       <c r="V4" t="n">
         <v>48.3</v>
@@ -1118,10 +1118,10 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>8055.52</v>
+        <v>8041.19</v>
       </c>
       <c r="AO4" t="n">
-        <v>7646.07</v>
+        <v>7635.76</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>105169.94</v>
+        <v>350150.12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,145 +1179,145 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2199.8</v>
+        <v>11903</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹2190.26 - ₹2214.11</t>
+          <t>₹11859.37 - ₹11968.45</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2237.97</v>
+        <v>12077.53</v>
       </c>
       <c r="I5" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>2140.62</v>
+        <v>11421.23</v>
       </c>
       <c r="K5" t="n">
-        <v>2061.08</v>
+        <v>11269.86</v>
       </c>
       <c r="L5" t="n">
-        <v>1703.8</v>
+        <v>11569.69</v>
       </c>
       <c r="M5" t="n">
-        <v>27.05</v>
+        <v>2.4</v>
       </c>
       <c r="N5" t="n">
-        <v>29.77</v>
+        <v>143.27</v>
       </c>
       <c r="O5" t="n">
-        <v>35.4</v>
+        <v>124.24</v>
       </c>
       <c r="P5" t="n">
-        <v>-5.63</v>
+        <v>19.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>47.71</v>
+        <v>218.17</v>
       </c>
       <c r="R5" t="n">
         <v>11.76</v>
       </c>
       <c r="S5" t="n">
-        <v>49.8</v>
+        <v>52</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.23</v>
+        <v>-0.9</v>
       </c>
       <c r="V5" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="X5" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>2184.76</v>
+        <v>11731.98</v>
       </c>
       <c r="Z5" t="n">
-        <v>2261.76</v>
+        <v>12148.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>2217.76</v>
+        <v>11998.22</v>
       </c>
       <c r="AB5" t="n">
-        <v>2128.24</v>
+        <v>11575.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>2191.3</v>
+        <v>11903.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>2221.1</v>
+        <v>12008.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>2242.4</v>
+        <v>12113.67</v>
       </c>
       <c r="AF5" t="n">
-        <v>57.9</v>
+        <v>62.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI5" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ5" t="n">
-        <v>97.09999999999999</v>
+        <v>41</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.5</v>
+        <v>15.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AM5" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>2266.77</v>
+        <v>12169.67</v>
       </c>
       <c r="AO5" t="n">
-        <v>2139.2</v>
+        <v>11653.21</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹350,150.12 Cr., a P/E ratio of 40.98, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (143.27) trades above Signal (124.24) with an expanding histogram (+19.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.40% above the 200-day DMA (₹11569.69). Daily volatility envelope is bounded by ATR(14) of ₹218.17.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,903.00) is positioned above the 30-day DMA (₹11,421.23), 50-day DMA (₹11,269.86), and 200-day DMA (₹11,569.69). The price distance from 200 DMA is +2.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[2199.8, 2217.76, 2235.72, 2253.68, 2271.64, 2289.6]</t>
+          <t>[11903.0, 11938.71, 11974.42, 12010.13, 12045.84, 12081.54]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[2199.8, 2236.84, 2262.71, 2286.73, 2309.8, 2332.27]</t>
+          <t>[11903.0, 12025.98, 12097.83, 12161.28, 12220.37, 12276.68]</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>[2199.8, 2203.45, 2215.48, 2228.89, 2243.01, 2257.59]</t>
+          <t>[11903.0, 11873.26, 11881.86, 11896.76, 11914.94, 11935.19]</t>
         </is>
       </c>
     </row>
@@ -1329,162 +1329,162 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>105127.58</v>
+        <v>263368.34</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>738.55</v>
+        <v>2747.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹735.6 - ₹742.98</t>
+          <t>₹2735.68 - ₹2764.73</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>750.37</v>
+        <v>2793.77</v>
       </c>
       <c r="I6" t="n">
-        <v>225</v>
+        <v>57</v>
       </c>
       <c r="J6" t="n">
-        <v>729.51</v>
+        <v>2687.86</v>
       </c>
       <c r="K6" t="n">
-        <v>703.6799999999999</v>
+        <v>2678.76</v>
       </c>
       <c r="L6" t="n">
-        <v>686.09</v>
+        <v>2570.71</v>
       </c>
       <c r="M6" t="n">
-        <v>9.210000000000001</v>
+        <v>6.83</v>
       </c>
       <c r="N6" t="n">
-        <v>8.49</v>
+        <v>16.14</v>
       </c>
       <c r="O6" t="n">
-        <v>9.380000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9</v>
+        <v>6.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.77</v>
+        <v>58.09</v>
       </c>
       <c r="R6" t="n">
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>46.5</v>
+        <v>52.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.23</v>
+        <v>-1.1</v>
       </c>
       <c r="V6" t="n">
         <v>55</v>
       </c>
       <c r="W6" t="n">
-        <v>5.75</v>
+        <v>1.89</v>
       </c>
       <c r="X6" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>720.8200000000001</v>
+        <v>2707.06</v>
       </c>
       <c r="Z6" t="n">
-        <v>725.27</v>
+        <v>2803.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>744.46</v>
+        <v>2769.28</v>
       </c>
       <c r="AB6" t="n">
-        <v>716.39</v>
+        <v>2660.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>744.27</v>
+        <v>2751.53</v>
       </c>
       <c r="AD6" t="n">
-        <v>751.6900000000001</v>
+        <v>2770.66</v>
       </c>
       <c r="AE6" t="n">
-        <v>764.8200000000001</v>
+        <v>2794.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>48.2</v>
+        <v>62.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI6" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>49</v>
+        <v>55.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>15.1</v>
+        <v>17.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>20.9</v>
+        <v>12.8</v>
       </c>
       <c r="AM6" t="n">
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>758.27</v>
+        <v>2815.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>719.9400000000001</v>
+        <v>2690.4</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹263,368.34 Cr., a P/E ratio of 55.24, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.38 (Bullish Momentum Zone), while MACD Line (16.14) trades above Signal (10.09) with an expanding histogram (+6.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.83% above the 200-day DMA (₹2570.71). Daily volatility envelope is bounded by ATR(14) of ₹58.09.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,747.30) is positioned above the 30-day DMA (₹2,687.86), 50-day DMA (₹2,678.76), and 200-day DMA (₹2,570.71). The price distance from 200 DMA is +6.83%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
+          <t>[2747.3, 2755.54, 2763.78, 2772.03, 2780.27, 2788.51]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
+          <t>[2747.3, 2778.78, 2796.64, 2812.27, 2826.74, 2840.46]</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
+          <t>[2747.3, 2738.12, 2739.14, 2741.84, 2745.42, 2749.54]</t>
         </is>
       </c>
     </row>
@@ -1496,162 +1496,162 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>310746.28</v>
+        <v>105169.94</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4646.5</v>
+        <v>2199.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹4629.85 - ₹4671.48</t>
+          <t>₹2190.26 - ₹2214.11</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4713.1</v>
+        <v>2237.97</v>
       </c>
       <c r="I7" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="J7" t="n">
-        <v>4471.9</v>
+        <v>2140.62</v>
       </c>
       <c r="K7" t="n">
-        <v>4404.23</v>
+        <v>2061.08</v>
       </c>
       <c r="L7" t="n">
-        <v>4346.03</v>
+        <v>1703.8</v>
       </c>
       <c r="M7" t="n">
-        <v>5.42</v>
+        <v>27.05</v>
       </c>
       <c r="N7" t="n">
-        <v>56.6</v>
+        <v>29.77</v>
       </c>
       <c r="O7" t="n">
-        <v>49.9</v>
+        <v>35.4</v>
       </c>
       <c r="P7" t="n">
-        <v>6.7</v>
+        <v>-5.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>83.25</v>
+        <v>47.71</v>
       </c>
       <c r="R7" t="n">
         <v>11.76</v>
       </c>
       <c r="S7" t="n">
-        <v>41.7</v>
+        <v>50.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.23</v>
+        <v>-1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="W7" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="X7" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>4548.57</v>
+        <v>2184.77</v>
       </c>
       <c r="Z7" t="n">
-        <v>4711.2</v>
+        <v>2261.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>4683.67</v>
+        <v>2217.76</v>
       </c>
       <c r="AB7" t="n">
-        <v>4521.62</v>
+        <v>2128.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>4635.53</v>
+        <v>2191.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>4679.96</v>
+        <v>2221.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>4713.43</v>
+        <v>2242.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI7" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.8</v>
+        <v>17.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>27.5</v>
+        <v>6.4</v>
       </c>
       <c r="AM7" t="n">
-        <v>24</v>
+        <v>11.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>4768.55</v>
+        <v>2269.73</v>
       </c>
       <c r="AO7" t="n">
-        <v>4526.98</v>
+        <v>2143.05</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[4646.5, 4660.44, 4674.38, 4688.32, 4702.26, 4716.2]</t>
+          <t>[2199.8, 2217.76, 2235.73, 2253.69, 2271.66, 2289.62]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[4646.5, 4693.74, 4721.47, 4746.0, 4768.86, 4790.66]</t>
+          <t>[2199.8, 2236.85, 2262.72, 2286.74, 2309.82, 2332.29]</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>[4646.5, 4635.46, 4639.06, 4645.06, 4652.31, 4660.35]</t>
+          <t>[2199.8, 2203.45, 2215.49, 2228.9, 2243.03, 2257.62]</t>
         </is>
       </c>
     </row>
@@ -1663,16 +1663,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>98206.09</v>
+        <v>105127.58</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,145 +1680,145 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>372.95</v>
+        <v>738.55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹371.41 - ₹375.26</t>
+          <t>₹735.6 - ₹742.98</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>379.11</v>
+        <v>750.37</v>
       </c>
       <c r="I8" t="n">
-        <v>432</v>
+        <v>225</v>
       </c>
       <c r="J8" t="n">
-        <v>357.21</v>
+        <v>729.51</v>
       </c>
       <c r="K8" t="n">
-        <v>349.78</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>347.56</v>
+        <v>686.09</v>
       </c>
       <c r="M8" t="n">
-        <v>6.64</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>4.07</v>
+        <v>8.49</v>
       </c>
       <c r="O8" t="n">
-        <v>2.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>-0.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.7</v>
+        <v>14.77</v>
       </c>
       <c r="R8" t="n">
         <v>11.76</v>
       </c>
       <c r="S8" t="n">
-        <v>47.2</v>
+        <v>46.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.26</v>
+        <v>-1.23</v>
       </c>
       <c r="V8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="W8" t="n">
-        <v>2.81</v>
+        <v>5.75</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>366.16</v>
+        <v>720.8200000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>379.22</v>
+        <v>725.27</v>
       </c>
       <c r="AA8" t="n">
-        <v>375.93</v>
+        <v>744.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>361.4</v>
+        <v>716.39</v>
       </c>
       <c r="AC8" t="n">
-        <v>372.32</v>
+        <v>744.27</v>
       </c>
       <c r="AD8" t="n">
-        <v>374.64</v>
+        <v>751.6900000000001</v>
       </c>
       <c r="AE8" t="n">
-        <v>376.32</v>
+        <v>764.8200000000001</v>
       </c>
       <c r="AF8" t="n">
-        <v>78.3</v>
+        <v>48.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI8" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6.1</v>
+        <v>49</v>
       </c>
       <c r="AK8" t="n">
-        <v>25.2</v>
+        <v>15.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>68.90000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="AM8" t="n">
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>383.02</v>
+        <v>757.9</v>
       </c>
       <c r="AO8" t="n">
-        <v>363.06</v>
+        <v>721.0599999999999</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹98,206.09 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
+          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
+          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
+          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
         </is>
       </c>
     </row>
@@ -1830,16 +1830,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>119011.76</v>
+        <v>310746.28</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,145 +1847,145 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1473.2</v>
+        <v>4646.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹1466.31 - ₹1483.53</t>
+          <t>₹4629.85 - ₹4671.48</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1500.76</v>
+        <v>4713.1</v>
       </c>
       <c r="I9" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="J9" t="n">
-        <v>1436.14</v>
+        <v>4471.9</v>
       </c>
       <c r="K9" t="n">
-        <v>1414.83</v>
+        <v>4404.23</v>
       </c>
       <c r="L9" t="n">
-        <v>1396.09</v>
+        <v>4346.03</v>
       </c>
       <c r="M9" t="n">
-        <v>5.04</v>
+        <v>5.42</v>
       </c>
       <c r="N9" t="n">
-        <v>8.130000000000001</v>
+        <v>56.6</v>
       </c>
       <c r="O9" t="n">
-        <v>6.31</v>
+        <v>49.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>6.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>34.45</v>
+        <v>83.25</v>
       </c>
       <c r="R9" t="n">
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>47</v>
+        <v>41.7</v>
       </c>
       <c r="T9" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.48</v>
+        <v>-1.23</v>
       </c>
       <c r="V9" t="n">
-        <v>45</v>
+        <v>41.7</v>
       </c>
       <c r="W9" t="n">
-        <v>11.03</v>
+        <v>2.15</v>
       </c>
       <c r="X9" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>1431.86</v>
+        <v>4548.63</v>
       </c>
       <c r="Z9" t="n">
-        <v>1388.25</v>
+        <v>4711.26</v>
       </c>
       <c r="AA9" t="n">
-        <v>1484.99</v>
+        <v>4683.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>1421.52</v>
+        <v>4521.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>1471.43</v>
+        <v>4635.53</v>
       </c>
       <c r="AD9" t="n">
-        <v>1480.56</v>
+        <v>4679.96</v>
       </c>
       <c r="AE9" t="n">
-        <v>1487.93</v>
+        <v>4713.43</v>
       </c>
       <c r="AF9" t="n">
-        <v>56.5</v>
+        <v>59.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.08</v>
+        <v>0.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI9" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>35.3</v>
+        <v>34.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
-        <v>12</v>
+        <v>27.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AN9" t="n">
-        <v>1504.86</v>
+        <v>4762.32</v>
       </c>
       <c r="AO9" t="n">
-        <v>1439.62</v>
+        <v>4517.79</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
+          <t>[4646.5, 4660.44, 4674.38, 4688.32, 4702.26, 4716.2]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
+          <t>[4646.5, 4693.74, 4721.47, 4746.0, 4768.86, 4790.66]</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
+          <t>[4646.5, 4635.46, 4639.06, 4645.06, 4652.31, 4660.35]</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2006,153 +2006,153 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>246283.11</v>
+        <v>25000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1046.7</v>
+        <v>372.95</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹1040.39 - ₹1056.17</t>
+          <t>₹371.41 - ₹375.26</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1071.96</v>
+        <v>379.11</v>
       </c>
       <c r="I10" t="n">
-        <v>105</v>
+        <v>432</v>
       </c>
       <c r="J10" t="n">
-        <v>1032.61</v>
+        <v>357.21</v>
       </c>
       <c r="K10" t="n">
-        <v>994.9400000000001</v>
+        <v>349.78</v>
       </c>
       <c r="L10" t="n">
-        <v>942.9400000000001</v>
+        <v>347.56</v>
       </c>
       <c r="M10" t="n">
-        <v>8.94</v>
+        <v>6.64</v>
       </c>
       <c r="N10" t="n">
-        <v>8.390000000000001</v>
+        <v>4.07</v>
       </c>
       <c r="O10" t="n">
-        <v>12.02</v>
+        <v>2.35</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>31.57</v>
+        <v>7.7</v>
       </c>
       <c r="R10" t="n">
         <v>11.76</v>
       </c>
       <c r="S10" t="n">
-        <v>50.8</v>
+        <v>47</v>
       </c>
       <c r="T10" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.82</v>
+        <v>-1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="W10" t="n">
-        <v>3.38</v>
+        <v>2.81</v>
       </c>
       <c r="X10" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>1019.37</v>
+        <v>366.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>1056.01</v>
+        <v>379.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>1055.07</v>
+        <v>375.93</v>
       </c>
       <c r="AB10" t="n">
-        <v>999.34</v>
+        <v>361.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1043.47</v>
+        <v>372.32</v>
       </c>
       <c r="AD10" t="n">
-        <v>1057.84</v>
+        <v>374.64</v>
       </c>
       <c r="AE10" t="n">
-        <v>1068.97</v>
+        <v>376.32</v>
       </c>
       <c r="AF10" t="n">
-        <v>46.1</v>
+        <v>78.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI10" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18.5</v>
+        <v>6.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>39.1</v>
+        <v>25.2</v>
       </c>
       <c r="AL10" t="n">
-        <v>50.1</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AM10" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AN10" t="n">
-        <v>1088.74</v>
+        <v>382.92</v>
       </c>
       <c r="AO10" t="n">
-        <v>1013.57</v>
+        <v>362.82</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹246,283.11 Cr., a P/E ratio of 18.48, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,046.70) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[1046.7, 1049.84, 1052.98, 1056.12, 1059.26, 1062.4]</t>
+          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[1046.7, 1062.47, 1070.84, 1077.99, 1084.52, 1090.64]</t>
+          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>[1046.7, 1040.37, 1039.59, 1039.72, 1040.32, 1041.22]</t>
+          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
         </is>
       </c>
     </row>
@@ -2164,16 +2164,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>146280.27</v>
+        <v>68767.81</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2181,145 +2181,145 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1651.3</v>
+        <v>5751.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹1641.81 - ₹1665.54</t>
+          <t>₹5727.01 - ₹5788.23</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1689.26</v>
+        <v>5849.44</v>
       </c>
       <c r="I11" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="J11" t="n">
-        <v>1478.49</v>
+        <v>5575</v>
       </c>
       <c r="K11" t="n">
-        <v>1460.44</v>
+        <v>5484.08</v>
       </c>
       <c r="L11" t="n">
-        <v>1458.79</v>
+        <v>5521.06</v>
       </c>
       <c r="M11" t="n">
-        <v>14.41</v>
+        <v>5.35</v>
       </c>
       <c r="N11" t="n">
-        <v>56.22</v>
+        <v>57.19</v>
       </c>
       <c r="O11" t="n">
-        <v>42.84</v>
+        <v>51.96</v>
       </c>
       <c r="P11" t="n">
-        <v>13.38</v>
+        <v>5.23</v>
       </c>
       <c r="Q11" t="n">
-        <v>47.45</v>
+        <v>122.43</v>
       </c>
       <c r="R11" t="n">
         <v>11.76</v>
       </c>
       <c r="S11" t="n">
-        <v>44.4</v>
+        <v>46.9</v>
       </c>
       <c r="T11" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.04</v>
+        <v>-1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>48.3</v>
+        <v>53.3</v>
       </c>
       <c r="W11" t="n">
-        <v>8.69</v>
+        <v>2.81</v>
       </c>
       <c r="X11" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>1625.33</v>
+        <v>5710.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>1683.13</v>
+        <v>5912.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1664.51</v>
+        <v>5797.51</v>
       </c>
       <c r="AB11" t="n">
-        <v>1580.13</v>
+        <v>5567.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>1641.1</v>
+        <v>5773.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1671.7</v>
+        <v>5811.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>1692.1</v>
+        <v>5871.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>86.2</v>
+        <v>58.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI11" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>28.6</v>
+        <v>29.9</v>
       </c>
       <c r="AK11" t="n">
-        <v>17.7</v>
+        <v>14.6</v>
       </c>
       <c r="AL11" t="n">
-        <v>8.699999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="AM11" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>1700.37</v>
+        <v>5882.46</v>
       </c>
       <c r="AO11" t="n">
-        <v>1608.23</v>
+        <v>5634.05</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,767.81 Cr., a P/E ratio of 29.85, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,751.50) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
+          <t>[5751.5, 5797.12, 5842.75, 5888.37, 5934.0, 5979.62]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
+          <t>[5751.5, 5846.1, 5912.0, 5973.19, 6031.94, 6089.12]</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
+          <t>[5751.5, 5760.4, 5790.81, 5824.76, 5860.54, 5897.49]</t>
         </is>
       </c>
     </row>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>85420.58</v>
+        <v>119011.76</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2348,145 +2348,145 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14049</v>
+        <v>1473.2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹13965.8 - ₹14173.8</t>
+          <t>₹1466.31 - ₹1483.53</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14381.8</v>
+        <v>1500.76</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="J12" t="n">
-        <v>13190.57</v>
+        <v>1436.14</v>
       </c>
       <c r="K12" t="n">
-        <v>12605.68</v>
+        <v>1414.83</v>
       </c>
       <c r="L12" t="n">
-        <v>12333.95</v>
+        <v>1396.09</v>
       </c>
       <c r="M12" t="n">
-        <v>16.25</v>
+        <v>5.04</v>
       </c>
       <c r="N12" t="n">
-        <v>477.1</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>503.84</v>
+        <v>6.31</v>
       </c>
       <c r="P12" t="n">
-        <v>-26.74</v>
+        <v>1.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>416</v>
+        <v>34.45</v>
       </c>
       <c r="R12" t="n">
         <v>11.76</v>
       </c>
       <c r="S12" t="n">
-        <v>45.7</v>
+        <v>47</v>
       </c>
       <c r="T12" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.05</v>
+        <v>-1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>46.7</v>
+        <v>45</v>
       </c>
       <c r="W12" t="n">
-        <v>6.67</v>
+        <v>11.03</v>
       </c>
       <c r="X12" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>13634.81</v>
+        <v>1431.86</v>
       </c>
       <c r="Z12" t="n">
-        <v>14126.52</v>
+        <v>1388.21</v>
       </c>
       <c r="AA12" t="n">
-        <v>14161.39</v>
+        <v>1484.99</v>
       </c>
       <c r="AB12" t="n">
-        <v>13425</v>
+        <v>1421.52</v>
       </c>
       <c r="AC12" t="n">
-        <v>14079.67</v>
+        <v>1471.43</v>
       </c>
       <c r="AD12" t="n">
-        <v>14558.34</v>
+        <v>1480.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>15067.67</v>
+        <v>1487.93</v>
       </c>
       <c r="AF12" t="n">
-        <v>64.7</v>
+        <v>56.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI12" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>41.2</v>
+        <v>35.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>21.1</v>
+        <v>3.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="AM12" t="n">
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>14625.09</v>
+        <v>1504.74</v>
       </c>
       <c r="AO12" t="n">
-        <v>13525.23</v>
+        <v>1442.89</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
+          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
+          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
+          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
         </is>
       </c>
     </row>
@@ -2498,16 +2498,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17572.27</v>
+        <v>133901.31</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2515,90 +2515,90 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>613.35</v>
+        <v>3760</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹608.87 - ₹620.07</t>
+          <t>₹3740.59 - ₹3789.12</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>631.27</v>
+        <v>3837.66</v>
       </c>
       <c r="I13" t="n">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="J13" t="n">
-        <v>578.01</v>
+        <v>3594.31</v>
       </c>
       <c r="K13" t="n">
-        <v>541.38</v>
+        <v>3627.85</v>
       </c>
       <c r="L13" t="n">
-        <v>553.54</v>
+        <v>3330.53</v>
       </c>
       <c r="M13" t="n">
-        <v>10.74</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>14.56</v>
+        <v>22.06</v>
       </c>
       <c r="O13" t="n">
-        <v>16.43</v>
+        <v>10.09</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.88</v>
+        <v>11.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.4</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="R13" t="n">
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.26</v>
+        <v>-1.51</v>
       </c>
       <c r="V13" t="n">
         <v>53.3</v>
       </c>
       <c r="W13" t="n">
-        <v>4.8</v>
+        <v>2.23</v>
       </c>
       <c r="X13" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>590.26</v>
+        <v>3684.03</v>
       </c>
       <c r="Z13" t="n">
-        <v>611.73</v>
+        <v>3815.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>618.26</v>
+        <v>3790.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>579.75</v>
+        <v>3614.39</v>
       </c>
       <c r="AC13" t="n">
-        <v>616.27</v>
+        <v>3743.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>624.54</v>
+        <v>3824.9</v>
       </c>
       <c r="AE13" t="n">
-        <v>635.72</v>
+        <v>3889.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>60.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2609,51 +2609,51 @@
         <v>0.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>88.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AK13" t="n">
-        <v>-10.1</v>
+        <v>14.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.7</v>
+        <v>9.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>645.35</v>
+        <v>3874.14</v>
       </c>
       <c r="AO13" t="n">
-        <v>584.29</v>
+        <v>3650.76</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,901.31 Cr., a P/E ratio of 79.36, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,760.00) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
+          <t>[3760.0, 3771.28, 3782.56, 3793.84, 3805.12, 3816.4]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
+          <t>[3760.0, 3810.11, 3837.47, 3861.1, 3882.78, 3903.23]</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
+          <t>[3760.0, 3742.16, 3741.37, 3743.4, 3746.88, 3751.28]</t>
         </is>
       </c>
     </row>
@@ -2665,162 +2665,162 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>63429.15</v>
+        <v>246283.11</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2105.7</v>
+        <v>1046.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹2092.64 - ₹2125.3</t>
+          <t>₹1040.39 - ₹1056.17</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2157.96</v>
+        <v>1071.96</v>
       </c>
       <c r="I14" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="J14" t="n">
-        <v>1999.45</v>
+        <v>1032.61</v>
       </c>
       <c r="K14" t="n">
-        <v>1888.17</v>
+        <v>994.9400000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>1880.41</v>
+        <v>942.9400000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>12.26</v>
+        <v>8.94</v>
       </c>
       <c r="N14" t="n">
-        <v>62.25</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>68.98</v>
+        <v>12.02</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.73</v>
+        <v>-3.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>65.31999999999999</v>
+        <v>31.57</v>
       </c>
       <c r="R14" t="n">
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>42.9</v>
+        <v>50.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.31</v>
+        <v>-1.86</v>
       </c>
       <c r="V14" t="n">
-        <v>51.7</v>
+        <v>55</v>
       </c>
       <c r="W14" t="n">
-        <v>4.49</v>
+        <v>3.38</v>
       </c>
       <c r="X14" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>2027.32</v>
+        <v>1019.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>2032.25</v>
+        <v>1056.01</v>
       </c>
       <c r="AA14" t="n">
-        <v>2122.55</v>
+        <v>1055.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>2007.72</v>
+        <v>999.34</v>
       </c>
       <c r="AC14" t="n">
-        <v>2111.93</v>
+        <v>1043.47</v>
       </c>
       <c r="AD14" t="n">
-        <v>2127.76</v>
+        <v>1057.84</v>
       </c>
       <c r="AE14" t="n">
-        <v>2149.83</v>
+        <v>1068.97</v>
       </c>
       <c r="AF14" t="n">
-        <v>48.8</v>
+        <v>46.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.14</v>
+        <v>-0.14</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI14" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>34.2</v>
+        <v>18.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>63</v>
+        <v>39.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>36.1</v>
+        <v>50.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>2174.81</v>
+        <v>1085.27</v>
       </c>
       <c r="AO14" t="n">
-        <v>2031.51</v>
+        <v>1011.43</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹246,283.11 Cr., a P/E ratio of 18.48, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,046.70) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
+          <t>[1046.7, 1049.84, 1052.98, 1056.12, 1059.26, 1062.4]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
+          <t>[1046.7, 1062.47, 1070.84, 1077.99, 1084.52, 1090.64]</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
+          <t>[1046.7, 1040.37, 1039.59, 1039.72, 1040.32, 1041.22]</t>
         </is>
       </c>
     </row>
@@ -2832,16 +2832,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>278417.14</v>
+        <v>146280.27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2849,145 +2849,145 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>302.45</v>
+        <v>1651.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹300.39 - ₹305.53</t>
+          <t>₹1641.81 - ₹1665.54</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>310.68</v>
+        <v>1689.26</v>
       </c>
       <c r="I15" t="n">
-        <v>324</v>
+        <v>70</v>
       </c>
       <c r="J15" t="n">
-        <v>281.7</v>
+        <v>1478.49</v>
       </c>
       <c r="K15" t="n">
-        <v>268.93</v>
+        <v>1460.44</v>
       </c>
       <c r="L15" t="n">
-        <v>274.01</v>
+        <v>1458.79</v>
       </c>
       <c r="M15" t="n">
-        <v>13.37</v>
+        <v>14.41</v>
       </c>
       <c r="N15" t="n">
-        <v>9.93</v>
+        <v>56.22</v>
       </c>
       <c r="O15" t="n">
-        <v>8.42</v>
+        <v>42.84</v>
       </c>
       <c r="P15" t="n">
-        <v>1.51</v>
+        <v>13.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>10.28</v>
+        <v>47.45</v>
       </c>
       <c r="R15" t="n">
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.53</v>
+        <v>-2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="W15" t="n">
-        <v>2.44</v>
+        <v>8.69</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>299.26</v>
+        <v>1625.39</v>
       </c>
       <c r="Z15" t="n">
-        <v>309.85</v>
+        <v>1683.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>304.87</v>
+        <v>1664.51</v>
       </c>
       <c r="AB15" t="n">
-        <v>287.03</v>
+        <v>1580.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>306.75</v>
+        <v>1641.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>311.7</v>
+        <v>1671.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>320.95</v>
+        <v>1692.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>65.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>672.1</v>
+        <v>28.6</v>
       </c>
       <c r="AK15" t="n">
-        <v>182</v>
+        <v>17.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM15" t="n">
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>313.72</v>
+        <v>1698.85</v>
       </c>
       <c r="AO15" t="n">
-        <v>292.31</v>
+        <v>1606.55</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[302.45, 303.8, 305.15, 306.5, 307.85, 309.19]</t>
+          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[302.45, 307.91, 310.96, 313.62, 316.07, 318.39]</t>
+          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[302.45, 300.71, 300.79, 301.15, 301.68, 302.3]</t>
+          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76187.09</v>
+        <v>85420.58</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3016,145 +3016,980 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1721</v>
+        <v>14049</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹1709.13 - ₹1738.8</t>
+          <t>₹13965.8 - ₹14173.8</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1768.46</v>
+        <v>14381.8</v>
       </c>
       <c r="I16" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>1505.99</v>
+        <v>13190.57</v>
       </c>
       <c r="K16" t="n">
-        <v>1472.15</v>
+        <v>12605.68</v>
       </c>
       <c r="L16" t="n">
-        <v>1507.99</v>
+        <v>12333.95</v>
       </c>
       <c r="M16" t="n">
-        <v>15.58</v>
+        <v>16.25</v>
       </c>
       <c r="N16" t="n">
-        <v>53.48</v>
+        <v>477.1</v>
       </c>
       <c r="O16" t="n">
-        <v>30.14</v>
+        <v>503.84</v>
       </c>
       <c r="P16" t="n">
-        <v>23.34</v>
+        <v>-26.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>59.33</v>
+        <v>416</v>
       </c>
       <c r="R16" t="n">
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>41.3</v>
+        <v>45.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.7</v>
+        <v>-2.05</v>
       </c>
       <c r="V16" t="n">
-        <v>48.3</v>
+        <v>46.7</v>
       </c>
       <c r="W16" t="n">
-        <v>7.48</v>
+        <v>6.67</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>1705.12</v>
+        <v>13634.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>1765.36</v>
+        <v>14126.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1734.77</v>
+        <v>14161.39</v>
       </c>
       <c r="AB16" t="n">
-        <v>1632.01</v>
+        <v>13425</v>
       </c>
       <c r="AC16" t="n">
-        <v>1713.83</v>
+        <v>14079.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>1745.96</v>
+        <v>14558.34</v>
       </c>
       <c r="AE16" t="n">
-        <v>1770.93</v>
+        <v>15067.67</v>
       </c>
       <c r="AF16" t="n">
-        <v>77.3</v>
+        <v>64.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>35.2</v>
+        <v>41.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>49.9</v>
+        <v>21.1</v>
       </c>
       <c r="AL16" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="AM16" t="n">
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>1788.88</v>
+        <v>14602.01</v>
       </c>
       <c r="AO16" t="n">
-        <v>1658.41</v>
+        <v>13496.81</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>17572.27</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>613.35</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>₹608.87 - ₹620.07</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>631.27</v>
+      </c>
+      <c r="I17" t="n">
+        <v>148</v>
+      </c>
+      <c r="J17" t="n">
+        <v>578.01</v>
+      </c>
+      <c r="K17" t="n">
+        <v>541.38</v>
+      </c>
+      <c r="L17" t="n">
+        <v>553.54</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="S17" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="V17" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>590.26</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>611.72</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>618.26</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>579.75</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>616.27</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>624.54</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>635.72</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>642.75</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>583.99</v>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>63429.15</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2105.7</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>₹2092.64 - ₹2125.3</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2157.96</v>
+      </c>
+      <c r="I18" t="n">
+        <v>51</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1999.45</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1888.17</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1880.41</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="N18" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>68.98</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-6.73</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>65.31999999999999</v>
+      </c>
+      <c r="R18" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="S18" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="V18" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2027.32</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2032.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2122.55</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2007.72</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2111.93</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2127.76</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2149.83</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>63</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2178.13</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2036.21</v>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>46194.13</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1135.3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>₹1128.39 - ₹1145.67</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1162.95</v>
+      </c>
+      <c r="I19" t="n">
+        <v>96</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1109.56</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1105.35</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1100.33</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="R19" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="S19" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="V19" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1114.04</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1153.77</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1144.38</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1083.45</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1144.43</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1156.86</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1178.43</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1168.39</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1102.13</v>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,194.13 Cr., a P/E ratio of 37.73, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,135.30) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>[1135.3, 1138.71, 1142.11, 1145.52, 1148.92, 1152.33]</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>[1135.3, 1152.53, 1161.66, 1169.46, 1176.58, 1183.24]</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>[1135.3, 1128.34, 1127.45, 1127.56, 1128.19, 1129.14]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>278417.14</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>302.45</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>₹300.39 - ₹305.53</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>310.68</v>
+      </c>
+      <c r="I20" t="n">
+        <v>324</v>
+      </c>
+      <c r="J20" t="n">
+        <v>281.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>268.93</v>
+      </c>
+      <c r="L20" t="n">
+        <v>274.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="R20" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="S20" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="V20" t="n">
+        <v>50</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>299.26</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>309.85</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>304.87</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>287.03</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>306.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>320.95</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>672.1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>182</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>314.21</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>292.09</v>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>[302.45, 303.8, 305.15, 306.5, 307.85, 309.19]</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>[302.45, 307.91, 310.96, 313.62, 316.07, 318.39]</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>[302.45, 300.71, 300.79, 301.15, 301.68, 302.3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>76187.09</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1721</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>₹1709.13 - ₹1738.8</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1768.46</v>
+      </c>
+      <c r="I21" t="n">
+        <v>56</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1505.99</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1472.15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1507.99</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="N21" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="O21" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="P21" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="R21" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="S21" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1705.17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1765.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1734.77</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1632.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1713.83</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1745.96</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1770.93</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1789.11</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1657.63</v>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
           <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,187.09 Cr., a P/E ratio of 35.21, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr">
+      <c r="AQ21" t="inlineStr">
         <is>
           <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.48) trades above Signal (30.14) with an expanding histogram (+23.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1507.99). Daily volatility envelope is bounded by ATR(14) of ₹59.33.</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
+      <c r="AR21" t="inlineStr">
         <is>
           <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,721.00) is positioned above the 30-day DMA (₹1,505.99), 50-day DMA (₹1,472.15), and 200-day DMA (₹1,507.99). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.21, 1823.74]</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>[1721.0, 1730.98, 1740.97, 1750.95, 1760.93, 1770.91]</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>[1721.0, 1754.71, 1774.53, 1792.05, 1808.39, 1823.98]</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>[1721.0, 1713.18, 1715.79, 1720.12, 1725.33, 1731.11]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -719,7 +719,7 @@
         <v>11.76</v>
       </c>
       <c r="S2" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
       <c r="T2" t="n">
         <v>0.32</v>
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1461.76</v>
+        <v>1460.19</v>
       </c>
       <c r="AO2" t="n">
-        <v>1408.25</v>
+        <v>1408.46</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -886,13 +886,13 @@
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>52.7</v>
+        <v>52.4</v>
       </c>
       <c r="T3" t="n">
         <v>0.29</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.88</v>
+        <v>-0.89</v>
       </c>
       <c r="V3" t="n">
         <v>51.7</v>
@@ -951,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>115.91</v>
+        <v>115.79</v>
       </c>
       <c r="AO3" t="n">
-        <v>109.56</v>
+        <v>109.46</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1053,13 +1053,13 @@
         <v>11.76</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="T4" t="n">
         <v>0.39</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="V4" t="n">
         <v>48.3</v>
@@ -1118,10 +1118,10 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>8041.19</v>
+        <v>8050.22</v>
       </c>
       <c r="AO4" t="n">
-        <v>7635.76</v>
+        <v>7643.31</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1220,13 +1220,13 @@
         <v>11.76</v>
       </c>
       <c r="S5" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="T5" t="n">
         <v>0.29</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9</v>
+        <v>-0.91</v>
       </c>
       <c r="V5" t="n">
         <v>48.3</v>
@@ -1285,10 +1285,10 @@
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12169.67</v>
+        <v>12157.55</v>
       </c>
       <c r="AO5" t="n">
-        <v>11653.21</v>
+        <v>11639.05</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>52.2</v>
+        <v>51.8</v>
       </c>
       <c r="T6" t="n">
         <v>0.25</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1</v>
+        <v>-1.11</v>
       </c>
       <c r="V6" t="n">
         <v>55</v>
@@ -1405,10 +1405,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>2707.06</v>
+        <v>2707.04</v>
       </c>
       <c r="Z6" t="n">
-        <v>2803.21</v>
+        <v>2803.2</v>
       </c>
       <c r="AA6" t="n">
         <v>2769.28</v>
@@ -1452,10 +1452,10 @@
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>2815.67</v>
+        <v>2813.78</v>
       </c>
       <c r="AO6" t="n">
-        <v>2690.4</v>
+        <v>2687.55</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1554,13 +1554,13 @@
         <v>11.76</v>
       </c>
       <c r="S7" t="n">
-        <v>50.6</v>
+        <v>50.2</v>
       </c>
       <c r="T7" t="n">
         <v>0.25</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.19</v>
+        <v>-1.21</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -1619,10 +1619,10 @@
         <v>11.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>2269.73</v>
+        <v>2267.44</v>
       </c>
       <c r="AO7" t="n">
-        <v>2143.05</v>
+        <v>2135.19</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>757.9</v>
+        <v>756.09</v>
       </c>
       <c r="AO8" t="n">
-        <v>721.0599999999999</v>
+        <v>720.15</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="T9" t="n">
         <v>0.3</v>
@@ -1906,10 +1906,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>4548.63</v>
+        <v>4548.55</v>
       </c>
       <c r="Z9" t="n">
-        <v>4711.26</v>
+        <v>4711.17</v>
       </c>
       <c r="AA9" t="n">
         <v>4683.67</v>
@@ -1953,10 +1953,10 @@
         <v>24</v>
       </c>
       <c r="AN9" t="n">
-        <v>4762.32</v>
+        <v>4762.74</v>
       </c>
       <c r="AO9" t="n">
-        <v>4517.79</v>
+        <v>4513.06</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -2055,13 +2055,13 @@
         <v>11.76</v>
       </c>
       <c r="S10" t="n">
-        <v>47</v>
+        <v>47.3</v>
       </c>
       <c r="T10" t="n">
         <v>0.26</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.27</v>
+        <v>-1.25</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -2120,10 +2120,10 @@
         <v>15</v>
       </c>
       <c r="AN10" t="n">
-        <v>382.92</v>
+        <v>382.63</v>
       </c>
       <c r="AO10" t="n">
-        <v>362.82</v>
+        <v>363.05</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2222,19 +2222,19 @@
         <v>11.76</v>
       </c>
       <c r="S11" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="T11" t="n">
         <v>0.25</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.32</v>
+        <v>-1.33</v>
       </c>
       <c r="V11" t="n">
         <v>53.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="X11" t="n">
         <v>-0.77</v>
@@ -2287,10 +2287,10 @@
         <v>17.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>5882.46</v>
+        <v>5880.64</v>
       </c>
       <c r="AO11" t="n">
-        <v>5634.05</v>
+        <v>5616.46</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2331,162 +2331,162 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>119011.76</v>
+        <v>133901.31</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1473.2</v>
+        <v>3760</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹1466.31 - ₹1483.53</t>
+          <t>₹3740.59 - ₹3789.12</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1500.76</v>
+        <v>3837.66</v>
       </c>
       <c r="I12" t="n">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="J12" t="n">
-        <v>1436.14</v>
+        <v>3594.31</v>
       </c>
       <c r="K12" t="n">
-        <v>1414.83</v>
+        <v>3627.85</v>
       </c>
       <c r="L12" t="n">
-        <v>1396.09</v>
+        <v>3330.53</v>
       </c>
       <c r="M12" t="n">
-        <v>5.04</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.130000000000001</v>
+        <v>22.06</v>
       </c>
       <c r="O12" t="n">
-        <v>6.31</v>
+        <v>10.09</v>
       </c>
       <c r="P12" t="n">
-        <v>1.82</v>
+        <v>11.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>34.45</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>11.76</v>
       </c>
       <c r="S12" t="n">
-        <v>47</v>
+        <v>50.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.48</v>
+        <v>-1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>45</v>
+        <v>53.3</v>
       </c>
       <c r="W12" t="n">
-        <v>11.03</v>
+        <v>2.23</v>
       </c>
       <c r="X12" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>1431.86</v>
+        <v>3684.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>1388.21</v>
+        <v>3815.63</v>
       </c>
       <c r="AA12" t="n">
-        <v>1484.99</v>
+        <v>3790.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1421.52</v>
+        <v>3614.39</v>
       </c>
       <c r="AC12" t="n">
-        <v>1471.43</v>
+        <v>3743.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1480.56</v>
+        <v>3824.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>1487.93</v>
+        <v>3889.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>56.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.08</v>
+        <v>0.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI12" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>35.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.5</v>
+        <v>14.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="AM12" t="n">
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>1504.74</v>
+        <v>3879.57</v>
       </c>
       <c r="AO12" t="n">
-        <v>1442.89</v>
+        <v>3640.08</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,901.31 Cr., a P/E ratio of 79.36, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,760.00) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
+          <t>[3760.0, 3771.28, 3782.56, 3793.84, 3805.12, 3816.4]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
+          <t>[3760.0, 3810.11, 3837.47, 3861.1, 3882.78, 3903.23]</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
+          <t>[3760.0, 3742.16, 3741.37, 3743.4, 3746.88, 3751.28]</t>
         </is>
       </c>
     </row>
@@ -2498,162 +2498,162 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>133901.31</v>
+        <v>119011.76</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3760</v>
+        <v>1473.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹3740.59 - ₹3789.12</t>
+          <t>₹1466.31 - ₹1483.53</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3837.66</v>
+        <v>1500.76</v>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="J13" t="n">
-        <v>3594.31</v>
+        <v>1436.14</v>
       </c>
       <c r="K13" t="n">
-        <v>3627.85</v>
+        <v>1414.83</v>
       </c>
       <c r="L13" t="n">
-        <v>3330.53</v>
+        <v>1396.09</v>
       </c>
       <c r="M13" t="n">
-        <v>9.859999999999999</v>
+        <v>5.04</v>
       </c>
       <c r="N13" t="n">
-        <v>22.06</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>10.09</v>
+        <v>6.31</v>
       </c>
       <c r="P13" t="n">
-        <v>11.97</v>
+        <v>1.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>97.06999999999999</v>
+        <v>34.45</v>
       </c>
       <c r="R13" t="n">
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>50.5</v>
+        <v>46.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="U13" t="n">
         <v>-1.51</v>
       </c>
       <c r="V13" t="n">
-        <v>53.3</v>
+        <v>45</v>
       </c>
       <c r="W13" t="n">
-        <v>2.23</v>
+        <v>11.03</v>
       </c>
       <c r="X13" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>3684.03</v>
+        <v>1431.86</v>
       </c>
       <c r="Z13" t="n">
-        <v>3815.63</v>
+        <v>1388.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>3790.08</v>
+        <v>1484.99</v>
       </c>
       <c r="AB13" t="n">
-        <v>3614.39</v>
+        <v>1421.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>3743.5</v>
+        <v>1471.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>3824.9</v>
+        <v>1480.56</v>
       </c>
       <c r="AE13" t="n">
-        <v>3889.8</v>
+        <v>1487.93</v>
       </c>
       <c r="AF13" t="n">
-        <v>74.09999999999999</v>
+        <v>56.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.08</v>
+        <v>-0.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI13" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>79.40000000000001</v>
+        <v>35.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>14.6</v>
+        <v>3.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="AM13" t="n">
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>3874.14</v>
+        <v>1504.9</v>
       </c>
       <c r="AO13" t="n">
-        <v>3650.76</v>
+        <v>1441.85</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,901.31 Cr., a P/E ratio of 79.36, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,760.00) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[3760.0, 3771.28, 3782.56, 3793.84, 3805.12, 3816.4]</t>
+          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[3760.0, 3810.11, 3837.47, 3861.1, 3882.78, 3903.23]</t>
+          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>[3760.0, 3742.16, 3741.37, 3743.4, 3746.88, 3751.28]</t>
+          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
         </is>
       </c>
     </row>
@@ -2723,13 +2723,13 @@
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="T14" t="n">
         <v>0.18</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.86</v>
+        <v>-1.85</v>
       </c>
       <c r="V14" t="n">
         <v>55</v>
@@ -2788,10 +2788,10 @@
         <v>18.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>1085.27</v>
+        <v>1083.53</v>
       </c>
       <c r="AO14" t="n">
-        <v>1011.43</v>
+        <v>1012.2</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2890,13 +2890,13 @@
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="T15" t="n">
         <v>0.19</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.04</v>
+        <v>-2.05</v>
       </c>
       <c r="V15" t="n">
         <v>48.3</v>
@@ -2908,10 +2908,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>1625.39</v>
+        <v>1625.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>1683.18</v>
+        <v>1683.13</v>
       </c>
       <c r="AA15" t="n">
         <v>1664.51</v>
@@ -2955,10 +2955,10 @@
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>1698.85</v>
+        <v>1693.3</v>
       </c>
       <c r="AO15" t="n">
-        <v>1606.55</v>
+        <v>1605.68</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -3057,13 +3057,13 @@
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="T16" t="n">
         <v>0.18</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.05</v>
+        <v>-2.06</v>
       </c>
       <c r="V16" t="n">
         <v>46.7</v>
@@ -3075,10 +3075,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>13634.58</v>
+        <v>13634.81</v>
       </c>
       <c r="Z16" t="n">
-        <v>14126.3</v>
+        <v>14126.52</v>
       </c>
       <c r="AA16" t="n">
         <v>14161.39</v>
@@ -3122,10 +3122,10 @@
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>14602.01</v>
+        <v>14594.57</v>
       </c>
       <c r="AO16" t="n">
-        <v>13496.81</v>
+        <v>13496.42</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>11.76</v>
       </c>
       <c r="S17" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="T17" t="n">
         <v>0.15</v>
@@ -3245,7 +3245,7 @@
         <v>590.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>611.72</v>
+        <v>611.73</v>
       </c>
       <c r="AA17" t="n">
         <v>618.26</v>
@@ -3289,10 +3289,10 @@
         <v>6.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>642.75</v>
+        <v>644.0599999999999</v>
       </c>
       <c r="AO17" t="n">
-        <v>583.99</v>
+        <v>580.53</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -3391,13 +3391,13 @@
         <v>11.76</v>
       </c>
       <c r="S18" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="T18" t="n">
         <v>0.17</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.29</v>
+        <v>-2.3</v>
       </c>
       <c r="V18" t="n">
         <v>51.7</v>
@@ -3456,10 +3456,10 @@
         <v>10</v>
       </c>
       <c r="AN18" t="n">
-        <v>2178.13</v>
+        <v>2180.46</v>
       </c>
       <c r="AO18" t="n">
-        <v>2036.21</v>
+        <v>2028.86</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3558,13 +3558,13 @@
         <v>11.76</v>
       </c>
       <c r="S19" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="T19" t="n">
         <v>0.18</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.45</v>
+        <v>-2.44</v>
       </c>
       <c r="V19" t="n">
         <v>46.7</v>
@@ -3576,10 +3576,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1114.04</v>
+        <v>1113.98</v>
       </c>
       <c r="Z19" t="n">
-        <v>1153.77</v>
+        <v>1153.71</v>
       </c>
       <c r="AA19" t="n">
         <v>1144.38</v>
@@ -3623,10 +3623,10 @@
         <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>1168.39</v>
+        <v>1172.37</v>
       </c>
       <c r="AO19" t="n">
-        <v>1102.13</v>
+        <v>1102.74</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3725,13 +3725,13 @@
         <v>11.76</v>
       </c>
       <c r="S20" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="T20" t="n">
         <v>0.16</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.52</v>
+        <v>-2.51</v>
       </c>
       <c r="V20" t="n">
         <v>50</v>
@@ -3790,10 +3790,10 @@
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>314.21</v>
+        <v>313.14</v>
       </c>
       <c r="AO20" t="n">
-        <v>292.09</v>
+        <v>292.4</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3892,13 +3892,13 @@
         <v>11.76</v>
       </c>
       <c r="S21" t="n">
-        <v>41.4</v>
+        <v>40.9</v>
       </c>
       <c r="T21" t="n">
         <v>0.15</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.7</v>
+        <v>-2.73</v>
       </c>
       <c r="V21" t="n">
         <v>48.3</v>
@@ -3910,10 +3910,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>1705.17</v>
+        <v>1705.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>1765.4</v>
+        <v>1765.38</v>
       </c>
       <c r="AA21" t="n">
         <v>1734.77</v>
@@ -3957,10 +3957,10 @@
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>1789.11</v>
+        <v>1789.56</v>
       </c>
       <c r="AO21" t="n">
-        <v>1657.63</v>
+        <v>1656.01</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -3979,17 +3979,17 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>[1721.0, 1730.98, 1740.97, 1750.95, 1760.93, 1770.91]</t>
+          <t>[1721.0, 1730.96, 1740.93, 1750.89, 1760.85, 1770.82]</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[1721.0, 1754.71, 1774.53, 1792.05, 1808.39, 1823.98]</t>
+          <t>[1721.0, 1754.69, 1774.49, 1791.99, 1808.32, 1823.88]</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>[1721.0, 1713.18, 1715.79, 1720.12, 1725.33, 1731.11]</t>
+          <t>[1721.0, 1713.17, 1715.76, 1720.06, 1725.26, 1731.02]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -719,13 +719,13 @@
         <v>11.76</v>
       </c>
       <c r="S2" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="T2" t="n">
         <v>0.32</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="V2" t="n">
         <v>60</v>
@@ -784,10 +784,10 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1460.19</v>
+        <v>1461.85</v>
       </c>
       <c r="AO2" t="n">
-        <v>1408.46</v>
+        <v>1409.86</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -886,13 +886,13 @@
         <v>11.76</v>
       </c>
       <c r="S3" t="n">
-        <v>52.4</v>
+        <v>52.8</v>
       </c>
       <c r="T3" t="n">
         <v>0.29</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.89</v>
+        <v>-0.88</v>
       </c>
       <c r="V3" t="n">
         <v>51.7</v>
@@ -951,10 +951,10 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>115.79</v>
+        <v>115.85</v>
       </c>
       <c r="AO3" t="n">
-        <v>109.46</v>
+        <v>109.34</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>11.76</v>
       </c>
       <c r="S4" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="T4" t="n">
         <v>0.39</v>
@@ -1118,10 +1118,10 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>8050.22</v>
+        <v>8042.84</v>
       </c>
       <c r="AO4" t="n">
-        <v>7643.31</v>
+        <v>7633.97</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1220,13 +1220,13 @@
         <v>11.76</v>
       </c>
       <c r="S5" t="n">
-        <v>51.9</v>
+        <v>51.5</v>
       </c>
       <c r="T5" t="n">
         <v>0.29</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.91</v>
+        <v>-0.92</v>
       </c>
       <c r="V5" t="n">
         <v>48.3</v>
@@ -1238,10 +1238,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>11731.98</v>
+        <v>11732.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>12148.58</v>
+        <v>12148.72</v>
       </c>
       <c r="AA5" t="n">
         <v>11998.22</v>
@@ -1285,10 +1285,10 @@
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12157.55</v>
+        <v>12155.36</v>
       </c>
       <c r="AO5" t="n">
-        <v>11639.05</v>
+        <v>11646.4</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         <v>11.76</v>
       </c>
       <c r="S6" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="T6" t="n">
         <v>0.25</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="V6" t="n">
         <v>55</v>
@@ -1452,10 +1452,10 @@
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>2813.78</v>
+        <v>2817.62</v>
       </c>
       <c r="AO6" t="n">
-        <v>2687.55</v>
+        <v>2683.36</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>11.76</v>
       </c>
       <c r="S7" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="T7" t="n">
         <v>0.25</v>
@@ -1572,7 +1572,7 @@
         <v>-0.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>2184.77</v>
+        <v>2184.76</v>
       </c>
       <c r="Z7" t="n">
         <v>2261.76</v>
@@ -1619,10 +1619,10 @@
         <v>11.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>2267.44</v>
+        <v>2267.45</v>
       </c>
       <c r="AO7" t="n">
-        <v>2135.19</v>
+        <v>2143.19</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -1641,17 +1641,17 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2199.8, 2217.76, 2235.73, 2253.69, 2271.66, 2289.62]</t>
+          <t>[2199.8, 2217.76, 2235.72, 2253.68, 2271.64, 2289.6]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2199.8, 2236.85, 2262.72, 2286.74, 2309.82, 2332.29]</t>
+          <t>[2199.8, 2236.84, 2262.71, 2286.73, 2309.8, 2332.27]</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>[2199.8, 2203.45, 2215.49, 2228.9, 2243.03, 2257.62]</t>
+          <t>[2199.8, 2203.45, 2215.48, 2228.89, 2243.01, 2257.59]</t>
         </is>
       </c>
     </row>
@@ -1721,13 +1721,13 @@
         <v>11.76</v>
       </c>
       <c r="S8" t="n">
-        <v>46.5</v>
+        <v>46.2</v>
       </c>
       <c r="T8" t="n">
         <v>0.27</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.23</v>
+        <v>-1.24</v>
       </c>
       <c r="V8" t="n">
         <v>55</v>
@@ -1786,10 +1786,10 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>756.09</v>
+        <v>757.62</v>
       </c>
       <c r="AO8" t="n">
-        <v>720.15</v>
+        <v>720.98</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -1888,13 +1888,13 @@
         <v>11.76</v>
       </c>
       <c r="S9" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="T9" t="n">
         <v>0.3</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.23</v>
+        <v>-1.24</v>
       </c>
       <c r="V9" t="n">
         <v>41.7</v>
@@ -1906,10 +1906,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>4548.55</v>
+        <v>4548.57</v>
       </c>
       <c r="Z9" t="n">
-        <v>4711.17</v>
+        <v>4711.2</v>
       </c>
       <c r="AA9" t="n">
         <v>4683.67</v>
@@ -1953,10 +1953,10 @@
         <v>24</v>
       </c>
       <c r="AN9" t="n">
-        <v>4762.74</v>
+        <v>4765.9</v>
       </c>
       <c r="AO9" t="n">
-        <v>4513.06</v>
+        <v>4525.47</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -2120,10 +2120,10 @@
         <v>15</v>
       </c>
       <c r="AN10" t="n">
-        <v>382.63</v>
+        <v>383.26</v>
       </c>
       <c r="AO10" t="n">
-        <v>363.05</v>
+        <v>363.06</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2222,13 +2222,13 @@
         <v>11.76</v>
       </c>
       <c r="S11" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="T11" t="n">
         <v>0.25</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.33</v>
+        <v>-1.34</v>
       </c>
       <c r="V11" t="n">
         <v>53.3</v>
@@ -2287,10 +2287,10 @@
         <v>17.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>5880.64</v>
+        <v>5874.26</v>
       </c>
       <c r="AO11" t="n">
-        <v>5616.46</v>
+        <v>5617.74</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>3684.03</v>
+        <v>3683.99</v>
       </c>
       <c r="Z12" t="n">
-        <v>3815.63</v>
+        <v>3815.59</v>
       </c>
       <c r="AA12" t="n">
         <v>3790.08</v>
@@ -2454,10 +2454,10 @@
         <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>3879.57</v>
+        <v>3882.26</v>
       </c>
       <c r="AO12" t="n">
-        <v>3640.08</v>
+        <v>3647.31</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2556,13 +2556,13 @@
         <v>11.76</v>
       </c>
       <c r="S13" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
       <c r="T13" t="n">
         <v>0.23</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.51</v>
+        <v>-1.52</v>
       </c>
       <c r="V13" t="n">
         <v>45</v>
@@ -2621,10 +2621,10 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>1504.9</v>
+        <v>1500.75</v>
       </c>
       <c r="AO13" t="n">
-        <v>1441.85</v>
+        <v>1440.03</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2723,13 +2723,13 @@
         <v>11.76</v>
       </c>
       <c r="S14" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
       <c r="T14" t="n">
         <v>0.18</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.85</v>
+        <v>-1.83</v>
       </c>
       <c r="V14" t="n">
         <v>55</v>
@@ -2741,10 +2741,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>1019.37</v>
+        <v>1019.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>1056.01</v>
+        <v>1055.99</v>
       </c>
       <c r="AA14" t="n">
         <v>1055.07</v>
@@ -2788,10 +2788,10 @@
         <v>18.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>1083.53</v>
+        <v>1086.01</v>
       </c>
       <c r="AO14" t="n">
-        <v>1012.2</v>
+        <v>1013.31</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>146280.27</v>
+        <v>85420.58</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2849,145 +2849,145 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1651.3</v>
+        <v>14049</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹1641.81 - ₹1665.54</t>
+          <t>₹13965.8 - ₹14173.8</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1689.26</v>
+        <v>14381.8</v>
       </c>
       <c r="I15" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>1478.49</v>
+        <v>13190.57</v>
       </c>
       <c r="K15" t="n">
-        <v>1460.44</v>
+        <v>12605.68</v>
       </c>
       <c r="L15" t="n">
-        <v>1458.79</v>
+        <v>12333.95</v>
       </c>
       <c r="M15" t="n">
-        <v>14.41</v>
+        <v>16.25</v>
       </c>
       <c r="N15" t="n">
-        <v>56.22</v>
+        <v>477.1</v>
       </c>
       <c r="O15" t="n">
-        <v>42.84</v>
+        <v>503.84</v>
       </c>
       <c r="P15" t="n">
-        <v>13.38</v>
+        <v>-26.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>47.45</v>
+        <v>416</v>
       </c>
       <c r="R15" t="n">
         <v>11.76</v>
       </c>
       <c r="S15" t="n">
-        <v>44.2</v>
+        <v>45.8</v>
       </c>
       <c r="T15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.05</v>
+        <v>-2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>48.3</v>
+        <v>46.7</v>
       </c>
       <c r="W15" t="n">
-        <v>8.69</v>
+        <v>6.67</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>1625.33</v>
+        <v>13634.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>1683.13</v>
+        <v>14126.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1664.51</v>
+        <v>14161.39</v>
       </c>
       <c r="AB15" t="n">
-        <v>1580.13</v>
+        <v>13425</v>
       </c>
       <c r="AC15" t="n">
-        <v>1641.1</v>
+        <v>14079.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1671.7</v>
+        <v>14558.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>1692.1</v>
+        <v>15067.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>86.2</v>
+        <v>64.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>28.6</v>
+        <v>41.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>17.7</v>
+        <v>21.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>8.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AM15" t="n">
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>1693.3</v>
+        <v>14632.09</v>
       </c>
       <c r="AO15" t="n">
-        <v>1605.68</v>
+        <v>13525.18</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
+          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
+          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
+          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>85420.58</v>
+        <v>146280.27</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3016,145 +3016,145 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>14049</v>
+        <v>1651.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹13965.8 - ₹14173.8</t>
+          <t>₹1641.81 - ₹1665.54</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14381.8</v>
+        <v>1689.26</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="J16" t="n">
-        <v>13190.57</v>
+        <v>1478.49</v>
       </c>
       <c r="K16" t="n">
-        <v>12605.68</v>
+        <v>1460.44</v>
       </c>
       <c r="L16" t="n">
-        <v>12333.95</v>
+        <v>1458.79</v>
       </c>
       <c r="M16" t="n">
-        <v>16.25</v>
+        <v>14.41</v>
       </c>
       <c r="N16" t="n">
-        <v>477.1</v>
+        <v>56.22</v>
       </c>
       <c r="O16" t="n">
-        <v>503.84</v>
+        <v>42.84</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.74</v>
+        <v>13.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>416</v>
+        <v>47.45</v>
       </c>
       <c r="R16" t="n">
         <v>11.76</v>
       </c>
       <c r="S16" t="n">
-        <v>45.5</v>
+        <v>44.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.06</v>
+        <v>-2.05</v>
       </c>
       <c r="V16" t="n">
-        <v>46.7</v>
+        <v>48.3</v>
       </c>
       <c r="W16" t="n">
-        <v>6.67</v>
+        <v>8.69</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>13634.81</v>
+        <v>1625.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>14126.52</v>
+        <v>1683.12</v>
       </c>
       <c r="AA16" t="n">
-        <v>14161.39</v>
+        <v>1664.51</v>
       </c>
       <c r="AB16" t="n">
-        <v>13425</v>
+        <v>1580.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>14079.67</v>
+        <v>1641.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>14558.34</v>
+        <v>1671.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>15067.67</v>
+        <v>1692.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>64.7</v>
+        <v>86.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>41.2</v>
+        <v>28.6</v>
       </c>
       <c r="AK16" t="n">
-        <v>21.1</v>
+        <v>17.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM16" t="n">
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>14594.57</v>
+        <v>1696.61</v>
       </c>
       <c r="AO16" t="n">
-        <v>13496.42</v>
+        <v>1605</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
+          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
+          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
+          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
         </is>
       </c>
     </row>
@@ -3289,10 +3289,10 @@
         <v>6.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>644.0599999999999</v>
+        <v>642</v>
       </c>
       <c r="AO17" t="n">
-        <v>580.53</v>
+        <v>584.67</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>11.76</v>
       </c>
       <c r="S18" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="T18" t="n">
         <v>0.17</v>
@@ -3456,10 +3456,10 @@
         <v>10</v>
       </c>
       <c r="AN18" t="n">
-        <v>2180.46</v>
+        <v>2179.47</v>
       </c>
       <c r="AO18" t="n">
-        <v>2028.86</v>
+        <v>2029.04</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3558,13 +3558,13 @@
         <v>11.76</v>
       </c>
       <c r="S19" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
         <v>0.18</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.44</v>
+        <v>-2.41</v>
       </c>
       <c r="V19" t="n">
         <v>46.7</v>
@@ -3576,10 +3576,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1113.98</v>
+        <v>1114</v>
       </c>
       <c r="Z19" t="n">
-        <v>1153.71</v>
+        <v>1153.74</v>
       </c>
       <c r="AA19" t="n">
         <v>1144.38</v>
@@ -3623,10 +3623,10 @@
         <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>1172.37</v>
+        <v>1170.43</v>
       </c>
       <c r="AO19" t="n">
-        <v>1102.74</v>
+        <v>1102.69</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3725,13 +3725,13 @@
         <v>11.76</v>
       </c>
       <c r="S20" t="n">
-        <v>43.9</v>
+        <v>44.1</v>
       </c>
       <c r="T20" t="n">
         <v>0.16</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.51</v>
+        <v>-2.5</v>
       </c>
       <c r="V20" t="n">
         <v>50</v>
@@ -3790,10 +3790,10 @@
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>313.14</v>
+        <v>313.79</v>
       </c>
       <c r="AO20" t="n">
-        <v>292.4</v>
+        <v>292.28</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3892,13 +3892,13 @@
         <v>11.76</v>
       </c>
       <c r="S21" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="T21" t="n">
         <v>0.15</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.73</v>
+        <v>-2.72</v>
       </c>
       <c r="V21" t="n">
         <v>48.3</v>
@@ -3910,10 +3910,10 @@
         <v>-0.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>1705.15</v>
+        <v>1705.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>1765.38</v>
+        <v>1765.36</v>
       </c>
       <c r="AA21" t="n">
         <v>1734.77</v>
@@ -3957,10 +3957,10 @@
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>1789.56</v>
+        <v>1787.2</v>
       </c>
       <c r="AO21" t="n">
-        <v>1656.01</v>
+        <v>1652.75</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -3979,17 +3979,17 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>[1721.0, 1730.96, 1740.93, 1750.89, 1760.85, 1770.82]</t>
+          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[1721.0, 1754.69, 1774.49, 1791.99, 1808.32, 1823.88]</t>
+          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.21, 1823.74]</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>[1721.0, 1713.17, 1715.76, 1720.06, 1725.26, 1731.02]</t>
+          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU21"/>
+  <dimension ref="A1:AU22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,7 +656,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1029652.24</v>
+        <v>1030297.85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,94 +678,94 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1435.4</v>
+        <v>1436.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹1430.56 - ₹1442.67</t>
+          <t>₹1431.73 - ₹1443.16</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1454.78</v>
+        <v>1454.6</v>
       </c>
       <c r="I2" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J2" t="n">
-        <v>1407.32</v>
+        <v>1398.49</v>
       </c>
       <c r="K2" t="n">
-        <v>1357.92</v>
+        <v>1349.96</v>
       </c>
       <c r="L2" t="n">
-        <v>1348.12</v>
+        <v>1337.12</v>
       </c>
       <c r="M2" t="n">
-        <v>6.36</v>
+        <v>6.45</v>
       </c>
       <c r="N2" t="n">
-        <v>21.9</v>
+        <v>20.38</v>
       </c>
       <c r="O2" t="n">
-        <v>25.69</v>
+        <v>24.46</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.79</v>
+        <v>-4.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>24.22</v>
+        <v>22.87</v>
       </c>
       <c r="R2" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S2" t="n">
-        <v>54.8</v>
+        <v>54.4</v>
       </c>
       <c r="T2" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.71</v>
+        <v>-0.65</v>
       </c>
       <c r="V2" t="n">
         <v>60</v>
       </c>
       <c r="W2" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="X2" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y2" t="n">
-        <v>1424.81</v>
+        <v>1417.46</v>
       </c>
       <c r="Z2" t="n">
-        <v>1471.73</v>
+        <v>1467.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>1446.88</v>
+        <v>1447.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>1399.07</v>
+        <v>1401.99</v>
       </c>
       <c r="AC2" t="n">
-        <v>1436.23</v>
+        <v>1437.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1441.06</v>
+        <v>1441.46</v>
       </c>
       <c r="AE2" t="n">
-        <v>1446.73</v>
+        <v>1446.63</v>
       </c>
       <c r="AF2" t="n">
-        <v>62.2</v>
+        <v>60.1</v>
       </c>
       <c r="AG2" t="n">
         <v>-0.01</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI2" t="n">
@@ -784,46 +784,46 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1461.85</v>
+        <v>1463.42</v>
       </c>
       <c r="AO2" t="n">
-        <v>1409.86</v>
+        <v>1409.75</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,029,652.24 Cr., a P/E ratio of 18.55, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
+          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,030,297.85 Cr., a P/E ratio of 18.56, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.16 (Bullish Momentum Zone), while MACD Line (21.90) trades below Signal (25.69) with an expanding histogram (-3.79). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.36% above the 200-day DMA (₹1348.12). Daily volatility envelope is bounded by ATR(14) of ₹24.22.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.14 (Bullish Momentum Zone), while MACD Line (20.38) trades below Signal (24.46) with an expanding histogram (-4.08). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.45% above the 200-day DMA (₹1337.12). Daily volatility envelope is bounded by ATR(14) of ₹22.87.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,435.40) is positioned above the 30-day DMA (₹1,407.32), 50-day DMA (₹1,357.92), and 200-day DMA (₹1,348.12). The price distance from 200 DMA is +6.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,436.30) is positioned above the 30-day DMA (₹1,398.49), 50-day DMA (₹1,349.96), and 200-day DMA (₹1,337.12). The price distance from 200 DMA is +6.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[1435.4, 1446.34, 1457.29, 1468.23, 1479.18, 1490.12]</t>
+          <t>[1436.3, 1440.61, 1444.92, 1449.23, 1453.54, 1457.84]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[1435.4, 1456.03, 1470.99, 1485.02, 1498.56, 1511.79]</t>
+          <t>[1436.3, 1449.76, 1457.86, 1465.07, 1471.83, 1478.3]</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>[1435.4, 1439.08, 1447.01, 1455.65, 1464.65, 1473.88]</t>
+          <t>[1436.3, 1433.75, 1435.21, 1437.34, 1439.81, 1442.5]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -837,102 +837,102 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>129536.96</v>
+        <v>130456.39</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>112.71</v>
+        <v>113.51</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹112.3 - ₹113.33</t>
+          <t>₹113.11 - ₹114.11</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>114.37</v>
+        <v>115.11</v>
       </c>
       <c r="I3" t="n">
-        <v>1607</v>
+        <v>1670</v>
       </c>
       <c r="J3" t="n">
-        <v>107.66</v>
+        <v>107.8</v>
       </c>
       <c r="K3" t="n">
-        <v>106.31</v>
+        <v>106.57</v>
       </c>
       <c r="L3" t="n">
         <v>112.63</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.88</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
         <v>0.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S3" t="n">
         <v>52.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.88</v>
+        <v>-0.82</v>
       </c>
       <c r="V3" t="n">
-        <v>51.7</v>
+        <v>53.3</v>
       </c>
       <c r="W3" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="X3" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>111.33</v>
+        <v>111.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>115.27</v>
+        <v>115.16</v>
       </c>
       <c r="AA3" t="n">
-        <v>113.61</v>
+        <v>114.42</v>
       </c>
       <c r="AB3" t="n">
-        <v>109.6</v>
+        <v>110.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>112.47</v>
+        <v>113.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>113.25</v>
+        <v>113.83</v>
       </c>
       <c r="AE3" t="n">
-        <v>113.78</v>
+        <v>114.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>70.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI3" t="n">
@@ -951,60 +951,60 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>115.85</v>
+        <v>116.81</v>
       </c>
       <c r="AO3" t="n">
-        <v>109.34</v>
+        <v>110.49</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹129,536.96 Cr., a P/E ratio of 5.86, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,456.39 Cr., a P/E ratio of 5.91, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.92 (Bullish Momentum Zone), while MACD Line (1.59) trades above Signal (1.18) with an expanding histogram (+0.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading -0.88% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.19 (Bullish Momentum Zone), while MACD Line (1.69) trades above Signal (1.28) with an expanding histogram (+0.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.07% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.00.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹112.71) is positioned above the 30-day DMA (₹107.66), 50-day DMA (₹106.31), and 200-day DMA (₹112.63). The price distance from 200 DMA is -0.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.51) is positioned above the 30-day DMA (₹107.80), 50-day DMA (₹106.57), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.07%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[112.71, 113.05, 113.39, 113.72, 114.06, 114.4]</t>
+          <t>[113.51, 113.85, 114.19, 114.53, 114.87, 115.21]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[112.71, 113.88, 114.56, 115.16, 115.72, 116.26]</t>
+          <t>[113.51, 114.65, 115.32, 115.91, 116.47, 117.0]</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>[112.71, 112.43, 112.51, 112.65, 112.82, 113.01]</t>
+          <t>[113.51, 113.25, 113.34, 113.49, 113.67, 113.87]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>215046.57</v>
+        <v>352591.73</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,157 +1012,157 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7833.5</v>
+        <v>11986</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹7803.39 - ₹7878.67</t>
+          <t>₹11941.83 - ₹12052.25</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>7953.95</v>
+        <v>12162.68</v>
       </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>7437.81</v>
+        <v>11446.68</v>
       </c>
       <c r="K4" t="n">
-        <v>7344.46</v>
+        <v>11281.17</v>
       </c>
       <c r="L4" t="n">
-        <v>7171.21</v>
+        <v>11569.56</v>
       </c>
       <c r="M4" t="n">
-        <v>9.19</v>
+        <v>2.88</v>
       </c>
       <c r="N4" t="n">
-        <v>121.41</v>
+        <v>152.76</v>
       </c>
       <c r="O4" t="n">
-        <v>84.98999999999999</v>
+        <v>129.95</v>
       </c>
       <c r="P4" t="n">
-        <v>36.42</v>
+        <v>22.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>150.57</v>
+        <v>220.85</v>
       </c>
       <c r="R4" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S4" t="n">
-        <v>49.7</v>
+        <v>51.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
       <c r="W4" t="n">
-        <v>1.92</v>
+        <v>2.67</v>
       </c>
       <c r="X4" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>7803.37</v>
+        <v>11868.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>8059.35</v>
+        <v>12287.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>7920.87</v>
+        <v>12081.89</v>
       </c>
       <c r="AB4" t="n">
-        <v>7607.65</v>
+        <v>11654.73</v>
       </c>
       <c r="AC4" t="n">
-        <v>7842.17</v>
+        <v>11965.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>7890.34</v>
+        <v>12006.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>7947.17</v>
+        <v>12026.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>74.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI4" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>37.3</v>
+        <v>41.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>31.5</v>
+        <v>15.9</v>
       </c>
       <c r="AL4" t="n">
-        <v>23.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>8042.84</v>
+        <v>12268.82</v>
       </c>
       <c r="AO4" t="n">
-        <v>7633.97</v>
+        <v>11705</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹215,046.57 Cr., a P/E ratio of 37.31, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹352,591.73 Cr., a P/E ratio of 41.27, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.10 (Bullish Momentum Zone), while MACD Line (121.41) trades above Signal (84.99) with an expanding histogram (+36.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.19% above the 200-day DMA (₹7171.21). Daily volatility envelope is bounded by ATR(14) of ₹150.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.23 (Bullish Momentum Zone), while MACD Line (152.76) trades above Signal (129.95) with an expanding histogram (+22.81). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.88% above the 200-day DMA (₹11569.56). Daily volatility envelope is bounded by ATR(14) of ₹220.85.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,833.50) is positioned above the 30-day DMA (₹7,437.81), 50-day DMA (₹7,344.46), and 200-day DMA (₹7,171.21). The price distance from 200 DMA is +9.19%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,986.00) is positioned above the 30-day DMA (₹11,446.68), 50-day DMA (₹11,281.17), and 200-day DMA (₹11,569.56). The price distance from 200 DMA is +2.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[7833.5, 7920.87, 8008.25, 8095.62, 8183.0, 8270.37]</t>
+          <t>[11986.0, 12047.98, 12109.95, 12171.93, 12233.91, 12295.88]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[7833.5, 7981.1, 8093.42, 8199.94, 8303.45, 8405.04]</t>
+          <t>[11986.0, 12136.31, 12234.88, 12324.94, 12410.58, 12493.41]</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>[7833.5, 7875.7, 7944.37, 8017.39, 8092.66, 8169.37]</t>
+          <t>[11986.0, 11981.72, 12016.26, 12057.17, 12101.4, 12147.73]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,174 +1171,174 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>350150.12</v>
+        <v>266253.87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🟢 HIGH CONVICTION BUY</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11903</v>
+        <v>2775.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹11859.37 - ₹11968.45</t>
+          <t>₹2764.36 - ₹2793.21</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12077.53</v>
+        <v>2822.07</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="J5" t="n">
-        <v>11421.23</v>
+        <v>2689.12</v>
       </c>
       <c r="K5" t="n">
-        <v>11269.86</v>
+        <v>2681.37</v>
       </c>
       <c r="L5" t="n">
-        <v>11569.69</v>
+        <v>2572.85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4</v>
+        <v>6.78</v>
       </c>
       <c r="N5" t="n">
-        <v>143.27</v>
+        <v>18.17</v>
       </c>
       <c r="O5" t="n">
-        <v>124.24</v>
+        <v>11.71</v>
       </c>
       <c r="P5" t="n">
-        <v>19.02</v>
+        <v>6.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>218.17</v>
+        <v>57.71</v>
       </c>
       <c r="R5" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S5" t="n">
-        <v>51.5</v>
+        <v>54.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.92</v>
+        <v>-0.95</v>
       </c>
       <c r="V5" t="n">
-        <v>48.3</v>
+        <v>56.7</v>
       </c>
       <c r="W5" t="n">
-        <v>2.67</v>
+        <v>1.92</v>
       </c>
       <c r="X5" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>11732.12</v>
+        <v>2757.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>12148.72</v>
+        <v>2854.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>11998.22</v>
+        <v>2799.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>11575.75</v>
+        <v>2689.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>11903.67</v>
+        <v>2773.07</v>
       </c>
       <c r="AD5" t="n">
-        <v>12008.34</v>
+        <v>2782.84</v>
       </c>
       <c r="AE5" t="n">
-        <v>12113.67</v>
+        <v>2789.77</v>
       </c>
       <c r="AF5" t="n">
-        <v>62.6</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.23</v>
+        <v>-0.03</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI5" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ5" t="n">
-        <v>41</v>
+        <v>55.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>9.300000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="AM5" t="n">
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12155.36</v>
+        <v>2850</v>
       </c>
       <c r="AO5" t="n">
-        <v>11646.4</v>
+        <v>2717.54</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹350,150.12 Cr., a P/E ratio of 40.98, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹266,253.87 Cr., a P/E ratio of 55.85, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (143.27) trades above Signal (124.24) with an expanding histogram (+19.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.40% above the 200-day DMA (₹11569.69). Daily volatility envelope is bounded by ATR(14) of ₹218.17.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 68.92 (Bullish Momentum Zone), while MACD Line (18.17) trades above Signal (11.71) with an expanding histogram (+6.46). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.78% above the 200-day DMA (₹2572.85). Daily volatility envelope is bounded by ATR(14) of ₹57.71.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,903.00) is positioned above the 30-day DMA (₹11,421.23), 50-day DMA (₹11,269.86), and 200-day DMA (₹11,569.69). The price distance from 200 DMA is +2.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,775.90) is positioned above the 30-day DMA (₹2,689.12), 50-day DMA (₹2,681.37), and 200-day DMA (₹2,572.85). The price distance from 200 DMA is +6.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[11903.0, 11938.71, 11974.42, 12010.13, 12045.84, 12081.54]</t>
+          <t>[2775.9, 2799.45, 2823.0, 2846.55, 2870.11, 2893.66]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[11903.0, 12025.98, 12097.83, 12161.28, 12220.37, 12276.68]</t>
+          <t>[2775.9, 2822.54, 2855.65, 2886.54, 2916.28, 2945.28]</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>[11903.0, 11873.26, 11881.86, 11896.76, 11914.94, 11935.19]</t>
+          <t>[2775.9, 2782.14, 2798.52, 2816.57, 2835.48, 2854.94]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>263368.34</v>
+        <v>215856.41</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,166 +1346,166 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2747.3</v>
+        <v>7857</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2735.68 - ₹2764.73</t>
+          <t>₹7826.88 - ₹7902.18</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2793.77</v>
+        <v>7977.49</v>
       </c>
       <c r="I6" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>2687.86</v>
+        <v>7447.86</v>
       </c>
       <c r="K6" t="n">
-        <v>2678.76</v>
+        <v>7362.95</v>
       </c>
       <c r="L6" t="n">
-        <v>2570.71</v>
+        <v>7176.17</v>
       </c>
       <c r="M6" t="n">
-        <v>6.83</v>
+        <v>9.16</v>
       </c>
       <c r="N6" t="n">
-        <v>16.14</v>
+        <v>130.62</v>
       </c>
       <c r="O6" t="n">
-        <v>10.09</v>
+        <v>94.11</v>
       </c>
       <c r="P6" t="n">
-        <v>6.05</v>
+        <v>36.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>58.09</v>
+        <v>150.61</v>
       </c>
       <c r="R6" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S6" t="n">
-        <v>51.7</v>
+        <v>51.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.12</v>
+        <v>-1</v>
       </c>
       <c r="V6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="X6" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>2707.04</v>
+        <v>7705.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>2803.2</v>
+        <v>7980.54</v>
       </c>
       <c r="AA6" t="n">
-        <v>2769.28</v>
+        <v>7919.86</v>
       </c>
       <c r="AB6" t="n">
-        <v>2660.17</v>
+        <v>7631.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>2751.53</v>
+        <v>7877.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>2770.66</v>
+        <v>7899</v>
       </c>
       <c r="AE6" t="n">
-        <v>2794.03</v>
+        <v>7941</v>
       </c>
       <c r="AF6" t="n">
-        <v>62.4</v>
+        <v>79</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.03</v>
+        <v>0.16</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI6" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55.2</v>
+        <v>37.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.9</v>
+        <v>31.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>12.8</v>
+        <v>23.2</v>
       </c>
       <c r="AM6" t="n">
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>2817.62</v>
+        <v>8053.83</v>
       </c>
       <c r="AO6" t="n">
-        <v>2683.36</v>
+        <v>7674.73</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹263,368.34 Cr., a P/E ratio of 55.24, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹215,856.41 Cr., a P/E ratio of 37.45, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.38 (Bullish Momentum Zone), while MACD Line (16.14) trades above Signal (10.09) with an expanding histogram (+6.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.83% above the 200-day DMA (₹2570.71). Daily volatility envelope is bounded by ATR(14) of ₹58.09.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.95 (Bullish Momentum Zone), while MACD Line (130.62) trades above Signal (94.11) with an expanding histogram (+36.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.16% above the 200-day DMA (₹7176.17). Daily volatility envelope is bounded by ATR(14) of ₹150.61.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,747.30) is positioned above the 30-day DMA (₹2,687.86), 50-day DMA (₹2,678.76), and 200-day DMA (₹2,570.71). The price distance from 200 DMA is +6.83%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,857.00) is positioned above the 30-day DMA (₹7,447.86), 50-day DMA (₹7,362.95), and 200-day DMA (₹7,176.17). The price distance from 200 DMA is +9.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2747.3, 2755.54, 2763.78, 2772.03, 2780.27, 2788.51]</t>
+          <t>[7857.0, 7880.57, 7904.14, 7927.71, 7951.28, 7974.85]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2747.3, 2778.78, 2796.64, 2812.27, 2826.74, 2840.46]</t>
+          <t>[7857.0, 7940.81, 7989.34, 8032.06, 8071.77, 8109.56]</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>[2747.3, 2738.12, 2739.14, 2741.84, 2745.42, 2749.54]</t>
+          <t>[7857.0, 7835.39, 7840.24, 7849.45, 7860.92, 7873.82]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>105169.94</v>
+        <v>25000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,152 +1513,152 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2199.8</v>
+        <v>376.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹2190.26 - ₹2214.11</t>
+          <t>₹374.98 - ₹378.78</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2237.97</v>
+        <v>382.59</v>
       </c>
       <c r="I7" t="n">
-        <v>69</v>
+        <v>437</v>
       </c>
       <c r="J7" t="n">
-        <v>2140.62</v>
+        <v>357.93</v>
       </c>
       <c r="K7" t="n">
-        <v>2061.08</v>
+        <v>350.57</v>
       </c>
       <c r="L7" t="n">
-        <v>1703.8</v>
+        <v>347.65</v>
       </c>
       <c r="M7" t="n">
-        <v>27.05</v>
+        <v>7.28</v>
       </c>
       <c r="N7" t="n">
-        <v>29.77</v>
+        <v>4.74</v>
       </c>
       <c r="O7" t="n">
-        <v>35.4</v>
+        <v>2.83</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.63</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>47.71</v>
+        <v>7.61</v>
       </c>
       <c r="R7" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S7" t="n">
-        <v>50.3</v>
+        <v>51.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.21</v>
+        <v>-1.07</v>
       </c>
       <c r="V7" t="n">
-        <v>50</v>
+        <v>51.7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.78</v>
+        <v>2.94</v>
       </c>
       <c r="X7" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>2184.76</v>
+        <v>367.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>2261.76</v>
+        <v>378.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>2217.76</v>
+        <v>379.51</v>
       </c>
       <c r="AB7" t="n">
-        <v>2128.24</v>
+        <v>365.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>2191.3</v>
+        <v>375.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>2221.1</v>
+        <v>377.55</v>
       </c>
       <c r="AE7" t="n">
-        <v>2242.4</v>
+        <v>378.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>57.9</v>
+        <v>81.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI7" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>97.09999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>17.5</v>
+        <v>25.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AN7" t="n">
-        <v>2267.45</v>
+        <v>386.53</v>
       </c>
       <c r="AO7" t="n">
-        <v>2143.19</v>
+        <v>366.51</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,169.94 Cr., a P/E ratio of 97.08, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.20, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.85 (Bullish Momentum Zone), while MACD Line (29.77) trades below Signal (35.40) with an expanding histogram (-5.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.05% above the 200-day DMA (₹1703.80). Daily volatility envelope is bounded by ATR(14) of ₹47.71.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 81.18 (Bullish Momentum Zone), while MACD Line (4.74) trades above Signal (2.83) with an expanding histogram (+1.91). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.28% above the 200-day DMA (₹347.65). Daily volatility envelope is bounded by ATR(14) of ₹7.61.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,199.80) is positioned above the 30-day DMA (₹2,140.62), 50-day DMA (₹2,061.08), and 200-day DMA (₹1,703.80). The price distance from 200 DMA is +27.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹376.50) is positioned above the 30-day DMA (₹357.93), 50-day DMA (₹350.57), and 200-day DMA (₹347.65). The price distance from 200 DMA is +7.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2199.8, 2217.76, 2235.72, 2253.68, 2271.64, 2289.6]</t>
+          <t>[376.5, 377.63, 378.76, 379.89, 381.02, 382.15]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2199.8, 2236.84, 2262.71, 2286.73, 2309.8, 2332.27]</t>
+          <t>[376.5, 380.67, 383.07, 385.16, 387.11, 388.96]</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>[2199.8, 2203.45, 2215.48, 2228.89, 2243.01, 2257.59]</t>
+          <t>[376.5, 375.35, 375.53, 375.93, 376.45, 377.04]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1672,109 +1672,109 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105127.58</v>
+        <v>105696.96</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>738.55</v>
+        <v>742.55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹735.6 - ₹742.98</t>
+          <t>₹739.53 - ₹747.08</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>750.37</v>
+        <v>754.63</v>
       </c>
       <c r="I8" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J8" t="n">
-        <v>729.51</v>
+        <v>730.08</v>
       </c>
       <c r="K8" t="n">
-        <v>703.6799999999999</v>
+        <v>705.51</v>
       </c>
       <c r="L8" t="n">
-        <v>686.09</v>
+        <v>686.16</v>
       </c>
       <c r="M8" t="n">
-        <v>9.210000000000001</v>
+        <v>7.63</v>
       </c>
       <c r="N8" t="n">
-        <v>8.49</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>9.380000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.77</v>
+        <v>15.1</v>
       </c>
       <c r="R8" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S8" t="n">
-        <v>46.2</v>
+        <v>51.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.24</v>
+        <v>-1.08</v>
       </c>
       <c r="V8" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
       <c r="W8" t="n">
-        <v>5.75</v>
+        <v>6.51</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>720.8200000000001</v>
+        <v>724.4299999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>725.27</v>
+        <v>736.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>744.46</v>
+        <v>748.49</v>
       </c>
       <c r="AB8" t="n">
-        <v>716.39</v>
+        <v>719.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>744.27</v>
+        <v>742.17</v>
       </c>
       <c r="AD8" t="n">
-        <v>751.6900000000001</v>
+        <v>744.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>764.8200000000001</v>
+        <v>746.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>48.2</v>
+        <v>50</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI8" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="AK8" t="n">
         <v>15.1</v>
@@ -1786,394 +1786,394 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>757.62</v>
+        <v>762.51</v>
       </c>
       <c r="AO8" t="n">
-        <v>720.98</v>
+        <v>724.41</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,127.58 Cr., a P/E ratio of 49.01, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,696.96 Cr., a P/E ratio of 49.27, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.00 (Consolidation Zone), while MACD Line (8.21) trades below Signal (9.15) with an expanding histogram (-0.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.63% above the 200-day DMA (₹686.16). Daily volatility envelope is bounded by ATR(14) of ₹15.10.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹738.55) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹742.55) is positioned above the 30-day DMA (₹730.08), 50-day DMA (₹705.51), and 200-day DMA (₹686.16). The price distance from 200 DMA is +7.63%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[738.55, 740.77, 742.98, 745.2, 747.41, 749.63]</t>
+          <t>[742.55, 744.78, 747.01, 749.23, 751.46, 753.69]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[738.55, 746.67, 751.34, 755.43, 759.23, 762.84]</t>
+          <t>[742.55, 750.82, 755.55, 759.69, 763.54, 767.19]</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>[738.55, 736.33, 736.71, 737.52, 738.55, 739.72]</t>
+          <t>[742.55, 740.25, 740.6, 741.39, 742.4, 743.56]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>310746.28</v>
+        <v>108208.54</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4646.5</v>
+        <v>1111.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹4629.85 - ₹4671.48</t>
+          <t>₹1107.05 - ₹1118.93</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4713.1</v>
+        <v>1130.82</v>
       </c>
       <c r="I9" t="n">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="J9" t="n">
-        <v>4471.9</v>
+        <v>1107.37</v>
       </c>
       <c r="K9" t="n">
-        <v>4404.23</v>
+        <v>1064.71</v>
       </c>
       <c r="L9" t="n">
-        <v>4346.03</v>
+        <v>1056.34</v>
       </c>
       <c r="M9" t="n">
-        <v>5.42</v>
+        <v>3.99</v>
       </c>
       <c r="N9" t="n">
-        <v>56.6</v>
+        <v>7.41</v>
       </c>
       <c r="O9" t="n">
-        <v>49.9</v>
+        <v>8.82</v>
       </c>
       <c r="P9" t="n">
-        <v>6.7</v>
+        <v>-1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>83.25</v>
+        <v>23.77</v>
       </c>
       <c r="R9" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S9" t="n">
-        <v>41.4</v>
+        <v>51.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.24</v>
+        <v>-1.15</v>
       </c>
       <c r="V9" t="n">
-        <v>41.7</v>
+        <v>55</v>
       </c>
       <c r="W9" t="n">
-        <v>2.15</v>
+        <v>7.71</v>
       </c>
       <c r="X9" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>4548.57</v>
+        <v>1083.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>4711.2</v>
+        <v>1090.79</v>
       </c>
       <c r="AA9" t="n">
-        <v>4683.67</v>
+        <v>1120.69</v>
       </c>
       <c r="AB9" t="n">
-        <v>4521.62</v>
+        <v>1076.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>4635.53</v>
+        <v>1111.17</v>
       </c>
       <c r="AD9" t="n">
-        <v>4679.96</v>
+        <v>1114.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>4713.43</v>
+        <v>1117.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>59.3</v>
+        <v>47.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI9" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34.1</v>
+        <v>75.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>12.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>27.5</v>
+        <v>17.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>24</v>
+        <v>14.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>4765.9</v>
+        <v>1142.26</v>
       </c>
       <c r="AO9" t="n">
-        <v>4525.47</v>
+        <v>1081.35</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,746.28 Cr., a P/E ratio of 34.13, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>MAXHEALTH operates in the Healthcare sector. With an estimated Market Cap of ₹108,208.54 Cr., a P/E ratio of 75.53, and YoY Revenue Growth of +12.2%, the company demonstrates strong institutional backing, solid operating profit margins (17.23%), and healthy Return on Equity (14.33%).</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.70 (Consolidation Zone), while MACD Line (7.41) trades below Signal (8.82) with an expanding histogram (-1.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.99% above the 200-day DMA (₹1056.34). Daily volatility envelope is bounded by ATR(14) of ₹23.77.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,646.50) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MAXHEALTH. Current Market Price (₹1,111.80) is positioned above the 30-day DMA (₹1,107.37), 50-day DMA (₹1,064.71), and 200-day DMA (₹1,056.34). The price distance from 200 DMA is +3.99%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[4646.5, 4660.44, 4674.38, 4688.32, 4702.26, 4716.2]</t>
+          <t>[1111.8, 1115.14, 1118.47, 1121.81, 1125.14, 1128.48]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[4646.5, 4693.74, 4721.47, 4746.0, 4768.86, 4790.66]</t>
+          <t>[1111.8, 1124.64, 1131.92, 1138.28, 1144.16, 1149.74]</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>[4646.5, 4635.46, 4639.06, 4645.06, 4652.31, 4660.35]</t>
+          <t>[1111.8, 1108.0, 1108.39, 1109.45, 1110.88, 1112.53]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25000</v>
+        <v>68421.07000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>372.95</v>
+        <v>5722.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹371.41 - ₹375.26</t>
+          <t>₹5698.55 - ₹5758.43</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>379.11</v>
+        <v>5818.3</v>
       </c>
       <c r="I10" t="n">
-        <v>432</v>
+        <v>27</v>
       </c>
       <c r="J10" t="n">
-        <v>357.21</v>
+        <v>5587.6</v>
       </c>
       <c r="K10" t="n">
-        <v>349.78</v>
+        <v>5491.02</v>
       </c>
       <c r="L10" t="n">
-        <v>347.56</v>
+        <v>5522.76</v>
       </c>
       <c r="M10" t="n">
-        <v>6.64</v>
+        <v>4.14</v>
       </c>
       <c r="N10" t="n">
-        <v>4.07</v>
+        <v>60.48</v>
       </c>
       <c r="O10" t="n">
-        <v>2.35</v>
+        <v>53.66</v>
       </c>
       <c r="P10" t="n">
-        <v>1.72</v>
+        <v>6.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.7</v>
+        <v>119.75</v>
       </c>
       <c r="R10" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S10" t="n">
-        <v>47.3</v>
+        <v>49.7</v>
       </c>
       <c r="T10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.25</v>
+        <v>-1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>50</v>
+        <v>51.7</v>
       </c>
       <c r="W10" t="n">
-        <v>2.81</v>
+        <v>3.12</v>
       </c>
       <c r="X10" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>366.16</v>
+        <v>5612.76</v>
       </c>
       <c r="Z10" t="n">
-        <v>379.22</v>
+        <v>5813.04</v>
       </c>
       <c r="AA10" t="n">
-        <v>375.93</v>
+        <v>5768.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>361.4</v>
+        <v>5542.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>372.32</v>
+        <v>5739.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>374.64</v>
+        <v>5757.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>376.32</v>
+        <v>5791.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>78.3</v>
+        <v>61</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.08</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI10" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6.1</v>
+        <v>29.7</v>
       </c>
       <c r="AK10" t="n">
-        <v>25.2</v>
+        <v>14.6</v>
       </c>
       <c r="AL10" t="n">
-        <v>68.90000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="AM10" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>383.26</v>
+        <v>5845.03</v>
       </c>
       <c r="AO10" t="n">
-        <v>363.06</v>
+        <v>5589.4</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,421.07 Cr., a P/E ratio of 29.70, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.98 (Bullish Momentum Zone), while MACD Line (60.48) trades above Signal (53.66) with an expanding histogram (+6.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹5522.76). Daily volatility envelope is bounded by ATR(14) of ₹119.75.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹372.95) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,722.50) is positioned above the 30-day DMA (₹5,587.60), 50-day DMA (₹5,491.02), and 200-day DMA (₹5,522.76). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[372.95, 374.07, 375.19, 376.31, 377.43, 378.54]</t>
+          <t>[5722.5, 5739.67, 5756.84, 5774.0, 5791.17, 5808.34]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[372.95, 377.15, 379.54, 381.64, 383.59, 385.43]</t>
+          <t>[5722.5, 5787.57, 5824.58, 5856.97, 5886.97, 5915.45]</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>[372.95, 371.76, 371.92, 372.31, 372.8, 373.38]</t>
+          <t>[5722.5, 5703.74, 5706.03, 5711.78, 5719.32, 5728.01]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68767.81</v>
+        <v>312919.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2181,166 +2181,166 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5751.5</v>
+        <v>4679</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹5727.01 - ₹5788.23</t>
+          <t>₹4662.29 - ₹4704.06</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5849.44</v>
+        <v>4745.82</v>
       </c>
       <c r="I11" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>5575</v>
+        <v>4479.85</v>
       </c>
       <c r="K11" t="n">
-        <v>5484.08</v>
+        <v>4409.79</v>
       </c>
       <c r="L11" t="n">
-        <v>5521.06</v>
+        <v>4345.73</v>
       </c>
       <c r="M11" t="n">
-        <v>5.35</v>
+        <v>6.92</v>
       </c>
       <c r="N11" t="n">
-        <v>57.19</v>
+        <v>59.87</v>
       </c>
       <c r="O11" t="n">
-        <v>51.96</v>
+        <v>51.89</v>
       </c>
       <c r="P11" t="n">
-        <v>5.23</v>
+        <v>7.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>122.43</v>
+        <v>83.53</v>
       </c>
       <c r="R11" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S11" t="n">
-        <v>46.5</v>
+        <v>42.8</v>
       </c>
       <c r="T11" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.34</v>
+        <v>-1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>53.3</v>
+        <v>43.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.82</v>
+        <v>2.31</v>
       </c>
       <c r="X11" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>5710.85</v>
+        <v>4578.77</v>
       </c>
       <c r="Z11" t="n">
-        <v>5912.15</v>
+        <v>4740.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>5797.51</v>
+        <v>4716.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>5567.86</v>
+        <v>4553.71</v>
       </c>
       <c r="AC11" t="n">
-        <v>5773.17</v>
+        <v>4675.37</v>
       </c>
       <c r="AD11" t="n">
-        <v>5811.34</v>
+        <v>4690.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>5871.17</v>
+        <v>4701.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>58.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI11" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>29.9</v>
+        <v>34.4</v>
       </c>
       <c r="AK11" t="n">
-        <v>14.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>15.6</v>
+        <v>27.5</v>
       </c>
       <c r="AM11" t="n">
-        <v>17.6</v>
+        <v>24</v>
       </c>
       <c r="AN11" t="n">
-        <v>5874.26</v>
+        <v>4800.74</v>
       </c>
       <c r="AO11" t="n">
-        <v>5617.74</v>
+        <v>4550.75</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,767.81 Cr., a P/E ratio of 29.85, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹312,919.80 Cr., a P/E ratio of 34.37, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.59 (Bullish Momentum Zone), while MACD Line (59.87) trades above Signal (51.89) with an expanding histogram (+7.98). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.92% above the 200-day DMA (₹4345.73). Daily volatility envelope is bounded by ATR(14) of ₹83.53.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,751.50) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,679.00) is positioned above the 30-day DMA (₹4,479.85), 50-day DMA (₹4,409.79), and 200-day DMA (₹4,345.73). The price distance from 200 DMA is +6.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[5751.5, 5797.12, 5842.75, 5888.37, 5934.0, 5979.62]</t>
+          <t>[4679.0, 4693.04, 4707.07, 4721.11, 4735.15, 4749.18]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[5751.5, 5846.1, 5912.0, 5973.19, 6031.94, 6089.12]</t>
+          <t>[4679.0, 4726.45, 4754.32, 4778.98, 4801.97, 4823.9]</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>[5751.5, 5760.4, 5790.81, 5824.76, 5860.54, 5897.49]</t>
+          <t>[4679.0, 4667.98, 4671.64, 4677.71, 4685.03, 4693.15]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>133901.31</v>
+        <v>105767.55</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2348,491 +2348,491 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3760</v>
+        <v>2212.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹3740.59 - ₹3789.12</t>
+          <t>₹2202.84 - ₹2226.49</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3837.66</v>
+        <v>2250.15</v>
       </c>
       <c r="I12" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="J12" t="n">
-        <v>3594.31</v>
+        <v>2146.11</v>
       </c>
       <c r="K12" t="n">
-        <v>3627.85</v>
+        <v>2067.23</v>
       </c>
       <c r="L12" t="n">
-        <v>3330.53</v>
+        <v>1708.73</v>
       </c>
       <c r="M12" t="n">
-        <v>9.859999999999999</v>
+        <v>28.74</v>
       </c>
       <c r="N12" t="n">
-        <v>22.06</v>
+        <v>30.53</v>
       </c>
       <c r="O12" t="n">
-        <v>10.09</v>
+        <v>34.42</v>
       </c>
       <c r="P12" t="n">
-        <v>11.97</v>
+        <v>-3.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>97.06999999999999</v>
+        <v>47.31</v>
       </c>
       <c r="R12" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S12" t="n">
-        <v>50.6</v>
+        <v>49.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.51</v>
+        <v>-1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="W12" t="n">
-        <v>2.23</v>
+        <v>1.76</v>
       </c>
       <c r="X12" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>3683.99</v>
+        <v>2184.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>3815.59</v>
+        <v>2261.79</v>
       </c>
       <c r="AA12" t="n">
-        <v>3790.08</v>
+        <v>2230</v>
       </c>
       <c r="AB12" t="n">
-        <v>3614.39</v>
+        <v>2141.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>3743.5</v>
+        <v>2212.13</v>
       </c>
       <c r="AD12" t="n">
-        <v>3824.9</v>
+        <v>2218.16</v>
       </c>
       <c r="AE12" t="n">
-        <v>3889.8</v>
+        <v>2224.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>74.09999999999999</v>
+        <v>58.7</v>
       </c>
       <c r="AG12" t="n">
         <v>0.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI12" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>79.40000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AK12" t="n">
-        <v>14.6</v>
+        <v>17.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="AM12" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>3882.26</v>
+        <v>2282.89</v>
       </c>
       <c r="AO12" t="n">
-        <v>3647.31</v>
+        <v>2153.31</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,901.31 Cr., a P/E ratio of 79.36, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
+          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,767.55 Cr., a P/E ratio of 97.63, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (30.53) trades below Signal (34.42) with an expanding histogram (-3.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +28.74% above the 200-day DMA (₹1708.73). Daily volatility envelope is bounded by ATR(14) of ₹47.31.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,760.00) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,212.30) is positioned above the 30-day DMA (₹2,146.11), 50-day DMA (₹2,067.23), and 200-day DMA (₹1,708.73). The price distance from 200 DMA is +28.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[3760.0, 3771.28, 3782.56, 3793.84, 3805.12, 3816.4]</t>
+          <t>[2212.3, 2218.94, 2225.57, 2232.21, 2238.85, 2245.48]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[3760.0, 3810.11, 3837.47, 3861.1, 3882.78, 3903.23]</t>
+          <t>[2212.3, 2237.86, 2252.33, 2264.99, 2276.69, 2287.8]</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>[3760.0, 3742.16, 3741.37, 3743.4, 3746.88, 3751.28]</t>
+          <t>[2212.3, 2204.74, 2205.5, 2207.63, 2210.46, 2213.75]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>119011.76</v>
+        <v>133288.78</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1473.2</v>
+        <v>3742.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1466.31 - ₹1483.53</t>
+          <t>₹3723.39 - ₹3771.92</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1500.76</v>
+        <v>3820.46</v>
       </c>
       <c r="I13" t="n">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="J13" t="n">
-        <v>1436.14</v>
+        <v>3594.31</v>
       </c>
       <c r="K13" t="n">
-        <v>1414.83</v>
+        <v>3627.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1396.09</v>
+        <v>3330.53</v>
       </c>
       <c r="M13" t="n">
-        <v>5.04</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.130000000000001</v>
+        <v>22.06</v>
       </c>
       <c r="O13" t="n">
-        <v>6.31</v>
+        <v>10.09</v>
       </c>
       <c r="P13" t="n">
-        <v>1.82</v>
+        <v>11.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.45</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S13" t="n">
-        <v>46.1</v>
+        <v>51.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.52</v>
+        <v>-1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>45</v>
+        <v>53.3</v>
       </c>
       <c r="W13" t="n">
-        <v>11.03</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>1431.86</v>
+        <v>3658.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>1388.25</v>
+        <v>3789.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>1484.99</v>
+        <v>3772.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1421.52</v>
+        <v>3597.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>1471.43</v>
+        <v>3737.07</v>
       </c>
       <c r="AD13" t="n">
-        <v>1480.56</v>
+        <v>3764.14</v>
       </c>
       <c r="AE13" t="n">
-        <v>1487.93</v>
+        <v>3785.47</v>
       </c>
       <c r="AF13" t="n">
-        <v>56.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.08</v>
+        <v>0.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI13" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>35.3</v>
+        <v>79</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.5</v>
+        <v>14.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="AM13" t="n">
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>1500.75</v>
+        <v>3858.87</v>
       </c>
       <c r="AO13" t="n">
-        <v>1440.03</v>
+        <v>3636.68</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,011.76 Cr., a P/E ratio of 35.34, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,288.78 Cr., a P/E ratio of 79.00, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,473.20) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,742.80) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1473.2, 1477.62, 1482.04, 1486.46, 1490.88, 1495.3]</t>
+          <t>[3742.8, 3754.03, 3765.26, 3776.49, 3787.71, 3798.94]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1473.2, 1491.4, 1501.53, 1510.33, 1518.44, 1526.11]</t>
+          <t>[3742.8, 3792.86, 3820.17, 3843.74, 3865.37, 3885.77]</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>[1473.2, 1467.28, 1467.42, 1468.56, 1470.21, 1472.19]</t>
+          <t>[3742.8, 3724.91, 3724.07, 3726.04, 3729.47, 3733.82]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>246283.11</v>
+        <v>118632.09</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1046.7</v>
+        <v>1468.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹1040.39 - ₹1056.17</t>
+          <t>₹1461.7 - ₹1478.7</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1071.96</v>
+        <v>1495.69</v>
       </c>
       <c r="I14" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="J14" t="n">
-        <v>1032.61</v>
+        <v>1440.19</v>
       </c>
       <c r="K14" t="n">
-        <v>994.9400000000001</v>
+        <v>1416.57</v>
       </c>
       <c r="L14" t="n">
-        <v>942.9400000000001</v>
+        <v>1395.71</v>
       </c>
       <c r="M14" t="n">
-        <v>8.94</v>
+        <v>5.55</v>
       </c>
       <c r="N14" t="n">
-        <v>8.390000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="O14" t="n">
-        <v>12.02</v>
+        <v>7.12</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.63</v>
+        <v>3.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>31.57</v>
+        <v>33.99</v>
       </c>
       <c r="R14" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S14" t="n">
-        <v>50.6</v>
+        <v>42.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.83</v>
+        <v>-1.65</v>
       </c>
       <c r="V14" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="W14" t="n">
-        <v>3.38</v>
+        <v>12.88</v>
       </c>
       <c r="X14" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>1019.36</v>
+        <v>1427.72</v>
       </c>
       <c r="Z14" t="n">
-        <v>1055.99</v>
+        <v>1439.07</v>
       </c>
       <c r="AA14" t="n">
-        <v>1055.07</v>
+        <v>1480.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>999.34</v>
+        <v>1417.52</v>
       </c>
       <c r="AC14" t="n">
-        <v>1043.47</v>
+        <v>1470.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1057.84</v>
+        <v>1474</v>
       </c>
       <c r="AE14" t="n">
-        <v>1068.97</v>
+        <v>1479.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>46.1</v>
+        <v>61.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.14</v>
+        <v>-0.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI14" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>18.5</v>
+        <v>35.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>39.1</v>
+        <v>3.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>50.1</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>1086.01</v>
+        <v>1501.32</v>
       </c>
       <c r="AO14" t="n">
-        <v>1013.31</v>
+        <v>1437.8</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹246,283.11 Cr., a P/E ratio of 18.48, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹118,632.09 Cr., a P/E ratio of 35.22, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.58 (Bullish Momentum Zone), while MACD Line (10.35) trades above Signal (7.12) with an expanding histogram (+3.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.55% above the 200-day DMA (₹1395.71). Daily volatility envelope is bounded by ATR(14) of ₹33.99.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,046.70) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,468.50) is positioned above the 30-day DMA (₹1,440.19), 50-day DMA (₹1,416.57), and 200-day DMA (₹1,395.71). The price distance from 200 DMA is +5.55%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[1046.7, 1049.84, 1052.98, 1056.12, 1059.26, 1062.4]</t>
+          <t>[1468.5, 1472.91, 1477.31, 1481.72, 1486.12, 1490.53]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[1046.7, 1062.47, 1070.84, 1077.99, 1084.52, 1090.64]</t>
+          <t>[1468.5, 1486.5, 1496.54, 1505.26, 1513.31, 1520.93]</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>[1046.7, 1040.37, 1039.59, 1039.72, 1040.32, 1041.22]</t>
+          <t>[1468.5, 1462.71, 1462.89, 1464.06, 1465.73, 1467.73]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2841,842 +2841,842 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85420.58</v>
+        <v>147485.03</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14049</v>
+        <v>1664.9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹13965.8 - ₹14173.8</t>
+          <t>₹1655.73 - ₹1678.66</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14381.8</v>
+        <v>1701.6</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="J15" t="n">
-        <v>13190.57</v>
+        <v>1487.74</v>
       </c>
       <c r="K15" t="n">
-        <v>12605.68</v>
+        <v>1465.74</v>
       </c>
       <c r="L15" t="n">
-        <v>12333.95</v>
+        <v>1460.05</v>
       </c>
       <c r="M15" t="n">
-        <v>16.25</v>
+        <v>13.1</v>
       </c>
       <c r="N15" t="n">
-        <v>477.1</v>
+        <v>57.77</v>
       </c>
       <c r="O15" t="n">
-        <v>503.84</v>
+        <v>45.82</v>
       </c>
       <c r="P15" t="n">
-        <v>-26.74</v>
+        <v>11.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>416</v>
+        <v>45.87</v>
       </c>
       <c r="R15" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S15" t="n">
-        <v>45.8</v>
+        <v>50.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.04</v>
+        <v>-1.66</v>
       </c>
       <c r="V15" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="W15" t="n">
-        <v>6.67</v>
+        <v>7.74</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>13634.58</v>
+        <v>1610.03</v>
       </c>
       <c r="Z15" t="n">
-        <v>14126.3</v>
+        <v>1668.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>14161.39</v>
+        <v>1678.22</v>
       </c>
       <c r="AB15" t="n">
-        <v>13425</v>
+        <v>1596.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>14079.67</v>
+        <v>1664.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>14558.34</v>
+        <v>1669.46</v>
       </c>
       <c r="AE15" t="n">
-        <v>15067.67</v>
+        <v>1674.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>64.7</v>
+        <v>77.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>41.2</v>
+        <v>28.8</v>
       </c>
       <c r="AK15" t="n">
-        <v>21.1</v>
+        <v>17.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM15" t="n">
         <v>15</v>
       </c>
       <c r="AN15" t="n">
-        <v>14632.09</v>
+        <v>1710.83</v>
       </c>
       <c r="AO15" t="n">
-        <v>13525.18</v>
+        <v>1620.71</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,420.58 Cr., a P/E ratio of 41.15, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹147,485.03 Cr., a P/E ratio of 28.80, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.82 (Bullish Momentum Zone), while MACD Line (57.77) trades above Signal (45.82) with an expanding histogram (+11.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.10% above the 200-day DMA (₹1460.05). Daily volatility envelope is bounded by ATR(14) of ₹45.87.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,049.00) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,664.90) is positioned above the 30-day DMA (₹1,487.74), 50-day DMA (₹1,465.74), and 200-day DMA (₹1,460.05). The price distance from 200 DMA is +13.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[14049.0, 14091.15, 14133.29, 14175.44, 14217.59, 14259.73]</t>
+          <t>[1664.9, 1669.89, 1674.89, 1679.88, 1684.88, 1689.87]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[14049.0, 14257.55, 14368.62, 14463.65, 14550.39, 14631.82]</t>
+          <t>[1664.9, 1688.24, 1700.84, 1711.66, 1721.58, 1730.9]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[14049.0, 13966.35, 13956.8, 13959.28, 13967.99, 13980.67]</t>
+          <t>[1664.9, 1656.13, 1655.43, 1656.05, 1657.36, 1659.1]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>146280.27</v>
+        <v>250353.71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1651.3</v>
+        <v>1064</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹1641.81 - ₹1665.54</t>
+          <t>₹1057.81 - ₹1073.29</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1689.26</v>
+        <v>1088.76</v>
       </c>
       <c r="I16" t="n">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="J16" t="n">
-        <v>1478.49</v>
+        <v>1034.29</v>
       </c>
       <c r="K16" t="n">
-        <v>1460.44</v>
+        <v>997.16</v>
       </c>
       <c r="L16" t="n">
-        <v>1458.79</v>
+        <v>944.85</v>
       </c>
       <c r="M16" t="n">
-        <v>14.41</v>
+        <v>10.78</v>
       </c>
       <c r="N16" t="n">
-        <v>56.22</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>42.84</v>
+        <v>11.36</v>
       </c>
       <c r="P16" t="n">
-        <v>13.38</v>
+        <v>-2.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.45</v>
+        <v>30.95</v>
       </c>
       <c r="R16" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S16" t="n">
-        <v>44.3</v>
+        <v>50.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.05</v>
+        <v>-1.78</v>
       </c>
       <c r="V16" t="n">
-        <v>48.3</v>
+        <v>56.7</v>
       </c>
       <c r="W16" t="n">
-        <v>8.69</v>
+        <v>3.75</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>1625.32</v>
+        <v>1035.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>1683.12</v>
+        <v>1072.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>1664.51</v>
+        <v>1072.51</v>
       </c>
       <c r="AB16" t="n">
-        <v>1580.13</v>
+        <v>1017.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>1641.1</v>
+        <v>1061.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1671.7</v>
+        <v>1067.86</v>
       </c>
       <c r="AE16" t="n">
-        <v>1692.1</v>
+        <v>1071.73</v>
       </c>
       <c r="AF16" t="n">
-        <v>86.2</v>
+        <v>49.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28.6</v>
+        <v>18.8</v>
       </c>
       <c r="AK16" t="n">
-        <v>17.7</v>
+        <v>39.1</v>
       </c>
       <c r="AL16" t="n">
-        <v>8.699999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>1696.61</v>
+        <v>1103</v>
       </c>
       <c r="AO16" t="n">
-        <v>1605</v>
+        <v>1026.08</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,280.27 Cr., a P/E ratio of 28.57, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹250,353.71 Cr., a P/E ratio of 18.79, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.70 (Consolidation Zone), while MACD Line (8.70) trades below Signal (11.36) with an expanding histogram (-2.65). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹944.85). Daily volatility envelope is bounded by ATR(14) of ₹30.95.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,651.30) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,064.00) is positioned above the 30-day DMA (₹1,034.29), 50-day DMA (₹997.16), and 200-day DMA (₹944.85). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[1651.3, 1656.25, 1661.21, 1666.16, 1671.12, 1676.07]</t>
+          <t>[1064.0, 1067.19, 1070.38, 1073.58, 1076.77, 1079.96]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[1651.3, 1675.23, 1688.05, 1699.04, 1709.08, 1718.51]</t>
+          <t>[1064.0, 1079.57, 1087.89, 1095.02, 1101.53, 1107.64]</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>[1651.3, 1642.02, 1641.08, 1641.51, 1642.65, 1644.24]</t>
+          <t>[1064.0, 1057.91, 1057.25, 1057.49, 1058.2, 1059.2]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17572.27</v>
+        <v>63438.19</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>613.35</v>
+        <v>2106</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹608.87 - ₹620.07</t>
+          <t>₹2093.22 - ₹2125.18</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>631.27</v>
+        <v>2157.13</v>
       </c>
       <c r="I17" t="n">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="J17" t="n">
-        <v>578.01</v>
+        <v>2010.06</v>
       </c>
       <c r="K17" t="n">
-        <v>541.38</v>
+        <v>1895.79</v>
       </c>
       <c r="L17" t="n">
-        <v>553.54</v>
+        <v>1880.5</v>
       </c>
       <c r="M17" t="n">
-        <v>10.74</v>
+        <v>11.98</v>
       </c>
       <c r="N17" t="n">
-        <v>14.56</v>
+        <v>59.11</v>
       </c>
       <c r="O17" t="n">
-        <v>16.43</v>
+        <v>67</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.88</v>
+        <v>-7.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.4</v>
+        <v>63.92</v>
       </c>
       <c r="R17" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S17" t="n">
-        <v>51.3</v>
+        <v>47.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.26</v>
+        <v>-2.01</v>
       </c>
       <c r="V17" t="n">
         <v>53.3</v>
       </c>
       <c r="W17" t="n">
-        <v>4.8</v>
+        <v>5.64</v>
       </c>
       <c r="X17" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y17" t="n">
-        <v>590.26</v>
+        <v>2029.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>611.73</v>
+        <v>2012.41</v>
       </c>
       <c r="AA17" t="n">
-        <v>618.26</v>
+        <v>2122.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>579.75</v>
+        <v>2010.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>616.27</v>
+        <v>2112.87</v>
       </c>
       <c r="AD17" t="n">
-        <v>624.54</v>
+        <v>2119.74</v>
       </c>
       <c r="AE17" t="n">
-        <v>635.72</v>
+        <v>2133.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>60.8</v>
+        <v>45</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI17" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ17" t="n">
-        <v>88.5</v>
+        <v>34.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>-10.1</v>
+        <v>63</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.7</v>
+        <v>36.1</v>
       </c>
       <c r="AM17" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="AN17" t="n">
-        <v>642</v>
+        <v>2182.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>584.67</v>
+        <v>2035.08</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,572.27 Cr., a P/E ratio of 88.51, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,438.19 Cr., a P/E ratio of 34.25, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 45.03 (Consolidation Zone), while MACD Line (59.11) trades below Signal (67.00) with an expanding histogram (-7.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.98% above the 200-day DMA (₹1880.50). Daily volatility envelope is bounded by ATR(14) of ₹63.92.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹613.35) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,106.00) is positioned above the 30-day DMA (₹2,010.06), 50-day DMA (₹1,895.79), and 200-day DMA (₹1,880.50). The price distance from 200 DMA is +11.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[613.35, 615.19, 617.03, 618.87, 620.71, 622.55]</t>
+          <t>[2106.0, 2112.32, 2118.64, 2124.95, 2131.27, 2137.59]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[613.35, 624.15, 629.7, 634.39, 638.63, 642.59]</t>
+          <t>[2106.0, 2137.89, 2154.79, 2169.24, 2182.41, 2194.76]</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>[613.35, 608.47, 607.53, 607.23, 607.27, 607.52]</t>
+          <t>[2106.0, 2093.14, 2091.52, 2091.74, 2092.92, 2094.71]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63429.15</v>
+        <v>17608.09</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2105.7</v>
+        <v>614.6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹2092.64 - ₹2125.3</t>
+          <t>₹610.34 - ₹620.99</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2157.96</v>
+        <v>631.64</v>
       </c>
       <c r="I18" t="n">
-        <v>51</v>
+        <v>156</v>
       </c>
       <c r="J18" t="n">
-        <v>1999.45</v>
+        <v>579.77</v>
       </c>
       <c r="K18" t="n">
-        <v>1888.17</v>
+        <v>544.3099999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1880.41</v>
+        <v>553.6900000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>12.26</v>
+        <v>10.78</v>
       </c>
       <c r="N18" t="n">
-        <v>62.25</v>
+        <v>15.03</v>
       </c>
       <c r="O18" t="n">
-        <v>68.98</v>
+        <v>16.15</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.73</v>
+        <v>-1.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>65.31999999999999</v>
+        <v>21.3</v>
       </c>
       <c r="R18" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S18" t="n">
-        <v>43.2</v>
+        <v>53</v>
       </c>
       <c r="T18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.3</v>
+        <v>-2.02</v>
       </c>
       <c r="V18" t="n">
-        <v>51.7</v>
+        <v>55</v>
       </c>
       <c r="W18" t="n">
-        <v>4.49</v>
+        <v>4.79</v>
       </c>
       <c r="X18" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y18" t="n">
-        <v>2027.32</v>
+        <v>589.04</v>
       </c>
       <c r="Z18" t="n">
-        <v>2032.25</v>
+        <v>602.8099999999999</v>
       </c>
       <c r="AA18" t="n">
-        <v>2122.55</v>
+        <v>619.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>2007.72</v>
+        <v>582.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>2111.93</v>
+        <v>614.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>2127.76</v>
+        <v>617.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>2149.83</v>
+        <v>620.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>48.8</v>
+        <v>56.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI18" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34.2</v>
+        <v>88.7</v>
       </c>
       <c r="AK18" t="n">
-        <v>63</v>
+        <v>-10.1</v>
       </c>
       <c r="AL18" t="n">
-        <v>36.1</v>
+        <v>3.7</v>
       </c>
       <c r="AM18" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="AN18" t="n">
-        <v>2179.47</v>
+        <v>643.86</v>
       </c>
       <c r="AO18" t="n">
-        <v>2029.04</v>
+        <v>582.27</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,429.15 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,608.09 Cr., a P/E ratio of 88.69, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.93 (Bullish Momentum Zone), while MACD Line (15.03) trades below Signal (16.15) with an expanding histogram (-1.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹553.69). Daily volatility envelope is bounded by ATR(14) of ₹21.30.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,105.70) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹614.60) is positioned above the 30-day DMA (₹579.77), 50-day DMA (₹544.31), and 200-day DMA (₹553.69). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[2105.7, 2112.02, 2118.33, 2124.65, 2130.97, 2137.29]</t>
+          <t>[614.6, 616.44, 618.29, 620.13, 621.98, 623.82]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[2105.7, 2138.14, 2155.28, 2169.91, 2183.22, 2195.71]</t>
+          <t>[614.6, 624.96, 630.34, 634.89, 639.02, 642.87]</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>[2105.7, 2092.42, 2090.62, 2090.71, 2091.78, 2093.47]</t>
+          <t>[614.6, 610.05, 609.25, 609.06, 609.2, 609.53]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>46194.13</v>
+        <v>76643.06</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1135.3</v>
+        <v>1731.3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>₹1128.39 - ₹1145.67</t>
+          <t>₹1719.7 - ₹1748.7</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1162.95</v>
+        <v>1777.71</v>
       </c>
       <c r="I19" t="n">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="J19" t="n">
-        <v>1109.56</v>
+        <v>1511.17</v>
       </c>
       <c r="K19" t="n">
-        <v>1105.35</v>
+        <v>1475.45</v>
       </c>
       <c r="L19" t="n">
-        <v>1100.33</v>
+        <v>1504.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.87</v>
+        <v>14.12</v>
       </c>
       <c r="N19" t="n">
-        <v>9.130000000000001</v>
+        <v>60.69</v>
       </c>
       <c r="O19" t="n">
-        <v>4.71</v>
+        <v>36.2</v>
       </c>
       <c r="P19" t="n">
-        <v>4.42</v>
+        <v>24.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>34.56</v>
+        <v>58.01</v>
       </c>
       <c r="R19" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>48.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.41</v>
+        <v>-2.12</v>
       </c>
       <c r="V19" t="n">
-        <v>46.7</v>
+        <v>48.3</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>7.28</v>
       </c>
       <c r="X19" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1114</v>
+        <v>1722.01</v>
       </c>
       <c r="Z19" t="n">
-        <v>1153.74</v>
+        <v>1782.61</v>
       </c>
       <c r="AA19" t="n">
-        <v>1144.38</v>
+        <v>1747.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>1083.45</v>
+        <v>1644.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>1144.43</v>
+        <v>1735.13</v>
       </c>
       <c r="AD19" t="n">
-        <v>1156.86</v>
+        <v>1742.16</v>
       </c>
       <c r="AE19" t="n">
-        <v>1178.43</v>
+        <v>1753.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>52.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AG19" t="n">
         <v>0.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI19" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ19" t="n">
-        <v>37.7</v>
+        <v>35.4</v>
       </c>
       <c r="AK19" t="n">
-        <v>29.9</v>
+        <v>49.9</v>
       </c>
       <c r="AL19" t="n">
-        <v>26.5</v>
+        <v>9.6</v>
       </c>
       <c r="AM19" t="n">
         <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>1170.43</v>
+        <v>1798.17</v>
       </c>
       <c r="AO19" t="n">
-        <v>1102.69</v>
+        <v>1666.23</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,194.13 Cr., a P/E ratio of 37.73, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,643.06 Cr., a P/E ratio of 35.42, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.40 (Bullish Momentum Zone), while MACD Line (60.69) trades above Signal (36.20) with an expanding histogram (+24.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.12% above the 200-day DMA (₹1504.57). Daily volatility envelope is bounded by ATR(14) of ₹58.01.</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,135.30) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,731.30) is positioned above the 30-day DMA (₹1,511.17), 50-day DMA (₹1,475.45), and 200-day DMA (₹1,504.57). The price distance from 200 DMA is +14.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>[1135.3, 1138.71, 1142.11, 1145.52, 1148.92, 1152.33]</t>
+          <t>[1731.3, 1747.98, 1764.66, 1781.34, 1798.02, 1814.7]</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>[1135.3, 1152.53, 1161.66, 1169.46, 1176.58, 1183.24]</t>
+          <t>[1731.3, 1771.19, 1797.48, 1821.53, 1844.43, 1866.59]</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>[1135.3, 1128.34, 1127.45, 1127.56, 1128.19, 1129.14]</t>
+          <t>[1731.3, 1730.58, 1740.05, 1751.2, 1763.21, 1775.79]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>278417.14</v>
+        <v>46698.67</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -3684,312 +3684,479 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>302.45</v>
+        <v>1147.7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>₹300.39 - ₹305.53</t>
+          <t>₹1140.79 - ₹1158.06</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>310.68</v>
+        <v>1175.34</v>
       </c>
       <c r="I20" t="n">
-        <v>324</v>
+        <v>96</v>
       </c>
       <c r="J20" t="n">
-        <v>281.7</v>
+        <v>1109.24</v>
       </c>
       <c r="K20" t="n">
-        <v>268.93</v>
+        <v>1105.8</v>
       </c>
       <c r="L20" t="n">
-        <v>274.01</v>
+        <v>1100.59</v>
       </c>
       <c r="M20" t="n">
-        <v>13.37</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>9.93</v>
+        <v>9.49</v>
       </c>
       <c r="O20" t="n">
-        <v>8.42</v>
+        <v>5.67</v>
       </c>
       <c r="P20" t="n">
-        <v>1.51</v>
+        <v>3.82</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.28</v>
+        <v>34.55</v>
       </c>
       <c r="R20" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S20" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="T20" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.5</v>
+        <v>-2.18</v>
       </c>
       <c r="V20" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="W20" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="X20" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y20" t="n">
-        <v>299.26</v>
+        <v>1131.84</v>
       </c>
       <c r="Z20" t="n">
-        <v>309.85</v>
+        <v>1172.01</v>
       </c>
       <c r="AA20" t="n">
-        <v>304.87</v>
+        <v>1156.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>287.03</v>
+        <v>1095.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>306.75</v>
+        <v>1148.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>311.7</v>
+        <v>1152.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>320.95</v>
+        <v>1157.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>65.40000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI20" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>672.1</v>
+        <v>38.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>182</v>
+        <v>29.9</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.6</v>
+        <v>26.5</v>
       </c>
       <c r="AM20" t="n">
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>313.79</v>
+        <v>1183.56</v>
       </c>
       <c r="AO20" t="n">
-        <v>292.28</v>
+        <v>1112.16</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹278,417.14 Cr., a P/E ratio of 672.11, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,698.67 Cr., a P/E ratio of 38.14, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.63 (Consolidation Zone), while MACD Line (9.49) trades above Signal (5.67) with an expanding histogram (+3.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.15% above the 200-day DMA (₹1100.59). Daily volatility envelope is bounded by ATR(14) of ₹34.55.</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹302.45) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,147.70) is positioned above the 30-day DMA (₹1,109.24), 50-day DMA (₹1,105.80), and 200-day DMA (₹1,100.59). The price distance from 200 DMA is +3.15%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>[302.45, 303.8, 305.15, 306.5, 307.85, 309.19]</t>
+          <t>[1147.7, 1151.14, 1154.59, 1158.03, 1161.47, 1164.92]</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>[302.45, 307.91, 310.96, 313.62, 316.07, 318.39]</t>
+          <t>[1147.7, 1164.96, 1174.13, 1181.97, 1189.11, 1195.82]</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>[302.45, 300.71, 300.79, 301.15, 301.68, 302.3]</t>
+          <t>[1147.7, 1140.78, 1139.93, 1140.08, 1140.74, 1141.74]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>76187.09</v>
+        <v>280442.31</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1721</v>
+        <v>304.65</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>₹1709.13 - ₹1738.8</t>
+          <t>₹302.46 - ₹307.93</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1768.46</v>
+        <v>313.4</v>
       </c>
       <c r="I21" t="n">
-        <v>56</v>
+        <v>304</v>
       </c>
       <c r="J21" t="n">
-        <v>1505.99</v>
+        <v>282.98</v>
       </c>
       <c r="K21" t="n">
-        <v>1472.15</v>
+        <v>270.14</v>
       </c>
       <c r="L21" t="n">
-        <v>1507.99</v>
+        <v>273.78</v>
       </c>
       <c r="M21" t="n">
-        <v>15.58</v>
+        <v>10.47</v>
       </c>
       <c r="N21" t="n">
-        <v>53.48</v>
+        <v>9.73</v>
       </c>
       <c r="O21" t="n">
-        <v>30.14</v>
+        <v>8.68</v>
       </c>
       <c r="P21" t="n">
-        <v>23.34</v>
+        <v>1.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.33</v>
+        <v>10.94</v>
       </c>
       <c r="R21" t="n">
-        <v>11.76</v>
+        <v>11.86</v>
       </c>
       <c r="S21" t="n">
-        <v>41.1</v>
+        <v>48.8</v>
       </c>
       <c r="T21" t="n">
         <v>0.15</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.72</v>
+        <v>-2.37</v>
       </c>
       <c r="V21" t="n">
-        <v>48.3</v>
+        <v>51.7</v>
       </c>
       <c r="W21" t="n">
-        <v>7.48</v>
+        <v>2.33</v>
       </c>
       <c r="X21" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>1705.12</v>
+        <v>299.48</v>
       </c>
       <c r="Z21" t="n">
-        <v>1765.36</v>
+        <v>310.14</v>
       </c>
       <c r="AA21" t="n">
-        <v>1734.77</v>
+        <v>307.09</v>
       </c>
       <c r="AB21" t="n">
-        <v>1632.01</v>
+        <v>288.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>1713.83</v>
+        <v>304.27</v>
       </c>
       <c r="AD21" t="n">
-        <v>1745.96</v>
+        <v>305.54</v>
       </c>
       <c r="AE21" t="n">
-        <v>1770.93</v>
+        <v>306.42</v>
       </c>
       <c r="AF21" t="n">
-        <v>77.3</v>
+        <v>62</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI21" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>35.2</v>
+        <v>677</v>
       </c>
       <c r="AK21" t="n">
-        <v>49.9</v>
+        <v>182</v>
       </c>
       <c r="AL21" t="n">
-        <v>9.6</v>
+        <v>0.6</v>
       </c>
       <c r="AM21" t="n">
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>1787.2</v>
+        <v>315.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>1652.75</v>
+        <v>294.19</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,187.09 Cr., a P/E ratio of 35.21, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹280,442.31 Cr., a P/E ratio of 677.00, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.48) trades above Signal (30.14) with an expanding histogram (+23.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1507.99). Daily volatility envelope is bounded by ATR(14) of ₹59.33.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.99 (Bullish Momentum Zone), while MACD Line (9.73) trades above Signal (8.68) with an expanding histogram (+1.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.47% above the 200-day DMA (₹273.78). Daily volatility envelope is bounded by ATR(14) of ₹10.94.</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,721.00) is positioned above the 30-day DMA (₹1,505.99), 50-day DMA (₹1,472.15), and 200-day DMA (₹1,507.99). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹304.65) is positioned above the 30-day DMA (₹282.98), 50-day DMA (₹270.14), and 200-day DMA (₹273.78). The price distance from 200 DMA is +10.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>[1721.0, 1730.94, 1740.87, 1750.81, 1760.74, 1770.68]</t>
+          <t>[304.65, 305.56, 306.48, 307.39, 308.31, 309.22]</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[1721.0, 1754.67, 1774.43, 1791.91, 1808.21, 1823.74]</t>
+          <t>[304.65, 309.94, 312.66, 314.97, 317.05, 319.0]</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>[1721.0, 1713.14, 1715.7, 1719.98, 1725.15, 1730.88]</t>
+          <t>[304.65, 302.28, 301.84, 301.71, 301.74, 301.88]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>82739.21000000001</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>13608</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>₹13515.67 - ₹13746.49</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>13977.31</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13241.63</v>
+      </c>
+      <c r="K22" t="n">
+        <v>12652.22</v>
+      </c>
+      <c r="L22" t="n">
+        <v>12318.23</v>
+      </c>
+      <c r="M22" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>450.74</v>
+      </c>
+      <c r="O22" t="n">
+        <v>493.22</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-42.48</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>461.64</v>
+      </c>
+      <c r="R22" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="S22" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="V22" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>13054.03</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>13375.37</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>13716.86</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12915.54</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>13694.33</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>13788.66</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>13969.33</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (11.86) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>14142.33</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>13095.48</v>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹82,739.21 Cr., a P/E ratio of 39.86, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.38 (Bullish Momentum Zone), while MACD Line (450.74) trades below Signal (493.22) with an expanding histogram (-42.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.05% above the 200-day DMA (₹12318.23). Daily volatility envelope is bounded by ATR(14) of ₹461.64.</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,608.00) is positioned above the 30-day DMA (₹13,241.63), 50-day DMA (₹12,652.22), and 200-day DMA (₹12,318.23). The price distance from 200 DMA is +14.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>[13608.0, 13648.82, 13689.65, 13730.47, 13771.3, 13812.12]</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>[13608.0, 13833.48, 13950.79, 14050.31, 14140.61, 14225.03]</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>[13608.0, 13510.33, 13493.79, 13490.6, 13494.31, 13502.44]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU22"/>
+  <dimension ref="A1:AU21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1030297.85</v>
+        <v>1036968.89</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,15 +678,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1436.3</v>
+        <v>1445.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹1431.73 - ₹1443.16</t>
+          <t>₹1441.03 - ₹1452.46</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1454.6</v>
+        <v>1463.9</v>
       </c>
       <c r="I2" t="n">
         <v>145</v>
@@ -716,46 +716,46 @@
         <v>22.87</v>
       </c>
       <c r="R2" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S2" t="n">
-        <v>54.4</v>
+        <v>54.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="V2" t="n">
         <v>60</v>
       </c>
       <c r="W2" t="n">
-        <v>6.33</v>
+        <v>6.34</v>
       </c>
       <c r="X2" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y2" t="n">
-        <v>1417.46</v>
+        <v>1427.64</v>
       </c>
       <c r="Z2" t="n">
-        <v>1467.73</v>
+        <v>1478.24</v>
       </c>
       <c r="AA2" t="n">
-        <v>1447.79</v>
+        <v>1457.16</v>
       </c>
       <c r="AB2" t="n">
-        <v>1401.99</v>
+        <v>1411.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>1437.83</v>
+        <v>1442.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1441.46</v>
+        <v>1452.66</v>
       </c>
       <c r="AE2" t="n">
-        <v>1446.63</v>
+        <v>1459.73</v>
       </c>
       <c r="AF2" t="n">
         <v>60.1</v>
@@ -765,14 +765,14 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI2" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AK2" t="n">
         <v>11.4</v>
@@ -784,14 +784,14 @@
         <v>16.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1463.42</v>
+        <v>1470.66</v>
       </c>
       <c r="AO2" t="n">
-        <v>1409.75</v>
+        <v>1419.05</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,030,297.85 Cr., a P/E ratio of 18.56, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
+          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,036,968.89 Cr., a P/E ratio of 18.68, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -801,22 +801,22 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,436.30) is positioned above the 30-day DMA (₹1,398.49), 50-day DMA (₹1,349.96), and 200-day DMA (₹1,337.12). The price distance from 200 DMA is +6.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,445.60) is positioned above the 30-day DMA (₹1,398.49), 50-day DMA (₹1,349.96), and 200-day DMA (₹1,337.12). The price distance from 200 DMA is +6.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[1436.3, 1440.61, 1444.92, 1449.23, 1453.54, 1457.84]</t>
+          <t>[1445.6, 1449.94, 1454.27, 1458.61, 1462.95, 1467.28]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[1436.3, 1449.76, 1457.86, 1465.07, 1471.83, 1478.3]</t>
+          <t>[1445.6, 1459.09, 1467.21, 1474.46, 1481.24, 1487.74]</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>[1436.3, 1433.75, 1435.21, 1437.34, 1439.81, 1442.5]</t>
+          <t>[1445.6, 1443.08, 1444.57, 1446.73, 1449.22, 1451.94]</t>
         </is>
       </c>
     </row>
@@ -837,23 +837,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>130456.39</v>
+        <v>130962.08</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🟢 HIGH CONVICTION BUY</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>113.51</v>
+        <v>113.95</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹113.11 - ₹114.11</t>
+          <t>₹113.55 - ₹114.55</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>115.11</v>
+        <v>115.55</v>
       </c>
       <c r="I3" t="n">
         <v>1670</v>
@@ -883,46 +883,46 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S3" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
       <c r="T3" t="n">
         <v>0.3</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.82</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>53.3</v>
       </c>
       <c r="W3" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="X3" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>111.19</v>
+        <v>111.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>115.16</v>
+        <v>115.69</v>
       </c>
       <c r="AA3" t="n">
-        <v>114.42</v>
+        <v>114.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>110.52</v>
+        <v>110.96</v>
       </c>
       <c r="AC3" t="n">
-        <v>113.42</v>
+        <v>113.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>113.83</v>
+        <v>114.72</v>
       </c>
       <c r="AE3" t="n">
-        <v>114.16</v>
+        <v>115.5</v>
       </c>
       <c r="AF3" t="n">
         <v>71.2</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI3" t="n">
@@ -951,14 +951,14 @@
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>116.81</v>
+        <v>117.13</v>
       </c>
       <c r="AO3" t="n">
-        <v>110.49</v>
+        <v>110.81</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,456.39 Cr., a P/E ratio of 5.91, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,962.08 Cr., a P/E ratio of 5.93, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -968,22 +968,22 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.51) is positioned above the 30-day DMA (₹107.80), 50-day DMA (₹106.57), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.07%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.95) is positioned above the 30-day DMA (₹107.80), 50-day DMA (₹106.57), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.07%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[113.51, 113.85, 114.19, 114.53, 114.87, 115.21]</t>
+          <t>[113.95, 114.29, 114.63, 114.98, 115.32, 115.66]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[113.51, 114.65, 115.32, 115.91, 116.47, 117.0]</t>
+          <t>[113.95, 115.09, 115.76, 116.36, 116.91, 117.44]</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>[113.51, 113.25, 113.34, 113.49, 113.67, 113.87]</t>
+          <t>[113.95, 113.69, 113.79, 113.94, 114.12, 114.32]</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>352591.73</v>
+        <v>352003.37</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,48 +1012,48 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11986</v>
+        <v>11966</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹11941.83 - ₹12052.25</t>
+          <t>₹11922.37 - ₹12031.45</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12162.68</v>
+        <v>12140.53</v>
       </c>
       <c r="I4" t="n">
         <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>11446.68</v>
+        <v>11421.23</v>
       </c>
       <c r="K4" t="n">
-        <v>11281.17</v>
+        <v>11269.86</v>
       </c>
       <c r="L4" t="n">
-        <v>11569.56</v>
+        <v>11569.69</v>
       </c>
       <c r="M4" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="N4" t="n">
-        <v>152.76</v>
+        <v>143.27</v>
       </c>
       <c r="O4" t="n">
-        <v>129.95</v>
+        <v>124.24</v>
       </c>
       <c r="P4" t="n">
-        <v>22.81</v>
+        <v>19.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>220.85</v>
+        <v>218.17</v>
       </c>
       <c r="R4" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S4" t="n">
-        <v>51.2</v>
+        <v>50.7</v>
       </c>
       <c r="T4" t="n">
         <v>0.29</v>
@@ -1062,51 +1062,51 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="W4" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="X4" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>11868.19</v>
+        <v>11818.79</v>
       </c>
       <c r="Z4" t="n">
-        <v>12287.7</v>
+        <v>12237.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>12081.89</v>
+        <v>12061.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>11654.73</v>
+        <v>11638.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>11965.67</v>
+        <v>11957</v>
       </c>
       <c r="AD4" t="n">
-        <v>12006.34</v>
+        <v>12009</v>
       </c>
       <c r="AE4" t="n">
-        <v>12026.67</v>
+        <v>12052</v>
       </c>
       <c r="AF4" t="n">
-        <v>70.2</v>
+        <v>62.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI4" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="AK4" t="n">
         <v>15.9</v>
@@ -1118,39 +1118,39 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>12268.82</v>
+        <v>12244.52</v>
       </c>
       <c r="AO4" t="n">
-        <v>11705</v>
+        <v>11679.97</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹352,591.73 Cr., a P/E ratio of 41.27, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹352,003.37 Cr., a P/E ratio of 41.20, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.23 (Bullish Momentum Zone), while MACD Line (152.76) trades above Signal (129.95) with an expanding histogram (+22.81). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.88% above the 200-day DMA (₹11569.56). Daily volatility envelope is bounded by ATR(14) of ₹220.85.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (143.27) trades above Signal (124.24) with an expanding histogram (+19.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.40% above the 200-day DMA (₹11569.69). Daily volatility envelope is bounded by ATR(14) of ₹218.17.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,986.00) is positioned above the 30-day DMA (₹11,446.68), 50-day DMA (₹11,281.17), and 200-day DMA (₹11,569.56). The price distance from 200 DMA is +2.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,966.00) is positioned above the 30-day DMA (₹11,421.23), 50-day DMA (₹11,269.86), and 200-day DMA (₹11,569.69). The price distance from 200 DMA is +2.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[11986.0, 12047.98, 12109.95, 12171.93, 12233.91, 12295.88]</t>
+          <t>[11966.0, 12001.9, 12037.8, 12073.69, 12109.59, 12145.49]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[11986.0, 12136.31, 12234.88, 12324.94, 12410.58, 12493.41]</t>
+          <t>[11966.0, 12089.16, 12161.21, 12224.84, 12284.13, 12340.62]</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>[11986.0, 11981.72, 12016.26, 12057.17, 12101.4, 12147.73]</t>
+          <t>[11966.0, 11936.45, 11945.24, 11960.33, 11978.69, 11999.14]</t>
         </is>
       </c>
     </row>
@@ -1162,162 +1162,162 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>266253.87</v>
+        <v>220660.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2775.9</v>
+        <v>8038</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹2764.36 - ₹2793.21</t>
+          <t>₹8007.88 - ₹8083.18</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2822.07</v>
+        <v>8158.49</v>
       </c>
       <c r="I5" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="J5" t="n">
-        <v>2689.12</v>
+        <v>7447.86</v>
       </c>
       <c r="K5" t="n">
-        <v>2681.37</v>
+        <v>7362.95</v>
       </c>
       <c r="L5" t="n">
-        <v>2572.85</v>
+        <v>7176.17</v>
       </c>
       <c r="M5" t="n">
-        <v>6.78</v>
+        <v>9.16</v>
       </c>
       <c r="N5" t="n">
-        <v>18.17</v>
+        <v>130.62</v>
       </c>
       <c r="O5" t="n">
-        <v>11.71</v>
+        <v>94.11</v>
       </c>
       <c r="P5" t="n">
-        <v>6.46</v>
+        <v>36.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.71</v>
+        <v>150.61</v>
       </c>
       <c r="R5" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S5" t="n">
-        <v>54.6</v>
+        <v>51.1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.95</v>
+        <v>-0.97</v>
       </c>
       <c r="V5" t="n">
-        <v>56.7</v>
+        <v>50</v>
       </c>
       <c r="W5" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>2757.81</v>
+        <v>7909.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>2854.97</v>
+        <v>8191.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2799.45</v>
+        <v>8102.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>2689.33</v>
+        <v>7812.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>2773.07</v>
+        <v>7982</v>
       </c>
       <c r="AD5" t="n">
-        <v>2782.84</v>
+        <v>8112</v>
       </c>
       <c r="AE5" t="n">
-        <v>2789.77</v>
+        <v>8186</v>
       </c>
       <c r="AF5" t="n">
-        <v>68.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.03</v>
+        <v>0.16</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI5" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ5" t="n">
-        <v>55.8</v>
+        <v>38.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.9</v>
+        <v>31.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>12.8</v>
+        <v>23.2</v>
       </c>
       <c r="AM5" t="n">
         <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>2850</v>
+        <v>8270.43</v>
       </c>
       <c r="AO5" t="n">
-        <v>2717.54</v>
+        <v>7843.91</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹266,253.87 Cr., a P/E ratio of 55.85, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹220,660.55 Cr., a P/E ratio of 38.29, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 68.92 (Bullish Momentum Zone), while MACD Line (18.17) trades above Signal (11.71) with an expanding histogram (+6.46). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.78% above the 200-day DMA (₹2572.85). Daily volatility envelope is bounded by ATR(14) of ₹57.71.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.95 (Bullish Momentum Zone), while MACD Line (130.62) trades above Signal (94.11) with an expanding histogram (+36.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.16% above the 200-day DMA (₹7176.17). Daily volatility envelope is bounded by ATR(14) of ₹150.61.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,775.90) is positioned above the 30-day DMA (₹2,689.12), 50-day DMA (₹2,681.37), and 200-day DMA (₹2,572.85). The price distance from 200 DMA is +6.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹8,038.00) is positioned above the 30-day DMA (₹7,447.86), 50-day DMA (₹7,362.95), and 200-day DMA (₹7,176.17). The price distance from 200 DMA is +9.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[2775.9, 2799.45, 2823.0, 2846.55, 2870.11, 2893.66]</t>
+          <t>[8038.0, 8062.11, 8086.23, 8110.34, 8134.46, 8158.57]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[2775.9, 2822.54, 2855.65, 2886.54, 2916.28, 2945.28]</t>
+          <t>[8038.0, 8122.36, 8171.43, 8214.69, 8254.94, 8293.28]</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>[2775.9, 2782.14, 2798.52, 2816.57, 2835.48, 2854.94]</t>
+          <t>[8038.0, 8016.93, 8022.33, 8032.08, 8044.09, 8057.54]</t>
         </is>
       </c>
     </row>
@@ -1329,162 +1329,162 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>215856.41</v>
+        <v>265899.16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🟢 HIGH CONVICTION BUY</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7857</v>
+        <v>2773.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹7826.88 - ₹7902.18</t>
+          <t>₹2762.16 - ₹2791.01</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7977.49</v>
+        <v>2819.87</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J6" t="n">
-        <v>7447.86</v>
+        <v>2689.12</v>
       </c>
       <c r="K6" t="n">
-        <v>7362.95</v>
+        <v>2681.37</v>
       </c>
       <c r="L6" t="n">
-        <v>7176.17</v>
+        <v>2572.85</v>
       </c>
       <c r="M6" t="n">
-        <v>9.16</v>
+        <v>6.78</v>
       </c>
       <c r="N6" t="n">
-        <v>130.62</v>
+        <v>18.17</v>
       </c>
       <c r="O6" t="n">
-        <v>94.11</v>
+        <v>11.71</v>
       </c>
       <c r="P6" t="n">
-        <v>36.5</v>
+        <v>6.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>150.61</v>
+        <v>57.71</v>
       </c>
       <c r="R6" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S6" t="n">
-        <v>51.1</v>
+        <v>53.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="U6" t="n">
-        <v>-1</v>
+        <v>-0.99</v>
       </c>
       <c r="V6" t="n">
-        <v>50</v>
+        <v>56.7</v>
       </c>
       <c r="W6" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="X6" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>7705.55</v>
+        <v>2755.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>7980.54</v>
+        <v>2852.32</v>
       </c>
       <c r="AA6" t="n">
-        <v>7919.86</v>
+        <v>2796.84</v>
       </c>
       <c r="AB6" t="n">
-        <v>7631.09</v>
+        <v>2687.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>7877.5</v>
+        <v>2775.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>7899</v>
+        <v>2787.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>7941</v>
+        <v>2801.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>79</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI6" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37.5</v>
+        <v>55.8</v>
       </c>
       <c r="AK6" t="n">
-        <v>31.5</v>
+        <v>17.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>23.2</v>
+        <v>12.8</v>
       </c>
       <c r="AM6" t="n">
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>8053.83</v>
+        <v>2841.27</v>
       </c>
       <c r="AO6" t="n">
-        <v>7674.73</v>
+        <v>2705.45</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹215,856.41 Cr., a P/E ratio of 37.45, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹265,899.16 Cr., a P/E ratio of 55.78, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.95 (Bullish Momentum Zone), while MACD Line (130.62) trades above Signal (94.11) with an expanding histogram (+36.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.16% above the 200-day DMA (₹7176.17). Daily volatility envelope is bounded by ATR(14) of ₹150.61.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 68.92 (Bullish Momentum Zone), while MACD Line (18.17) trades above Signal (11.71) with an expanding histogram (+6.46). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.78% above the 200-day DMA (₹2572.85). Daily volatility envelope is bounded by ATR(14) of ₹57.71.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,857.00) is positioned above the 30-day DMA (₹7,447.86), 50-day DMA (₹7,362.95), and 200-day DMA (₹7,176.17). The price distance from 200 DMA is +9.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,773.70) is positioned above the 30-day DMA (₹2,689.12), 50-day DMA (₹2,681.37), and 200-day DMA (₹2,572.85). The price distance from 200 DMA is +6.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[7857.0, 7880.57, 7904.14, 7927.71, 7951.28, 7974.85]</t>
+          <t>[2773.7, 2796.84, 2819.98, 2843.12, 2866.27, 2889.41]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[7857.0, 7940.81, 7989.34, 8032.06, 8071.77, 8109.56]</t>
+          <t>[2773.7, 2819.93, 2852.63, 2883.11, 2912.44, 2941.03]</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>[7857.0, 7835.39, 7840.24, 7849.45, 7860.92, 7873.82]</t>
+          <t>[2773.7, 2779.53, 2795.5, 2813.13, 2831.64, 2850.69]</t>
         </is>
       </c>
     </row>
@@ -1513,15 +1513,15 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>376.5</v>
+        <v>373</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹374.98 - ₹378.78</t>
+          <t>₹371.48 - ₹375.28</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>382.59</v>
+        <v>379.09</v>
       </c>
       <c r="I7" t="n">
         <v>437</v>
@@ -1551,10 +1551,10 @@
         <v>7.61</v>
       </c>
       <c r="R7" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S7" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="T7" t="n">
         <v>0.26</v>
@@ -1566,31 +1566,31 @@
         <v>51.7</v>
       </c>
       <c r="W7" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="X7" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>367.37</v>
+        <v>363.87</v>
       </c>
       <c r="Z7" t="n">
-        <v>378.22</v>
+        <v>374.26</v>
       </c>
       <c r="AA7" t="n">
-        <v>379.51</v>
+        <v>375.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>365.08</v>
+        <v>361.58</v>
       </c>
       <c r="AC7" t="n">
-        <v>375.45</v>
+        <v>373.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>377.55</v>
+        <v>376.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>378.6</v>
+        <v>379.13</v>
       </c>
       <c r="AF7" t="n">
         <v>81.2</v>
@@ -1600,14 +1600,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI7" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AK7" t="n">
         <v>25.2</v>
@@ -1619,14 +1619,14 @@
         <v>15</v>
       </c>
       <c r="AN7" t="n">
-        <v>386.53</v>
+        <v>383.03</v>
       </c>
       <c r="AO7" t="n">
-        <v>366.51</v>
+        <v>363.66</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.20, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1636,22 +1636,22 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹376.50) is positioned above the 30-day DMA (₹357.93), 50-day DMA (₹350.57), and 200-day DMA (₹347.65). The price distance from 200 DMA is +7.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹373.00) is positioned above the 30-day DMA (₹357.93), 50-day DMA (₹350.57), and 200-day DMA (₹347.65). The price distance from 200 DMA is +7.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[376.5, 377.63, 378.76, 379.89, 381.02, 382.15]</t>
+          <t>[373.0, 374.12, 375.24, 376.36, 377.48, 378.59]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[376.5, 380.67, 383.07, 385.16, 387.11, 388.96]</t>
+          <t>[373.0, 377.16, 379.54, 381.63, 383.57, 385.4]</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>[376.5, 375.35, 375.53, 375.93, 376.45, 377.04]</t>
+          <t>[373.0, 371.84, 372.01, 372.4, 372.91, 373.49]</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105696.96</v>
+        <v>105938.94</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,15 +1680,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>742.55</v>
+        <v>744.25</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹739.53 - ₹747.08</t>
+          <t>₹741.23 - ₹748.78</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>754.63</v>
+        <v>756.33</v>
       </c>
       <c r="I8" t="n">
         <v>220</v>
@@ -1718,10 +1718,10 @@
         <v>15.1</v>
       </c>
       <c r="R8" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S8" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="T8" t="n">
         <v>0.26</v>
@@ -1733,31 +1733,31 @@
         <v>56.7</v>
       </c>
       <c r="W8" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
       <c r="X8" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>724.4299999999999</v>
+        <v>726.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>736.91</v>
+        <v>738.8200000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>748.49</v>
+        <v>750.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>719.9</v>
+        <v>721.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>742.17</v>
+        <v>743.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>744.34</v>
+        <v>747.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>746.12</v>
+        <v>750.35</v>
       </c>
       <c r="AF8" t="n">
         <v>50</v>
@@ -1767,14 +1767,14 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI8" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="AK8" t="n">
         <v>15.1</v>
@@ -1786,14 +1786,14 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>762.51</v>
+        <v>762.84</v>
       </c>
       <c r="AO8" t="n">
-        <v>724.41</v>
+        <v>724.5599999999999</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,696.96 Cr., a P/E ratio of 49.27, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,938.94 Cr., a P/E ratio of 49.39, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1803,22 +1803,22 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹742.55) is positioned above the 30-day DMA (₹730.08), 50-day DMA (₹705.51), and 200-day DMA (₹686.16). The price distance from 200 DMA is +7.63%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹744.25) is positioned above the 30-day DMA (₹730.08), 50-day DMA (₹705.51), and 200-day DMA (₹686.16). The price distance from 200 DMA is +7.63%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[742.55, 744.78, 747.01, 749.23, 751.46, 753.69]</t>
+          <t>[744.25, 746.48, 748.72, 750.95, 753.18, 755.41]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[742.55, 750.82, 755.55, 759.69, 763.54, 767.19]</t>
+          <t>[744.25, 752.52, 757.26, 761.41, 765.26, 768.92]</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>[742.55, 740.25, 740.6, 741.39, 742.4, 743.56]</t>
+          <t>[744.25, 741.95, 742.31, 743.1, 744.12, 745.28]</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>108208.54</v>
+        <v>107751.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,15 +1847,15 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1111.8</v>
+        <v>1107.6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹1107.05 - ₹1118.93</t>
+          <t>₹1102.85 - ₹1114.73</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1130.82</v>
+        <v>1126.62</v>
       </c>
       <c r="I9" t="n">
         <v>140</v>
@@ -1885,16 +1885,16 @@
         <v>23.77</v>
       </c>
       <c r="R9" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S9" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="T9" t="n">
         <v>0.25</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.15</v>
+        <v>-1.16</v>
       </c>
       <c r="V9" t="n">
         <v>55</v>
@@ -1906,25 +1906,25 @@
         <v>-0.77</v>
       </c>
       <c r="Y9" t="n">
-        <v>1083.27</v>
+        <v>1079.07</v>
       </c>
       <c r="Z9" t="n">
-        <v>1090.79</v>
+        <v>1086.23</v>
       </c>
       <c r="AA9" t="n">
-        <v>1120.69</v>
+        <v>1116.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>1076.14</v>
+        <v>1071.94</v>
       </c>
       <c r="AC9" t="n">
-        <v>1111.17</v>
+        <v>1107.07</v>
       </c>
       <c r="AD9" t="n">
-        <v>1114.44</v>
+        <v>1114.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>1117.07</v>
+        <v>1121.07</v>
       </c>
       <c r="AF9" t="n">
         <v>47.7</v>
@@ -1934,14 +1934,14 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI9" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75.5</v>
+        <v>75.2</v>
       </c>
       <c r="AK9" t="n">
         <v>12.2</v>
@@ -1953,14 +1953,14 @@
         <v>14.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>1142.26</v>
+        <v>1139.12</v>
       </c>
       <c r="AO9" t="n">
-        <v>1081.35</v>
+        <v>1081.07</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>MAXHEALTH operates in the Healthcare sector. With an estimated Market Cap of ₹108,208.54 Cr., a P/E ratio of 75.53, and YoY Revenue Growth of +12.2%, the company demonstrates strong institutional backing, solid operating profit margins (17.23%), and healthy Return on Equity (14.33%).</t>
+          <t>MAXHEALTH operates in the Healthcare sector. With an estimated Market Cap of ₹107,751.10 Cr., a P/E ratio of 75.21, and YoY Revenue Growth of +12.2%, the company demonstrates strong institutional backing, solid operating profit margins (17.23%), and healthy Return on Equity (14.33%).</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -1970,22 +1970,22 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MAXHEALTH. Current Market Price (₹1,111.80) is positioned above the 30-day DMA (₹1,107.37), 50-day DMA (₹1,064.71), and 200-day DMA (₹1,056.34). The price distance from 200 DMA is +3.99%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MAXHEALTH. Current Market Price (₹1,107.60) is positioned above the 30-day DMA (₹1,107.37), 50-day DMA (₹1,064.71), and 200-day DMA (₹1,056.34). The price distance from 200 DMA is +3.99%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[1111.8, 1115.14, 1118.47, 1121.81, 1125.14, 1128.48]</t>
+          <t>[1107.6, 1110.92, 1114.25, 1117.57, 1120.89, 1124.21]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[1111.8, 1124.64, 1131.92, 1138.28, 1144.16, 1149.74]</t>
+          <t>[1107.6, 1120.43, 1127.69, 1134.04, 1139.91, 1145.48]</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>[1111.8, 1108.0, 1108.39, 1109.45, 1110.88, 1112.53]</t>
+          <t>[1107.6, 1103.79, 1104.16, 1105.22, 1106.63, 1108.27]</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68421.07000000001</v>
+        <v>68259.66</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2014,15 +2014,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5722.5</v>
+        <v>5709</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹5698.55 - ₹5758.43</t>
+          <t>₹5685.05 - ₹5744.93</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5818.3</v>
+        <v>5804.8</v>
       </c>
       <c r="I10" t="n">
         <v>27</v>
@@ -2052,7 +2052,7 @@
         <v>119.75</v>
       </c>
       <c r="R10" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S10" t="n">
         <v>49.7</v>
@@ -2061,37 +2061,37 @@
         <v>0.25</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.18</v>
+        <v>-1.19</v>
       </c>
       <c r="V10" t="n">
         <v>51.7</v>
       </c>
       <c r="W10" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="X10" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>5612.76</v>
+        <v>5597.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>5813.04</v>
+        <v>5796.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>5768.28</v>
+        <v>5754.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>5542.88</v>
+        <v>5529.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>5739.83</v>
+        <v>5718</v>
       </c>
       <c r="AD10" t="n">
-        <v>5757.16</v>
+        <v>5765.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>5791.83</v>
+        <v>5822</v>
       </c>
       <c r="AF10" t="n">
         <v>61</v>
@@ -2101,14 +2101,14 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI10" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="AK10" t="n">
         <v>14.6</v>
@@ -2120,14 +2120,14 @@
         <v>17.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>5845.03</v>
+        <v>5835.96</v>
       </c>
       <c r="AO10" t="n">
-        <v>5589.4</v>
+        <v>5588.12</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,421.07 Cr., a P/E ratio of 29.70, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,259.66 Cr., a P/E ratio of 29.63, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,722.50) is positioned above the 30-day DMA (₹5,587.60), 50-day DMA (₹5,491.02), and 200-day DMA (₹5,522.76). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,709.00) is positioned above the 30-day DMA (₹5,587.60), 50-day DMA (₹5,491.02), and 200-day DMA (₹5,522.76). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[5722.5, 5739.67, 5756.84, 5774.0, 5791.17, 5808.34]</t>
+          <t>[5709.0, 5726.13, 5743.25, 5760.38, 5777.51, 5794.63]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[5722.5, 5787.57, 5824.58, 5856.97, 5886.97, 5915.45]</t>
+          <t>[5709.0, 5774.03, 5810.99, 5843.35, 5873.31, 5901.74]</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>[5722.5, 5703.74, 5706.03, 5711.78, 5719.32, 5728.01]</t>
+          <t>[5709.0, 5690.2, 5692.45, 5698.16, 5705.66, 5714.3]</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>312919.8</v>
+        <v>311782.91</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2181,15 +2181,15 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4679</v>
+        <v>4662</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹4662.29 - ₹4704.06</t>
+          <t>₹4645.29 - ₹4687.06</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4745.82</v>
+        <v>4728.82</v>
       </c>
       <c r="I11" t="n">
         <v>39</v>
@@ -2219,46 +2219,46 @@
         <v>83.53</v>
       </c>
       <c r="R11" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S11" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
       <c r="T11" t="n">
         <v>0.3</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.19</v>
+        <v>-1.21</v>
       </c>
       <c r="V11" t="n">
         <v>43.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="X11" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>4578.77</v>
+        <v>4561.77</v>
       </c>
       <c r="Z11" t="n">
-        <v>4740.7</v>
+        <v>4720.59</v>
       </c>
       <c r="AA11" t="n">
-        <v>4716.43</v>
+        <v>4699.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>4553.71</v>
+        <v>4536.71</v>
       </c>
       <c r="AC11" t="n">
-        <v>4675.37</v>
+        <v>4666.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>4690.34</v>
+        <v>4684.84</v>
       </c>
       <c r="AE11" t="n">
-        <v>4701.67</v>
+        <v>4707.67</v>
       </c>
       <c r="AF11" t="n">
         <v>64.59999999999999</v>
@@ -2268,14 +2268,14 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI11" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="AK11" t="n">
         <v>1.8</v>
@@ -2287,14 +2287,14 @@
         <v>24</v>
       </c>
       <c r="AN11" t="n">
-        <v>4800.74</v>
+        <v>4789.62</v>
       </c>
       <c r="AO11" t="n">
-        <v>4550.75</v>
+        <v>4536.31</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹312,919.80 Cr., a P/E ratio of 34.37, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹311,782.91 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2304,22 +2304,22 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,679.00) is positioned above the 30-day DMA (₹4,479.85), 50-day DMA (₹4,409.79), and 200-day DMA (₹4,345.73). The price distance from 200 DMA is +6.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,662.00) is positioned above the 30-day DMA (₹4,479.85), 50-day DMA (₹4,409.79), and 200-day DMA (₹4,345.73). The price distance from 200 DMA is +6.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[4679.0, 4693.04, 4707.07, 4721.11, 4735.15, 4749.18]</t>
+          <t>[4662.0, 4675.99, 4689.97, 4703.96, 4717.94, 4731.93]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[4679.0, 4726.45, 4754.32, 4778.98, 4801.97, 4823.9]</t>
+          <t>[4662.0, 4709.4, 4737.22, 4761.83, 4784.77, 4806.64]</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>[4679.0, 4667.98, 4671.64, 4677.71, 4685.03, 4693.15]</t>
+          <t>[4662.0, 4650.93, 4654.53, 4660.56, 4667.83, 4675.9]</t>
         </is>
       </c>
     </row>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>105767.55</v>
+        <v>138010.94</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2348,145 +2348,145 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2212.3</v>
+        <v>3875.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹2202.84 - ₹2226.49</t>
+          <t>₹3854.67 - ₹3906.5</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2250.15</v>
+        <v>3958.34</v>
       </c>
       <c r="I12" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="J12" t="n">
-        <v>2146.11</v>
+        <v>3594.93</v>
       </c>
       <c r="K12" t="n">
-        <v>2067.23</v>
+        <v>3627.18</v>
       </c>
       <c r="L12" t="n">
-        <v>1708.73</v>
+        <v>3333.67</v>
       </c>
       <c r="M12" t="n">
-        <v>28.74</v>
+        <v>12.79</v>
       </c>
       <c r="N12" t="n">
-        <v>30.53</v>
+        <v>30.14</v>
       </c>
       <c r="O12" t="n">
-        <v>34.42</v>
+        <v>14.1</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.9</v>
+        <v>16.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>47.31</v>
+        <v>103.67</v>
       </c>
       <c r="R12" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S12" t="n">
-        <v>49.5</v>
+        <v>52.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.22</v>
+        <v>-1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>51.7</v>
+        <v>55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.76</v>
+        <v>2.51</v>
       </c>
       <c r="X12" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>2184.36</v>
+        <v>3827.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>2261.79</v>
+        <v>3963.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>2230</v>
+        <v>3906.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2141.34</v>
+        <v>3719.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>2212.13</v>
+        <v>3818.53</v>
       </c>
       <c r="AD12" t="n">
-        <v>2218.16</v>
+        <v>3942.86</v>
       </c>
       <c r="AE12" t="n">
-        <v>2224.03</v>
+        <v>4010.33</v>
       </c>
       <c r="AF12" t="n">
-        <v>58.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI12" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>97.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="AK12" t="n">
-        <v>17.5</v>
+        <v>14.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.4</v>
+        <v>9.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AN12" t="n">
-        <v>2282.89</v>
+        <v>3998.64</v>
       </c>
       <c r="AO12" t="n">
-        <v>2153.31</v>
+        <v>3763.45</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,767.55 Cr., a P/E ratio of 97.63, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
+          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹138,010.94 Cr., a P/E ratio of 81.79, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (30.53) trades below Signal (34.42) with an expanding histogram (-3.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +28.74% above the 200-day DMA (₹1708.73). Daily volatility envelope is bounded by ATR(14) of ₹47.31.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 82.88 (Bullish Momentum Zone), while MACD Line (30.14) trades above Signal (14.10) with an expanding histogram (+16.04). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.79% above the 200-day DMA (₹3333.67). Daily volatility envelope is bounded by ATR(14) of ₹103.67.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,212.30) is positioned above the 30-day DMA (₹2,146.11), 50-day DMA (₹2,067.23), and 200-day DMA (₹1,708.73). The price distance from 200 DMA is +28.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,875.40) is positioned above the 30-day DMA (₹3,594.93), 50-day DMA (₹3,627.18), and 200-day DMA (₹3,333.67). The price distance from 200 DMA is +12.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[2212.3, 2218.94, 2225.57, 2232.21, 2238.85, 2245.48]</t>
+          <t>[3875.4, 3887.03, 3898.65, 3910.28, 3921.9, 3933.53]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[2212.3, 2237.86, 2252.33, 2264.99, 2276.69, 2287.8]</t>
+          <t>[3875.4, 3928.5, 3957.3, 3982.11, 4004.84, 4026.26]</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>[2212.3, 2204.74, 2205.5, 2207.63, 2210.46, 2213.75]</t>
+          <t>[3875.4, 3855.92, 3854.67, 3856.41, 3859.7, 3863.98]</t>
         </is>
       </c>
     </row>
@@ -2498,162 +2498,162 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>133288.78</v>
+        <v>118914.84</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3742.8</v>
+        <v>1472</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹3723.39 - ₹3771.92</t>
+          <t>₹1465.2 - ₹1482.2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3820.46</v>
+        <v>1499.19</v>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="J13" t="n">
-        <v>3594.31</v>
+        <v>1440.19</v>
       </c>
       <c r="K13" t="n">
-        <v>3627.85</v>
+        <v>1416.57</v>
       </c>
       <c r="L13" t="n">
-        <v>3330.53</v>
+        <v>1395.71</v>
       </c>
       <c r="M13" t="n">
-        <v>9.859999999999999</v>
+        <v>5.55</v>
       </c>
       <c r="N13" t="n">
-        <v>22.06</v>
+        <v>10.35</v>
       </c>
       <c r="O13" t="n">
-        <v>10.09</v>
+        <v>7.12</v>
       </c>
       <c r="P13" t="n">
-        <v>11.97</v>
+        <v>3.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>97.06999999999999</v>
+        <v>33.99</v>
       </c>
       <c r="R13" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S13" t="n">
-        <v>51.1</v>
+        <v>42.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.49</v>
+        <v>-1.65</v>
       </c>
       <c r="V13" t="n">
-        <v>53.3</v>
+        <v>45</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>12.88</v>
       </c>
       <c r="X13" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>3658.14</v>
+        <v>1431.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>3789.14</v>
+        <v>1442.78</v>
       </c>
       <c r="AA13" t="n">
-        <v>3772.74</v>
+        <v>1483.78</v>
       </c>
       <c r="AB13" t="n">
-        <v>3597.19</v>
+        <v>1421.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>3737.07</v>
+        <v>1470.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>3764.14</v>
+        <v>1482.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>3785.47</v>
+        <v>1492.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>74.09999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI13" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>79</v>
+        <v>35.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>14.6</v>
+        <v>3.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="AM13" t="n">
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>3858.87</v>
+        <v>1504.94</v>
       </c>
       <c r="AO13" t="n">
-        <v>3636.68</v>
+        <v>1442.68</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹133,288.78 Cr., a P/E ratio of 79.00, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹118,914.84 Cr., a P/E ratio of 35.31, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.58 (Bullish Momentum Zone), while MACD Line (10.35) trades above Signal (7.12) with an expanding histogram (+3.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.55% above the 200-day DMA (₹1395.71). Daily volatility envelope is bounded by ATR(14) of ₹33.99.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,742.80) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,472.00) is positioned above the 30-day DMA (₹1,440.19), 50-day DMA (₹1,416.57), and 200-day DMA (₹1,395.71). The price distance from 200 DMA is +5.55%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[3742.8, 3754.03, 3765.26, 3776.49, 3787.71, 3798.94]</t>
+          <t>[1472.0, 1476.42, 1480.83, 1485.25, 1489.66, 1494.08]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[3742.8, 3792.86, 3820.17, 3843.74, 3865.37, 3885.77]</t>
+          <t>[1472.0, 1490.01, 1500.06, 1508.79, 1516.85, 1524.48]</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>[3742.8, 3724.91, 3724.07, 3726.04, 3729.47, 3733.82]</t>
+          <t>[1472.0, 1466.22, 1466.41, 1467.59, 1469.27, 1471.28]</t>
         </is>
       </c>
     </row>
@@ -2665,162 +2665,162 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>118632.09</v>
+        <v>257271.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1468.5</v>
+        <v>1093.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹1461.7 - ₹1478.7</t>
+          <t>₹1087.71 - ₹1103.19</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1495.69</v>
+        <v>1118.66</v>
       </c>
       <c r="I14" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J14" t="n">
-        <v>1440.19</v>
+        <v>1034.29</v>
       </c>
       <c r="K14" t="n">
-        <v>1416.57</v>
+        <v>997.16</v>
       </c>
       <c r="L14" t="n">
-        <v>1395.71</v>
+        <v>944.85</v>
       </c>
       <c r="M14" t="n">
-        <v>5.55</v>
+        <v>10.78</v>
       </c>
       <c r="N14" t="n">
-        <v>10.35</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>7.12</v>
+        <v>11.36</v>
       </c>
       <c r="P14" t="n">
-        <v>3.23</v>
+        <v>-2.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>33.99</v>
+        <v>30.95</v>
       </c>
       <c r="R14" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S14" t="n">
-        <v>42.7</v>
+        <v>50.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.65</v>
+        <v>-1.7</v>
       </c>
       <c r="V14" t="n">
-        <v>45</v>
+        <v>56.7</v>
       </c>
       <c r="W14" t="n">
-        <v>12.88</v>
+        <v>3.89</v>
       </c>
       <c r="X14" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>1427.72</v>
+        <v>1072.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>1439.07</v>
+        <v>1110.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>1480.25</v>
+        <v>1102.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1417.52</v>
+        <v>1047.48</v>
       </c>
       <c r="AC14" t="n">
-        <v>1470.9</v>
+        <v>1080.17</v>
       </c>
       <c r="AD14" t="n">
-        <v>1474</v>
+        <v>1108.74</v>
       </c>
       <c r="AE14" t="n">
-        <v>1479.5</v>
+        <v>1123.57</v>
       </c>
       <c r="AF14" t="n">
-        <v>61.6</v>
+        <v>49.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI14" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>35.2</v>
+        <v>19.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.5</v>
+        <v>39.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>50.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>1501.32</v>
+        <v>1134.67</v>
       </c>
       <c r="AO14" t="n">
-        <v>1437.8</v>
+        <v>1057.43</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹118,632.09 Cr., a P/E ratio of 35.22, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹257,271.40 Cr., a P/E ratio of 19.31, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.58 (Bullish Momentum Zone), while MACD Line (10.35) trades above Signal (7.12) with an expanding histogram (+3.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.55% above the 200-day DMA (₹1395.71). Daily volatility envelope is bounded by ATR(14) of ₹33.99.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.70 (Consolidation Zone), while MACD Line (8.70) trades below Signal (11.36) with an expanding histogram (-2.65). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹944.85). Daily volatility envelope is bounded by ATR(14) of ₹30.95.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,468.50) is positioned above the 30-day DMA (₹1,440.19), 50-day DMA (₹1,416.57), and 200-day DMA (₹1,395.71). The price distance from 200 DMA is +5.55%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,093.90) is positioned above the 30-day DMA (₹1,034.29), 50-day DMA (₹997.16), and 200-day DMA (₹944.85). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[1468.5, 1472.91, 1477.31, 1481.72, 1486.12, 1490.53]</t>
+          <t>[1093.9, 1097.18, 1100.46, 1103.75, 1107.03, 1110.31]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[1468.5, 1486.5, 1496.54, 1505.26, 1513.31, 1520.93]</t>
+          <t>[1093.9, 1109.56, 1117.97, 1125.19, 1131.79, 1137.99]</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>[1468.5, 1462.71, 1462.89, 1464.06, 1465.73, 1467.73]</t>
+          <t>[1093.9, 1087.9, 1087.33, 1087.66, 1088.46, 1089.55]</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>147485.03</v>
+        <v>17728.42</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2849,145 +2849,145 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1664.9</v>
+        <v>618.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹1655.73 - ₹1678.66</t>
+          <t>₹614.54 - ₹625.19</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1701.6</v>
+        <v>635.84</v>
       </c>
       <c r="I15" t="n">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="J15" t="n">
-        <v>1487.74</v>
+        <v>579.77</v>
       </c>
       <c r="K15" t="n">
-        <v>1465.74</v>
+        <v>544.3099999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>1460.05</v>
+        <v>553.6900000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>13.1</v>
+        <v>10.78</v>
       </c>
       <c r="N15" t="n">
-        <v>57.77</v>
+        <v>15.03</v>
       </c>
       <c r="O15" t="n">
-        <v>45.82</v>
+        <v>16.15</v>
       </c>
       <c r="P15" t="n">
-        <v>11.95</v>
+        <v>-1.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>45.87</v>
+        <v>21.3</v>
       </c>
       <c r="R15" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S15" t="n">
-        <v>50.1</v>
+        <v>53.8</v>
       </c>
       <c r="T15" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.66</v>
+        <v>-1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="W15" t="n">
-        <v>7.74</v>
+        <v>4.79</v>
       </c>
       <c r="X15" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>1610.03</v>
+        <v>593.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>1668.3</v>
+        <v>607.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1678.22</v>
+        <v>623.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1596.09</v>
+        <v>586.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>1664.73</v>
+        <v>620</v>
       </c>
       <c r="AD15" t="n">
-        <v>1669.46</v>
+        <v>627.8</v>
       </c>
       <c r="AE15" t="n">
-        <v>1674.03</v>
+        <v>636.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>77.8</v>
+        <v>56.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI15" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>28.8</v>
+        <v>89.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>17.7</v>
+        <v>-10.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>8.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AM15" t="n">
-        <v>15</v>
+        <v>6.7</v>
       </c>
       <c r="AN15" t="n">
-        <v>1710.83</v>
+        <v>649.9</v>
       </c>
       <c r="AO15" t="n">
-        <v>1620.71</v>
+        <v>590.38</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹147,485.03 Cr., a P/E ratio of 28.80, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,728.42 Cr., a P/E ratio of 89.29, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.82 (Bullish Momentum Zone), while MACD Line (57.77) trades above Signal (45.82) with an expanding histogram (+11.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.10% above the 200-day DMA (₹1460.05). Daily volatility envelope is bounded by ATR(14) of ₹45.87.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.93 (Bullish Momentum Zone), while MACD Line (15.03) trades below Signal (16.15) with an expanding histogram (-1.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹553.69). Daily volatility envelope is bounded by ATR(14) of ₹21.30.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,664.90) is positioned above the 30-day DMA (₹1,487.74), 50-day DMA (₹1,465.74), and 200-day DMA (₹1,460.05). The price distance from 200 DMA is +13.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹618.80) is positioned above the 30-day DMA (₹579.77), 50-day DMA (₹544.31), and 200-day DMA (₹553.69). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[1664.9, 1669.89, 1674.89, 1679.88, 1684.88, 1689.87]</t>
+          <t>[618.8, 620.66, 622.51, 624.37, 626.23, 628.08]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[1664.9, 1688.24, 1700.84, 1711.66, 1721.58, 1730.9]</t>
+          <t>[618.8, 629.18, 634.56, 639.13, 643.27, 647.13]</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>[1664.9, 1656.13, 1655.43, 1656.05, 1657.36, 1659.1]</t>
+          <t>[618.8, 614.27, 613.48, 613.3, 613.45, 613.79]</t>
         </is>
       </c>
     </row>
@@ -2999,162 +2999,162 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>250353.71</v>
+        <v>145119.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1064</v>
+        <v>1638.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹1057.81 - ₹1073.29</t>
+          <t>₹1629.33 - ₹1652.26</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1088.76</v>
+        <v>1675.2</v>
       </c>
       <c r="I16" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="J16" t="n">
-        <v>1034.29</v>
+        <v>1487.74</v>
       </c>
       <c r="K16" t="n">
-        <v>997.16</v>
+        <v>1465.74</v>
       </c>
       <c r="L16" t="n">
-        <v>944.85</v>
+        <v>1460.05</v>
       </c>
       <c r="M16" t="n">
-        <v>10.78</v>
+        <v>13.1</v>
       </c>
       <c r="N16" t="n">
-        <v>8.699999999999999</v>
+        <v>57.77</v>
       </c>
       <c r="O16" t="n">
-        <v>11.36</v>
+        <v>45.82</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.65</v>
+        <v>11.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>30.95</v>
+        <v>45.87</v>
       </c>
       <c r="R16" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S16" t="n">
-        <v>50.1</v>
+        <v>43.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.78</v>
+        <v>-2.03</v>
       </c>
       <c r="V16" t="n">
-        <v>56.7</v>
+        <v>48.3</v>
       </c>
       <c r="W16" t="n">
-        <v>3.75</v>
+        <v>7.73</v>
       </c>
       <c r="X16" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>1035.41</v>
+        <v>1583.45</v>
       </c>
       <c r="Z16" t="n">
-        <v>1072.65</v>
+        <v>1638.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1072.51</v>
+        <v>1651.61</v>
       </c>
       <c r="AB16" t="n">
-        <v>1017.57</v>
+        <v>1569.69</v>
       </c>
       <c r="AC16" t="n">
-        <v>1061.13</v>
+        <v>1647.87</v>
       </c>
       <c r="AD16" t="n">
-        <v>1067.86</v>
+        <v>1660.64</v>
       </c>
       <c r="AE16" t="n">
-        <v>1071.73</v>
+        <v>1682.77</v>
       </c>
       <c r="AF16" t="n">
-        <v>49.7</v>
+        <v>77.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.09</v>
+        <v>0.12</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI16" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18.8</v>
+        <v>28.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>39.1</v>
+        <v>17.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>50.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM16" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>1103</v>
+        <v>1686.05</v>
       </c>
       <c r="AO16" t="n">
-        <v>1026.08</v>
+        <v>1595.19</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹250,353.71 Cr., a P/E ratio of 18.79, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹145,119.80 Cr., a P/E ratio of 28.34, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.70 (Consolidation Zone), while MACD Line (8.70) trades below Signal (11.36) with an expanding histogram (-2.65). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹944.85). Daily volatility envelope is bounded by ATR(14) of ₹30.95.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.82 (Bullish Momentum Zone), while MACD Line (57.77) trades above Signal (45.82) with an expanding histogram (+11.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.10% above the 200-day DMA (₹1460.05). Daily volatility envelope is bounded by ATR(14) of ₹45.87.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,064.00) is positioned above the 30-day DMA (₹1,034.29), 50-day DMA (₹997.16), and 200-day DMA (₹944.85). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,638.50) is positioned above the 30-day DMA (₹1,487.74), 50-day DMA (₹1,465.74), and 200-day DMA (₹1,460.05). The price distance from 200 DMA is +13.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[1064.0, 1067.19, 1070.38, 1073.58, 1076.77, 1079.96]</t>
+          <t>[1638.5, 1643.42, 1648.33, 1653.25, 1658.16, 1663.08]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[1064.0, 1079.57, 1087.89, 1095.02, 1101.53, 1107.64]</t>
+          <t>[1638.5, 1661.76, 1674.28, 1685.03, 1694.86, 1704.11]</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>[1064.0, 1057.91, 1057.25, 1057.49, 1058.2, 1059.2]</t>
+          <t>[1638.5, 1629.65, 1628.87, 1629.41, 1630.64, 1632.31]</t>
         </is>
       </c>
     </row>
@@ -3166,162 +3166,162 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63438.19</v>
+        <v>76558.95</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2106</v>
+        <v>1729.4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹2093.22 - ₹2125.18</t>
+          <t>₹1717.8 - ₹1746.8</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2157.13</v>
+        <v>1775.81</v>
       </c>
       <c r="I17" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J17" t="n">
-        <v>2010.06</v>
+        <v>1511.17</v>
       </c>
       <c r="K17" t="n">
-        <v>1895.79</v>
+        <v>1475.45</v>
       </c>
       <c r="L17" t="n">
-        <v>1880.5</v>
+        <v>1504.57</v>
       </c>
       <c r="M17" t="n">
-        <v>11.98</v>
+        <v>14.12</v>
       </c>
       <c r="N17" t="n">
-        <v>59.11</v>
+        <v>60.69</v>
       </c>
       <c r="O17" t="n">
-        <v>67</v>
+        <v>36.2</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.9</v>
+        <v>24.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.92</v>
+        <v>58.01</v>
       </c>
       <c r="R17" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S17" t="n">
-        <v>47.5</v>
+        <v>48.4</v>
       </c>
       <c r="T17" t="n">
         <v>0.18</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.01</v>
+        <v>-2.15</v>
       </c>
       <c r="V17" t="n">
-        <v>53.3</v>
+        <v>48.3</v>
       </c>
       <c r="W17" t="n">
-        <v>5.64</v>
+        <v>7.28</v>
       </c>
       <c r="X17" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y17" t="n">
-        <v>2029.3</v>
+        <v>1719.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>2012.41</v>
+        <v>1780.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2122.85</v>
+        <v>1745.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>2010.12</v>
+        <v>1642.38</v>
       </c>
       <c r="AC17" t="n">
-        <v>2112.87</v>
+        <v>1731.47</v>
       </c>
       <c r="AD17" t="n">
-        <v>2119.74</v>
+        <v>1743.94</v>
       </c>
       <c r="AE17" t="n">
-        <v>2133.47</v>
+        <v>1758.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>45</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI17" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34.2</v>
+        <v>35.4</v>
       </c>
       <c r="AK17" t="n">
-        <v>63</v>
+        <v>49.9</v>
       </c>
       <c r="AL17" t="n">
-        <v>36.1</v>
+        <v>9.6</v>
       </c>
       <c r="AM17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>2182.8</v>
+        <v>1794.82</v>
       </c>
       <c r="AO17" t="n">
-        <v>2035.08</v>
+        <v>1664.13</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,438.19 Cr., a P/E ratio of 34.25, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,558.95 Cr., a P/E ratio of 35.38, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 45.03 (Consolidation Zone), while MACD Line (59.11) trades below Signal (67.00) with an expanding histogram (-7.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.98% above the 200-day DMA (₹1880.50). Daily volatility envelope is bounded by ATR(14) of ₹63.92.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.40 (Bullish Momentum Zone), while MACD Line (60.69) trades above Signal (36.20) with an expanding histogram (+24.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.12% above the 200-day DMA (₹1504.57). Daily volatility envelope is bounded by ATR(14) of ₹58.01.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,106.00) is positioned above the 30-day DMA (₹2,010.06), 50-day DMA (₹1,895.79), and 200-day DMA (₹1,880.50). The price distance from 200 DMA is +11.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,729.40) is positioned above the 30-day DMA (₹1,511.17), 50-day DMA (₹1,475.45), and 200-day DMA (₹1,504.57). The price distance from 200 DMA is +14.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[2106.0, 2112.32, 2118.64, 2124.95, 2131.27, 2137.59]</t>
+          <t>[1729.4, 1745.46, 1761.51, 1777.57, 1793.63, 1809.69]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[2106.0, 2137.89, 2154.79, 2169.24, 2182.41, 2194.76]</t>
+          <t>[1729.4, 1768.66, 1794.33, 1817.76, 1840.04, 1861.57]</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>[2106.0, 2093.14, 2091.52, 2091.74, 2092.92, 2094.71]</t>
+          <t>[1729.4, 1728.05, 1736.9, 1747.43, 1758.82, 1770.77]</t>
         </is>
       </c>
     </row>
@@ -3333,162 +3333,162 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17608.09</v>
+        <v>47081.15</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>614.6</v>
+        <v>1157.1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹610.34 - ₹620.99</t>
+          <t>₹1150.19 - ₹1167.46</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>631.64</v>
+        <v>1184.74</v>
       </c>
       <c r="I18" t="n">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="J18" t="n">
-        <v>579.77</v>
+        <v>1109.24</v>
       </c>
       <c r="K18" t="n">
-        <v>544.3099999999999</v>
+        <v>1105.8</v>
       </c>
       <c r="L18" t="n">
-        <v>553.6900000000001</v>
+        <v>1100.59</v>
       </c>
       <c r="M18" t="n">
-        <v>10.78</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>15.03</v>
+        <v>9.49</v>
       </c>
       <c r="O18" t="n">
-        <v>16.15</v>
+        <v>5.67</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.12</v>
+        <v>3.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.3</v>
+        <v>34.55</v>
       </c>
       <c r="R18" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S18" t="n">
-        <v>53</v>
+        <v>43.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.02</v>
+        <v>-2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>55</v>
+        <v>48.3</v>
       </c>
       <c r="W18" t="n">
-        <v>4.79</v>
+        <v>2.28</v>
       </c>
       <c r="X18" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y18" t="n">
-        <v>589.04</v>
+        <v>1142.83</v>
       </c>
       <c r="Z18" t="n">
-        <v>602.8099999999999</v>
+        <v>1183.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>619.52</v>
+        <v>1166.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>582.65</v>
+        <v>1105.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>614.9</v>
+        <v>1150.73</v>
       </c>
       <c r="AD18" t="n">
-        <v>617.4</v>
+        <v>1164.86</v>
       </c>
       <c r="AE18" t="n">
-        <v>620.2</v>
+        <v>1172.63</v>
       </c>
       <c r="AF18" t="n">
-        <v>56.9</v>
+        <v>53.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI18" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>88.7</v>
+        <v>38.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>-10.1</v>
+        <v>29.9</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.7</v>
+        <v>26.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="AN18" t="n">
-        <v>643.86</v>
+        <v>1193.78</v>
       </c>
       <c r="AO18" t="n">
-        <v>582.27</v>
+        <v>1123.79</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,608.09 Cr., a P/E ratio of 88.69, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹47,081.15 Cr., a P/E ratio of 38.45, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.93 (Bullish Momentum Zone), while MACD Line (15.03) trades below Signal (16.15) with an expanding histogram (-1.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹553.69). Daily volatility envelope is bounded by ATR(14) of ₹21.30.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.63 (Consolidation Zone), while MACD Line (9.49) trades above Signal (5.67) with an expanding histogram (+3.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.15% above the 200-day DMA (₹1100.59). Daily volatility envelope is bounded by ATR(14) of ₹34.55.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹614.60) is positioned above the 30-day DMA (₹579.77), 50-day DMA (₹544.31), and 200-day DMA (₹553.69). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,157.10) is positioned above the 30-day DMA (₹1,109.24), 50-day DMA (₹1,105.80), and 200-day DMA (₹1,100.59). The price distance from 200 DMA is +3.15%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[614.6, 616.44, 618.29, 620.13, 621.98, 623.82]</t>
+          <t>[1157.1, 1160.57, 1164.04, 1167.51, 1170.99, 1174.46]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[614.6, 624.96, 630.34, 634.89, 639.02, 642.87]</t>
+          <t>[1157.1, 1174.39, 1183.59, 1191.45, 1198.63, 1205.36]</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>[614.6, 610.05, 609.25, 609.06, 609.2, 609.53]</t>
+          <t>[1157.1, 1150.21, 1149.38, 1149.56, 1150.26, 1151.28]</t>
         </is>
       </c>
     </row>
@@ -3500,162 +3500,162 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>76643.06</v>
+        <v>62989.36</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1731.3</v>
+        <v>2091.1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>₹1719.7 - ₹1748.7</t>
+          <t>₹2078.32 - ₹2110.28</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1777.71</v>
+        <v>2142.23</v>
       </c>
       <c r="I19" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J19" t="n">
-        <v>1511.17</v>
+        <v>2010.06</v>
       </c>
       <c r="K19" t="n">
-        <v>1475.45</v>
+        <v>1895.79</v>
       </c>
       <c r="L19" t="n">
-        <v>1504.57</v>
+        <v>1880.5</v>
       </c>
       <c r="M19" t="n">
-        <v>14.12</v>
+        <v>11.98</v>
       </c>
       <c r="N19" t="n">
-        <v>60.69</v>
+        <v>59.11</v>
       </c>
       <c r="O19" t="n">
-        <v>36.2</v>
+        <v>67</v>
       </c>
       <c r="P19" t="n">
-        <v>24.49</v>
+        <v>-7.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.01</v>
+        <v>63.92</v>
       </c>
       <c r="R19" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S19" t="n">
-        <v>48.5</v>
+        <v>42.6</v>
       </c>
       <c r="T19" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.12</v>
+        <v>-2.29</v>
       </c>
       <c r="V19" t="n">
-        <v>48.3</v>
+        <v>51.7</v>
       </c>
       <c r="W19" t="n">
-        <v>7.28</v>
+        <v>5.61</v>
       </c>
       <c r="X19" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1722.01</v>
+        <v>2014.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>1782.61</v>
+        <v>1996.91</v>
       </c>
       <c r="AA19" t="n">
-        <v>1747.98</v>
+        <v>2107.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1644.28</v>
+        <v>1995.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>1735.13</v>
+        <v>2101.93</v>
       </c>
       <c r="AD19" t="n">
-        <v>1742.16</v>
+        <v>2115.76</v>
       </c>
       <c r="AE19" t="n">
-        <v>1753.03</v>
+        <v>2140.43</v>
       </c>
       <c r="AF19" t="n">
-        <v>71.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI19" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ19" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="AK19" t="n">
-        <v>49.9</v>
+        <v>63</v>
       </c>
       <c r="AL19" t="n">
-        <v>9.6</v>
+        <v>36.1</v>
       </c>
       <c r="AM19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AN19" t="n">
-        <v>1798.17</v>
+        <v>2162.91</v>
       </c>
       <c r="AO19" t="n">
-        <v>1666.23</v>
+        <v>2016.02</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,643.06 Cr., a P/E ratio of 35.42, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹62,989.36 Cr., a P/E ratio of 34.01, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.40 (Bullish Momentum Zone), while MACD Line (60.69) trades above Signal (36.20) with an expanding histogram (+24.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.12% above the 200-day DMA (₹1504.57). Daily volatility envelope is bounded by ATR(14) of ₹58.01.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 45.03 (Consolidation Zone), while MACD Line (59.11) trades below Signal (67.00) with an expanding histogram (-7.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.98% above the 200-day DMA (₹1880.50). Daily volatility envelope is bounded by ATR(14) of ₹63.92.</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,731.30) is positioned above the 30-day DMA (₹1,511.17), 50-day DMA (₹1,475.45), and 200-day DMA (₹1,504.57). The price distance from 200 DMA is +14.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,091.10) is positioned above the 30-day DMA (₹2,010.06), 50-day DMA (₹1,895.79), and 200-day DMA (₹1,880.50). The price distance from 200 DMA is +11.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>[1731.3, 1747.98, 1764.66, 1781.34, 1798.02, 1814.7]</t>
+          <t>[2091.1, 2097.37, 2103.65, 2109.92, 2116.19, 2122.47]</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>[1731.3, 1771.19, 1797.48, 1821.53, 1844.43, 1866.59]</t>
+          <t>[2091.1, 2122.94, 2139.8, 2154.2, 2167.33, 2179.64]</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>[1731.3, 1730.58, 1740.05, 1751.2, 1763.21, 1775.79]</t>
+          <t>[2091.1, 2078.2, 2076.53, 2076.71, 2077.84, 2079.59]</t>
         </is>
       </c>
     </row>
@@ -3667,162 +3667,162 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46698.67</v>
+        <v>281685.03</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1147.7</v>
+        <v>306</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>₹1140.79 - ₹1158.06</t>
+          <t>₹303.81 - ₹309.28</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1175.34</v>
+        <v>314.75</v>
       </c>
       <c r="I20" t="n">
-        <v>96</v>
+        <v>304</v>
       </c>
       <c r="J20" t="n">
-        <v>1109.24</v>
+        <v>282.98</v>
       </c>
       <c r="K20" t="n">
-        <v>1105.8</v>
+        <v>270.14</v>
       </c>
       <c r="L20" t="n">
-        <v>1100.59</v>
+        <v>273.78</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>10.47</v>
       </c>
       <c r="N20" t="n">
-        <v>9.49</v>
+        <v>9.73</v>
       </c>
       <c r="O20" t="n">
-        <v>5.67</v>
+        <v>8.68</v>
       </c>
       <c r="P20" t="n">
-        <v>3.82</v>
+        <v>1.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>34.55</v>
+        <v>10.94</v>
       </c>
       <c r="R20" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S20" t="n">
-        <v>43.9</v>
+        <v>48.7</v>
       </c>
       <c r="T20" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.18</v>
+        <v>-2.36</v>
       </c>
       <c r="V20" t="n">
-        <v>48.3</v>
+        <v>51.7</v>
       </c>
       <c r="W20" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="X20" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y20" t="n">
-        <v>1131.84</v>
+        <v>301.02</v>
       </c>
       <c r="Z20" t="n">
-        <v>1172.01</v>
+        <v>311.73</v>
       </c>
       <c r="AA20" t="n">
-        <v>1156.88</v>
+        <v>308.45</v>
       </c>
       <c r="AB20" t="n">
-        <v>1095.87</v>
+        <v>289.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1148.6</v>
+        <v>304.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>1152.7</v>
+        <v>309.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>1157.7</v>
+        <v>313.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>53.6</v>
+        <v>62</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI20" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>38.1</v>
+        <v>680</v>
       </c>
       <c r="AK20" t="n">
-        <v>29.9</v>
+        <v>182</v>
       </c>
       <c r="AL20" t="n">
-        <v>26.5</v>
+        <v>0.6</v>
       </c>
       <c r="AM20" t="n">
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>1183.56</v>
+        <v>317.76</v>
       </c>
       <c r="AO20" t="n">
-        <v>1112.16</v>
+        <v>295.12</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,698.67 Cr., a P/E ratio of 38.14, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹281,685.03 Cr., a P/E ratio of 680.00, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.63 (Consolidation Zone), while MACD Line (9.49) trades above Signal (5.67) with an expanding histogram (+3.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.15% above the 200-day DMA (₹1100.59). Daily volatility envelope is bounded by ATR(14) of ₹34.55.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.99 (Bullish Momentum Zone), while MACD Line (9.73) trades above Signal (8.68) with an expanding histogram (+1.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.47% above the 200-day DMA (₹273.78). Daily volatility envelope is bounded by ATR(14) of ₹10.94.</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,147.70) is positioned above the 30-day DMA (₹1,109.24), 50-day DMA (₹1,105.80), and 200-day DMA (₹1,100.59). The price distance from 200 DMA is +3.15%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹306.00) is positioned above the 30-day DMA (₹282.98), 50-day DMA (₹270.14), and 200-day DMA (₹273.78). The price distance from 200 DMA is +10.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>[1147.7, 1151.14, 1154.59, 1158.03, 1161.47, 1164.92]</t>
+          <t>[306.0, 306.92, 307.84, 308.75, 309.67, 310.59]</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>[1147.7, 1164.96, 1174.13, 1181.97, 1189.11, 1195.82]</t>
+          <t>[306.0, 311.29, 314.02, 316.33, 318.42, 320.37]</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>[1147.7, 1140.78, 1139.93, 1140.08, 1140.74, 1141.74]</t>
+          <t>[306.0, 303.64, 303.2, 303.07, 303.11, 303.25]</t>
         </is>
       </c>
     </row>
@@ -3834,329 +3834,162 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>280442.31</v>
+        <v>84733.52</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>304.65</v>
+        <v>13936</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>₹302.46 - ₹307.93</t>
+          <t>₹13843.67 - ₹14074.49</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>313.4</v>
+        <v>14305.31</v>
       </c>
       <c r="I21" t="n">
-        <v>304</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>282.98</v>
+        <v>13241.63</v>
       </c>
       <c r="K21" t="n">
-        <v>270.14</v>
+        <v>12652.22</v>
       </c>
       <c r="L21" t="n">
-        <v>273.78</v>
+        <v>12318.23</v>
       </c>
       <c r="M21" t="n">
-        <v>10.47</v>
+        <v>14.05</v>
       </c>
       <c r="N21" t="n">
-        <v>9.73</v>
+        <v>450.74</v>
       </c>
       <c r="O21" t="n">
-        <v>8.68</v>
+        <v>493.22</v>
       </c>
       <c r="P21" t="n">
-        <v>1.05</v>
+        <v>-42.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.94</v>
+        <v>461.64</v>
       </c>
       <c r="R21" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="S21" t="n">
-        <v>48.8</v>
+        <v>44.7</v>
       </c>
       <c r="T21" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.37</v>
+        <v>-2.39</v>
       </c>
       <c r="V21" t="n">
-        <v>51.7</v>
+        <v>46.7</v>
       </c>
       <c r="W21" t="n">
-        <v>2.33</v>
+        <v>6.26</v>
       </c>
       <c r="X21" t="n">
         <v>-0.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>299.48</v>
+        <v>13382.03</v>
       </c>
       <c r="Z21" t="n">
-        <v>310.14</v>
+        <v>13783.45</v>
       </c>
       <c r="AA21" t="n">
-        <v>307.09</v>
+        <v>14047.49</v>
       </c>
       <c r="AB21" t="n">
-        <v>288.25</v>
+        <v>13243.54</v>
       </c>
       <c r="AC21" t="n">
-        <v>304.27</v>
+        <v>13866.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>305.54</v>
+        <v>14154.34</v>
       </c>
       <c r="AE21" t="n">
-        <v>306.42</v>
+        <v>14372.67</v>
       </c>
       <c r="AF21" t="n">
-        <v>62</v>
+        <v>58.4</v>
       </c>
       <c r="AG21" t="n">
         <v>0.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.86) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.96) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AI21" t="n">
         <v>0.15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>677</v>
+        <v>40.8</v>
       </c>
       <c r="AK21" t="n">
-        <v>182</v>
+        <v>21.1</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="AM21" t="n">
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>315.25</v>
+        <v>14444.12</v>
       </c>
       <c r="AO21" t="n">
-        <v>294.19</v>
+        <v>13351.05</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹280,442.31 Cr., a P/E ratio of 677.00, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹84,733.52 Cr., a P/E ratio of 40.82, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.99 (Bullish Momentum Zone), while MACD Line (9.73) trades above Signal (8.68) with an expanding histogram (+1.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.47% above the 200-day DMA (₹273.78). Daily volatility envelope is bounded by ATR(14) of ₹10.94.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.38 (Bullish Momentum Zone), while MACD Line (450.74) trades below Signal (493.22) with an expanding histogram (-42.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.05% above the 200-day DMA (₹12318.23). Daily volatility envelope is bounded by ATR(14) of ₹461.64.</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹304.65) is positioned above the 30-day DMA (₹282.98), 50-day DMA (₹270.14), and 200-day DMA (₹273.78). The price distance from 200 DMA is +10.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,936.00) is positioned above the 30-day DMA (₹13,241.63), 50-day DMA (₹12,652.22), and 200-day DMA (₹12,318.23). The price distance from 200 DMA is +14.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>[304.65, 305.56, 306.48, 307.39, 308.31, 309.22]</t>
+          <t>[13936.0, 13977.81, 14019.62, 14061.42, 14103.23, 14145.04]</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[304.65, 309.94, 312.66, 314.97, 317.05, 319.0]</t>
+          <t>[13936.0, 14162.47, 14280.76, 14381.26, 14472.55, 14557.95]</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>[304.65, 302.28, 301.84, 301.71, 301.74, 301.88]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>82739.21000000001</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>13608</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>₹13515.67 - ₹13746.49</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>13977.31</v>
-      </c>
-      <c r="I22" t="n">
-        <v>7</v>
-      </c>
-      <c r="J22" t="n">
-        <v>13241.63</v>
-      </c>
-      <c r="K22" t="n">
-        <v>12652.22</v>
-      </c>
-      <c r="L22" t="n">
-        <v>12318.23</v>
-      </c>
-      <c r="M22" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="N22" t="n">
-        <v>450.74</v>
-      </c>
-      <c r="O22" t="n">
-        <v>493.22</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-42.48</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>461.64</v>
-      </c>
-      <c r="R22" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="S22" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U22" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="V22" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="W22" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>13054.03</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>13375.37</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>13716.86</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>12915.54</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>13694.33</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>13788.66</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>13969.33</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.86) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AI22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>14142.33</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>13095.48</v>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹82,739.21 Cr., a P/E ratio of 39.86, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.38 (Bullish Momentum Zone), while MACD Line (450.74) trades below Signal (493.22) with an expanding histogram (-42.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.05% above the 200-day DMA (₹12318.23). Daily volatility envelope is bounded by ATR(14) of ₹461.64.</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,608.00) is positioned above the 30-day DMA (₹13,241.63), 50-day DMA (₹12,652.22), and 200-day DMA (₹12,318.23). The price distance from 200 DMA is +14.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>[13608.0, 13648.82, 13689.65, 13730.47, 13771.3, 13812.12]</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>[13608.0, 13833.48, 13950.79, 14050.31, 14140.61, 14225.03]</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>[13608.0, 13510.33, 13493.79, 13490.6, 13494.31, 13502.44]</t>
+          <t>[13936.0, 13839.32, 13823.76, 13821.55, 13826.25, 13835.36]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU21"/>
+  <dimension ref="A1:AT21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,195 +459,190 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Rec_Shares_To_Buy</t>
+          <t>30_DMA</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>30_DMA</t>
+          <t>50_DMA</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>50_DMA</t>
+          <t>200_DMA</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>200_DMA</t>
+          <t>200_DMA_Dist_%</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>200_DMA_Dist_%</t>
+          <t>MACD_Line</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>MACD_Line</t>
+          <t>MACD_Signal</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>MACD_Signal</t>
+          <t>MACD_Hist</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>MACD_Hist</t>
+          <t>ATR_14</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>ATR_14</t>
+          <t>India_VIX</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>India_VIX</t>
+          <t>Final_Win_Probability_%</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Final_Win_Probability_%</t>
+          <t>Risk_Reward_Ratio</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Risk_Reward_Ratio</t>
+          <t>Expected_Value_EV_%</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Expected_Value_EV_%</t>
+          <t>Hist_Backtest_Win_Rate_%</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Hist_Backtest_Win_Rate_%</t>
+          <t>Model_MAE_%</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model_MAE_%</t>
+          <t>Out_Sample_R2</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Out_Sample_R2</t>
+          <t>Next_Day_Expected_Low</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Next_Day_Expected_Low</t>
+          <t>Next_Day_Expected_High</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Next_Day_Expected_High</t>
+          <t>Target_Price</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Target_Price</t>
+          <t>Stop_Loss</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Stop_Loss</t>
+          <t>Pivot_PP</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Pivot_PP</t>
+          <t>Pivot_R1</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Pivot_R1</t>
+          <t>Pivot_R2</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Pivot_R2</t>
+          <t>RSI_14</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>RSI_14</t>
+          <t>CMF_20</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>CMF_20</t>
+          <t>Key_Drivers</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Key_Drivers</t>
+          <t>News_Sentiment</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>News_Sentiment</t>
+          <t>PE_Ratio</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>PE_Ratio</t>
+          <t>Revenue_Growth_%</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>Revenue_Growth_%</t>
+          <t>Profit_Margin_%</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>Profit_Margin_%</t>
+          <t>ROE_%</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>ROE_%</t>
+          <t>MC_Expected_High_95CI</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>MC_Expected_High_95CI</t>
+          <t>MC_Expected_Low_95CI</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>MC_Expected_Low_95CI</t>
+          <t>Fundamental_Synthesis</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>Fundamental_Synthesis</t>
+          <t>Technical_Synthesis</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>Technical_Synthesis</t>
+          <t>CAR_Synthesis</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>CAR_Synthesis</t>
+          <t>Forecast_5D_Close</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>Forecast_5D_Close</t>
+          <t>Forecast_5D_High</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
-        <is>
-          <t>Forecast_5D_High</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
         <is>
           <t>Forecast_5D_Low</t>
         </is>
@@ -670,153 +665,124 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1036968.89</v>
+        <v>1047298.52</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1445.6</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹1441.03 - ₹1452.46</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1463.9</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>145</v>
+        <v>1395.55</v>
       </c>
       <c r="J2" t="n">
-        <v>1398.49</v>
+        <v>1346.57</v>
       </c>
       <c r="K2" t="n">
-        <v>1349.96</v>
+        <v>1336.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1337.12</v>
+        <v>6.36</v>
       </c>
       <c r="M2" t="n">
-        <v>6.45</v>
+        <v>21.72</v>
       </c>
       <c r="N2" t="n">
-        <v>20.38</v>
+        <v>25.48</v>
       </c>
       <c r="O2" t="n">
-        <v>24.46</v>
+        <v>-3.76</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.08</v>
+        <v>24.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.87</v>
+        <v>11.76</v>
       </c>
       <c r="R2" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S2" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.34</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>-0.66</v>
+        <v>60</v>
       </c>
       <c r="V2" t="n">
-        <v>60</v>
+        <v>7.01</v>
       </c>
       <c r="W2" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="X2" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1427.64</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1478.24</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1457.16</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1411.29</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1442.83</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1452.66</v>
-      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>1459.73</v>
+        <v>62.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="AG2" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.15</v>
+        <v>18.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18.7</v>
+        <v>11.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>11.4</v>
+        <v>27.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="AM2" t="n">
         <v>16.1</v>
       </c>
-      <c r="AN2" t="n">
-        <v>1470.66</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1419.05</v>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,047,298.52 Cr., a P/E ratio of 18.87, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
+        </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,036,968.89 Cr., a P/E ratio of 18.68, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.16 (Bullish Momentum Zone), while MACD Line (21.72) trades below Signal (25.48) with an expanding histogram (-3.76). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.36% above the 200-day DMA (₹1336.85). Daily volatility envelope is bounded by ATR(14) of ₹24.02.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.14 (Bullish Momentum Zone), while MACD Line (20.38) trades below Signal (24.46) with an expanding histogram (-4.08). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.45% above the 200-day DMA (₹1337.12). Daily volatility envelope is bounded by ATR(14) of ₹22.87.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,395.55), 50-day DMA (₹1,346.57), and 200-day DMA (₹1,336.85). The price distance from 200 DMA is +6.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,445.60) is positioned above the 30-day DMA (₹1,398.49), 50-day DMA (₹1,349.96), and 200-day DMA (₹1,337.12). The price distance from 200 DMA is +6.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[1445.6, 1449.94, 1454.27, 1458.61, 1462.95, 1467.28]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[1445.6, 1459.09, 1467.21, 1474.46, 1481.24, 1487.74]</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>[1445.6, 1443.08, 1444.57, 1446.73, 1449.22, 1451.94]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -837,153 +803,124 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>130962.08</v>
+        <v>129870.25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>113.95</v>
-      </c>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹113.55 - ₹114.55</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>115.55</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>1670</v>
+        <v>107.66</v>
       </c>
       <c r="J3" t="n">
-        <v>107.8</v>
+        <v>106.31</v>
       </c>
       <c r="K3" t="n">
-        <v>106.57</v>
+        <v>112.63</v>
       </c>
       <c r="L3" t="n">
-        <v>112.63</v>
+        <v>-0.88</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="N3" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>0.41</v>
       </c>
       <c r="P3" t="n">
-        <v>0.41</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>11.76</v>
       </c>
       <c r="R3" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S3" t="n">
-        <v>53</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>52.6</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>51.7</v>
       </c>
       <c r="V3" t="n">
-        <v>53.3</v>
+        <v>3.38</v>
       </c>
       <c r="W3" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="X3" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y3" t="n">
-        <v>111.7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>115.69</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>114.86</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>110.96</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>113.69</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>114.72</v>
-      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>115.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AF3" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.17</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.15</v>
+        <v>5.9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5.9</v>
+        <v>15.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>15.2</v>
+        <v>38.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="AM3" t="n">
         <v>15</v>
       </c>
-      <c r="AN3" t="n">
-        <v>117.13</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>110.81</v>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹129,870.25 Cr., a P/E ratio of 5.88, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+        </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,962.08 Cr., a P/E ratio of 5.93, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.92 (Bullish Momentum Zone), while MACD Line (1.59) trades above Signal (1.18) with an expanding histogram (+0.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading -0.88% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.07.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.19 (Bullish Momentum Zone), while MACD Line (1.69) trades above Signal (1.28) with an expanding histogram (+0.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.07% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.00.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹nan) is positioned above the 30-day DMA (₹107.66), 50-day DMA (₹106.31), and 200-day DMA (₹112.63). The price distance from 200 DMA is -0.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.95) is positioned above the 30-day DMA (₹107.80), 50-day DMA (₹106.57), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.07%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[113.95, 114.29, 114.63, 114.98, 115.32, 115.66]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[113.95, 115.09, 115.76, 116.36, 116.91, 117.44]</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>[113.95, 113.69, 113.79, 113.94, 114.12, 114.32]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -995,7 +932,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1004,153 +941,124 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>352003.37</v>
+        <v>269379.04</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>11966</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹11922.37 - ₹12031.45</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>12140.53</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
+        <v>2687.86</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2678.76</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2570.71</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="P4" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="R4" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>55</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AL4" t="n">
         <v>15</v>
       </c>
-      <c r="J4" t="n">
-        <v>11421.23</v>
-      </c>
-      <c r="K4" t="n">
-        <v>11269.86</v>
-      </c>
-      <c r="L4" t="n">
-        <v>11569.69</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>143.27</v>
-      </c>
-      <c r="O4" t="n">
-        <v>124.24</v>
-      </c>
-      <c r="P4" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>218.17</v>
-      </c>
-      <c r="R4" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="V4" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>11818.79</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>12237.6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>12061.73</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11638.75</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>11957</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>12009</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>12052</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>12244.52</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>11679.97</v>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹269,379.04 Cr., a P/E ratio of 56.51, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹352,003.37 Cr., a P/E ratio of 41.20, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.38 (Bullish Momentum Zone), while MACD Line (16.14) trades above Signal (10.09) with an expanding histogram (+6.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.83% above the 200-day DMA (₹2570.71). Daily volatility envelope is bounded by ATR(14) of ₹58.09.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (143.27) trades above Signal (124.24) with an expanding histogram (+19.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.40% above the 200-day DMA (₹11569.69). Daily volatility envelope is bounded by ATR(14) of ₹218.17.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹nan) is positioned above the 30-day DMA (₹2,687.86), 50-day DMA (₹2,678.76), and 200-day DMA (₹2,570.71). The price distance from 200 DMA is +6.83%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,966.00) is positioned above the 30-day DMA (₹11,421.23), 50-day DMA (₹11,269.86), and 200-day DMA (₹11,569.69). The price distance from 200 DMA is +2.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[11966.0, 12001.9, 12037.8, 12073.69, 12109.59, 12145.49]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[11966.0, 12089.16, 12161.21, 12224.84, 12284.13, 12340.62]</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>[11966.0, 11936.45, 11945.24, 11960.33, 11978.69, 11999.14]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -1162,162 +1070,133 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>220660.55</v>
+        <v>17705.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>8038</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹8007.88 - ₹8083.18</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>8158.49</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>22</v>
+        <v>578.01</v>
       </c>
       <c r="J5" t="n">
-        <v>7447.86</v>
+        <v>541.38</v>
       </c>
       <c r="K5" t="n">
-        <v>7362.95</v>
+        <v>553.54</v>
       </c>
       <c r="L5" t="n">
-        <v>7176.17</v>
+        <v>10.74</v>
       </c>
       <c r="M5" t="n">
-        <v>9.16</v>
+        <v>14.56</v>
       </c>
       <c r="N5" t="n">
-        <v>130.62</v>
+        <v>16.43</v>
       </c>
       <c r="O5" t="n">
-        <v>94.11</v>
+        <v>-1.88</v>
       </c>
       <c r="P5" t="n">
-        <v>36.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>150.61</v>
+        <v>11.76</v>
       </c>
       <c r="R5" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S5" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.28</v>
-      </c>
+        <v>51.4</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-0.97</v>
+        <v>53.3</v>
       </c>
       <c r="V5" t="n">
-        <v>50</v>
+        <v>4.89</v>
       </c>
       <c r="W5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X5" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y5" t="n">
-        <v>7909.75</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>8191.08</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>8102.3</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7812.09</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7982</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>8112</v>
-      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>8186</v>
+        <v>60.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>79</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.1</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.15</v>
+        <v>89.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38.3</v>
+        <v>-10.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>31.5</v>
+        <v>3.7</v>
       </c>
       <c r="AL5" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>8270.43</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>7843.91</v>
+        <v>6.7</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,705.50 Cr., a P/E ratio of 89.18, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+        </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹220,660.55 Cr., a P/E ratio of 38.29, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.95 (Bullish Momentum Zone), while MACD Line (130.62) trades above Signal (94.11) with an expanding histogram (+36.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.16% above the 200-day DMA (₹7176.17). Daily volatility envelope is bounded by ATR(14) of ₹150.61.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹nan) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹8,038.00) is positioned above the 30-day DMA (₹7,447.86), 50-day DMA (₹7,362.95), and 200-day DMA (₹7,176.17). The price distance from 200 DMA is +9.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[8038.0, 8062.11, 8086.23, 8110.34, 8134.46, 8158.57]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[8038.0, 8122.36, 8171.43, 8214.69, 8254.94, 8293.28]</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>[8038.0, 8016.93, 8022.33, 8032.08, 8044.09, 8057.54]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1208,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,153 +1217,124 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>265899.16</v>
+        <v>354592.07</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2773.7</v>
-      </c>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2762.16 - ₹2791.01</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2819.87</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>57</v>
+        <v>11421.23</v>
       </c>
       <c r="J6" t="n">
-        <v>2689.12</v>
+        <v>11269.86</v>
       </c>
       <c r="K6" t="n">
-        <v>2681.37</v>
+        <v>11569.69</v>
       </c>
       <c r="L6" t="n">
-        <v>2572.85</v>
+        <v>2.4</v>
       </c>
       <c r="M6" t="n">
-        <v>6.78</v>
+        <v>143.27</v>
       </c>
       <c r="N6" t="n">
-        <v>18.17</v>
+        <v>124.24</v>
       </c>
       <c r="O6" t="n">
-        <v>11.71</v>
+        <v>19.02</v>
       </c>
       <c r="P6" t="n">
-        <v>6.46</v>
+        <v>218.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>57.71</v>
+        <v>11.76</v>
       </c>
       <c r="R6" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S6" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.27</v>
-      </c>
+        <v>51.1</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>-0.99</v>
+        <v>48.3</v>
       </c>
       <c r="V6" t="n">
-        <v>56.7</v>
+        <v>2.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X6" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y6" t="n">
-        <v>2755.24</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2852.32</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2796.84</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2687.13</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2775.33</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2787.36</v>
-      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>2801.03</v>
+        <v>62.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.23</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.15</v>
+        <v>41.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55.8</v>
+        <v>15.9</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AL6" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AM6" t="n">
         <v>15</v>
       </c>
-      <c r="AN6" t="n">
-        <v>2841.27</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>2705.45</v>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹354,592.07 Cr., a P/E ratio of 41.50, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹265,899.16 Cr., a P/E ratio of 55.78, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (143.27) trades above Signal (124.24) with an expanding histogram (+19.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.40% above the 200-day DMA (₹11569.69). Daily volatility envelope is bounded by ATR(14) of ₹218.17.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 68.92 (Bullish Momentum Zone), while MACD Line (18.17) trades above Signal (11.71) with an expanding histogram (+6.46). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.78% above the 200-day DMA (₹2572.85). Daily volatility envelope is bounded by ATR(14) of ₹57.71.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹nan) is positioned above the 30-day DMA (₹11,421.23), 50-day DMA (₹11,269.86), and 200-day DMA (₹11,569.69). The price distance from 200 DMA is +2.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,773.70) is positioned above the 30-day DMA (₹2,689.12), 50-day DMA (₹2,681.37), and 200-day DMA (₹2,572.85). The price distance from 200 DMA is +6.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2773.7, 2796.84, 2819.98, 2843.12, 2866.27, 2889.41]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2773.7, 2819.93, 2852.63, 2883.11, 2912.44, 2941.03]</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>[2773.7, 2779.53, 2795.5, 2813.13, 2831.64, 2850.69]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1346,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,153 +1355,124 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25000</v>
+        <v>256518.44</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>373</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹371.48 - ₹375.28</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>379.09</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>437</v>
+        <v>1032.61</v>
       </c>
       <c r="J7" t="n">
-        <v>357.93</v>
+        <v>994.9400000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>350.57</v>
+        <v>942.9400000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>347.65</v>
+        <v>8.94</v>
       </c>
       <c r="M7" t="n">
-        <v>7.28</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>4.74</v>
+        <v>12.02</v>
       </c>
       <c r="O7" t="n">
-        <v>2.83</v>
+        <v>-3.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>31.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.61</v>
+        <v>11.76</v>
       </c>
       <c r="R7" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S7" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.26</v>
-      </c>
+        <v>50.7</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>-1.07</v>
+        <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>51.7</v>
+        <v>3.56</v>
       </c>
       <c r="W7" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X7" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y7" t="n">
-        <v>363.87</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>374.26</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>375.98</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>361.58</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>373.63</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>376.06</v>
-      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>379.13</v>
+        <v>46.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>-0.14</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.15</v>
+        <v>19.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6.1</v>
+        <v>39.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>25.2</v>
+        <v>50.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>383.03</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>363.66</v>
+        <v>18.5</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹256,518.44 Cr., a P/E ratio of 19.25, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+        </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 81.18 (Bullish Momentum Zone), while MACD Line (4.74) trades above Signal (2.83) with an expanding histogram (+1.91). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.28% above the 200-day DMA (₹347.65). Daily volatility envelope is bounded by ATR(14) of ₹7.61.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹373.00) is positioned above the 30-day DMA (₹357.93), 50-day DMA (₹350.57), and 200-day DMA (₹347.65). The price distance from 200 DMA is +7.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[373.0, 374.12, 375.24, 376.36, 377.48, 378.59]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[373.0, 377.16, 379.54, 381.63, 383.57, 385.4]</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>[373.0, 371.84, 372.01, 372.4, 372.91, 373.49]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -1663,162 +1484,133 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105938.94</v>
+        <v>138887</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>744.25</v>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹741.23 - ₹748.78</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>756.33</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>220</v>
+        <v>3594.31</v>
       </c>
       <c r="J8" t="n">
-        <v>730.08</v>
+        <v>3627.85</v>
       </c>
       <c r="K8" t="n">
-        <v>705.51</v>
+        <v>3330.53</v>
       </c>
       <c r="L8" t="n">
-        <v>686.16</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>7.63</v>
+        <v>22.06</v>
       </c>
       <c r="N8" t="n">
-        <v>8.210000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="O8" t="n">
-        <v>9.15</v>
+        <v>11.97</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.1</v>
+        <v>11.76</v>
       </c>
       <c r="R8" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S8" t="n">
-        <v>51</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.26</v>
-      </c>
+        <v>50.7</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>-1.08</v>
+        <v>53.3</v>
       </c>
       <c r="V8" t="n">
-        <v>56.7</v>
+        <v>2.18</v>
       </c>
       <c r="W8" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="X8" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y8" t="n">
-        <v>726.13</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>738.8200000000001</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>750.2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>721.6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>743.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>747.3</v>
-      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>750.35</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AF8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.08</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.15</v>
+        <v>82.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>49.4</v>
+        <v>14.6</v>
       </c>
       <c r="AK8" t="n">
-        <v>15.1</v>
+        <v>9.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AM8" t="n">
         <v>15</v>
       </c>
-      <c r="AN8" t="n">
-        <v>762.84</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>724.5599999999999</v>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹138,887.00 Cr., a P/E ratio of 82.31, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,938.94 Cr., a P/E ratio of 49.39, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.00 (Consolidation Zone), while MACD Line (8.21) trades below Signal (9.15) with an expanding histogram (-0.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.63% above the 200-day DMA (₹686.16). Daily volatility envelope is bounded by ATR(14) of ₹15.10.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹nan) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹744.25) is positioned above the 30-day DMA (₹730.08), 50-day DMA (₹705.51), and 200-day DMA (₹686.16). The price distance from 200 DMA is +7.63%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[744.25, 746.48, 748.72, 750.95, 753.18, 755.41]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[744.25, 752.52, 757.26, 761.41, 765.26, 768.92]</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>[744.25, 741.95, 742.31, 743.1, 744.12, 745.28]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -1830,162 +1622,133 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107751.1</v>
+        <v>220989.96</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1107.6</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹1102.85 - ₹1114.73</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1126.62</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>140</v>
+        <v>7437.81</v>
       </c>
       <c r="J9" t="n">
-        <v>1107.37</v>
+        <v>7344.46</v>
       </c>
       <c r="K9" t="n">
-        <v>1064.71</v>
+        <v>7171.21</v>
       </c>
       <c r="L9" t="n">
-        <v>1056.34</v>
+        <v>9.19</v>
       </c>
       <c r="M9" t="n">
-        <v>3.99</v>
+        <v>121.41</v>
       </c>
       <c r="N9" t="n">
-        <v>7.41</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>8.82</v>
+        <v>36.42</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.41</v>
+        <v>150.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.77</v>
+        <v>11.76</v>
       </c>
       <c r="R9" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S9" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.25</v>
-      </c>
+        <v>49.7</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>-1.16</v>
+        <v>48.3</v>
       </c>
       <c r="V9" t="n">
-        <v>55</v>
+        <v>1.83</v>
       </c>
       <c r="W9" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="X9" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1079.07</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1086.23</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1116.46</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1071.94</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1107.07</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1114.34</v>
-      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>1121.07</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AF9" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.19</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.15</v>
+        <v>38.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75.2</v>
+        <v>31.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>12.2</v>
+        <v>23.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1139.12</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1081.07</v>
+        <v>15</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹220,989.96 Cr., a P/E ratio of 38.34, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>MAXHEALTH operates in the Healthcare sector. With an estimated Market Cap of ₹107,751.10 Cr., a P/E ratio of 75.21, and YoY Revenue Growth of +12.2%, the company demonstrates strong institutional backing, solid operating profit margins (17.23%), and healthy Return on Equity (14.33%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.10 (Bullish Momentum Zone), while MACD Line (121.41) trades above Signal (84.99) with an expanding histogram (+36.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.19% above the 200-day DMA (₹7171.21). Daily volatility envelope is bounded by ATR(14) of ₹150.57.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.70 (Consolidation Zone), while MACD Line (7.41) trades below Signal (8.82) with an expanding histogram (-1.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.99% above the 200-day DMA (₹1056.34). Daily volatility envelope is bounded by ATR(14) of ₹23.77.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹nan) is positioned above the 30-day DMA (₹7,437.81), 50-day DMA (₹7,344.46), and 200-day DMA (₹7,171.21). The price distance from 200 DMA is +9.19%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MAXHEALTH. Current Market Price (₹1,107.60) is positioned above the 30-day DMA (₹1,107.37), 50-day DMA (₹1,064.71), and 200-day DMA (₹1,056.34). The price distance from 200 DMA is +3.99%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[1107.6, 1110.92, 1114.25, 1117.57, 1120.89, 1124.21]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[1107.6, 1120.43, 1127.69, 1134.04, 1139.91, 1145.48]</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>[1107.6, 1103.79, 1104.16, 1105.22, 1106.63, 1108.27]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -2006,153 +1769,124 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68259.66</v>
+        <v>68235.74000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>5709</v>
-      </c>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹5685.05 - ₹5744.93</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5804.8</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>27</v>
+        <v>5575</v>
       </c>
       <c r="J10" t="n">
-        <v>5587.6</v>
+        <v>5484.08</v>
       </c>
       <c r="K10" t="n">
-        <v>5491.02</v>
+        <v>5521.06</v>
       </c>
       <c r="L10" t="n">
-        <v>5522.76</v>
+        <v>5.35</v>
       </c>
       <c r="M10" t="n">
-        <v>4.14</v>
+        <v>57.19</v>
       </c>
       <c r="N10" t="n">
-        <v>60.48</v>
+        <v>51.96</v>
       </c>
       <c r="O10" t="n">
-        <v>53.66</v>
+        <v>5.23</v>
       </c>
       <c r="P10" t="n">
-        <v>6.82</v>
+        <v>122.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>119.75</v>
+        <v>11.76</v>
       </c>
       <c r="R10" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S10" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.25</v>
-      </c>
+        <v>47.1</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>-1.19</v>
+        <v>53.3</v>
       </c>
       <c r="V10" t="n">
-        <v>51.7</v>
+        <v>2.79</v>
       </c>
       <c r="W10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="X10" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y10" t="n">
-        <v>5597.07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5796.88</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5754.67</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>5529.38</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5718</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5765.5</v>
-      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>5822</v>
+        <v>58.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>61</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.02</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.15</v>
+        <v>29.6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>29.6</v>
+        <v>14.6</v>
       </c>
       <c r="AK10" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="AL10" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="AM10" t="n">
         <v>17.6</v>
       </c>
-      <c r="AN10" t="n">
-        <v>5835.96</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>5588.12</v>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,235.74 Cr., a P/E ratio of 29.62, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+        </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,259.66 Cr., a P/E ratio of 29.63, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.98 (Bullish Momentum Zone), while MACD Line (60.48) trades above Signal (53.66) with an expanding histogram (+6.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹5522.76). Daily volatility envelope is bounded by ATR(14) of ₹119.75.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹nan) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,709.00) is positioned above the 30-day DMA (₹5,587.60), 50-day DMA (₹5,491.02), and 200-day DMA (₹5,522.76). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[5709.0, 5726.13, 5743.25, 5760.38, 5777.51, 5794.63]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[5709.0, 5774.03, 5810.99, 5843.35, 5873.31, 5901.74]</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>[5709.0, 5690.2, 5692.45, 5698.16, 5705.66, 5714.3]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -2164,162 +1898,133 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>311782.91</v>
+        <v>25000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>4662</v>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹4645.29 - ₹4687.06</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>4728.82</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>357.21</v>
       </c>
       <c r="J11" t="n">
-        <v>4479.85</v>
+        <v>349.78</v>
       </c>
       <c r="K11" t="n">
-        <v>4409.79</v>
+        <v>347.56</v>
       </c>
       <c r="L11" t="n">
-        <v>4345.73</v>
+        <v>6.64</v>
       </c>
       <c r="M11" t="n">
-        <v>6.92</v>
+        <v>4.07</v>
       </c>
       <c r="N11" t="n">
-        <v>59.87</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>51.89</v>
+        <v>1.72</v>
       </c>
       <c r="P11" t="n">
-        <v>7.98</v>
+        <v>7.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>83.53</v>
+        <v>11.76</v>
       </c>
       <c r="R11" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S11" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.3</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>-1.21</v>
+        <v>50</v>
       </c>
       <c r="V11" t="n">
-        <v>43.3</v>
+        <v>2.89</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X11" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y11" t="n">
-        <v>4561.77</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4720.59</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4699.3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>4536.71</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4666.17</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4684.84</v>
-      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>4707.67</v>
+        <v>78.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.08</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.15</v>
+        <v>6.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34.2</v>
+        <v>25.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AL11" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>4789.62</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>4536.31</v>
+        <v>15</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.06, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹311,782.91 Cr., a P/E ratio of 34.24, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.59 (Bullish Momentum Zone), while MACD Line (59.87) trades above Signal (51.89) with an expanding histogram (+7.98). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.92% above the 200-day DMA (₹4345.73). Daily volatility envelope is bounded by ATR(14) of ₹83.53.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹nan) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,662.00) is positioned above the 30-day DMA (₹4,479.85), 50-day DMA (₹4,409.79), and 200-day DMA (₹4,345.73). The price distance from 200 DMA is +6.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[4662.0, 4675.99, 4689.97, 4703.96, 4717.94, 4731.93]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[4662.0, 4709.4, 4737.22, 4761.83, 4784.77, 4806.64]</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>[4662.0, 4650.93, 4654.53, 4660.56, 4667.83, 4675.9]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -2331,162 +2036,133 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>138010.94</v>
+        <v>107099.01</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>3875.4</v>
-      </c>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹3854.67 - ₹3906.5</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>3958.34</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>32</v>
+        <v>1107.18</v>
       </c>
       <c r="J12" t="n">
-        <v>3594.93</v>
+        <v>1063.17</v>
       </c>
       <c r="K12" t="n">
-        <v>3627.18</v>
+        <v>1056.55</v>
       </c>
       <c r="L12" t="n">
-        <v>3333.67</v>
+        <v>6.46</v>
       </c>
       <c r="M12" t="n">
-        <v>12.79</v>
+        <v>8.48</v>
       </c>
       <c r="N12" t="n">
-        <v>30.14</v>
+        <v>9.17</v>
       </c>
       <c r="O12" t="n">
-        <v>14.1</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>16.04</v>
+        <v>22.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>103.67</v>
+        <v>11.76</v>
       </c>
       <c r="R12" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S12" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.2</v>
-      </c>
+        <v>46.8</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>-1.5</v>
+        <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>55</v>
+        <v>7.65</v>
       </c>
       <c r="W12" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="X12" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y12" t="n">
-        <v>3827.81</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3963.45</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3906.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3719.89</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3818.53</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3942.86</v>
-      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>4010.33</v>
+        <v>55.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>-0.09</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.15</v>
+        <v>74.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>81.8</v>
+        <v>12.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>14.6</v>
+        <v>17.2</v>
       </c>
       <c r="AL12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3998.64</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>3763.45</v>
+        <v>14.3</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>MAXHEALTH operates in the Healthcare sector. With an estimated Market Cap of ₹107,099.01 Cr., a P/E ratio of 74.76, and YoY Revenue Growth of +12.2%, the company demonstrates strong institutional backing, solid operating profit margins (17.23%), and healthy Return on Equity (14.33%).</t>
+        </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹138,010.94 Cr., a P/E ratio of 81.79, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.85 (Bullish Momentum Zone), while MACD Line (8.48) trades below Signal (9.17) with an expanding histogram (-0.69). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.46% above the 200-day DMA (₹1056.55). Daily volatility envelope is bounded by ATR(14) of ₹22.56.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 82.88 (Bullish Momentum Zone), while MACD Line (30.14) trades above Signal (14.10) with an expanding histogram (+16.04). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.79% above the 200-day DMA (₹3333.67). Daily volatility envelope is bounded by ATR(14) of ₹103.67.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MAXHEALTH. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,107.18), 50-day DMA (₹1,063.17), and 200-day DMA (₹1,056.55). The price distance from 200 DMA is +6.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹3,875.40) is positioned above the 30-day DMA (₹3,594.93), 50-day DMA (₹3,627.18), and 200-day DMA (₹3,333.67). The price distance from 200 DMA is +12.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[3875.4, 3887.03, 3898.65, 3910.28, 3921.9, 3933.53]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[3875.4, 3928.5, 3957.3, 3982.11, 4004.84, 4026.26]</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>[3875.4, 3855.92, 3854.67, 3856.41, 3859.7, 3863.98]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -2507,153 +2183,124 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>118914.84</v>
+        <v>119108.72</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1472</v>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1465.2 - ₹1482.2</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1499.19</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>98</v>
+        <v>1436.14</v>
       </c>
       <c r="J13" t="n">
-        <v>1440.19</v>
+        <v>1414.83</v>
       </c>
       <c r="K13" t="n">
-        <v>1416.57</v>
+        <v>1396.09</v>
       </c>
       <c r="L13" t="n">
-        <v>1395.71</v>
+        <v>5.04</v>
       </c>
       <c r="M13" t="n">
-        <v>5.55</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>10.35</v>
+        <v>6.31</v>
       </c>
       <c r="O13" t="n">
-        <v>7.12</v>
+        <v>1.82</v>
       </c>
       <c r="P13" t="n">
-        <v>3.23</v>
+        <v>34.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>33.99</v>
+        <v>11.76</v>
       </c>
       <c r="R13" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S13" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.23</v>
-      </c>
+        <v>46.8</v>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>-1.65</v>
+        <v>45</v>
       </c>
       <c r="V13" t="n">
-        <v>45</v>
+        <v>11.8</v>
       </c>
       <c r="W13" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="X13" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1431.22</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1442.78</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1483.78</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1421.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1470.3</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1482.3</v>
-      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
-        <v>1492.6</v>
+        <v>56.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>-0.08</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.15</v>
+        <v>35.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>35.3</v>
+        <v>3.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AL13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AM13" t="n">
         <v>15</v>
       </c>
-      <c r="AN13" t="n">
-        <v>1504.94</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1442.68</v>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,108.72 Cr., a P/E ratio of 35.37, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹118,914.84 Cr., a P/E ratio of 35.31, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.58 (Bullish Momentum Zone), while MACD Line (10.35) trades above Signal (7.12) with an expanding histogram (+3.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.55% above the 200-day DMA (₹1395.71). Daily volatility envelope is bounded by ATR(14) of ₹33.99.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,472.00) is positioned above the 30-day DMA (₹1,440.19), 50-day DMA (₹1,416.57), and 200-day DMA (₹1,395.71). The price distance from 200 DMA is +5.55%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1472.0, 1476.42, 1480.83, 1485.25, 1489.66, 1494.08]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1472.0, 1490.01, 1500.06, 1508.79, 1516.85, 1524.48]</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>[1472.0, 1466.22, 1466.41, 1467.59, 1469.27, 1471.28]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -2665,162 +2312,133 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>257271.4</v>
+        <v>107042.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1093.9</v>
-      </c>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹1087.71 - ₹1103.19</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1118.66</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>107</v>
+        <v>729.51</v>
       </c>
       <c r="J14" t="n">
-        <v>1034.29</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>997.16</v>
+        <v>686.09</v>
       </c>
       <c r="L14" t="n">
-        <v>944.85</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>10.78</v>
+        <v>8.49</v>
       </c>
       <c r="N14" t="n">
-        <v>8.699999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>11.36</v>
+        <v>-0.9</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.65</v>
+        <v>14.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>30.95</v>
+        <v>11.76</v>
       </c>
       <c r="R14" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S14" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.19</v>
-      </c>
+        <v>46.7</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>-1.7</v>
+        <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>56.7</v>
+        <v>6.2</v>
       </c>
       <c r="W14" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="X14" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1072.05</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1110.34</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1102.65</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1047.48</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1080.17</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1108.74</v>
-      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="n">
-        <v>1123.57</v>
+        <v>48.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.04</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.15</v>
+        <v>49.9</v>
       </c>
       <c r="AJ14" t="n">
-        <v>19.3</v>
+        <v>15.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>39.1</v>
+        <v>20.9</v>
       </c>
       <c r="AL14" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1134.67</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1057.43</v>
+        <v>15</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,042.10 Cr., a P/E ratio of 49.90, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹257,271.40 Cr., a P/E ratio of 19.31, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.70 (Consolidation Zone), while MACD Line (8.70) trades below Signal (11.36) with an expanding histogram (-2.65). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹944.85). Daily volatility envelope is bounded by ATR(14) of ₹30.95.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹nan) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,093.90) is positioned above the 30-day DMA (₹1,034.29), 50-day DMA (₹997.16), and 200-day DMA (₹944.85). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[1093.9, 1097.18, 1100.46, 1103.75, 1107.03, 1110.31]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[1093.9, 1109.56, 1117.97, 1125.19, 1131.79, 1137.99]</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>[1093.9, 1087.9, 1087.33, 1087.66, 1088.46, 1089.55]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2450,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2841,153 +2459,124 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17728.42</v>
+        <v>84465.99000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>618.8</v>
-      </c>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹614.54 - ₹625.19</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>635.84</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>156</v>
+        <v>13190.57</v>
       </c>
       <c r="J15" t="n">
-        <v>579.77</v>
+        <v>12605.68</v>
       </c>
       <c r="K15" t="n">
-        <v>544.3099999999999</v>
+        <v>12333.95</v>
       </c>
       <c r="L15" t="n">
-        <v>553.6900000000001</v>
+        <v>16.25</v>
       </c>
       <c r="M15" t="n">
-        <v>10.78</v>
+        <v>477.1</v>
       </c>
       <c r="N15" t="n">
-        <v>15.03</v>
+        <v>503.84</v>
       </c>
       <c r="O15" t="n">
-        <v>16.15</v>
+        <v>-26.74</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.12</v>
+        <v>416</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.3</v>
+        <v>11.76</v>
       </c>
       <c r="R15" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S15" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="T15" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
         <v>0.15</v>
       </c>
-      <c r="U15" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="V15" t="n">
-        <v>55</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>593.24</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>607.6</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>623.75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>586.85</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>620</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>627.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>636.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
-      </c>
       <c r="AI15" t="n">
-        <v>0.15</v>
+        <v>40.7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>89.3</v>
+        <v>21.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>-10.1</v>
+        <v>3.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>649.9</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>590.38</v>
+        <v>15</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹84,465.99 Cr., a P/E ratio of 40.69, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,728.42 Cr., a P/E ratio of 89.29, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.93 (Bullish Momentum Zone), while MACD Line (15.03) trades below Signal (16.15) with an expanding histogram (-1.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹553.69). Daily volatility envelope is bounded by ATR(14) of ₹21.30.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹nan) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹618.80) is positioned above the 30-day DMA (₹579.77), 50-day DMA (₹544.31), and 200-day DMA (₹553.69). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[618.8, 620.66, 622.51, 624.37, 626.23, 628.08]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[618.8, 629.18, 634.56, 639.13, 643.27, 647.13]</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>[618.8, 614.27, 613.48, 613.3, 613.45, 613.79]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -3008,153 +2597,124 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>145119.8</v>
+        <v>146076.52</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1638.5</v>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹1629.33 - ₹1652.26</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1675.2</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>72</v>
+        <v>1478.49</v>
       </c>
       <c r="J16" t="n">
-        <v>1487.74</v>
+        <v>1460.44</v>
       </c>
       <c r="K16" t="n">
-        <v>1465.74</v>
+        <v>1458.79</v>
       </c>
       <c r="L16" t="n">
-        <v>1460.05</v>
+        <v>14.41</v>
       </c>
       <c r="M16" t="n">
-        <v>13.1</v>
+        <v>56.22</v>
       </c>
       <c r="N16" t="n">
-        <v>57.77</v>
+        <v>42.84</v>
       </c>
       <c r="O16" t="n">
-        <v>45.82</v>
+        <v>13.38</v>
       </c>
       <c r="P16" t="n">
-        <v>11.95</v>
+        <v>47.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>45.87</v>
+        <v>11.76</v>
       </c>
       <c r="R16" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S16" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.19</v>
-      </c>
+        <v>45.1</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>-2.03</v>
+        <v>48.3</v>
       </c>
       <c r="V16" t="n">
-        <v>48.3</v>
+        <v>8.18</v>
       </c>
       <c r="W16" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="X16" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1583.45</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1638.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1651.61</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1569.69</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1647.87</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1660.64</v>
-      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>1682.77</v>
+        <v>86.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.06</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.15</v>
+        <v>28.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28.3</v>
+        <v>17.7</v>
       </c>
       <c r="AK16" t="n">
-        <v>17.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AL16" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AM16" t="n">
         <v>15</v>
       </c>
-      <c r="AN16" t="n">
-        <v>1686.05</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1595.19</v>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,076.52 Cr., a P/E ratio of 28.53, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹145,119.80 Cr., a P/E ratio of 28.34, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.82 (Bullish Momentum Zone), while MACD Line (57.77) trades above Signal (45.82) with an expanding histogram (+11.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.10% above the 200-day DMA (₹1460.05). Daily volatility envelope is bounded by ATR(14) of ₹45.87.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,638.50) is positioned above the 30-day DMA (₹1,487.74), 50-day DMA (₹1,465.74), and 200-day DMA (₹1,460.05). The price distance from 200 DMA is +13.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[1638.5, 1643.42, 1648.33, 1653.25, 1658.16, 1663.08]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[1638.5, 1661.76, 1674.28, 1685.03, 1694.86, 1704.11]</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>[1638.5, 1629.65, 1628.87, 1629.41, 1630.64, 1632.31]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -3166,162 +2726,133 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>76558.95</v>
+        <v>285827.48</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1729.4</v>
-      </c>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹1717.8 - ₹1746.8</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1775.81</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>57</v>
+        <v>281.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1511.17</v>
+        <v>268.93</v>
       </c>
       <c r="K17" t="n">
-        <v>1475.45</v>
+        <v>274.01</v>
       </c>
       <c r="L17" t="n">
-        <v>1504.57</v>
+        <v>13.37</v>
       </c>
       <c r="M17" t="n">
-        <v>14.12</v>
+        <v>9.93</v>
       </c>
       <c r="N17" t="n">
-        <v>60.69</v>
+        <v>8.42</v>
       </c>
       <c r="O17" t="n">
-        <v>36.2</v>
+        <v>1.51</v>
       </c>
       <c r="P17" t="n">
-        <v>24.49</v>
+        <v>10.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>58.01</v>
+        <v>11.76</v>
       </c>
       <c r="R17" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S17" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.18</v>
-      </c>
+        <v>43.3</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>-2.15</v>
+        <v>50</v>
       </c>
       <c r="V17" t="n">
-        <v>48.3</v>
+        <v>2.41</v>
       </c>
       <c r="W17" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="X17" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1719.52</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1780.05</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1745.46</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1642.38</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1731.47</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1743.94</v>
-      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>1758.47</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AF17" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.12</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.15</v>
+        <v>690</v>
       </c>
       <c r="AJ17" t="n">
-        <v>35.4</v>
+        <v>182</v>
       </c>
       <c r="AK17" t="n">
-        <v>49.9</v>
+        <v>0.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AM17" t="n">
         <v>15</v>
       </c>
-      <c r="AN17" t="n">
-        <v>1794.82</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1664.13</v>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹285,827.48 Cr., a P/E ratio of 690.00, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹76,558.95 Cr., a P/E ratio of 35.38, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.40 (Bullish Momentum Zone), while MACD Line (60.69) trades above Signal (36.20) with an expanding histogram (+24.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.12% above the 200-day DMA (₹1504.57). Daily volatility envelope is bounded by ATR(14) of ₹58.01.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹nan) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,729.40) is positioned above the 30-day DMA (₹1,511.17), 50-day DMA (₹1,475.45), and 200-day DMA (₹1,504.57). The price distance from 200 DMA is +14.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[1729.4, 1745.46, 1761.51, 1777.57, 1793.63, 1809.69]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[1729.4, 1768.66, 1794.33, 1817.76, 1840.04, 1861.57]</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>[1729.4, 1728.05, 1736.9, 1747.43, 1758.82, 1770.77]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -3333,162 +2864,133 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47081.15</v>
+        <v>62947.18</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1157.1</v>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹1150.19 - ₹1167.46</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1184.74</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>96</v>
+        <v>1999.45</v>
       </c>
       <c r="J18" t="n">
-        <v>1109.24</v>
+        <v>1888.17</v>
       </c>
       <c r="K18" t="n">
-        <v>1105.8</v>
+        <v>1880.41</v>
       </c>
       <c r="L18" t="n">
-        <v>1100.59</v>
+        <v>12.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>62.25</v>
       </c>
       <c r="N18" t="n">
-        <v>9.49</v>
+        <v>68.98</v>
       </c>
       <c r="O18" t="n">
-        <v>5.67</v>
+        <v>-6.73</v>
       </c>
       <c r="P18" t="n">
-        <v>3.82</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.55</v>
+        <v>11.76</v>
       </c>
       <c r="R18" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S18" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.18</v>
-      </c>
+        <v>43.2</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="n">
-        <v>-2.16</v>
+        <v>51.7</v>
       </c>
       <c r="V18" t="n">
-        <v>48.3</v>
+        <v>4.94</v>
       </c>
       <c r="W18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X18" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1142.83</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1183.33</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1166.36</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1105.27</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1150.73</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1164.86</v>
-      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>1172.63</v>
+        <v>48.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="AG18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
         <v>0.15</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
-      </c>
       <c r="AI18" t="n">
-        <v>0.15</v>
+        <v>34</v>
       </c>
       <c r="AJ18" t="n">
-        <v>38.5</v>
+        <v>63</v>
       </c>
       <c r="AK18" t="n">
-        <v>29.9</v>
+        <v>36.1</v>
       </c>
       <c r="AL18" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1193.78</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1123.79</v>
+        <v>10</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹62,947.18 Cr., a P/E ratio of 33.98, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+        </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹47,081.15 Cr., a P/E ratio of 38.45, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.63 (Consolidation Zone), while MACD Line (9.49) trades above Signal (5.67) with an expanding histogram (+3.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.15% above the 200-day DMA (₹1100.59). Daily volatility envelope is bounded by ATR(14) of ₹34.55.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,157.10) is positioned above the 30-day DMA (₹1,109.24), 50-day DMA (₹1,105.80), and 200-day DMA (₹1,100.59). The price distance from 200 DMA is +3.15%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[1157.1, 1160.57, 1164.04, 1167.51, 1170.99, 1174.46]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[1157.1, 1174.39, 1183.59, 1191.45, 1198.63, 1205.36]</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>[1157.1, 1150.21, 1149.38, 1149.56, 1150.26, 1151.28]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -3500,162 +3002,133 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62989.36</v>
+        <v>313655.45</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>2091.1</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>₹2078.32 - ₹2110.28</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>2142.23</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>52</v>
+        <v>4471.9</v>
       </c>
       <c r="J19" t="n">
-        <v>2010.06</v>
+        <v>4404.23</v>
       </c>
       <c r="K19" t="n">
-        <v>1895.79</v>
+        <v>4346.03</v>
       </c>
       <c r="L19" t="n">
-        <v>1880.5</v>
+        <v>5.42</v>
       </c>
       <c r="M19" t="n">
-        <v>11.98</v>
+        <v>56.6</v>
       </c>
       <c r="N19" t="n">
-        <v>59.11</v>
+        <v>49.9</v>
       </c>
       <c r="O19" t="n">
-        <v>67</v>
+        <v>6.7</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.9</v>
+        <v>83.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>63.92</v>
+        <v>11.76</v>
       </c>
       <c r="R19" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S19" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.17</v>
-      </c>
+        <v>41.7</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>-2.29</v>
+        <v>41.7</v>
       </c>
       <c r="V19" t="n">
-        <v>51.7</v>
+        <v>2.29</v>
       </c>
       <c r="W19" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="X19" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y19" t="n">
-        <v>2014.4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1996.91</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2107.83</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1995.22</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2101.93</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2115.76</v>
-      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>2140.43</v>
+        <v>59.3</v>
       </c>
       <c r="AF19" t="n">
-        <v>45</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.2</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.15</v>
+        <v>34.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>34</v>
+        <v>1.8</v>
       </c>
       <c r="AK19" t="n">
-        <v>63</v>
+        <v>27.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2162.91</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>2016.02</v>
+        <v>24</v>
+      </c>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹313,655.45 Cr., a P/E ratio of 34.45, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+        </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹62,989.36 Cr., a P/E ratio of 34.01, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 45.03 (Consolidation Zone), while MACD Line (59.11) trades below Signal (67.00) with an expanding histogram (-7.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.98% above the 200-day DMA (₹1880.50). Daily volatility envelope is bounded by ATR(14) of ₹63.92.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹nan) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,091.10) is positioned above the 30-day DMA (₹2,010.06), 50-day DMA (₹1,895.79), and 200-day DMA (₹1,880.50). The price distance from 200 DMA is +11.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>[2091.1, 2097.37, 2103.65, 2109.92, 2116.19, 2122.47]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>[2091.1, 2122.94, 2139.8, 2154.2, 2167.33, 2179.64]</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>[2091.1, 2078.2, 2076.53, 2076.71, 2077.84, 2079.59]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -3667,162 +3140,133 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>281685.03</v>
+        <v>78267.74000000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>306</v>
-      </c>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>₹303.81 - ₹309.28</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>314.75</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>304</v>
+        <v>1502.49</v>
       </c>
       <c r="J20" t="n">
-        <v>282.98</v>
+        <v>1468.73</v>
       </c>
       <c r="K20" t="n">
-        <v>270.14</v>
+        <v>1504.48</v>
       </c>
       <c r="L20" t="n">
-        <v>273.78</v>
+        <v>15.58</v>
       </c>
       <c r="M20" t="n">
-        <v>10.47</v>
+        <v>53.36</v>
       </c>
       <c r="N20" t="n">
-        <v>9.73</v>
+        <v>30.07</v>
       </c>
       <c r="O20" t="n">
-        <v>8.68</v>
+        <v>23.28</v>
       </c>
       <c r="P20" t="n">
-        <v>1.05</v>
+        <v>59.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.94</v>
+        <v>11.76</v>
       </c>
       <c r="R20" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S20" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="T20" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
         <v>0.15</v>
       </c>
-      <c r="U20" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="V20" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>301.02</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>311.73</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>308.45</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>289.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>304.95</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>309.85</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>313.7</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>62</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
-      </c>
       <c r="AI20" t="n">
-        <v>0.15</v>
+        <v>36.2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>680</v>
+        <v>49.9</v>
       </c>
       <c r="AK20" t="n">
-        <v>182</v>
+        <v>9.6</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AM20" t="n">
         <v>15</v>
       </c>
-      <c r="AN20" t="n">
-        <v>317.76</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>295.12</v>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹78,267.74 Cr., a P/E ratio of 36.17, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹281,685.03 Cr., a P/E ratio of 680.00, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.36) trades above Signal (30.07) with an expanding histogram (+23.28). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1504.48). Daily volatility envelope is bounded by ATR(14) of ₹59.19.</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.99 (Bullish Momentum Zone), while MACD Line (9.73) trades above Signal (8.68) with an expanding histogram (+1.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.47% above the 200-day DMA (₹273.78). Daily volatility envelope is bounded by ATR(14) of ₹10.94.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,502.49), 50-day DMA (₹1,468.73), and 200-day DMA (₹1,504.48). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹306.00) is positioned above the 30-day DMA (₹282.98), 50-day DMA (₹270.14), and 200-day DMA (₹273.78). The price distance from 200 DMA is +10.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>[306.0, 306.92, 307.84, 308.75, 309.67, 310.59]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>[306.0, 311.29, 314.02, 316.33, 318.42, 320.37]</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>[306.0, 303.64, 303.2, 303.07, 303.11, 303.25]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>
@@ -3834,162 +3278,133 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>84733.52</v>
+        <v>46702.74</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>13936</v>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>₹13843.67 - ₹14074.49</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>14305.31</v>
-      </c>
+          <t>₹nan - ₹nan</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>1109.56</v>
       </c>
       <c r="J21" t="n">
-        <v>13241.63</v>
+        <v>1105.35</v>
       </c>
       <c r="K21" t="n">
-        <v>12652.22</v>
+        <v>1100.33</v>
       </c>
       <c r="L21" t="n">
-        <v>12318.23</v>
+        <v>3.87</v>
       </c>
       <c r="M21" t="n">
-        <v>14.05</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>450.74</v>
+        <v>4.71</v>
       </c>
       <c r="O21" t="n">
-        <v>493.22</v>
+        <v>4.42</v>
       </c>
       <c r="P21" t="n">
-        <v>-42.48</v>
+        <v>34.56</v>
       </c>
       <c r="Q21" t="n">
-        <v>461.64</v>
+        <v>11.76</v>
       </c>
       <c r="R21" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="S21" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.16</v>
-      </c>
+        <v>40.1</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
-        <v>-2.39</v>
+        <v>46.7</v>
       </c>
       <c r="V21" t="n">
-        <v>46.7</v>
+        <v>2.47</v>
       </c>
       <c r="W21" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="X21" t="n">
         <v>-0.77</v>
       </c>
-      <c r="Y21" t="n">
-        <v>13382.03</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>13783.45</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>14047.49</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>13243.54</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>13866.67</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>14154.34</v>
-      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>14372.67</v>
+        <v>52.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.96) | LSTM Deep Net</t>
-        </is>
+        <v>0.2</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.15</v>
+        <v>38.1</v>
       </c>
       <c r="AJ21" t="n">
-        <v>40.8</v>
+        <v>29.9</v>
       </c>
       <c r="AK21" t="n">
-        <v>21.1</v>
+        <v>26.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AM21" t="n">
         <v>15</v>
       </c>
-      <c r="AN21" t="n">
-        <v>14444.12</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>13351.05</v>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,702.74 Cr., a P/E ratio of 38.15, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+        </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹84,733.52 Cr., a P/E ratio of 40.82, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.38 (Bullish Momentum Zone), while MACD Line (450.74) trades below Signal (493.22) with an expanding histogram (-42.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.05% above the 200-day DMA (₹12318.23). Daily volatility envelope is bounded by ATR(14) of ₹461.64.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,936.00) is positioned above the 30-day DMA (₹13,241.63), 50-day DMA (₹12,652.22), and 200-day DMA (₹12,318.23). The price distance from 200 DMA is +14.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>[13936.0, 13977.81, 14019.62, 14061.42, 14103.23, 14145.04]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>[13936.0, 14162.47, 14280.76, 14381.26, 14472.55, 14557.95]</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>[13936.0, 13839.32, 13823.76, 13821.55, 13826.25, 13835.36]</t>
+          <t>[nan, nan, nan, nan, nan, nan]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT21"/>
+  <dimension ref="A1:AT20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,7 +651,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -665,84 +665,106 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1047298.52</v>
+        <v>1039049.16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>1448.5</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>₹1443.93 - ₹1455.36</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1466.8</v>
+      </c>
       <c r="I2" t="n">
-        <v>1395.55</v>
+        <v>1398.49</v>
       </c>
       <c r="J2" t="n">
-        <v>1346.57</v>
+        <v>1349.96</v>
       </c>
       <c r="K2" t="n">
-        <v>1336.85</v>
+        <v>1337.12</v>
       </c>
       <c r="L2" t="n">
-        <v>6.36</v>
+        <v>6.45</v>
       </c>
       <c r="M2" t="n">
-        <v>21.72</v>
+        <v>20.38</v>
       </c>
       <c r="N2" t="n">
-        <v>25.48</v>
+        <v>24.46</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.76</v>
+        <v>-4.08</v>
       </c>
       <c r="P2" t="n">
-        <v>24.02</v>
+        <v>22.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R2" t="n">
-        <v>54</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+        <v>54.3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.65</v>
+      </c>
       <c r="U2" t="n">
         <v>60</v>
       </c>
       <c r="V2" t="n">
-        <v>7.01</v>
+        <v>6.34</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>1431.07</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1481.77</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1460.09</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1414.19</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1447.87</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1452.64</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1456.77</v>
+      </c>
       <c r="AE2" t="n">
-        <v>62.2</v>
+        <v>60.1</v>
       </c>
       <c r="AF2" t="n">
         <v>-0.01</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="AJ2" t="n">
         <v>11.4</v>
@@ -753,43 +775,47 @@
       <c r="AL2" t="n">
         <v>16.1</v>
       </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>1474.03</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1422.45</v>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,047,298.52 Cr., a P/E ratio of 18.87, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
+          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,039,049.16 Cr., a P/E ratio of 18.72, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.16 (Bullish Momentum Zone), while MACD Line (21.72) trades below Signal (25.48) with an expanding histogram (-3.76). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.36% above the 200-day DMA (₹1336.85). Daily volatility envelope is bounded by ATR(14) of ₹24.02.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.14 (Bullish Momentum Zone), while MACD Line (20.38) trades below Signal (24.46) with an expanding histogram (-4.08). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.45% above the 200-day DMA (₹1337.12). Daily volatility envelope is bounded by ATR(14) of ₹22.87.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,395.55), 50-day DMA (₹1,346.57), and 200-day DMA (₹1,336.85). The price distance from 200 DMA is +6.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,448.50) is positioned above the 30-day DMA (₹1,398.49), 50-day DMA (₹1,349.96), and 200-day DMA (₹1,337.12). The price distance from 200 DMA is +6.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1448.5, 1452.85, 1457.19, 1461.54, 1465.88, 1470.23]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1448.5, 1461.99, 1470.13, 1477.38, 1484.18, 1490.68]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1448.5, 1445.98, 1447.49, 1449.65, 1452.16, 1454.88]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -803,77 +829,99 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>129870.25</v>
+        <v>130249.52</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>113.33</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>₹112.93 - ₹113.93</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>114.93</v>
+      </c>
       <c r="I3" t="n">
-        <v>107.66</v>
+        <v>107.8</v>
       </c>
       <c r="J3" t="n">
-        <v>106.31</v>
+        <v>106.57</v>
       </c>
       <c r="K3" t="n">
         <v>112.63</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.88</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="N3" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="O3" t="n">
         <v>0.41</v>
       </c>
       <c r="P3" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R3" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+        <v>52.9</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.82</v>
+      </c>
       <c r="U3" t="n">
-        <v>51.7</v>
+        <v>53.3</v>
       </c>
       <c r="V3" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>110.98</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>114.24</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>110.34</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>113.21</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>113.76</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>114.2</v>
+      </c>
       <c r="AE3" t="n">
-        <v>70.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
@@ -891,43 +939,47 @@
       <c r="AL3" t="n">
         <v>15</v>
       </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+      <c r="AM3" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>110.26</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹129,870.25 Cr., a P/E ratio of 5.88, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,249.52 Cr., a P/E ratio of 5.90, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.92 (Bullish Momentum Zone), while MACD Line (1.59) trades above Signal (1.18) with an expanding histogram (+0.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading -0.88% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.19 (Bullish Momentum Zone), while MACD Line (1.69) trades above Signal (1.28) with an expanding histogram (+0.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.07% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.00.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹nan) is positioned above the 30-day DMA (₹107.66), 50-day DMA (₹106.31), and 200-day DMA (₹112.63). The price distance from 200 DMA is -0.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.33) is positioned above the 30-day DMA (₹107.80), 50-day DMA (₹106.57), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.07%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[113.33, 113.67, 114.01, 114.35, 114.69, 115.03]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[113.33, 114.47, 115.14, 115.73, 116.29, 116.81]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[113.33, 113.07, 113.16, 113.31, 113.49, 113.69]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -941,84 +993,106 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>269379.04</v>
+        <v>267480.94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2790.4</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>₹2778.86 - ₹2807.71</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2836.57</v>
+      </c>
       <c r="I4" t="n">
-        <v>2687.86</v>
+        <v>2689.12</v>
       </c>
       <c r="J4" t="n">
-        <v>2678.76</v>
+        <v>2681.37</v>
       </c>
       <c r="K4" t="n">
-        <v>2570.71</v>
+        <v>2572.85</v>
       </c>
       <c r="L4" t="n">
-        <v>6.83</v>
+        <v>6.78</v>
       </c>
       <c r="M4" t="n">
-        <v>16.14</v>
+        <v>18.17</v>
       </c>
       <c r="N4" t="n">
-        <v>10.09</v>
+        <v>11.71</v>
       </c>
       <c r="O4" t="n">
-        <v>6.05</v>
+        <v>6.46</v>
       </c>
       <c r="P4" t="n">
-        <v>58.09</v>
+        <v>57.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R4" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+        <v>54.1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
       <c r="U4" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>2773.76</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2871.43</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2815.62</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2703.83</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2784.13</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2798.16</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2805.93</v>
+      </c>
       <c r="AE4" t="n">
-        <v>62.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AF4" t="n">
         <v>-0.03</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>56.5</v>
+        <v>56.1</v>
       </c>
       <c r="AJ4" t="n">
         <v>17.9</v>
@@ -1029,1014 +1103,1200 @@
       <c r="AL4" t="n">
         <v>15</v>
       </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>2858.81</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2729.1</v>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹269,379.04 Cr., a P/E ratio of 56.51, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹267,480.94 Cr., a P/E ratio of 56.11, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.38 (Bullish Momentum Zone), while MACD Line (16.14) trades above Signal (10.09) with an expanding histogram (+6.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.83% above the 200-day DMA (₹2570.71). Daily volatility envelope is bounded by ATR(14) of ₹58.09.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 68.92 (Bullish Momentum Zone), while MACD Line (18.17) trades above Signal (11.71) with an expanding histogram (+6.46). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.78% above the 200-day DMA (₹2572.85). Daily volatility envelope is bounded by ATR(14) of ₹57.71.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹nan) is positioned above the 30-day DMA (₹2,687.86), 50-day DMA (₹2,678.76), and 200-day DMA (₹2,570.71). The price distance from 200 DMA is +6.83%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,790.40) is positioned above the 30-day DMA (₹2,689.12), 50-day DMA (₹2,681.37), and 200-day DMA (₹2,572.85). The price distance from 200 DMA is +6.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[2790.4, 2815.62, 2840.84, 2866.05, 2891.27, 2916.49]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[2790.4, 2838.7, 2873.48, 2906.04, 2937.44, 2968.11]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[2790.4, 2798.3, 2816.35, 2836.07, 2856.64, 2877.78]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17705.5</v>
+        <v>351709.22</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>11956</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>₹11911.83 - ₹12022.25</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>12132.68</v>
+      </c>
       <c r="I5" t="n">
-        <v>578.01</v>
+        <v>11446.68</v>
       </c>
       <c r="J5" t="n">
-        <v>541.38</v>
+        <v>11281.17</v>
       </c>
       <c r="K5" t="n">
-        <v>553.54</v>
+        <v>11569.56</v>
       </c>
       <c r="L5" t="n">
-        <v>10.74</v>
+        <v>2.88</v>
       </c>
       <c r="M5" t="n">
-        <v>14.56</v>
+        <v>152.76</v>
       </c>
       <c r="N5" t="n">
-        <v>16.43</v>
+        <v>129.95</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.88</v>
+        <v>22.81</v>
       </c>
       <c r="P5" t="n">
-        <v>22.4</v>
+        <v>220.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R5" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+        <v>50.9</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.95</v>
+      </c>
       <c r="U5" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="V5" t="n">
-        <v>4.89</v>
+        <v>2.68</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>11837.36</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>12255.82</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>12051.65</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>11624.73</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>11939.33</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11973.66</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>11991.33</v>
+      </c>
       <c r="AE5" t="n">
-        <v>60.8</v>
+        <v>70.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>89.2</v>
+        <v>41.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-10.1</v>
+        <v>15.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>12222.66</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11695.3</v>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,705.50 Cr., a P/E ratio of 89.18, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹351,709.22 Cr., a P/E ratio of 41.17, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.77 (Bullish Momentum Zone), while MACD Line (14.56) trades below Signal (16.43) with an expanding histogram (-1.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.74% above the 200-day DMA (₹553.54). Daily volatility envelope is bounded by ATR(14) of ₹22.40.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.23 (Bullish Momentum Zone), while MACD Line (152.76) trades above Signal (129.95) with an expanding histogram (+22.81). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.88% above the 200-day DMA (₹11569.56). Daily volatility envelope is bounded by ATR(14) of ₹220.85.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹nan) is positioned above the 30-day DMA (₹578.01), 50-day DMA (₹541.38), and 200-day DMA (₹553.54). The price distance from 200 DMA is +10.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,956.00) is positioned above the 30-day DMA (₹11,446.68), 50-day DMA (₹11,281.17), and 200-day DMA (₹11,569.56). The price distance from 200 DMA is +2.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[11956.0, 12016.7, 12077.4, 12138.1, 12198.8, 12259.5]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[11956.0, 12105.04, 12202.33, 12291.11, 12375.48, 12457.03]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[11956.0, 11950.45, 11983.7, 12023.34, 12066.29, 12111.35]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>354592.07</v>
+        <v>219274.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>7990</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>₹7959.88 - ₹8035.18</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>8110.49</v>
+      </c>
       <c r="I6" t="n">
-        <v>11421.23</v>
+        <v>7447.86</v>
       </c>
       <c r="J6" t="n">
-        <v>11269.86</v>
+        <v>7362.95</v>
       </c>
       <c r="K6" t="n">
-        <v>11569.69</v>
+        <v>7176.17</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4</v>
+        <v>9.16</v>
       </c>
       <c r="M6" t="n">
-        <v>143.27</v>
+        <v>130.62</v>
       </c>
       <c r="N6" t="n">
-        <v>124.24</v>
+        <v>94.11</v>
       </c>
       <c r="O6" t="n">
-        <v>19.02</v>
+        <v>36.5</v>
       </c>
       <c r="P6" t="n">
-        <v>218.17</v>
+        <v>150.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R6" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.98</v>
+      </c>
       <c r="U6" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
       <c r="V6" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>7851.28</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8130.93</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8053.92</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7764.09</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7988</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8026</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>8062</v>
+      </c>
       <c r="AE6" t="n">
-        <v>62.6</v>
+        <v>79</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>41.5</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15.9</v>
+        <v>31.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>9.300000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>8212.709999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7794.35</v>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹354,592.07 Cr., a P/E ratio of 41.50, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹219,274.20 Cr., a P/E ratio of 38.05, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (143.27) trades above Signal (124.24) with an expanding histogram (+19.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.40% above the 200-day DMA (₹11569.69). Daily volatility envelope is bounded by ATR(14) of ₹218.17.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.95 (Bullish Momentum Zone), while MACD Line (130.62) trades above Signal (94.11) with an expanding histogram (+36.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.16% above the 200-day DMA (₹7176.17). Daily volatility envelope is bounded by ATR(14) of ₹150.61.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹nan) is positioned above the 30-day DMA (₹11,421.23), 50-day DMA (₹11,269.86), and 200-day DMA (₹11,569.69). The price distance from 200 DMA is +2.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,990.00) is positioned above the 30-day DMA (₹7,447.86), 50-day DMA (₹7,362.95), and 200-day DMA (₹7,176.17). The price distance from 200 DMA is +9.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[7990.0, 8013.97, 8037.94, 8061.91, 8085.88, 8109.85]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[7990.0, 8074.21, 8123.14, 8166.25, 8206.37, 8244.56]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[7990.0, 7968.79, 7974.04, 7983.65, 7995.51, 8008.82]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>256518.44</v>
+        <v>106508.31</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>748.25</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>₹745.23 - ₹752.78</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>760.33</v>
+      </c>
       <c r="I7" t="n">
-        <v>1032.61</v>
+        <v>730.08</v>
       </c>
       <c r="J7" t="n">
-        <v>994.9400000000001</v>
+        <v>705.51</v>
       </c>
       <c r="K7" t="n">
-        <v>942.9400000000001</v>
+        <v>686.16</v>
       </c>
       <c r="L7" t="n">
-        <v>8.94</v>
+        <v>7.63</v>
       </c>
       <c r="M7" t="n">
-        <v>8.390000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>12.02</v>
+        <v>9.15</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.63</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>31.57</v>
+        <v>15.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R7" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+        <v>50.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1.09</v>
+      </c>
       <c r="U7" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
       <c r="V7" t="n">
-        <v>3.56</v>
+        <v>6.54</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>730.13</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>743.3200000000001</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>754.24</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>725.6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>747.53</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>751.66</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>755.08</v>
+      </c>
       <c r="AE7" t="n">
-        <v>46.1</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.14</v>
+        <v>-0.04</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>19.3</v>
+        <v>49.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>39.1</v>
+        <v>15.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>50.1</v>
+        <v>20.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>765.65</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>728.03</v>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹256,518.44 Cr., a P/E ratio of 19.25, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,508.31 Cr., a P/E ratio of 49.65, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (8.39) trades below Signal (12.02) with an expanding histogram (-3.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.94% above the 200-day DMA (₹942.94). Daily volatility envelope is bounded by ATR(14) of ₹31.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.00 (Consolidation Zone), while MACD Line (8.21) trades below Signal (9.15) with an expanding histogram (-0.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.63% above the 200-day DMA (₹686.16). Daily volatility envelope is bounded by ATR(14) of ₹15.10.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,032.61), 50-day DMA (₹994.94), and 200-day DMA (₹942.94). The price distance from 200 DMA is +8.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹748.25) is positioned above the 30-day DMA (₹730.08), 50-day DMA (₹705.51), and 200-day DMA (₹686.16). The price distance from 200 DMA is +7.63%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[748.25, 750.49, 752.74, 754.98, 757.23, 759.47]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[748.25, 756.53, 761.28, 765.45, 769.31, 772.98]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[748.25, 745.96, 746.33, 747.14, 748.17, 749.34]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>138887</v>
+        <v>67954.77</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>🟡 MODERATE BUY</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>5683.5</v>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>₹5659.55 - ₹5719.43</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5779.3</v>
+      </c>
       <c r="I8" t="n">
-        <v>3594.31</v>
+        <v>5587.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3627.85</v>
+        <v>5491.02</v>
       </c>
       <c r="K8" t="n">
-        <v>3330.53</v>
+        <v>5522.76</v>
       </c>
       <c r="L8" t="n">
-        <v>9.859999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="M8" t="n">
-        <v>22.06</v>
+        <v>60.48</v>
       </c>
       <c r="N8" t="n">
-        <v>10.09</v>
+        <v>53.66</v>
       </c>
       <c r="O8" t="n">
-        <v>11.97</v>
+        <v>6.82</v>
       </c>
       <c r="P8" t="n">
-        <v>97.06999999999999</v>
+        <v>119.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R8" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+        <v>49.7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1.19</v>
+      </c>
       <c r="U8" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V8" t="n">
-        <v>2.18</v>
+        <v>3.12</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>5567.47</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5766.39</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5728.97</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5503.88</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5691.83</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5701.66</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>5719.83</v>
+      </c>
       <c r="AE8" t="n">
-        <v>74.09999999999999</v>
+        <v>61</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.08</v>
+        <v>-0</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>82.3</v>
+        <v>29.5</v>
       </c>
       <c r="AJ8" t="n">
         <v>14.6</v>
       </c>
       <c r="AK8" t="n">
-        <v>9.5</v>
+        <v>15.6</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5811.8</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5557.63</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>SIEMENS operates in the Industrials sector. With an estimated Market Cap of ₹138,887.00 Cr., a P/E ratio of 82.31, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (9.46%), and healthy Return on Equity (15.00%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,954.77 Cr., a P/E ratio of 29.50, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.09 (Bullish Momentum Zone), while MACD Line (22.06) trades above Signal (10.09) with an expanding histogram (+11.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.86% above the 200-day DMA (₹3330.53). Daily volatility envelope is bounded by ATR(14) of ₹97.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.98 (Bullish Momentum Zone), while MACD Line (60.48) trades above Signal (53.66) with an expanding histogram (+6.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹5522.76). Daily volatility envelope is bounded by ATR(14) of ₹119.75.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SIEMENS. Current Market Price (₹nan) is positioned above the 30-day DMA (₹3,594.31), 50-day DMA (₹3,627.85), and 200-day DMA (₹3,330.53). The price distance from 200 DMA is +9.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,683.50) is positioned above the 30-day DMA (₹5,587.60), 50-day DMA (₹5,491.02), and 200-day DMA (₹5,522.76). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[5683.5, 5700.55, 5717.6, 5734.65, 5751.7, 5768.75]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[5683.5, 5748.45, 5785.34, 5817.62, 5847.5, 5875.86]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[5683.5, 5664.63, 5666.8, 5672.43, 5679.85, 5688.42]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>220989.96</v>
+        <v>312291.18</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>4669</v>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>₹4652.29 - ₹4694.06</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>4735.82</v>
+      </c>
       <c r="I9" t="n">
-        <v>7437.81</v>
+        <v>4479.85</v>
       </c>
       <c r="J9" t="n">
-        <v>7344.46</v>
+        <v>4409.79</v>
       </c>
       <c r="K9" t="n">
-        <v>7171.21</v>
+        <v>4345.73</v>
       </c>
       <c r="L9" t="n">
-        <v>9.19</v>
+        <v>6.92</v>
       </c>
       <c r="M9" t="n">
-        <v>121.41</v>
+        <v>59.87</v>
       </c>
       <c r="N9" t="n">
-        <v>84.98999999999999</v>
+        <v>51.89</v>
       </c>
       <c r="O9" t="n">
-        <v>36.42</v>
+        <v>7.98</v>
       </c>
       <c r="P9" t="n">
-        <v>150.57</v>
+        <v>83.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R9" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+        <v>42.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.2</v>
+      </c>
       <c r="U9" t="n">
-        <v>48.3</v>
+        <v>43.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>4568.77</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>4728.97</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4706.35</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4543.71</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4666.33</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4682.66</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4696.33</v>
+      </c>
       <c r="AE9" t="n">
-        <v>74.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Vol Spike 2.7x | Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>38.3</v>
+        <v>34.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>31.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK9" t="n">
-        <v>23.2</v>
+        <v>27.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>4794.15</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4553.76</v>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹220,989.96 Cr., a P/E ratio of 38.34, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹312,291.18 Cr., a P/E ratio of 34.30, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.10 (Bullish Momentum Zone), while MACD Line (121.41) trades above Signal (84.99) with an expanding histogram (+36.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.19% above the 200-day DMA (₹7171.21). Daily volatility envelope is bounded by ATR(14) of ₹150.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.59 (Bullish Momentum Zone), while MACD Line (59.87) trades above Signal (51.89) with an expanding histogram (+7.98). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.92% above the 200-day DMA (₹4345.73). Daily volatility envelope is bounded by ATR(14) of ₹83.53.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹nan) is positioned above the 30-day DMA (₹7,437.81), 50-day DMA (₹7,344.46), and 200-day DMA (₹7,171.21). The price distance from 200 DMA is +9.19%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,669.00) is positioned above the 30-day DMA (₹4,479.85), 50-day DMA (₹4,409.79), and 200-day DMA (₹4,345.73). The price distance from 200 DMA is +6.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[4669.0, 4683.01, 4697.01, 4711.02, 4725.03, 4739.03]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[4669.0, 4716.42, 4744.26, 4768.89, 4791.85, 4813.75]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[4669.0, 4657.95, 4661.58, 4667.62, 4674.91, 4683.0]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68235.74000000001</v>
+        <v>25000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>368</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>₹366.48 - ₹370.28</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>374.09</v>
+      </c>
       <c r="I10" t="n">
-        <v>5575</v>
+        <v>357.93</v>
       </c>
       <c r="J10" t="n">
-        <v>5484.08</v>
+        <v>350.57</v>
       </c>
       <c r="K10" t="n">
-        <v>5521.06</v>
+        <v>347.65</v>
       </c>
       <c r="L10" t="n">
-        <v>5.35</v>
+        <v>7.28</v>
       </c>
       <c r="M10" t="n">
-        <v>57.19</v>
+        <v>4.74</v>
       </c>
       <c r="N10" t="n">
-        <v>51.96</v>
+        <v>2.83</v>
       </c>
       <c r="O10" t="n">
-        <v>5.23</v>
+        <v>1.91</v>
       </c>
       <c r="P10" t="n">
-        <v>122.43</v>
+        <v>7.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R10" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+        <v>45.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.34</v>
+      </c>
       <c r="U10" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="V10" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="X10" t="n">
+        <v>358.87</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>368.64</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>370.94</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>356.58</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>367.83</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>369.73</v>
+      </c>
       <c r="AE10" t="n">
-        <v>58.4</v>
+        <v>81.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>29.6</v>
+        <v>6.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>14.6</v>
+        <v>25.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>15.6</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AL10" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>377.63</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>358.57</v>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,235.74 Cr., a P/E ratio of 29.62, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.06, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 81.18 (Bullish Momentum Zone), while MACD Line (4.74) trades above Signal (2.83) with an expanding histogram (+1.91). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.28% above the 200-day DMA (₹347.65). Daily volatility envelope is bounded by ATR(14) of ₹7.61.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹nan) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹368.00) is positioned above the 30-day DMA (₹357.93), 50-day DMA (₹350.57), and 200-day DMA (₹347.65). The price distance from 200 DMA is +7.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[368.0, 369.1, 370.21, 371.31, 372.42, 373.52]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[368.0, 372.15, 374.51, 376.59, 378.51, 380.33]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[368.0, 366.82, 366.98, 367.36, 367.85, 368.41]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25000</v>
+        <v>104754.01</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>2191.1</v>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>₹2181.64 - ₹2205.29</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2228.95</v>
+      </c>
       <c r="I11" t="n">
-        <v>357.21</v>
+        <v>2146.11</v>
       </c>
       <c r="J11" t="n">
-        <v>349.78</v>
+        <v>2067.23</v>
       </c>
       <c r="K11" t="n">
-        <v>347.56</v>
+        <v>1708.73</v>
       </c>
       <c r="L11" t="n">
-        <v>6.64</v>
+        <v>28.74</v>
       </c>
       <c r="M11" t="n">
-        <v>4.07</v>
+        <v>30.53</v>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>34.42</v>
       </c>
       <c r="O11" t="n">
-        <v>1.72</v>
+        <v>-3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>7.7</v>
+        <v>47.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R11" t="n">
-        <v>47</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+        <v>44.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.45</v>
+      </c>
       <c r="U11" t="n">
         <v>50</v>
       </c>
       <c r="V11" t="n">
-        <v>2.89</v>
+        <v>1.76</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>2160.81</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2237.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2208.63</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2120.14</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2198.67</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2207.34</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2223.57</v>
+      </c>
       <c r="AE11" t="n">
-        <v>78.3</v>
+        <v>58.7</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.1</v>
+        <v>96.7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>25.2</v>
+        <v>17.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>68.90000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AL11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
+        <v>11.6</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>2258.91</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2131.82</v>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.06, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹104,754.01 Cr., a P/E ratio of 96.69, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.30 (Bullish Momentum Zone), while MACD Line (4.07) trades above Signal (2.35) with an expanding histogram (+1.72). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.64% above the 200-day DMA (₹347.56). Daily volatility envelope is bounded by ATR(14) of ₹7.70.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (30.53) trades below Signal (34.42) with an expanding histogram (-3.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +28.74% above the 200-day DMA (₹1708.73). Daily volatility envelope is bounded by ATR(14) of ₹47.31.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹nan) is positioned above the 30-day DMA (₹357.21), 50-day DMA (₹349.78), and 200-day DMA (₹347.56). The price distance from 200 DMA is +6.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,191.10) is positioned above the 30-day DMA (₹2,146.11), 50-day DMA (₹2,067.23), and 200-day DMA (₹1,708.73). The price distance from 200 DMA is +28.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[2191.1, 2197.67, 2204.25, 2210.82, 2217.39, 2223.97]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[2191.1, 2216.6, 2231.01, 2243.6, 2255.24, 2266.28]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[2191.1, 2183.48, 2184.18, 2186.24, 2189.01, 2192.23]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2045,412 +2305,490 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>107099.01</v>
+        <v>117703.06</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>1457</v>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>₹1450.2 - ₹1467.2</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1484.19</v>
+      </c>
       <c r="I12" t="n">
-        <v>1107.18</v>
+        <v>1440.19</v>
       </c>
       <c r="J12" t="n">
-        <v>1063.17</v>
+        <v>1416.57</v>
       </c>
       <c r="K12" t="n">
-        <v>1056.55</v>
+        <v>1395.71</v>
       </c>
       <c r="L12" t="n">
-        <v>6.46</v>
+        <v>5.55</v>
       </c>
       <c r="M12" t="n">
-        <v>8.48</v>
+        <v>10.35</v>
       </c>
       <c r="N12" t="n">
-        <v>9.17</v>
+        <v>7.12</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="P12" t="n">
-        <v>22.56</v>
+        <v>33.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R12" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+        <v>42.7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.66</v>
+      </c>
       <c r="U12" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="V12" t="n">
-        <v>7.65</v>
+        <v>12.85</v>
       </c>
       <c r="W12" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>1416.22</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1426.41</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1468.66</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1406.02</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1460.67</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1465.94</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1474.87</v>
+      </c>
       <c r="AE12" t="n">
-        <v>55.9</v>
+        <v>61.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH12" t="n">
         <v>0.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>74.8</v>
+        <v>34.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>17.2</v>
+        <v>12</v>
       </c>
       <c r="AL12" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1489.15</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1426.99</v>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>MAXHEALTH operates in the Healthcare sector. With an estimated Market Cap of ₹107,099.01 Cr., a P/E ratio of 74.76, and YoY Revenue Growth of +12.2%, the company demonstrates strong institutional backing, solid operating profit margins (17.23%), and healthy Return on Equity (14.33%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,703.06 Cr., a P/E ratio of 34.95, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.85 (Bullish Momentum Zone), while MACD Line (8.48) trades below Signal (9.17) with an expanding histogram (-0.69). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.46% above the 200-day DMA (₹1056.55). Daily volatility envelope is bounded by ATR(14) of ₹22.56.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.58 (Bullish Momentum Zone), while MACD Line (10.35) trades above Signal (7.12) with an expanding histogram (+3.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.55% above the 200-day DMA (₹1395.71). Daily volatility envelope is bounded by ATR(14) of ₹33.99.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MAXHEALTH. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,107.18), 50-day DMA (₹1,063.17), and 200-day DMA (₹1,056.55). The price distance from 200 DMA is +6.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,457.00) is positioned above the 30-day DMA (₹1,440.19), 50-day DMA (₹1,416.57), and 200-day DMA (₹1,395.71). The price distance from 200 DMA is +5.55%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1457.0, 1461.37, 1465.74, 1470.11, 1474.48, 1478.85]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1457.0, 1474.97, 1484.97, 1493.66, 1501.67, 1509.25]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1457.0, 1451.18, 1451.32, 1452.45, 1454.09, 1456.06]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>119108.72</v>
+        <v>255694.89</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1086.7</v>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>₹1080.51 - ₹1095.98</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1111.46</v>
+      </c>
       <c r="I13" t="n">
-        <v>1436.14</v>
+        <v>1034.29</v>
       </c>
       <c r="J13" t="n">
-        <v>1414.83</v>
+        <v>997.16</v>
       </c>
       <c r="K13" t="n">
-        <v>1396.09</v>
+        <v>944.85</v>
       </c>
       <c r="L13" t="n">
-        <v>5.04</v>
+        <v>10.78</v>
       </c>
       <c r="M13" t="n">
-        <v>8.130000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>6.31</v>
+        <v>11.36</v>
       </c>
       <c r="O13" t="n">
-        <v>1.82</v>
+        <v>-2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>34.45</v>
+        <v>30.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R13" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+        <v>49.9</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1.74</v>
+      </c>
       <c r="U13" t="n">
-        <v>45</v>
+        <v>56.7</v>
       </c>
       <c r="V13" t="n">
-        <v>11.8</v>
+        <v>3.86</v>
       </c>
       <c r="W13" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>1062.61</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1100.65</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1095.39</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1040.27</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1083.27</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1090.74</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1094.77</v>
+      </c>
       <c r="AE13" t="n">
-        <v>56.5</v>
+        <v>49.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH13" t="n">
         <v>0.15</v>
       </c>
       <c r="AI13" t="n">
-        <v>35.4</v>
+        <v>19.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.5</v>
+        <v>39.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>12</v>
+        <v>50.1</v>
       </c>
       <c r="AL13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1127.04</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1048.17</v>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹119,108.72 Cr., a P/E ratio of 35.37, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹255,694.89 Cr., a P/E ratio of 19.19, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.53 (Bullish Momentum Zone), while MACD Line (8.13) trades above Signal (6.31) with an expanding histogram (+1.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.04% above the 200-day DMA (₹1396.09). Daily volatility envelope is bounded by ATR(14) of ₹34.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.70 (Consolidation Zone), while MACD Line (8.70) trades below Signal (11.36) with an expanding histogram (-2.65). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹944.85). Daily volatility envelope is bounded by ATR(14) of ₹30.95.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,436.14), 50-day DMA (₹1,414.83), and 200-day DMA (₹1,396.09). The price distance from 200 DMA is +5.04%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,086.70) is positioned above the 30-day DMA (₹1,034.29), 50-day DMA (₹997.16), and 200-day DMA (₹944.85). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1086.7, 1089.96, 1093.22, 1096.48, 1099.74, 1103.0]</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1086.7, 1102.34, 1110.73, 1117.92, 1124.5, 1130.68]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1086.7, 1080.68, 1080.09, 1080.4, 1081.17, 1082.24]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>107042.1</v>
+        <v>77222.99000000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1744.4</v>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>₹1732.8 - ₹1761.8</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1790.81</v>
+      </c>
       <c r="I14" t="n">
-        <v>729.51</v>
+        <v>1511.17</v>
       </c>
       <c r="J14" t="n">
-        <v>703.6799999999999</v>
+        <v>1475.45</v>
       </c>
       <c r="K14" t="n">
-        <v>686.09</v>
+        <v>1504.57</v>
       </c>
       <c r="L14" t="n">
-        <v>9.210000000000001</v>
+        <v>14.12</v>
       </c>
       <c r="M14" t="n">
-        <v>8.49</v>
+        <v>60.69</v>
       </c>
       <c r="N14" t="n">
-        <v>9.380000000000001</v>
+        <v>36.2</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9</v>
+        <v>24.49</v>
       </c>
       <c r="P14" t="n">
-        <v>14.77</v>
+        <v>58.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R14" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+        <v>48.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-2</v>
+      </c>
       <c r="U14" t="n">
-        <v>55</v>
+        <v>48.3</v>
       </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>7.29</v>
       </c>
       <c r="W14" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>1738.72</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1799.77</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1764.89</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1657.38</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1753.93</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1765.26</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1786.13</v>
+      </c>
       <c r="AE14" t="n">
-        <v>48.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH14" t="n">
         <v>0.15</v>
       </c>
       <c r="AI14" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>49.9</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>15.1</v>
-      </c>
       <c r="AK14" t="n">
-        <v>20.9</v>
+        <v>9.6</v>
       </c>
       <c r="AL14" t="n">
         <v>15</v>
       </c>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
+      <c r="AM14" t="n">
+        <v>1814.73</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1677.94</v>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,042.10 Cr., a P/E ratio of 49.90, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹77,222.99 Cr., a P/E ratio of 35.69, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.23 (Consolidation Zone), while MACD Line (8.49) trades below Signal (9.38) with an expanding histogram (-0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.21% above the 200-day DMA (₹686.09). Daily volatility envelope is bounded by ATR(14) of ₹14.77.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.40 (Bullish Momentum Zone), while MACD Line (60.69) trades above Signal (36.20) with an expanding histogram (+24.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.12% above the 200-day DMA (₹1504.57). Daily volatility envelope is bounded by ATR(14) of ₹58.01.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹nan) is positioned above the 30-day DMA (₹729.51), 50-day DMA (₹703.68), and 200-day DMA (₹686.09). The price distance from 200 DMA is +9.21%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,744.40) is positioned above the 30-day DMA (₹1,511.17), 50-day DMA (₹1,475.45), and 200-day DMA (₹1,504.57). The price distance from 200 DMA is +14.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1744.4, 1764.89, 1785.37, 1805.86, 1826.35, 1846.83]</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1744.4, 1788.09, 1818.19, 1846.05, 1872.76, 1898.72]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1744.4, 1747.48, 1760.76, 1775.72, 1791.54, 1807.92]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2459,131 +2797,157 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84465.99000000001</v>
+        <v>17778.55</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>620.55</v>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>₹616.29 - ₹626.94</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>637.59</v>
+      </c>
       <c r="I15" t="n">
-        <v>13190.57</v>
+        <v>579.77</v>
       </c>
       <c r="J15" t="n">
-        <v>12605.68</v>
+        <v>544.3099999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>12333.95</v>
+        <v>553.6900000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>16.25</v>
+        <v>10.78</v>
       </c>
       <c r="M15" t="n">
-        <v>477.1</v>
+        <v>15.03</v>
       </c>
       <c r="N15" t="n">
-        <v>503.84</v>
+        <v>16.15</v>
       </c>
       <c r="O15" t="n">
-        <v>-26.74</v>
+        <v>-1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>416</v>
+        <v>21.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R15" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+        <v>52.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-2.01</v>
+      </c>
       <c r="U15" t="n">
-        <v>46.7</v>
+        <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>7.09</v>
+        <v>4.79</v>
       </c>
       <c r="W15" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>594.99</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>609.58</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>625.51</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>588.6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>618.28</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>624.96</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>629.38</v>
+      </c>
       <c r="AE15" t="n">
-        <v>64.7</v>
+        <v>56.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH15" t="n">
         <v>0.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>40.7</v>
+        <v>89.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21.1</v>
+        <v>-10.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
+        <v>6.7</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>652.5599999999999</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>589.25</v>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹84,465.99 Cr., a P/E ratio of 40.69, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,778.55 Cr., a P/E ratio of 89.55, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.72 (Bullish Momentum Zone), while MACD Line (477.10) trades below Signal (503.84) with an expanding histogram (-26.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.25% above the 200-day DMA (₹12333.95). Daily volatility envelope is bounded by ATR(14) of ₹416.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.93 (Bullish Momentum Zone), while MACD Line (15.03) trades below Signal (16.15) with an expanding histogram (-1.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹553.69). Daily volatility envelope is bounded by ATR(14) of ₹21.30.</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹nan) is positioned above the 30-day DMA (₹13,190.57), 50-day DMA (₹12,605.68), and 200-day DMA (₹12,333.95). The price distance from 200 DMA is +16.25%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹620.55) is positioned above the 30-day DMA (₹579.77), 50-day DMA (₹544.31), and 200-day DMA (₹553.69). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[620.55, 622.41, 624.27, 626.13, 628.0, 629.86]</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[620.55, 630.93, 636.32, 640.89, 645.04, 648.91]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[620.55, 616.02, 615.24, 615.07, 615.22, 615.57]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2597,77 +2961,99 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>146076.52</v>
+        <v>145925.93</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>1647.3</v>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>₹1638.13 - ₹1661.06</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1684</v>
+      </c>
       <c r="I16" t="n">
-        <v>1478.49</v>
+        <v>1487.74</v>
       </c>
       <c r="J16" t="n">
-        <v>1460.44</v>
+        <v>1465.74</v>
       </c>
       <c r="K16" t="n">
-        <v>1458.79</v>
+        <v>1460.05</v>
       </c>
       <c r="L16" t="n">
-        <v>14.41</v>
+        <v>13.1</v>
       </c>
       <c r="M16" t="n">
-        <v>56.22</v>
+        <v>57.77</v>
       </c>
       <c r="N16" t="n">
-        <v>42.84</v>
+        <v>45.82</v>
       </c>
       <c r="O16" t="n">
-        <v>13.38</v>
+        <v>11.95</v>
       </c>
       <c r="P16" t="n">
-        <v>47.45</v>
+        <v>45.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R16" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+        <v>43.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-2.02</v>
+      </c>
       <c r="U16" t="n">
         <v>48.3</v>
       </c>
       <c r="V16" t="n">
-        <v>8.18</v>
+        <v>7.73</v>
       </c>
       <c r="W16" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>1592.25</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1648.98</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1660.48</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1578.49</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1649.83</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1656.46</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1665.63</v>
+      </c>
       <c r="AE16" t="n">
-        <v>86.2</v>
+        <v>77.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH16" t="n">
@@ -2685,181 +3071,211 @@
       <c r="AL16" t="n">
         <v>15</v>
       </c>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
+      <c r="AM16" t="n">
+        <v>1694.76</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1602.78</v>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,076.52 Cr., a P/E ratio of 28.53, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹145,925.93 Cr., a P/E ratio of 28.50, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 86.21 (Bullish Momentum Zone), while MACD Line (56.22) trades above Signal (42.84) with an expanding histogram (+13.38). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.41% above the 200-day DMA (₹1458.79). Daily volatility envelope is bounded by ATR(14) of ₹47.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.82 (Bullish Momentum Zone), while MACD Line (57.77) trades above Signal (45.82) with an expanding histogram (+11.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.10% above the 200-day DMA (₹1460.05). Daily volatility envelope is bounded by ATR(14) of ₹45.87.</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,478.49), 50-day DMA (₹1,460.44), and 200-day DMA (₹1,458.79). The price distance from 200 DMA is +14.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,647.30) is positioned above the 30-day DMA (₹1,487.74), 50-day DMA (₹1,465.74), and 200-day DMA (₹1,460.05). The price distance from 200 DMA is +13.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1647.3, 1652.24, 1657.18, 1662.13, 1667.07, 1672.01]</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1647.3, 1670.59, 1683.13, 1693.91, 1703.76, 1713.04]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1647.3, 1638.48, 1637.72, 1638.29, 1639.54, 1641.24]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>285827.48</v>
+        <v>46971.29</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>1154.2</v>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>₹1147.29 - ₹1164.56</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1181.84</v>
+      </c>
       <c r="I17" t="n">
-        <v>281.7</v>
+        <v>1109.24</v>
       </c>
       <c r="J17" t="n">
-        <v>268.93</v>
+        <v>1105.8</v>
       </c>
       <c r="K17" t="n">
-        <v>274.01</v>
+        <v>1100.59</v>
       </c>
       <c r="L17" t="n">
-        <v>13.37</v>
+        <v>3.15</v>
       </c>
       <c r="M17" t="n">
-        <v>9.93</v>
+        <v>9.49</v>
       </c>
       <c r="N17" t="n">
-        <v>8.42</v>
+        <v>5.67</v>
       </c>
       <c r="O17" t="n">
-        <v>1.51</v>
+        <v>3.82</v>
       </c>
       <c r="P17" t="n">
-        <v>10.28</v>
+        <v>34.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R17" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+        <v>43.9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-2.17</v>
+      </c>
       <c r="U17" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="V17" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="W17" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>1139.35</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1179.75</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1163.43</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1102.37</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1151.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1158.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1163</v>
+      </c>
       <c r="AE17" t="n">
-        <v>65.40000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH17" t="n">
         <v>0.15</v>
       </c>
       <c r="AI17" t="n">
-        <v>690</v>
+        <v>38.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>182</v>
+        <v>29.9</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.6</v>
+        <v>26.5</v>
       </c>
       <c r="AL17" t="n">
         <v>15</v>
       </c>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
+      <c r="AM17" t="n">
+        <v>1189.48</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1122.84</v>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹285,827.48 Cr., a P/E ratio of 690.00, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,971.29 Cr., a P/E ratio of 38.36, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (8.42) with an expanding histogram (+1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.37% above the 200-day DMA (₹274.01). Daily volatility envelope is bounded by ATR(14) of ₹10.28.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.63 (Consolidation Zone), while MACD Line (9.49) trades above Signal (5.67) with an expanding histogram (+3.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.15% above the 200-day DMA (₹1100.59). Daily volatility envelope is bounded by ATR(14) of ₹34.55.</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹nan) is positioned above the 30-day DMA (₹281.70), 50-day DMA (₹268.93), and 200-day DMA (₹274.01). The price distance from 200 DMA is +13.37%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,154.20) is positioned above the 30-day DMA (₹1,109.24), 50-day DMA (₹1,105.80), and 200-day DMA (₹1,100.59). The price distance from 200 DMA is +3.15%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1154.2, 1157.66, 1161.13, 1164.59, 1168.05, 1171.51]</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1154.2, 1171.48, 1180.67, 1188.52, 1195.69, 1202.42]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[1154.2, 1147.3, 1146.47, 1146.64, 1147.32, 1148.34]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2873,84 +3289,106 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>62947.18</v>
+        <v>62432.09</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>2072.6</v>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>₹2059.82 - ₹2091.78</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2123.73</v>
+      </c>
       <c r="I18" t="n">
-        <v>1999.45</v>
+        <v>2010.06</v>
       </c>
       <c r="J18" t="n">
-        <v>1888.17</v>
+        <v>1895.79</v>
       </c>
       <c r="K18" t="n">
-        <v>1880.41</v>
+        <v>1880.5</v>
       </c>
       <c r="L18" t="n">
-        <v>12.26</v>
+        <v>11.98</v>
       </c>
       <c r="M18" t="n">
-        <v>62.25</v>
+        <v>59.11</v>
       </c>
       <c r="N18" t="n">
-        <v>68.98</v>
+        <v>67</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.73</v>
+        <v>-7.9</v>
       </c>
       <c r="P18" t="n">
-        <v>65.31999999999999</v>
+        <v>63.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R18" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+        <v>42.6</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-2.31</v>
+      </c>
       <c r="U18" t="n">
         <v>51.7</v>
       </c>
       <c r="V18" t="n">
-        <v>4.94</v>
+        <v>5.56</v>
       </c>
       <c r="W18" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>1995.9</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1977.22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2089.18</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1976.72</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2068.87</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2091.74</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2110.87</v>
+      </c>
       <c r="AE18" t="n">
-        <v>48.8</v>
+        <v>45</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH18" t="n">
         <v>0.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>34</v>
+        <v>33.7</v>
       </c>
       <c r="AJ18" t="n">
         <v>63</v>
@@ -2961,186 +3399,216 @@
       <c r="AL18" t="n">
         <v>10</v>
       </c>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
+      <c r="AM18" t="n">
+        <v>2149.08</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2003.47</v>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹62,947.18 Cr., a P/E ratio of 33.98, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹62,432.09 Cr., a P/E ratio of 33.71, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.80 (Consolidation Zone), while MACD Line (62.25) trades below Signal (68.98) with an expanding histogram (-6.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1880.41). Daily volatility envelope is bounded by ATR(14) of ₹65.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 45.03 (Consolidation Zone), while MACD Line (59.11) trades below Signal (67.00) with an expanding histogram (-7.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.98% above the 200-day DMA (₹1880.50). Daily volatility envelope is bounded by ATR(14) of ₹63.92.</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,999.45), 50-day DMA (₹1,888.17), and 200-day DMA (₹1,880.41). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,072.60) is positioned above the 30-day DMA (₹2,010.06), 50-day DMA (₹1,895.79), and 200-day DMA (₹1,880.50). The price distance from 200 DMA is +11.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[2072.6, 2078.82, 2085.04, 2091.25, 2097.47, 2103.69]</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[2072.6, 2104.38, 2121.19, 2135.54, 2148.61, 2160.86]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[2072.6, 2059.64, 2057.92, 2058.04, 2059.12, 2060.81]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>313655.45</v>
+        <v>286794.03</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>311.6</v>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>₹309.41 - ₹314.88</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>320.35</v>
+      </c>
       <c r="I19" t="n">
-        <v>4471.9</v>
+        <v>282.98</v>
       </c>
       <c r="J19" t="n">
-        <v>4404.23</v>
+        <v>270.14</v>
       </c>
       <c r="K19" t="n">
-        <v>4346.03</v>
+        <v>273.78</v>
       </c>
       <c r="L19" t="n">
-        <v>5.42</v>
+        <v>10.47</v>
       </c>
       <c r="M19" t="n">
-        <v>56.6</v>
+        <v>9.73</v>
       </c>
       <c r="N19" t="n">
-        <v>49.9</v>
+        <v>8.68</v>
       </c>
       <c r="O19" t="n">
-        <v>6.7</v>
+        <v>1.05</v>
       </c>
       <c r="P19" t="n">
-        <v>83.25</v>
+        <v>10.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R19" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+        <v>48.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-2.33</v>
+      </c>
       <c r="U19" t="n">
-        <v>41.7</v>
+        <v>51.7</v>
       </c>
       <c r="V19" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="W19" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
+      <c r="X19" t="n">
+        <v>307.48</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>318.39</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>314.09</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>310.93</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>312.46</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>313.33</v>
+      </c>
       <c r="AE19" t="n">
-        <v>59.3</v>
+        <v>62</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH19" t="n">
         <v>0.15</v>
       </c>
       <c r="AI19" t="n">
-        <v>34.4</v>
+        <v>692.3</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.8</v>
+        <v>182</v>
       </c>
       <c r="AK19" t="n">
-        <v>27.5</v>
+        <v>0.6</v>
       </c>
       <c r="AL19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>322.51</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>300.96</v>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹313,655.45 Cr., a P/E ratio of 34.45, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹286,794.03 Cr., a P/E ratio of 692.33, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.26 (Bullish Momentum Zone), while MACD Line (56.60) trades above Signal (49.90) with an expanding histogram (+6.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.42% above the 200-day DMA (₹4346.03). Daily volatility envelope is bounded by ATR(14) of ₹83.25.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.99 (Bullish Momentum Zone), while MACD Line (9.73) trades above Signal (8.68) with an expanding histogram (+1.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.47% above the 200-day DMA (₹273.78). Daily volatility envelope is bounded by ATR(14) of ₹10.94.</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹nan) is positioned above the 30-day DMA (₹4,471.90), 50-day DMA (₹4,404.23), and 200-day DMA (₹4,346.03). The price distance from 200 DMA is +5.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹311.60) is positioned above the 30-day DMA (₹282.98), 50-day DMA (₹270.14), and 200-day DMA (₹273.78). The price distance from 200 DMA is +10.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[311.6, 312.53, 313.47, 314.4, 315.34, 316.27]</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[311.6, 316.91, 319.66, 321.98, 324.09, 326.06]</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[311.6, 309.25, 308.83, 308.72, 308.78, 308.94]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3149,262 +3617,150 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78267.74000000001</v>
+        <v>84490.31</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>13896</v>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>₹13803.67 - ₹14034.49</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>14265.31</v>
+      </c>
       <c r="I20" t="n">
-        <v>1502.49</v>
+        <v>13241.63</v>
       </c>
       <c r="J20" t="n">
-        <v>1468.73</v>
+        <v>12652.22</v>
       </c>
       <c r="K20" t="n">
-        <v>1504.48</v>
+        <v>12318.23</v>
       </c>
       <c r="L20" t="n">
-        <v>15.58</v>
+        <v>14.05</v>
       </c>
       <c r="M20" t="n">
-        <v>53.36</v>
+        <v>450.74</v>
       </c>
       <c r="N20" t="n">
-        <v>30.07</v>
+        <v>493.22</v>
       </c>
       <c r="O20" t="n">
-        <v>23.28</v>
+        <v>-42.48</v>
       </c>
       <c r="P20" t="n">
-        <v>59.19</v>
+        <v>461.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.76</v>
+        <v>12.03</v>
       </c>
       <c r="R20" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+        <v>44.7</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-2.4</v>
+      </c>
       <c r="U20" t="n">
-        <v>48.3</v>
+        <v>46.7</v>
       </c>
       <c r="V20" t="n">
-        <v>7.69</v>
+        <v>6.25</v>
       </c>
       <c r="W20" t="n">
         <v>-0.77</v>
       </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
+      <c r="X20" t="n">
+        <v>13342.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13734.17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>14007.17</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>13203.54</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>13905.33</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>13943.66</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>13991.33</v>
+      </c>
       <c r="AE20" t="n">
-        <v>77.3</v>
+        <v>58.4</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.03) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH20" t="n">
         <v>0.15</v>
       </c>
       <c r="AI20" t="n">
-        <v>36.2</v>
+        <v>40.7</v>
       </c>
       <c r="AJ20" t="n">
-        <v>49.9</v>
+        <v>21.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="AL20" t="n">
         <v>15</v>
       </c>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
+      <c r="AM20" t="n">
+        <v>14414.15</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>13368.24</v>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹78,267.74 Cr., a P/E ratio of 36.17, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹84,490.31 Cr., a P/E ratio of 40.70, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.31 (Bullish Momentum Zone), while MACD Line (53.36) trades above Signal (30.07) with an expanding histogram (+23.28). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.58% above the 200-day DMA (₹1504.48). Daily volatility envelope is bounded by ATR(14) of ₹59.19.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.38 (Bullish Momentum Zone), while MACD Line (450.74) trades below Signal (493.22) with an expanding histogram (-42.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.05% above the 200-day DMA (₹12318.23). Daily volatility envelope is bounded by ATR(14) of ₹461.64.</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,502.49), 50-day DMA (₹1,468.73), and 200-day DMA (₹1,504.48). The price distance from 200 DMA is +15.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,896.00) is positioned above the 30-day DMA (₹13,241.63), 50-day DMA (₹12,652.22), and 200-day DMA (₹12,318.23). The price distance from 200 DMA is +14.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[13896.0, 13937.69, 13979.38, 14021.06, 14062.75, 14104.44]</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[13896.0, 14122.35, 14240.52, 14340.9, 14432.07, 14517.35]</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>360ONE</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>46702.74</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>₹nan - ₹nan</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
-        <v>1109.56</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1105.35</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1100.33</v>
-      </c>
-      <c r="L21" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="M21" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="P21" t="n">
-        <v>34.56</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="R21" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="V21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.76) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,702.74 Cr., a P/E ratio of 38.15, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹nan) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>[nan, nan, nan, nan, nan, nan]</t>
+          <t>[13896.0, 13799.2, 13783.52, 13781.19, 13785.77, 13794.76]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1039049.16</v>
+        <v>1036466.83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -673,15 +673,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1448.5</v>
+        <v>1444.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹1443.93 - ₹1455.36</t>
+          <t>₹1440.33 - ₹1451.76</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1466.8</v>
+        <v>1463.2</v>
       </c>
       <c r="I2" t="n">
         <v>1398.49</v>
@@ -708,10 +708,10 @@
         <v>22.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R2" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="S2" t="n">
         <v>0.34</v>
@@ -729,25 +729,25 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>1431.07</v>
+        <v>1426.82</v>
       </c>
       <c r="Y2" t="n">
-        <v>1481.77</v>
+        <v>1477.39</v>
       </c>
       <c r="Z2" t="n">
-        <v>1460.09</v>
+        <v>1456.46</v>
       </c>
       <c r="AA2" t="n">
-        <v>1414.19</v>
+        <v>1410.59</v>
       </c>
       <c r="AB2" t="n">
-        <v>1447.87</v>
+        <v>1447.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>1452.64</v>
+        <v>1451.16</v>
       </c>
       <c r="AD2" t="n">
-        <v>1456.77</v>
+        <v>1457.43</v>
       </c>
       <c r="AE2" t="n">
         <v>60.1</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
@@ -776,14 +776,14 @@
         <v>16.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1474.03</v>
+        <v>1470.78</v>
       </c>
       <c r="AN2" t="n">
-        <v>1422.45</v>
+        <v>1418.03</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,039,049.16 Cr., a P/E ratio of 18.72, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
+          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,036,466.83 Cr., a P/E ratio of 18.68, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -793,22 +793,22 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,448.50) is positioned above the 30-day DMA (₹1,398.49), 50-day DMA (₹1,349.96), and 200-day DMA (₹1,337.12). The price distance from 200 DMA is +6.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,444.90) is positioned above the 30-day DMA (₹1,398.49), 50-day DMA (₹1,349.96), and 200-day DMA (₹1,337.12). The price distance from 200 DMA is +6.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[1448.5, 1452.85, 1457.19, 1461.54, 1465.88, 1470.23]</t>
+          <t>[1444.9, 1449.23, 1453.57, 1457.9, 1462.24, 1466.57]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[1448.5, 1461.99, 1470.13, 1477.38, 1484.18, 1490.68]</t>
+          <t>[1444.9, 1458.38, 1466.51, 1473.75, 1480.54, 1487.03]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[1448.5, 1445.98, 1447.49, 1449.65, 1452.16, 1454.88]</t>
+          <t>[1444.9, 1442.37, 1443.87, 1446.02, 1448.52, 1451.23]</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>130249.52</v>
+        <v>130502.37</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -837,15 +837,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>113.33</v>
+        <v>113.55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹112.93 - ₹113.93</t>
+          <t>₹113.15 - ₹114.15</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>114.93</v>
+        <v>115.15</v>
       </c>
       <c r="I3" t="n">
         <v>107.8</v>
@@ -872,7 +872,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R3" t="n">
         <v>52.9</v>
@@ -893,25 +893,25 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>110.98</v>
+        <v>111.23</v>
       </c>
       <c r="Y3" t="n">
-        <v>114.95</v>
+        <v>115.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>114.24</v>
+        <v>114.46</v>
       </c>
       <c r="AA3" t="n">
-        <v>110.34</v>
+        <v>110.56</v>
       </c>
       <c r="AB3" t="n">
-        <v>113.21</v>
+        <v>113.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>113.76</v>
+        <v>114.16</v>
       </c>
       <c r="AD3" t="n">
-        <v>114.2</v>
+        <v>114.76</v>
       </c>
       <c r="AE3" t="n">
         <v>71.2</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
@@ -940,14 +940,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>116.45</v>
+        <v>117.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>110.26</v>
+        <v>110.28</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,249.52 Cr., a P/E ratio of 5.90, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,502.37 Cr., a P/E ratio of 5.91, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -957,22 +957,22 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.33) is positioned above the 30-day DMA (₹107.80), 50-day DMA (₹106.57), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.07%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.55) is positioned above the 30-day DMA (₹107.80), 50-day DMA (₹106.57), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.07%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[113.33, 113.67, 114.01, 114.35, 114.69, 115.03]</t>
+          <t>[113.55, 113.89, 114.23, 114.57, 114.91, 115.25]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[113.33, 114.47, 115.14, 115.73, 116.29, 116.81]</t>
+          <t>[113.55, 114.69, 115.36, 115.95, 116.51, 117.04]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[113.33, 113.07, 113.16, 113.31, 113.49, 113.69]</t>
+          <t>[113.55, 113.29, 113.38, 113.53, 113.72, 113.91]</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>267480.94</v>
+        <v>268075.27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1001,15 +1001,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2790.4</v>
+        <v>2796.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹2778.86 - ₹2807.71</t>
+          <t>₹2784.86 - ₹2813.71</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2836.57</v>
+        <v>2842.57</v>
       </c>
       <c r="I4" t="n">
         <v>2689.12</v>
@@ -1036,16 +1036,16 @@
         <v>57.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R4" t="n">
-        <v>54.1</v>
+        <v>54</v>
       </c>
       <c r="S4" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.92</v>
       </c>
       <c r="U4" t="n">
         <v>56.7</v>
@@ -1057,25 +1057,25 @@
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2773.76</v>
+        <v>2780.55</v>
       </c>
       <c r="Y4" t="n">
-        <v>2871.43</v>
+        <v>2878.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>2815.62</v>
+        <v>2822.49</v>
       </c>
       <c r="AA4" t="n">
-        <v>2703.83</v>
+        <v>2709.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>2784.13</v>
+        <v>2791.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>2798.16</v>
+        <v>2812.44</v>
       </c>
       <c r="AD4" t="n">
-        <v>2805.93</v>
+        <v>2828.47</v>
       </c>
       <c r="AE4" t="n">
         <v>68.90000000000001</v>
@@ -1085,14 +1085,14 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="AJ4" t="n">
         <v>17.9</v>
@@ -1104,14 +1104,14 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2858.81</v>
+        <v>2865.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>2729.1</v>
+        <v>2733.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹267,480.94 Cr., a P/E ratio of 56.11, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹268,075.27 Cr., a P/E ratio of 56.23, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1121,22 +1121,22 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,790.40) is positioned above the 30-day DMA (₹2,689.12), 50-day DMA (₹2,681.37), and 200-day DMA (₹2,572.85). The price distance from 200 DMA is +6.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,796.40) is positioned above the 30-day DMA (₹2,689.12), 50-day DMA (₹2,681.37), and 200-day DMA (₹2,572.85). The price distance from 200 DMA is +6.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[2790.4, 2815.62, 2840.84, 2866.05, 2891.27, 2916.49]</t>
+          <t>[2796.4, 2822.49, 2848.59, 2874.68, 2900.78, 2926.88]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[2790.4, 2838.7, 2873.48, 2906.04, 2937.44, 2968.11]</t>
+          <t>[2796.4, 2845.58, 2881.24, 2914.67, 2946.95, 2978.5]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[2790.4, 2798.3, 2816.35, 2836.07, 2856.64, 2877.78]</t>
+          <t>[2796.4, 2805.18, 2824.1, 2844.7, 2866.15, 2888.16]</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>351709.22</v>
+        <v>352650.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1165,15 +1165,15 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11956</v>
+        <v>11988</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹11911.83 - ₹12022.25</t>
+          <t>₹11943.83 - ₹12054.25</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12132.68</v>
+        <v>12164.68</v>
       </c>
       <c r="I5" t="n">
         <v>11446.68</v>
@@ -1200,7 +1200,7 @@
         <v>220.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R5" t="n">
         <v>50.9</v>
@@ -1221,25 +1221,25 @@
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>11837.36</v>
+        <v>11870.24</v>
       </c>
       <c r="Y5" t="n">
-        <v>12255.82</v>
+        <v>12289.82</v>
       </c>
       <c r="Z5" t="n">
-        <v>12051.65</v>
+        <v>12083.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>11624.73</v>
+        <v>11656.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>11939.33</v>
+        <v>11964.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>11973.66</v>
+        <v>12023.66</v>
       </c>
       <c r="AD5" t="n">
-        <v>11991.33</v>
+        <v>12059.33</v>
       </c>
       <c r="AE5" t="n">
         <v>70.2</v>
@@ -1249,14 +1249,14 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="AJ5" t="n">
         <v>15.9</v>
@@ -1268,14 +1268,14 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>12222.66</v>
+        <v>12264.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>11695.3</v>
+        <v>11741.41</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹351,709.22 Cr., a P/E ratio of 41.17, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹352,650.55 Cr., a P/E ratio of 41.28, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,956.00) is positioned above the 30-day DMA (₹11,446.68), 50-day DMA (₹11,281.17), and 200-day DMA (₹11,569.56). The price distance from 200 DMA is +2.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,988.00) is positioned above the 30-day DMA (₹11,446.68), 50-day DMA (₹11,281.17), and 200-day DMA (₹11,569.56). The price distance from 200 DMA is +2.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[11956.0, 12016.7, 12077.4, 12138.1, 12198.8, 12259.5]</t>
+          <t>[11988.0, 12050.06, 12112.12, 12174.18, 12236.24, 12298.29]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[11956.0, 12105.04, 12202.33, 12291.11, 12375.48, 12457.03]</t>
+          <t>[11988.0, 12138.4, 12237.05, 12327.18, 12412.91, 12495.83]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[11956.0, 11950.45, 11983.7, 12023.34, 12066.29, 12111.35]</t>
+          <t>[11988.0, 11983.8, 12018.42, 12059.42, 12103.73, 12150.15]</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>219274.2</v>
+        <v>218299.66</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1329,15 +1329,15 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7990</v>
+        <v>7952</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹7959.88 - ₹8035.18</t>
+          <t>₹7921.88 - ₹7997.18</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8110.49</v>
+        <v>8072.49</v>
       </c>
       <c r="I6" t="n">
         <v>7447.86</v>
@@ -1364,46 +1364,46 @@
         <v>150.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R6" t="n">
-        <v>51</v>
+        <v>51.4</v>
       </c>
       <c r="S6" t="n">
         <v>0.28</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.98</v>
+        <v>-0.97</v>
       </c>
       <c r="U6" t="n">
         <v>50</v>
       </c>
       <c r="V6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>7851.28</v>
+        <v>7807.39</v>
       </c>
       <c r="Y6" t="n">
-        <v>8130.93</v>
+        <v>8085.71</v>
       </c>
       <c r="Z6" t="n">
-        <v>8053.92</v>
+        <v>8015.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>7764.09</v>
+        <v>7726.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>7988</v>
+        <v>7971.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>8026</v>
+        <v>8004.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>8062</v>
+        <v>8057.33</v>
       </c>
       <c r="AE6" t="n">
         <v>79</v>
@@ -1413,14 +1413,14 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="AJ6" t="n">
         <v>31.5</v>
@@ -1432,14 +1432,14 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>8212.709999999999</v>
+        <v>8184.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>7794.35</v>
+        <v>7755.87</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹219,274.20 Cr., a P/E ratio of 38.05, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹218,299.66 Cr., a P/E ratio of 37.88, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1449,22 +1449,22 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,990.00) is positioned above the 30-day DMA (₹7,447.86), 50-day DMA (₹7,362.95), and 200-day DMA (₹7,176.17). The price distance from 200 DMA is +9.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,952.00) is positioned above the 30-day DMA (₹7,447.86), 50-day DMA (₹7,362.95), and 200-day DMA (₹7,176.17). The price distance from 200 DMA is +9.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[7990.0, 8013.97, 8037.94, 8061.91, 8085.88, 8109.85]</t>
+          <t>[7952.0, 7975.86, 7999.71, 8023.57, 8047.42, 8071.28]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[7990.0, 8074.21, 8123.14, 8166.25, 8206.37, 8244.56]</t>
+          <t>[7952.0, 8036.1, 8084.91, 8127.91, 8167.91, 8205.99]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[7990.0, 7968.79, 7974.04, 7983.65, 7995.51, 8008.82]</t>
+          <t>[7952.0, 7930.67, 7935.81, 7945.31, 7957.06, 7970.25]</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>106508.31</v>
+        <v>106102.64</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1493,15 +1493,15 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>748.25</v>
+        <v>745.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹745.23 - ₹752.78</t>
+          <t>₹742.38 - ₹749.93</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>760.33</v>
+        <v>757.48</v>
       </c>
       <c r="I7" t="n">
         <v>730.08</v>
@@ -1528,46 +1528,46 @@
         <v>15.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R7" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="S7" t="n">
         <v>0.26</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.09</v>
+        <v>-1.08</v>
       </c>
       <c r="U7" t="n">
         <v>56.7</v>
       </c>
       <c r="V7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>730.13</v>
+        <v>727.28</v>
       </c>
       <c r="Y7" t="n">
-        <v>743.3200000000001</v>
+        <v>739.98</v>
       </c>
       <c r="Z7" t="n">
-        <v>754.24</v>
+        <v>751.36</v>
       </c>
       <c r="AA7" t="n">
-        <v>725.6</v>
+        <v>722.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>747.53</v>
+        <v>746.58</v>
       </c>
       <c r="AC7" t="n">
-        <v>751.66</v>
+        <v>749.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>755.08</v>
+        <v>754.13</v>
       </c>
       <c r="AE7" t="n">
         <v>50</v>
@@ -1577,14 +1577,14 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="AJ7" t="n">
         <v>15.1</v>
@@ -1596,14 +1596,14 @@
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>765.65</v>
+        <v>763.46</v>
       </c>
       <c r="AN7" t="n">
-        <v>728.03</v>
+        <v>726.74</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,508.31 Cr., a P/E ratio of 49.65, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,102.64 Cr., a P/E ratio of 49.46, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1613,22 +1613,22 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹748.25) is positioned above the 30-day DMA (₹730.08), 50-day DMA (₹705.51), and 200-day DMA (₹686.16). The price distance from 200 DMA is +7.63%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹745.40) is positioned above the 30-day DMA (₹730.08), 50-day DMA (₹705.51), and 200-day DMA (₹686.16). The price distance from 200 DMA is +7.63%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[748.25, 750.49, 752.74, 754.98, 757.23, 759.47]</t>
+          <t>[745.4, 747.64, 749.87, 752.11, 754.34, 756.58]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[748.25, 756.53, 761.28, 765.45, 769.31, 772.98]</t>
+          <t>[745.4, 753.68, 758.41, 762.57, 766.42, 770.09]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[748.25, 745.96, 746.33, 747.14, 748.17, 749.34]</t>
+          <t>[745.4, 743.11, 743.47, 744.26, 745.28, 746.45]</t>
         </is>
       </c>
     </row>
@@ -1640,159 +1640,159 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>67954.77</v>
+        <v>312919.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5683.5</v>
+        <v>4679</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹5659.55 - ₹5719.43</t>
+          <t>₹4662.29 - ₹4704.06</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5779.3</v>
+        <v>4745.82</v>
       </c>
       <c r="I8" t="n">
-        <v>5587.6</v>
+        <v>4479.85</v>
       </c>
       <c r="J8" t="n">
-        <v>5491.02</v>
+        <v>4409.79</v>
       </c>
       <c r="K8" t="n">
-        <v>5522.76</v>
+        <v>4345.73</v>
       </c>
       <c r="L8" t="n">
-        <v>4.14</v>
+        <v>6.92</v>
       </c>
       <c r="M8" t="n">
-        <v>60.48</v>
+        <v>59.87</v>
       </c>
       <c r="N8" t="n">
-        <v>53.66</v>
+        <v>51.89</v>
       </c>
       <c r="O8" t="n">
-        <v>6.82</v>
+        <v>7.98</v>
       </c>
       <c r="P8" t="n">
-        <v>119.75</v>
+        <v>83.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R8" t="n">
-        <v>49.7</v>
+        <v>43.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.19</v>
+        <v>-1.18</v>
       </c>
       <c r="U8" t="n">
-        <v>51.7</v>
+        <v>43.3</v>
       </c>
       <c r="V8" t="n">
-        <v>3.12</v>
+        <v>2.31</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>5567.47</v>
+        <v>4578.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>5766.39</v>
+        <v>4740.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>5728.97</v>
+        <v>4716.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>5503.88</v>
+        <v>4553.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>5691.83</v>
+        <v>4682.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>5701.66</v>
+        <v>4714.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>5719.83</v>
+        <v>4750.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>61</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0</v>
+        <v>0.26</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>29.5</v>
+        <v>34.4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14.6</v>
+        <v>1.8</v>
       </c>
       <c r="AK8" t="n">
-        <v>15.6</v>
+        <v>27.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>17.6</v>
+        <v>24</v>
       </c>
       <c r="AM8" t="n">
-        <v>5811.8</v>
+        <v>4800.69</v>
       </c>
       <c r="AN8" t="n">
-        <v>5557.63</v>
+        <v>4552.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,954.77 Cr., a P/E ratio of 29.50, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹312,919.80 Cr., a P/E ratio of 34.37, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.98 (Bullish Momentum Zone), while MACD Line (60.48) trades above Signal (53.66) with an expanding histogram (+6.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹5522.76). Daily volatility envelope is bounded by ATR(14) of ₹119.75.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.59 (Bullish Momentum Zone), while MACD Line (59.87) trades above Signal (51.89) with an expanding histogram (+7.98). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.92% above the 200-day DMA (₹4345.73). Daily volatility envelope is bounded by ATR(14) of ₹83.53.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,683.50) is positioned above the 30-day DMA (₹5,587.60), 50-day DMA (₹5,491.02), and 200-day DMA (₹5,522.76). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,679.00) is positioned above the 30-day DMA (₹4,479.85), 50-day DMA (₹4,409.79), and 200-day DMA (₹4,345.73). The price distance from 200 DMA is +6.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[5683.5, 5700.55, 5717.6, 5734.65, 5751.7, 5768.75]</t>
+          <t>[4679.0, 4693.04, 4707.07, 4721.11, 4735.15, 4749.18]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[5683.5, 5748.45, 5785.34, 5817.62, 5847.5, 5875.86]</t>
+          <t>[4679.0, 4726.45, 4754.32, 4778.98, 4801.97, 4823.9]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[5683.5, 5664.63, 5666.8, 5672.43, 5679.85, 5688.42]</t>
+          <t>[4679.0, 4667.98, 4671.64, 4677.71, 4685.03, 4693.15]</t>
         </is>
       </c>
     </row>
@@ -1804,159 +1804,159 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>312291.18</v>
+        <v>67984.66</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4669</v>
+        <v>5686</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹4652.29 - ₹4694.06</t>
+          <t>₹5662.05 - ₹5721.93</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4735.82</v>
+        <v>5781.8</v>
       </c>
       <c r="I9" t="n">
-        <v>4479.85</v>
+        <v>5587.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4409.79</v>
+        <v>5491.02</v>
       </c>
       <c r="K9" t="n">
-        <v>4345.73</v>
+        <v>5522.76</v>
       </c>
       <c r="L9" t="n">
-        <v>6.92</v>
+        <v>4.14</v>
       </c>
       <c r="M9" t="n">
-        <v>59.87</v>
+        <v>60.48</v>
       </c>
       <c r="N9" t="n">
-        <v>51.89</v>
+        <v>53.66</v>
       </c>
       <c r="O9" t="n">
-        <v>7.98</v>
+        <v>6.82</v>
       </c>
       <c r="P9" t="n">
-        <v>83.53</v>
+        <v>119.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R9" t="n">
-        <v>42.5</v>
+        <v>49.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="T9" t="n">
         <v>-1.2</v>
       </c>
       <c r="U9" t="n">
-        <v>43.3</v>
+        <v>51.7</v>
       </c>
       <c r="V9" t="n">
-        <v>2.31</v>
+        <v>3.13</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>4568.77</v>
+        <v>5570.27</v>
       </c>
       <c r="Y9" t="n">
-        <v>4728.97</v>
+        <v>5769.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>4706.35</v>
+        <v>5731.49</v>
       </c>
       <c r="AA9" t="n">
-        <v>4543.71</v>
+        <v>5506.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>4666.33</v>
+        <v>5691.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>4682.66</v>
+        <v>5704.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>4696.33</v>
+        <v>5723</v>
       </c>
       <c r="AE9" t="n">
-        <v>64.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.26</v>
+        <v>-0</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>34.3</v>
+        <v>29.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.8</v>
+        <v>14.6</v>
       </c>
       <c r="AK9" t="n">
-        <v>27.5</v>
+        <v>15.6</v>
       </c>
       <c r="AL9" t="n">
-        <v>24</v>
+        <v>17.6</v>
       </c>
       <c r="AM9" t="n">
-        <v>4794.15</v>
+        <v>5812.74</v>
       </c>
       <c r="AN9" t="n">
-        <v>4553.76</v>
+        <v>5564.44</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹312,291.18 Cr., a P/E ratio of 34.30, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,984.66 Cr., a P/E ratio of 29.51, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.59 (Bullish Momentum Zone), while MACD Line (59.87) trades above Signal (51.89) with an expanding histogram (+7.98). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.92% above the 200-day DMA (₹4345.73). Daily volatility envelope is bounded by ATR(14) of ₹83.53.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.98 (Bullish Momentum Zone), while MACD Line (60.48) trades above Signal (53.66) with an expanding histogram (+6.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹5522.76). Daily volatility envelope is bounded by ATR(14) of ₹119.75.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,669.00) is positioned above the 30-day DMA (₹4,479.85), 50-day DMA (₹4,409.79), and 200-day DMA (₹4,345.73). The price distance from 200 DMA is +6.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,686.00) is positioned above the 30-day DMA (₹5,587.60), 50-day DMA (₹5,491.02), and 200-day DMA (₹5,522.76). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[4669.0, 4683.01, 4697.01, 4711.02, 4725.03, 4739.03]</t>
+          <t>[5686.0, 5703.06, 5720.12, 5737.17, 5754.23, 5771.29]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[4669.0, 4716.42, 4744.26, 4768.89, 4791.85, 4813.75]</t>
+          <t>[5686.0, 5750.96, 5787.86, 5820.14, 5850.03, 5878.4]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[4669.0, 4657.95, 4661.58, 4667.62, 4674.91, 4683.0]</t>
+          <t>[5686.0, 5667.13, 5669.31, 5674.95, 5682.38, 5690.96]</t>
         </is>
       </c>
     </row>
@@ -1985,15 +1985,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>368</v>
+        <v>369.75</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹366.48 - ₹370.28</t>
+          <t>₹368.23 - ₹372.03</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>374.09</v>
+        <v>375.84</v>
       </c>
       <c r="I10" t="n">
         <v>357.93</v>
@@ -2020,7 +2020,7 @@
         <v>7.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R10" t="n">
         <v>45.2</v>
@@ -2029,37 +2029,37 @@
         <v>0.26</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.34</v>
+        <v>-1.33</v>
       </c>
       <c r="U10" t="n">
         <v>50</v>
       </c>
       <c r="V10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>358.87</v>
+        <v>360.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>368.64</v>
+        <v>370.58</v>
       </c>
       <c r="Z10" t="n">
-        <v>370.94</v>
+        <v>372.71</v>
       </c>
       <c r="AA10" t="n">
-        <v>356.58</v>
+        <v>358.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>367.83</v>
+        <v>369.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>368.86</v>
+        <v>371.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>369.73</v>
+        <v>372.85</v>
       </c>
       <c r="AE10" t="n">
         <v>81.2</v>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
@@ -2088,14 +2088,14 @@
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>377.63</v>
+        <v>379.19</v>
       </c>
       <c r="AN10" t="n">
-        <v>358.57</v>
+        <v>359.41</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.06, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.09, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2105,22 +2105,22 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹368.00) is positioned above the 30-day DMA (₹357.93), 50-day DMA (₹350.57), and 200-day DMA (₹347.65). The price distance from 200 DMA is +7.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹369.75) is positioned above the 30-day DMA (₹357.93), 50-day DMA (₹350.57), and 200-day DMA (₹347.65). The price distance from 200 DMA is +7.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[368.0, 369.1, 370.21, 371.31, 372.42, 373.52]</t>
+          <t>[369.75, 370.86, 371.97, 373.08, 374.19, 375.3]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[368.0, 372.15, 374.51, 376.59, 378.51, 380.33]</t>
+          <t>[369.75, 373.9, 376.27, 378.35, 380.28, 382.11]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[368.0, 366.82, 366.98, 367.36, 367.85, 368.41]</t>
+          <t>[369.75, 368.58, 368.74, 369.12, 369.62, 370.19]</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>104754.01</v>
+        <v>104701.41</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2149,15 +2149,15 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2191.1</v>
+        <v>2190</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹2181.64 - ₹2205.29</t>
+          <t>₹2180.54 - ₹2204.19</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2228.95</v>
+        <v>2227.85</v>
       </c>
       <c r="I11" t="n">
         <v>2146.11</v>
@@ -2184,10 +2184,10 @@
         <v>47.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R11" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="S11" t="n">
         <v>0.25</v>
@@ -2205,25 +2205,25 @@
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>2160.81</v>
+        <v>2159.51</v>
       </c>
       <c r="Y11" t="n">
-        <v>2237.5</v>
+        <v>2236.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>2208.63</v>
+        <v>2207.52</v>
       </c>
       <c r="AA11" t="n">
-        <v>2120.14</v>
+        <v>2119.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>2198.67</v>
+        <v>2196.43</v>
       </c>
       <c r="AC11" t="n">
-        <v>2207.34</v>
+        <v>2208.46</v>
       </c>
       <c r="AD11" t="n">
-        <v>2223.57</v>
+        <v>2226.93</v>
       </c>
       <c r="AE11" t="n">
         <v>58.7</v>
@@ -2233,14 +2233,14 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AJ11" t="n">
         <v>17.5</v>
@@ -2252,14 +2252,14 @@
         <v>11.6</v>
       </c>
       <c r="AM11" t="n">
-        <v>2258.91</v>
+        <v>2260.71</v>
       </c>
       <c r="AN11" t="n">
-        <v>2131.82</v>
+        <v>2126.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹104,754.01 Cr., a P/E ratio of 96.69, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
+          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹104,701.41 Cr., a P/E ratio of 96.65, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2269,22 +2269,22 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,191.10) is positioned above the 30-day DMA (₹2,146.11), 50-day DMA (₹2,067.23), and 200-day DMA (₹1,708.73). The price distance from 200 DMA is +28.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,190.00) is positioned above the 30-day DMA (₹2,146.11), 50-day DMA (₹2,067.23), and 200-day DMA (₹1,708.73). The price distance from 200 DMA is +28.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[2191.1, 2197.67, 2204.25, 2210.82, 2217.39, 2223.97]</t>
+          <t>[2190.0, 2196.57, 2203.14, 2209.71, 2216.28, 2222.85]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[2191.1, 2216.6, 2231.01, 2243.6, 2255.24, 2266.28]</t>
+          <t>[2190.0, 2215.49, 2229.9, 2242.49, 2254.13, 2265.16]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[2191.1, 2183.48, 2184.18, 2186.24, 2189.01, 2192.23]</t>
+          <t>[2190.0, 2182.38, 2183.07, 2185.13, 2187.9, 2191.12]</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>117703.06</v>
+        <v>117533.42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2313,15 +2313,15 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1457</v>
+        <v>1454.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹1450.2 - ₹1467.2</t>
+          <t>₹1448.1 - ₹1465.1</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1484.19</v>
+        <v>1482.09</v>
       </c>
       <c r="I12" t="n">
         <v>1440.19</v>
@@ -2348,16 +2348,16 @@
         <v>33.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R12" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="S12" t="n">
         <v>0.23</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.66</v>
+        <v>-1.68</v>
       </c>
       <c r="U12" t="n">
         <v>45</v>
@@ -2369,25 +2369,25 @@
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>1416.22</v>
+        <v>1414.12</v>
       </c>
       <c r="Y12" t="n">
-        <v>1426.41</v>
+        <v>1423.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1468.66</v>
+        <v>1466.54</v>
       </c>
       <c r="AA12" t="n">
-        <v>1406.02</v>
+        <v>1403.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>1460.67</v>
+        <v>1459.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>1465.94</v>
+        <v>1465.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1474.87</v>
+        <v>1475.77</v>
       </c>
       <c r="AE12" t="n">
         <v>61.6</v>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH12" t="n">
@@ -2416,14 +2416,14 @@
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>1489.15</v>
+        <v>1486.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>1426.99</v>
+        <v>1423.67</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,703.06 Cr., a P/E ratio of 34.95, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,533.42 Cr., a P/E ratio of 34.90, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2433,22 +2433,22 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,457.00) is positioned above the 30-day DMA (₹1,440.19), 50-day DMA (₹1,416.57), and 200-day DMA (₹1,395.71). The price distance from 200 DMA is +5.55%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,454.90) is positioned above the 30-day DMA (₹1,440.19), 50-day DMA (₹1,416.57), and 200-day DMA (₹1,395.71). The price distance from 200 DMA is +5.55%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[1457.0, 1461.37, 1465.74, 1470.11, 1474.48, 1478.85]</t>
+          <t>[1454.9, 1459.26, 1463.63, 1467.99, 1472.36, 1476.72]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1457.0, 1474.97, 1484.97, 1493.66, 1501.67, 1509.25]</t>
+          <t>[1454.9, 1472.86, 1482.85, 1491.54, 1499.55, 1507.12]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1457.0, 1451.18, 1451.32, 1452.45, 1454.09, 1456.06]</t>
+          <t>[1454.9, 1449.07, 1449.21, 1450.33, 1451.97, 1453.93]</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>255694.89</v>
+        <v>256306.68</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2477,15 +2477,15 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1086.7</v>
+        <v>1089.3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1080.51 - ₹1095.98</t>
+          <t>₹1083.11 - ₹1098.59</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1111.46</v>
+        <v>1114.06</v>
       </c>
       <c r="I13" t="n">
         <v>1034.29</v>
@@ -2512,46 +2512,46 @@
         <v>30.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R13" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="S13" t="n">
         <v>0.19</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.74</v>
+        <v>-1.73</v>
       </c>
       <c r="U13" t="n">
         <v>56.7</v>
       </c>
       <c r="V13" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="W13" t="n">
         <v>-0.77</v>
       </c>
       <c r="X13" t="n">
-        <v>1062.61</v>
+        <v>1066.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1100.65</v>
+        <v>1104.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>1095.39</v>
+        <v>1098.01</v>
       </c>
       <c r="AA13" t="n">
-        <v>1040.27</v>
+        <v>1042.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>1083.27</v>
+        <v>1085.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>1090.74</v>
+        <v>1095.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1094.77</v>
+        <v>1101.5</v>
       </c>
       <c r="AE13" t="n">
         <v>49.7</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH13" t="n">
@@ -2580,14 +2580,14 @@
         <v>18.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>1127.04</v>
+        <v>1128.1</v>
       </c>
       <c r="AN13" t="n">
-        <v>1048.17</v>
+        <v>1051.57</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹255,694.89 Cr., a P/E ratio of 19.19, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹256,306.68 Cr., a P/E ratio of 19.24, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2597,22 +2597,22 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,086.70) is positioned above the 30-day DMA (₹1,034.29), 50-day DMA (₹997.16), and 200-day DMA (₹944.85). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,089.30) is positioned above the 30-day DMA (₹1,034.29), 50-day DMA (₹997.16), and 200-day DMA (₹944.85). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>[1086.7, 1089.96, 1093.22, 1096.48, 1099.74, 1103.0]</t>
+          <t>[1089.3, 1092.57, 1095.84, 1099.1, 1102.37, 1105.64]</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1086.7, 1102.34, 1110.73, 1117.92, 1124.5, 1130.68]</t>
+          <t>[1089.3, 1104.95, 1113.34, 1120.55, 1127.13, 1133.32]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1086.7, 1080.68, 1080.09, 1080.4, 1081.17, 1082.24]</t>
+          <t>[1089.3, 1083.28, 1082.7, 1083.02, 1083.8, 1084.88]</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>77222.99000000001</v>
+        <v>77400.06</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2641,15 +2641,15 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1744.4</v>
+        <v>1748.4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹1732.8 - ₹1761.8</t>
+          <t>₹1736.8 - ₹1765.8</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1790.81</v>
+        <v>1794.81</v>
       </c>
       <c r="I14" t="n">
         <v>1511.17</v>
@@ -2676,16 +2676,16 @@
         <v>58.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R14" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="S14" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="T14" t="n">
-        <v>-2</v>
+        <v>-1.93</v>
       </c>
       <c r="U14" t="n">
         <v>48.3</v>
@@ -2697,25 +2697,25 @@
         <v>-0.77</v>
       </c>
       <c r="X14" t="n">
-        <v>1738.72</v>
+        <v>1744.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1799.77</v>
+        <v>1805.59</v>
       </c>
       <c r="Z14" t="n">
-        <v>1764.89</v>
+        <v>1770.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>1657.38</v>
+        <v>1661.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>1753.93</v>
+        <v>1754.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>1765.26</v>
+        <v>1768.36</v>
       </c>
       <c r="AD14" t="n">
-        <v>1786.13</v>
+        <v>1788.33</v>
       </c>
       <c r="AE14" t="n">
         <v>71.40000000000001</v>
@@ -2725,14 +2725,14 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH14" t="n">
         <v>0.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="AJ14" t="n">
         <v>49.9</v>
@@ -2744,14 +2744,14 @@
         <v>15</v>
       </c>
       <c r="AM14" t="n">
-        <v>1814.73</v>
+        <v>1812.84</v>
       </c>
       <c r="AN14" t="n">
-        <v>1677.94</v>
+        <v>1682.07</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹77,222.99 Cr., a P/E ratio of 35.69, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹77,400.06 Cr., a P/E ratio of 35.77, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -2761,22 +2761,22 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,744.40) is positioned above the 30-day DMA (₹1,511.17), 50-day DMA (₹1,475.45), and 200-day DMA (₹1,504.57). The price distance from 200 DMA is +14.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,748.40) is positioned above the 30-day DMA (₹1,511.17), 50-day DMA (₹1,475.45), and 200-day DMA (₹1,504.57). The price distance from 200 DMA is +14.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>[1744.4, 1764.89, 1785.37, 1805.86, 1826.35, 1846.83]</t>
+          <t>[1748.4, 1770.62, 1792.85, 1815.07, 1837.29, 1859.51]</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[1744.4, 1788.09, 1818.19, 1846.05, 1872.76, 1898.72]</t>
+          <t>[1748.4, 1793.83, 1825.66, 1855.26, 1883.7, 1911.4]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[1744.4, 1747.48, 1760.76, 1775.72, 1791.54, 1807.92]</t>
+          <t>[1748.4, 1753.22, 1768.23, 1784.92, 1802.48, 1820.6]</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17778.55</v>
+        <v>17754.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2805,15 +2805,15 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>620.55</v>
+        <v>619.7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹616.29 - ₹626.94</t>
+          <t>₹615.44 - ₹626.09</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>637.59</v>
+        <v>636.74</v>
       </c>
       <c r="I15" t="n">
         <v>579.77</v>
@@ -2840,16 +2840,16 @@
         <v>21.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R15" t="n">
-        <v>52.8</v>
+        <v>53.2</v>
       </c>
       <c r="S15" t="n">
         <v>0.16</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.01</v>
+        <v>-1.99</v>
       </c>
       <c r="U15" t="n">
         <v>55</v>
@@ -2861,25 +2861,25 @@
         <v>-0.77</v>
       </c>
       <c r="X15" t="n">
-        <v>594.99</v>
+        <v>594.14</v>
       </c>
       <c r="Y15" t="n">
-        <v>609.58</v>
+        <v>608.59</v>
       </c>
       <c r="Z15" t="n">
-        <v>625.51</v>
+        <v>624.66</v>
       </c>
       <c r="AA15" t="n">
-        <v>588.6</v>
+        <v>587.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>618.28</v>
+        <v>618.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>624.96</v>
+        <v>630.4400000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>629.38</v>
+        <v>641.17</v>
       </c>
       <c r="AE15" t="n">
         <v>56.9</v>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH15" t="n">
         <v>0.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AJ15" t="n">
         <v>-10.1</v>
@@ -2908,14 +2908,14 @@
         <v>6.7</v>
       </c>
       <c r="AM15" t="n">
-        <v>652.5599999999999</v>
+        <v>648.89</v>
       </c>
       <c r="AN15" t="n">
-        <v>589.25</v>
+        <v>586.98</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,778.55 Cr., a P/E ratio of 89.55, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,754.20 Cr., a P/E ratio of 89.42, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹620.55) is positioned above the 30-day DMA (₹579.77), 50-day DMA (₹544.31), and 200-day DMA (₹553.69). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹619.70) is positioned above the 30-day DMA (₹579.77), 50-day DMA (₹544.31), and 200-day DMA (₹553.69). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>[620.55, 622.41, 624.27, 626.13, 628.0, 629.86]</t>
+          <t>[619.7, 621.56, 623.42, 625.28, 627.14, 629.0]</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[620.55, 630.93, 636.32, 640.89, 645.04, 648.91]</t>
+          <t>[619.7, 630.08, 635.47, 640.03, 644.18, 648.05]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[620.55, 616.02, 615.24, 615.07, 615.22, 615.57]</t>
+          <t>[619.7, 615.17, 614.38, 614.21, 614.36, 614.71]</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>145925.93</v>
+        <v>146111.96</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2969,15 +2969,15 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1647.3</v>
+        <v>1649.4</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹1638.13 - ₹1661.06</t>
+          <t>₹1640.23 - ₹1663.16</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1684</v>
+        <v>1686.1</v>
       </c>
       <c r="I16" t="n">
         <v>1487.74</v>
@@ -3004,46 +3004,46 @@
         <v>45.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R16" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="S16" t="n">
         <v>0.19</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.02</v>
+        <v>-2.03</v>
       </c>
       <c r="U16" t="n">
         <v>48.3</v>
       </c>
       <c r="V16" t="n">
-        <v>7.73</v>
+        <v>7.74</v>
       </c>
       <c r="W16" t="n">
         <v>-0.77</v>
       </c>
       <c r="X16" t="n">
-        <v>1592.25</v>
+        <v>1594.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>1648.98</v>
+        <v>1651.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>1660.48</v>
+        <v>1662.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1578.49</v>
+        <v>1580.59</v>
       </c>
       <c r="AB16" t="n">
-        <v>1649.83</v>
+        <v>1649.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1656.46</v>
+        <v>1658.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1665.63</v>
+        <v>1668.4</v>
       </c>
       <c r="AE16" t="n">
         <v>77.8</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH16" t="n">
@@ -3072,14 +3072,14 @@
         <v>15</v>
       </c>
       <c r="AM16" t="n">
-        <v>1694.76</v>
+        <v>1694.09</v>
       </c>
       <c r="AN16" t="n">
-        <v>1602.78</v>
+        <v>1607.04</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹145,925.93 Cr., a P/E ratio of 28.50, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,111.96 Cr., a P/E ratio of 28.54, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -3089,22 +3089,22 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,647.30) is positioned above the 30-day DMA (₹1,487.74), 50-day DMA (₹1,465.74), and 200-day DMA (₹1,460.05). The price distance from 200 DMA is +13.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,649.40) is positioned above the 30-day DMA (₹1,487.74), 50-day DMA (₹1,465.74), and 200-day DMA (₹1,460.05). The price distance from 200 DMA is +13.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>[1647.3, 1652.24, 1657.18, 1662.13, 1667.07, 1672.01]</t>
+          <t>[1649.4, 1654.35, 1659.3, 1664.24, 1669.19, 1674.14]</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[1647.3, 1670.59, 1683.13, 1693.91, 1703.76, 1713.04]</t>
+          <t>[1649.4, 1672.7, 1685.25, 1696.03, 1705.89, 1715.17]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[1647.3, 1638.48, 1637.72, 1638.29, 1639.54, 1641.24]</t>
+          <t>[1649.4, 1640.59, 1639.83, 1640.41, 1641.67, 1643.37]</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46971.29</v>
+        <v>47370.04</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3133,15 +3133,15 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1154.2</v>
+        <v>1164.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹1147.29 - ₹1164.56</t>
+          <t>₹1157.29 - ₹1174.56</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1181.84</v>
+        <v>1191.84</v>
       </c>
       <c r="I17" t="n">
         <v>1109.24</v>
@@ -3168,7 +3168,7 @@
         <v>34.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R17" t="n">
         <v>43.9</v>
@@ -3177,37 +3177,37 @@
         <v>0.18</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.17</v>
+        <v>-2.15</v>
       </c>
       <c r="U17" t="n">
         <v>48.3</v>
       </c>
       <c r="V17" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="W17" t="n">
         <v>-0.77</v>
       </c>
       <c r="X17" t="n">
-        <v>1139.35</v>
+        <v>1151.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1179.75</v>
+        <v>1191.94</v>
       </c>
       <c r="Z17" t="n">
-        <v>1163.43</v>
+        <v>1173.51</v>
       </c>
       <c r="AA17" t="n">
-        <v>1102.37</v>
+        <v>1112.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1151.5</v>
+        <v>1160.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>1158.6</v>
+        <v>1177.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1163</v>
+        <v>1190.47</v>
       </c>
       <c r="AE17" t="n">
         <v>53.6</v>
@@ -3217,14 +3217,14 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH17" t="n">
         <v>0.15</v>
       </c>
       <c r="AI17" t="n">
-        <v>38.4</v>
+        <v>38.7</v>
       </c>
       <c r="AJ17" t="n">
         <v>29.9</v>
@@ -3236,14 +3236,14 @@
         <v>15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1189.48</v>
+        <v>1198.17</v>
       </c>
       <c r="AN17" t="n">
-        <v>1122.84</v>
+        <v>1128.1</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹46,971.29 Cr., a P/E ratio of 38.36, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹47,370.04 Cr., a P/E ratio of 38.69, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
@@ -3253,22 +3253,22 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,154.20) is positioned above the 30-day DMA (₹1,109.24), 50-day DMA (₹1,105.80), and 200-day DMA (₹1,100.59). The price distance from 200 DMA is +3.15%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,164.20) is positioned above the 30-day DMA (₹1,109.24), 50-day DMA (₹1,105.80), and 200-day DMA (₹1,100.59). The price distance from 200 DMA is +3.15%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>[1154.2, 1157.66, 1161.13, 1164.59, 1168.05, 1171.51]</t>
+          <t>[1164.2, 1168.66, 1173.12, 1177.58, 1182.03, 1186.49]</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[1154.2, 1171.48, 1180.67, 1188.52, 1195.69, 1202.42]</t>
+          <t>[1164.2, 1182.48, 1192.66, 1201.51, 1209.67, 1217.4]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[1154.2, 1147.3, 1146.47, 1146.64, 1147.32, 1148.34]</t>
+          <t>[1164.2, 1158.29, 1158.46, 1159.62, 1161.3, 1163.32]</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>62432.09</v>
+        <v>62076.64</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3297,15 +3297,15 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2072.6</v>
+        <v>2060.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹2059.82 - ₹2091.78</t>
+          <t>₹2048.02 - ₹2079.98</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2123.73</v>
+        <v>2111.93</v>
       </c>
       <c r="I18" t="n">
         <v>2010.06</v>
@@ -3332,7 +3332,7 @@
         <v>63.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R18" t="n">
         <v>42.6</v>
@@ -3341,37 +3341,37 @@
         <v>0.17</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.31</v>
+        <v>-2.33</v>
       </c>
       <c r="U18" t="n">
         <v>51.7</v>
       </c>
       <c r="V18" t="n">
-        <v>5.56</v>
+        <v>5.54</v>
       </c>
       <c r="W18" t="n">
         <v>-0.77</v>
       </c>
       <c r="X18" t="n">
-        <v>1995.9</v>
+        <v>1984.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1977.22</v>
+        <v>1963.68</v>
       </c>
       <c r="Z18" t="n">
-        <v>2089.18</v>
+        <v>2077.29</v>
       </c>
       <c r="AA18" t="n">
-        <v>1976.72</v>
+        <v>1964.92</v>
       </c>
       <c r="AB18" t="n">
-        <v>2068.87</v>
+        <v>2064.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>2091.74</v>
+        <v>2084.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>2110.87</v>
+        <v>2107.4</v>
       </c>
       <c r="AE18" t="n">
         <v>45</v>
@@ -3381,14 +3381,14 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH18" t="n">
         <v>0.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>33.7</v>
+        <v>33.5</v>
       </c>
       <c r="AJ18" t="n">
         <v>63</v>
@@ -3400,14 +3400,14 @@
         <v>10</v>
       </c>
       <c r="AM18" t="n">
-        <v>2149.08</v>
+        <v>2135.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>2003.47</v>
+        <v>1990.93</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹62,432.09 Cr., a P/E ratio of 33.71, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹62,076.64 Cr., a P/E ratio of 33.51, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,072.60) is positioned above the 30-day DMA (₹2,010.06), 50-day DMA (₹1,895.79), and 200-day DMA (₹1,880.50). The price distance from 200 DMA is +11.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,060.80) is positioned above the 30-day DMA (₹2,010.06), 50-day DMA (₹1,895.79), and 200-day DMA (₹1,880.50). The price distance from 200 DMA is +11.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>[2072.6, 2078.82, 2085.04, 2091.25, 2097.47, 2103.69]</t>
+          <t>[2060.8, 2066.98, 2073.16, 2079.35, 2085.53, 2091.71]</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[2072.6, 2104.38, 2121.19, 2135.54, 2148.61, 2160.86]</t>
+          <t>[2060.8, 2092.55, 2109.32, 2123.63, 2136.66, 2148.88]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[2072.6, 2059.64, 2057.92, 2058.04, 2059.12, 2060.81]</t>
+          <t>[2060.8, 2047.81, 2046.05, 2046.13, 2047.18, 2048.83]</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>286794.03</v>
+        <v>286103.62</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3461,15 +3461,15 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>311.6</v>
+        <v>310.8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>₹309.41 - ₹314.88</t>
+          <t>₹308.61 - ₹314.08</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>320.35</v>
+        <v>319.55</v>
       </c>
       <c r="I19" t="n">
         <v>282.98</v>
@@ -3496,46 +3496,46 @@
         <v>10.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R19" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="S19" t="n">
         <v>0.15</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.33</v>
+        <v>-2.34</v>
       </c>
       <c r="U19" t="n">
         <v>51.7</v>
       </c>
       <c r="V19" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="W19" t="n">
         <v>-0.77</v>
       </c>
       <c r="X19" t="n">
-        <v>307.48</v>
+        <v>306.51</v>
       </c>
       <c r="Y19" t="n">
-        <v>318.39</v>
+        <v>317.39</v>
       </c>
       <c r="Z19" t="n">
-        <v>314.09</v>
+        <v>313.29</v>
       </c>
       <c r="AA19" t="n">
-        <v>295.2</v>
+        <v>294.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>310.93</v>
+        <v>310.97</v>
       </c>
       <c r="AC19" t="n">
-        <v>312.46</v>
+        <v>312.54</v>
       </c>
       <c r="AD19" t="n">
-        <v>313.33</v>
+        <v>314.27</v>
       </c>
       <c r="AE19" t="n">
         <v>62</v>
@@ -3545,14 +3545,14 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH19" t="n">
         <v>0.15</v>
       </c>
       <c r="AI19" t="n">
-        <v>692.3</v>
+        <v>690.7</v>
       </c>
       <c r="AJ19" t="n">
         <v>182</v>
@@ -3564,14 +3564,14 @@
         <v>15</v>
       </c>
       <c r="AM19" t="n">
-        <v>322.51</v>
+        <v>321.35</v>
       </c>
       <c r="AN19" t="n">
-        <v>300.96</v>
+        <v>300.74</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹286,794.03 Cr., a P/E ratio of 692.33, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹286,103.62 Cr., a P/E ratio of 690.67, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
@@ -3581,22 +3581,22 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹311.60) is positioned above the 30-day DMA (₹282.98), 50-day DMA (₹270.14), and 200-day DMA (₹273.78). The price distance from 200 DMA is +10.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹310.80) is positioned above the 30-day DMA (₹282.98), 50-day DMA (₹270.14), and 200-day DMA (₹273.78). The price distance from 200 DMA is +10.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>[311.6, 312.53, 313.47, 314.4, 315.34, 316.27]</t>
+          <t>[310.8, 311.73, 312.66, 313.6, 314.53, 315.46]</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>[311.6, 316.91, 319.66, 321.98, 324.09, 326.06]</t>
+          <t>[310.8, 316.11, 318.85, 321.17, 323.28, 325.24]</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>[311.6, 309.25, 308.83, 308.72, 308.78, 308.94]</t>
+          <t>[310.8, 308.45, 308.03, 307.91, 307.97, 308.13]</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>84490.31</v>
+        <v>84903.75999999999</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -3625,15 +3625,15 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>13896</v>
+        <v>13964</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>₹13803.67 - ₹14034.49</t>
+          <t>₹13871.67 - ₹14102.49</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>14265.31</v>
+        <v>14333.31</v>
       </c>
       <c r="I20" t="n">
         <v>13241.63</v>
@@ -3660,10 +3660,10 @@
         <v>461.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>12.03</v>
+        <v>11.97</v>
       </c>
       <c r="R20" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
       <c r="S20" t="n">
         <v>0.16</v>
@@ -3675,31 +3675,31 @@
         <v>46.7</v>
       </c>
       <c r="V20" t="n">
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
       <c r="W20" t="n">
         <v>-0.77</v>
       </c>
       <c r="X20" t="n">
-        <v>13342.03</v>
+        <v>13410.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>13734.17</v>
+        <v>13817.92</v>
       </c>
       <c r="Z20" t="n">
-        <v>14007.17</v>
+        <v>14075.71</v>
       </c>
       <c r="AA20" t="n">
-        <v>13203.54</v>
+        <v>13271.54</v>
       </c>
       <c r="AB20" t="n">
-        <v>13905.33</v>
+        <v>13954</v>
       </c>
       <c r="AC20" t="n">
-        <v>13943.66</v>
+        <v>14096</v>
       </c>
       <c r="AD20" t="n">
-        <v>13991.33</v>
+        <v>14228</v>
       </c>
       <c r="AE20" t="n">
         <v>58.4</v>
@@ -3709,14 +3709,14 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.03) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH20" t="n">
         <v>0.15</v>
       </c>
       <c r="AI20" t="n">
-        <v>40.7</v>
+        <v>40.9</v>
       </c>
       <c r="AJ20" t="n">
         <v>21.1</v>
@@ -3728,14 +3728,14 @@
         <v>15</v>
       </c>
       <c r="AM20" t="n">
-        <v>14414.15</v>
+        <v>14521.35</v>
       </c>
       <c r="AN20" t="n">
-        <v>13368.24</v>
+        <v>13400.48</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹84,490.31 Cr., a P/E ratio of 40.70, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹84,903.76 Cr., a P/E ratio of 40.90, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -3745,22 +3745,22 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,896.00) is positioned above the 30-day DMA (₹13,241.63), 50-day DMA (₹12,652.22), and 200-day DMA (₹12,318.23). The price distance from 200 DMA is +14.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,964.00) is positioned above the 30-day DMA (₹13,241.63), 50-day DMA (₹12,652.22), and 200-day DMA (₹12,318.23). The price distance from 200 DMA is +14.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>[13896.0, 13937.69, 13979.38, 14021.06, 14062.75, 14104.44]</t>
+          <t>[13964.0, 14005.89, 14047.78, 14089.68, 14131.57, 14173.46]</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>[13896.0, 14122.35, 14240.52, 14340.9, 14432.07, 14517.35]</t>
+          <t>[13964.0, 14190.55, 14308.93, 14409.51, 14500.88, 14586.37]</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>[13896.0, 13799.2, 13783.52, 13781.19, 13785.77, 13794.76]</t>
+          <t>[13964.0, 13867.4, 13851.93, 13849.8, 13854.58, 13863.78]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1036466.83</v>
+        <v>1034171.29</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -673,15 +673,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1444.9</v>
+        <v>1441.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹1440.33 - ₹1451.76</t>
+          <t>₹1437.13 - ₹1448.56</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1463.2</v>
+        <v>1460</v>
       </c>
       <c r="I2" t="n">
         <v>1398.49</v>
@@ -708,16 +708,16 @@
         <v>22.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R2" t="n">
-        <v>54.4</v>
+        <v>54.8</v>
       </c>
       <c r="S2" t="n">
         <v>0.34</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="U2" t="n">
         <v>60</v>
@@ -729,25 +729,25 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>1426.82</v>
+        <v>1423.17</v>
       </c>
       <c r="Y2" t="n">
-        <v>1477.39</v>
+        <v>1473.63</v>
       </c>
       <c r="Z2" t="n">
-        <v>1456.46</v>
+        <v>1453.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>1410.59</v>
+        <v>1407.39</v>
       </c>
       <c r="AB2" t="n">
-        <v>1447.13</v>
+        <v>1445.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>1451.16</v>
+        <v>1449.54</v>
       </c>
       <c r="AD2" t="n">
-        <v>1457.43</v>
+        <v>1457.37</v>
       </c>
       <c r="AE2" t="n">
         <v>60.1</v>
@@ -757,14 +757,14 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AJ2" t="n">
         <v>11.4</v>
@@ -776,14 +776,14 @@
         <v>16.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1470.78</v>
+        <v>1469.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>1418.03</v>
+        <v>1414.71</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,036,466.83 Cr., a P/E ratio of 18.68, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
+          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,034,171.29 Cr., a P/E ratio of 18.63, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -793,22 +793,22 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,444.90) is positioned above the 30-day DMA (₹1,398.49), 50-day DMA (₹1,349.96), and 200-day DMA (₹1,337.12). The price distance from 200 DMA is +6.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,441.70) is positioned above the 30-day DMA (₹1,398.49), 50-day DMA (₹1,349.96), and 200-day DMA (₹1,337.12). The price distance from 200 DMA is +6.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[1444.9, 1449.23, 1453.57, 1457.9, 1462.24, 1466.57]</t>
+          <t>[1441.7, 1446.03, 1450.35, 1454.68, 1459.0, 1463.33]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[1444.9, 1458.38, 1466.51, 1473.75, 1480.54, 1487.03]</t>
+          <t>[1441.7, 1455.17, 1463.29, 1470.52, 1477.3, 1483.78]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[1444.9, 1442.37, 1443.87, 1446.02, 1448.52, 1451.23]</t>
+          <t>[1441.7, 1439.16, 1440.65, 1442.79, 1445.28, 1447.98]</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>130502.37</v>
+        <v>130329.98</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -837,15 +837,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>113.55</v>
+        <v>113.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹113.15 - ₹114.15</t>
+          <t>₹113.0 - ₹114.0</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>115.15</v>
+        <v>115</v>
       </c>
       <c r="I3" t="n">
         <v>107.8</v>
@@ -872,7 +872,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R3" t="n">
         <v>52.9</v>
@@ -893,25 +893,25 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>111.23</v>
+        <v>111.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>115.21</v>
+        <v>115.03</v>
       </c>
       <c r="Z3" t="n">
-        <v>114.46</v>
+        <v>114.31</v>
       </c>
       <c r="AA3" t="n">
-        <v>110.56</v>
+        <v>110.41</v>
       </c>
       <c r="AB3" t="n">
-        <v>113.4</v>
+        <v>113.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>114.16</v>
+        <v>114.06</v>
       </c>
       <c r="AD3" t="n">
-        <v>114.76</v>
+        <v>114.71</v>
       </c>
       <c r="AE3" t="n">
         <v>71.2</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
@@ -940,14 +940,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>117.05</v>
+        <v>116.74</v>
       </c>
       <c r="AN3" t="n">
-        <v>110.28</v>
+        <v>110.2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,502.37 Cr., a P/E ratio of 5.91, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,329.98 Cr., a P/E ratio of 5.90, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -957,22 +957,22 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.55) is positioned above the 30-day DMA (₹107.80), 50-day DMA (₹106.57), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.07%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.40) is positioned above the 30-day DMA (₹107.80), 50-day DMA (₹106.57), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.07%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[113.55, 113.89, 114.23, 114.57, 114.91, 115.25]</t>
+          <t>[113.4, 113.74, 114.08, 114.42, 114.76, 115.1]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[113.55, 114.69, 115.36, 115.95, 116.51, 117.04]</t>
+          <t>[113.4, 114.54, 115.21, 115.8, 116.36, 116.89]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[113.55, 113.29, 113.38, 113.53, 113.72, 113.91]</t>
+          <t>[113.4, 113.14, 113.23, 113.38, 113.56, 113.76]</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -993,150 +993,150 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>268075.27</v>
+        <v>351473.87</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2796.4</v>
+        <v>11948</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹2784.86 - ₹2813.71</t>
+          <t>₹11904.37 - ₹12013.45</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2842.57</v>
+        <v>12122.53</v>
       </c>
       <c r="I4" t="n">
-        <v>2689.12</v>
+        <v>11421.23</v>
       </c>
       <c r="J4" t="n">
-        <v>2681.37</v>
+        <v>11269.86</v>
       </c>
       <c r="K4" t="n">
-        <v>2572.85</v>
+        <v>11569.69</v>
       </c>
       <c r="L4" t="n">
-        <v>6.78</v>
+        <v>2.4</v>
       </c>
       <c r="M4" t="n">
-        <v>18.17</v>
+        <v>143.27</v>
       </c>
       <c r="N4" t="n">
-        <v>11.71</v>
+        <v>124.24</v>
       </c>
       <c r="O4" t="n">
-        <v>6.46</v>
+        <v>19.02</v>
       </c>
       <c r="P4" t="n">
-        <v>57.71</v>
+        <v>218.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R4" t="n">
-        <v>54</v>
+        <v>50.9</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.92</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>56.7</v>
+        <v>48.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2780.55</v>
+        <v>11799.64</v>
       </c>
       <c r="Y4" t="n">
-        <v>2878.42</v>
+        <v>12217.82</v>
       </c>
       <c r="Z4" t="n">
-        <v>2822.49</v>
+        <v>12043.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>2709.83</v>
+        <v>11620.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>2791.27</v>
+        <v>11951</v>
       </c>
       <c r="AC4" t="n">
-        <v>2812.44</v>
+        <v>11997</v>
       </c>
       <c r="AD4" t="n">
-        <v>2828.47</v>
+        <v>12046</v>
       </c>
       <c r="AE4" t="n">
-        <v>68.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>56.2</v>
+        <v>41.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="AK4" t="n">
-        <v>12.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2865.26</v>
+        <v>12220.44</v>
       </c>
       <c r="AN4" t="n">
-        <v>2733.38</v>
+        <v>11681.27</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹268,075.27 Cr., a P/E ratio of 56.23, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹351,473.87 Cr., a P/E ratio of 41.14, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 68.92 (Bullish Momentum Zone), while MACD Line (18.17) trades above Signal (11.71) with an expanding histogram (+6.46). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.78% above the 200-day DMA (₹2572.85). Daily volatility envelope is bounded by ATR(14) of ₹57.71.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (143.27) trades above Signal (124.24) with an expanding histogram (+19.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.40% above the 200-day DMA (₹11569.69). Daily volatility envelope is bounded by ATR(14) of ₹218.17.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,796.40) is positioned above the 30-day DMA (₹2,689.12), 50-day DMA (₹2,681.37), and 200-day DMA (₹2,572.85). The price distance from 200 DMA is +6.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,948.00) is positioned above the 30-day DMA (₹11,421.23), 50-day DMA (₹11,269.86), and 200-day DMA (₹11,569.69). The price distance from 200 DMA is +2.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[2796.4, 2822.49, 2848.59, 2874.68, 2900.78, 2926.88]</t>
+          <t>[11948.0, 11983.84, 12019.69, 12055.53, 12091.38, 12127.22]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[2796.4, 2845.58, 2881.24, 2914.67, 2946.95, 2978.5]</t>
+          <t>[11948.0, 12071.11, 12143.1, 12206.68, 12265.91, 12322.35]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[2796.4, 2805.18, 2824.1, 2844.7, 2866.15, 2888.16]</t>
+          <t>[11948.0, 11918.39, 11927.13, 11942.17, 11960.48, 11980.87]</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>352650.55</v>
+        <v>217229.02</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1165,142 +1165,142 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11988</v>
+        <v>7913</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹11943.83 - ₹12054.25</t>
+          <t>₹7882.88 - ₹7958.18</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12164.68</v>
+        <v>8033.49</v>
       </c>
       <c r="I5" t="n">
-        <v>11446.68</v>
+        <v>7447.86</v>
       </c>
       <c r="J5" t="n">
-        <v>11281.17</v>
+        <v>7362.95</v>
       </c>
       <c r="K5" t="n">
-        <v>11569.56</v>
+        <v>7176.17</v>
       </c>
       <c r="L5" t="n">
-        <v>2.88</v>
+        <v>9.16</v>
       </c>
       <c r="M5" t="n">
-        <v>152.76</v>
+        <v>130.62</v>
       </c>
       <c r="N5" t="n">
-        <v>129.95</v>
+        <v>94.11</v>
       </c>
       <c r="O5" t="n">
-        <v>22.81</v>
+        <v>36.5</v>
       </c>
       <c r="P5" t="n">
-        <v>220.85</v>
+        <v>150.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R5" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.95</v>
+        <v>-0.98</v>
       </c>
       <c r="U5" t="n">
         <v>50</v>
       </c>
       <c r="V5" t="n">
-        <v>2.68</v>
+        <v>2.03</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>11870.24</v>
+        <v>7764.31</v>
       </c>
       <c r="Y5" t="n">
-        <v>12289.82</v>
+        <v>8041.27</v>
       </c>
       <c r="Z5" t="n">
-        <v>12083.9</v>
+        <v>7976.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>11656.73</v>
+        <v>7687.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>11964.33</v>
+        <v>7948.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>12023.66</v>
+        <v>7988.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>12059.33</v>
+        <v>8064</v>
       </c>
       <c r="AE5" t="n">
-        <v>70.2</v>
+        <v>79</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>41.3</v>
+        <v>37.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15.9</v>
+        <v>31.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>9.300000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>12264.67</v>
+        <v>8132.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>11741.41</v>
+        <v>7726.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹352,650.55 Cr., a P/E ratio of 41.28, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹217,229.02 Cr., a P/E ratio of 37.69, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.23 (Bullish Momentum Zone), while MACD Line (152.76) trades above Signal (129.95) with an expanding histogram (+22.81). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.88% above the 200-day DMA (₹11569.56). Daily volatility envelope is bounded by ATR(14) of ₹220.85.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.95 (Bullish Momentum Zone), while MACD Line (130.62) trades above Signal (94.11) with an expanding histogram (+36.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.16% above the 200-day DMA (₹7176.17). Daily volatility envelope is bounded by ATR(14) of ₹150.61.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,988.00) is positioned above the 30-day DMA (₹11,446.68), 50-day DMA (₹11,281.17), and 200-day DMA (₹11,569.56). The price distance from 200 DMA is +2.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,913.00) is positioned above the 30-day DMA (₹7,447.86), 50-day DMA (₹7,362.95), and 200-day DMA (₹7,176.17). The price distance from 200 DMA is +9.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[11988.0, 12050.06, 12112.12, 12174.18, 12236.24, 12298.29]</t>
+          <t>[7913.0, 7936.74, 7960.48, 7984.22, 8007.96, 8031.69]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[11988.0, 12138.4, 12237.05, 12327.18, 12412.91, 12495.83]</t>
+          <t>[7913.0, 7996.98, 8045.68, 8088.56, 8128.44, 8166.4]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[11988.0, 11983.8, 12018.42, 12059.42, 12103.73, 12150.15]</t>
+          <t>[7913.0, 7891.56, 7896.58, 7905.96, 7917.59, 7930.66]</t>
         </is>
       </c>
     </row>
@@ -1312,16 +1312,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>218299.66</v>
+        <v>266886.58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1329,142 +1329,142 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7952</v>
+        <v>2784</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹7921.88 - ₹7997.18</t>
+          <t>₹2772.38 - ₹2801.43</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8072.49</v>
+        <v>2830.47</v>
       </c>
       <c r="I6" t="n">
-        <v>7447.86</v>
+        <v>2687.86</v>
       </c>
       <c r="J6" t="n">
-        <v>7362.95</v>
+        <v>2678.76</v>
       </c>
       <c r="K6" t="n">
-        <v>7176.17</v>
+        <v>2570.71</v>
       </c>
       <c r="L6" t="n">
-        <v>9.16</v>
+        <v>6.83</v>
       </c>
       <c r="M6" t="n">
-        <v>130.62</v>
+        <v>16.14</v>
       </c>
       <c r="N6" t="n">
-        <v>94.11</v>
+        <v>10.09</v>
       </c>
       <c r="O6" t="n">
-        <v>36.5</v>
+        <v>6.05</v>
       </c>
       <c r="P6" t="n">
-        <v>150.61</v>
+        <v>58.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R6" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="S6" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.97</v>
+        <v>-1.1</v>
       </c>
       <c r="U6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>7807.39</v>
+        <v>2746.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>8085.71</v>
+        <v>2843.69</v>
       </c>
       <c r="Z6" t="n">
-        <v>8015.62</v>
+        <v>2806.27</v>
       </c>
       <c r="AA6" t="n">
-        <v>7726.09</v>
+        <v>2696.87</v>
       </c>
       <c r="AB6" t="n">
-        <v>7971.33</v>
+        <v>2787.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>8004.66</v>
+        <v>2804.16</v>
       </c>
       <c r="AD6" t="n">
-        <v>8057.33</v>
+        <v>2824.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>79</v>
+        <v>62.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>37.9</v>
+        <v>56</v>
       </c>
       <c r="AJ6" t="n">
-        <v>31.5</v>
+        <v>17.9</v>
       </c>
       <c r="AK6" t="n">
-        <v>23.2</v>
+        <v>12.8</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>8184.5</v>
+        <v>2852.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>7755.87</v>
+        <v>2719.67</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹218,299.66 Cr., a P/E ratio of 37.88, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹266,886.58 Cr., a P/E ratio of 55.98, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.95 (Bullish Momentum Zone), while MACD Line (130.62) trades above Signal (94.11) with an expanding histogram (+36.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.16% above the 200-day DMA (₹7176.17). Daily volatility envelope is bounded by ATR(14) of ₹150.61.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.38 (Bullish Momentum Zone), while MACD Line (16.14) trades above Signal (10.09) with an expanding histogram (+6.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.83% above the 200-day DMA (₹2570.71). Daily volatility envelope is bounded by ATR(14) of ₹58.09.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,952.00) is positioned above the 30-day DMA (₹7,447.86), 50-day DMA (₹7,362.95), and 200-day DMA (₹7,176.17). The price distance from 200 DMA is +9.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,784.00) is positioned above the 30-day DMA (₹2,687.86), 50-day DMA (₹2,678.76), and 200-day DMA (₹2,570.71). The price distance from 200 DMA is +6.83%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[7952.0, 7975.86, 7999.71, 8023.57, 8047.42, 8071.28]</t>
+          <t>[2784.0, 2792.35, 2800.7, 2809.06, 2817.41, 2825.76]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[7952.0, 8036.1, 8084.91, 8127.91, 8167.91, 8205.99]</t>
+          <t>[2784.0, 2815.59, 2833.56, 2849.3, 2863.88, 2877.71]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[7952.0, 7930.67, 7935.81, 7945.31, 7957.06, 7970.25]</t>
+          <t>[2784.0, 2774.93, 2776.06, 2778.87, 2782.56, 2786.79]</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>106102.64</v>
+        <v>105597.31</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1493,15 +1493,15 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>745.4</v>
+        <v>741.85</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹742.38 - ₹749.93</t>
+          <t>₹738.83 - ₹746.38</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>757.48</v>
+        <v>753.9299999999999</v>
       </c>
       <c r="I7" t="n">
         <v>730.08</v>
@@ -1528,46 +1528,46 @@
         <v>15.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R7" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="S7" t="n">
         <v>0.26</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.08</v>
+        <v>-1.1</v>
       </c>
       <c r="U7" t="n">
         <v>56.7</v>
       </c>
       <c r="V7" t="n">
-        <v>6.53</v>
+        <v>6.51</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>727.28</v>
+        <v>723.73</v>
       </c>
       <c r="Y7" t="n">
-        <v>739.98</v>
+        <v>736.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>751.36</v>
+        <v>747.78</v>
       </c>
       <c r="AA7" t="n">
-        <v>722.75</v>
+        <v>719.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>746.58</v>
+        <v>744</v>
       </c>
       <c r="AC7" t="n">
-        <v>749.76</v>
+        <v>748.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>754.13</v>
+        <v>755.75</v>
       </c>
       <c r="AE7" t="n">
         <v>50</v>
@@ -1577,14 +1577,14 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="AJ7" t="n">
         <v>15.1</v>
@@ -1596,14 +1596,14 @@
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>763.46</v>
+        <v>759.9299999999999</v>
       </c>
       <c r="AN7" t="n">
-        <v>726.74</v>
+        <v>724.3</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,102.64 Cr., a P/E ratio of 49.46, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,597.31 Cr., a P/E ratio of 49.23, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1613,22 +1613,22 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹745.40) is positioned above the 30-day DMA (₹730.08), 50-day DMA (₹705.51), and 200-day DMA (₹686.16). The price distance from 200 DMA is +7.63%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.85) is positioned above the 30-day DMA (₹730.08), 50-day DMA (₹705.51), and 200-day DMA (₹686.16). The price distance from 200 DMA is +7.63%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[745.4, 747.64, 749.87, 752.11, 754.34, 756.58]</t>
+          <t>[741.85, 744.08, 746.3, 748.53, 750.75, 752.98]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[745.4, 753.68, 758.41, 762.57, 766.42, 770.09]</t>
+          <t>[741.85, 750.12, 754.84, 758.99, 762.83, 766.48]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[745.4, 743.11, 743.47, 744.26, 745.28, 746.45]</t>
+          <t>[741.85, 739.55, 739.89, 740.68, 741.69, 742.85]</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>312919.8</v>
+        <v>311495.33</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1657,15 +1657,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4679</v>
+        <v>4657.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹4662.29 - ₹4704.06</t>
+          <t>₹4640.99 - ₹4682.76</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4745.82</v>
+        <v>4724.52</v>
       </c>
       <c r="I8" t="n">
         <v>4479.85</v>
@@ -1692,46 +1692,46 @@
         <v>83.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R8" t="n">
-        <v>43.2</v>
+        <v>42.3</v>
       </c>
       <c r="S8" t="n">
         <v>0.3</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.18</v>
+        <v>-1.21</v>
       </c>
       <c r="U8" t="n">
         <v>43.3</v>
       </c>
       <c r="V8" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>4578.77</v>
+        <v>4557.47</v>
       </c>
       <c r="Y8" t="n">
-        <v>4740.7</v>
+        <v>4716.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4716.43</v>
+        <v>4694.96</v>
       </c>
       <c r="AA8" t="n">
-        <v>4553.71</v>
+        <v>4532.41</v>
       </c>
       <c r="AB8" t="n">
-        <v>4682.33</v>
+        <v>4675.23</v>
       </c>
       <c r="AC8" t="n">
-        <v>4714.66</v>
+        <v>4700.46</v>
       </c>
       <c r="AD8" t="n">
-        <v>4750.33</v>
+        <v>4743.23</v>
       </c>
       <c r="AE8" t="n">
         <v>64.59999999999999</v>
@@ -1741,14 +1741,14 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.8</v>
@@ -1760,14 +1760,14 @@
         <v>24</v>
       </c>
       <c r="AM8" t="n">
-        <v>4800.69</v>
+        <v>4773.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>4552.81</v>
+        <v>4531.88</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹312,919.80 Cr., a P/E ratio of 34.37, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹311,495.33 Cr., a P/E ratio of 34.21, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1777,22 +1777,22 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,679.00) is positioned above the 30-day DMA (₹4,479.85), 50-day DMA (₹4,409.79), and 200-day DMA (₹4,345.73). The price distance from 200 DMA is +6.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,657.70) is positioned above the 30-day DMA (₹4,479.85), 50-day DMA (₹4,409.79), and 200-day DMA (₹4,345.73). The price distance from 200 DMA is +6.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[4679.0, 4693.04, 4707.07, 4721.11, 4735.15, 4749.18]</t>
+          <t>[4657.7, 4671.67, 4685.65, 4699.62, 4713.59, 4727.57]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[4679.0, 4726.45, 4754.32, 4778.98, 4801.97, 4823.9]</t>
+          <t>[4657.7, 4705.08, 4732.9, 4757.49, 4780.42, 4802.28]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[4679.0, 4667.98, 4671.64, 4677.71, 4685.03, 4693.15]</t>
+          <t>[4657.7, 4646.61, 4650.21, 4656.22, 4663.48, 4671.53]</t>
         </is>
       </c>
     </row>
@@ -1813,99 +1813,99 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>67984.66</v>
+        <v>67936.83</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5686</v>
+        <v>5682</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹5662.05 - ₹5721.93</t>
+          <t>₹5657.51 - ₹5718.73</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5781.8</v>
+        <v>5779.94</v>
       </c>
       <c r="I9" t="n">
-        <v>5587.6</v>
+        <v>5575</v>
       </c>
       <c r="J9" t="n">
-        <v>5491.02</v>
+        <v>5484.08</v>
       </c>
       <c r="K9" t="n">
-        <v>5522.76</v>
+        <v>5521.06</v>
       </c>
       <c r="L9" t="n">
-        <v>4.14</v>
+        <v>5.35</v>
       </c>
       <c r="M9" t="n">
-        <v>60.48</v>
+        <v>57.19</v>
       </c>
       <c r="N9" t="n">
-        <v>53.66</v>
+        <v>51.96</v>
       </c>
       <c r="O9" t="n">
-        <v>6.82</v>
+        <v>5.23</v>
       </c>
       <c r="P9" t="n">
-        <v>119.75</v>
+        <v>122.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R9" t="n">
-        <v>49.5</v>
+        <v>47.2</v>
       </c>
       <c r="S9" t="n">
         <v>0.25</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2</v>
+        <v>-1.33</v>
       </c>
       <c r="U9" t="n">
-        <v>51.7</v>
+        <v>53.3</v>
       </c>
       <c r="V9" t="n">
-        <v>3.13</v>
+        <v>2.8</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>5570.27</v>
+        <v>5624.76</v>
       </c>
       <c r="Y9" t="n">
-        <v>5769.28</v>
+        <v>5823.63</v>
       </c>
       <c r="Z9" t="n">
-        <v>5731.49</v>
+        <v>5727.46</v>
       </c>
       <c r="AA9" t="n">
-        <v>5506.38</v>
+        <v>5498.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>5691.5</v>
+        <v>5690.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>5704.5</v>
+        <v>5701.84</v>
       </c>
       <c r="AD9" t="n">
-        <v>5723</v>
+        <v>5721.67</v>
       </c>
       <c r="AE9" t="n">
-        <v>61</v>
+        <v>58.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
@@ -1924,39 +1924,39 @@
         <v>17.6</v>
       </c>
       <c r="AM9" t="n">
-        <v>5812.74</v>
+        <v>5810.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>5564.44</v>
+        <v>5561.22</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,984.66 Cr., a P/E ratio of 29.51, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,936.83 Cr., a P/E ratio of 29.49, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.98 (Bullish Momentum Zone), while MACD Line (60.48) trades above Signal (53.66) with an expanding histogram (+6.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹5522.76). Daily volatility envelope is bounded by ATR(14) of ₹119.75.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,686.00) is positioned above the 30-day DMA (₹5,587.60), 50-day DMA (₹5,491.02), and 200-day DMA (₹5,522.76). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,682.00) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[5686.0, 5703.06, 5720.12, 5737.17, 5754.23, 5771.29]</t>
+          <t>[5682.0, 5709.99, 5737.98, 5765.98, 5793.97, 5821.96]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[5686.0, 5750.96, 5787.86, 5820.14, 5850.03, 5878.4]</t>
+          <t>[5682.0, 5758.96, 5807.24, 5850.8, 5891.91, 5931.46]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[5686.0, 5667.13, 5669.31, 5674.95, 5682.38, 5690.96]</t>
+          <t>[5682.0, 5673.26, 5686.04, 5702.36, 5720.51, 5739.83]</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25000</v>
+        <v>97297.62</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1985,15 +1985,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>369.75</v>
+        <v>369.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹368.23 - ₹372.03</t>
+          <t>₹367.98 - ₹371.78</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>375.84</v>
+        <v>375.59</v>
       </c>
       <c r="I10" t="n">
         <v>357.93</v>
@@ -2020,16 +2020,16 @@
         <v>7.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R10" t="n">
-        <v>45.2</v>
+        <v>44.8</v>
       </c>
       <c r="S10" t="n">
         <v>0.26</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.33</v>
+        <v>-1.35</v>
       </c>
       <c r="U10" t="n">
         <v>50</v>
@@ -2041,25 +2041,25 @@
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>360.62</v>
+        <v>360.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>370.58</v>
+        <v>370.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>372.71</v>
+        <v>372.46</v>
       </c>
       <c r="AA10" t="n">
-        <v>358.33</v>
+        <v>358.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>369.05</v>
+        <v>369.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>371.3</v>
+        <v>371.26</v>
       </c>
       <c r="AD10" t="n">
-        <v>372.85</v>
+        <v>373.03</v>
       </c>
       <c r="AE10" t="n">
         <v>81.2</v>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
@@ -2088,14 +2088,14 @@
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>379.19</v>
+        <v>378.95</v>
       </c>
       <c r="AN10" t="n">
-        <v>359.41</v>
+        <v>359.73</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.09, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹97,297.62 Cr., a P/E ratio of 6.08, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2105,22 +2105,22 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹369.75) is positioned above the 30-day DMA (₹357.93), 50-day DMA (₹350.57), and 200-day DMA (₹347.65). The price distance from 200 DMA is +7.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹369.50) is positioned above the 30-day DMA (₹357.93), 50-day DMA (₹350.57), and 200-day DMA (₹347.65). The price distance from 200 DMA is +7.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[369.75, 370.86, 371.97, 373.08, 374.19, 375.3]</t>
+          <t>[369.5, 370.61, 371.72, 372.83, 373.93, 375.04]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[369.75, 373.9, 376.27, 378.35, 380.28, 382.11]</t>
+          <t>[369.5, 373.65, 376.02, 378.1, 380.02, 381.85]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[369.75, 368.58, 368.74, 369.12, 369.62, 370.19]</t>
+          <t>[369.5, 368.32, 368.49, 368.87, 369.37, 369.94]</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>104701.41</v>
+        <v>104333.29</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2149,15 +2149,15 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2190</v>
+        <v>2182.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹2180.54 - ₹2204.19</t>
+          <t>₹2172.84 - ₹2196.49</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2227.85</v>
+        <v>2220.15</v>
       </c>
       <c r="I11" t="n">
         <v>2146.11</v>
@@ -2184,16 +2184,16 @@
         <v>47.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R11" t="n">
-        <v>44.2</v>
+        <v>43.9</v>
       </c>
       <c r="S11" t="n">
         <v>0.25</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.45</v>
+        <v>-1.47</v>
       </c>
       <c r="U11" t="n">
         <v>50</v>
@@ -2205,25 +2205,25 @@
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>2159.51</v>
+        <v>2150.54</v>
       </c>
       <c r="Y11" t="n">
-        <v>2236.16</v>
+        <v>2226.92</v>
       </c>
       <c r="Z11" t="n">
-        <v>2207.52</v>
+        <v>2199.76</v>
       </c>
       <c r="AA11" t="n">
-        <v>2119.04</v>
+        <v>2111.34</v>
       </c>
       <c r="AB11" t="n">
-        <v>2196.43</v>
+        <v>2191.93</v>
       </c>
       <c r="AC11" t="n">
-        <v>2208.46</v>
+        <v>2205.26</v>
       </c>
       <c r="AD11" t="n">
-        <v>2226.93</v>
+        <v>2228.23</v>
       </c>
       <c r="AE11" t="n">
         <v>58.7</v>
@@ -2233,14 +2233,14 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>96.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="AJ11" t="n">
         <v>17.5</v>
@@ -2252,14 +2252,14 @@
         <v>11.6</v>
       </c>
       <c r="AM11" t="n">
-        <v>2260.71</v>
+        <v>2250.84</v>
       </c>
       <c r="AN11" t="n">
-        <v>2126.54</v>
+        <v>2125.16</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹104,701.41 Cr., a P/E ratio of 96.65, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
+          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹104,333.29 Cr., a P/E ratio of 96.31, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2269,22 +2269,22 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,190.00) is positioned above the 30-day DMA (₹2,146.11), 50-day DMA (₹2,067.23), and 200-day DMA (₹1,708.73). The price distance from 200 DMA is +28.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,182.30) is positioned above the 30-day DMA (₹2,146.11), 50-day DMA (₹2,067.23), and 200-day DMA (₹1,708.73). The price distance from 200 DMA is +28.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[2190.0, 2196.57, 2203.14, 2209.71, 2216.28, 2222.85]</t>
+          <t>[2182.3, 2188.85, 2195.39, 2201.94, 2208.49, 2215.03]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[2190.0, 2215.49, 2229.9, 2242.49, 2254.13, 2265.16]</t>
+          <t>[2182.3, 2207.77, 2222.15, 2234.72, 2246.33, 2257.35]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[2190.0, 2182.38, 2183.07, 2185.13, 2187.9, 2191.12]</t>
+          <t>[2182.3, 2174.65, 2175.32, 2177.36, 2180.1, 2183.3]</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>117533.42</v>
+        <v>117468.78</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2313,15 +2313,15 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1454.9</v>
+        <v>1454.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹1448.1 - ₹1465.1</t>
+          <t>₹1447.3 - ₹1464.3</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1482.09</v>
+        <v>1481.29</v>
       </c>
       <c r="I12" t="n">
         <v>1440.19</v>
@@ -2348,10 +2348,10 @@
         <v>33.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R12" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="S12" t="n">
         <v>0.23</v>
@@ -2369,25 +2369,25 @@
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>1414.12</v>
+        <v>1413.32</v>
       </c>
       <c r="Y12" t="n">
-        <v>1423.8</v>
+        <v>1422.88</v>
       </c>
       <c r="Z12" t="n">
-        <v>1466.54</v>
+        <v>1465.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>1403.92</v>
+        <v>1403.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1459.17</v>
+        <v>1458.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1465.34</v>
+        <v>1465.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1475.77</v>
+        <v>1477.1</v>
       </c>
       <c r="AE12" t="n">
         <v>61.6</v>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH12" t="n">
@@ -2416,14 +2416,14 @@
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>1486.6</v>
+        <v>1486.24</v>
       </c>
       <c r="AN12" t="n">
-        <v>1423.67</v>
+        <v>1421.82</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,533.42 Cr., a P/E ratio of 34.90, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,468.78 Cr., a P/E ratio of 34.88, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2433,22 +2433,22 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,454.90) is positioned above the 30-day DMA (₹1,440.19), 50-day DMA (₹1,416.57), and 200-day DMA (₹1,395.71). The price distance from 200 DMA is +5.55%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,454.10) is positioned above the 30-day DMA (₹1,440.19), 50-day DMA (₹1,416.57), and 200-day DMA (₹1,395.71). The price distance from 200 DMA is +5.55%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[1454.9, 1459.26, 1463.63, 1467.99, 1472.36, 1476.72]</t>
+          <t>[1454.1, 1458.46, 1462.82, 1467.19, 1471.55, 1475.91]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1454.9, 1472.86, 1482.85, 1491.54, 1499.55, 1507.12]</t>
+          <t>[1454.1, 1472.06, 1482.05, 1490.73, 1498.74, 1506.31]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1454.9, 1449.07, 1449.21, 1450.33, 1451.97, 1453.93]</t>
+          <t>[1454.1, 1448.27, 1448.41, 1449.53, 1451.16, 1453.11]</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>256306.68</v>
+        <v>254918.45</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2477,15 +2477,15 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1089.3</v>
+        <v>1083.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1083.11 - ₹1098.59</t>
+          <t>₹1077.21 - ₹1092.69</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1114.06</v>
+        <v>1108.16</v>
       </c>
       <c r="I13" t="n">
         <v>1034.29</v>
@@ -2512,46 +2512,46 @@
         <v>30.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R13" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="S13" t="n">
         <v>0.19</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.73</v>
+        <v>-1.72</v>
       </c>
       <c r="U13" t="n">
         <v>56.7</v>
       </c>
       <c r="V13" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="W13" t="n">
         <v>-0.77</v>
       </c>
       <c r="X13" t="n">
-        <v>1066.15</v>
+        <v>1058.52</v>
       </c>
       <c r="Y13" t="n">
-        <v>1104.28</v>
+        <v>1096.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>1098.01</v>
+        <v>1092.07</v>
       </c>
       <c r="AA13" t="n">
-        <v>1042.88</v>
+        <v>1036.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1085.6</v>
+        <v>1083.63</v>
       </c>
       <c r="AC13" t="n">
-        <v>1095.4</v>
+        <v>1091.46</v>
       </c>
       <c r="AD13" t="n">
-        <v>1101.5</v>
+        <v>1099.53</v>
       </c>
       <c r="AE13" t="n">
         <v>49.7</v>
@@ -2561,14 +2561,14 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH13" t="n">
         <v>0.15</v>
       </c>
       <c r="AI13" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AJ13" t="n">
         <v>39.1</v>
@@ -2580,14 +2580,14 @@
         <v>18.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>1128.1</v>
+        <v>1123.14</v>
       </c>
       <c r="AN13" t="n">
-        <v>1051.57</v>
+        <v>1051.08</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹256,306.68 Cr., a P/E ratio of 19.24, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹254,918.45 Cr., a P/E ratio of 19.13, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2597,22 +2597,22 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,089.30) is positioned above the 30-day DMA (₹1,034.29), 50-day DMA (₹997.16), and 200-day DMA (₹944.85). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,083.40) is positioned above the 30-day DMA (₹1,034.29), 50-day DMA (₹997.16), and 200-day DMA (₹944.85). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>[1089.3, 1092.57, 1095.84, 1099.1, 1102.37, 1105.64]</t>
+          <t>[1083.4, 1086.65, 1089.9, 1093.15, 1096.4, 1099.65]</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1089.3, 1104.95, 1113.34, 1120.55, 1127.13, 1133.32]</t>
+          <t>[1083.4, 1099.03, 1107.41, 1114.59, 1121.16, 1127.33]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1089.3, 1083.28, 1082.7, 1083.02, 1083.8, 1084.88]</t>
+          <t>[1083.4, 1077.37, 1076.77, 1077.07, 1077.83, 1078.89]</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>77400.06</v>
+        <v>17628.14</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2641,142 +2641,142 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1748.4</v>
+        <v>615.3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹1736.8 - ₹1765.8</t>
+          <t>₹611.04 - ₹621.69</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1794.81</v>
+        <v>632.34</v>
       </c>
       <c r="I14" t="n">
-        <v>1511.17</v>
+        <v>579.77</v>
       </c>
       <c r="J14" t="n">
-        <v>1475.45</v>
+        <v>544.3099999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>1504.57</v>
+        <v>553.6900000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>14.12</v>
+        <v>10.78</v>
       </c>
       <c r="M14" t="n">
-        <v>60.69</v>
+        <v>15.03</v>
       </c>
       <c r="N14" t="n">
-        <v>36.2</v>
+        <v>16.15</v>
       </c>
       <c r="O14" t="n">
-        <v>24.49</v>
+        <v>-1.12</v>
       </c>
       <c r="P14" t="n">
-        <v>58.01</v>
+        <v>21.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R14" t="n">
-        <v>48.8</v>
+        <v>53.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.93</v>
+        <v>-2.01</v>
       </c>
       <c r="U14" t="n">
-        <v>48.3</v>
+        <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>7.29</v>
+        <v>4.79</v>
       </c>
       <c r="W14" t="n">
         <v>-0.77</v>
       </c>
       <c r="X14" t="n">
-        <v>1744.4</v>
+        <v>589.74</v>
       </c>
       <c r="Y14" t="n">
-        <v>1805.59</v>
+        <v>603.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>1770.62</v>
+        <v>620.22</v>
       </c>
       <c r="AA14" t="n">
-        <v>1661.38</v>
+        <v>583.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1754.83</v>
+        <v>617.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1768.36</v>
+        <v>627.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1788.33</v>
+        <v>639.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>71.40000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH14" t="n">
         <v>0.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>35.8</v>
+        <v>88.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>49.9</v>
+        <v>-10.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>9.6</v>
+        <v>3.7</v>
       </c>
       <c r="AL14" t="n">
-        <v>15</v>
+        <v>6.7</v>
       </c>
       <c r="AM14" t="n">
-        <v>1812.84</v>
+        <v>645.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>1682.07</v>
+        <v>584.4400000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹77,400.06 Cr., a P/E ratio of 35.77, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,628.14 Cr., a P/E ratio of 88.79, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.40 (Bullish Momentum Zone), while MACD Line (60.69) trades above Signal (36.20) with an expanding histogram (+24.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.12% above the 200-day DMA (₹1504.57). Daily volatility envelope is bounded by ATR(14) of ₹58.01.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.93 (Bullish Momentum Zone), while MACD Line (15.03) trades below Signal (16.15) with an expanding histogram (-1.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹553.69). Daily volatility envelope is bounded by ATR(14) of ₹21.30.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,748.40) is positioned above the 30-day DMA (₹1,511.17), 50-day DMA (₹1,475.45), and 200-day DMA (₹1,504.57). The price distance from 200 DMA is +14.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹615.30) is positioned above the 30-day DMA (₹579.77), 50-day DMA (₹544.31), and 200-day DMA (₹553.69). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>[1748.4, 1770.62, 1792.85, 1815.07, 1837.29, 1859.51]</t>
+          <t>[615.3, 617.15, 618.99, 620.84, 622.68, 624.53]</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[1748.4, 1793.83, 1825.66, 1855.26, 1883.7, 1911.4]</t>
+          <t>[615.3, 625.67, 631.04, 635.59, 639.72, 643.58]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[1748.4, 1753.22, 1768.23, 1784.92, 1802.48, 1820.6]</t>
+          <t>[615.3, 610.76, 609.95, 609.77, 609.9, 610.24]</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17754.2</v>
+        <v>77165.44</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2805,142 +2805,142 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>619.7</v>
+        <v>1743.1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹615.44 - ₹626.09</t>
+          <t>₹1731.5 - ₹1760.5</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>636.74</v>
+        <v>1789.51</v>
       </c>
       <c r="I15" t="n">
-        <v>579.77</v>
+        <v>1511.17</v>
       </c>
       <c r="J15" t="n">
-        <v>544.3099999999999</v>
+        <v>1475.45</v>
       </c>
       <c r="K15" t="n">
-        <v>553.6900000000001</v>
+        <v>1504.57</v>
       </c>
       <c r="L15" t="n">
-        <v>10.78</v>
+        <v>14.12</v>
       </c>
       <c r="M15" t="n">
-        <v>15.03</v>
+        <v>60.69</v>
       </c>
       <c r="N15" t="n">
-        <v>16.15</v>
+        <v>36.2</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.12</v>
+        <v>24.49</v>
       </c>
       <c r="P15" t="n">
-        <v>21.3</v>
+        <v>58.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R15" t="n">
-        <v>53.2</v>
+        <v>48.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.99</v>
+        <v>-2.01</v>
       </c>
       <c r="U15" t="n">
-        <v>55</v>
+        <v>48.3</v>
       </c>
       <c r="V15" t="n">
-        <v>4.79</v>
+        <v>7.29</v>
       </c>
       <c r="W15" t="n">
         <v>-0.77</v>
       </c>
       <c r="X15" t="n">
-        <v>594.14</v>
+        <v>1737.19</v>
       </c>
       <c r="Y15" t="n">
-        <v>608.59</v>
+        <v>1798.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>624.66</v>
+        <v>1763.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>587.75</v>
+        <v>1656.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>618.72</v>
+        <v>1752.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>630.4400000000001</v>
+        <v>1765.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>641.17</v>
+        <v>1787.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>56.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH15" t="n">
         <v>0.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>89.40000000000001</v>
+        <v>35.7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-10.1</v>
+        <v>49.9</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.7</v>
+        <v>9.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="AM15" t="n">
-        <v>648.89</v>
+        <v>1812.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>586.98</v>
+        <v>1679.44</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,754.20 Cr., a P/E ratio of 89.42, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹77,165.44 Cr., a P/E ratio of 35.66, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.93 (Bullish Momentum Zone), while MACD Line (15.03) trades below Signal (16.15) with an expanding histogram (-1.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹553.69). Daily volatility envelope is bounded by ATR(14) of ₹21.30.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.40 (Bullish Momentum Zone), while MACD Line (60.69) trades above Signal (36.20) with an expanding histogram (+24.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.12% above the 200-day DMA (₹1504.57). Daily volatility envelope is bounded by ATR(14) of ₹58.01.</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹619.70) is positioned above the 30-day DMA (₹579.77), 50-day DMA (₹544.31), and 200-day DMA (₹553.69). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,743.10) is positioned above the 30-day DMA (₹1,511.17), 50-day DMA (₹1,475.45), and 200-day DMA (₹1,504.57). The price distance from 200 DMA is +14.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>[619.7, 621.56, 623.42, 625.28, 627.14, 629.0]</t>
+          <t>[1743.1, 1763.33, 1783.57, 1803.8, 1824.04, 1844.27]</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[619.7, 630.08, 635.47, 640.03, 644.18, 648.05]</t>
+          <t>[1743.1, 1786.54, 1816.38, 1843.99, 1870.45, 1896.16]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[619.7, 615.17, 614.38, 614.21, 614.36, 614.71]</t>
+          <t>[1743.1, 1745.93, 1758.96, 1773.66, 1789.23, 1805.35]</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>146111.96</v>
+        <v>146005.65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2969,15 +2969,15 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1649.4</v>
+        <v>1648.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹1640.23 - ₹1663.16</t>
+          <t>₹1639.03 - ₹1661.96</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1686.1</v>
+        <v>1684.9</v>
       </c>
       <c r="I16" t="n">
         <v>1487.74</v>
@@ -3004,16 +3004,16 @@
         <v>45.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R16" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="S16" t="n">
         <v>0.19</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.03</v>
+        <v>-2.01</v>
       </c>
       <c r="U16" t="n">
         <v>48.3</v>
@@ -3025,25 +3025,25 @@
         <v>-0.77</v>
       </c>
       <c r="X16" t="n">
-        <v>1594.35</v>
+        <v>1593.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1651.15</v>
+        <v>1649.86</v>
       </c>
       <c r="Z16" t="n">
-        <v>1662.6</v>
+        <v>1661.39</v>
       </c>
       <c r="AA16" t="n">
-        <v>1580.59</v>
+        <v>1579.39</v>
       </c>
       <c r="AB16" t="n">
-        <v>1649.5</v>
+        <v>1649.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>1658.9</v>
+        <v>1658.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1668.4</v>
+        <v>1668</v>
       </c>
       <c r="AE16" t="n">
         <v>77.8</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH16" t="n">
@@ -3072,14 +3072,14 @@
         <v>15</v>
       </c>
       <c r="AM16" t="n">
-        <v>1694.09</v>
+        <v>1694.52</v>
       </c>
       <c r="AN16" t="n">
-        <v>1607.04</v>
+        <v>1601.79</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,111.96 Cr., a P/E ratio of 28.54, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,005.65 Cr., a P/E ratio of 28.52, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -3089,22 +3089,22 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,649.40) is positioned above the 30-day DMA (₹1,487.74), 50-day DMA (₹1,465.74), and 200-day DMA (₹1,460.05). The price distance from 200 DMA is +13.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,648.20) is positioned above the 30-day DMA (₹1,487.74), 50-day DMA (₹1,465.74), and 200-day DMA (₹1,460.05). The price distance from 200 DMA is +13.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>[1649.4, 1654.35, 1659.3, 1664.24, 1669.19, 1674.14]</t>
+          <t>[1648.2, 1653.14, 1658.09, 1663.03, 1667.98, 1672.92]</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[1649.4, 1672.7, 1685.25, 1696.03, 1705.89, 1715.17]</t>
+          <t>[1648.2, 1671.49, 1684.04, 1694.81, 1704.68, 1713.95]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[1649.4, 1640.59, 1639.83, 1640.41, 1641.67, 1643.37]</t>
+          <t>[1648.2, 1639.38, 1638.63, 1639.2, 1640.46, 1642.15]</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>47370.04</v>
+        <v>47357.83</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3133,91 +3133,91 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1164.2</v>
+        <v>1163.9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹1157.29 - ₹1174.56</t>
+          <t>₹1156.99 - ₹1174.27</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1191.84</v>
+        <v>1191.55</v>
       </c>
       <c r="I17" t="n">
-        <v>1109.24</v>
+        <v>1109.56</v>
       </c>
       <c r="J17" t="n">
-        <v>1105.8</v>
+        <v>1105.35</v>
       </c>
       <c r="K17" t="n">
-        <v>1100.59</v>
+        <v>1100.33</v>
       </c>
       <c r="L17" t="n">
-        <v>3.15</v>
+        <v>3.87</v>
       </c>
       <c r="M17" t="n">
-        <v>9.49</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>5.67</v>
+        <v>4.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.82</v>
+        <v>4.42</v>
       </c>
       <c r="P17" t="n">
-        <v>34.55</v>
+        <v>34.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R17" t="n">
-        <v>43.9</v>
+        <v>45.1</v>
       </c>
       <c r="S17" t="n">
         <v>0.18</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.15</v>
+        <v>-2.08</v>
       </c>
       <c r="U17" t="n">
         <v>48.3</v>
       </c>
       <c r="V17" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="W17" t="n">
         <v>-0.77</v>
       </c>
       <c r="X17" t="n">
-        <v>1151.2</v>
+        <v>1148.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1191.94</v>
+        <v>1188.79</v>
       </c>
       <c r="Z17" t="n">
-        <v>1173.51</v>
+        <v>1173.21</v>
       </c>
       <c r="AA17" t="n">
-        <v>1112.37</v>
+        <v>1112.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1160.87</v>
+        <v>1160.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>1177.34</v>
+        <v>1177.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>1190.47</v>
+        <v>1190.37</v>
       </c>
       <c r="AE17" t="n">
-        <v>53.6</v>
+        <v>52.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH17" t="n">
@@ -3236,39 +3236,39 @@
         <v>15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1198.17</v>
+        <v>1197.39</v>
       </c>
       <c r="AN17" t="n">
-        <v>1128.1</v>
+        <v>1129.04</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹47,370.04 Cr., a P/E ratio of 38.69, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹47,357.83 Cr., a P/E ratio of 38.68, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.63 (Consolidation Zone), while MACD Line (9.49) trades above Signal (5.67) with an expanding histogram (+3.82). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.15% above the 200-day DMA (₹1100.59). Daily volatility envelope is bounded by ATR(14) of ₹34.55.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,164.20) is positioned above the 30-day DMA (₹1,109.24), 50-day DMA (₹1,105.80), and 200-day DMA (₹1,100.59). The price distance from 200 DMA is +3.15%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,163.90) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>[1164.2, 1168.66, 1173.12, 1177.58, 1182.03, 1186.49]</t>
+          <t>[1163.9, 1167.39, 1170.88, 1174.38, 1177.87, 1181.36]</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[1164.2, 1182.48, 1192.66, 1201.51, 1209.67, 1217.4]</t>
+          <t>[1163.9, 1181.22, 1190.44, 1198.32, 1205.52, 1212.27]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[1164.2, 1158.29, 1158.46, 1159.62, 1161.3, 1163.32]</t>
+          <t>[1163.9, 1157.02, 1156.22, 1156.41, 1157.13, 1158.17]</t>
         </is>
       </c>
     </row>
@@ -3280,159 +3280,159 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>62076.64</v>
+        <v>285413.21</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2060.8</v>
+        <v>310.05</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹2048.02 - ₹2079.98</t>
+          <t>₹307.86 - ₹313.33</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2111.93</v>
+        <v>318.8</v>
       </c>
       <c r="I18" t="n">
-        <v>2010.06</v>
+        <v>282.98</v>
       </c>
       <c r="J18" t="n">
-        <v>1895.79</v>
+        <v>270.14</v>
       </c>
       <c r="K18" t="n">
-        <v>1880.5</v>
+        <v>273.78</v>
       </c>
       <c r="L18" t="n">
-        <v>11.98</v>
+        <v>10.47</v>
       </c>
       <c r="M18" t="n">
-        <v>59.11</v>
+        <v>9.73</v>
       </c>
       <c r="N18" t="n">
-        <v>67</v>
+        <v>8.68</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.9</v>
+        <v>1.05</v>
       </c>
       <c r="P18" t="n">
-        <v>63.92</v>
+        <v>10.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R18" t="n">
-        <v>42.6</v>
+        <v>48.7</v>
       </c>
       <c r="S18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.33</v>
+        <v>-2.32</v>
       </c>
       <c r="U18" t="n">
         <v>51.7</v>
       </c>
       <c r="V18" t="n">
-        <v>5.54</v>
+        <v>2.35</v>
       </c>
       <c r="W18" t="n">
         <v>-0.77</v>
       </c>
       <c r="X18" t="n">
-        <v>1984.1</v>
+        <v>305.64</v>
       </c>
       <c r="Y18" t="n">
-        <v>1963.68</v>
+        <v>316.49</v>
       </c>
       <c r="Z18" t="n">
-        <v>2077.29</v>
+        <v>312.53</v>
       </c>
       <c r="AA18" t="n">
-        <v>1964.92</v>
+        <v>293.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2064.7</v>
+        <v>310.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>2084.1</v>
+        <v>312.04</v>
       </c>
       <c r="AD18" t="n">
-        <v>2107.4</v>
+        <v>314.02</v>
       </c>
       <c r="AE18" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH18" t="n">
         <v>0.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>33.5</v>
+        <v>689</v>
       </c>
       <c r="AJ18" t="n">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="AK18" t="n">
-        <v>36.1</v>
+        <v>0.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AM18" t="n">
-        <v>2135.22</v>
+        <v>321.78</v>
       </c>
       <c r="AN18" t="n">
-        <v>1990.93</v>
+        <v>299.7</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹62,076.64 Cr., a P/E ratio of 33.51, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹285,413.21 Cr., a P/E ratio of 689.00, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 45.03 (Consolidation Zone), while MACD Line (59.11) trades below Signal (67.00) with an expanding histogram (-7.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.98% above the 200-day DMA (₹1880.50). Daily volatility envelope is bounded by ATR(14) of ₹63.92.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.99 (Bullish Momentum Zone), while MACD Line (9.73) trades above Signal (8.68) with an expanding histogram (+1.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.47% above the 200-day DMA (₹273.78). Daily volatility envelope is bounded by ATR(14) of ₹10.94.</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,060.80) is positioned above the 30-day DMA (₹2,010.06), 50-day DMA (₹1,895.79), and 200-day DMA (₹1,880.50). The price distance from 200 DMA is +11.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹310.05) is positioned above the 30-day DMA (₹282.98), 50-day DMA (₹270.14), and 200-day DMA (₹273.78). The price distance from 200 DMA is +10.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>[2060.8, 2066.98, 2073.16, 2079.35, 2085.53, 2091.71]</t>
+          <t>[310.05, 310.98, 311.91, 312.84, 313.77, 314.7]</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[2060.8, 2092.55, 2109.32, 2123.63, 2136.66, 2148.88]</t>
+          <t>[310.05, 315.35, 318.1, 320.42, 322.52, 324.48]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[2060.8, 2047.81, 2046.05, 2046.13, 2047.18, 2048.83]</t>
+          <t>[310.05, 307.7, 307.27, 307.16, 307.21, 307.36]</t>
         </is>
       </c>
     </row>
@@ -3444,159 +3444,159 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>286103.62</v>
+        <v>61248.27</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>310.8</v>
+        <v>2033.3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>₹308.61 - ₹314.08</t>
+          <t>₹2020.52 - ₹2052.48</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>319.55</v>
+        <v>2084.43</v>
       </c>
       <c r="I19" t="n">
-        <v>282.98</v>
+        <v>2010.06</v>
       </c>
       <c r="J19" t="n">
-        <v>270.14</v>
+        <v>1895.79</v>
       </c>
       <c r="K19" t="n">
-        <v>273.78</v>
+        <v>1880.5</v>
       </c>
       <c r="L19" t="n">
-        <v>10.47</v>
+        <v>11.98</v>
       </c>
       <c r="M19" t="n">
-        <v>9.73</v>
+        <v>59.11</v>
       </c>
       <c r="N19" t="n">
-        <v>8.68</v>
+        <v>67</v>
       </c>
       <c r="O19" t="n">
-        <v>1.05</v>
+        <v>-7.9</v>
       </c>
       <c r="P19" t="n">
-        <v>10.94</v>
+        <v>63.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R19" t="n">
-        <v>48.3</v>
+        <v>42.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.34</v>
+        <v>-2.38</v>
       </c>
       <c r="U19" t="n">
         <v>51.7</v>
       </c>
       <c r="V19" t="n">
-        <v>2.35</v>
+        <v>5.48</v>
       </c>
       <c r="W19" t="n">
         <v>-0.77</v>
       </c>
       <c r="X19" t="n">
-        <v>306.51</v>
+        <v>1956.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>317.39</v>
+        <v>1931.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>313.29</v>
+        <v>2049.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>294.4</v>
+        <v>1937.42</v>
       </c>
       <c r="AB19" t="n">
-        <v>310.97</v>
+        <v>2037.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>312.54</v>
+        <v>2084.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>314.27</v>
+        <v>2135.1</v>
       </c>
       <c r="AE19" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH19" t="n">
         <v>0.15</v>
       </c>
       <c r="AI19" t="n">
-        <v>690.7</v>
+        <v>33.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>182</v>
+        <v>63</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.6</v>
+        <v>36.1</v>
       </c>
       <c r="AL19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AM19" t="n">
-        <v>321.35</v>
+        <v>2104.86</v>
       </c>
       <c r="AN19" t="n">
-        <v>300.74</v>
+        <v>1959.14</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹286,103.62 Cr., a P/E ratio of 690.67, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹61,248.27 Cr., a P/E ratio of 33.07, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.99 (Bullish Momentum Zone), while MACD Line (9.73) trades above Signal (8.68) with an expanding histogram (+1.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.47% above the 200-day DMA (₹273.78). Daily volatility envelope is bounded by ATR(14) of ₹10.94.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 45.03 (Consolidation Zone), while MACD Line (59.11) trades below Signal (67.00) with an expanding histogram (-7.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.98% above the 200-day DMA (₹1880.50). Daily volatility envelope is bounded by ATR(14) of ₹63.92.</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹310.80) is positioned above the 30-day DMA (₹282.98), 50-day DMA (₹270.14), and 200-day DMA (₹273.78). The price distance from 200 DMA is +10.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,033.30) is positioned above the 30-day DMA (₹2,010.06), 50-day DMA (₹1,895.79), and 200-day DMA (₹1,880.50). The price distance from 200 DMA is +11.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>[310.8, 311.73, 312.66, 313.6, 314.53, 315.46]</t>
+          <t>[2033.3, 2039.4, 2045.5, 2051.6, 2057.7, 2063.8]</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>[310.8, 316.11, 318.85, 321.17, 323.28, 325.24]</t>
+          <t>[2033.3, 2064.97, 2081.66, 2095.88, 2108.83, 2120.97]</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>[310.8, 308.45, 308.03, 307.91, 307.97, 308.13]</t>
+          <t>[2033.3, 2020.22, 2018.38, 2018.39, 2019.35, 2020.92]</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>84903.75999999999</v>
+        <v>84836.88</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -3625,15 +3625,15 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>13964</v>
+        <v>13953</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>₹13871.67 - ₹14102.49</t>
+          <t>₹13860.67 - ₹14091.49</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>14333.31</v>
+        <v>14322.31</v>
       </c>
       <c r="I20" t="n">
         <v>13241.63</v>
@@ -3660,16 +3660,16 @@
         <v>461.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.97</v>
+        <v>12.19</v>
       </c>
       <c r="R20" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="S20" t="n">
         <v>0.16</v>
       </c>
       <c r="T20" t="n">
-        <v>-2.4</v>
+        <v>-2.39</v>
       </c>
       <c r="U20" t="n">
         <v>46.7</v>
@@ -3681,25 +3681,25 @@
         <v>-0.77</v>
       </c>
       <c r="X20" t="n">
-        <v>13410.03</v>
+        <v>13399.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>13817.92</v>
+        <v>13802.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>14075.71</v>
+        <v>14064.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>13271.54</v>
+        <v>13260.54</v>
       </c>
       <c r="AB20" t="n">
-        <v>13954</v>
+        <v>13950.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>14096</v>
+        <v>14088.66</v>
       </c>
       <c r="AD20" t="n">
-        <v>14228</v>
+        <v>14224.33</v>
       </c>
       <c r="AE20" t="n">
         <v>58.4</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH20" t="n">
@@ -3728,14 +3728,14 @@
         <v>15</v>
       </c>
       <c r="AM20" t="n">
-        <v>14521.35</v>
+        <v>14509.24</v>
       </c>
       <c r="AN20" t="n">
-        <v>13400.48</v>
+        <v>13432.72</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹84,903.76 Cr., a P/E ratio of 40.90, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹84,836.88 Cr., a P/E ratio of 40.87, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -3745,22 +3745,22 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,964.00) is positioned above the 30-day DMA (₹13,241.63), 50-day DMA (₹12,652.22), and 200-day DMA (₹12,318.23). The price distance from 200 DMA is +14.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,953.00) is positioned above the 30-day DMA (₹13,241.63), 50-day DMA (₹12,652.22), and 200-day DMA (₹12,318.23). The price distance from 200 DMA is +14.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>[13964.0, 14005.89, 14047.78, 14089.68, 14131.57, 14173.46]</t>
+          <t>[13953.0, 13994.86, 14036.72, 14078.58, 14120.44, 14162.29]</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>[13964.0, 14190.55, 14308.93, 14409.51, 14500.88, 14586.37]</t>
+          <t>[13953.0, 14179.52, 14297.86, 14398.41, 14489.75, 14575.2]</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>[13964.0, 13867.4, 13851.93, 13849.8, 13854.58, 13863.78]</t>
+          <t>[13953.0, 13856.37, 13840.86, 13838.7, 13843.45, 13852.62]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT20"/>
+  <dimension ref="A1:AT15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,7 +656,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -665,150 +665,150 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1034171.29</v>
+        <v>131008.05</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🟢 HIGH CONVICTION BUY</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1441.7</v>
+        <v>113.99</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹1437.13 - ₹1448.56</t>
+          <t>₹113.59 - ₹114.59</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1460</v>
+        <v>115.59</v>
       </c>
       <c r="I2" t="n">
-        <v>1398.49</v>
+        <v>107.9</v>
       </c>
       <c r="J2" t="n">
-        <v>1349.96</v>
+        <v>106.76</v>
       </c>
       <c r="K2" t="n">
-        <v>1337.12</v>
+        <v>112.63</v>
       </c>
       <c r="L2" t="n">
-        <v>6.45</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>20.38</v>
+        <v>1.77</v>
       </c>
       <c r="N2" t="n">
-        <v>24.46</v>
+        <v>1.38</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.08</v>
+        <v>0.4</v>
       </c>
       <c r="P2" t="n">
-        <v>22.87</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
         <v>12.19</v>
       </c>
       <c r="R2" t="n">
-        <v>54.8</v>
+        <v>55</v>
       </c>
       <c r="S2" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.64</v>
+        <v>-0.74</v>
       </c>
       <c r="U2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V2" t="n">
-        <v>6.34</v>
+        <v>3.33</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>1423.17</v>
+        <v>111.59</v>
       </c>
       <c r="Y2" t="n">
-        <v>1473.63</v>
+        <v>115.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1453.23</v>
+        <v>114.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1407.39</v>
+        <v>110.99</v>
       </c>
       <c r="AB2" t="n">
-        <v>1445.57</v>
+        <v>113.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>1449.54</v>
+        <v>114.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>1457.37</v>
+        <v>114.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>60.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>18.6</v>
+        <v>5.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11.4</v>
+        <v>15.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>27.5</v>
+        <v>38.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>1469.5</v>
+        <v>116.96</v>
       </c>
       <c r="AN2" t="n">
-        <v>1414.71</v>
+        <v>110.62</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,034,171.29 Cr., a P/E ratio of 18.63, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹131,008.05 Cr., a P/E ratio of 5.88, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.14 (Bullish Momentum Zone), while MACD Line (20.38) trades below Signal (24.46) with an expanding histogram (-4.08). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.45% above the 200-day DMA (₹1337.12). Daily volatility envelope is bounded by ATR(14) of ₹22.87.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.61 (Bullish Momentum Zone), while MACD Line (1.77) trades above Signal (1.38) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.33% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.00.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,441.70) is positioned above the 30-day DMA (₹1,398.49), 50-day DMA (₹1,349.96), and 200-day DMA (₹1,337.12). The price distance from 200 DMA is +6.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.99) is positioned above the 30-day DMA (₹107.90), 50-day DMA (₹106.76), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.33%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[1441.7, 1446.03, 1450.35, 1454.68, 1459.0, 1463.33]</t>
+          <t>[113.99, 114.33, 114.67, 115.02, 115.36, 115.7]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[1441.7, 1455.17, 1463.29, 1470.52, 1477.3, 1483.78]</t>
+          <t>[113.99, 115.13, 115.81, 116.4, 116.96, 117.49]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[1441.7, 1439.16, 1440.65, 1442.79, 1445.28, 1447.98]</t>
+          <t>[113.99, 113.73, 113.83, 113.98, 114.16, 114.36]</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>130329.98</v>
+        <v>1043424.87</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -837,142 +837,142 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>113.4</v>
+        <v>1454.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹113.0 - ₹114.0</t>
+          <t>₹1449.78 - ₹1461.82</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>115</v>
+        <v>1473.87</v>
       </c>
       <c r="I3" t="n">
-        <v>107.8</v>
+        <v>1402.46</v>
       </c>
       <c r="J3" t="n">
-        <v>106.57</v>
+        <v>1353.54</v>
       </c>
       <c r="K3" t="n">
-        <v>112.63</v>
+        <v>1337.56</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07000000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="M3" t="n">
-        <v>1.69</v>
+        <v>22.02</v>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>23.97</v>
       </c>
       <c r="O3" t="n">
-        <v>0.41</v>
+        <v>-1.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>24.08</v>
       </c>
       <c r="Q3" t="n">
         <v>12.19</v>
       </c>
       <c r="R3" t="n">
-        <v>52.9</v>
+        <v>48.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.82</v>
+        <v>-0.89</v>
       </c>
       <c r="U3" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="V3" t="n">
-        <v>3.26</v>
+        <v>6.38</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>111.06</v>
+        <v>1425.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>115.03</v>
+        <v>1444.72</v>
       </c>
       <c r="Z3" t="n">
-        <v>114.31</v>
+        <v>1466.24</v>
       </c>
       <c r="AA3" t="n">
-        <v>110.41</v>
+        <v>1418.48</v>
       </c>
       <c r="AB3" t="n">
-        <v>113.35</v>
+        <v>1446.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>114.06</v>
+        <v>1462.54</v>
       </c>
       <c r="AD3" t="n">
-        <v>114.71</v>
+        <v>1470.47</v>
       </c>
       <c r="AE3" t="n">
-        <v>71.2</v>
+        <v>69.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.9</v>
+        <v>18.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15.2</v>
+        <v>11.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>38.1</v>
+        <v>27.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>15</v>
+        <v>16.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>116.74</v>
+        <v>1481.72</v>
       </c>
       <c r="AN3" t="n">
-        <v>110.2</v>
+        <v>1424.57</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,329.98 Cr., a P/E ratio of 5.90, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,043,424.87 Cr., a P/E ratio of 18.80, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.19 (Bullish Momentum Zone), while MACD Line (1.69) trades above Signal (1.28) with an expanding histogram (+0.41). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.07% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 69.84 (Bullish Momentum Zone), while MACD Line (22.02) trades below Signal (23.97) with an expanding histogram (-1.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.15% above the 200-day DMA (₹1337.56). Daily volatility envelope is bounded by ATR(14) of ₹24.08.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.40) is positioned above the 30-day DMA (₹107.80), 50-day DMA (₹106.57), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.07%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,454.60) is positioned above the 30-day DMA (₹1,402.46), 50-day DMA (₹1,353.54), and 200-day DMA (₹1,337.56). The price distance from 200 DMA is +9.15%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[113.4, 113.74, 114.08, 114.42, 114.76, 115.1]</t>
+          <t>[1454.6, 1458.96, 1463.33, 1467.69, 1472.06, 1476.42]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[113.4, 114.54, 115.21, 115.8, 116.36, 116.89]</t>
+          <t>[1454.6, 1468.6, 1476.95, 1484.38, 1491.32, 1497.96]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[113.4, 113.14, 113.23, 113.38, 113.56, 113.76]</t>
+          <t>[1454.6, 1451.74, 1453.11, 1455.18, 1457.61, 1460.26]</t>
         </is>
       </c>
     </row>
@@ -993,106 +993,106 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>351473.87</v>
+        <v>354474.39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11948</v>
+        <v>12050</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹11904.37 - ₹12013.45</t>
+          <t>₹12006.7 - ₹12114.95</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12122.53</v>
+        <v>12223.21</v>
       </c>
       <c r="I4" t="n">
-        <v>11421.23</v>
+        <v>11476.02</v>
       </c>
       <c r="J4" t="n">
-        <v>11269.86</v>
+        <v>11292.42</v>
       </c>
       <c r="K4" t="n">
-        <v>11569.69</v>
+        <v>11570.69</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4</v>
+        <v>4.18</v>
       </c>
       <c r="M4" t="n">
-        <v>143.27</v>
+        <v>170.5</v>
       </c>
       <c r="N4" t="n">
-        <v>124.24</v>
+        <v>138.06</v>
       </c>
       <c r="O4" t="n">
-        <v>19.02</v>
+        <v>32.44</v>
       </c>
       <c r="P4" t="n">
-        <v>218.17</v>
+        <v>216.51</v>
       </c>
       <c r="Q4" t="n">
         <v>12.19</v>
       </c>
       <c r="R4" t="n">
-        <v>50.9</v>
+        <v>45.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.12</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
       <c r="V4" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>11799.64</v>
+        <v>11917.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>12217.82</v>
+        <v>12339.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>12043.58</v>
+        <v>12146.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>11620.75</v>
+        <v>11725.23</v>
       </c>
       <c r="AB4" t="n">
-        <v>11951</v>
+        <v>12001.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>11997</v>
+        <v>12098.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>12046</v>
+        <v>12146.67</v>
       </c>
       <c r="AE4" t="n">
-        <v>62.6</v>
+        <v>76.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>15.9</v>
@@ -1104,39 +1104,39 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>12220.44</v>
+        <v>12333.94</v>
       </c>
       <c r="AN4" t="n">
-        <v>11681.27</v>
+        <v>11762.57</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹351,473.87 Cr., a P/E ratio of 41.14, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹354,474.39 Cr., a P/E ratio of 41.49, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (143.27) trades above Signal (124.24) with an expanding histogram (+19.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.40% above the 200-day DMA (₹11569.69). Daily volatility envelope is bounded by ATR(14) of ₹218.17.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 76.80 (Bullish Momentum Zone), while MACD Line (170.50) trades above Signal (138.06) with an expanding histogram (+32.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹11570.69). Daily volatility envelope is bounded by ATR(14) of ₹216.51.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹11,948.00) is positioned above the 30-day DMA (₹11,421.23), 50-day DMA (₹11,269.86), and 200-day DMA (₹11,569.69). The price distance from 200 DMA is +2.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,050.00) is positioned above the 30-day DMA (₹11,476.02), 50-day DMA (₹11,292.42), and 200-day DMA (₹11,570.69). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[11948.0, 11983.84, 12019.69, 12055.53, 12091.38, 12127.22]</t>
+          <t>[12050.0, 12098.52, 12147.03, 12195.55, 12244.06, 12292.58]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[11948.0, 12071.11, 12143.1, 12206.68, 12265.91, 12322.35]</t>
+          <t>[12050.0, 12185.12, 12269.51, 12345.55, 12417.27, 12486.23]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[11948.0, 11918.39, 11927.13, 11942.17, 11960.48, 11980.87]</t>
+          <t>[12050.0, 12033.56, 12055.17, 12083.04, 12114.15, 12147.33]</t>
         </is>
       </c>
     </row>
@@ -1157,95 +1157,95 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>217229.02</v>
+        <v>217832.96</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7913</v>
+        <v>7935</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹7882.88 - ₹7958.18</t>
+          <t>₹7904.15 - ₹7981.28</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8033.49</v>
+        <v>8058.42</v>
       </c>
       <c r="I5" t="n">
-        <v>7447.86</v>
+        <v>7464.18</v>
       </c>
       <c r="J5" t="n">
-        <v>7362.95</v>
+        <v>7377.2</v>
       </c>
       <c r="K5" t="n">
-        <v>7176.17</v>
+        <v>7182.35</v>
       </c>
       <c r="L5" t="n">
-        <v>9.16</v>
+        <v>12.08</v>
       </c>
       <c r="M5" t="n">
-        <v>130.62</v>
+        <v>153.61</v>
       </c>
       <c r="N5" t="n">
-        <v>94.11</v>
+        <v>106.01</v>
       </c>
       <c r="O5" t="n">
-        <v>36.5</v>
+        <v>47.6</v>
       </c>
       <c r="P5" t="n">
-        <v>150.61</v>
+        <v>154.27</v>
       </c>
       <c r="Q5" t="n">
         <v>12.19</v>
       </c>
       <c r="R5" t="n">
-        <v>51.2</v>
+        <v>47.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.98</v>
+        <v>-1.14</v>
       </c>
       <c r="U5" t="n">
         <v>50</v>
       </c>
       <c r="V5" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>7764.31</v>
+        <v>7834.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>8041.27</v>
+        <v>8112.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>7976.3</v>
+        <v>7998.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>7687.09</v>
+        <v>7703.59</v>
       </c>
       <c r="AB5" t="n">
-        <v>7948.5</v>
+        <v>7942.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>7988.5</v>
+        <v>8016.84</v>
       </c>
       <c r="AD5" t="n">
-        <v>8064</v>
+        <v>8098.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>79</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>37.7</v>
+        <v>38.3</v>
       </c>
       <c r="AJ5" t="n">
         <v>31.5</v>
@@ -1268,39 +1268,39 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>8132.35</v>
+        <v>8157.87</v>
       </c>
       <c r="AN5" t="n">
-        <v>7726.48</v>
+        <v>7748.81</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹217,229.02 Cr., a P/E ratio of 37.69, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹217,832.96 Cr., a P/E ratio of 38.31, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.95 (Bullish Momentum Zone), while MACD Line (130.62) trades above Signal (94.11) with an expanding histogram (+36.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.16% above the 200-day DMA (₹7176.17). Daily volatility envelope is bounded by ATR(14) of ₹150.61.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 83.63 (Bullish Momentum Zone), while MACD Line (153.61) trades above Signal (106.01) with an expanding histogram (+47.60). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.08% above the 200-day DMA (₹7182.35). Daily volatility envelope is bounded by ATR(14) of ₹154.27.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,913.00) is positioned above the 30-day DMA (₹7,447.86), 50-day DMA (₹7,362.95), and 200-day DMA (₹7,176.17). The price distance from 200 DMA is +9.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,935.00) is positioned above the 30-day DMA (₹7,464.18), 50-day DMA (₹7,377.20), and 200-day DMA (₹7,182.35). The price distance from 200 DMA is +12.08%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[7913.0, 7936.74, 7960.48, 7984.22, 8007.96, 8031.69]</t>
+          <t>[7935.0, 7958.8, 7982.61, 8006.41, 8030.22, 8054.02]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[7913.0, 7996.98, 8045.68, 8088.56, 8128.44, 8166.4]</t>
+          <t>[7935.0, 8020.51, 8069.88, 8113.3, 8153.64, 8192.01]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[7913.0, 7891.56, 7896.58, 7905.96, 7917.59, 7930.66]</t>
+          <t>[7935.0, 7912.52, 7917.16, 7926.25, 7937.66, 7950.54]</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>266886.58</v>
+        <v>266023.78</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1329,98 +1329,98 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2784</v>
+        <v>2775</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2772.38 - ₹2801.43</t>
+          <t>₹2763.65 - ₹2792.03</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2830.47</v>
+        <v>2820.41</v>
       </c>
       <c r="I6" t="n">
-        <v>2687.86</v>
+        <v>2694.42</v>
       </c>
       <c r="J6" t="n">
-        <v>2678.76</v>
+        <v>2684.87</v>
       </c>
       <c r="K6" t="n">
-        <v>2570.71</v>
+        <v>2575.43</v>
       </c>
       <c r="L6" t="n">
-        <v>6.83</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>16.14</v>
+        <v>24.54</v>
       </c>
       <c r="N6" t="n">
-        <v>10.09</v>
+        <v>14.28</v>
       </c>
       <c r="O6" t="n">
-        <v>6.05</v>
+        <v>10.27</v>
       </c>
       <c r="P6" t="n">
-        <v>58.09</v>
+        <v>56.76</v>
       </c>
       <c r="Q6" t="n">
         <v>12.19</v>
       </c>
       <c r="R6" t="n">
-        <v>51.6</v>
+        <v>49.4</v>
       </c>
       <c r="S6" t="n">
         <v>0.26</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1</v>
+        <v>-1.16</v>
       </c>
       <c r="U6" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2746.25</v>
+        <v>2728.39</v>
       </c>
       <c r="Y6" t="n">
-        <v>2843.69</v>
+        <v>2825.51</v>
       </c>
       <c r="Z6" t="n">
-        <v>2806.27</v>
+        <v>2797.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2696.87</v>
+        <v>2689.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>2787.13</v>
+        <v>2771.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>2804.16</v>
+        <v>2810.74</v>
       </c>
       <c r="AD6" t="n">
-        <v>2824.33</v>
+        <v>2846.47</v>
       </c>
       <c r="AE6" t="n">
-        <v>62.4</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.03</v>
+        <v>-0</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Vol Spike 2.4x | TTM Squeeze | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="AJ6" t="n">
         <v>17.9</v>
@@ -1432,39 +1432,39 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>2852.19</v>
+        <v>2840.51</v>
       </c>
       <c r="AN6" t="n">
-        <v>2719.67</v>
+        <v>2713.89</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹266,886.58 Cr., a P/E ratio of 55.98, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹266,023.78 Cr., a P/E ratio of 56.49, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.38 (Bullish Momentum Zone), while MACD Line (16.14) trades above Signal (10.09) with an expanding histogram (+6.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.83% above the 200-day DMA (₹2570.71). Daily volatility envelope is bounded by ATR(14) of ₹58.09.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.87 (Bullish Momentum Zone), while MACD Line (24.54) trades above Signal (14.28) with an expanding histogram (+10.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.11% above the 200-day DMA (₹2575.43). Daily volatility envelope is bounded by ATR(14) of ₹56.76.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,784.00) is positioned above the 30-day DMA (₹2,687.86), 50-day DMA (₹2,678.76), and 200-day DMA (₹2,570.71). The price distance from 200 DMA is +6.83%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,775.00) is positioned above the 30-day DMA (₹2,694.42), 50-day DMA (₹2,684.87), and 200-day DMA (₹2,575.43). The price distance from 200 DMA is +9.11%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[2784.0, 2792.35, 2800.7, 2809.06, 2817.41, 2825.76]</t>
+          <t>[2775.0, 2783.32, 2791.65, 2799.97, 2808.3, 2816.62]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2784.0, 2815.59, 2833.56, 2849.3, 2863.88, 2877.71]</t>
+          <t>[2775.0, 2806.03, 2823.76, 2839.3, 2853.71, 2867.4]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2784.0, 2774.93, 2776.06, 2778.87, 2782.56, 2786.79]</t>
+          <t>[2775.0, 2766.3, 2767.57, 2770.48, 2774.24, 2778.55]</t>
         </is>
       </c>
     </row>
@@ -1476,159 +1476,159 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>105597.31</v>
+        <v>309977.21</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>741.85</v>
+        <v>4635</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹738.83 - ₹746.38</t>
+          <t>₹4619.25 - ₹4658.63</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>753.9299999999999</v>
+        <v>4698.01</v>
       </c>
       <c r="I7" t="n">
-        <v>730.08</v>
+        <v>4485.67</v>
       </c>
       <c r="J7" t="n">
-        <v>705.51</v>
+        <v>4415.07</v>
       </c>
       <c r="K7" t="n">
-        <v>686.16</v>
+        <v>4345.64</v>
       </c>
       <c r="L7" t="n">
-        <v>7.63</v>
+        <v>7.92</v>
       </c>
       <c r="M7" t="n">
-        <v>8.210000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="N7" t="n">
-        <v>9.15</v>
+        <v>54.56</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9399999999999999</v>
+        <v>10.67</v>
       </c>
       <c r="P7" t="n">
-        <v>15.1</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>12.19</v>
       </c>
       <c r="R7" t="n">
-        <v>50.8</v>
+        <v>39.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1</v>
+        <v>-1.23</v>
       </c>
       <c r="U7" t="n">
-        <v>56.7</v>
+        <v>43.3</v>
       </c>
       <c r="V7" t="n">
-        <v>6.51</v>
+        <v>2.22</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>723.73</v>
+        <v>4540.49</v>
       </c>
       <c r="Y7" t="n">
-        <v>736.16</v>
+        <v>4633.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>747.78</v>
+        <v>4672.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>719.2</v>
+        <v>4516.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>744</v>
+        <v>4659.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>748.8</v>
+        <v>4693.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>755.75</v>
+        <v>4751.67</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>78.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.04</v>
+        <v>0.31</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>49.2</v>
+        <v>34</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15.1</v>
+        <v>1.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>20.9</v>
+        <v>27.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AM7" t="n">
-        <v>759.9299999999999</v>
+        <v>4764.64</v>
       </c>
       <c r="AN7" t="n">
-        <v>724.3</v>
+        <v>4505.59</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,597.31 Cr., a P/E ratio of 49.23, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹309,977.21 Cr., a P/E ratio of 34.05, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.00 (Consolidation Zone), while MACD Line (8.21) trades below Signal (9.15) with an expanding histogram (-0.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.63% above the 200-day DMA (₹686.16). Daily volatility envelope is bounded by ATR(14) of ₹15.10.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.26 (Bullish Momentum Zone), while MACD Line (65.22) trades above Signal (54.56) with an expanding histogram (+10.67). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.92% above the 200-day DMA (₹4345.64). Daily volatility envelope is bounded by ATR(14) of ₹78.76.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.85) is positioned above the 30-day DMA (₹730.08), 50-day DMA (₹705.51), and 200-day DMA (₹686.16). The price distance from 200 DMA is +7.63%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,635.00) is positioned above the 30-day DMA (₹4,485.67), 50-day DMA (₹4,415.07), and 200-day DMA (₹4,345.64). The price distance from 200 DMA is +7.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[741.85, 744.08, 746.3, 748.53, 750.75, 752.98]</t>
+          <t>[4635.0, 4648.9, 4662.81, 4676.71, 4690.62, 4704.52]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[741.85, 750.12, 754.84, 758.99, 762.83, 766.48]</t>
+          <t>[4635.0, 4680.41, 4707.36, 4731.28, 4753.63, 4774.97]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[741.85, 739.55, 739.89, 740.68, 741.69, 742.85]</t>
+          <t>[4635.0, 4625.28, 4629.4, 4635.79, 4643.37, 4651.69]</t>
         </is>
       </c>
     </row>
@@ -1640,16 +1640,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>311495.33</v>
+        <v>106757.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1657,142 +1657,142 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4657.7</v>
+        <v>750</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹4640.99 - ₹4682.76</t>
+          <t>₹746.96 - ₹754.56</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4724.52</v>
+        <v>762.15</v>
       </c>
       <c r="I8" t="n">
-        <v>4479.85</v>
+        <v>730.8200000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>4409.79</v>
+        <v>707.34</v>
       </c>
       <c r="K8" t="n">
-        <v>4345.73</v>
+        <v>686.34</v>
       </c>
       <c r="L8" t="n">
-        <v>6.92</v>
+        <v>9.57</v>
       </c>
       <c r="M8" t="n">
-        <v>59.87</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>51.89</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>7.98</v>
+        <v>-0.15</v>
       </c>
       <c r="P8" t="n">
-        <v>83.53</v>
+        <v>15.19</v>
       </c>
       <c r="Q8" t="n">
         <v>12.19</v>
       </c>
       <c r="R8" t="n">
-        <v>42.3</v>
+        <v>44.7</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.21</v>
+        <v>-1.32</v>
       </c>
       <c r="U8" t="n">
-        <v>43.3</v>
+        <v>56.7</v>
       </c>
       <c r="V8" t="n">
-        <v>2.3</v>
+        <v>6.67</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>4557.47</v>
+        <v>731.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>4716.2</v>
+        <v>739.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>4694.96</v>
+        <v>756</v>
       </c>
       <c r="AA8" t="n">
-        <v>4532.41</v>
+        <v>727.22</v>
       </c>
       <c r="AB8" t="n">
-        <v>4675.23</v>
+        <v>746.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>4700.46</v>
+        <v>754.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>4743.23</v>
+        <v>758.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>64.59999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.26</v>
+        <v>-0.01</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>34.2</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.8</v>
+        <v>15.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.5</v>
+        <v>20.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>4773.62</v>
+        <v>768.5700000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>4531.88</v>
+        <v>731.38</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹311,495.33 Cr., a P/E ratio of 34.21, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,757.42 Cr., a P/E ratio of 50.00, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.59 (Bullish Momentum Zone), while MACD Line (59.87) trades above Signal (51.89) with an expanding histogram (+7.98). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.92% above the 200-day DMA (₹4345.73). Daily volatility envelope is bounded by ATR(14) of ₹83.53.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.22 (Bullish Momentum Zone), while MACD Line (8.97) trades below Signal (9.11) with an expanding histogram (-0.15). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.57% above the 200-day DMA (₹686.34). Daily volatility envelope is bounded by ATR(14) of ₹15.19.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,657.70) is positioned above the 30-day DMA (₹4,479.85), 50-day DMA (₹4,409.79), and 200-day DMA (₹4,345.73). The price distance from 200 DMA is +6.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹750.00) is positioned above the 30-day DMA (₹730.82), 50-day DMA (₹707.34), and 200-day DMA (₹686.34). The price distance from 200 DMA is +9.57%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[4657.7, 4671.67, 4685.65, 4699.62, 4713.59, 4727.57]</t>
+          <t>[750.0, 752.25, 754.5, 756.75, 759.0, 761.25]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[4657.7, 4705.08, 4732.9, 4757.49, 4780.42, 4802.28]</t>
+          <t>[750.0, 758.33, 763.09, 767.27, 771.15, 774.84]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[4657.7, 4646.61, 4650.21, 4656.22, 4663.48, 4671.53]</t>
+          <t>[750.0, 747.69, 748.06, 748.86, 749.89, 751.06]</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>67936.83</v>
+        <v>117946.57</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1821,142 +1821,142 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5682</v>
+        <v>1460</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹5657.51 - ₹5718.73</t>
+          <t>₹1453.24 - ₹1470.13</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5779.94</v>
+        <v>1487.02</v>
       </c>
       <c r="I9" t="n">
-        <v>5575</v>
+        <v>1442.14</v>
       </c>
       <c r="J9" t="n">
-        <v>5484.08</v>
+        <v>1418.05</v>
       </c>
       <c r="K9" t="n">
-        <v>5521.06</v>
+        <v>1395.4</v>
       </c>
       <c r="L9" t="n">
-        <v>5.35</v>
+        <v>5.66</v>
       </c>
       <c r="M9" t="n">
-        <v>57.19</v>
+        <v>12.07</v>
       </c>
       <c r="N9" t="n">
-        <v>51.96</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>5.23</v>
+        <v>3.96</v>
       </c>
       <c r="P9" t="n">
-        <v>122.43</v>
+        <v>33.78</v>
       </c>
       <c r="Q9" t="n">
         <v>12.19</v>
       </c>
       <c r="R9" t="n">
-        <v>47.2</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.33</v>
+        <v>-1.63</v>
       </c>
       <c r="U9" t="n">
-        <v>53.3</v>
+        <v>46.7</v>
       </c>
       <c r="V9" t="n">
-        <v>2.8</v>
+        <v>12.19</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>5624.76</v>
+        <v>1419.47</v>
       </c>
       <c r="Y9" t="n">
-        <v>5823.63</v>
+        <v>1423.79</v>
       </c>
       <c r="Z9" t="n">
-        <v>5727.46</v>
+        <v>1471.68</v>
       </c>
       <c r="AA9" t="n">
-        <v>5498.36</v>
+        <v>1409.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>5690.17</v>
+        <v>1459.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>5701.84</v>
+        <v>1469.96</v>
       </c>
       <c r="AD9" t="n">
-        <v>5721.67</v>
+        <v>1479.93</v>
       </c>
       <c r="AE9" t="n">
-        <v>58.4</v>
+        <v>59.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Vol Spike 2.0x | TTM Squeeze | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>29.5</v>
+        <v>35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14.6</v>
+        <v>3.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>15.6</v>
+        <v>12</v>
       </c>
       <c r="AL9" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>5810.15</v>
+        <v>1489.66</v>
       </c>
       <c r="AN9" t="n">
-        <v>5561.22</v>
+        <v>1432.43</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,936.83 Cr., a P/E ratio of 29.49, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,946.57 Cr., a P/E ratio of 35.02, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.37 (Bullish Momentum Zone), while MACD Line (57.19) trades above Signal (51.96) with an expanding histogram (+5.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.35% above the 200-day DMA (₹5521.06). Daily volatility envelope is bounded by ATR(14) of ₹122.43.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.53 (Bullish Momentum Zone), while MACD Line (12.07) trades above Signal (8.11) with an expanding histogram (+3.96). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.66% above the 200-day DMA (₹1395.40). Daily volatility envelope is bounded by ATR(14) of ₹33.78.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,682.00) is positioned above the 30-day DMA (₹5,575.00), 50-day DMA (₹5,484.08), and 200-day DMA (₹5,521.06). The price distance from 200 DMA is +5.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,460.00) is positioned above the 30-day DMA (₹1,442.14), 50-day DMA (₹1,418.05), and 200-day DMA (₹1,395.40). The price distance from 200 DMA is +5.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[5682.0, 5709.99, 5737.98, 5765.98, 5793.97, 5821.96]</t>
+          <t>[1460.0, 1464.38, 1468.76, 1473.14, 1477.52, 1481.9]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[5682.0, 5758.96, 5807.24, 5850.8, 5891.91, 5931.46]</t>
+          <t>[1460.0, 1477.89, 1487.87, 1496.54, 1504.54, 1512.11]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[5682.0, 5673.26, 5686.04, 5702.36, 5720.51, 5739.83]</t>
+          <t>[1460.0, 1454.25, 1454.43, 1455.59, 1457.25, 1459.24]</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>97297.62</v>
+        <v>255836.11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1985,142 +1985,142 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>369.5</v>
+        <v>1087.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹367.98 - ₹371.78</t>
+          <t>₹1081.01 - ₹1096.74</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>375.59</v>
+        <v>1112.47</v>
       </c>
       <c r="I10" t="n">
-        <v>357.93</v>
+        <v>1037.72</v>
       </c>
       <c r="J10" t="n">
-        <v>350.57</v>
+        <v>999.83</v>
       </c>
       <c r="K10" t="n">
-        <v>347.65</v>
+        <v>946.97</v>
       </c>
       <c r="L10" t="n">
-        <v>7.28</v>
+        <v>15.12</v>
       </c>
       <c r="M10" t="n">
-        <v>4.74</v>
+        <v>12.32</v>
       </c>
       <c r="N10" t="n">
-        <v>2.83</v>
+        <v>11.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.91</v>
+        <v>0.77</v>
       </c>
       <c r="P10" t="n">
-        <v>7.61</v>
+        <v>31.46</v>
       </c>
       <c r="Q10" t="n">
         <v>12.19</v>
       </c>
       <c r="R10" t="n">
-        <v>44.8</v>
+        <v>47.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.35</v>
+        <v>-1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>50</v>
+        <v>56.7</v>
       </c>
       <c r="V10" t="n">
-        <v>2.89</v>
+        <v>4.41</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>360.37</v>
+        <v>1049.54</v>
       </c>
       <c r="Y10" t="n">
-        <v>370.21</v>
+        <v>1076.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>372.46</v>
+        <v>1096</v>
       </c>
       <c r="AA10" t="n">
-        <v>358.08</v>
+        <v>1040.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>369.03</v>
+        <v>1084.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>371.26</v>
+        <v>1094.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>373.03</v>
+        <v>1101.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>81.2</v>
+        <v>65.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.1</v>
+        <v>19.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25.2</v>
+        <v>39.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>68.90000000000001</v>
+        <v>50.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>378.95</v>
+        <v>1128.09</v>
       </c>
       <c r="AN10" t="n">
-        <v>359.73</v>
+        <v>1050.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹97,297.62 Cr., a P/E ratio of 6.08, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹255,836.11 Cr., a P/E ratio of 19.20, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 81.18 (Bullish Momentum Zone), while MACD Line (4.74) trades above Signal (2.83) with an expanding histogram (+1.91). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.28% above the 200-day DMA (₹347.65). Daily volatility envelope is bounded by ATR(14) of ₹7.61.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.71 (Bullish Momentum Zone), while MACD Line (12.32) trades above Signal (11.55) with an expanding histogram (+0.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.12% above the 200-day DMA (₹946.97). Daily volatility envelope is bounded by ATR(14) of ₹31.46.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹369.50) is positioned above the 30-day DMA (₹357.93), 50-day DMA (₹350.57), and 200-day DMA (₹347.65). The price distance from 200 DMA is +7.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,087.30) is positioned above the 30-day DMA (₹1,037.72), 50-day DMA (₹999.83), and 200-day DMA (₹946.97). The price distance from 200 DMA is +15.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[369.5, 370.61, 371.72, 372.83, 373.93, 375.04]</t>
+          <t>[1087.3, 1090.56, 1093.82, 1097.09, 1100.35, 1103.61]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[369.5, 373.65, 376.02, 378.1, 380.02, 381.85]</t>
+          <t>[1087.3, 1103.15, 1111.62, 1118.88, 1125.52, 1131.75]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[369.5, 368.32, 368.49, 368.87, 369.37, 369.94]</t>
+          <t>[1087.3, 1081.12, 1080.47, 1080.74, 1081.47, 1082.5]</t>
         </is>
       </c>
     </row>
@@ -2132,104 +2132,104 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>104333.29</v>
+        <v>17533.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2182.3</v>
+        <v>612</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹2172.84 - ₹2196.49</t>
+          <t>₹607.79 - ₹618.32</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2220.15</v>
+        <v>628.86</v>
       </c>
       <c r="I11" t="n">
-        <v>2146.11</v>
+        <v>581.45</v>
       </c>
       <c r="J11" t="n">
-        <v>2067.23</v>
+        <v>547.25</v>
       </c>
       <c r="K11" t="n">
-        <v>1708.73</v>
+        <v>553.9299999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>28.74</v>
+        <v>11.57</v>
       </c>
       <c r="M11" t="n">
-        <v>30.53</v>
+        <v>15.6</v>
       </c>
       <c r="N11" t="n">
-        <v>34.42</v>
+        <v>16.04</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.9</v>
+        <v>-0.44</v>
       </c>
       <c r="P11" t="n">
-        <v>47.31</v>
+        <v>21.07</v>
       </c>
       <c r="Q11" t="n">
         <v>12.19</v>
       </c>
       <c r="R11" t="n">
-        <v>43.9</v>
+        <v>50.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.47</v>
+        <v>-2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>1.76</v>
+        <v>4.89</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>2150.54</v>
+        <v>586.71</v>
       </c>
       <c r="Y11" t="n">
-        <v>2226.92</v>
+        <v>605.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>2199.76</v>
+        <v>616.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2111.34</v>
+        <v>580.39</v>
       </c>
       <c r="AB11" t="n">
-        <v>2191.93</v>
+        <v>616.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2205.26</v>
+        <v>625.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>2228.23</v>
+        <v>638.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>58.7</v>
+        <v>56.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2240,51 +2240,51 @@
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>96.3</v>
+        <v>88.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17.5</v>
+        <v>-10.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>11.6</v>
+        <v>6.7</v>
       </c>
       <c r="AM11" t="n">
-        <v>2250.84</v>
+        <v>641.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>2125.16</v>
+        <v>582.3099999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>BHARATFORG operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹104,333.29 Cr., a P/E ratio of 96.31, and YoY Revenue Growth of +17.5%, the company demonstrates strong institutional backing, solid operating profit margins (6.42%), and healthy Return on Equity (11.60%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,533.60 Cr., a P/E ratio of 88.31, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (30.53) trades below Signal (34.42) with an expanding histogram (-3.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +28.74% above the 200-day DMA (₹1708.73). Daily volatility envelope is bounded by ATR(14) of ₹47.31.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.73 (Bullish Momentum Zone), while MACD Line (15.60) trades below Signal (16.04) with an expanding histogram (-0.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.57% above the 200-day DMA (₹553.93). Daily volatility envelope is bounded by ATR(14) of ₹21.07.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHARATFORG. Current Market Price (₹2,182.30) is positioned above the 30-day DMA (₹2,146.11), 50-day DMA (₹2,067.23), and 200-day DMA (₹1,708.73). The price distance from 200 DMA is +28.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹612.00) is positioned above the 30-day DMA (₹581.45), 50-day DMA (₹547.25), and 200-day DMA (₹553.93). The price distance from 200 DMA is +11.57%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[2182.3, 2188.85, 2195.39, 2201.94, 2208.49, 2215.03]</t>
+          <t>[612.0, 613.84, 615.67, 617.51, 619.34, 621.18]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[2182.3, 2207.77, 2222.15, 2234.72, 2246.33, 2257.35]</t>
+          <t>[612.0, 622.26, 627.59, 632.11, 636.2, 640.03]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[2182.3, 2174.65, 2175.32, 2177.36, 2180.1, 2183.3]</t>
+          <t>[612.0, 607.51, 606.73, 606.56, 606.7, 607.04]</t>
         </is>
       </c>
     </row>
@@ -2296,159 +2296,159 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>117468.78</v>
+        <v>85049.67999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1454.1</v>
+        <v>13988</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹1447.3 - ₹1464.3</t>
+          <t>₹13892.87 - ₹14130.69</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1481.29</v>
+        <v>14368.51</v>
       </c>
       <c r="I12" t="n">
-        <v>1440.19</v>
+        <v>13293.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1416.57</v>
+        <v>12693.58</v>
       </c>
       <c r="K12" t="n">
-        <v>1395.71</v>
+        <v>12304.51</v>
       </c>
       <c r="L12" t="n">
-        <v>5.55</v>
+        <v>12.9</v>
       </c>
       <c r="M12" t="n">
-        <v>10.35</v>
+        <v>412.43</v>
       </c>
       <c r="N12" t="n">
-        <v>7.12</v>
+        <v>477.06</v>
       </c>
       <c r="O12" t="n">
-        <v>3.23</v>
+        <v>-64.63</v>
       </c>
       <c r="P12" t="n">
-        <v>33.99</v>
+        <v>475.64</v>
       </c>
       <c r="Q12" t="n">
         <v>12.19</v>
       </c>
       <c r="R12" t="n">
-        <v>42.5</v>
+        <v>48.6</v>
       </c>
       <c r="S12" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.68</v>
+        <v>-2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>48.3</v>
       </c>
       <c r="V12" t="n">
-        <v>12.85</v>
+        <v>6.89</v>
       </c>
       <c r="W12" t="n">
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>1413.32</v>
+        <v>13830.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>1422.88</v>
+        <v>14320.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>1465.73</v>
+        <v>14099.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1403.12</v>
+        <v>13274.54</v>
       </c>
       <c r="AB12" t="n">
-        <v>1458.1</v>
+        <v>13962</v>
       </c>
       <c r="AC12" t="n">
-        <v>1465.6</v>
+        <v>14112</v>
       </c>
       <c r="AD12" t="n">
-        <v>1477.1</v>
+        <v>14236</v>
       </c>
       <c r="AE12" t="n">
-        <v>61.6</v>
+        <v>57.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH12" t="n">
         <v>0.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>34.9</v>
+        <v>41</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.5</v>
+        <v>21.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="AL12" t="n">
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>1486.24</v>
+        <v>14528.71</v>
       </c>
       <c r="AN12" t="n">
-        <v>1421.82</v>
+        <v>13462.53</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,468.78 Cr., a P/E ratio of 34.88, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,049.68 Cr., a P/E ratio of 40.97, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.58 (Bullish Momentum Zone), while MACD Line (10.35) trades above Signal (7.12) with an expanding histogram (+3.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.55% above the 200-day DMA (₹1395.71). Daily volatility envelope is bounded by ATR(14) of ₹33.99.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.83 (Bullish Momentum Zone), while MACD Line (412.43) trades below Signal (477.06) with an expanding histogram (-64.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.90% above the 200-day DMA (₹12304.51). Daily volatility envelope is bounded by ATR(14) of ₹475.64.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,454.10) is positioned above the 30-day DMA (₹1,440.19), 50-day DMA (₹1,416.57), and 200-day DMA (₹1,395.71). The price distance from 200 DMA is +5.55%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,988.00) is positioned above the 30-day DMA (₹13,293.50), 50-day DMA (₹12,693.58), and 200-day DMA (₹12,304.51). The price distance from 200 DMA is +12.90%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[1454.1, 1458.46, 1462.82, 1467.19, 1471.55, 1475.91]</t>
+          <t>[13988.0, 14040.72, 14093.43, 14146.15, 14198.87, 14251.58]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1454.1, 1472.06, 1482.05, 1490.73, 1498.74, 1506.31]</t>
+          <t>[13988.0, 14230.97, 14362.5, 14475.68, 14579.38, 14677.01]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1454.1, 1448.27, 1448.41, 1449.53, 1451.16, 1453.11]</t>
+          <t>[13988.0, 13898.02, 13891.63, 13899.0, 13913.48, 13932.51]</t>
         </is>
       </c>
     </row>
@@ -2460,16 +2460,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>254918.45</v>
+        <v>287576.48</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2477,142 +2477,142 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1083.4</v>
+        <v>312.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1077.21 - ₹1092.69</t>
+          <t>₹310.19 - ₹315.71</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1108.16</v>
+        <v>321.23</v>
       </c>
       <c r="I13" t="n">
-        <v>1034.29</v>
+        <v>284.54</v>
       </c>
       <c r="J13" t="n">
-        <v>997.16</v>
+        <v>271.4</v>
       </c>
       <c r="K13" t="n">
-        <v>944.85</v>
+        <v>273.6</v>
       </c>
       <c r="L13" t="n">
-        <v>10.78</v>
+        <v>13.49</v>
       </c>
       <c r="M13" t="n">
-        <v>8.699999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="N13" t="n">
-        <v>11.36</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.65</v>
+        <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>30.95</v>
+        <v>11.04</v>
       </c>
       <c r="Q13" t="n">
         <v>12.19</v>
       </c>
       <c r="R13" t="n">
-        <v>50.5</v>
+        <v>48.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.72</v>
+        <v>-2.31</v>
       </c>
       <c r="U13" t="n">
-        <v>56.7</v>
+        <v>53.3</v>
       </c>
       <c r="V13" t="n">
-        <v>3.84</v>
+        <v>2.32</v>
       </c>
       <c r="W13" t="n">
         <v>-0.77</v>
       </c>
       <c r="X13" t="n">
-        <v>1058.52</v>
+        <v>310.46</v>
       </c>
       <c r="Y13" t="n">
-        <v>1096.44</v>
+        <v>321.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>1092.07</v>
+        <v>315.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>1036.98</v>
+        <v>295.84</v>
       </c>
       <c r="AB13" t="n">
-        <v>1083.63</v>
+        <v>311.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>1091.46</v>
+        <v>313.74</v>
       </c>
       <c r="AD13" t="n">
-        <v>1099.53</v>
+        <v>315.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>49.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.09</v>
+        <v>0.12</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH13" t="n">
         <v>0.15</v>
       </c>
       <c r="AI13" t="n">
-        <v>19.1</v>
+        <v>664.7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>39.1</v>
+        <v>182</v>
       </c>
       <c r="AK13" t="n">
-        <v>50.1</v>
+        <v>0.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AM13" t="n">
-        <v>1123.14</v>
+        <v>323</v>
       </c>
       <c r="AN13" t="n">
-        <v>1051.08</v>
+        <v>302.02</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹254,918.45 Cr., a P/E ratio of 19.13, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹287,576.48 Cr., a P/E ratio of 664.68, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.70 (Consolidation Zone), while MACD Line (8.70) trades below Signal (11.36) with an expanding histogram (-2.65). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹944.85). Daily volatility envelope is bounded by ATR(14) of ₹30.95.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (10.11) trades above Signal (8.97) with an expanding histogram (+1.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.49% above the 200-day DMA (₹273.60). Daily volatility envelope is bounded by ATR(14) of ₹11.04.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,083.40) is positioned above the 30-day DMA (₹1,034.29), 50-day DMA (₹997.16), and 200-day DMA (₹944.85). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹312.40) is positioned above the 30-day DMA (₹284.54), 50-day DMA (₹271.40), and 200-day DMA (₹273.60). The price distance from 200 DMA is +13.49%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>[1083.4, 1086.65, 1089.9, 1093.15, 1096.4, 1099.65]</t>
+          <t>[312.4, 315.14, 317.88, 320.62, 323.37, 326.11]</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1083.4, 1099.03, 1107.41, 1114.59, 1121.16, 1127.33]</t>
+          <t>[312.4, 319.56, 324.13, 328.27, 332.2, 335.98]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1083.4, 1077.37, 1076.77, 1077.07, 1077.83, 1078.89]</t>
+          <t>[312.4, 311.83, 313.2, 314.89, 316.74, 318.7]</t>
         </is>
       </c>
     </row>
@@ -2624,104 +2624,104 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17628.14</v>
+        <v>61257.31</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>615.3</v>
+        <v>2033.6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹611.04 - ₹621.69</t>
+          <t>₹2020.74 - ₹2052.89</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>632.34</v>
+        <v>2085.04</v>
       </c>
       <c r="I14" t="n">
-        <v>579.77</v>
+        <v>2020.05</v>
       </c>
       <c r="J14" t="n">
-        <v>544.3099999999999</v>
+        <v>1902.41</v>
       </c>
       <c r="K14" t="n">
-        <v>553.6900000000001</v>
+        <v>1880.72</v>
       </c>
       <c r="L14" t="n">
-        <v>10.78</v>
+        <v>11.11</v>
       </c>
       <c r="M14" t="n">
-        <v>15.03</v>
+        <v>54.69</v>
       </c>
       <c r="N14" t="n">
-        <v>16.15</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.12</v>
+        <v>-9.85</v>
       </c>
       <c r="P14" t="n">
-        <v>21.3</v>
+        <v>64.3</v>
       </c>
       <c r="Q14" t="n">
         <v>12.19</v>
       </c>
       <c r="R14" t="n">
-        <v>53.1</v>
+        <v>42.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.01</v>
+        <v>-2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>55</v>
+        <v>51.7</v>
       </c>
       <c r="V14" t="n">
-        <v>4.79</v>
+        <v>6.23</v>
       </c>
       <c r="W14" t="n">
         <v>-0.77</v>
       </c>
       <c r="X14" t="n">
-        <v>589.74</v>
+        <v>1956.44</v>
       </c>
       <c r="Y14" t="n">
-        <v>603.6</v>
+        <v>2003.87</v>
       </c>
       <c r="Z14" t="n">
-        <v>620.22</v>
+        <v>2049.87</v>
       </c>
       <c r="AA14" t="n">
-        <v>583.35</v>
+        <v>1937.16</v>
       </c>
       <c r="AB14" t="n">
-        <v>617.25</v>
+        <v>2037.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>627.5</v>
+        <v>2084.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>639.7</v>
+        <v>2135.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>56.9</v>
+        <v>49.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2732,51 +2732,51 @@
         <v>0.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>88.8</v>
+        <v>34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-10.1</v>
+        <v>63</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.7</v>
+        <v>36.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>645.33</v>
+        <v>2107.15</v>
       </c>
       <c r="AN14" t="n">
-        <v>584.4400000000001</v>
+        <v>1954.18</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,628.14 Cr., a P/E ratio of 88.79, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹61,257.31 Cr., a P/E ratio of 34.01, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.93 (Bullish Momentum Zone), while MACD Line (15.03) trades below Signal (16.15) with an expanding histogram (-1.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.78% above the 200-day DMA (₹553.69). Daily volatility envelope is bounded by ATR(14) of ₹21.30.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.12 (Consolidation Zone), while MACD Line (54.69) trades below Signal (64.54) with an expanding histogram (-9.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.11% above the 200-day DMA (₹1880.72). Daily volatility envelope is bounded by ATR(14) of ₹64.30.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹615.30) is positioned above the 30-day DMA (₹579.77), 50-day DMA (₹544.31), and 200-day DMA (₹553.69). The price distance from 200 DMA is +10.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,033.60) is positioned above the 30-day DMA (₹2,020.05), 50-day DMA (₹1,902.41), and 200-day DMA (₹1,880.72). The price distance from 200 DMA is +11.11%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>[615.3, 617.15, 618.99, 620.84, 622.68, 624.53]</t>
+          <t>[2033.6, 2039.7, 2045.8, 2051.9, 2058.0, 2064.1]</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[615.3, 625.67, 631.04, 635.59, 639.72, 643.58]</t>
+          <t>[2033.6, 2065.42, 2082.17, 2096.45, 2109.44, 2121.61]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[615.3, 610.76, 609.95, 609.77, 609.9, 610.24]</t>
+          <t>[2033.6, 2020.41, 2018.52, 2018.49, 2019.43, 2020.97]</t>
         </is>
       </c>
     </row>
@@ -2797,106 +2797,106 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77165.44</v>
+        <v>77466.47</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1743.1</v>
+        <v>1749.9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹1731.5 - ₹1760.5</t>
+          <t>₹1738.07 - ₹1767.64</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1789.51</v>
+        <v>1797.22</v>
       </c>
       <c r="I15" t="n">
-        <v>1511.17</v>
+        <v>1520.87</v>
       </c>
       <c r="J15" t="n">
-        <v>1475.45</v>
+        <v>1482.98</v>
       </c>
       <c r="K15" t="n">
-        <v>1504.57</v>
+        <v>1504.98</v>
       </c>
       <c r="L15" t="n">
-        <v>14.12</v>
+        <v>17.48</v>
       </c>
       <c r="M15" t="n">
-        <v>60.69</v>
+        <v>69.8</v>
       </c>
       <c r="N15" t="n">
-        <v>36.2</v>
+        <v>42.92</v>
       </c>
       <c r="O15" t="n">
-        <v>24.49</v>
+        <v>26.89</v>
       </c>
       <c r="P15" t="n">
-        <v>58.01</v>
+        <v>59.15</v>
       </c>
       <c r="Q15" t="n">
         <v>12.19</v>
       </c>
       <c r="R15" t="n">
-        <v>48.4</v>
+        <v>41</v>
       </c>
       <c r="S15" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.01</v>
+        <v>-2.66</v>
       </c>
       <c r="U15" t="n">
         <v>48.3</v>
       </c>
       <c r="V15" t="n">
-        <v>7.29</v>
+        <v>6.76</v>
       </c>
       <c r="W15" t="n">
         <v>-0.77</v>
       </c>
       <c r="X15" t="n">
-        <v>1737.19</v>
+        <v>1736.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>1798.2</v>
+        <v>1797.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>1763.33</v>
+        <v>1763.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>1656.08</v>
+        <v>1661.18</v>
       </c>
       <c r="AB15" t="n">
-        <v>1752.77</v>
+        <v>1752.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>1765.14</v>
+        <v>1772.06</v>
       </c>
       <c r="AD15" t="n">
-        <v>1787.17</v>
+        <v>1794.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>71.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH15" t="n">
         <v>0.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>35.7</v>
+        <v>36.2</v>
       </c>
       <c r="AJ15" t="n">
         <v>49.9</v>
@@ -2908,859 +2908,39 @@
         <v>15</v>
       </c>
       <c r="AM15" t="n">
-        <v>1812.38</v>
+        <v>1819.02</v>
       </c>
       <c r="AN15" t="n">
-        <v>1679.44</v>
+        <v>1686.61</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹77,165.44 Cr., a P/E ratio of 35.66, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹77,466.47 Cr., a P/E ratio of 36.23, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.40 (Bullish Momentum Zone), while MACD Line (60.69) trades above Signal (36.20) with an expanding histogram (+24.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.12% above the 200-day DMA (₹1504.57). Daily volatility envelope is bounded by ATR(14) of ₹58.01.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 75.45 (Bullish Momentum Zone), while MACD Line (69.80) trades above Signal (42.92) with an expanding histogram (+26.89). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.48% above the 200-day DMA (₹1504.98). Daily volatility envelope is bounded by ATR(14) of ₹59.15.</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,743.10) is positioned above the 30-day DMA (₹1,511.17), 50-day DMA (₹1,475.45), and 200-day DMA (₹1,504.57). The price distance from 200 DMA is +14.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,749.90) is positioned above the 30-day DMA (₹1,520.87), 50-day DMA (₹1,482.98), and 200-day DMA (₹1,504.98). The price distance from 200 DMA is +17.48%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>[1743.1, 1763.33, 1783.57, 1803.8, 1824.04, 1844.27]</t>
+          <t>[1749.9, 1762.37, 1774.83, 1787.3, 1799.77, 1812.24]</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[1743.1, 1786.54, 1816.38, 1843.99, 1870.45, 1896.16]</t>
+          <t>[1749.9, 1786.03, 1808.29, 1828.28, 1847.09, 1865.14]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[1743.1, 1745.93, 1758.96, 1773.66, 1789.23, 1805.35]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>146005.65</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1648.2</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>₹1639.03 - ₹1661.96</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1684.9</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1487.74</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1465.74</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1460.05</v>
-      </c>
-      <c r="L16" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>57.77</v>
-      </c>
-      <c r="N16" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="O16" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="P16" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="R16" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="U16" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.74</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1593.15</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1649.86</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1661.39</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1579.39</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1649.1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1658.1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1668</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1694.52</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1601.79</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,005.65 Cr., a P/E ratio of 28.52, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.82 (Bullish Momentum Zone), while MACD Line (57.77) trades above Signal (45.82) with an expanding histogram (+11.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.10% above the 200-day DMA (₹1460.05). Daily volatility envelope is bounded by ATR(14) of ₹45.87.</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,648.20) is positioned above the 30-day DMA (₹1,487.74), 50-day DMA (₹1,465.74), and 200-day DMA (₹1,460.05). The price distance from 200 DMA is +13.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>[1648.2, 1653.14, 1658.09, 1663.03, 1667.98, 1672.92]</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>[1648.2, 1671.49, 1684.04, 1694.81, 1704.68, 1713.95]</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>[1648.2, 1639.38, 1638.63, 1639.2, 1640.46, 1642.15]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>360ONE</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>47357.83</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1163.9</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>₹1156.99 - ₹1174.27</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1191.55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1109.56</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1105.35</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1100.33</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="M17" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="O17" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="P17" t="n">
-        <v>34.56</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="R17" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="U17" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1148.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1188.79</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1173.21</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1112.05</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1160.77</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1177.14</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1190.37</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.19) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1197.39</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1129.04</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹47,357.83 Cr., a P/E ratio of 38.68, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.88 (Consolidation Zone), while MACD Line (9.13) trades above Signal (4.71) with an expanding histogram (+4.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.87% above the 200-day DMA (₹1100.33). Daily volatility envelope is bounded by ATR(14) of ₹34.56.</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,163.90) is positioned above the 30-day DMA (₹1,109.56), 50-day DMA (₹1,105.35), and 200-day DMA (₹1,100.33). The price distance from 200 DMA is +3.87%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>[1163.9, 1167.39, 1170.88, 1174.38, 1177.87, 1181.36]</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>[1163.9, 1181.22, 1190.44, 1198.32, 1205.52, 1212.27]</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>[1163.9, 1157.02, 1156.22, 1156.41, 1157.13, 1158.17]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>285413.21</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>310.05</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>₹307.86 - ₹313.33</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>318.8</v>
-      </c>
-      <c r="I18" t="n">
-        <v>282.98</v>
-      </c>
-      <c r="J18" t="n">
-        <v>270.14</v>
-      </c>
-      <c r="K18" t="n">
-        <v>273.78</v>
-      </c>
-      <c r="L18" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="N18" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="R18" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-2.32</v>
-      </c>
-      <c r="U18" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X18" t="n">
-        <v>305.64</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>316.49</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>312.53</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>293.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>310.72</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>312.04</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>314.02</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>62</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>689</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>182</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>321.78</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>299.7</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹285,413.21 Cr., a P/E ratio of 689.00, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.99 (Bullish Momentum Zone), while MACD Line (9.73) trades above Signal (8.68) with an expanding histogram (+1.05). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.47% above the 200-day DMA (₹273.78). Daily volatility envelope is bounded by ATR(14) of ₹10.94.</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹310.05) is positioned above the 30-day DMA (₹282.98), 50-day DMA (₹270.14), and 200-day DMA (₹273.78). The price distance from 200 DMA is +10.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>[310.05, 310.98, 311.91, 312.84, 313.77, 314.7]</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>[310.05, 315.35, 318.1, 320.42, 322.52, 324.48]</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>[310.05, 307.7, 307.27, 307.16, 307.21, 307.36]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>61248.27</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>2033.3</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>₹2020.52 - ₹2052.48</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>2084.43</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2010.06</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1895.79</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1880.5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>11.98</v>
-      </c>
-      <c r="M19" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="N19" t="n">
-        <v>67</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="P19" t="n">
-        <v>63.92</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="R19" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="U19" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1956.6</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1931.52</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2049.57</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1937.42</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2037.1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2084.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2135.1</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>45</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>Low VIX (12.19) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH19" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>63</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>2104.86</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1959.14</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹61,248.27 Cr., a P/E ratio of 33.07, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 45.03 (Consolidation Zone), while MACD Line (59.11) trades below Signal (67.00) with an expanding histogram (-7.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.98% above the 200-day DMA (₹1880.50). Daily volatility envelope is bounded by ATR(14) of ₹63.92.</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,033.30) is positioned above the 30-day DMA (₹2,010.06), 50-day DMA (₹1,895.79), and 200-day DMA (₹1,880.50). The price distance from 200 DMA is +11.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>[2033.3, 2039.4, 2045.5, 2051.6, 2057.7, 2063.8]</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>[2033.3, 2064.97, 2081.66, 2095.88, 2108.83, 2120.97]</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>[2033.3, 2020.22, 2018.38, 2018.39, 2019.35, 2020.92]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>84836.88</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>13953</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>₹13860.67 - ₹14091.49</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>14322.31</v>
-      </c>
-      <c r="I20" t="n">
-        <v>13241.63</v>
-      </c>
-      <c r="J20" t="n">
-        <v>12652.22</v>
-      </c>
-      <c r="K20" t="n">
-        <v>12318.23</v>
-      </c>
-      <c r="L20" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="M20" t="n">
-        <v>450.74</v>
-      </c>
-      <c r="N20" t="n">
-        <v>493.22</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-42.48</v>
-      </c>
-      <c r="P20" t="n">
-        <v>461.64</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="R20" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="U20" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X20" t="n">
-        <v>13399.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>13802.11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>14064.62</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>13260.54</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>13950.33</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>14088.66</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>14224.33</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH20" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>14509.24</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>13432.72</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹84,836.88 Cr., a P/E ratio of 40.87, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.38 (Bullish Momentum Zone), while MACD Line (450.74) trades below Signal (493.22) with an expanding histogram (-42.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.05% above the 200-day DMA (₹12318.23). Daily volatility envelope is bounded by ATR(14) of ₹461.64.</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,953.00) is positioned above the 30-day DMA (₹13,241.63), 50-day DMA (₹12,652.22), and 200-day DMA (₹12,318.23). The price distance from 200 DMA is +14.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>[13953.0, 13994.86, 14036.72, 14078.58, 14120.44, 14162.29]</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>[13953.0, 14179.52, 14297.86, 14398.41, 14489.75, 14575.2]</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>[13953.0, 13856.37, 13840.86, 13838.7, 13843.45, 13852.62]</t>
+          <t>[1749.9, 1744.62, 1749.74, 1756.57, 1764.28, 1772.56]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT15"/>
+  <dimension ref="A1:AT18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,7 +651,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>131008.05</v>
+        <v>131375.82</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -673,91 +673,91 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>113.99</v>
+        <v>114.31</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹113.59 - ₹114.59</t>
+          <t>₹113.92 - ₹114.9</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>115.59</v>
+        <v>115.87</v>
       </c>
       <c r="I2" t="n">
-        <v>107.9</v>
+        <v>108.12</v>
       </c>
       <c r="J2" t="n">
-        <v>106.76</v>
+        <v>106.98</v>
       </c>
       <c r="K2" t="n">
-        <v>112.63</v>
+        <v>112.64</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="N2" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R2" t="n">
-        <v>55</v>
+        <v>56.2</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.74</v>
+        <v>-0.67</v>
       </c>
       <c r="U2" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
       <c r="V2" t="n">
-        <v>3.33</v>
+        <v>3.01</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>111.59</v>
+        <v>111.97</v>
       </c>
       <c r="Y2" t="n">
-        <v>115.3</v>
+        <v>115.43</v>
       </c>
       <c r="Z2" t="n">
-        <v>114.9</v>
+        <v>115.22</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.99</v>
+        <v>111.38</v>
       </c>
       <c r="AB2" t="n">
-        <v>113.54</v>
+        <v>114.47</v>
       </c>
       <c r="AC2" t="n">
-        <v>114.44</v>
+        <v>115.03</v>
       </c>
       <c r="AD2" t="n">
-        <v>114.9</v>
+        <v>115.76</v>
       </c>
       <c r="AE2" t="n">
-        <v>78.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
@@ -776,60 +776,60 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>116.96</v>
+        <v>117.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>110.62</v>
+        <v>111.45</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹131,008.05 Cr., a P/E ratio of 5.88, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹131,375.82 Cr., a P/E ratio of 5.90, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.61 (Bullish Momentum Zone), while MACD Line (1.77) trades above Signal (1.38) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.33% above the 200-day DMA (₹112.63). Daily volatility envelope is bounded by ATR(14) of ₹2.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 79.03 (Bullish Momentum Zone), while MACD Line (1.90) trades above Signal (1.48) with an expanding histogram (+0.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +1.20% above the 200-day DMA (₹112.64). Daily volatility envelope is bounded by ATR(14) of ₹1.95.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.99) is positioned above the 30-day DMA (₹107.90), 50-day DMA (₹106.76), and 200-day DMA (₹112.63). The price distance from 200 DMA is +0.33%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹114.31) is positioned above the 30-day DMA (₹108.12), 50-day DMA (₹106.98), and 200-day DMA (₹112.64). The price distance from 200 DMA is +1.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[113.99, 114.33, 114.67, 115.02, 115.36, 115.7]</t>
+          <t>[114.31, 114.65, 115.0, 115.34, 115.68, 116.02]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[113.99, 115.13, 115.81, 116.4, 116.96, 117.49]</t>
+          <t>[114.31, 115.43, 116.1, 116.69, 117.24, 117.77]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[113.99, 113.73, 113.83, 113.98, 114.16, 114.36]</t>
+          <t>[114.31, 114.07, 114.17, 114.32, 114.51, 114.72]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1043424.87</v>
+        <v>359769.47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -837,655 +837,655 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1454.6</v>
+        <v>12230</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹1449.78 - ₹1461.82</t>
+          <t>₹12186.77 - ₹12294.85</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1473.87</v>
+        <v>12402.92</v>
       </c>
       <c r="I3" t="n">
-        <v>1402.46</v>
+        <v>11480.92</v>
       </c>
       <c r="J3" t="n">
-        <v>1353.54</v>
+        <v>11295.36</v>
       </c>
       <c r="K3" t="n">
-        <v>1337.56</v>
+        <v>11571.42</v>
       </c>
       <c r="L3" t="n">
-        <v>9.15</v>
+        <v>4.14</v>
       </c>
       <c r="M3" t="n">
-        <v>22.02</v>
+        <v>179.48</v>
       </c>
       <c r="N3" t="n">
-        <v>23.97</v>
+        <v>141.78</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.95</v>
+        <v>37.7</v>
       </c>
       <c r="P3" t="n">
-        <v>24.08</v>
+        <v>216.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R3" t="n">
-        <v>48.5</v>
+        <v>49.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.89</v>
+        <v>-0.93</v>
       </c>
       <c r="U3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="V3" t="n">
-        <v>6.38</v>
+        <v>2.71</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>1425.7</v>
+        <v>12119.84</v>
       </c>
       <c r="Y3" t="n">
-        <v>1444.72</v>
+        <v>12547.89</v>
       </c>
       <c r="Z3" t="n">
-        <v>1466.24</v>
+        <v>12327.84</v>
       </c>
       <c r="AA3" t="n">
-        <v>1418.48</v>
+        <v>11905.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>1446.67</v>
+        <v>12146.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>1462.54</v>
+        <v>12322.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>1470.47</v>
+        <v>12415.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>69.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.01</v>
+        <v>0.27</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>18.8</v>
+        <v>42.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11.4</v>
+        <v>15.9</v>
       </c>
       <c r="AK3" t="n">
-        <v>27.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AL3" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>1481.72</v>
+        <v>12498.59</v>
       </c>
       <c r="AN3" t="n">
-        <v>1424.57</v>
+        <v>11948.19</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ICICIBANK operates in the Financial Services sector. With an estimated Market Cap of ₹1,043,424.87 Cr., a P/E ratio of 18.80, and YoY Revenue Growth of +11.4%, the company demonstrates strong institutional backing, solid operating profit margins (27.53%), and healthy Return on Equity (16.07%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹359,769.47 Cr., a P/E ratio of 42.11, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 69.84 (Bullish Momentum Zone), while MACD Line (22.02) trades below Signal (23.97) with an expanding histogram (-1.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.15% above the 200-day DMA (₹1337.56). Daily volatility envelope is bounded by ATR(14) of ₹24.08.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 76.59 (Bullish Momentum Zone), while MACD Line (179.48) trades above Signal (141.78) with an expanding histogram (+37.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹11571.42). Daily volatility envelope is bounded by ATR(14) of ₹216.16.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ICICIBANK. Current Market Price (₹1,454.60) is positioned above the 30-day DMA (₹1,402.46), 50-day DMA (₹1,353.54), and 200-day DMA (₹1,337.56). The price distance from 200 DMA is +9.15%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,230.00) is positioned above the 30-day DMA (₹11,480.92), 50-day DMA (₹11,295.36), and 200-day DMA (₹11,571.42). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[1454.6, 1458.96, 1463.33, 1467.69, 1472.06, 1476.42]</t>
+          <t>[12230.0, 12303.29, 12376.58, 12449.88, 12523.17, 12596.46]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[1454.6, 1468.6, 1476.95, 1484.38, 1491.32, 1497.96]</t>
+          <t>[12230.0, 12389.75, 12498.86, 12599.63, 12696.09, 12789.79]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[1454.6, 1451.74, 1453.11, 1455.18, 1457.61, 1460.26]</t>
+          <t>[12230.0, 12238.45, 12284.88, 12337.56, 12393.47, 12451.46]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>354474.39</v>
+        <v>218999.69</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12050</v>
+        <v>7977.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹12006.7 - ₹12114.95</t>
+          <t>₹7946.14 - ₹8024.54</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12223.21</v>
+        <v>8102.95</v>
       </c>
       <c r="I4" t="n">
-        <v>11476.02</v>
+        <v>7478.7</v>
       </c>
       <c r="J4" t="n">
-        <v>11292.42</v>
+        <v>7389.91</v>
       </c>
       <c r="K4" t="n">
-        <v>11570.69</v>
+        <v>7187.9</v>
       </c>
       <c r="L4" t="n">
-        <v>4.18</v>
+        <v>10.39</v>
       </c>
       <c r="M4" t="n">
-        <v>170.5</v>
+        <v>160.7</v>
       </c>
       <c r="N4" t="n">
-        <v>138.06</v>
+        <v>116.95</v>
       </c>
       <c r="O4" t="n">
-        <v>32.44</v>
+        <v>43.75</v>
       </c>
       <c r="P4" t="n">
-        <v>216.51</v>
+        <v>156.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R4" t="n">
-        <v>45.2</v>
+        <v>51</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.12</v>
+        <v>-1.04</v>
       </c>
       <c r="U4" t="n">
-        <v>50</v>
+        <v>51.7</v>
       </c>
       <c r="V4" t="n">
-        <v>2.69</v>
+        <v>2.08</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>11917.77</v>
+        <v>7852.76</v>
       </c>
       <c r="Y4" t="n">
-        <v>12339.52</v>
+        <v>8131.97</v>
       </c>
       <c r="Z4" t="n">
-        <v>12146.4</v>
+        <v>8041.32</v>
       </c>
       <c r="AA4" t="n">
-        <v>11725.23</v>
+        <v>7742.28</v>
       </c>
       <c r="AB4" t="n">
-        <v>12001.67</v>
+        <v>7959.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>12098.34</v>
+        <v>8013.16</v>
       </c>
       <c r="AD4" t="n">
-        <v>12146.67</v>
+        <v>8048.83</v>
       </c>
       <c r="AE4" t="n">
-        <v>76.8</v>
+        <v>74.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>41.5</v>
+        <v>38.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15.9</v>
+        <v>31.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>9.300000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>12333.94</v>
+        <v>8193.860000000001</v>
       </c>
       <c r="AN4" t="n">
-        <v>11762.57</v>
+        <v>7771.46</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹354,474.39 Cr., a P/E ratio of 41.49, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹218,999.69 Cr., a P/E ratio of 38.52, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 76.80 (Bullish Momentum Zone), while MACD Line (170.50) trades above Signal (138.06) with an expanding histogram (+32.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹11570.69). Daily volatility envelope is bounded by ATR(14) of ₹216.51.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.31 (Bullish Momentum Zone), while MACD Line (160.70) trades above Signal (116.95) with an expanding histogram (+43.75). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.39% above the 200-day DMA (₹7187.90). Daily volatility envelope is bounded by ATR(14) of ₹156.81.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,050.00) is positioned above the 30-day DMA (₹11,476.02), 50-day DMA (₹11,292.42), and 200-day DMA (₹11,570.69). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,977.50) is positioned above the 30-day DMA (₹7,478.70), 50-day DMA (₹7,389.91), and 200-day DMA (₹7,187.90). The price distance from 200 DMA is +10.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[12050.0, 12098.52, 12147.03, 12195.55, 12244.06, 12292.58]</t>
+          <t>[7977.5, 8001.43, 8025.36, 8049.3, 8073.23, 8097.16]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[12050.0, 12185.12, 12269.51, 12345.55, 12417.27, 12486.23]</t>
+          <t>[7977.5, 8064.16, 8114.07, 8157.94, 8198.68, 8237.42]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[12050.0, 12033.56, 12055.17, 12083.04, 12114.15, 12147.33]</t>
+          <t>[7977.5, 7954.39, 7958.84, 7967.82, 7979.14, 7991.97]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>217832.96</v>
+        <v>67548.24000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7935</v>
+        <v>5649.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹7904.15 - ₹7981.28</t>
+          <t>₹5624.83 - ₹5686.51</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8058.42</v>
+        <v>5748.19</v>
       </c>
       <c r="I5" t="n">
-        <v>7464.18</v>
+        <v>5586.12</v>
       </c>
       <c r="J5" t="n">
-        <v>7377.2</v>
+        <v>5490.13</v>
       </c>
       <c r="K5" t="n">
-        <v>7182.35</v>
+        <v>5522.54</v>
       </c>
       <c r="L5" t="n">
-        <v>12.08</v>
+        <v>3.34</v>
       </c>
       <c r="M5" t="n">
-        <v>153.61</v>
+        <v>56.93</v>
       </c>
       <c r="N5" t="n">
-        <v>106.01</v>
+        <v>52.95</v>
       </c>
       <c r="O5" t="n">
-        <v>47.6</v>
+        <v>3.98</v>
       </c>
       <c r="P5" t="n">
-        <v>154.27</v>
+        <v>123.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R5" t="n">
-        <v>47.8</v>
+        <v>50.1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.14</v>
+        <v>-1.23</v>
       </c>
       <c r="U5" t="n">
-        <v>50</v>
+        <v>51.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.95</v>
+        <v>3.12</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>7834.45</v>
+        <v>5501.47</v>
       </c>
       <c r="Y5" t="n">
-        <v>8112.18</v>
+        <v>5661.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7998.48</v>
+        <v>5694.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>7703.59</v>
+        <v>5464.46</v>
       </c>
       <c r="AB5" t="n">
-        <v>7942.17</v>
+        <v>5623.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>8016.84</v>
+        <v>5691.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>8098.67</v>
+        <v>5733.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>83.59999999999999</v>
+        <v>57.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>38.3</v>
+        <v>29.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>31.5</v>
+        <v>14.6</v>
       </c>
       <c r="AK5" t="n">
-        <v>23.2</v>
+        <v>15.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="AM5" t="n">
-        <v>8157.87</v>
+        <v>5795.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>7748.81</v>
+        <v>5523.57</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹217,832.96 Cr., a P/E ratio of 38.31, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,548.24 Cr., a P/E ratio of 29.32, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 83.63 (Bullish Momentum Zone), while MACD Line (153.61) trades above Signal (106.01) with an expanding histogram (+47.60). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.08% above the 200-day DMA (₹7182.35). Daily volatility envelope is bounded by ATR(14) of ₹154.27.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.91 (Bullish Momentum Zone), while MACD Line (56.93) trades above Signal (52.95) with an expanding histogram (+3.98). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.34% above the 200-day DMA (₹5522.54). Daily volatility envelope is bounded by ATR(14) of ₹123.36.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,935.00) is positioned above the 30-day DMA (₹7,464.18), 50-day DMA (₹7,377.20), and 200-day DMA (₹7,182.35). The price distance from 200 DMA is +12.08%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,649.50) is positioned above the 30-day DMA (₹5,586.12), 50-day DMA (₹5,490.13), and 200-day DMA (₹5,522.54). The price distance from 200 DMA is +3.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[7935.0, 7958.8, 7982.61, 8006.41, 8030.22, 8054.02]</t>
+          <t>[5649.5, 5666.45, 5683.4, 5700.35, 5717.29, 5734.24]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[7935.0, 8020.51, 8069.88, 8113.3, 8153.64, 8192.01]</t>
+          <t>[5649.5, 5715.79, 5753.18, 5785.81, 5815.98, 5844.58]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[7935.0, 7912.52, 7917.16, 7926.25, 7937.66, 7950.54]</t>
+          <t>[5649.5, 5629.44, 5631.06, 5636.25, 5643.28, 5651.49]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>266023.78</v>
+        <v>308760.02</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2775</v>
+        <v>4616.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2763.65 - ₹2792.03</t>
+          <t>₹4600.76 - ₹4640.86</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2820.41</v>
+        <v>4680.95</v>
       </c>
       <c r="I6" t="n">
-        <v>2694.42</v>
+        <v>4490.17</v>
       </c>
       <c r="J6" t="n">
-        <v>2684.87</v>
+        <v>4419.22</v>
       </c>
       <c r="K6" t="n">
-        <v>2575.43</v>
+        <v>4344.79</v>
       </c>
       <c r="L6" t="n">
-        <v>9.109999999999999</v>
+        <v>6.68</v>
       </c>
       <c r="M6" t="n">
-        <v>24.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>14.28</v>
+        <v>56.51</v>
       </c>
       <c r="O6" t="n">
-        <v>10.27</v>
+        <v>7.78</v>
       </c>
       <c r="P6" t="n">
-        <v>56.76</v>
+        <v>80.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R6" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.16</v>
+        <v>-1.23</v>
       </c>
       <c r="U6" t="n">
-        <v>56.7</v>
+        <v>41.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2728.39</v>
+        <v>4520.58</v>
       </c>
       <c r="Y6" t="n">
-        <v>2825.51</v>
+        <v>4655.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>2797.2</v>
+        <v>4653.73</v>
       </c>
       <c r="AA6" t="n">
-        <v>2689.85</v>
+        <v>4496.52</v>
       </c>
       <c r="AB6" t="n">
-        <v>2771.57</v>
+        <v>4631.23</v>
       </c>
       <c r="AC6" t="n">
-        <v>2810.74</v>
+        <v>4658.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>2846.47</v>
+        <v>4701.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>77.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0</v>
+        <v>0.27</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>56.5</v>
+        <v>33.9</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17.9</v>
+        <v>1.8</v>
       </c>
       <c r="AK6" t="n">
-        <v>12.8</v>
+        <v>27.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AM6" t="n">
-        <v>2840.51</v>
+        <v>4743.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>2713.89</v>
+        <v>4486.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹266,023.78 Cr., a P/E ratio of 56.49, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹308,760.02 Cr., a P/E ratio of 33.91, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.87 (Bullish Momentum Zone), while MACD Line (24.54) trades above Signal (14.28) with an expanding histogram (+10.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.11% above the 200-day DMA (₹2575.43). Daily volatility envelope is bounded by ATR(14) of ₹56.76.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.77 (Bullish Momentum Zone), while MACD Line (64.29) trades above Signal (56.51) with an expanding histogram (+7.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.68% above the 200-day DMA (₹4344.79). Daily volatility envelope is bounded by ATR(14) of ₹80.19.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,775.00) is positioned above the 30-day DMA (₹2,694.42), 50-day DMA (₹2,684.87), and 200-day DMA (₹2,575.43). The price distance from 200 DMA is +9.11%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,616.80) is positioned above the 30-day DMA (₹4,490.17), 50-day DMA (₹4,419.22), and 200-day DMA (₹4,344.79). The price distance from 200 DMA is +6.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[2775.0, 2783.32, 2791.65, 2799.97, 2808.3, 2816.62]</t>
+          <t>[4616.8, 4630.65, 4644.5, 4658.35, 4672.2, 4686.05]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2775.0, 2806.03, 2823.76, 2839.3, 2853.71, 2867.4]</t>
+          <t>[4616.8, 4662.72, 4689.86, 4713.91, 4736.35, 4757.77]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2775.0, 2766.3, 2767.57, 2770.48, 2774.24, 2778.55]</t>
+          <t>[4616.8, 4606.59, 4610.48, 4616.69, 4624.09, 4632.26]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>309977.21</v>
+        <v>265247.29</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1493,149 +1493,149 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4635</v>
+        <v>2766.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹4619.25 - ₹4658.63</t>
+          <t>₹2755.03 - ₹2784.7</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4698.01</v>
+        <v>2814.38</v>
       </c>
       <c r="I7" t="n">
-        <v>4485.67</v>
+        <v>2695.34</v>
       </c>
       <c r="J7" t="n">
-        <v>4415.07</v>
+        <v>2685.42</v>
       </c>
       <c r="K7" t="n">
-        <v>4345.64</v>
+        <v>2575.56</v>
       </c>
       <c r="L7" t="n">
-        <v>7.92</v>
+        <v>7.74</v>
       </c>
       <c r="M7" t="n">
-        <v>65.22</v>
+        <v>25.61</v>
       </c>
       <c r="N7" t="n">
-        <v>54.56</v>
+        <v>15.29</v>
       </c>
       <c r="O7" t="n">
-        <v>10.67</v>
+        <v>10.32</v>
       </c>
       <c r="P7" t="n">
-        <v>78.76000000000001</v>
+        <v>59.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R7" t="n">
-        <v>39.4</v>
+        <v>47.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.23</v>
+        <v>-1.31</v>
       </c>
       <c r="U7" t="n">
-        <v>43.3</v>
+        <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>4540.49</v>
+        <v>2695.68</v>
       </c>
       <c r="Y7" t="n">
-        <v>4633.45</v>
+        <v>2792.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4672.08</v>
+        <v>2789.04</v>
       </c>
       <c r="AA7" t="n">
-        <v>4516.86</v>
+        <v>2677.87</v>
       </c>
       <c r="AB7" t="n">
-        <v>4659.67</v>
+        <v>2767.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>4693.34</v>
+        <v>2786.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>4751.67</v>
+        <v>2805.83</v>
       </c>
       <c r="AE7" t="n">
-        <v>78.3</v>
+        <v>69.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.31</v>
+        <v>0.02</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>34</v>
+        <v>56.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.8</v>
+        <v>17.9</v>
       </c>
       <c r="AK7" t="n">
-        <v>27.5</v>
+        <v>12.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>4764.64</v>
+        <v>2830.02</v>
       </c>
       <c r="AN7" t="n">
-        <v>4505.59</v>
+        <v>2706.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹309,977.21 Cr., a P/E ratio of 34.05, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹265,247.29 Cr., a P/E ratio of 56.33, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 78.26 (Bullish Momentum Zone), while MACD Line (65.22) trades above Signal (54.56) with an expanding histogram (+10.67). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.92% above the 200-day DMA (₹4345.64). Daily volatility envelope is bounded by ATR(14) of ₹78.76.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 69.81 (Bullish Momentum Zone), while MACD Line (25.61) trades above Signal (15.29) with an expanding histogram (+10.32). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.74% above the 200-day DMA (₹2575.56). Daily volatility envelope is bounded by ATR(14) of ₹59.35.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,635.00) is positioned above the 30-day DMA (₹4,485.67), 50-day DMA (₹4,415.07), and 200-day DMA (₹4,345.64). The price distance from 200 DMA is +7.92%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,766.90) is positioned above the 30-day DMA (₹2,695.34), 50-day DMA (₹2,685.42), and 200-day DMA (₹2,575.56). The price distance from 200 DMA is +7.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[4635.0, 4648.9, 4662.81, 4676.71, 4690.62, 4704.52]</t>
+          <t>[2766.9, 2775.2, 2783.5, 2791.8, 2800.1, 2808.4]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[4635.0, 4680.41, 4707.36, 4731.28, 4753.63, 4774.97]</t>
+          <t>[2766.9, 2798.94, 2817.07, 2832.92, 2847.58, 2861.49]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[4635.0, 4625.28, 4629.4, 4635.79, 4643.37, 4651.69]</t>
+          <t>[2766.9, 2757.4, 2758.32, 2760.96, 2764.49, 2768.59]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>106757.42</v>
+        <v>106686.24</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1657,91 +1657,91 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>750</v>
+        <v>749.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹746.96 - ₹754.56</t>
+          <t>₹746.51 - ₹753.99</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>762.15</v>
+        <v>761.48</v>
       </c>
       <c r="I8" t="n">
-        <v>730.8200000000001</v>
+        <v>731.6799999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>707.34</v>
+        <v>709.25</v>
       </c>
       <c r="K8" t="n">
-        <v>686.34</v>
+        <v>686.46</v>
       </c>
       <c r="L8" t="n">
-        <v>9.57</v>
+        <v>9.26</v>
       </c>
       <c r="M8" t="n">
-        <v>8.970000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>9.109999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="P8" t="n">
-        <v>15.19</v>
+        <v>14.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R8" t="n">
-        <v>44.7</v>
+        <v>43.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.32</v>
+        <v>-1.34</v>
       </c>
       <c r="U8" t="n">
-        <v>56.7</v>
+        <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>6.67</v>
+        <v>6.36</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>731.77</v>
+        <v>731.53</v>
       </c>
       <c r="Y8" t="n">
-        <v>739.7</v>
+        <v>743.64</v>
       </c>
       <c r="Z8" t="n">
-        <v>756</v>
+        <v>755.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>727.22</v>
+        <v>727.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>746.72</v>
+        <v>749.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>754.24</v>
+        <v>753.1900000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>758.47</v>
+        <v>756.87</v>
       </c>
       <c r="AE8" t="n">
-        <v>60.2</v>
+        <v>54.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
@@ -1760,60 +1760,60 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>768.5700000000001</v>
+        <v>769.26</v>
       </c>
       <c r="AN8" t="n">
-        <v>731.38</v>
+        <v>731.1799999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,757.42 Cr., a P/E ratio of 50.00, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,686.24 Cr., a P/E ratio of 49.97, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.22 (Bullish Momentum Zone), while MACD Line (8.97) trades below Signal (9.11) with an expanding histogram (-0.15). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.57% above the 200-day DMA (₹686.34). Daily volatility envelope is bounded by ATR(14) of ₹15.19.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.07 (Consolidation Zone), while MACD Line (9.30) trades above Signal (9.15) with an expanding histogram (+0.15). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.26% above the 200-day DMA (₹686.46). Daily volatility envelope is bounded by ATR(14) of ₹14.97.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹750.00) is positioned above the 30-day DMA (₹730.82), 50-day DMA (₹707.34), and 200-day DMA (₹686.34). The price distance from 200 DMA is +9.57%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹749.50) is positioned above the 30-day DMA (₹731.68), 50-day DMA (₹709.25), and 200-day DMA (₹686.46). The price distance from 200 DMA is +9.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[750.0, 752.25, 754.5, 756.75, 759.0, 761.25]</t>
+          <t>[749.5, 751.75, 754.0, 756.25, 758.49, 760.74]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[750.0, 758.33, 763.09, 767.27, 771.15, 774.84]</t>
+          <t>[749.5, 757.74, 762.47, 766.62, 770.47, 774.13]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[750.0, 747.69, 748.06, 748.86, 749.89, 751.06]</t>
+          <t>[749.5, 747.26, 747.65, 748.47, 749.51, 750.7]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>117946.57</v>
+        <v>96468.16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1821,163 +1821,163 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1460</v>
+        <v>366.35</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹1453.24 - ₹1470.13</t>
+          <t>₹364.78 - ₹368.7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1487.02</v>
+        <v>372.61</v>
       </c>
       <c r="I9" t="n">
-        <v>1442.14</v>
+        <v>358.01</v>
       </c>
       <c r="J9" t="n">
-        <v>1418.05</v>
+        <v>351.17</v>
       </c>
       <c r="K9" t="n">
-        <v>1395.4</v>
+        <v>347.72</v>
       </c>
       <c r="L9" t="n">
-        <v>5.66</v>
+        <v>5.86</v>
       </c>
       <c r="M9" t="n">
-        <v>12.07</v>
+        <v>4.82</v>
       </c>
       <c r="N9" t="n">
-        <v>8.109999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="O9" t="n">
-        <v>3.96</v>
+        <v>1.59</v>
       </c>
       <c r="P9" t="n">
-        <v>33.78</v>
+        <v>7.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R9" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.63</v>
+        <v>-1.46</v>
       </c>
       <c r="U9" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="V9" t="n">
-        <v>12.19</v>
+        <v>3</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>1419.47</v>
+        <v>358.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1423.79</v>
+        <v>371.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>1471.68</v>
+        <v>369.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1409.33</v>
+        <v>354.61</v>
       </c>
       <c r="AB9" t="n">
-        <v>1459.63</v>
+        <v>368.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>1469.96</v>
+        <v>370.54</v>
       </c>
       <c r="AD9" t="n">
-        <v>1479.93</v>
+        <v>374.72</v>
       </c>
       <c r="AE9" t="n">
-        <v>59.5</v>
+        <v>71.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.06</v>
+        <v>0.13</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.5</v>
+        <v>25.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>12</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>1489.66</v>
+        <v>376.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>1432.43</v>
+        <v>357.16</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,946.57 Cr., a P/E ratio of 35.02, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹96,468.16 Cr., a P/E ratio of 6.03, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.53 (Bullish Momentum Zone), while MACD Line (12.07) trades above Signal (8.11) with an expanding histogram (+3.96). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.66% above the 200-day DMA (₹1395.40). Daily volatility envelope is bounded by ATR(14) of ₹33.78.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.84 (Bullish Momentum Zone), while MACD Line (4.82) trades above Signal (3.23) with an expanding histogram (+1.59). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.86% above the 200-day DMA (₹347.72). Daily volatility envelope is bounded by ATR(14) of ₹7.83.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,460.00) is positioned above the 30-day DMA (₹1,442.14), 50-day DMA (₹1,418.05), and 200-day DMA (₹1,395.40). The price distance from 200 DMA is +5.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹366.35) is positioned above the 30-day DMA (₹358.01), 50-day DMA (₹351.17), and 200-day DMA (₹347.72). The price distance from 200 DMA is +5.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[1460.0, 1464.38, 1468.76, 1473.14, 1477.52, 1481.9]</t>
+          <t>[366.35, 367.45, 368.55, 369.65, 370.75, 371.85]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[1460.0, 1477.89, 1487.87, 1496.54, 1504.54, 1512.11]</t>
+          <t>[366.35, 370.58, 372.97, 375.07, 377.01, 378.84]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[1460.0, 1454.25, 1454.43, 1455.59, 1457.25, 1459.24]</t>
+          <t>[366.35, 365.1, 365.23, 365.58, 366.05, 366.6]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>255836.11</v>
+        <v>117332.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1985,154 +1985,154 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1087.3</v>
+        <v>1452.4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹1081.01 - ₹1096.74</t>
+          <t>₹1445.57 - ₹1462.64</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1112.47</v>
+        <v>1479.71</v>
       </c>
       <c r="I10" t="n">
-        <v>1037.72</v>
+        <v>1443.04</v>
       </c>
       <c r="J10" t="n">
-        <v>999.83</v>
+        <v>1419.16</v>
       </c>
       <c r="K10" t="n">
-        <v>946.97</v>
+        <v>1394.98</v>
       </c>
       <c r="L10" t="n">
-        <v>15.12</v>
+        <v>4.66</v>
       </c>
       <c r="M10" t="n">
-        <v>12.32</v>
+        <v>12.13</v>
       </c>
       <c r="N10" t="n">
-        <v>11.55</v>
+        <v>8.92</v>
       </c>
       <c r="O10" t="n">
-        <v>0.77</v>
+        <v>3.22</v>
       </c>
       <c r="P10" t="n">
-        <v>31.46</v>
+        <v>34.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R10" t="n">
-        <v>47.2</v>
+        <v>42.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.91</v>
+        <v>-1.69</v>
       </c>
       <c r="U10" t="n">
-        <v>56.7</v>
+        <v>45</v>
       </c>
       <c r="V10" t="n">
-        <v>4.41</v>
+        <v>12.14</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>1049.54</v>
+        <v>1411.43</v>
       </c>
       <c r="Y10" t="n">
-        <v>1076.4</v>
+        <v>1414.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>1096</v>
+        <v>1464.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>1040.1</v>
+        <v>1401.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>1084.7</v>
+        <v>1451.97</v>
       </c>
       <c r="AC10" t="n">
-        <v>1094.3</v>
+        <v>1460.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>1101.3</v>
+        <v>1468.47</v>
       </c>
       <c r="AE10" t="n">
-        <v>65.7</v>
+        <v>55.4</v>
       </c>
       <c r="AF10" t="n">
         <v>-0.02</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>19.2</v>
+        <v>35.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.1</v>
+        <v>3.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>50.1</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>1128.09</v>
+        <v>1482.56</v>
       </c>
       <c r="AN10" t="n">
-        <v>1050.42</v>
+        <v>1423.79</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN operates in the Financial Services sector. With an estimated Market Cap of ₹255,836.11 Cr., a P/E ratio of 19.20, and YoY Revenue Growth of +39.1%, the company demonstrates strong institutional backing, solid operating profit margins (50.11%), and healthy Return on Equity (18.50%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,332.60 Cr., a P/E ratio of 35.15, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.71 (Bullish Momentum Zone), while MACD Line (12.32) trades above Signal (11.55) with an expanding histogram (+0.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.12% above the 200-day DMA (₹946.97). Daily volatility envelope is bounded by ATR(14) of ₹31.46.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.37 (Bullish Momentum Zone), while MACD Line (12.13) trades above Signal (8.92) with an expanding histogram (+3.22). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.66% above the 200-day DMA (₹1394.98). Daily volatility envelope is bounded by ATR(14) of ₹34.14.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for SHRIRAMFIN. Current Market Price (₹1,087.30) is positioned above the 30-day DMA (₹1,037.72), 50-day DMA (₹999.83), and 200-day DMA (₹946.97). The price distance from 200 DMA is +15.12%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,452.40) is positioned above the 30-day DMA (₹1,443.04), 50-day DMA (₹1,419.16), and 200-day DMA (₹1,394.98). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[1087.3, 1090.56, 1093.82, 1097.09, 1100.35, 1103.61]</t>
+          <t>[1452.4, 1456.76, 1461.11, 1465.47, 1469.83, 1474.19]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[1087.3, 1103.15, 1111.62, 1118.88, 1125.52, 1131.75]</t>
+          <t>[1452.4, 1470.41, 1480.43, 1489.13, 1497.14, 1504.72]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[1087.3, 1081.12, 1080.47, 1080.74, 1081.47, 1082.5]</t>
+          <t>[1452.4, 1446.51, 1446.63, 1447.73, 1449.34, 1451.28]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17533.6</v>
+        <v>147307.86</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2149,163 +2149,163 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>612</v>
+        <v>1662.9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹607.79 - ₹618.32</t>
+          <t>₹1653.79 - ₹1676.57</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>628.86</v>
+        <v>1699.36</v>
       </c>
       <c r="I11" t="n">
-        <v>581.45</v>
+        <v>1496.08</v>
       </c>
       <c r="J11" t="n">
-        <v>547.25</v>
+        <v>1470.74</v>
       </c>
       <c r="K11" t="n">
-        <v>553.9299999999999</v>
+        <v>1461.21</v>
       </c>
       <c r="L11" t="n">
-        <v>11.57</v>
+        <v>12.85</v>
       </c>
       <c r="M11" t="n">
-        <v>15.6</v>
+        <v>58.14</v>
       </c>
       <c r="N11" t="n">
-        <v>16.04</v>
+        <v>48.29</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.44</v>
+        <v>9.85</v>
       </c>
       <c r="P11" t="n">
-        <v>21.07</v>
+        <v>45.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R11" t="n">
-        <v>50.3</v>
+        <v>48.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.16</v>
+        <v>-1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="V11" t="n">
-        <v>4.89</v>
+        <v>7.95</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>586.71</v>
+        <v>1634.56</v>
       </c>
       <c r="Y11" t="n">
-        <v>605.55</v>
+        <v>1692.76</v>
       </c>
       <c r="Z11" t="n">
-        <v>616.9</v>
+        <v>1676.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>580.39</v>
+        <v>1594.54</v>
       </c>
       <c r="AB11" t="n">
-        <v>616.15</v>
+        <v>1658.47</v>
       </c>
       <c r="AC11" t="n">
-        <v>625.3</v>
+        <v>1669.24</v>
       </c>
       <c r="AD11" t="n">
-        <v>638.6</v>
+        <v>1675.57</v>
       </c>
       <c r="AE11" t="n">
-        <v>56.7</v>
+        <v>83.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>88.3</v>
+        <v>28.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-10.1</v>
+        <v>17.7</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AL11" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>641.1</v>
+        <v>1710.59</v>
       </c>
       <c r="AN11" t="n">
-        <v>582.3099999999999</v>
+        <v>1616</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,533.60 Cr., a P/E ratio of 88.31, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹147,307.86 Cr., a P/E ratio of 28.77, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.73 (Bullish Momentum Zone), while MACD Line (15.60) trades below Signal (16.04) with an expanding histogram (-0.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.57% above the 200-day DMA (₹553.93). Daily volatility envelope is bounded by ATR(14) of ₹21.07.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 83.49 (Bullish Momentum Zone), while MACD Line (58.14) trades above Signal (48.29) with an expanding histogram (+9.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.85% above the 200-day DMA (₹1461.21). Daily volatility envelope is bounded by ATR(14) of ₹45.57.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹612.00) is positioned above the 30-day DMA (₹581.45), 50-day DMA (₹547.25), and 200-day DMA (₹553.93). The price distance from 200 DMA is +11.57%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,662.90) is positioned above the 30-day DMA (₹1,496.08), 50-day DMA (₹1,470.74), and 200-day DMA (₹1,461.21). The price distance from 200 DMA is +12.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[612.0, 613.84, 615.67, 617.51, 619.34, 621.18]</t>
+          <t>[1662.9, 1667.89, 1672.88, 1677.87, 1682.85, 1687.84]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[612.0, 622.26, 627.59, 632.11, 636.2, 640.03]</t>
+          <t>[1662.9, 1686.12, 1698.66, 1709.44, 1719.31, 1728.6]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[612.0, 607.51, 606.73, 606.56, 606.7, 607.04]</t>
+          <t>[1662.9, 1654.22, 1653.54, 1654.19, 1655.51, 1657.27]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>85049.67999999999</v>
+        <v>48196.02</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2313,163 +2313,163 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13988</v>
+        <v>1184.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹13892.87 - ₹14130.69</t>
+          <t>₹1177.76 - ₹1194.61</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14368.51</v>
+        <v>1211.45</v>
       </c>
       <c r="I12" t="n">
-        <v>13293.5</v>
+        <v>1109.65</v>
       </c>
       <c r="J12" t="n">
-        <v>12693.58</v>
+        <v>1106.05</v>
       </c>
       <c r="K12" t="n">
-        <v>12304.51</v>
+        <v>1100.66</v>
       </c>
       <c r="L12" t="n">
-        <v>12.9</v>
+        <v>4.28</v>
       </c>
       <c r="M12" t="n">
-        <v>412.43</v>
+        <v>10.48</v>
       </c>
       <c r="N12" t="n">
-        <v>477.06</v>
+        <v>5.87</v>
       </c>
       <c r="O12" t="n">
-        <v>-64.63</v>
+        <v>4.62</v>
       </c>
       <c r="P12" t="n">
-        <v>475.64</v>
+        <v>33.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R12" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.23</v>
+        <v>-1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
       <c r="V12" t="n">
-        <v>6.89</v>
+        <v>2.31</v>
       </c>
       <c r="W12" t="n">
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>13830.9</v>
+        <v>1174.79</v>
       </c>
       <c r="Y12" t="n">
-        <v>14320.48</v>
+        <v>1216.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>14099.9</v>
+        <v>1193.98</v>
       </c>
       <c r="AA12" t="n">
-        <v>13274.54</v>
+        <v>1133.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>13962</v>
+        <v>1179.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>14112</v>
+        <v>1195.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>14236</v>
+        <v>1207.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>57.8</v>
+        <v>56.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH12" t="n">
         <v>0.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>41</v>
+        <v>39.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>21.1</v>
+        <v>29.9</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.6</v>
+        <v>26.5</v>
       </c>
       <c r="AL12" t="n">
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>14528.71</v>
+        <v>1220.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>13462.53</v>
+        <v>1146.87</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹85,049.68 Cr., a P/E ratio of 40.97, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹48,196.02 Cr., a P/E ratio of 39.39, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.83 (Bullish Momentum Zone), while MACD Line (412.43) trades below Signal (477.06) with an expanding histogram (-64.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.90% above the 200-day DMA (₹12304.51). Daily volatility envelope is bounded by ATR(14) of ₹475.64.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.33 (Bullish Momentum Zone), while MACD Line (10.48) trades above Signal (5.87) with an expanding histogram (+4.62). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.28% above the 200-day DMA (₹1100.66). Daily volatility envelope is bounded by ATR(14) of ₹33.69.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹13,988.00) is positioned above the 30-day DMA (₹13,293.50), 50-day DMA (₹12,693.58), and 200-day DMA (₹12,304.51). The price distance from 200 DMA is +12.90%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,184.50) is positioned above the 30-day DMA (₹1,109.65), 50-day DMA (₹1,106.05), and 200-day DMA (₹1,100.66). The price distance from 200 DMA is +4.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[13988.0, 14040.72, 14093.43, 14146.15, 14198.87, 14251.58]</t>
+          <t>[1184.5, 1192.55, 1200.61, 1208.66, 1216.71, 1224.76]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[13988.0, 14230.97, 14362.5, 14475.68, 14579.38, 14677.01]</t>
+          <t>[1184.5, 1206.03, 1219.66, 1232.0, 1243.66, 1254.89]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[13988.0, 13898.02, 13891.63, 13899.0, 13913.48, 13932.51]</t>
+          <t>[1184.5, 1182.45, 1186.31, 1191.15, 1196.5, 1202.17]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>287576.48</v>
+        <v>78812.25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2477,318 +2477,318 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>312.4</v>
+        <v>1780.3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹310.19 - ₹315.71</t>
+          <t>₹1768.66 - ₹1797.76</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>321.23</v>
+        <v>1826.85</v>
       </c>
       <c r="I13" t="n">
-        <v>284.54</v>
+        <v>1530.06</v>
       </c>
       <c r="J13" t="n">
-        <v>271.4</v>
+        <v>1489.66</v>
       </c>
       <c r="K13" t="n">
-        <v>273.6</v>
+        <v>1504.99</v>
       </c>
       <c r="L13" t="n">
-        <v>13.49</v>
+        <v>16.27</v>
       </c>
       <c r="M13" t="n">
-        <v>10.11</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.970000000000001</v>
+        <v>49.28</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>25.43</v>
       </c>
       <c r="P13" t="n">
-        <v>11.04</v>
+        <v>58.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R13" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="S13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.31</v>
+        <v>-1.82</v>
       </c>
       <c r="U13" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="V13" t="n">
-        <v>2.32</v>
+        <v>7.75</v>
       </c>
       <c r="W13" t="n">
         <v>-0.77</v>
       </c>
       <c r="X13" t="n">
-        <v>310.46</v>
+        <v>1779.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>321.39</v>
+        <v>1841.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>315.14</v>
+        <v>1805.77</v>
       </c>
       <c r="AA13" t="n">
-        <v>295.84</v>
+        <v>1693.01</v>
       </c>
       <c r="AB13" t="n">
-        <v>311.37</v>
+        <v>1769.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>313.74</v>
+        <v>1794.04</v>
       </c>
       <c r="AD13" t="n">
-        <v>315.07</v>
+        <v>1807.77</v>
       </c>
       <c r="AE13" t="n">
-        <v>65.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH13" t="n">
         <v>0.15</v>
       </c>
       <c r="AI13" t="n">
-        <v>664.7</v>
+        <v>36.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>182</v>
+        <v>49.9</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.6</v>
+        <v>9.6</v>
       </c>
       <c r="AL13" t="n">
         <v>15</v>
       </c>
       <c r="AM13" t="n">
-        <v>323</v>
+        <v>1848.76</v>
       </c>
       <c r="AN13" t="n">
-        <v>302.02</v>
+        <v>1707.79</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹287,576.48 Cr., a P/E ratio of 664.68, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹78,812.25 Cr., a P/E ratio of 36.42, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.40 (Bullish Momentum Zone), while MACD Line (10.11) trades above Signal (8.97) with an expanding histogram (+1.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.49% above the 200-day DMA (₹273.60). Daily volatility envelope is bounded by ATR(14) of ₹11.04.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.86 (Bullish Momentum Zone), while MACD Line (74.71) trades above Signal (49.28) with an expanding histogram (+25.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.27% above the 200-day DMA (₹1504.99). Daily volatility envelope is bounded by ATR(14) of ₹58.19.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹312.40) is positioned above the 30-day DMA (₹284.54), 50-day DMA (₹271.40), and 200-day DMA (₹273.60). The price distance from 200 DMA is +13.49%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,780.30) is positioned above the 30-day DMA (₹1,530.06), 50-day DMA (₹1,489.66), and 200-day DMA (₹1,504.99). The price distance from 200 DMA is +16.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>[312.4, 315.14, 317.88, 320.62, 323.37, 326.11]</t>
+          <t>[1780.3, 1805.77, 1831.25, 1856.72, 1882.2, 1907.67]</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[312.4, 319.56, 324.13, 328.27, 332.2, 335.98]</t>
+          <t>[1780.3, 1829.05, 1864.17, 1897.04, 1928.75, 1959.72]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[312.4, 311.83, 313.2, 314.89, 316.74, 318.7]</t>
+          <t>[1780.3, 1788.32, 1806.56, 1826.48, 1847.28, 1868.63]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61257.31</v>
+        <v>288773.19</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2033.6</v>
+        <v>313.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹2020.74 - ₹2052.89</t>
+          <t>₹311.63 - ₹316.81</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2085.04</v>
+        <v>321.98</v>
       </c>
       <c r="I14" t="n">
-        <v>2020.05</v>
+        <v>286.32</v>
       </c>
       <c r="J14" t="n">
-        <v>1902.41</v>
+        <v>272.64</v>
       </c>
       <c r="K14" t="n">
-        <v>1880.72</v>
+        <v>273.39</v>
       </c>
       <c r="L14" t="n">
-        <v>11.11</v>
+        <v>14.27</v>
       </c>
       <c r="M14" t="n">
-        <v>54.69</v>
+        <v>10.44</v>
       </c>
       <c r="N14" t="n">
-        <v>64.54000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.85</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>64.3</v>
+        <v>10.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R14" t="n">
-        <v>42.3</v>
+        <v>50.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.4</v>
+        <v>-2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>51.7</v>
+        <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>6.23</v>
+        <v>2.43</v>
       </c>
       <c r="W14" t="n">
         <v>-0.77</v>
       </c>
       <c r="X14" t="n">
-        <v>1956.44</v>
+        <v>309.61</v>
       </c>
       <c r="Y14" t="n">
-        <v>2003.87</v>
+        <v>320.59</v>
       </c>
       <c r="Z14" t="n">
-        <v>2049.87</v>
+        <v>316.21</v>
       </c>
       <c r="AA14" t="n">
-        <v>1937.16</v>
+        <v>298.18</v>
       </c>
       <c r="AB14" t="n">
-        <v>2037.2</v>
+        <v>313.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2084.4</v>
+        <v>315.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>2135.2</v>
+        <v>316.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>49.1</v>
+        <v>62.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH14" t="n">
         <v>0.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>34</v>
+        <v>667.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="AK14" t="n">
-        <v>36.1</v>
+        <v>0.6</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AM14" t="n">
-        <v>2107.15</v>
+        <v>325.52</v>
       </c>
       <c r="AN14" t="n">
-        <v>1954.18</v>
+        <v>303.48</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹61,257.31 Cr., a P/E ratio of 34.01, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹288,773.19 Cr., a P/E ratio of 667.45, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.12 (Consolidation Zone), while MACD Line (54.69) trades below Signal (64.54) with an expanding histogram (-9.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.11% above the 200-day DMA (₹1880.72). Daily volatility envelope is bounded by ATR(14) of ₹64.30.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.17 (Bullish Momentum Zone), while MACD Line (10.44) trades above Signal (9.26) with an expanding histogram (+1.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.27% above the 200-day DMA (₹273.39). Daily volatility envelope is bounded by ATR(14) of ₹10.35.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,033.60) is positioned above the 30-day DMA (₹2,020.05), 50-day DMA (₹1,902.41), and 200-day DMA (₹1,880.72). The price distance from 200 DMA is +11.11%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹313.70) is positioned above the 30-day DMA (₹286.32), 50-day DMA (₹272.64), and 200-day DMA (₹273.39). The price distance from 200 DMA is +14.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>[2033.6, 2039.7, 2045.8, 2051.9, 2058.0, 2064.1]</t>
+          <t>[313.7, 314.64, 315.58, 316.52, 317.46, 318.41]</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[2033.6, 2065.42, 2082.17, 2096.45, 2109.44, 2121.61]</t>
+          <t>[313.7, 318.78, 321.44, 323.69, 325.74, 327.66]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[2033.6, 2020.41, 2018.52, 2018.49, 2019.43, 2020.97]</t>
+          <t>[313.7, 311.54, 311.19, 311.15, 311.25, 311.46]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2797,150 +2797,642 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77466.47</v>
+        <v>87159.50999999999</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1749.9</v>
+        <v>14335</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹1738.07 - ₹1767.64</t>
+          <t>₹14241.1 - ₹14475.85</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1797.22</v>
+        <v>14710.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1520.87</v>
+        <v>13362.03</v>
       </c>
       <c r="J15" t="n">
-        <v>1482.98</v>
+        <v>12739.88</v>
       </c>
       <c r="K15" t="n">
-        <v>1504.98</v>
+        <v>12290.57</v>
       </c>
       <c r="L15" t="n">
-        <v>17.48</v>
+        <v>13.81</v>
       </c>
       <c r="M15" t="n">
-        <v>69.8</v>
+        <v>385.37</v>
       </c>
       <c r="N15" t="n">
-        <v>42.92</v>
+        <v>458.72</v>
       </c>
       <c r="O15" t="n">
-        <v>26.89</v>
+        <v>-73.34999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>59.15</v>
+        <v>469.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="R15" t="n">
-        <v>41</v>
+        <v>49.7</v>
       </c>
       <c r="S15" t="n">
         <v>0.16</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.66</v>
+        <v>-2.07</v>
       </c>
       <c r="U15" t="n">
         <v>48.3</v>
       </c>
       <c r="V15" t="n">
-        <v>6.76</v>
+        <v>6.4</v>
       </c>
       <c r="W15" t="n">
         <v>-0.77</v>
       </c>
       <c r="X15" t="n">
-        <v>1736.12</v>
+        <v>14230.59</v>
       </c>
       <c r="Y15" t="n">
-        <v>1797.37</v>
+        <v>14732.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>1763.9</v>
+        <v>14449.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>1661.18</v>
+        <v>13630.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1752.63</v>
+        <v>14241</v>
       </c>
       <c r="AC15" t="n">
-        <v>1772.06</v>
+        <v>14459</v>
       </c>
       <c r="AD15" t="n">
-        <v>1794.23</v>
+        <v>14583</v>
       </c>
       <c r="AE15" t="n">
-        <v>75.5</v>
+        <v>55.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.22</v>
+        <v>0.05</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.19) | LSTM Deep Net</t>
+          <t>Low VIX (11.97) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH15" t="n">
         <v>0.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>36.2</v>
+        <v>41.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>49.9</v>
+        <v>21.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="AL15" t="n">
         <v>15</v>
       </c>
       <c r="AM15" t="n">
-        <v>1819.02</v>
+        <v>14929.51</v>
       </c>
       <c r="AN15" t="n">
-        <v>1686.61</v>
+        <v>13769.3</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹77,466.47 Cr., a P/E ratio of 36.23, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹87,159.51 Cr., a P/E ratio of 41.83, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 75.45 (Bullish Momentum Zone), while MACD Line (69.80) trades above Signal (42.92) with an expanding histogram (+26.89). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.48% above the 200-day DMA (₹1504.98). Daily volatility envelope is bounded by ATR(14) of ₹59.15.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.30 (Bullish Momentum Zone), while MACD Line (385.37) trades below Signal (458.72) with an expanding histogram (-73.35). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.81% above the 200-day DMA (₹12290.57). Daily volatility envelope is bounded by ATR(14) of ₹469.50.</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,749.90) is positioned above the 30-day DMA (₹1,520.87), 50-day DMA (₹1,482.98), and 200-day DMA (₹1,504.98). The price distance from 200 DMA is +17.48%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,335.00) is positioned above the 30-day DMA (₹13,362.03), 50-day DMA (₹12,739.88), and 200-day DMA (₹12,290.57). The price distance from 200 DMA is +13.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>[1749.9, 1762.37, 1774.83, 1787.3, 1799.77, 1812.24]</t>
+          <t>[14335.0, 14445.61, 14556.23, 14666.84, 14777.46, 14888.07]</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[1749.9, 1786.03, 1808.29, 1828.28, 1847.09, 1865.14]</t>
+          <t>[14335.0, 14633.41, 14821.82, 14992.12, 15153.06, 15308.0]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[1749.9, 1744.62, 1749.74, 1756.57, 1764.28, 1772.56]</t>
+          <t>[14335.0, 14304.76, 14357.04, 14422.88, 14495.76, 14573.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>17669.68</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>616.75</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>₹612.46 - ₹623.19</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>633.92</v>
+      </c>
+      <c r="I16" t="n">
+        <v>583.11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>550.15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>554.14</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="P16" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="R16" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="U16" t="n">
+        <v>55</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X16" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>605.51</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>621.6799999999999</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>584.5599999999999</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>621.08</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>628.16</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>639.58</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Low VIX (11.97) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>646.28</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>585.86</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,669.68 Cr., a P/E ratio of 90.04, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.70 (Consolidation Zone), while MACD Line (15.39) trades below Signal (15.91) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.44% above the 200-day DMA (₹554.14). Daily volatility envelope is bounded by ATR(14) of ₹21.46.</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹616.75) is positioned above the 30-day DMA (₹583.11), 50-day DMA (₹550.15), and 200-day DMA (₹554.14). The price distance from 200 DMA is +10.44%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>[616.75, 618.6, 620.45, 622.3, 624.15, 626.0]</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>[616.75, 627.18, 632.59, 637.17, 641.32, 645.2]</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>[616.75, 612.16, 611.35, 611.15, 611.27, 611.6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>63980.39</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2124</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>₹2110.33 - ₹2144.51</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2178.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2028.46</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1908.05</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1880.26</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="M17" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="N17" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-14.73</v>
+      </c>
+      <c r="P17" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="R17" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="U17" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2041.95</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2028.7</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2140.99</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2021.44</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2107.87</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2160.04</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2196.07</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>63</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>2204.13</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2047.52</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,980.39 Cr., a P/E ratio of 34.54, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.71 (Consolidation Zone), while MACD Line (46.13) trades below Signal (60.86) with an expanding histogram (-14.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.16% above the 200-day DMA (₹1880.26). Daily volatility envelope is bounded by ATR(14) of ₹68.37.</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,124.00) is positioned above the 30-day DMA (₹2,028.46), 50-day DMA (₹1,908.05), and 200-day DMA (₹1,880.26). The price distance from 200 DMA is +8.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>[2124.0, 2130.37, 2136.74, 2143.12, 2149.49, 2155.86]</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>[2124.0, 2157.72, 2175.42, 2190.49, 2204.19, 2217.02]</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>[2124.0, 2109.86, 2107.73, 2107.59, 2108.46, 2109.99]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11608.92</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>130.54</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>₹129.67 - ₹131.85</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>134.03</v>
+      </c>
+      <c r="I18" t="n">
+        <v>124.43</v>
+      </c>
+      <c r="J18" t="n">
+        <v>123.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>127.99</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="R18" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="U18" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X18" t="n">
+        <v>125.97</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>130.54</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>131.58</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>123.99</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>130.43</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>131.05</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>131.57</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>136.03</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>124.46</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>IEX operates in the Financial Services sector. With an estimated Market Cap of ₹11,608.92 Cr., a P/E ratio of 22.90, and YoY Revenue Growth of +10.1%, the company demonstrates strong institutional backing, solid operating profit margins (66.22%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.41 (Bullish Momentum Zone), while MACD Line (2.09) trades above Signal (1.41) with an expanding histogram (+0.68). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.95% above the 200-day DMA (₹127.99). Daily volatility envelope is bounded by ATR(14) of ₹4.36.</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for IEX. Current Market Price (₹130.54) is positioned above the 30-day DMA (₹124.43), 50-day DMA (₹123.96), and 200-day DMA (₹127.99). The price distance from 200 DMA is +0.95%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>[130.54, 130.93, 131.32, 131.71, 132.11, 132.5]</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>[130.54, 132.68, 133.79, 134.74, 135.6, 136.4]</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>[130.54, 129.62, 129.47, 129.45, 129.49, 129.57]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -656,159 +656,159 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>131375.82</v>
+        <v>357916.19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>114.31</v>
+        <v>12167</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹113.92 - ₹114.9</t>
+          <t>₹12126.59 - ₹12227.61</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>115.87</v>
+        <v>12328.62</v>
       </c>
       <c r="I2" t="n">
-        <v>108.12</v>
+        <v>11508.32</v>
       </c>
       <c r="J2" t="n">
-        <v>106.98</v>
+        <v>11305.61</v>
       </c>
       <c r="K2" t="n">
-        <v>112.64</v>
+        <v>11570.61</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.14</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9</v>
+        <v>182.14</v>
       </c>
       <c r="N2" t="n">
-        <v>1.48</v>
+        <v>146.87</v>
       </c>
       <c r="O2" t="n">
-        <v>0.42</v>
+        <v>35.27</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>202.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R2" t="n">
-        <v>56.2</v>
+        <v>50.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.67</v>
+        <v>-0.83</v>
       </c>
       <c r="U2" t="n">
-        <v>56.7</v>
+        <v>50</v>
       </c>
       <c r="V2" t="n">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>111.97</v>
+        <v>12073.64</v>
       </c>
       <c r="Y2" t="n">
-        <v>115.43</v>
+        <v>12470.04</v>
       </c>
       <c r="Z2" t="n">
-        <v>115.22</v>
+        <v>12264.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.38</v>
+        <v>11863.96</v>
       </c>
       <c r="AB2" t="n">
-        <v>114.47</v>
+        <v>12125.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>115.03</v>
+        <v>12280.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>115.76</v>
+        <v>12394.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>79</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.9</v>
+        <v>41.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15.2</v>
+        <v>15.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>38.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>117.55</v>
+        <v>12431.89</v>
       </c>
       <c r="AN2" t="n">
-        <v>111.45</v>
+        <v>11891.42</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹131,375.82 Cr., a P/E ratio of 5.90, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹357,916.19 Cr., a P/E ratio of 41.89, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 79.03 (Bullish Momentum Zone), while MACD Line (1.90) trades above Signal (1.48) with an expanding histogram (+0.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +1.20% above the 200-day DMA (₹112.64). Daily volatility envelope is bounded by ATR(14) of ₹1.95.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.37 (Bullish Momentum Zone), while MACD Line (182.14) trades above Signal (146.87) with an expanding histogram (+35.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹11570.61). Daily volatility envelope is bounded by ATR(14) of ₹202.03.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹114.31) is positioned above the 30-day DMA (₹108.12), 50-day DMA (₹106.98), and 200-day DMA (₹112.64). The price distance from 200 DMA is +1.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,167.00) is positioned above the 30-day DMA (₹11,508.32), 50-day DMA (₹11,305.61), and 200-day DMA (₹11,570.61). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[114.31, 114.65, 115.0, 115.34, 115.68, 116.02]</t>
+          <t>[12167.0, 12256.14, 12345.28, 12434.43, 12523.57, 12612.71]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[114.31, 115.43, 116.1, 116.69, 117.24, 117.77]</t>
+          <t>[12167.0, 12336.95, 12459.57, 12574.39, 12685.19, 12793.41]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[114.31, 114.07, 114.17, 114.32, 114.51, 114.72]</t>
+          <t>[12167.0, 12195.53, 12259.57, 12329.45, 12402.35, 12477.19]</t>
         </is>
       </c>
     </row>
@@ -820,16 +820,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>359769.47</v>
+        <v>130674.76</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -837,142 +837,142 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12230</v>
+        <v>113.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹12186.77 - ₹12294.85</t>
+          <t>₹113.31 - ₹114.29</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12402.92</v>
+        <v>115.26</v>
       </c>
       <c r="I3" t="n">
-        <v>11480.92</v>
+        <v>108.12</v>
       </c>
       <c r="J3" t="n">
-        <v>11295.36</v>
+        <v>106.98</v>
       </c>
       <c r="K3" t="n">
-        <v>11571.42</v>
+        <v>112.64</v>
       </c>
       <c r="L3" t="n">
-        <v>4.14</v>
+        <v>1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>179.48</v>
+        <v>1.9</v>
       </c>
       <c r="N3" t="n">
-        <v>141.78</v>
+        <v>1.48</v>
       </c>
       <c r="O3" t="n">
-        <v>37.7</v>
+        <v>0.42</v>
       </c>
       <c r="P3" t="n">
-        <v>216.16</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R3" t="n">
         <v>49.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.93</v>
+        <v>-0.89</v>
       </c>
       <c r="U3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>2.71</v>
+        <v>3.01</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>12119.84</v>
+        <v>111.36</v>
       </c>
       <c r="Y3" t="n">
-        <v>12547.89</v>
+        <v>114.77</v>
       </c>
       <c r="Z3" t="n">
-        <v>12327.84</v>
+        <v>114.61</v>
       </c>
       <c r="AA3" t="n">
-        <v>11905.77</v>
+        <v>110.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>12146.33</v>
+        <v>114.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>12322.66</v>
+        <v>114.71</v>
       </c>
       <c r="AD3" t="n">
-        <v>12415.33</v>
+        <v>115.72</v>
       </c>
       <c r="AE3" t="n">
-        <v>76.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>42.1</v>
+        <v>5.9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>9.300000000000001</v>
+        <v>38.1</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>12498.59</v>
+        <v>116.75</v>
       </c>
       <c r="AN3" t="n">
-        <v>11948.19</v>
+        <v>110.96</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹359,769.47 Cr., a P/E ratio of 42.11, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,674.76 Cr., a P/E ratio of 5.86, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 76.59 (Bullish Momentum Zone), while MACD Line (179.48) trades above Signal (141.78) with an expanding histogram (+37.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹11571.42). Daily volatility envelope is bounded by ATR(14) of ₹216.16.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 79.03 (Bullish Momentum Zone), while MACD Line (1.90) trades above Signal (1.48) with an expanding histogram (+0.42). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +1.20% above the 200-day DMA (₹112.64). Daily volatility envelope is bounded by ATR(14) of ₹1.95.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,230.00) is positioned above the 30-day DMA (₹11,480.92), 50-day DMA (₹11,295.36), and 200-day DMA (₹11,571.42). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.70) is positioned above the 30-day DMA (₹108.12), 50-day DMA (₹106.98), and 200-day DMA (₹112.64). The price distance from 200 DMA is +1.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[12230.0, 12303.29, 12376.58, 12449.88, 12523.17, 12596.46]</t>
+          <t>[113.7, 114.04, 114.38, 114.72, 115.06, 115.41]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[12230.0, 12389.75, 12498.86, 12599.63, 12696.09, 12789.79]</t>
+          <t>[113.7, 114.82, 115.49, 116.08, 116.63, 117.15]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[12230.0, 12238.45, 12284.88, 12337.56, 12393.47, 12451.46]</t>
+          <t>[113.7, 113.46, 113.55, 113.71, 113.89, 114.1]</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>218999.69</v>
+        <v>218629.08</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1001,15 +1001,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7977.5</v>
+        <v>7964</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹7946.14 - ₹8024.54</t>
+          <t>₹7932.64 - ₹8011.04</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8102.95</v>
+        <v>8089.45</v>
       </c>
       <c r="I4" t="n">
         <v>7478.7</v>
@@ -1036,16 +1036,16 @@
         <v>156.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R4" t="n">
-        <v>51</v>
+        <v>51.4</v>
       </c>
       <c r="S4" t="n">
         <v>0.27</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.04</v>
+        <v>-1.02</v>
       </c>
       <c r="U4" t="n">
         <v>51.7</v>
@@ -1057,25 +1057,25 @@
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>7852.76</v>
+        <v>7838.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>8131.97</v>
+        <v>8117.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>8041.32</v>
+        <v>8027.71</v>
       </c>
       <c r="AA4" t="n">
-        <v>7742.28</v>
+        <v>7728.78</v>
       </c>
       <c r="AB4" t="n">
-        <v>7959.33</v>
+        <v>7954.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>8013.16</v>
+        <v>8004.16</v>
       </c>
       <c r="AD4" t="n">
-        <v>8048.83</v>
+        <v>8044.33</v>
       </c>
       <c r="AE4" t="n">
         <v>74.3</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
@@ -1104,14 +1104,14 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>8193.860000000001</v>
+        <v>8191.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>7771.46</v>
+        <v>7776.28</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹218,999.69 Cr., a P/E ratio of 38.52, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹218,629.08 Cr., a P/E ratio of 38.45, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1121,22 +1121,22 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,977.50) is positioned above the 30-day DMA (₹7,478.70), 50-day DMA (₹7,389.91), and 200-day DMA (₹7,187.90). The price distance from 200 DMA is +10.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,964.00) is positioned above the 30-day DMA (₹7,478.70), 50-day DMA (₹7,389.91), and 200-day DMA (₹7,187.90). The price distance from 200 DMA is +10.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[7977.5, 8001.43, 8025.36, 8049.3, 8073.23, 8097.16]</t>
+          <t>[7964.0, 7987.89, 8011.78, 8035.68, 8059.57, 8083.46]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[7977.5, 8064.16, 8114.07, 8157.94, 8198.68, 8237.42]</t>
+          <t>[7964.0, 8050.62, 8100.49, 8144.32, 8185.02, 8223.72]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[7977.5, 7954.39, 7958.84, 7967.82, 7979.14, 7991.97]</t>
+          <t>[7964.0, 7940.85, 7945.25, 7954.19, 7965.48, 7978.27]</t>
         </is>
       </c>
     </row>
@@ -1148,159 +1148,159 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>67548.24000000001</v>
+        <v>308592.82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5649.5</v>
+        <v>4614.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹5624.83 - ₹5686.51</t>
+          <t>₹4598.26 - ₹4638.36</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5748.19</v>
+        <v>4678.45</v>
       </c>
       <c r="I5" t="n">
-        <v>5586.12</v>
+        <v>4490.17</v>
       </c>
       <c r="J5" t="n">
-        <v>5490.13</v>
+        <v>4419.22</v>
       </c>
       <c r="K5" t="n">
-        <v>5522.54</v>
+        <v>4344.79</v>
       </c>
       <c r="L5" t="n">
-        <v>3.34</v>
+        <v>6.68</v>
       </c>
       <c r="M5" t="n">
-        <v>56.93</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>52.95</v>
+        <v>56.51</v>
       </c>
       <c r="O5" t="n">
-        <v>3.98</v>
+        <v>7.78</v>
       </c>
       <c r="P5" t="n">
-        <v>123.36</v>
+        <v>80.19</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R5" t="n">
-        <v>50.1</v>
+        <v>40.7</v>
       </c>
       <c r="S5" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.23</v>
+        <v>-1.22</v>
       </c>
       <c r="U5" t="n">
-        <v>51.7</v>
+        <v>41.7</v>
       </c>
       <c r="V5" t="n">
-        <v>3.12</v>
+        <v>2.34</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>5501.47</v>
+        <v>4518.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>5661.36</v>
+        <v>4652.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>5694.7</v>
+        <v>4651.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>5464.46</v>
+        <v>4494.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>5623.67</v>
+        <v>4630.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>5691.34</v>
+        <v>4657.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>5733.17</v>
+        <v>4700.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>57.9</v>
+        <v>72.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>29.3</v>
+        <v>33.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.6</v>
+        <v>1.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>15.6</v>
+        <v>27.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>17.6</v>
+        <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>5795.08</v>
+        <v>4738.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>5523.57</v>
+        <v>4490.62</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,548.24 Cr., a P/E ratio of 29.32, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹308,592.82 Cr., a P/E ratio of 33.89, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.91 (Bullish Momentum Zone), while MACD Line (56.93) trades above Signal (52.95) with an expanding histogram (+3.98). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.34% above the 200-day DMA (₹5522.54). Daily volatility envelope is bounded by ATR(14) of ₹123.36.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.77 (Bullish Momentum Zone), while MACD Line (64.29) trades above Signal (56.51) with an expanding histogram (+7.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.68% above the 200-day DMA (₹4344.79). Daily volatility envelope is bounded by ATR(14) of ₹80.19.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,649.50) is positioned above the 30-day DMA (₹5,586.12), 50-day DMA (₹5,490.13), and 200-day DMA (₹5,522.54). The price distance from 200 DMA is +3.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,614.30) is positioned above the 30-day DMA (₹4,490.17), 50-day DMA (₹4,419.22), and 200-day DMA (₹4,344.79). The price distance from 200 DMA is +6.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[5649.5, 5666.45, 5683.4, 5700.35, 5717.29, 5734.24]</t>
+          <t>[4614.3, 4628.14, 4641.99, 4655.83, 4669.67, 4683.51]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[5649.5, 5715.79, 5753.18, 5785.81, 5815.98, 5844.58]</t>
+          <t>[4614.3, 4660.22, 4687.35, 4711.38, 4733.82, 4755.23]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[5649.5, 5629.44, 5631.06, 5636.25, 5643.28, 5651.49]</t>
+          <t>[4614.3, 4604.09, 4607.97, 4614.16, 4621.56, 4629.72]</t>
         </is>
       </c>
     </row>
@@ -1312,16 +1312,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>308760.02</v>
+        <v>67434.66</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1329,142 +1329,142 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4616.8</v>
+        <v>5640</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹4600.76 - ₹4640.86</t>
+          <t>₹5616.66 - ₹5675.0</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4680.95</v>
+        <v>5733.34</v>
       </c>
       <c r="I6" t="n">
-        <v>4490.17</v>
+        <v>5598.93</v>
       </c>
       <c r="J6" t="n">
-        <v>4419.22</v>
+        <v>5497.15</v>
       </c>
       <c r="K6" t="n">
-        <v>4344.79</v>
+        <v>5524.06</v>
       </c>
       <c r="L6" t="n">
-        <v>6.68</v>
+        <v>3.31</v>
       </c>
       <c r="M6" t="n">
-        <v>64.29000000000001</v>
+        <v>58.81</v>
       </c>
       <c r="N6" t="n">
-        <v>56.51</v>
+        <v>54.69</v>
       </c>
       <c r="O6" t="n">
-        <v>7.78</v>
+        <v>4.12</v>
       </c>
       <c r="P6" t="n">
-        <v>80.19</v>
+        <v>116.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R6" t="n">
-        <v>40.4</v>
+        <v>46.7</v>
       </c>
       <c r="S6" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.23</v>
+        <v>-1.28</v>
       </c>
       <c r="U6" t="n">
-        <v>41.7</v>
+        <v>51.7</v>
       </c>
       <c r="V6" t="n">
-        <v>2.34</v>
+        <v>2.81</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>4520.58</v>
+        <v>5499.99</v>
       </c>
       <c r="Y6" t="n">
-        <v>4655.54</v>
+        <v>5606.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>4653.73</v>
+        <v>5685.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>4496.52</v>
+        <v>5464.98</v>
       </c>
       <c r="AB6" t="n">
-        <v>4631.23</v>
+        <v>5620.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4658.96</v>
+        <v>5685</v>
       </c>
       <c r="AD6" t="n">
-        <v>4701.13</v>
+        <v>5730</v>
       </c>
       <c r="AE6" t="n">
-        <v>72.8</v>
+        <v>56.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.27</v>
+        <v>-0.03</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>33.9</v>
+        <v>29.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.8</v>
+        <v>14.6</v>
       </c>
       <c r="AK6" t="n">
-        <v>27.5</v>
+        <v>15.6</v>
       </c>
       <c r="AL6" t="n">
-        <v>24</v>
+        <v>17.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>4743.19</v>
+        <v>5768.09</v>
       </c>
       <c r="AN6" t="n">
-        <v>4486.26</v>
+        <v>5520.18</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹308,760.02 Cr., a P/E ratio of 33.91, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,434.66 Cr., a P/E ratio of 29.27, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.77 (Bullish Momentum Zone), while MACD Line (64.29) trades above Signal (56.51) with an expanding histogram (+7.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.68% above the 200-day DMA (₹4344.79). Daily volatility envelope is bounded by ATR(14) of ₹80.19.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.20 (Bullish Momentum Zone), while MACD Line (58.81) trades above Signal (54.69) with an expanding histogram (+4.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.31% above the 200-day DMA (₹5524.06). Daily volatility envelope is bounded by ATR(14) of ₹116.68.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,616.80) is positioned above the 30-day DMA (₹4,490.17), 50-day DMA (₹4,419.22), and 200-day DMA (₹4,344.79). The price distance from 200 DMA is +6.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,640.00) is positioned above the 30-day DMA (₹5,598.93), 50-day DMA (₹5,497.15), and 200-day DMA (₹5,524.06). The price distance from 200 DMA is +3.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[4616.8, 4630.65, 4644.5, 4658.35, 4672.2, 4686.05]</t>
+          <t>[5640.0, 5656.92, 5673.84, 5690.76, 5707.68, 5724.6]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[4616.8, 4662.72, 4689.86, 4713.91, 4736.35, 4757.77]</t>
+          <t>[5640.0, 5703.59, 5739.84, 5771.6, 5801.02, 5828.96]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[4616.8, 4606.59, 4610.48, 4616.69, 4624.09, 4632.26]</t>
+          <t>[5640.0, 5621.92, 5624.34, 5630.13, 5637.67, 5646.33]</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>265247.29</v>
+        <v>264844.66</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1493,98 +1493,98 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2766.9</v>
+        <v>2762.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹2755.03 - ₹2784.7</t>
+          <t>₹2750.45 - ₹2780.07</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2814.38</v>
+        <v>2809.69</v>
       </c>
       <c r="I7" t="n">
-        <v>2695.34</v>
+        <v>2698.21</v>
       </c>
       <c r="J7" t="n">
-        <v>2685.42</v>
+        <v>2687.88</v>
       </c>
       <c r="K7" t="n">
-        <v>2575.56</v>
+        <v>2577.55</v>
       </c>
       <c r="L7" t="n">
-        <v>7.74</v>
+        <v>7.66</v>
       </c>
       <c r="M7" t="n">
-        <v>25.61</v>
+        <v>26.47</v>
       </c>
       <c r="N7" t="n">
-        <v>15.29</v>
+        <v>16.72</v>
       </c>
       <c r="O7" t="n">
-        <v>10.32</v>
+        <v>9.76</v>
       </c>
       <c r="P7" t="n">
-        <v>59.35</v>
+        <v>59.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R7" t="n">
-        <v>47.5</v>
+        <v>47.9</v>
       </c>
       <c r="S7" t="n">
         <v>0.25</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.31</v>
+        <v>-1.29</v>
       </c>
       <c r="U7" t="n">
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2695.68</v>
+        <v>2691.22</v>
       </c>
       <c r="Y7" t="n">
-        <v>2792.17</v>
+        <v>2784.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2789.04</v>
+        <v>2784.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>2677.87</v>
+        <v>2673.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>2767.53</v>
+        <v>2766</v>
       </c>
       <c r="AC7" t="n">
-        <v>2786.36</v>
+        <v>2783.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>2805.83</v>
+        <v>2804.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>69.8</v>
+        <v>67</v>
       </c>
       <c r="AF7" t="n">
         <v>0.02</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="AJ7" t="n">
         <v>17.9</v>
@@ -1596,39 +1596,39 @@
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>2830.02</v>
+        <v>2824.01</v>
       </c>
       <c r="AN7" t="n">
-        <v>2706.16</v>
+        <v>2699.84</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹265,247.29 Cr., a P/E ratio of 56.33, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹264,844.66 Cr., a P/E ratio of 56.24, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 69.81 (Bullish Momentum Zone), while MACD Line (25.61) trades above Signal (15.29) with an expanding histogram (+10.32). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.74% above the 200-day DMA (₹2575.56). Daily volatility envelope is bounded by ATR(14) of ₹59.35.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.98 (Bullish Momentum Zone), while MACD Line (26.47) trades above Signal (16.72) with an expanding histogram (+9.76). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.66% above the 200-day DMA (₹2577.55). Daily volatility envelope is bounded by ATR(14) of ₹59.24.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,766.90) is positioned above the 30-day DMA (₹2,695.34), 50-day DMA (₹2,685.42), and 200-day DMA (₹2,575.56). The price distance from 200 DMA is +7.74%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,762.30) is positioned above the 30-day DMA (₹2,698.21), 50-day DMA (₹2,687.88), and 200-day DMA (₹2,577.55). The price distance from 200 DMA is +7.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[2766.9, 2775.2, 2783.5, 2791.8, 2800.1, 2808.4]</t>
+          <t>[2762.3, 2770.59, 2778.87, 2787.16, 2795.45, 2803.73]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2766.9, 2798.94, 2817.07, 2832.92, 2847.58, 2861.49]</t>
+          <t>[2762.3, 2794.28, 2812.38, 2828.2, 2842.84, 2856.72]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2766.9, 2757.4, 2758.32, 2760.96, 2764.49, 2768.59]</t>
+          <t>[2762.3, 2752.82, 2753.74, 2756.38, 2759.91, 2764.0]</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>106686.24</v>
+        <v>105547.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1657,15 +1657,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>749.5</v>
+        <v>741.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹746.51 - ₹753.99</t>
+          <t>₹738.11 - ₹745.59</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>761.48</v>
+        <v>753.08</v>
       </c>
       <c r="I8" t="n">
         <v>731.6799999999999</v>
@@ -1692,46 +1692,46 @@
         <v>14.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R8" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="S8" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.34</v>
+        <v>-1.35</v>
       </c>
       <c r="U8" t="n">
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>6.36</v>
+        <v>6.32</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>731.53</v>
+        <v>723.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>743.64</v>
+        <v>734</v>
       </c>
       <c r="Z8" t="n">
-        <v>755.5</v>
+        <v>747.03</v>
       </c>
       <c r="AA8" t="n">
-        <v>727.04</v>
+        <v>718.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>749.22</v>
+        <v>744.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>753.1900000000001</v>
+        <v>749.21</v>
       </c>
       <c r="AD8" t="n">
-        <v>756.87</v>
+        <v>757.33</v>
       </c>
       <c r="AE8" t="n">
         <v>54.1</v>
@@ -1741,14 +1741,14 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>50</v>
+        <v>49.4</v>
       </c>
       <c r="AJ8" t="n">
         <v>15.1</v>
@@ -1760,14 +1760,14 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>769.26</v>
+        <v>760.01</v>
       </c>
       <c r="AN8" t="n">
-        <v>731.1799999999999</v>
+        <v>721.91</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,686.24 Cr., a P/E ratio of 49.97, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,547.50 Cr., a P/E ratio of 49.43, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1777,22 +1777,22 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹749.50) is positioned above the 30-day DMA (₹731.68), 50-day DMA (₹709.25), and 200-day DMA (₹686.46). The price distance from 200 DMA is +9.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.10) is positioned above the 30-day DMA (₹731.68), 50-day DMA (₹709.25), and 200-day DMA (₹686.46). The price distance from 200 DMA is +9.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[749.5, 751.75, 754.0, 756.25, 758.49, 760.74]</t>
+          <t>[741.1, 743.32, 745.55, 747.77, 749.99, 752.22]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[749.5, 757.74, 762.47, 766.62, 770.47, 774.13]</t>
+          <t>[741.1, 749.31, 754.02, 758.14, 761.97, 765.61]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[749.5, 747.26, 747.65, 748.47, 749.51, 750.7]</t>
+          <t>[741.1, 738.83, 739.19, 739.99, 741.01, 742.17]</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96468.16</v>
+        <v>25000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1821,15 +1821,15 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>366.35</v>
+        <v>366.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹364.78 - ₹368.7</t>
+          <t>₹364.73 - ₹368.65</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>372.61</v>
+        <v>372.56</v>
       </c>
       <c r="I9" t="n">
         <v>358.01</v>
@@ -1856,16 +1856,16 @@
         <v>7.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R9" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="S9" t="n">
         <v>0.25</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.46</v>
+        <v>-1.47</v>
       </c>
       <c r="U9" t="n">
         <v>50</v>
@@ -1877,25 +1877,25 @@
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>358.4</v>
+        <v>358.35</v>
       </c>
       <c r="Y9" t="n">
-        <v>371.22</v>
+        <v>371.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>369.28</v>
+        <v>369.23</v>
       </c>
       <c r="AA9" t="n">
-        <v>354.61</v>
+        <v>354.56</v>
       </c>
       <c r="AB9" t="n">
-        <v>368.12</v>
+        <v>368.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>370.54</v>
+        <v>370.59</v>
       </c>
       <c r="AD9" t="n">
-        <v>374.72</v>
+        <v>374.87</v>
       </c>
       <c r="AE9" t="n">
         <v>71.8</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
@@ -1924,14 +1924,14 @@
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>376.12</v>
+        <v>375.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>357.16</v>
+        <v>356.96</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹96,468.16 Cr., a P/E ratio of 6.03, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.03, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1941,22 +1941,22 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹366.35) is positioned above the 30-day DMA (₹358.01), 50-day DMA (₹351.17), and 200-day DMA (₹347.72). The price distance from 200 DMA is +5.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹366.30) is positioned above the 30-day DMA (₹358.01), 50-day DMA (₹351.17), and 200-day DMA (₹347.72). The price distance from 200 DMA is +5.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[366.35, 367.45, 368.55, 369.65, 370.75, 371.85]</t>
+          <t>[366.3, 367.4, 368.5, 369.6, 370.7, 371.79]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[366.35, 370.58, 372.97, 375.07, 377.01, 378.84]</t>
+          <t>[366.3, 370.53, 372.92, 375.02, 376.96, 378.79]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[366.35, 365.1, 365.23, 365.58, 366.05, 366.6]</t>
+          <t>[366.3, 365.05, 365.18, 365.53, 366.0, 366.55]</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>117332.6</v>
+        <v>116839.81</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1985,15 +1985,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1452.4</v>
+        <v>1446.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹1445.57 - ₹1462.64</t>
+          <t>₹1439.47 - ₹1456.54</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1479.71</v>
+        <v>1473.61</v>
       </c>
       <c r="I10" t="n">
         <v>1443.04</v>
@@ -2020,46 +2020,46 @@
         <v>34.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R10" t="n">
-        <v>42.4</v>
+        <v>41.9</v>
       </c>
       <c r="S10" t="n">
         <v>0.23</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.69</v>
+        <v>-1.72</v>
       </c>
       <c r="U10" t="n">
         <v>45</v>
       </c>
       <c r="V10" t="n">
-        <v>12.14</v>
+        <v>12.13</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>1411.43</v>
+        <v>1405.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>1414.42</v>
+        <v>1407.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>1464.02</v>
+        <v>1457.87</v>
       </c>
       <c r="AA10" t="n">
-        <v>1401.19</v>
+        <v>1395.09</v>
       </c>
       <c r="AB10" t="n">
-        <v>1451.97</v>
+        <v>1449.93</v>
       </c>
       <c r="AC10" t="n">
-        <v>1460.44</v>
+        <v>1456.36</v>
       </c>
       <c r="AD10" t="n">
-        <v>1468.47</v>
+        <v>1466.43</v>
       </c>
       <c r="AE10" t="n">
         <v>55.4</v>
@@ -2069,14 +2069,14 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="AJ10" t="n">
         <v>3.5</v>
@@ -2088,14 +2088,14 @@
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>1482.56</v>
+        <v>1477.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>1423.79</v>
+        <v>1416.76</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,332.60 Cr., a P/E ratio of 35.15, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹116,839.81 Cr., a P/E ratio of 35.00, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2105,22 +2105,22 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,452.40) is positioned above the 30-day DMA (₹1,443.04), 50-day DMA (₹1,419.16), and 200-day DMA (₹1,394.98). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,446.30) is positioned above the 30-day DMA (₹1,443.04), 50-day DMA (₹1,419.16), and 200-day DMA (₹1,394.98). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[1452.4, 1456.76, 1461.11, 1465.47, 1469.83, 1474.19]</t>
+          <t>[1446.3, 1450.64, 1454.98, 1459.32, 1463.66, 1467.99]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[1452.4, 1470.41, 1480.43, 1489.13, 1497.14, 1504.72]</t>
+          <t>[1446.3, 1464.3, 1474.29, 1482.97, 1490.97, 1498.53]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[1452.4, 1446.51, 1446.63, 1447.73, 1449.34, 1451.28]</t>
+          <t>[1446.3, 1440.4, 1440.49, 1441.58, 1443.17, 1445.09]</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>147307.86</v>
+        <v>147059.82</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2149,15 +2149,15 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1662.9</v>
+        <v>1660.1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹1653.79 - ₹1676.57</t>
+          <t>₹1650.99 - ₹1673.77</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1699.36</v>
+        <v>1696.56</v>
       </c>
       <c r="I11" t="n">
         <v>1496.08</v>
@@ -2184,16 +2184,16 @@
         <v>45.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R11" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="S11" t="n">
         <v>0.19</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.73</v>
+        <v>-1.76</v>
       </c>
       <c r="U11" t="n">
         <v>50</v>
@@ -2205,25 +2205,25 @@
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>1634.56</v>
+        <v>1631.55</v>
       </c>
       <c r="Y11" t="n">
-        <v>1692.76</v>
+        <v>1689.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>1676.2</v>
+        <v>1673.38</v>
       </c>
       <c r="AA11" t="n">
-        <v>1594.54</v>
+        <v>1591.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1658.47</v>
+        <v>1657.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>1669.24</v>
+        <v>1667.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>1675.57</v>
+        <v>1674.63</v>
       </c>
       <c r="AE11" t="n">
         <v>83.5</v>
@@ -2233,14 +2233,14 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="AJ11" t="n">
         <v>17.7</v>
@@ -2252,14 +2252,14 @@
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>1710.59</v>
+        <v>1703.43</v>
       </c>
       <c r="AN11" t="n">
-        <v>1616</v>
+        <v>1615.17</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹147,307.86 Cr., a P/E ratio of 28.77, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹147,059.82 Cr., a P/E ratio of 28.72, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2269,22 +2269,22 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,662.90) is positioned above the 30-day DMA (₹1,496.08), 50-day DMA (₹1,470.74), and 200-day DMA (₹1,461.21). The price distance from 200 DMA is +12.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,660.10) is positioned above the 30-day DMA (₹1,496.08), 50-day DMA (₹1,470.74), and 200-day DMA (₹1,461.21). The price distance from 200 DMA is +12.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[1662.9, 1667.89, 1672.88, 1677.87, 1682.85, 1687.84]</t>
+          <t>[1660.1, 1665.08, 1670.06, 1675.04, 1680.02, 1685.0]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[1662.9, 1686.12, 1698.66, 1709.44, 1719.31, 1728.6]</t>
+          <t>[1660.1, 1683.31, 1695.84, 1706.61, 1716.48, 1725.76]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[1662.9, 1654.22, 1653.54, 1654.19, 1655.51, 1657.27]</t>
+          <t>[1660.1, 1651.41, 1650.73, 1651.36, 1652.68, 1654.43]</t>
         </is>
       </c>
     </row>
@@ -2296,16 +2296,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48196.02</v>
+        <v>78803.39</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2313,142 +2313,142 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1184.5</v>
+        <v>1780.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹1177.76 - ₹1194.61</t>
+          <t>₹1768.46 - ₹1797.56</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1211.45</v>
+        <v>1826.65</v>
       </c>
       <c r="I12" t="n">
-        <v>1109.65</v>
+        <v>1530.06</v>
       </c>
       <c r="J12" t="n">
-        <v>1106.05</v>
+        <v>1489.66</v>
       </c>
       <c r="K12" t="n">
-        <v>1100.66</v>
+        <v>1504.99</v>
       </c>
       <c r="L12" t="n">
-        <v>4.28</v>
+        <v>16.27</v>
       </c>
       <c r="M12" t="n">
-        <v>10.48</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>5.87</v>
+        <v>49.28</v>
       </c>
       <c r="O12" t="n">
-        <v>4.62</v>
+        <v>25.43</v>
       </c>
       <c r="P12" t="n">
-        <v>33.69</v>
+        <v>58.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R12" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.81</v>
+        <v>-1.79</v>
       </c>
       <c r="U12" t="n">
         <v>50</v>
       </c>
       <c r="V12" t="n">
-        <v>2.31</v>
+        <v>7.75</v>
       </c>
       <c r="W12" t="n">
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>1174.79</v>
+        <v>1778.84</v>
       </c>
       <c r="Y12" t="n">
-        <v>1216.24</v>
+        <v>1841.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>1193.98</v>
+        <v>1805.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>1133.97</v>
+        <v>1692.81</v>
       </c>
       <c r="AB12" t="n">
-        <v>1179.6</v>
+        <v>1771.07</v>
       </c>
       <c r="AC12" t="n">
-        <v>1195.9</v>
+        <v>1797.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>1207.3</v>
+        <v>1813.97</v>
       </c>
       <c r="AE12" t="n">
-        <v>56.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AF12" t="n">
         <v>0.19</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH12" t="n">
         <v>0.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>39.4</v>
+        <v>36.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>29.9</v>
+        <v>49.9</v>
       </c>
       <c r="AK12" t="n">
-        <v>26.5</v>
+        <v>9.6</v>
       </c>
       <c r="AL12" t="n">
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>1220.38</v>
+        <v>1852.95</v>
       </c>
       <c r="AN12" t="n">
-        <v>1146.87</v>
+        <v>1713.15</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹48,196.02 Cr., a P/E ratio of 39.39, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹78,803.39 Cr., a P/E ratio of 36.86, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.33 (Bullish Momentum Zone), while MACD Line (10.48) trades above Signal (5.87) with an expanding histogram (+4.62). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.28% above the 200-day DMA (₹1100.66). Daily volatility envelope is bounded by ATR(14) of ₹33.69.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.86 (Bullish Momentum Zone), while MACD Line (74.71) trades above Signal (49.28) with an expanding histogram (+25.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.27% above the 200-day DMA (₹1504.99). Daily volatility envelope is bounded by ATR(14) of ₹58.19.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,184.50) is positioned above the 30-day DMA (₹1,109.65), 50-day DMA (₹1,106.05), and 200-day DMA (₹1,100.66). The price distance from 200 DMA is +4.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,780.10) is positioned above the 30-day DMA (₹1,530.06), 50-day DMA (₹1,489.66), and 200-day DMA (₹1,504.99). The price distance from 200 DMA is +16.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[1184.5, 1192.55, 1200.61, 1208.66, 1216.71, 1224.76]</t>
+          <t>[1780.1, 1805.55, 1830.99, 1856.44, 1881.89, 1907.33]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1184.5, 1206.03, 1219.66, 1232.0, 1243.66, 1254.89]</t>
+          <t>[1780.1, 1828.82, 1863.91, 1896.76, 1928.44, 1959.38]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1184.5, 1182.45, 1186.31, 1191.15, 1196.5, 1202.17]</t>
+          <t>[1780.1, 1788.09, 1806.3, 1826.2, 1846.97, 1868.29]</t>
         </is>
       </c>
     </row>
@@ -2460,159 +2460,159 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>78812.25</v>
+        <v>48334.37</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1780.3</v>
+        <v>1187.9</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1768.66 - ₹1797.76</t>
+          <t>₹1181.11 - ₹1198.08</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1826.85</v>
+        <v>1215.05</v>
       </c>
       <c r="I13" t="n">
-        <v>1530.06</v>
+        <v>1109.52</v>
       </c>
       <c r="J13" t="n">
-        <v>1489.66</v>
+        <v>1105.91</v>
       </c>
       <c r="K13" t="n">
-        <v>1504.99</v>
+        <v>1100.89</v>
       </c>
       <c r="L13" t="n">
-        <v>16.27</v>
+        <v>4.26</v>
       </c>
       <c r="M13" t="n">
-        <v>74.70999999999999</v>
+        <v>10.65</v>
       </c>
       <c r="N13" t="n">
-        <v>49.28</v>
+        <v>6.66</v>
       </c>
       <c r="O13" t="n">
-        <v>25.43</v>
+        <v>3.99</v>
       </c>
       <c r="P13" t="n">
-        <v>58.19</v>
+        <v>33.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R13" t="n">
-        <v>48.7</v>
+        <v>47.7</v>
       </c>
       <c r="S13" t="n">
-        <v>0.29</v>
+        <v>0.19</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.82</v>
+        <v>-1.86</v>
       </c>
       <c r="U13" t="n">
         <v>50</v>
       </c>
       <c r="V13" t="n">
-        <v>7.75</v>
+        <v>2.35</v>
       </c>
       <c r="W13" t="n">
         <v>-0.77</v>
       </c>
       <c r="X13" t="n">
-        <v>1779.07</v>
+        <v>1170.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1841.38</v>
+        <v>1211.78</v>
       </c>
       <c r="Z13" t="n">
-        <v>1805.77</v>
+        <v>1197.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1693.01</v>
+        <v>1137</v>
       </c>
       <c r="AB13" t="n">
-        <v>1769.57</v>
+        <v>1180.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>1794.04</v>
+        <v>1198.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>1807.77</v>
+        <v>1208.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>72.90000000000001</v>
+        <v>60.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH13" t="n">
         <v>0.15</v>
       </c>
       <c r="AI13" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>49.9</v>
+        <v>29.9</v>
       </c>
       <c r="AK13" t="n">
-        <v>9.6</v>
+        <v>26.5</v>
       </c>
       <c r="AL13" t="n">
         <v>15</v>
       </c>
       <c r="AM13" t="n">
-        <v>1848.76</v>
+        <v>1224.16</v>
       </c>
       <c r="AN13" t="n">
-        <v>1707.79</v>
+        <v>1151.08</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹78,812.25 Cr., a P/E ratio of 36.42, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹48,334.37 Cr., a P/E ratio of 39.48, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.86 (Bullish Momentum Zone), while MACD Line (74.71) trades above Signal (49.28) with an expanding histogram (+25.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.27% above the 200-day DMA (₹1504.99). Daily volatility envelope is bounded by ATR(14) of ₹58.19.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.59 (Bullish Momentum Zone), while MACD Line (10.65) trades above Signal (6.66) with an expanding histogram (+3.99). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.26% above the 200-day DMA (₹1100.89). Daily volatility envelope is bounded by ATR(14) of ₹33.94.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,780.30) is positioned above the 30-day DMA (₹1,530.06), 50-day DMA (₹1,489.66), and 200-day DMA (₹1,504.99). The price distance from 200 DMA is +16.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,187.90) is positioned above the 30-day DMA (₹1,109.52), 50-day DMA (₹1,105.91), and 200-day DMA (₹1,100.89). The price distance from 200 DMA is +4.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>[1780.3, 1805.77, 1831.25, 1856.72, 1882.2, 1907.67]</t>
+          <t>[1187.9, 1191.46, 1195.03, 1198.59, 1202.15, 1205.72]</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1780.3, 1829.05, 1864.17, 1897.04, 1928.75, 1959.72]</t>
+          <t>[1187.9, 1205.04, 1214.22, 1222.1, 1229.3, 1236.07]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1780.3, 1788.32, 1806.56, 1826.48, 1847.28, 1868.63]</t>
+          <t>[1187.9, 1181.28, 1180.63, 1180.96, 1181.79, 1182.95]</t>
         </is>
       </c>
     </row>
@@ -2624,16 +2624,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>288773.19</v>
+        <v>87098.71000000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2641,142 +2641,142 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>313.7</v>
+        <v>14325</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹311.63 - ₹316.81</t>
+          <t>₹14231.1 - ₹14465.85</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>321.98</v>
+        <v>14700.6</v>
       </c>
       <c r="I14" t="n">
-        <v>286.32</v>
+        <v>13362.03</v>
       </c>
       <c r="J14" t="n">
-        <v>272.64</v>
+        <v>12739.88</v>
       </c>
       <c r="K14" t="n">
-        <v>273.39</v>
+        <v>12290.57</v>
       </c>
       <c r="L14" t="n">
-        <v>14.27</v>
+        <v>13.81</v>
       </c>
       <c r="M14" t="n">
-        <v>10.44</v>
+        <v>385.37</v>
       </c>
       <c r="N14" t="n">
-        <v>9.26</v>
+        <v>458.72</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>-73.34999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>10.35</v>
+        <v>469.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R14" t="n">
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
       <c r="S14" t="n">
         <v>0.16</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.05</v>
+        <v>-2.09</v>
       </c>
       <c r="U14" t="n">
-        <v>55</v>
+        <v>48.3</v>
       </c>
       <c r="V14" t="n">
-        <v>2.43</v>
+        <v>6.4</v>
       </c>
       <c r="W14" t="n">
         <v>-0.77</v>
       </c>
       <c r="X14" t="n">
-        <v>309.61</v>
+        <v>14218.88</v>
       </c>
       <c r="Y14" t="n">
-        <v>320.59</v>
+        <v>14720.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>316.21</v>
+        <v>14439.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>298.18</v>
+        <v>13620.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>313.25</v>
+        <v>14238.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>315.1</v>
+        <v>14453.66</v>
       </c>
       <c r="AD14" t="n">
-        <v>316.5</v>
+        <v>14582.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>62.2</v>
+        <v>55.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH14" t="n">
         <v>0.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>667.4</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>182</v>
+        <v>21.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="AL14" t="n">
         <v>15</v>
       </c>
       <c r="AM14" t="n">
-        <v>325.52</v>
+        <v>14823.15</v>
       </c>
       <c r="AN14" t="n">
-        <v>303.48</v>
+        <v>13781.84</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹288,773.19 Cr., a P/E ratio of 667.45, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹87,098.71 Cr., a P/E ratio of 41.96, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.17 (Bullish Momentum Zone), while MACD Line (10.44) trades above Signal (9.26) with an expanding histogram (+1.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.27% above the 200-day DMA (₹273.39). Daily volatility envelope is bounded by ATR(14) of ₹10.35.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.30 (Bullish Momentum Zone), while MACD Line (385.37) trades below Signal (458.72) with an expanding histogram (-73.35). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.81% above the 200-day DMA (₹12290.57). Daily volatility envelope is bounded by ATR(14) of ₹469.50.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹313.70) is positioned above the 30-day DMA (₹286.32), 50-day DMA (₹272.64), and 200-day DMA (₹273.39). The price distance from 200 DMA is +14.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,325.00) is positioned above the 30-day DMA (₹13,362.03), 50-day DMA (₹12,739.88), and 200-day DMA (₹12,290.57). The price distance from 200 DMA is +13.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>[313.7, 314.64, 315.58, 316.52, 317.46, 318.41]</t>
+          <t>[14325.0, 14433.75, 14542.5, 14651.25, 14760.01, 14868.76]</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[313.7, 318.78, 321.44, 323.69, 325.74, 327.66]</t>
+          <t>[14325.0, 14621.55, 14808.09, 14976.53, 15135.61, 15288.69]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[313.7, 311.54, 311.19, 311.15, 311.25, 311.46]</t>
+          <t>[14325.0, 14292.9, 14343.31, 14407.3, 14478.31, 14553.81]</t>
         </is>
       </c>
     </row>
@@ -2788,16 +2788,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>87159.50999999999</v>
+        <v>11537.78</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2805,142 +2805,142 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14335</v>
+        <v>129.74</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹14241.1 - ₹14475.85</t>
+          <t>₹128.87 - ₹131.05</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14710.6</v>
+        <v>133.23</v>
       </c>
       <c r="I15" t="n">
-        <v>13362.03</v>
+        <v>124.43</v>
       </c>
       <c r="J15" t="n">
-        <v>12739.88</v>
+        <v>123.96</v>
       </c>
       <c r="K15" t="n">
-        <v>12290.57</v>
+        <v>127.99</v>
       </c>
       <c r="L15" t="n">
-        <v>13.81</v>
+        <v>0.95</v>
       </c>
       <c r="M15" t="n">
-        <v>385.37</v>
+        <v>2.09</v>
       </c>
       <c r="N15" t="n">
-        <v>458.72</v>
+        <v>1.41</v>
       </c>
       <c r="O15" t="n">
-        <v>-73.34999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="P15" t="n">
-        <v>469.5</v>
+        <v>4.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R15" t="n">
-        <v>49.7</v>
+        <v>49</v>
       </c>
       <c r="S15" t="n">
         <v>0.16</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.07</v>
+        <v>-2.18</v>
       </c>
       <c r="U15" t="n">
         <v>48.3</v>
       </c>
       <c r="V15" t="n">
-        <v>6.4</v>
+        <v>3.62</v>
       </c>
       <c r="W15" t="n">
         <v>-0.77</v>
       </c>
       <c r="X15" t="n">
-        <v>14230.59</v>
+        <v>125.13</v>
       </c>
       <c r="Y15" t="n">
-        <v>14732.31</v>
+        <v>129.67</v>
       </c>
       <c r="Z15" t="n">
-        <v>14449.68</v>
+        <v>130.78</v>
       </c>
       <c r="AA15" t="n">
-        <v>13630.75</v>
+        <v>123.19</v>
       </c>
       <c r="AB15" t="n">
-        <v>14241</v>
+        <v>130.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>14459</v>
+        <v>130.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>14583</v>
+        <v>131.37</v>
       </c>
       <c r="AE15" t="n">
-        <v>55.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH15" t="n">
         <v>0.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>41.8</v>
+        <v>22.6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21.1</v>
+        <v>10.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.6</v>
+        <v>66.2</v>
       </c>
       <c r="AL15" t="n">
         <v>15</v>
       </c>
       <c r="AM15" t="n">
-        <v>14929.51</v>
+        <v>135.58</v>
       </c>
       <c r="AN15" t="n">
-        <v>13769.3</v>
+        <v>123.42</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹87,159.51 Cr., a P/E ratio of 41.83, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>IEX operates in the Financial Services sector. With an estimated Market Cap of ₹11,537.78 Cr., a P/E ratio of 22.56, and YoY Revenue Growth of +10.1%, the company demonstrates strong institutional backing, solid operating profit margins (66.22%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.30 (Bullish Momentum Zone), while MACD Line (385.37) trades below Signal (458.72) with an expanding histogram (-73.35). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +13.81% above the 200-day DMA (₹12290.57). Daily volatility envelope is bounded by ATR(14) of ₹469.50.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.41 (Bullish Momentum Zone), while MACD Line (2.09) trades above Signal (1.41) with an expanding histogram (+0.68). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.95% above the 200-day DMA (₹127.99). Daily volatility envelope is bounded by ATR(14) of ₹4.36.</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,335.00) is positioned above the 30-day DMA (₹13,362.03), 50-day DMA (₹12,739.88), and 200-day DMA (₹12,290.57). The price distance from 200 DMA is +13.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for IEX. Current Market Price (₹129.74) is positioned above the 30-day DMA (₹124.43), 50-day DMA (₹123.96), and 200-day DMA (₹127.99). The price distance from 200 DMA is +0.95%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>[14335.0, 14445.61, 14556.23, 14666.84, 14777.46, 14888.07]</t>
+          <t>[129.74, 130.13, 130.52, 130.91, 131.3, 131.69]</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[14335.0, 14633.41, 14821.82, 14992.12, 15153.06, 15308.0]</t>
+          <t>[129.74, 131.87, 132.99, 133.93, 134.79, 135.59]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[14335.0, 14304.76, 14357.04, 14422.88, 14495.76, 14573.12]</t>
+          <t>[129.74, 128.82, 128.67, 128.64, 128.68, 128.76]</t>
         </is>
       </c>
     </row>
@@ -2952,159 +2952,159 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17669.68</v>
+        <v>63787.61</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>616.75</v>
+        <v>2117.6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹612.46 - ₹623.19</t>
+          <t>₹2103.93 - ₹2138.11</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>633.92</v>
+        <v>2172.3</v>
       </c>
       <c r="I16" t="n">
-        <v>583.11</v>
+        <v>2028.46</v>
       </c>
       <c r="J16" t="n">
-        <v>550.15</v>
+        <v>1908.05</v>
       </c>
       <c r="K16" t="n">
-        <v>554.14</v>
+        <v>1880.26</v>
       </c>
       <c r="L16" t="n">
-        <v>10.44</v>
+        <v>8.16</v>
       </c>
       <c r="M16" t="n">
-        <v>15.39</v>
+        <v>46.13</v>
       </c>
       <c r="N16" t="n">
-        <v>15.91</v>
+        <v>60.86</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.52</v>
+        <v>-14.73</v>
       </c>
       <c r="P16" t="n">
-        <v>21.46</v>
+        <v>68.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R16" t="n">
-        <v>52.1</v>
+        <v>47.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.08</v>
+        <v>-2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>55</v>
+        <v>51.7</v>
       </c>
       <c r="V16" t="n">
-        <v>4.8</v>
+        <v>6.26</v>
       </c>
       <c r="W16" t="n">
         <v>-0.77</v>
       </c>
       <c r="X16" t="n">
-        <v>591</v>
+        <v>2035.55</v>
       </c>
       <c r="Y16" t="n">
-        <v>605.51</v>
+        <v>2019.52</v>
       </c>
       <c r="Z16" t="n">
-        <v>621.6799999999999</v>
+        <v>2134.54</v>
       </c>
       <c r="AA16" t="n">
-        <v>584.5599999999999</v>
+        <v>2015.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>621.08</v>
+        <v>2105.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>628.16</v>
+        <v>2155.76</v>
       </c>
       <c r="AD16" t="n">
-        <v>639.58</v>
+        <v>2193.93</v>
       </c>
       <c r="AE16" t="n">
-        <v>54.7</v>
+        <v>43.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.06</v>
+        <v>-0</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Low VIX (11.97) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH16" t="n">
         <v>0.15</v>
       </c>
       <c r="AI16" t="n">
-        <v>90</v>
+        <v>35.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-10.1</v>
+        <v>63</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.7</v>
+        <v>36.1</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="AM16" t="n">
-        <v>646.28</v>
+        <v>2193.47</v>
       </c>
       <c r="AN16" t="n">
-        <v>585.86</v>
+        <v>2042.38</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,669.68 Cr., a P/E ratio of 90.04, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,787.61 Cr., a P/E ratio of 35.42, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.70 (Consolidation Zone), while MACD Line (15.39) trades below Signal (15.91) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.44% above the 200-day DMA (₹554.14). Daily volatility envelope is bounded by ATR(14) of ₹21.46.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.71 (Consolidation Zone), while MACD Line (46.13) trades below Signal (60.86) with an expanding histogram (-14.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.16% above the 200-day DMA (₹1880.26). Daily volatility envelope is bounded by ATR(14) of ₹68.37.</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹616.75) is positioned above the 30-day DMA (₹583.11), 50-day DMA (₹550.15), and 200-day DMA (₹554.14). The price distance from 200 DMA is +10.44%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,117.60) is positioned above the 30-day DMA (₹2,028.46), 50-day DMA (₹1,908.05), and 200-day DMA (₹1,880.26). The price distance from 200 DMA is +8.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>[616.75, 618.6, 620.45, 622.3, 624.15, 626.0]</t>
+          <t>[2117.6, 2123.95, 2130.31, 2136.66, 2143.01, 2149.36]</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[616.75, 627.18, 632.59, 637.17, 641.32, 645.2]</t>
+          <t>[2117.6, 2151.3, 2168.98, 2184.03, 2197.71, 2210.52]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[616.75, 612.16, 611.35, 611.15, 611.27, 611.6]</t>
+          <t>[2117.6, 2103.44, 2101.3, 2101.13, 2101.99, 2103.5]</t>
         </is>
       </c>
     </row>
@@ -3116,16 +3116,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63980.39</v>
+        <v>287300.33</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3133,142 +3133,142 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2124</v>
+        <v>312.1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹2110.33 - ₹2144.51</t>
+          <t>₹310.03 - ₹315.21</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2178.7</v>
+        <v>320.38</v>
       </c>
       <c r="I17" t="n">
-        <v>2028.46</v>
+        <v>286.32</v>
       </c>
       <c r="J17" t="n">
-        <v>1908.05</v>
+        <v>272.64</v>
       </c>
       <c r="K17" t="n">
-        <v>1880.26</v>
+        <v>273.39</v>
       </c>
       <c r="L17" t="n">
-        <v>8.16</v>
+        <v>14.27</v>
       </c>
       <c r="M17" t="n">
-        <v>46.13</v>
+        <v>10.44</v>
       </c>
       <c r="N17" t="n">
-        <v>60.86</v>
+        <v>9.26</v>
       </c>
       <c r="O17" t="n">
-        <v>-14.73</v>
+        <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>68.37</v>
+        <v>10.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R17" t="n">
-        <v>47.3</v>
+        <v>45.9</v>
       </c>
       <c r="S17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.17</v>
+        <v>-2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>51.7</v>
+        <v>53.3</v>
       </c>
       <c r="V17" t="n">
-        <v>6.28</v>
+        <v>2.43</v>
       </c>
       <c r="W17" t="n">
         <v>-0.77</v>
       </c>
       <c r="X17" t="n">
-        <v>2041.95</v>
+        <v>307.76</v>
       </c>
       <c r="Y17" t="n">
-        <v>2028.7</v>
+        <v>318.69</v>
       </c>
       <c r="Z17" t="n">
-        <v>2140.99</v>
+        <v>314.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>2021.44</v>
+        <v>296.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>2107.87</v>
+        <v>312.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>2160.04</v>
+        <v>314.04</v>
       </c>
       <c r="AD17" t="n">
-        <v>2196.07</v>
+        <v>315.97</v>
       </c>
       <c r="AE17" t="n">
-        <v>43.7</v>
+        <v>62.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH17" t="n">
         <v>0.15</v>
       </c>
       <c r="AI17" t="n">
-        <v>34.5</v>
+        <v>664</v>
       </c>
       <c r="AJ17" t="n">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="AK17" t="n">
-        <v>36.1</v>
+        <v>0.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AM17" t="n">
-        <v>2204.13</v>
+        <v>323.72</v>
       </c>
       <c r="AN17" t="n">
-        <v>2047.52</v>
+        <v>301.39</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,980.39 Cr., a P/E ratio of 34.54, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹287,300.33 Cr., a P/E ratio of 664.04, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.71 (Consolidation Zone), while MACD Line (46.13) trades below Signal (60.86) with an expanding histogram (-14.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.16% above the 200-day DMA (₹1880.26). Daily volatility envelope is bounded by ATR(14) of ₹68.37.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.17 (Bullish Momentum Zone), while MACD Line (10.44) trades above Signal (9.26) with an expanding histogram (+1.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.27% above the 200-day DMA (₹273.39). Daily volatility envelope is bounded by ATR(14) of ₹10.35.</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,124.00) is positioned above the 30-day DMA (₹2,028.46), 50-day DMA (₹1,908.05), and 200-day DMA (₹1,880.26). The price distance from 200 DMA is +8.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹312.10) is positioned above the 30-day DMA (₹286.32), 50-day DMA (₹272.64), and 200-day DMA (₹273.39). The price distance from 200 DMA is +14.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>[2124.0, 2130.37, 2136.74, 2143.12, 2149.49, 2155.86]</t>
+          <t>[312.1, 313.04, 313.97, 314.91, 315.85, 316.78]</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[2124.0, 2157.72, 2175.42, 2190.49, 2204.19, 2217.02]</t>
+          <t>[312.1, 317.18, 319.83, 322.08, 324.13, 326.04]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[2124.0, 2109.86, 2107.73, 2107.59, 2108.46, 2109.99]</t>
+          <t>[312.1, 309.93, 309.58, 309.53, 309.64, 309.84]</t>
         </is>
       </c>
     </row>
@@ -3280,159 +3280,159 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11608.92</v>
+        <v>17449.08</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>130.54</v>
+        <v>609.05</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹129.67 - ₹131.85</t>
+          <t>₹604.76 - ₹615.49</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>134.03</v>
+        <v>626.22</v>
       </c>
       <c r="I18" t="n">
-        <v>124.43</v>
+        <v>583.11</v>
       </c>
       <c r="J18" t="n">
-        <v>123.96</v>
+        <v>550.15</v>
       </c>
       <c r="K18" t="n">
-        <v>127.99</v>
+        <v>554.14</v>
       </c>
       <c r="L18" t="n">
-        <v>0.95</v>
+        <v>10.44</v>
       </c>
       <c r="M18" t="n">
-        <v>2.09</v>
+        <v>15.39</v>
       </c>
       <c r="N18" t="n">
-        <v>1.41</v>
+        <v>15.91</v>
       </c>
       <c r="O18" t="n">
-        <v>0.68</v>
+        <v>-0.52</v>
       </c>
       <c r="P18" t="n">
-        <v>4.36</v>
+        <v>21.46</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="R18" t="n">
-        <v>48.8</v>
+        <v>47.5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.18</v>
+        <v>-2.39</v>
       </c>
       <c r="U18" t="n">
-        <v>48.3</v>
+        <v>53.3</v>
       </c>
       <c r="V18" t="n">
-        <v>3.63</v>
+        <v>4.79</v>
       </c>
       <c r="W18" t="n">
         <v>-0.77</v>
       </c>
       <c r="X18" t="n">
-        <v>125.97</v>
+        <v>583.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>130.54</v>
+        <v>596.8200000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>131.58</v>
+        <v>613.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>123.99</v>
+        <v>576.86</v>
       </c>
       <c r="AB18" t="n">
-        <v>130.43</v>
+        <v>616.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>131.05</v>
+        <v>625.01</v>
       </c>
       <c r="AD18" t="n">
-        <v>131.57</v>
+        <v>640.98</v>
       </c>
       <c r="AE18" t="n">
-        <v>64.40000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (11.97) | LSTM Deep Net</t>
+          <t>Low VIX (12.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH18" t="n">
         <v>0.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>22.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="AJ18" t="n">
-        <v>10.1</v>
+        <v>-10.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>66.2</v>
+        <v>3.7</v>
       </c>
       <c r="AL18" t="n">
-        <v>15</v>
+        <v>6.7</v>
       </c>
       <c r="AM18" t="n">
-        <v>136.03</v>
+        <v>638.96</v>
       </c>
       <c r="AN18" t="n">
-        <v>124.46</v>
+        <v>578.59</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>IEX operates in the Financial Services sector. With an estimated Market Cap of ₹11,608.92 Cr., a P/E ratio of 22.90, and YoY Revenue Growth of +10.1%, the company demonstrates strong institutional backing, solid operating profit margins (66.22%), and healthy Return on Equity (15.00%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,449.08 Cr., a P/E ratio of 87.89, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.41 (Bullish Momentum Zone), while MACD Line (2.09) trades above Signal (1.41) with an expanding histogram (+0.68). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.95% above the 200-day DMA (₹127.99). Daily volatility envelope is bounded by ATR(14) of ₹4.36.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.70 (Consolidation Zone), while MACD Line (15.39) trades below Signal (15.91) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.44% above the 200-day DMA (₹554.14). Daily volatility envelope is bounded by ATR(14) of ₹21.46.</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for IEX. Current Market Price (₹130.54) is positioned above the 30-day DMA (₹124.43), 50-day DMA (₹123.96), and 200-day DMA (₹127.99). The price distance from 200 DMA is +0.95%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹609.05) is positioned above the 30-day DMA (₹583.11), 50-day DMA (₹550.15), and 200-day DMA (₹554.14). The price distance from 200 DMA is +10.44%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>[130.54, 130.93, 131.32, 131.71, 132.11, 132.5]</t>
+          <t>[609.05, 610.88, 612.7, 614.53, 616.36, 618.19]</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[130.54, 132.68, 133.79, 134.74, 135.6, 136.4]</t>
+          <t>[609.05, 619.46, 624.84, 629.4, 633.53, 637.38]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[130.54, 129.62, 129.47, 129.45, 129.49, 129.57]</t>
+          <t>[609.05, 604.44, 603.6, 603.38, 603.48, 603.79]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>357916.19</v>
+        <v>357416.09</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -673,15 +673,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12167</v>
+        <v>12150</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹12126.59 - ₹12227.61</t>
+          <t>₹12109.59 - ₹12210.61</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12328.62</v>
+        <v>12311.62</v>
       </c>
       <c r="I2" t="n">
         <v>11508.32</v>
@@ -708,10 +708,10 @@
         <v>202.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R2" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="S2" t="n">
         <v>0.32</v>
@@ -729,25 +729,25 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>12073.64</v>
+        <v>12055.35</v>
       </c>
       <c r="Y2" t="n">
-        <v>12470.04</v>
+        <v>12453.04</v>
       </c>
       <c r="Z2" t="n">
-        <v>12264.34</v>
+        <v>12247.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>11863.96</v>
+        <v>11846.96</v>
       </c>
       <c r="AB2" t="n">
-        <v>12125.33</v>
+        <v>12119.67</v>
       </c>
       <c r="AC2" t="n">
-        <v>12280.66</v>
+        <v>12269.34</v>
       </c>
       <c r="AD2" t="n">
-        <v>12394.33</v>
+        <v>12388.67</v>
       </c>
       <c r="AE2" t="n">
         <v>70.40000000000001</v>
@@ -757,14 +757,14 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="AJ2" t="n">
         <v>15.9</v>
@@ -776,14 +776,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>12431.89</v>
+        <v>12425.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>11891.42</v>
+        <v>11882.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹357,916.19 Cr., a P/E ratio of 41.89, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹357,416.09 Cr., a P/E ratio of 41.84, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -793,22 +793,22 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,167.00) is positioned above the 30-day DMA (₹11,508.32), 50-day DMA (₹11,305.61), and 200-day DMA (₹11,570.61). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,150.00) is positioned above the 30-day DMA (₹11,508.32), 50-day DMA (₹11,305.61), and 200-day DMA (₹11,570.61). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[12167.0, 12256.14, 12345.28, 12434.43, 12523.57, 12612.71]</t>
+          <t>[12150.0, 12237.6, 12325.2, 12412.8, 12500.41, 12588.01]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[12167.0, 12336.95, 12459.57, 12574.39, 12685.19, 12793.41]</t>
+          <t>[12150.0, 12318.41, 12439.49, 12552.77, 12662.03, 12768.7]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[12167.0, 12195.53, 12259.57, 12329.45, 12402.35, 12477.19]</t>
+          <t>[12150.0, 12176.99, 12239.49, 12307.83, 12379.19, 12452.48]</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>130674.76</v>
+        <v>130812.67</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -837,15 +837,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>113.7</v>
+        <v>113.82</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹113.31 - ₹114.29</t>
+          <t>₹113.43 - ₹114.41</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>115.26</v>
+        <v>115.38</v>
       </c>
       <c r="I3" t="n">
         <v>108.12</v>
@@ -872,16 +872,16 @@
         <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R3" t="n">
-        <v>49.8</v>
+        <v>49.4</v>
       </c>
       <c r="S3" t="n">
         <v>0.31</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.89</v>
+        <v>-0.91</v>
       </c>
       <c r="U3" t="n">
         <v>55</v>
@@ -893,25 +893,25 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>111.36</v>
+        <v>111.48</v>
       </c>
       <c r="Y3" t="n">
-        <v>114.77</v>
+        <v>114.91</v>
       </c>
       <c r="Z3" t="n">
-        <v>114.61</v>
+        <v>114.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>110.77</v>
+        <v>110.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>114.19</v>
+        <v>114.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>114.71</v>
+        <v>114.82</v>
       </c>
       <c r="AD3" t="n">
-        <v>115.72</v>
+        <v>115.81</v>
       </c>
       <c r="AE3" t="n">
         <v>79</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
@@ -940,14 +940,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>116.75</v>
+        <v>116.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>110.96</v>
+        <v>110.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,674.76 Cr., a P/E ratio of 5.86, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,812.67 Cr., a P/E ratio of 5.87, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -957,22 +957,22 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.70) is positioned above the 30-day DMA (₹108.12), 50-day DMA (₹106.98), and 200-day DMA (₹112.64). The price distance from 200 DMA is +1.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.82) is positioned above the 30-day DMA (₹108.12), 50-day DMA (₹106.98), and 200-day DMA (₹112.64). The price distance from 200 DMA is +1.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[113.7, 114.04, 114.38, 114.72, 115.06, 115.41]</t>
+          <t>[113.82, 114.16, 114.5, 114.84, 115.19, 115.53]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[113.7, 114.82, 115.49, 116.08, 116.63, 117.15]</t>
+          <t>[113.82, 114.94, 115.61, 116.2, 116.75, 117.27]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[113.7, 113.46, 113.55, 113.71, 113.89, 114.1]</t>
+          <t>[113.82, 113.58, 113.67, 113.83, 114.01, 114.22]</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>218629.08</v>
+        <v>219603.63</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1001,15 +1001,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7964</v>
+        <v>7999.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹7932.64 - ₹8011.04</t>
+          <t>₹7968.14 - ₹8046.54</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8089.45</v>
+        <v>8124.95</v>
       </c>
       <c r="I4" t="n">
         <v>7478.7</v>
@@ -1036,46 +1036,46 @@
         <v>156.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R4" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="S4" t="n">
         <v>0.27</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.02</v>
+        <v>-1.01</v>
       </c>
       <c r="U4" t="n">
         <v>51.7</v>
       </c>
       <c r="V4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>7838.88</v>
+        <v>7877.72</v>
       </c>
       <c r="Y4" t="n">
-        <v>8117.62</v>
+        <v>8157.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>8027.71</v>
+        <v>8063.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>7728.78</v>
+        <v>7764.28</v>
       </c>
       <c r="AB4" t="n">
-        <v>7954.83</v>
+        <v>7968.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>8004.16</v>
+        <v>8030.84</v>
       </c>
       <c r="AD4" t="n">
-        <v>8044.33</v>
+        <v>8062.17</v>
       </c>
       <c r="AE4" t="n">
         <v>74.3</v>
@@ -1085,14 +1085,14 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="AJ4" t="n">
         <v>31.5</v>
@@ -1104,14 +1104,14 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>8191.7</v>
+        <v>8209.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>7776.28</v>
+        <v>7811.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹218,629.08 Cr., a P/E ratio of 38.45, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹219,603.63 Cr., a P/E ratio of 38.63, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1121,22 +1121,22 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,964.00) is positioned above the 30-day DMA (₹7,478.70), 50-day DMA (₹7,389.91), and 200-day DMA (₹7,187.90). The price distance from 200 DMA is +10.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,999.50) is positioned above the 30-day DMA (₹7,478.70), 50-day DMA (₹7,389.91), and 200-day DMA (₹7,187.90). The price distance from 200 DMA is +10.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[7964.0, 7987.89, 8011.78, 8035.68, 8059.57, 8083.46]</t>
+          <t>[7999.5, 8023.5, 8047.5, 8071.5, 8095.49, 8119.49]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[7964.0, 8050.62, 8100.49, 8144.32, 8185.02, 8223.72]</t>
+          <t>[7999.5, 8086.22, 8136.2, 8180.14, 8220.94, 8259.75]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[7964.0, 7940.85, 7945.25, 7954.19, 7965.48, 7978.27]</t>
+          <t>[7999.5, 7976.46, 7980.97, 7990.01, 8001.41, 8014.3]</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>308592.82</v>
+        <v>309201.42</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1165,15 +1165,15 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4614.3</v>
+        <v>4623.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹4598.26 - ₹4638.36</t>
+          <t>₹4607.36 - ₹4647.46</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4678.45</v>
+        <v>4687.55</v>
       </c>
       <c r="I5" t="n">
         <v>4490.17</v>
@@ -1200,16 +1200,16 @@
         <v>80.19</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R5" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="S5" t="n">
         <v>0.31</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.22</v>
+        <v>-1.21</v>
       </c>
       <c r="U5" t="n">
         <v>41.7</v>
@@ -1221,25 +1221,25 @@
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>4518.08</v>
+        <v>4527.18</v>
       </c>
       <c r="Y5" t="n">
-        <v>4652.81</v>
+        <v>4662.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>4651.21</v>
+        <v>4660.39</v>
       </c>
       <c r="AA5" t="n">
-        <v>4494.02</v>
+        <v>4503.12</v>
       </c>
       <c r="AB5" t="n">
-        <v>4630.33</v>
+        <v>4633.37</v>
       </c>
       <c r="AC5" t="n">
-        <v>4657.36</v>
+        <v>4663.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>4700.43</v>
+        <v>4703.47</v>
       </c>
       <c r="AE5" t="n">
         <v>72.8</v>
@@ -1249,14 +1249,14 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.8</v>
@@ -1268,14 +1268,14 @@
         <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>4738.23</v>
+        <v>4748.28</v>
       </c>
       <c r="AN5" t="n">
-        <v>4490.62</v>
+        <v>4505.04</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹308,592.82 Cr., a P/E ratio of 33.89, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹309,201.42 Cr., a P/E ratio of 33.96, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,614.30) is positioned above the 30-day DMA (₹4,490.17), 50-day DMA (₹4,419.22), and 200-day DMA (₹4,344.79). The price distance from 200 DMA is +6.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,623.40) is positioned above the 30-day DMA (₹4,490.17), 50-day DMA (₹4,419.22), and 200-day DMA (₹4,344.79). The price distance from 200 DMA is +6.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[4614.3, 4628.14, 4641.99, 4655.83, 4669.67, 4683.51]</t>
+          <t>[4623.4, 4637.27, 4651.14, 4665.01, 4678.88, 4692.75]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[4614.3, 4660.22, 4687.35, 4711.38, 4733.82, 4755.23]</t>
+          <t>[4623.4, 4669.34, 4696.5, 4720.56, 4743.03, 4764.47]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[4614.3, 4604.09, 4607.97, 4614.16, 4621.56, 4629.72]</t>
+          <t>[4623.4, 4613.21, 4617.12, 4623.34, 4630.77, 4638.96]</t>
         </is>
       </c>
     </row>
@@ -1312,159 +1312,159 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67434.66</v>
+        <v>264394.09</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5640</v>
+        <v>2758</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹5616.66 - ₹5675.0</t>
+          <t>₹2746.15 - ₹2775.77</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5733.34</v>
+        <v>2805.39</v>
       </c>
       <c r="I6" t="n">
-        <v>5598.93</v>
+        <v>2698.21</v>
       </c>
       <c r="J6" t="n">
-        <v>5497.15</v>
+        <v>2687.88</v>
       </c>
       <c r="K6" t="n">
-        <v>5524.06</v>
+        <v>2577.55</v>
       </c>
       <c r="L6" t="n">
-        <v>3.31</v>
+        <v>7.66</v>
       </c>
       <c r="M6" t="n">
-        <v>58.81</v>
+        <v>26.47</v>
       </c>
       <c r="N6" t="n">
-        <v>54.69</v>
+        <v>16.72</v>
       </c>
       <c r="O6" t="n">
-        <v>4.12</v>
+        <v>9.76</v>
       </c>
       <c r="P6" t="n">
-        <v>116.68</v>
+        <v>59.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R6" t="n">
-        <v>46.7</v>
+        <v>48.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="T6" t="n">
         <v>-1.28</v>
       </c>
       <c r="U6" t="n">
-        <v>51.7</v>
+        <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>2.81</v>
+        <v>1.78</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>5499.99</v>
+        <v>2686.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>5606.19</v>
+        <v>2779.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>5685.12</v>
+        <v>2780.06</v>
       </c>
       <c r="AA6" t="n">
-        <v>5464.98</v>
+        <v>2669.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>5620.5</v>
+        <v>2764.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>5685</v>
+        <v>2780.44</v>
       </c>
       <c r="AD6" t="n">
-        <v>5730</v>
+        <v>2802.87</v>
       </c>
       <c r="AE6" t="n">
-        <v>56.2</v>
+        <v>67</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>29.3</v>
+        <v>56.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.6</v>
+        <v>17.9</v>
       </c>
       <c r="AK6" t="n">
-        <v>15.6</v>
+        <v>12.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>5768.09</v>
+        <v>2821.79</v>
       </c>
       <c r="AN6" t="n">
-        <v>5520.18</v>
+        <v>2696.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,434.66 Cr., a P/E ratio of 29.27, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹264,394.09 Cr., a P/E ratio of 56.15, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.20 (Bullish Momentum Zone), while MACD Line (58.81) trades above Signal (54.69) with an expanding histogram (+4.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.31% above the 200-day DMA (₹5524.06). Daily volatility envelope is bounded by ATR(14) of ₹116.68.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.98 (Bullish Momentum Zone), while MACD Line (26.47) trades above Signal (16.72) with an expanding histogram (+9.76). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.66% above the 200-day DMA (₹2577.55). Daily volatility envelope is bounded by ATR(14) of ₹59.24.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,640.00) is positioned above the 30-day DMA (₹5,598.93), 50-day DMA (₹5,497.15), and 200-day DMA (₹5,524.06). The price distance from 200 DMA is +3.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,758.00) is positioned above the 30-day DMA (₹2,698.21), 50-day DMA (₹2,687.88), and 200-day DMA (₹2,577.55). The price distance from 200 DMA is +7.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[5640.0, 5656.92, 5673.84, 5690.76, 5707.68, 5724.6]</t>
+          <t>[2758.0, 2766.27, 2774.55, 2782.82, 2791.1, 2799.37]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[5640.0, 5703.59, 5739.84, 5771.6, 5801.02, 5828.96]</t>
+          <t>[2758.0, 2789.97, 2808.06, 2823.86, 2838.48, 2852.35]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[5640.0, 5621.92, 5624.34, 5630.13, 5637.67, 5646.33]</t>
+          <t>[2758.0, 2748.5, 2749.42, 2752.04, 2755.55, 2759.63]</t>
         </is>
       </c>
     </row>
@@ -1476,16 +1476,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>264844.66</v>
+        <v>67315.09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1493,142 +1493,142 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2762.3</v>
+        <v>5629</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹2750.45 - ₹2780.07</t>
+          <t>₹5605.66 - ₹5664.0</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2809.69</v>
+        <v>5722.34</v>
       </c>
       <c r="I7" t="n">
-        <v>2698.21</v>
+        <v>5598.93</v>
       </c>
       <c r="J7" t="n">
-        <v>2687.88</v>
+        <v>5497.15</v>
       </c>
       <c r="K7" t="n">
-        <v>2577.55</v>
+        <v>5524.06</v>
       </c>
       <c r="L7" t="n">
-        <v>7.66</v>
+        <v>3.31</v>
       </c>
       <c r="M7" t="n">
-        <v>26.47</v>
+        <v>58.81</v>
       </c>
       <c r="N7" t="n">
-        <v>16.72</v>
+        <v>54.69</v>
       </c>
       <c r="O7" t="n">
-        <v>9.76</v>
+        <v>4.12</v>
       </c>
       <c r="P7" t="n">
-        <v>59.24</v>
+        <v>116.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R7" t="n">
-        <v>47.9</v>
+        <v>46.7</v>
       </c>
       <c r="S7" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.29</v>
+        <v>-1.28</v>
       </c>
       <c r="U7" t="n">
-        <v>55</v>
+        <v>51.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.78</v>
+        <v>2.82</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2691.22</v>
+        <v>5488.99</v>
       </c>
       <c r="Y7" t="n">
-        <v>2784.35</v>
+        <v>5594.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>2784.4</v>
+        <v>5674.03</v>
       </c>
       <c r="AA7" t="n">
-        <v>2673.45</v>
+        <v>5453.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>2766</v>
+        <v>5616.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>2783.3</v>
+        <v>5677.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>2804.3</v>
+        <v>5726.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>67</v>
+        <v>56.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>56.2</v>
+        <v>29.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17.9</v>
+        <v>14.6</v>
       </c>
       <c r="AK7" t="n">
-        <v>12.8</v>
+        <v>15.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="AM7" t="n">
-        <v>2824.01</v>
+        <v>5748.52</v>
       </c>
       <c r="AN7" t="n">
-        <v>2699.84</v>
+        <v>5495.23</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹264,844.66 Cr., a P/E ratio of 56.24, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,315.09 Cr., a P/E ratio of 29.22, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.98 (Bullish Momentum Zone), while MACD Line (26.47) trades above Signal (16.72) with an expanding histogram (+9.76). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.66% above the 200-day DMA (₹2577.55). Daily volatility envelope is bounded by ATR(14) of ₹59.24.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.20 (Bullish Momentum Zone), while MACD Line (58.81) trades above Signal (54.69) with an expanding histogram (+4.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.31% above the 200-day DMA (₹5524.06). Daily volatility envelope is bounded by ATR(14) of ₹116.68.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,762.30) is positioned above the 30-day DMA (₹2,698.21), 50-day DMA (₹2,687.88), and 200-day DMA (₹2,577.55). The price distance from 200 DMA is +7.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,629.00) is positioned above the 30-day DMA (₹5,598.93), 50-day DMA (₹5,497.15), and 200-day DMA (₹5,524.06). The price distance from 200 DMA is +3.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[2762.3, 2770.59, 2778.87, 2787.16, 2795.45, 2803.73]</t>
+          <t>[5629.0, 5645.89, 5662.77, 5679.66, 5696.55, 5713.43]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2762.3, 2794.28, 2812.38, 2828.2, 2842.84, 2856.72]</t>
+          <t>[5629.0, 5692.56, 5728.78, 5760.5, 5789.89, 5817.8]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2762.3, 2752.82, 2753.74, 2756.38, 2759.91, 2764.0]</t>
+          <t>[5629.0, 5610.88, 5613.27, 5619.03, 5626.54, 5635.16]</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105547.5</v>
+        <v>105590.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1657,15 +1657,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>741.1</v>
+        <v>741.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹738.11 - ₹745.59</t>
+          <t>₹738.81 - ₹746.29</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>753.08</v>
+        <v>753.78</v>
       </c>
       <c r="I8" t="n">
         <v>731.6799999999999</v>
@@ -1692,7 +1692,7 @@
         <v>14.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R8" t="n">
         <v>43.9</v>
@@ -1713,25 +1713,25 @@
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>723.13</v>
+        <v>723.83</v>
       </c>
       <c r="Y8" t="n">
-        <v>734</v>
+        <v>735.01</v>
       </c>
       <c r="Z8" t="n">
-        <v>747.03</v>
+        <v>747.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>718.64</v>
+        <v>719.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>744.78</v>
+        <v>745</v>
       </c>
       <c r="AC8" t="n">
-        <v>749.21</v>
+        <v>749.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>757.33</v>
+        <v>757.6</v>
       </c>
       <c r="AE8" t="n">
         <v>54.1</v>
@@ -1741,14 +1741,14 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="AJ8" t="n">
         <v>15.1</v>
@@ -1760,14 +1760,14 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>760.01</v>
+        <v>758.53</v>
       </c>
       <c r="AN8" t="n">
-        <v>721.91</v>
+        <v>725.13</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,547.50 Cr., a P/E ratio of 49.43, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,590.20 Cr., a P/E ratio of 49.45, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1777,22 +1777,22 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.10) is positioned above the 30-day DMA (₹731.68), 50-day DMA (₹709.25), and 200-day DMA (₹686.46). The price distance from 200 DMA is +9.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.80) is positioned above the 30-day DMA (₹731.68), 50-day DMA (₹709.25), and 200-day DMA (₹686.46). The price distance from 200 DMA is +9.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[741.1, 743.32, 745.55, 747.77, 749.99, 752.22]</t>
+          <t>[741.8, 744.03, 746.25, 748.48, 750.7, 752.93]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[741.1, 749.31, 754.02, 758.14, 761.97, 765.61]</t>
+          <t>[741.8, 750.01, 754.72, 758.85, 762.68, 766.32]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[741.1, 738.83, 739.19, 739.99, 741.01, 742.17]</t>
+          <t>[741.8, 739.53, 739.9, 740.7, 741.72, 742.88]</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25000</v>
+        <v>96086.34</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1821,15 +1821,15 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>366.3</v>
+        <v>364.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹364.73 - ₹368.65</t>
+          <t>₹363.33 - ₹367.25</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>372.56</v>
+        <v>371.16</v>
       </c>
       <c r="I9" t="n">
         <v>358.01</v>
@@ -1856,10 +1856,10 @@
         <v>7.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R9" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="S9" t="n">
         <v>0.25</v>
@@ -1877,25 +1877,25 @@
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>358.35</v>
+        <v>356.89</v>
       </c>
       <c r="Y9" t="n">
-        <v>371.17</v>
+        <v>369.66</v>
       </c>
       <c r="Z9" t="n">
-        <v>369.23</v>
+        <v>367.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>354.56</v>
+        <v>353.16</v>
       </c>
       <c r="AB9" t="n">
-        <v>368.02</v>
+        <v>367.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>370.59</v>
+        <v>370.04</v>
       </c>
       <c r="AD9" t="n">
-        <v>374.87</v>
+        <v>375.17</v>
       </c>
       <c r="AE9" t="n">
         <v>71.8</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
@@ -1924,14 +1924,14 @@
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>375.26</v>
+        <v>374.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>356.96</v>
+        <v>355.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 6.03, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹96,086.34 Cr., a P/E ratio of 6.00, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1941,22 +1941,22 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹366.30) is positioned above the 30-day DMA (₹358.01), 50-day DMA (₹351.17), and 200-day DMA (₹347.72). The price distance from 200 DMA is +5.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹364.90) is positioned above the 30-day DMA (₹358.01), 50-day DMA (₹351.17), and 200-day DMA (₹347.72). The price distance from 200 DMA is +5.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[366.3, 367.4, 368.5, 369.6, 370.7, 371.79]</t>
+          <t>[364.9, 365.99, 367.09, 368.18, 369.28, 370.37]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[366.3, 370.53, 372.92, 375.02, 376.96, 378.79]</t>
+          <t>[364.9, 369.12, 371.52, 373.61, 375.54, 377.37]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[366.3, 365.05, 365.18, 365.53, 366.0, 366.55]</t>
+          <t>[364.9, 363.65, 363.77, 364.12, 364.58, 365.12]</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>116839.81</v>
+        <v>117502.25</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1985,15 +1985,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1446.3</v>
+        <v>1454</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹1439.47 - ₹1456.54</t>
+          <t>₹1447.17 - ₹1464.24</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1473.61</v>
+        <v>1481.31</v>
       </c>
       <c r="I10" t="n">
         <v>1443.04</v>
@@ -2020,46 +2020,46 @@
         <v>34.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R10" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="S10" t="n">
         <v>0.23</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.72</v>
+        <v>-1.71</v>
       </c>
       <c r="U10" t="n">
         <v>45</v>
       </c>
       <c r="V10" t="n">
-        <v>12.13</v>
+        <v>12.14</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>1405.33</v>
+        <v>1413.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1407.39</v>
+        <v>1416.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>1457.87</v>
+        <v>1465.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>1395.09</v>
+        <v>1402.79</v>
       </c>
       <c r="AB10" t="n">
-        <v>1449.93</v>
+        <v>1452.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1456.36</v>
+        <v>1461.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1466.43</v>
+        <v>1469</v>
       </c>
       <c r="AE10" t="n">
         <v>55.4</v>
@@ -2069,14 +2069,14 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="AJ10" t="n">
         <v>3.5</v>
@@ -2088,14 +2088,14 @@
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>1477.31</v>
+        <v>1488.11</v>
       </c>
       <c r="AN10" t="n">
-        <v>1416.76</v>
+        <v>1423.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹116,839.81 Cr., a P/E ratio of 35.00, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,502.25 Cr., a P/E ratio of 35.20, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2105,22 +2105,22 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,446.30) is positioned above the 30-day DMA (₹1,443.04), 50-day DMA (₹1,419.16), and 200-day DMA (₹1,394.98). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,454.00) is positioned above the 30-day DMA (₹1,443.04), 50-day DMA (₹1,419.16), and 200-day DMA (₹1,394.98). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[1446.3, 1450.64, 1454.98, 1459.32, 1463.66, 1467.99]</t>
+          <t>[1454.0, 1458.36, 1462.72, 1467.09, 1471.45, 1475.81]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[1446.3, 1464.3, 1474.29, 1482.97, 1490.97, 1498.53]</t>
+          <t>[1454.0, 1472.02, 1482.04, 1490.74, 1498.76, 1506.35]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[1446.3, 1440.4, 1440.49, 1441.58, 1443.17, 1445.09]</t>
+          <t>[1454.0, 1448.12, 1448.24, 1449.34, 1450.96, 1452.91]</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>147059.82</v>
+        <v>146705.48</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2149,15 +2149,15 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1660.1</v>
+        <v>1656.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹1650.99 - ₹1673.77</t>
+          <t>₹1647.09 - ₹1669.87</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1696.56</v>
+        <v>1692.66</v>
       </c>
       <c r="I11" t="n">
         <v>1496.08</v>
@@ -2184,10 +2184,10 @@
         <v>45.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R11" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
         <v>0.19</v>
@@ -2199,31 +2199,31 @@
         <v>50</v>
       </c>
       <c r="V11" t="n">
-        <v>7.95</v>
+        <v>7.94</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>1631.55</v>
+        <v>1627.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>1689.65</v>
+        <v>1685.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>1673.38</v>
+        <v>1669.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1591.74</v>
+        <v>1587.84</v>
       </c>
       <c r="AB11" t="n">
-        <v>1657.53</v>
+        <v>1656.23</v>
       </c>
       <c r="AC11" t="n">
-        <v>1667.36</v>
+        <v>1664.76</v>
       </c>
       <c r="AD11" t="n">
-        <v>1674.63</v>
+        <v>1673.33</v>
       </c>
       <c r="AE11" t="n">
         <v>83.5</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
@@ -2252,14 +2252,14 @@
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>1703.43</v>
+        <v>1704.65</v>
       </c>
       <c r="AN11" t="n">
-        <v>1615.17</v>
+        <v>1613.8</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹147,059.82 Cr., a P/E ratio of 28.72, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,705.48 Cr., a P/E ratio of 28.65, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2269,22 +2269,22 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,660.10) is positioned above the 30-day DMA (₹1,496.08), 50-day DMA (₹1,470.74), and 200-day DMA (₹1,461.21). The price distance from 200 DMA is +12.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,656.20) is positioned above the 30-day DMA (₹1,496.08), 50-day DMA (₹1,470.74), and 200-day DMA (₹1,461.21). The price distance from 200 DMA is +12.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[1660.1, 1665.08, 1670.06, 1675.04, 1680.02, 1685.0]</t>
+          <t>[1656.2, 1661.17, 1666.14, 1671.11, 1676.07, 1681.04]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[1660.1, 1683.31, 1695.84, 1706.61, 1716.48, 1725.76]</t>
+          <t>[1656.2, 1679.4, 1691.92, 1702.68, 1712.53, 1721.8]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[1660.1, 1651.41, 1650.73, 1651.36, 1652.68, 1654.43]</t>
+          <t>[1656.2, 1647.5, 1646.8, 1647.43, 1648.73, 1650.47]</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>78803.39</v>
+        <v>78675.00999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2313,15 +2313,15 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1780.1</v>
+        <v>1777.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹1768.46 - ₹1797.56</t>
+          <t>₹1765.86 - ₹1794.96</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1826.65</v>
+        <v>1824.05</v>
       </c>
       <c r="I12" t="n">
         <v>1530.06</v>
@@ -2348,16 +2348,16 @@
         <v>58.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R12" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="S12" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.79</v>
+        <v>-1.84</v>
       </c>
       <c r="U12" t="n">
         <v>50</v>
@@ -2369,25 +2369,25 @@
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>1778.84</v>
+        <v>1775.22</v>
       </c>
       <c r="Y12" t="n">
-        <v>1841.15</v>
+        <v>1837.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>1805.55</v>
+        <v>1801.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>1692.81</v>
+        <v>1690.21</v>
       </c>
       <c r="AB12" t="n">
-        <v>1771.07</v>
+        <v>1770.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1797.04</v>
+        <v>1795.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1813.97</v>
+        <v>1813.1</v>
       </c>
       <c r="AE12" t="n">
         <v>72.90000000000001</v>
@@ -2397,14 +2397,14 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH12" t="n">
         <v>0.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="AJ12" t="n">
         <v>49.9</v>
@@ -2416,14 +2416,14 @@
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>1852.95</v>
+        <v>1843.54</v>
       </c>
       <c r="AN12" t="n">
-        <v>1713.15</v>
+        <v>1711.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹78,803.39 Cr., a P/E ratio of 36.86, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹78,675.01 Cr., a P/E ratio of 36.80, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2433,22 +2433,22 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,780.10) is positioned above the 30-day DMA (₹1,530.06), 50-day DMA (₹1,489.66), and 200-day DMA (₹1,504.99). The price distance from 200 DMA is +16.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,777.50) is positioned above the 30-day DMA (₹1,530.06), 50-day DMA (₹1,489.66), and 200-day DMA (₹1,504.99). The price distance from 200 DMA is +16.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[1780.1, 1805.55, 1830.99, 1856.44, 1881.89, 1907.33]</t>
+          <t>[1777.5, 1801.88, 1826.26, 1850.64, 1875.02, 1899.4]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1780.1, 1828.82, 1863.91, 1896.76, 1928.44, 1959.38]</t>
+          <t>[1777.5, 1825.16, 1859.18, 1890.96, 1921.58, 1951.45]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1780.1, 1788.09, 1806.3, 1826.2, 1846.97, 1868.29]</t>
+          <t>[1777.5, 1784.42, 1801.57, 1820.4, 1840.1, 1860.36]</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48334.37</v>
+        <v>48533.74</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2477,15 +2477,15 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1187.9</v>
+        <v>1192.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1181.11 - ₹1198.08</t>
+          <t>₹1186.01 - ₹1202.98</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1215.05</v>
+        <v>1219.95</v>
       </c>
       <c r="I13" t="n">
         <v>1109.52</v>
@@ -2512,46 +2512,46 @@
         <v>33.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R13" t="n">
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
       <c r="S13" t="n">
         <v>0.19</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.86</v>
+        <v>-1.87</v>
       </c>
       <c r="U13" t="n">
         <v>50</v>
       </c>
       <c r="V13" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="W13" t="n">
         <v>-0.77</v>
       </c>
       <c r="X13" t="n">
-        <v>1170.2</v>
+        <v>1176.91</v>
       </c>
       <c r="Y13" t="n">
-        <v>1211.78</v>
+        <v>1218.66</v>
       </c>
       <c r="Z13" t="n">
-        <v>1197.4</v>
+        <v>1202.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>1137</v>
+        <v>1141.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1180.73</v>
+        <v>1183.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>1198.16</v>
+        <v>1203.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1208.43</v>
+        <v>1215</v>
       </c>
       <c r="AE13" t="n">
         <v>60.6</v>
@@ -2561,14 +2561,14 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH13" t="n">
         <v>0.15</v>
       </c>
       <c r="AI13" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="AJ13" t="n">
         <v>29.9</v>
@@ -2580,14 +2580,14 @@
         <v>15</v>
       </c>
       <c r="AM13" t="n">
-        <v>1224.16</v>
+        <v>1228.87</v>
       </c>
       <c r="AN13" t="n">
-        <v>1151.08</v>
+        <v>1158.42</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹48,334.37 Cr., a P/E ratio of 39.48, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹48,533.74 Cr., a P/E ratio of 39.64, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2597,22 +2597,22 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,187.90) is positioned above the 30-day DMA (₹1,109.52), 50-day DMA (₹1,105.91), and 200-day DMA (₹1,100.89). The price distance from 200 DMA is +4.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,192.80) is positioned above the 30-day DMA (₹1,109.52), 50-day DMA (₹1,105.91), and 200-day DMA (₹1,100.89). The price distance from 200 DMA is +4.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>[1187.9, 1191.46, 1195.03, 1198.59, 1202.15, 1205.72]</t>
+          <t>[1192.8, 1196.38, 1199.96, 1203.54, 1207.11, 1210.69]</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1187.9, 1205.04, 1214.22, 1222.1, 1229.3, 1236.07]</t>
+          <t>[1192.8, 1209.95, 1219.15, 1227.05, 1234.26, 1241.05]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1187.9, 1181.28, 1180.63, 1180.96, 1181.79, 1182.95]</t>
+          <t>[1192.8, 1186.2, 1185.56, 1185.9, 1186.75, 1187.93]</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>87098.71000000001</v>
+        <v>86916.31</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2641,15 +2641,15 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14325</v>
+        <v>14295</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹14231.1 - ₹14465.85</t>
+          <t>₹14201.1 - ₹14435.85</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>14700.6</v>
+        <v>14670.6</v>
       </c>
       <c r="I14" t="n">
         <v>13362.03</v>
@@ -2676,46 +2676,46 @@
         <v>469.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R14" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="S14" t="n">
         <v>0.16</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.09</v>
+        <v>-2.08</v>
       </c>
       <c r="U14" t="n">
         <v>48.3</v>
       </c>
       <c r="V14" t="n">
-        <v>6.4</v>
+        <v>6.39</v>
       </c>
       <c r="W14" t="n">
         <v>-0.77</v>
       </c>
       <c r="X14" t="n">
-        <v>14218.88</v>
+        <v>14185.38</v>
       </c>
       <c r="Y14" t="n">
-        <v>14720.25</v>
+        <v>14685.71</v>
       </c>
       <c r="Z14" t="n">
-        <v>14439.6</v>
+        <v>14409.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>13620.75</v>
+        <v>13590.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>14238.33</v>
+        <v>14228.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>14453.66</v>
+        <v>14433.66</v>
       </c>
       <c r="AD14" t="n">
-        <v>14582.33</v>
+        <v>14572.33</v>
       </c>
       <c r="AE14" t="n">
         <v>55.3</v>
@@ -2725,14 +2725,14 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH14" t="n">
         <v>0.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="AJ14" t="n">
         <v>21.1</v>
@@ -2744,14 +2744,14 @@
         <v>15</v>
       </c>
       <c r="AM14" t="n">
-        <v>14823.15</v>
+        <v>14815.95</v>
       </c>
       <c r="AN14" t="n">
-        <v>13781.84</v>
+        <v>13766.25</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹87,098.71 Cr., a P/E ratio of 41.96, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹86,916.31 Cr., a P/E ratio of 41.87, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -2761,22 +2761,22 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,325.00) is positioned above the 30-day DMA (₹13,362.03), 50-day DMA (₹12,739.88), and 200-day DMA (₹12,290.57). The price distance from 200 DMA is +13.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,295.00) is positioned above the 30-day DMA (₹13,362.03), 50-day DMA (₹12,739.88), and 200-day DMA (₹12,290.57). The price distance from 200 DMA is +13.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>[14325.0, 14433.75, 14542.5, 14651.25, 14760.01, 14868.76]</t>
+          <t>[14295.0, 14399.81, 14504.61, 14609.42, 14714.23, 14819.03]</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[14325.0, 14621.55, 14808.09, 14976.53, 15135.61, 15288.69]</t>
+          <t>[14295.0, 14587.61, 14770.2, 14934.7, 15089.83, 15238.97]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[14325.0, 14292.9, 14343.31, 14407.3, 14478.31, 14553.81]</t>
+          <t>[14295.0, 14258.96, 14305.42, 14365.46, 14432.53, 14504.08]</t>
         </is>
       </c>
     </row>
@@ -2788,159 +2788,159 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11537.78</v>
+        <v>63739.41</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>129.74</v>
+        <v>2116</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹128.87 - ₹131.05</t>
+          <t>₹2102.33 - ₹2136.51</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>133.23</v>
+        <v>2170.7</v>
       </c>
       <c r="I15" t="n">
-        <v>124.43</v>
+        <v>2028.46</v>
       </c>
       <c r="J15" t="n">
-        <v>123.96</v>
+        <v>1908.05</v>
       </c>
       <c r="K15" t="n">
-        <v>127.99</v>
+        <v>1880.26</v>
       </c>
       <c r="L15" t="n">
-        <v>0.95</v>
+        <v>8.16</v>
       </c>
       <c r="M15" t="n">
-        <v>2.09</v>
+        <v>46.13</v>
       </c>
       <c r="N15" t="n">
-        <v>1.41</v>
+        <v>60.86</v>
       </c>
       <c r="O15" t="n">
-        <v>0.68</v>
+        <v>-14.73</v>
       </c>
       <c r="P15" t="n">
-        <v>4.36</v>
+        <v>68.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R15" t="n">
-        <v>49</v>
+        <v>47.5</v>
       </c>
       <c r="S15" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.18</v>
+        <v>-2.16</v>
       </c>
       <c r="U15" t="n">
-        <v>48.3</v>
+        <v>51.7</v>
       </c>
       <c r="V15" t="n">
-        <v>3.62</v>
+        <v>6.25</v>
       </c>
       <c r="W15" t="n">
         <v>-0.77</v>
       </c>
       <c r="X15" t="n">
-        <v>125.13</v>
+        <v>2033.95</v>
       </c>
       <c r="Y15" t="n">
-        <v>129.67</v>
+        <v>2017.79</v>
       </c>
       <c r="Z15" t="n">
-        <v>130.78</v>
+        <v>2132.93</v>
       </c>
       <c r="AA15" t="n">
-        <v>123.19</v>
+        <v>2013.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>130.13</v>
+        <v>2105.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>130.55</v>
+        <v>2154.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>131.37</v>
+        <v>2193.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>64.40000000000001</v>
+        <v>43.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH15" t="n">
         <v>0.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>22.6</v>
+        <v>35.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10.1</v>
+        <v>63</v>
       </c>
       <c r="AK15" t="n">
-        <v>66.2</v>
+        <v>36.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AM15" t="n">
-        <v>135.58</v>
+        <v>2193.96</v>
       </c>
       <c r="AN15" t="n">
-        <v>123.42</v>
+        <v>2046.54</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>IEX operates in the Financial Services sector. With an estimated Market Cap of ₹11,537.78 Cr., a P/E ratio of 22.56, and YoY Revenue Growth of +10.1%, the company demonstrates strong institutional backing, solid operating profit margins (66.22%), and healthy Return on Equity (15.00%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,739.41 Cr., a P/E ratio of 35.39, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.41 (Bullish Momentum Zone), while MACD Line (2.09) trades above Signal (1.41) with an expanding histogram (+0.68). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.95% above the 200-day DMA (₹127.99). Daily volatility envelope is bounded by ATR(14) of ₹4.36.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.71 (Consolidation Zone), while MACD Line (46.13) trades below Signal (60.86) with an expanding histogram (-14.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.16% above the 200-day DMA (₹1880.26). Daily volatility envelope is bounded by ATR(14) of ₹68.37.</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for IEX. Current Market Price (₹129.74) is positioned above the 30-day DMA (₹124.43), 50-day DMA (₹123.96), and 200-day DMA (₹127.99). The price distance from 200 DMA is +0.95%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,116.00) is positioned above the 30-day DMA (₹2,028.46), 50-day DMA (₹1,908.05), and 200-day DMA (₹1,880.26). The price distance from 200 DMA is +8.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>[129.74, 130.13, 130.52, 130.91, 131.3, 131.69]</t>
+          <t>[2116.0, 2122.35, 2128.7, 2135.04, 2141.39, 2147.74]</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[129.74, 131.87, 132.99, 133.93, 134.79, 135.59]</t>
+          <t>[2116.0, 2149.7, 2167.37, 2182.42, 2196.09, 2208.9]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[129.74, 128.82, 128.67, 128.64, 128.68, 128.76]</t>
+          <t>[2116.0, 2101.84, 2099.69, 2099.52, 2100.37, 2101.87]</t>
         </is>
       </c>
     </row>
@@ -2952,159 +2952,159 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>63787.61</v>
+        <v>11527.11</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2117.6</v>
+        <v>129.62</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹2103.93 - ₹2138.11</t>
+          <t>₹128.75 - ₹130.93</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2172.3</v>
+        <v>133.11</v>
       </c>
       <c r="I16" t="n">
-        <v>2028.46</v>
+        <v>124.43</v>
       </c>
       <c r="J16" t="n">
-        <v>1908.05</v>
+        <v>123.96</v>
       </c>
       <c r="K16" t="n">
-        <v>1880.26</v>
+        <v>127.99</v>
       </c>
       <c r="L16" t="n">
-        <v>8.16</v>
+        <v>0.95</v>
       </c>
       <c r="M16" t="n">
-        <v>46.13</v>
+        <v>2.09</v>
       </c>
       <c r="N16" t="n">
-        <v>60.86</v>
+        <v>1.41</v>
       </c>
       <c r="O16" t="n">
-        <v>-14.73</v>
+        <v>0.68</v>
       </c>
       <c r="P16" t="n">
-        <v>68.37</v>
+        <v>4.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R16" t="n">
-        <v>47.2</v>
+        <v>49.1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="T16" t="n">
         <v>-2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>51.7</v>
+        <v>48.3</v>
       </c>
       <c r="V16" t="n">
-        <v>6.26</v>
+        <v>3.62</v>
       </c>
       <c r="W16" t="n">
         <v>-0.77</v>
       </c>
       <c r="X16" t="n">
-        <v>2035.55</v>
+        <v>125</v>
       </c>
       <c r="Y16" t="n">
-        <v>2019.52</v>
+        <v>129.54</v>
       </c>
       <c r="Z16" t="n">
-        <v>2134.54</v>
+        <v>130.66</v>
       </c>
       <c r="AA16" t="n">
-        <v>2015.04</v>
+        <v>123.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>2105.73</v>
+        <v>129.97</v>
       </c>
       <c r="AC16" t="n">
-        <v>2155.76</v>
+        <v>130.59</v>
       </c>
       <c r="AD16" t="n">
-        <v>2193.93</v>
+        <v>131.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>43.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH16" t="n">
         <v>0.15</v>
       </c>
       <c r="AI16" t="n">
-        <v>35.4</v>
+        <v>22.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>63</v>
+        <v>10.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>36.1</v>
+        <v>66.2</v>
       </c>
       <c r="AL16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AM16" t="n">
-        <v>2193.47</v>
+        <v>135.08</v>
       </c>
       <c r="AN16" t="n">
-        <v>2042.38</v>
+        <v>123.93</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,787.61 Cr., a P/E ratio of 35.42, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>IEX operates in the Financial Services sector. With an estimated Market Cap of ₹11,527.11 Cr., a P/E ratio of 22.54, and YoY Revenue Growth of +10.1%, the company demonstrates strong institutional backing, solid operating profit margins (66.22%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.71 (Consolidation Zone), while MACD Line (46.13) trades below Signal (60.86) with an expanding histogram (-14.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.16% above the 200-day DMA (₹1880.26). Daily volatility envelope is bounded by ATR(14) of ₹68.37.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.41 (Bullish Momentum Zone), while MACD Line (2.09) trades above Signal (1.41) with an expanding histogram (+0.68). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +0.95% above the 200-day DMA (₹127.99). Daily volatility envelope is bounded by ATR(14) of ₹4.36.</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,117.60) is positioned above the 30-day DMA (₹2,028.46), 50-day DMA (₹1,908.05), and 200-day DMA (₹1,880.26). The price distance from 200 DMA is +8.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for IEX. Current Market Price (₹129.62) is positioned above the 30-day DMA (₹124.43), 50-day DMA (₹123.96), and 200-day DMA (₹127.99). The price distance from 200 DMA is +0.95%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>[2117.6, 2123.95, 2130.31, 2136.66, 2143.01, 2149.36]</t>
+          <t>[129.62, 130.01, 130.4, 130.79, 131.18, 131.56]</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[2117.6, 2151.3, 2168.98, 2184.03, 2197.71, 2210.52]</t>
+          <t>[129.62, 131.75, 132.87, 133.81, 134.67, 135.47]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[2117.6, 2103.44, 2101.3, 2101.13, 2101.99, 2103.5]</t>
+          <t>[129.62, 128.7, 128.55, 128.52, 128.56, 128.64]</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>287300.33</v>
+        <v>285965.55</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3133,15 +3133,15 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>312.1</v>
+        <v>310.7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹310.03 - ₹315.21</t>
+          <t>₹308.63 - ₹313.81</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>320.38</v>
+        <v>318.98</v>
       </c>
       <c r="I17" t="n">
         <v>286.32</v>
@@ -3168,16 +3168,16 @@
         <v>10.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R17" t="n">
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
       <c r="S17" t="n">
         <v>0.16</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.32</v>
+        <v>-2.35</v>
       </c>
       <c r="U17" t="n">
         <v>53.3</v>
@@ -3189,25 +3189,25 @@
         <v>-0.77</v>
       </c>
       <c r="X17" t="n">
-        <v>307.76</v>
+        <v>306.18</v>
       </c>
       <c r="Y17" t="n">
-        <v>318.69</v>
+        <v>317.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>314.6</v>
+        <v>313.19</v>
       </c>
       <c r="AA17" t="n">
-        <v>296.57</v>
+        <v>295.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>312.72</v>
+        <v>311.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>314.04</v>
+        <v>313.49</v>
       </c>
       <c r="AD17" t="n">
-        <v>315.97</v>
+        <v>316.27</v>
       </c>
       <c r="AE17" t="n">
         <v>62.2</v>
@@ -3217,14 +3217,14 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH17" t="n">
         <v>0.15</v>
       </c>
       <c r="AI17" t="n">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="AJ17" t="n">
         <v>182</v>
@@ -3236,14 +3236,14 @@
         <v>15</v>
       </c>
       <c r="AM17" t="n">
-        <v>323.72</v>
+        <v>321.59</v>
       </c>
       <c r="AN17" t="n">
-        <v>301.39</v>
+        <v>299.8</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹287,300.33 Cr., a P/E ratio of 664.04, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹285,965.55 Cr., a P/E ratio of 660.96, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
@@ -3253,22 +3253,22 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹312.10) is positioned above the 30-day DMA (₹286.32), 50-day DMA (₹272.64), and 200-day DMA (₹273.39). The price distance from 200 DMA is +14.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹310.70) is positioned above the 30-day DMA (₹286.32), 50-day DMA (₹272.64), and 200-day DMA (₹273.39). The price distance from 200 DMA is +14.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>[312.1, 313.04, 313.97, 314.91, 315.85, 316.78]</t>
+          <t>[310.7, 311.63, 312.56, 313.5, 314.43, 315.36]</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[312.1, 317.18, 319.83, 322.08, 324.13, 326.04]</t>
+          <t>[310.7, 315.77, 318.42, 320.67, 322.71, 324.62]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[312.1, 309.93, 309.58, 309.53, 309.64, 309.84]</t>
+          <t>[310.7, 308.53, 308.17, 308.12, 308.22, 308.42]</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17449.08</v>
+        <v>17441.92</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3297,15 +3297,15 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>609.05</v>
+        <v>608.1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹604.76 - ₹615.49</t>
+          <t>₹603.81 - ₹614.54</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>626.22</v>
+        <v>625.27</v>
       </c>
       <c r="I18" t="n">
         <v>583.11</v>
@@ -3332,7 +3332,7 @@
         <v>21.46</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.25</v>
+        <v>12.34</v>
       </c>
       <c r="R18" t="n">
         <v>47.5</v>
@@ -3341,37 +3341,37 @@
         <v>0.15</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.39</v>
+        <v>-2.4</v>
       </c>
       <c r="U18" t="n">
         <v>53.3</v>
       </c>
       <c r="V18" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="W18" t="n">
         <v>-0.77</v>
       </c>
       <c r="X18" t="n">
-        <v>583.3</v>
+        <v>582.35</v>
       </c>
       <c r="Y18" t="n">
-        <v>596.8200000000001</v>
+        <v>595.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>613.92</v>
+        <v>612.96</v>
       </c>
       <c r="AA18" t="n">
-        <v>576.86</v>
+        <v>575.91</v>
       </c>
       <c r="AB18" t="n">
-        <v>616.53</v>
+        <v>614.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>625.01</v>
+        <v>626.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>640.98</v>
+        <v>644.3</v>
       </c>
       <c r="AE18" t="n">
         <v>54.7</v>
@@ -3381,14 +3381,14 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Low VIX (12.25) | LSTM Deep Net</t>
+          <t>Low VIX (12.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH18" t="n">
         <v>0.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="AJ18" t="n">
         <v>-10.1</v>
@@ -3400,14 +3400,14 @@
         <v>6.7</v>
       </c>
       <c r="AM18" t="n">
-        <v>638.96</v>
+        <v>636.6799999999999</v>
       </c>
       <c r="AN18" t="n">
-        <v>578.59</v>
+        <v>576.48</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,449.08 Cr., a P/E ratio of 87.89, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,441.92 Cr., a P/E ratio of 87.85, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹609.05) is positioned above the 30-day DMA (₹583.11), 50-day DMA (₹550.15), and 200-day DMA (₹554.14). The price distance from 200 DMA is +10.44%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹608.10) is positioned above the 30-day DMA (₹583.11), 50-day DMA (₹550.15), and 200-day DMA (₹554.14). The price distance from 200 DMA is +10.44%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>[609.05, 610.88, 612.7, 614.53, 616.36, 618.19]</t>
+          <t>[608.1, 609.92, 611.75, 613.57, 615.4, 617.22]</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[609.05, 619.46, 624.84, 629.4, 633.53, 637.38]</t>
+          <t>[608.1, 618.51, 623.89, 628.44, 632.57, 636.42]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[609.05, 604.44, 603.6, 603.38, 603.48, 603.79]</t>
+          <t>[608.1, 603.49, 602.64, 602.42, 602.52, 602.83]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>357416.09</v>
+        <v>357563.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -673,15 +673,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12150</v>
+        <v>12155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹12109.59 - ₹12210.61</t>
+          <t>₹12114.59 - ₹12215.61</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12311.62</v>
+        <v>12316.62</v>
       </c>
       <c r="I2" t="n">
         <v>11508.32</v>
@@ -708,16 +708,16 @@
         <v>202.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R2" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="S2" t="n">
         <v>0.32</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="U2" t="n">
         <v>50</v>
@@ -729,25 +729,25 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>12055.35</v>
+        <v>12060.74</v>
       </c>
       <c r="Y2" t="n">
-        <v>12453.04</v>
+        <v>12458.04</v>
       </c>
       <c r="Z2" t="n">
-        <v>12247.2</v>
+        <v>12252.24</v>
       </c>
       <c r="AA2" t="n">
-        <v>11846.96</v>
+        <v>11851.96</v>
       </c>
       <c r="AB2" t="n">
-        <v>12119.67</v>
+        <v>12121.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>12269.34</v>
+        <v>12272.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>12388.67</v>
+        <v>12390.33</v>
       </c>
       <c r="AE2" t="n">
         <v>70.40000000000001</v>
@@ -757,14 +757,14 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="AJ2" t="n">
         <v>15.9</v>
@@ -776,14 +776,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>12425.44</v>
+        <v>12431.71</v>
       </c>
       <c r="AN2" t="n">
-        <v>11882.79</v>
+        <v>11884.91</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹357,416.09 Cr., a P/E ratio of 41.84, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹357,563.18 Cr., a P/E ratio of 41.85, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -793,22 +793,22 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,150.00) is positioned above the 30-day DMA (₹11,508.32), 50-day DMA (₹11,305.61), and 200-day DMA (₹11,570.61). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,155.00) is positioned above the 30-day DMA (₹11,508.32), 50-day DMA (₹11,305.61), and 200-day DMA (₹11,570.61). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[12150.0, 12237.6, 12325.2, 12412.8, 12500.41, 12588.01]</t>
+          <t>[12155.0, 12243.07, 12331.14, 12419.2, 12507.27, 12595.34]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[12150.0, 12318.41, 12439.49, 12552.77, 12662.03, 12768.7]</t>
+          <t>[12155.0, 12323.88, 12445.42, 12559.17, 12668.89, 12776.04]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[12150.0, 12176.99, 12239.49, 12307.83, 12379.19, 12452.48]</t>
+          <t>[12155.0, 12182.46, 12245.42, 12314.23, 12386.06, 12459.82]</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>130812.67</v>
+        <v>130674.76</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -837,15 +837,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>113.82</v>
+        <v>113.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹113.43 - ₹114.41</t>
+          <t>₹113.31 - ₹114.29</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>115.38</v>
+        <v>115.26</v>
       </c>
       <c r="I3" t="n">
         <v>108.12</v>
@@ -872,16 +872,16 @@
         <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R3" t="n">
-        <v>49.4</v>
+        <v>48.9</v>
       </c>
       <c r="S3" t="n">
         <v>0.31</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.91</v>
+        <v>-0.92</v>
       </c>
       <c r="U3" t="n">
         <v>55</v>
@@ -893,25 +893,25 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>111.48</v>
+        <v>111.36</v>
       </c>
       <c r="Y3" t="n">
-        <v>114.91</v>
+        <v>114.77</v>
       </c>
       <c r="Z3" t="n">
+        <v>114.61</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>110.77</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>114.16</v>
+      </c>
+      <c r="AC3" t="n">
         <v>114.73</v>
       </c>
-      <c r="AA3" t="n">
-        <v>110.89</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>114.21</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>114.82</v>
-      </c>
       <c r="AD3" t="n">
-        <v>115.81</v>
+        <v>115.77</v>
       </c>
       <c r="AE3" t="n">
         <v>79</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
@@ -940,14 +940,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>116.9</v>
+        <v>117.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>110.73</v>
+        <v>110.4</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,812.67 Cr., a P/E ratio of 5.87, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,674.76 Cr., a P/E ratio of 5.86, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -957,22 +957,22 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.82) is positioned above the 30-day DMA (₹108.12), 50-day DMA (₹106.98), and 200-day DMA (₹112.64). The price distance from 200 DMA is +1.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.70) is positioned above the 30-day DMA (₹108.12), 50-day DMA (₹106.98), and 200-day DMA (₹112.64). The price distance from 200 DMA is +1.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[113.82, 114.16, 114.5, 114.84, 115.19, 115.53]</t>
+          <t>[113.7, 114.04, 114.38, 114.72, 115.06, 115.41]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[113.82, 114.94, 115.61, 116.2, 116.75, 117.27]</t>
+          <t>[113.7, 114.82, 115.49, 116.08, 116.63, 117.15]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[113.82, 113.58, 113.67, 113.83, 114.01, 114.22]</t>
+          <t>[113.7, 113.46, 113.55, 113.71, 113.89, 114.1]</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>219603.63</v>
+        <v>219891.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1001,15 +1001,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7999.5</v>
+        <v>8010</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹7968.14 - ₹8046.54</t>
+          <t>₹7978.64 - ₹8057.04</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8124.95</v>
+        <v>8135.45</v>
       </c>
       <c r="I4" t="n">
         <v>7478.7</v>
@@ -1036,16 +1036,16 @@
         <v>156.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R4" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="S4" t="n">
         <v>0.27</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.01</v>
+        <v>-1.02</v>
       </c>
       <c r="U4" t="n">
         <v>51.7</v>
@@ -1057,25 +1057,25 @@
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>7877.72</v>
+        <v>7887.48</v>
       </c>
       <c r="Y4" t="n">
-        <v>8157.7</v>
+        <v>8167.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>8063.5</v>
+        <v>8074.08</v>
       </c>
       <c r="AA4" t="n">
-        <v>7764.28</v>
+        <v>7774.78</v>
       </c>
       <c r="AB4" t="n">
-        <v>7968.17</v>
+        <v>7977.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>8030.84</v>
+        <v>8050.16</v>
       </c>
       <c r="AD4" t="n">
-        <v>8062.17</v>
+        <v>8090.33</v>
       </c>
       <c r="AE4" t="n">
         <v>74.3</v>
@@ -1085,14 +1085,14 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="AJ4" t="n">
         <v>31.5</v>
@@ -1104,14 +1104,14 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>8209.23</v>
+        <v>8235.690000000001</v>
       </c>
       <c r="AN4" t="n">
-        <v>7811.34</v>
+        <v>7798.99</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹219,603.63 Cr., a P/E ratio of 38.63, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹219,891.88 Cr., a P/E ratio of 38.68, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1121,22 +1121,22 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,999.50) is positioned above the 30-day DMA (₹7,478.70), 50-day DMA (₹7,389.91), and 200-day DMA (₹7,187.90). The price distance from 200 DMA is +10.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹8,010.00) is positioned above the 30-day DMA (₹7,478.70), 50-day DMA (₹7,389.91), and 200-day DMA (₹7,187.90). The price distance from 200 DMA is +10.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[7999.5, 8023.5, 8047.5, 8071.5, 8095.49, 8119.49]</t>
+          <t>[8010.0, 8034.03, 8058.06, 8082.09, 8106.12, 8130.15]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[7999.5, 8086.22, 8136.2, 8180.14, 8220.94, 8259.75]</t>
+          <t>[8010.0, 8096.75, 8146.77, 8190.73, 8231.57, 8270.41]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[7999.5, 7976.46, 7980.97, 7990.01, 8001.41, 8014.3]</t>
+          <t>[8010.0, 7986.99, 7991.53, 8000.61, 8012.03, 8024.96]</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>309201.42</v>
+        <v>309709.69</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1165,15 +1165,15 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4623.4</v>
+        <v>4631</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹4607.36 - ₹4647.46</t>
+          <t>₹4614.96 - ₹4655.06</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4687.55</v>
+        <v>4695.15</v>
       </c>
       <c r="I5" t="n">
         <v>4490.17</v>
@@ -1200,16 +1200,16 @@
         <v>80.19</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R5" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="S5" t="n">
         <v>0.31</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.21</v>
+        <v>-1.22</v>
       </c>
       <c r="U5" t="n">
         <v>41.7</v>
@@ -1221,25 +1221,25 @@
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>4527.18</v>
+        <v>4534.78</v>
       </c>
       <c r="Y5" t="n">
-        <v>4662.53</v>
+        <v>4670.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>4660.39</v>
+        <v>4668.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4503.12</v>
+        <v>4510.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>4633.37</v>
+        <v>4635.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>4663.44</v>
+        <v>4668.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>4703.47</v>
+        <v>4706</v>
       </c>
       <c r="AE5" t="n">
         <v>72.8</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
@@ -1268,14 +1268,14 @@
         <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>4748.28</v>
+        <v>4757.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>4505.04</v>
+        <v>4494.93</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹309,201.42 Cr., a P/E ratio of 33.96, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹309,709.69 Cr., a P/E ratio of 34.02, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,623.40) is positioned above the 30-day DMA (₹4,490.17), 50-day DMA (₹4,419.22), and 200-day DMA (₹4,344.79). The price distance from 200 DMA is +6.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,631.00) is positioned above the 30-day DMA (₹4,490.17), 50-day DMA (₹4,419.22), and 200-day DMA (₹4,344.79). The price distance from 200 DMA is +6.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[4623.4, 4637.27, 4651.14, 4665.01, 4678.88, 4692.75]</t>
+          <t>[4631.0, 4644.89, 4658.79, 4672.68, 4686.57, 4700.46]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[4623.4, 4669.34, 4696.5, 4720.56, 4743.03, 4764.47]</t>
+          <t>[4631.0, 4676.97, 4704.15, 4728.23, 4750.72, 4772.19]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[4623.4, 4613.21, 4617.12, 4623.34, 4630.77, 4638.96]</t>
+          <t>[4631.0, 4620.84, 4624.77, 4631.01, 4638.46, 4646.67]</t>
         </is>
       </c>
     </row>
@@ -1312,159 +1312,159 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>264394.09</v>
+        <v>67440.64</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2758</v>
+        <v>5640.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2746.15 - ₹2775.77</t>
+          <t>₹5617.16 - ₹5675.5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2805.39</v>
+        <v>5733.84</v>
       </c>
       <c r="I6" t="n">
-        <v>2698.21</v>
+        <v>5598.93</v>
       </c>
       <c r="J6" t="n">
-        <v>2687.88</v>
+        <v>5497.15</v>
       </c>
       <c r="K6" t="n">
-        <v>2577.55</v>
+        <v>5524.06</v>
       </c>
       <c r="L6" t="n">
-        <v>7.66</v>
+        <v>3.31</v>
       </c>
       <c r="M6" t="n">
-        <v>26.47</v>
+        <v>58.81</v>
       </c>
       <c r="N6" t="n">
-        <v>16.72</v>
+        <v>54.69</v>
       </c>
       <c r="O6" t="n">
-        <v>9.76</v>
+        <v>4.12</v>
       </c>
       <c r="P6" t="n">
-        <v>59.24</v>
+        <v>116.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R6" t="n">
-        <v>48.2</v>
+        <v>47.1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.28</v>
+        <v>-1.26</v>
       </c>
       <c r="U6" t="n">
-        <v>55</v>
+        <v>51.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.78</v>
+        <v>2.82</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2686.92</v>
+        <v>5500.49</v>
       </c>
       <c r="Y6" t="n">
-        <v>2779.48</v>
+        <v>5606.71</v>
       </c>
       <c r="Z6" t="n">
-        <v>2780.06</v>
+        <v>5685.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>2669.15</v>
+        <v>5465.48</v>
       </c>
       <c r="AB6" t="n">
-        <v>2764.57</v>
+        <v>5620.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>2780.44</v>
+        <v>5685.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>2802.87</v>
+        <v>5730.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>67</v>
+        <v>56.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>56.1</v>
+        <v>29.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17.9</v>
+        <v>14.6</v>
       </c>
       <c r="AK6" t="n">
-        <v>12.8</v>
+        <v>15.6</v>
       </c>
       <c r="AL6" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>2821.79</v>
+        <v>5765.79</v>
       </c>
       <c r="AN6" t="n">
-        <v>2696.4</v>
+        <v>5506.54</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹264,394.09 Cr., a P/E ratio of 56.15, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,440.64 Cr., a P/E ratio of 29.27, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.98 (Bullish Momentum Zone), while MACD Line (26.47) trades above Signal (16.72) with an expanding histogram (+9.76). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.66% above the 200-day DMA (₹2577.55). Daily volatility envelope is bounded by ATR(14) of ₹59.24.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.20 (Bullish Momentum Zone), while MACD Line (58.81) trades above Signal (54.69) with an expanding histogram (+4.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.31% above the 200-day DMA (₹5524.06). Daily volatility envelope is bounded by ATR(14) of ₹116.68.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,758.00) is positioned above the 30-day DMA (₹2,698.21), 50-day DMA (₹2,687.88), and 200-day DMA (₹2,577.55). The price distance from 200 DMA is +7.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,640.50) is positioned above the 30-day DMA (₹5,598.93), 50-day DMA (₹5,497.15), and 200-day DMA (₹5,524.06). The price distance from 200 DMA is +3.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[2758.0, 2766.27, 2774.55, 2782.82, 2791.1, 2799.37]</t>
+          <t>[5640.5, 5657.42, 5674.34, 5691.26, 5708.19, 5725.11]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2758.0, 2789.97, 2808.06, 2823.86, 2838.48, 2852.35]</t>
+          <t>[5640.5, 5704.09, 5740.35, 5772.1, 5801.53, 5829.47]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2758.0, 2748.5, 2749.42, 2752.04, 2755.55, 2759.63]</t>
+          <t>[5640.5, 5622.42, 5624.84, 5630.64, 5638.18, 5646.84]</t>
         </is>
       </c>
     </row>
@@ -1476,159 +1476,159 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>67315.09</v>
+        <v>264489.95</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5629</v>
+        <v>2759</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹5605.66 - ₹5664.0</t>
+          <t>₹2747.15 - ₹2776.77</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5722.34</v>
+        <v>2806.39</v>
       </c>
       <c r="I7" t="n">
-        <v>5598.93</v>
+        <v>2698.21</v>
       </c>
       <c r="J7" t="n">
-        <v>5497.15</v>
+        <v>2687.88</v>
       </c>
       <c r="K7" t="n">
-        <v>5524.06</v>
+        <v>2577.55</v>
       </c>
       <c r="L7" t="n">
-        <v>3.31</v>
+        <v>7.66</v>
       </c>
       <c r="M7" t="n">
-        <v>58.81</v>
+        <v>26.47</v>
       </c>
       <c r="N7" t="n">
-        <v>54.69</v>
+        <v>16.72</v>
       </c>
       <c r="O7" t="n">
-        <v>4.12</v>
+        <v>9.76</v>
       </c>
       <c r="P7" t="n">
-        <v>116.68</v>
+        <v>59.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R7" t="n">
-        <v>46.7</v>
+        <v>48.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="T7" t="n">
         <v>-1.28</v>
       </c>
       <c r="U7" t="n">
-        <v>51.7</v>
+        <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>2.82</v>
+        <v>1.78</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>5488.99</v>
+        <v>2687.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>5594.42</v>
+        <v>2780.66</v>
       </c>
       <c r="Z7" t="n">
-        <v>5674.03</v>
+        <v>2781.07</v>
       </c>
       <c r="AA7" t="n">
-        <v>5453.98</v>
+        <v>2670.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>5616.83</v>
+        <v>2764.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>5677.66</v>
+        <v>2781.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>5726.33</v>
+        <v>2803.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>56.2</v>
+        <v>67</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>29.2</v>
+        <v>56.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14.6</v>
+        <v>17.9</v>
       </c>
       <c r="AK7" t="n">
-        <v>15.6</v>
+        <v>12.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>5748.52</v>
+        <v>2826.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>5495.23</v>
+        <v>2694.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,315.09 Cr., a P/E ratio of 29.22, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹264,489.95 Cr., a P/E ratio of 56.17, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.20 (Bullish Momentum Zone), while MACD Line (58.81) trades above Signal (54.69) with an expanding histogram (+4.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.31% above the 200-day DMA (₹5524.06). Daily volatility envelope is bounded by ATR(14) of ₹116.68.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.98 (Bullish Momentum Zone), while MACD Line (26.47) trades above Signal (16.72) with an expanding histogram (+9.76). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.66% above the 200-day DMA (₹2577.55). Daily volatility envelope is bounded by ATR(14) of ₹59.24.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,629.00) is positioned above the 30-day DMA (₹5,598.93), 50-day DMA (₹5,497.15), and 200-day DMA (₹5,524.06). The price distance from 200 DMA is +3.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,759.00) is positioned above the 30-day DMA (₹2,698.21), 50-day DMA (₹2,687.88), and 200-day DMA (₹2,577.55). The price distance from 200 DMA is +7.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[5629.0, 5645.89, 5662.77, 5679.66, 5696.55, 5713.43]</t>
+          <t>[2759.0, 2767.28, 2775.55, 2783.83, 2792.11, 2800.38]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[5629.0, 5692.56, 5728.78, 5760.5, 5789.89, 5817.8]</t>
+          <t>[2759.0, 2790.97, 2809.06, 2824.87, 2839.5, 2853.37]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[5629.0, 5610.88, 5613.27, 5619.03, 5626.54, 5635.16]</t>
+          <t>[2759.0, 2749.51, 2750.42, 2753.05, 2756.57, 2760.65]</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105590.2</v>
+        <v>104899.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1657,15 +1657,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>741.8</v>
+        <v>737.6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹738.81 - ₹746.29</t>
+          <t>₹734.61 - ₹742.09</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>753.78</v>
+        <v>749.58</v>
       </c>
       <c r="I8" t="n">
         <v>731.6799999999999</v>
@@ -1692,46 +1692,46 @@
         <v>14.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R8" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="S8" t="n">
         <v>0.26</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.35</v>
+        <v>-1.36</v>
       </c>
       <c r="U8" t="n">
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>723.83</v>
+        <v>719.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>735.01</v>
+        <v>729.87</v>
       </c>
       <c r="Z8" t="n">
-        <v>747.73</v>
+        <v>743.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>719.34</v>
+        <v>715.14</v>
       </c>
       <c r="AB8" t="n">
-        <v>745</v>
+        <v>742.4299999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>749.7</v>
+        <v>748.0599999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>757.6</v>
+        <v>758.53</v>
       </c>
       <c r="AE8" t="n">
         <v>54.1</v>
@@ -1741,14 +1741,14 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="AJ8" t="n">
         <v>15.1</v>
@@ -1760,14 +1760,14 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>758.53</v>
+        <v>755.92</v>
       </c>
       <c r="AN8" t="n">
-        <v>725.13</v>
+        <v>720</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,590.20 Cr., a P/E ratio of 49.45, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹104,899.84 Cr., a P/E ratio of 49.13, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1777,22 +1777,22 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.80) is positioned above the 30-day DMA (₹731.68), 50-day DMA (₹709.25), and 200-day DMA (₹686.46). The price distance from 200 DMA is +9.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹737.60) is positioned above the 30-day DMA (₹731.68), 50-day DMA (₹709.25), and 200-day DMA (₹686.46). The price distance from 200 DMA is +9.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[741.8, 744.03, 746.25, 748.48, 750.7, 752.93]</t>
+          <t>[737.6, 739.81, 742.03, 744.24, 746.45, 748.66]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[741.8, 750.01, 754.72, 758.85, 762.68, 766.32]</t>
+          <t>[737.6, 745.8, 750.49, 754.61, 758.43, 762.05]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[741.8, 739.53, 739.9, 740.7, 741.72, 742.88]</t>
+          <t>[737.6, 735.32, 735.67, 736.46, 737.47, 738.62]</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96086.34</v>
+        <v>95902.02</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1821,15 +1821,15 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>364.9</v>
+        <v>364.2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹363.33 - ₹367.25</t>
+          <t>₹362.64 - ₹366.55</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>371.16</v>
+        <v>370.46</v>
       </c>
       <c r="I9" t="n">
         <v>358.01</v>
@@ -1856,46 +1856,46 @@
         <v>7.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R9" t="n">
-        <v>43.6</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>0.25</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.47</v>
+        <v>-1.49</v>
       </c>
       <c r="U9" t="n">
         <v>50</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>356.89</v>
+        <v>356.16</v>
       </c>
       <c r="Y9" t="n">
-        <v>369.66</v>
+        <v>368.91</v>
       </c>
       <c r="Z9" t="n">
-        <v>367.82</v>
+        <v>367.11</v>
       </c>
       <c r="AA9" t="n">
-        <v>353.16</v>
+        <v>352.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>367.17</v>
+        <v>366.87</v>
       </c>
       <c r="AC9" t="n">
-        <v>370.04</v>
+        <v>369.64</v>
       </c>
       <c r="AD9" t="n">
-        <v>375.17</v>
+        <v>375.07</v>
       </c>
       <c r="AE9" t="n">
         <v>71.8</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
@@ -1924,14 +1924,14 @@
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>374.31</v>
+        <v>373.9</v>
       </c>
       <c r="AN9" t="n">
-        <v>355.32</v>
+        <v>354.41</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹96,086.34 Cr., a P/E ratio of 6.00, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹95,902.02 Cr., a P/E ratio of 5.99, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1941,22 +1941,22 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹364.90) is positioned above the 30-day DMA (₹358.01), 50-day DMA (₹351.17), and 200-day DMA (₹347.72). The price distance from 200 DMA is +5.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹364.20) is positioned above the 30-day DMA (₹358.01), 50-day DMA (₹351.17), and 200-day DMA (₹347.72). The price distance from 200 DMA is +5.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[364.9, 365.99, 367.09, 368.18, 369.28, 370.37]</t>
+          <t>[364.2, 365.29, 366.39, 367.48, 368.57, 369.66]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[364.9, 369.12, 371.52, 373.61, 375.54, 377.37]</t>
+          <t>[364.2, 368.42, 370.81, 372.9, 374.83, 376.66]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[364.9, 363.65, 363.77, 364.12, 364.58, 365.12]</t>
+          <t>[364.2, 362.95, 363.07, 363.41, 363.88, 364.41]</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>117502.25</v>
+        <v>117478.01</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1985,15 +1985,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1454</v>
+        <v>1454.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹1447.17 - ₹1464.24</t>
+          <t>₹1447.37 - ₹1464.44</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1481.31</v>
+        <v>1481.51</v>
       </c>
       <c r="I10" t="n">
         <v>1443.04</v>
@@ -2020,16 +2020,16 @@
         <v>34.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R10" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="S10" t="n">
         <v>0.23</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.71</v>
+        <v>-1.69</v>
       </c>
       <c r="U10" t="n">
         <v>45</v>
@@ -2041,25 +2041,25 @@
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>1413.03</v>
+        <v>1413.23</v>
       </c>
       <c r="Y10" t="n">
-        <v>1416.09</v>
+        <v>1416.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>1465.63</v>
+        <v>1465.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>1402.79</v>
+        <v>1402.99</v>
       </c>
       <c r="AB10" t="n">
-        <v>1452.5</v>
+        <v>1452.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>1461.5</v>
+        <v>1461.64</v>
       </c>
       <c r="AD10" t="n">
-        <v>1469</v>
+        <v>1469.07</v>
       </c>
       <c r="AE10" t="n">
         <v>55.4</v>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
@@ -2088,14 +2088,14 @@
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>1488.11</v>
+        <v>1486.32</v>
       </c>
       <c r="AN10" t="n">
-        <v>1423.03</v>
+        <v>1423.91</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,502.25 Cr., a P/E ratio of 35.20, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,478.01 Cr., a P/E ratio of 35.19, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2105,22 +2105,22 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,454.00) is positioned above the 30-day DMA (₹1,443.04), 50-day DMA (₹1,419.16), and 200-day DMA (₹1,394.98). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,454.20) is positioned above the 30-day DMA (₹1,443.04), 50-day DMA (₹1,419.16), and 200-day DMA (₹1,394.98). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[1454.0, 1458.36, 1462.72, 1467.09, 1471.45, 1475.81]</t>
+          <t>[1454.2, 1458.56, 1462.93, 1467.29, 1471.65, 1476.01]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[1454.0, 1472.02, 1482.04, 1490.74, 1498.76, 1506.35]</t>
+          <t>[1454.2, 1472.22, 1482.24, 1490.94, 1498.96, 1506.55]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[1454.0, 1448.12, 1448.24, 1449.34, 1450.96, 1452.91]</t>
+          <t>[1454.2, 1448.32, 1448.44, 1449.55, 1451.16, 1453.11]</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>146705.48</v>
+        <v>147121.83</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2149,15 +2149,15 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1656.2</v>
+        <v>1660.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹1647.09 - ₹1669.87</t>
+          <t>₹1651.69 - ₹1674.47</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1692.66</v>
+        <v>1697.26</v>
       </c>
       <c r="I11" t="n">
         <v>1496.08</v>
@@ -2184,46 +2184,46 @@
         <v>45.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R11" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="S11" t="n">
         <v>0.19</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.76</v>
+        <v>-1.74</v>
       </c>
       <c r="U11" t="n">
         <v>50</v>
       </c>
       <c r="V11" t="n">
-        <v>7.94</v>
+        <v>7.95</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>1627.4</v>
+        <v>1632.32</v>
       </c>
       <c r="Y11" t="n">
-        <v>1685.36</v>
+        <v>1690.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>1669.45</v>
+        <v>1674.09</v>
       </c>
       <c r="AA11" t="n">
-        <v>1587.84</v>
+        <v>1592.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>1656.23</v>
+        <v>1657.77</v>
       </c>
       <c r="AC11" t="n">
-        <v>1664.76</v>
+        <v>1667.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>1673.33</v>
+        <v>1674.87</v>
       </c>
       <c r="AE11" t="n">
         <v>83.5</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
@@ -2252,14 +2252,14 @@
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>1704.65</v>
+        <v>1703.67</v>
       </c>
       <c r="AN11" t="n">
-        <v>1613.8</v>
+        <v>1616.56</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,705.48 Cr., a P/E ratio of 28.65, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹147,121.83 Cr., a P/E ratio of 28.73, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2269,22 +2269,22 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,656.20) is positioned above the 30-day DMA (₹1,496.08), 50-day DMA (₹1,470.74), and 200-day DMA (₹1,461.21). The price distance from 200 DMA is +12.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,660.80) is positioned above the 30-day DMA (₹1,496.08), 50-day DMA (₹1,470.74), and 200-day DMA (₹1,461.21). The price distance from 200 DMA is +12.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[1656.2, 1661.17, 1666.14, 1671.11, 1676.07, 1681.04]</t>
+          <t>[1660.8, 1665.78, 1670.76, 1675.75, 1680.73, 1685.71]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[1656.2, 1679.4, 1691.92, 1702.68, 1712.53, 1721.8]</t>
+          <t>[1660.8, 1684.01, 1696.54, 1707.32, 1717.19, 1726.47]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[1656.2, 1647.5, 1646.8, 1647.43, 1648.73, 1650.47]</t>
+          <t>[1660.8, 1652.11, 1651.43, 1652.07, 1653.39, 1655.14]</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>78675.00999999999</v>
+        <v>78834.38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2313,15 +2313,15 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1777.5</v>
+        <v>1780.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹1765.86 - ₹1794.96</t>
+          <t>₹1769.26 - ₹1798.36</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1824.05</v>
+        <v>1827.45</v>
       </c>
       <c r="I12" t="n">
         <v>1530.06</v>
@@ -2348,16 +2348,16 @@
         <v>58.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R12" t="n">
-        <v>48.9</v>
+        <v>49.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.84</v>
+        <v>-1.76</v>
       </c>
       <c r="U12" t="n">
         <v>50</v>
@@ -2369,25 +2369,25 @@
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>1775.22</v>
+        <v>1779.76</v>
       </c>
       <c r="Y12" t="n">
-        <v>1837.43</v>
+        <v>1842.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>1801.88</v>
+        <v>1806.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>1690.21</v>
+        <v>1693.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>1770.2</v>
+        <v>1771.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>1795.3</v>
+        <v>1797.56</v>
       </c>
       <c r="AD12" t="n">
-        <v>1813.1</v>
+        <v>1814.23</v>
       </c>
       <c r="AE12" t="n">
         <v>72.90000000000001</v>
@@ -2397,14 +2397,14 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH12" t="n">
         <v>0.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="AJ12" t="n">
         <v>49.9</v>
@@ -2416,14 +2416,14 @@
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>1843.54</v>
+        <v>1850.92</v>
       </c>
       <c r="AN12" t="n">
-        <v>1711.42</v>
+        <v>1716.91</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹78,675.01 Cr., a P/E ratio of 36.80, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
+          <t>COFORGE operates in the Technology sector. With an estimated Market Cap of ₹78,834.38 Cr., a P/E ratio of 36.87, and YoY Revenue Growth of +49.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2433,22 +2433,22 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,777.50) is positioned above the 30-day DMA (₹1,530.06), 50-day DMA (₹1,489.66), and 200-day DMA (₹1,504.99). The price distance from 200 DMA is +16.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for COFORGE. Current Market Price (₹1,780.90) is positioned above the 30-day DMA (₹1,530.06), 50-day DMA (₹1,489.66), and 200-day DMA (₹1,504.99). The price distance from 200 DMA is +16.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[1777.5, 1801.88, 1826.26, 1850.64, 1875.02, 1899.4]</t>
+          <t>[1780.9, 1806.47, 1832.04, 1857.61, 1883.18, 1908.75]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1777.5, 1825.16, 1859.18, 1890.96, 1921.58, 1951.45]</t>
+          <t>[1780.9, 1829.75, 1864.96, 1897.93, 1929.73, 1960.8]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1777.5, 1784.42, 1801.57, 1820.4, 1840.1, 1860.36]</t>
+          <t>[1780.9, 1789.01, 1807.35, 1827.37, 1848.26, 1869.71]</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48533.74</v>
+        <v>48460.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2477,15 +2477,15 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1192.8</v>
+        <v>1191</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>₹1186.01 - ₹1202.98</t>
+          <t>₹1184.21 - ₹1201.18</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1219.95</v>
+        <v>1218.15</v>
       </c>
       <c r="I13" t="n">
         <v>1109.52</v>
@@ -2512,46 +2512,46 @@
         <v>33.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R13" t="n">
-        <v>47.3</v>
+        <v>47.6</v>
       </c>
       <c r="S13" t="n">
         <v>0.19</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.87</v>
+        <v>-1.86</v>
       </c>
       <c r="U13" t="n">
         <v>50</v>
       </c>
       <c r="V13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="W13" t="n">
         <v>-0.77</v>
       </c>
       <c r="X13" t="n">
-        <v>1176.91</v>
+        <v>1174.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1218.66</v>
+        <v>1215.78</v>
       </c>
       <c r="Z13" t="n">
-        <v>1202.34</v>
+        <v>1200.53</v>
       </c>
       <c r="AA13" t="n">
-        <v>1141.9</v>
+        <v>1140.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1183.6</v>
+        <v>1183</v>
       </c>
       <c r="AC13" t="n">
-        <v>1203.9</v>
+        <v>1202.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1215</v>
+        <v>1214.4</v>
       </c>
       <c r="AE13" t="n">
         <v>60.6</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH13" t="n">
@@ -2580,14 +2580,14 @@
         <v>15</v>
       </c>
       <c r="AM13" t="n">
-        <v>1228.87</v>
+        <v>1231.07</v>
       </c>
       <c r="AN13" t="n">
-        <v>1158.42</v>
+        <v>1154.3</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹48,533.74 Cr., a P/E ratio of 39.64, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
+          <t>360ONE operates in the Financial Services sector. With an estimated Market Cap of ₹48,460.50 Cr., a P/E ratio of 39.58, and YoY Revenue Growth of +29.9%, the company demonstrates strong institutional backing, solid operating profit margins (26.46%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2597,22 +2597,22 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,192.80) is positioned above the 30-day DMA (₹1,109.52), 50-day DMA (₹1,105.91), and 200-day DMA (₹1,100.89). The price distance from 200 DMA is +4.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for 360ONE. Current Market Price (₹1,191.00) is positioned above the 30-day DMA (₹1,109.52), 50-day DMA (₹1,105.91), and 200-day DMA (₹1,100.89). The price distance from 200 DMA is +4.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>[1192.8, 1196.38, 1199.96, 1203.54, 1207.11, 1210.69]</t>
+          <t>[1191.0, 1194.57, 1198.15, 1201.72, 1205.29, 1208.86]</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>[1192.8, 1209.95, 1219.15, 1227.05, 1234.26, 1241.05]</t>
+          <t>[1191.0, 1208.15, 1217.34, 1225.23, 1232.44, 1239.22]</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[1192.8, 1186.2, 1185.56, 1185.9, 1186.75, 1187.93]</t>
+          <t>[1191.0, 1184.39, 1183.75, 1184.09, 1184.93, 1186.1]</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>86916.31</v>
+        <v>87238.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2641,15 +2641,15 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14295</v>
+        <v>14348</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>₹14201.1 - ₹14435.85</t>
+          <t>₹14254.1 - ₹14488.85</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>14670.6</v>
+        <v>14723.6</v>
       </c>
       <c r="I14" t="n">
         <v>13362.03</v>
@@ -2676,46 +2676,46 @@
         <v>469.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R14" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="S14" t="n">
         <v>0.16</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.08</v>
+        <v>-2.09</v>
       </c>
       <c r="U14" t="n">
         <v>48.3</v>
       </c>
       <c r="V14" t="n">
-        <v>6.39</v>
+        <v>6.4</v>
       </c>
       <c r="W14" t="n">
         <v>-0.77</v>
       </c>
       <c r="X14" t="n">
-        <v>14185.38</v>
+        <v>14245.49</v>
       </c>
       <c r="Y14" t="n">
-        <v>14685.71</v>
+        <v>14747.67</v>
       </c>
       <c r="Z14" t="n">
-        <v>14409.36</v>
+        <v>14462.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>13590.75</v>
+        <v>13643.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>14228.33</v>
+        <v>14246</v>
       </c>
       <c r="AC14" t="n">
-        <v>14433.66</v>
+        <v>14469</v>
       </c>
       <c r="AD14" t="n">
-        <v>14572.33</v>
+        <v>14590</v>
       </c>
       <c r="AE14" t="n">
         <v>55.3</v>
@@ -2725,14 +2725,14 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH14" t="n">
         <v>0.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
         <v>21.1</v>
@@ -2744,14 +2744,14 @@
         <v>15</v>
       </c>
       <c r="AM14" t="n">
-        <v>14815.95</v>
+        <v>14900.38</v>
       </c>
       <c r="AN14" t="n">
-        <v>13766.25</v>
+        <v>13821.29</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹86,916.31 Cr., a P/E ratio of 41.87, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
+          <t>DIXON operates in the Technology sector. With an estimated Market Cap of ₹87,238.55 Cr., a P/E ratio of 42.03, and YoY Revenue Growth of +21.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -2761,22 +2761,22 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,295.00) is positioned above the 30-day DMA (₹13,362.03), 50-day DMA (₹12,739.88), and 200-day DMA (₹12,290.57). The price distance from 200 DMA is +13.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DIXON. Current Market Price (₹14,348.00) is positioned above the 30-day DMA (₹13,362.03), 50-day DMA (₹12,739.88), and 200-day DMA (₹12,290.57). The price distance from 200 DMA is +13.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>[14295.0, 14399.81, 14504.61, 14609.42, 14714.23, 14819.03]</t>
+          <t>[14348.0, 14460.71, 14573.42, 14686.13, 14798.85, 14911.56]</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>[14295.0, 14587.61, 14770.2, 14934.7, 15089.83, 15238.97]</t>
+          <t>[14348.0, 14648.51, 14839.01, 15011.41, 15174.45, 15331.49]</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>[14295.0, 14258.96, 14305.42, 14365.46, 14432.53, 14504.08]</t>
+          <t>[14348.0, 14319.86, 14374.23, 14442.18, 14517.15, 14596.61]</t>
         </is>
       </c>
     </row>
@@ -2788,159 +2788,159 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>63739.41</v>
+        <v>17537.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2116</v>
+        <v>612.15</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>₹2102.33 - ₹2136.51</t>
+          <t>₹607.86 - ₹618.59</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2170.7</v>
+        <v>629.3200000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2028.46</v>
+        <v>583.11</v>
       </c>
       <c r="J15" t="n">
-        <v>1908.05</v>
+        <v>550.15</v>
       </c>
       <c r="K15" t="n">
-        <v>1880.26</v>
+        <v>554.14</v>
       </c>
       <c r="L15" t="n">
-        <v>8.16</v>
+        <v>10.44</v>
       </c>
       <c r="M15" t="n">
-        <v>46.13</v>
+        <v>15.39</v>
       </c>
       <c r="N15" t="n">
-        <v>60.86</v>
+        <v>15.91</v>
       </c>
       <c r="O15" t="n">
-        <v>-14.73</v>
+        <v>-0.52</v>
       </c>
       <c r="P15" t="n">
-        <v>68.37</v>
+        <v>21.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R15" t="n">
-        <v>47.5</v>
+        <v>52.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.16</v>
+        <v>-2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>51.7</v>
+        <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>6.25</v>
+        <v>4.79</v>
       </c>
       <c r="W15" t="n">
         <v>-0.77</v>
       </c>
       <c r="X15" t="n">
-        <v>2033.95</v>
+        <v>586.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>2017.79</v>
+        <v>600.51</v>
       </c>
       <c r="Z15" t="n">
-        <v>2132.93</v>
+        <v>617.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>2013.44</v>
+        <v>579.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>2105.2</v>
+        <v>615.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>2154.7</v>
+        <v>628.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>2193.4</v>
+        <v>645.65</v>
       </c>
       <c r="AE15" t="n">
-        <v>43.7</v>
+        <v>54.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH15" t="n">
         <v>0.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>35.4</v>
+        <v>88.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>63</v>
+        <v>-10.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>36.1</v>
+        <v>3.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="AM15" t="n">
-        <v>2193.96</v>
+        <v>642.97</v>
       </c>
       <c r="AN15" t="n">
-        <v>2046.54</v>
+        <v>579.63</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,739.41 Cr., a P/E ratio of 35.39, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
+          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,537.90 Cr., a P/E ratio of 88.33, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.71 (Consolidation Zone), while MACD Line (46.13) trades below Signal (60.86) with an expanding histogram (-14.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.16% above the 200-day DMA (₹1880.26). Daily volatility envelope is bounded by ATR(14) of ₹68.37.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.70 (Consolidation Zone), while MACD Line (15.39) trades below Signal (15.91) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.44% above the 200-day DMA (₹554.14). Daily volatility envelope is bounded by ATR(14) of ₹21.46.</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,116.00) is positioned above the 30-day DMA (₹2,028.46), 50-day DMA (₹1,908.05), and 200-day DMA (₹1,880.26). The price distance from 200 DMA is +8.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹612.15) is positioned above the 30-day DMA (₹583.11), 50-day DMA (₹550.15), and 200-day DMA (₹554.14). The price distance from 200 DMA is +10.44%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>[2116.0, 2122.35, 2128.7, 2135.04, 2141.39, 2147.74]</t>
+          <t>[612.15, 613.99, 615.82, 617.66, 619.5, 621.33]</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>[2116.0, 2149.7, 2167.37, 2182.42, 2196.09, 2208.9]</t>
+          <t>[612.15, 622.57, 627.96, 632.53, 636.66, 640.53]</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>[2116.0, 2101.84, 2099.69, 2099.52, 2100.37, 2101.87]</t>
+          <t>[612.15, 607.55, 606.72, 606.51, 606.62, 606.94]</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11527.11</v>
+        <v>11540.45</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2969,15 +2969,15 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>129.62</v>
+        <v>129.77</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>₹128.75 - ₹130.93</t>
+          <t>₹128.9 - ₹131.08</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>133.11</v>
+        <v>133.26</v>
       </c>
       <c r="I16" t="n">
         <v>124.43</v>
@@ -3004,16 +3004,16 @@
         <v>4.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R16" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="S16" t="n">
         <v>0.16</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.18</v>
+        <v>-2.19</v>
       </c>
       <c r="U16" t="n">
         <v>48.3</v>
@@ -3025,25 +3025,25 @@
         <v>-0.77</v>
       </c>
       <c r="X16" t="n">
-        <v>125</v>
+        <v>125.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>129.54</v>
+        <v>129.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>130.66</v>
+        <v>130.81</v>
       </c>
       <c r="AA16" t="n">
-        <v>123.07</v>
+        <v>123.22</v>
       </c>
       <c r="AB16" t="n">
-        <v>129.97</v>
+        <v>130.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>130.59</v>
+        <v>130.69</v>
       </c>
       <c r="AD16" t="n">
-        <v>131.57</v>
+        <v>131.62</v>
       </c>
       <c r="AE16" t="n">
         <v>64.40000000000001</v>
@@ -3053,14 +3053,14 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH16" t="n">
         <v>0.15</v>
       </c>
       <c r="AI16" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AJ16" t="n">
         <v>10.1</v>
@@ -3072,14 +3072,14 @@
         <v>15</v>
       </c>
       <c r="AM16" t="n">
-        <v>135.08</v>
+        <v>135.41</v>
       </c>
       <c r="AN16" t="n">
-        <v>123.93</v>
+        <v>123.5</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>IEX operates in the Financial Services sector. With an estimated Market Cap of ₹11,527.11 Cr., a P/E ratio of 22.54, and YoY Revenue Growth of +10.1%, the company demonstrates strong institutional backing, solid operating profit margins (66.22%), and healthy Return on Equity (15.00%).</t>
+          <t>IEX operates in the Financial Services sector. With an estimated Market Cap of ₹11,540.45 Cr., a P/E ratio of 22.57, and YoY Revenue Growth of +10.1%, the company demonstrates strong institutional backing, solid operating profit margins (66.22%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -3089,22 +3089,22 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for IEX. Current Market Price (₹129.62) is positioned above the 30-day DMA (₹124.43), 50-day DMA (₹123.96), and 200-day DMA (₹127.99). The price distance from 200 DMA is +0.95%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for IEX. Current Market Price (₹129.77) is positioned above the 30-day DMA (₹124.43), 50-day DMA (₹123.96), and 200-day DMA (₹127.99). The price distance from 200 DMA is +0.95%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>[129.62, 130.01, 130.4, 130.79, 131.18, 131.56]</t>
+          <t>[129.77, 130.16, 130.55, 130.94, 131.33, 131.72]</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>[129.62, 131.75, 132.87, 133.81, 134.67, 135.47]</t>
+          <t>[129.77, 131.9, 133.02, 133.96, 134.82, 135.62]</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>[129.62, 128.7, 128.55, 128.52, 128.56, 128.64]</t>
+          <t>[129.77, 128.85, 128.7, 128.67, 128.71, 128.79]</t>
         </is>
       </c>
     </row>
@@ -3116,16 +3116,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>285965.55</v>
+        <v>63902.07</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3133,142 +3133,142 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>310.7</v>
+        <v>2121.4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>₹308.63 - ₹313.81</t>
+          <t>₹2107.72 - ₹2141.91</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>318.98</v>
+        <v>2176.1</v>
       </c>
       <c r="I17" t="n">
-        <v>286.32</v>
+        <v>2028.46</v>
       </c>
       <c r="J17" t="n">
-        <v>272.64</v>
+        <v>1908.05</v>
       </c>
       <c r="K17" t="n">
-        <v>273.39</v>
+        <v>1880.26</v>
       </c>
       <c r="L17" t="n">
-        <v>14.27</v>
+        <v>8.16</v>
       </c>
       <c r="M17" t="n">
-        <v>10.44</v>
+        <v>46.13</v>
       </c>
       <c r="N17" t="n">
-        <v>9.26</v>
+        <v>60.86</v>
       </c>
       <c r="O17" t="n">
-        <v>1.18</v>
+        <v>-14.73</v>
       </c>
       <c r="P17" t="n">
-        <v>10.35</v>
+        <v>68.37</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R17" t="n">
-        <v>45.6</v>
+        <v>46.9</v>
       </c>
       <c r="S17" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.35</v>
+        <v>-2.19</v>
       </c>
       <c r="U17" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V17" t="n">
-        <v>2.43</v>
+        <v>6.27</v>
       </c>
       <c r="W17" t="n">
         <v>-0.77</v>
       </c>
       <c r="X17" t="n">
-        <v>306.18</v>
+        <v>2039.35</v>
       </c>
       <c r="Y17" t="n">
-        <v>317.06</v>
+        <v>2024.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>313.19</v>
+        <v>2138.37</v>
       </c>
       <c r="AA17" t="n">
-        <v>295.18</v>
+        <v>2018.84</v>
       </c>
       <c r="AB17" t="n">
-        <v>311.87</v>
+        <v>2107</v>
       </c>
       <c r="AC17" t="n">
-        <v>313.49</v>
+        <v>2158.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>316.27</v>
+        <v>2195.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>62.2</v>
+        <v>43.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.34) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH17" t="n">
         <v>0.15</v>
       </c>
       <c r="AI17" t="n">
-        <v>661</v>
+        <v>35.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>182</v>
+        <v>63</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.6</v>
+        <v>36.1</v>
       </c>
       <c r="AL17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AM17" t="n">
-        <v>321.59</v>
+        <v>2194.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>299.8</v>
+        <v>2049.1</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹285,965.55 Cr., a P/E ratio of 660.96, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>GODREJPROP operates in the Real Estate sector. With an estimated Market Cap of ₹63,902.07 Cr., a P/E ratio of 35.48, and YoY Revenue Growth of +63.0%, the company demonstrates strong institutional backing, solid operating profit margins (36.06%), and healthy Return on Equity (9.97%).</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.17 (Bullish Momentum Zone), while MACD Line (10.44) trades above Signal (9.26) with an expanding histogram (+1.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.27% above the 200-day DMA (₹273.39). Daily volatility envelope is bounded by ATR(14) of ₹10.35.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.71 (Consolidation Zone), while MACD Line (46.13) trades below Signal (60.86) with an expanding histogram (-14.73). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.16% above the 200-day DMA (₹1880.26). Daily volatility envelope is bounded by ATR(14) of ₹68.37.</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹310.70) is positioned above the 30-day DMA (₹286.32), 50-day DMA (₹272.64), and 200-day DMA (₹273.39). The price distance from 200 DMA is +14.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for GODREJPROP. Current Market Price (₹2,121.40) is positioned above the 30-day DMA (₹2,028.46), 50-day DMA (₹1,908.05), and 200-day DMA (₹1,880.26). The price distance from 200 DMA is +8.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>[310.7, 311.63, 312.56, 313.5, 314.43, 315.36]</t>
+          <t>[2121.4, 2127.76, 2134.13, 2140.49, 2146.86, 2153.22]</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>[310.7, 315.77, 318.42, 320.67, 322.71, 324.62]</t>
+          <t>[2121.4, 2155.11, 2172.81, 2187.86, 2201.56, 2214.38]</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>[310.7, 308.53, 308.17, 308.12, 308.22, 308.42]</t>
+          <t>[2121.4, 2107.25, 2105.12, 2104.96, 2105.83, 2107.35]</t>
         </is>
       </c>
     </row>
@@ -3280,16 +3280,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17441.92</v>
+        <v>286425.82</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3297,142 +3297,142 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>608.1</v>
+        <v>311.35</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>₹603.81 - ₹614.54</t>
+          <t>₹309.28 - ₹314.46</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>625.27</v>
+        <v>319.63</v>
       </c>
       <c r="I18" t="n">
-        <v>583.11</v>
+        <v>286.32</v>
       </c>
       <c r="J18" t="n">
-        <v>550.15</v>
+        <v>272.64</v>
       </c>
       <c r="K18" t="n">
-        <v>554.14</v>
+        <v>273.39</v>
       </c>
       <c r="L18" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="M18" t="n">
         <v>10.44</v>
       </c>
-      <c r="M18" t="n">
-        <v>15.39</v>
-      </c>
       <c r="N18" t="n">
-        <v>15.91</v>
+        <v>9.26</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.52</v>
+        <v>1.18</v>
       </c>
       <c r="P18" t="n">
-        <v>21.46</v>
+        <v>10.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="R18" t="n">
-        <v>47.5</v>
+        <v>46.1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.4</v>
+        <v>-2.32</v>
       </c>
       <c r="U18" t="n">
         <v>53.3</v>
       </c>
       <c r="V18" t="n">
-        <v>4.78</v>
+        <v>2.43</v>
       </c>
       <c r="W18" t="n">
         <v>-0.77</v>
       </c>
       <c r="X18" t="n">
-        <v>582.35</v>
+        <v>306.87</v>
       </c>
       <c r="Y18" t="n">
-        <v>595.73</v>
+        <v>317.77</v>
       </c>
       <c r="Z18" t="n">
-        <v>612.96</v>
+        <v>313.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>575.91</v>
+        <v>295.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>614.4</v>
+        <v>312.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>626.2</v>
+        <v>313.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>644.3</v>
+        <v>316.48</v>
       </c>
       <c r="AE18" t="n">
-        <v>54.7</v>
+        <v>62.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Low VIX (12.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH18" t="n">
         <v>0.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>87.8</v>
+        <v>662</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-10.1</v>
+        <v>182</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="AM18" t="n">
-        <v>636.6799999999999</v>
+        <v>323.19</v>
       </c>
       <c r="AN18" t="n">
-        <v>576.48</v>
+        <v>300.17</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>PGEL operates in the Technology sector. With an estimated Market Cap of ₹17,441.92 Cr., a P/E ratio of 87.85, and YoY Revenue Growth of -10.1%, the company demonstrates strong institutional backing, solid operating profit margins (3.72%), and healthy Return on Equity (6.69%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹286,425.82 Cr., a P/E ratio of 662.02, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.70 (Consolidation Zone), while MACD Line (15.39) trades below Signal (15.91) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.44% above the 200-day DMA (₹554.14). Daily volatility envelope is bounded by ATR(14) of ₹21.46.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.17 (Bullish Momentum Zone), while MACD Line (10.44) trades above Signal (9.26) with an expanding histogram (+1.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.27% above the 200-day DMA (₹273.39). Daily volatility envelope is bounded by ATR(14) of ₹10.35.</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PGEL. Current Market Price (₹608.10) is positioned above the 30-day DMA (₹583.11), 50-day DMA (₹550.15), and 200-day DMA (₹554.14). The price distance from 200 DMA is +10.44%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹311.35) is positioned above the 30-day DMA (₹286.32), 50-day DMA (₹272.64), and 200-day DMA (₹273.39). The price distance from 200 DMA is +14.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>[608.1, 609.92, 611.75, 613.57, 615.4, 617.22]</t>
+          <t>[311.35, 312.28, 313.22, 314.15, 315.09, 316.02]</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>[608.1, 618.51, 623.89, 628.44, 632.57, 636.42]</t>
+          <t>[311.35, 316.42, 319.07, 321.32, 323.37, 325.28]</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>[608.1, 603.49, 602.64, 602.42, 602.52, 602.83]</t>
+          <t>[311.35, 309.18, 308.83, 308.77, 308.88, 309.08]</t>
         </is>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT18"/>
+  <dimension ref="A1:AU18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,6 +647,11 @@
           <t>Forecast_5D_Low</t>
         </is>
       </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Next_Day_Expected_Close</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -665,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>357563.18</v>
+        <v>358592.78</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -673,15 +678,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12155</v>
+        <v>12190</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹12114.59 - ₹12215.61</t>
+          <t>₹12149.59 - ₹12250.61</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12316.62</v>
+        <v>12351.62</v>
       </c>
       <c r="I2" t="n">
         <v>11508.32</v>
@@ -708,16 +713,16 @@
         <v>202.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.55</v>
+        <v>12.06</v>
       </c>
       <c r="R2" t="n">
-        <v>50.3</v>
+        <v>53</v>
       </c>
       <c r="S2" t="n">
         <v>0.32</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.84</v>
+        <v>-0.83</v>
       </c>
       <c r="U2" t="n">
         <v>50</v>
@@ -729,25 +734,25 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>12060.74</v>
+        <v>12190</v>
       </c>
       <c r="Y2" t="n">
-        <v>12458.04</v>
+        <v>12390.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>12252.24</v>
+        <v>12225.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>11851.96</v>
+        <v>11886.96</v>
       </c>
       <c r="AB2" t="n">
-        <v>12121.33</v>
+        <v>12133</v>
       </c>
       <c r="AC2" t="n">
-        <v>12272.66</v>
+        <v>12296</v>
       </c>
       <c r="AD2" t="n">
-        <v>12390.33</v>
+        <v>12402</v>
       </c>
       <c r="AE2" t="n">
         <v>70.40000000000001</v>
@@ -757,14 +762,14 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.06) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
         <v>15.9</v>
@@ -776,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>12431.71</v>
+        <v>12464.15</v>
       </c>
       <c r="AN2" t="n">
-        <v>11884.91</v>
+        <v>11916.26</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹357,563.18 Cr., a P/E ratio of 41.85, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
+          <t>ULTRACEMCO operates in the Basic Materials sector. With an estimated Market Cap of ₹358,592.78 Cr., a P/E ratio of 41.98, and YoY Revenue Growth of +15.9%, the company demonstrates strong institutional backing, solid operating profit margins (9.29%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -793,23 +798,26 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,155.00) is positioned above the 30-day DMA (₹11,508.32), 50-day DMA (₹11,305.61), and 200-day DMA (₹11,570.61). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ULTRACEMCO. Current Market Price (₹12,190.00) is positioned above the 30-day DMA (₹11,508.32), 50-day DMA (₹11,305.61), and 200-day DMA (₹11,570.61). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[12155.0, 12243.07, 12331.14, 12419.2, 12507.27, 12595.34]</t>
+          <t>[12190.0, 12282.19, 12374.39, 12466.58, 12558.78, 12650.97]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[12155.0, 12323.88, 12445.42, 12559.17, 12668.89, 12776.04]</t>
+          <t>[12190.0, 12363.0, 12488.67, 12606.55, 12720.4, 12831.67]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[12155.0, 12182.46, 12245.42, 12314.23, 12386.06, 12459.82]</t>
-        </is>
+          <t>[12190.0, 12221.59, 12288.68, 12361.61, 12437.56, 12515.45]</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>12225.1</v>
       </c>
     </row>
     <row r="3">
@@ -829,7 +837,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>130674.76</v>
+        <v>130502.37</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -837,15 +845,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>113.7</v>
+        <v>113.55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹113.31 - ₹114.29</t>
+          <t>₹113.16 - ₹114.14</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>115.26</v>
+        <v>115.11</v>
       </c>
       <c r="I3" t="n">
         <v>108.12</v>
@@ -872,16 +880,16 @@
         <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.55</v>
+        <v>12.06</v>
       </c>
       <c r="R3" t="n">
-        <v>48.9</v>
+        <v>51.8</v>
       </c>
       <c r="S3" t="n">
         <v>0.31</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.92</v>
+        <v>-0.91</v>
       </c>
       <c r="U3" t="n">
         <v>55</v>
@@ -893,25 +901,25 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>111.36</v>
+        <v>112.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>114.77</v>
+        <v>113.67</v>
       </c>
       <c r="Z3" t="n">
-        <v>114.61</v>
+        <v>113.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>110.77</v>
+        <v>110.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>114.16</v>
+        <v>114.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>114.73</v>
+        <v>114.74</v>
       </c>
       <c r="AD3" t="n">
-        <v>115.77</v>
+        <v>115.92</v>
       </c>
       <c r="AE3" t="n">
         <v>79</v>
@@ -921,7 +929,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.55) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.06) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
@@ -940,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>117.02</v>
+        <v>116.66</v>
       </c>
       <c r="AN3" t="n">
-        <v>110.4</v>
+        <v>110.59</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,674.76 Cr., a P/E ratio of 5.86, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹130,502.37 Cr., a P/E ratio of 5.86, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -957,23 +965,26 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.70) is positioned above the 30-day DMA (₹108.12), 50-day DMA (₹106.98), and 200-day DMA (₹112.64). The price distance from 200 DMA is +1.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹113.55) is positioned above the 30-day DMA (₹108.12), 50-day DMA (₹106.98), and 200-day DMA (₹112.64). The price distance from 200 DMA is +1.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[113.7, 114.04, 114.38, 114.72, 115.06, 115.41]</t>
+          <t>[113.55, 113.89, 114.23, 114.57, 114.91, 115.25]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[113.7, 114.82, 115.49, 116.08, 116.63, 117.15]</t>
+          <t>[113.55, 114.67, 115.34, 115.92, 116.47, 117.0]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[113.7, 113.46, 113.55, 113.71, 113.89, 114.1]</t>
-        </is>
+          <t>[113.55, 113.31, 113.4, 113.56, 113.74, 113.94]</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>113.4</v>
       </c>
     </row>
     <row r="4">
@@ -984,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>219891.88</v>
+        <v>68110.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1001,143 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8010</v>
+        <v>5696.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹7978.64 - ₹8057.04</t>
+          <t>₹5673.6 - ₹5730.85</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8135.45</v>
+        <v>5788.1</v>
       </c>
       <c r="I4" t="n">
-        <v>7478.7</v>
+        <v>5605.35</v>
       </c>
       <c r="J4" t="n">
-        <v>7389.91</v>
+        <v>5501.71</v>
       </c>
       <c r="K4" t="n">
-        <v>7187.9</v>
+        <v>5524.85</v>
       </c>
       <c r="L4" t="n">
-        <v>10.39</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>160.7</v>
+        <v>48.94</v>
       </c>
       <c r="N4" t="n">
-        <v>116.95</v>
+        <v>53.54</v>
       </c>
       <c r="O4" t="n">
-        <v>43.75</v>
+        <v>-4.6</v>
       </c>
       <c r="P4" t="n">
-        <v>156.81</v>
+        <v>114.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.55</v>
+        <v>12.06</v>
       </c>
       <c r="R4" t="n">
-        <v>51.2</v>
+        <v>55.4</v>
       </c>
       <c r="S4" t="n">
         <v>0.27</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.02</v>
+        <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>51.7</v>
+        <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>2.09</v>
+        <v>2.84</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>7887.48</v>
+        <v>5603.74</v>
       </c>
       <c r="Y4" t="n">
-        <v>8167.83</v>
+        <v>5753.04</v>
       </c>
       <c r="Z4" t="n">
-        <v>8074.08</v>
+        <v>5753.04</v>
       </c>
       <c r="AA4" t="n">
-        <v>7774.78</v>
+        <v>5524.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>7977.83</v>
+        <v>5649.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>8050.16</v>
+        <v>5743.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>8090.33</v>
+        <v>5790.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>74.3</v>
+        <v>47.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.06) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>38.7</v>
+        <v>30.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>31.5</v>
+        <v>14.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>23.2</v>
+        <v>15.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="AM4" t="n">
-        <v>8235.690000000001</v>
+        <v>5820.72</v>
       </c>
       <c r="AN4" t="n">
-        <v>7798.99</v>
+        <v>5567.02</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹219,891.88 Cr., a P/E ratio of 38.68, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
+          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹68,110.20 Cr., a P/E ratio of 30.14, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.31 (Bullish Momentum Zone), while MACD Line (160.70) trades above Signal (116.95) with an expanding histogram (+43.75). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.39% above the 200-day DMA (₹7187.90). Daily volatility envelope is bounded by ATR(14) of ₹156.81.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.14 (Consolidation Zone), while MACD Line (48.94) trades below Signal (53.54) with an expanding histogram (-4.60). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +1.51% above the 200-day DMA (₹5524.85). Daily volatility envelope is bounded by ATR(14) of ₹114.50.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹8,010.00) is positioned above the 30-day DMA (₹7,478.70), 50-day DMA (₹7,389.91), and 200-day DMA (₹7,187.90). The price distance from 200 DMA is +10.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,696.50) is positioned above the 30-day DMA (₹5,605.35), 50-day DMA (₹5,501.71), and 200-day DMA (₹5,524.85). The price distance from 200 DMA is +1.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[8010.0, 8034.03, 8058.06, 8082.09, 8106.12, 8130.15]</t>
+          <t>[5696.5, 5713.59, 5730.68, 5747.77, 5764.86, 5781.95]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[8010.0, 8096.75, 8146.77, 8190.73, 8231.57, 8270.41]</t>
+          <t>[5696.5, 5759.39, 5795.45, 5827.1, 5856.46, 5884.36]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[8010.0, 7986.99, 7991.53, 8000.61, 8012.03, 8024.96]</t>
-        </is>
+          <t>[5696.5, 5679.24, 5682.1, 5688.27, 5696.16, 5705.14]</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>5753.04</v>
       </c>
     </row>
     <row r="5">
@@ -1148,160 +1162,163 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>309709.69</v>
+        <v>219246.76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4631</v>
+        <v>7986.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹4614.96 - ₹4655.06</t>
+          <t>₹7955.14 - ₹8033.54</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4695.15</v>
+        <v>8111.95</v>
       </c>
       <c r="I5" t="n">
-        <v>4490.17</v>
+        <v>7478.7</v>
       </c>
       <c r="J5" t="n">
-        <v>4419.22</v>
+        <v>7389.91</v>
       </c>
       <c r="K5" t="n">
-        <v>4344.79</v>
+        <v>7187.9</v>
       </c>
       <c r="L5" t="n">
-        <v>6.68</v>
+        <v>10.39</v>
       </c>
       <c r="M5" t="n">
-        <v>64.29000000000001</v>
+        <v>160.7</v>
       </c>
       <c r="N5" t="n">
-        <v>56.51</v>
+        <v>116.95</v>
       </c>
       <c r="O5" t="n">
-        <v>7.78</v>
+        <v>43.75</v>
       </c>
       <c r="P5" t="n">
-        <v>80.19</v>
+        <v>156.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.55</v>
+        <v>12.06</v>
       </c>
       <c r="R5" t="n">
-        <v>40.6</v>
+        <v>51.1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.22</v>
+        <v>-1.03</v>
       </c>
       <c r="U5" t="n">
-        <v>41.7</v>
+        <v>51.7</v>
       </c>
       <c r="V5" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>4534.78</v>
+        <v>7927.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>4670.81</v>
+        <v>8076.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>4668.05</v>
+        <v>7963.04</v>
       </c>
       <c r="AA5" t="n">
-        <v>4510.72</v>
+        <v>7751.28</v>
       </c>
       <c r="AB5" t="n">
-        <v>4635.9</v>
+        <v>7970.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>4668.5</v>
+        <v>8035.16</v>
       </c>
       <c r="AD5" t="n">
-        <v>4706</v>
+        <v>8083.83</v>
       </c>
       <c r="AE5" t="n">
-        <v>72.8</v>
+        <v>74.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.06) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.8</v>
+        <v>31.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>27.5</v>
+        <v>23.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>4757.33</v>
+        <v>8198.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>4494.93</v>
+        <v>7783.85</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹309,709.69 Cr., a P/E ratio of 34.02, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
+          <t>EICHERMOT operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹219,246.76 Cr., a P/E ratio of 37.02, and YoY Revenue Growth of +31.5%, the company demonstrates strong institutional backing, solid operating profit margins (23.21%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.77 (Bullish Momentum Zone), while MACD Line (64.29) trades above Signal (56.51) with an expanding histogram (+7.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.68% above the 200-day DMA (₹4344.79). Daily volatility envelope is bounded by ATR(14) of ₹80.19.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 74.31 (Bullish Momentum Zone), while MACD Line (160.70) trades above Signal (116.95) with an expanding histogram (+43.75). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.39% above the 200-day DMA (₹7187.90). Daily volatility envelope is bounded by ATR(14) of ₹156.81.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,631.00) is positioned above the 30-day DMA (₹4,490.17), 50-day DMA (₹4,419.22), and 200-day DMA (₹4,344.79). The price distance from 200 DMA is +6.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for EICHERMOT. Current Market Price (₹7,986.50) is positioned above the 30-day DMA (₹7,478.70), 50-day DMA (₹7,389.91), and 200-day DMA (₹7,187.90). The price distance from 200 DMA is +10.39%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[4631.0, 4644.89, 4658.79, 4672.68, 4686.57, 4700.46]</t>
+          <t>[7986.5, 8010.46, 8034.42, 8058.38, 8082.34, 8106.3]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[4631.0, 4676.97, 4704.15, 4728.23, 4750.72, 4772.19]</t>
+          <t>[7986.5, 8073.18, 8123.12, 8167.02, 8207.79, 8246.55]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[4631.0, 4620.84, 4624.77, 4631.01, 4638.46, 4646.67]</t>
-        </is>
+          <t>[7986.5, 7963.42, 7967.89, 7976.9, 7988.25, 8001.11]</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>7963.04</v>
       </c>
     </row>
     <row r="6">
@@ -1312,16 +1329,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67440.64</v>
+        <v>310645.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1329,143 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5640.5</v>
+        <v>4645</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹5617.16 - ₹5675.5</t>
+          <t>₹4628.96 - ₹4669.06</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5733.84</v>
+        <v>4709.15</v>
       </c>
       <c r="I6" t="n">
-        <v>5598.93</v>
+        <v>4490.17</v>
       </c>
       <c r="J6" t="n">
-        <v>5497.15</v>
+        <v>4419.22</v>
       </c>
       <c r="K6" t="n">
-        <v>5524.06</v>
+        <v>4344.79</v>
       </c>
       <c r="L6" t="n">
-        <v>3.31</v>
+        <v>6.68</v>
       </c>
       <c r="M6" t="n">
-        <v>58.81</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>54.69</v>
+        <v>56.51</v>
       </c>
       <c r="O6" t="n">
-        <v>4.12</v>
+        <v>7.78</v>
       </c>
       <c r="P6" t="n">
-        <v>116.68</v>
+        <v>80.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.55</v>
+        <v>12.06</v>
       </c>
       <c r="R6" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.26</v>
+        <v>-1.07</v>
       </c>
       <c r="U6" t="n">
-        <v>51.7</v>
+        <v>43.3</v>
       </c>
       <c r="V6" t="n">
-        <v>2.82</v>
+        <v>2.35</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>5500.49</v>
+        <v>4585.31</v>
       </c>
       <c r="Y6" t="n">
-        <v>5606.71</v>
+        <v>4659.03</v>
       </c>
       <c r="Z6" t="n">
-        <v>5685.62</v>
+        <v>4659.03</v>
       </c>
       <c r="AA6" t="n">
-        <v>5465.48</v>
+        <v>4524.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>5620.67</v>
+        <v>4640.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>5685.34</v>
+        <v>4677.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>5730.17</v>
+        <v>4710.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>56.2</v>
+        <v>72.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.03</v>
+        <v>0.27</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.55) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.06) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>29.3</v>
+        <v>34.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.6</v>
+        <v>1.8</v>
       </c>
       <c r="AK6" t="n">
-        <v>15.6</v>
+        <v>27.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>17.6</v>
+        <v>24</v>
       </c>
       <c r="AM6" t="n">
-        <v>5765.79</v>
+        <v>4769.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>5506.54</v>
+        <v>4515.46</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>ALKEM operates in the Healthcare sector. With an estimated Market Cap of ₹67,440.64 Cr., a P/E ratio of 29.27, and YoY Revenue Growth of +14.6%, the company demonstrates strong institutional backing, solid operating profit margins (15.65%), and healthy Return on Equity (17.56%).</t>
+          <t>HAL operates in the Industrials sector. With an estimated Market Cap of ₹310,645.99 Cr., a P/E ratio of 34.44, and YoY Revenue Growth of +1.8%, the company demonstrates strong institutional backing, solid operating profit margins (27.55%), and healthy Return on Equity (23.98%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.20 (Bullish Momentum Zone), while MACD Line (58.81) trades above Signal (54.69) with an expanding histogram (+4.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.31% above the 200-day DMA (₹5524.06). Daily volatility envelope is bounded by ATR(14) of ₹116.68.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.77 (Bullish Momentum Zone), while MACD Line (64.29) trades above Signal (56.51) with an expanding histogram (+7.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.68% above the 200-day DMA (₹4344.79). Daily volatility envelope is bounded by ATR(14) of ₹80.19.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ALKEM. Current Market Price (₹5,640.50) is positioned above the 30-day DMA (₹5,598.93), 50-day DMA (₹5,497.15), and 200-day DMA (₹5,524.06). The price distance from 200 DMA is +3.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HAL. Current Market Price (₹4,645.00) is positioned above the 30-day DMA (₹4,490.17), 50-day DMA (₹4,419.22), and 200-day DMA (₹4,344.79). The price distance from 200 DMA is +6.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[5640.5, 5657.42, 5674.34, 5691.26, 5708.19, 5725.11]</t>
+          <t>[4645.0, 4658.93, 4672.87, 4686.8, 4700.74, 4714.67]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[5640.5, 5704.09, 5740.35, 5772.1, 5801.53, 5829.47]</t>
+          <t>[4645.0, 4691.01, 4718.23, 4742.36, 4764.89, 4786.4]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[5640.5, 5622.42, 5624.84, 5630.64, 5638.18, 5646.84]</t>
-        </is>
+          <t>[4645.0, 4634.88, 4638.85, 4645.14, 4652.63, 4660.88]</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>4659.03</v>
       </c>
     </row>
     <row r="7">
@@ -1485,7 +1505,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>264489.95</v>
+        <v>264585.82</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1493,15 +1513,15 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2759</v>
+        <v>2760</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹2747.15 - ₹2776.77</t>
+          <t>₹2748.15 - ₹2777.77</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2806.39</v>
+        <v>2807.39</v>
       </c>
       <c r="I7" t="n">
         <v>2698.21</v>
@@ -1528,16 +1548,16 @@
         <v>59.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.55</v>
+        <v>12.06</v>
       </c>
       <c r="R7" t="n">
-        <v>48.2</v>
+        <v>50.9</v>
       </c>
       <c r="S7" t="n">
         <v>0.25</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.28</v>
+        <v>-1.27</v>
       </c>
       <c r="U7" t="n">
         <v>55</v>
@@ -1549,25 +1569,25 @@
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2687.92</v>
+        <v>2710.51</v>
       </c>
       <c r="Y7" t="n">
-        <v>2780.66</v>
+        <v>2760.99</v>
       </c>
       <c r="Z7" t="n">
-        <v>2781.07</v>
+        <v>2760.99</v>
       </c>
       <c r="AA7" t="n">
-        <v>2670.15</v>
+        <v>2671.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>2764.9</v>
+        <v>2765.23</v>
       </c>
       <c r="AC7" t="n">
-        <v>2781.1</v>
+        <v>2781.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>2803.2</v>
+        <v>2803.53</v>
       </c>
       <c r="AE7" t="n">
         <v>67</v>
@@ -1577,14 +1597,14 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.06) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>56.2</v>
+        <v>54.3</v>
       </c>
       <c r="AJ7" t="n">
         <v>17.9</v>
@@ -1596,14 +1616,14 @@
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>2826.2</v>
+        <v>2825.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>2694.16</v>
+        <v>2702.76</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹264,489.95 Cr., a P/E ratio of 56.17, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
+          <t>ASIANPAINT operates in the Basic Materials sector. With an estimated Market Cap of ₹264,585.82 Cr., a P/E ratio of 54.27, and YoY Revenue Growth of +17.9%, the company demonstrates strong institutional backing, solid operating profit margins (12.81%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1613,23 +1633,26 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,759.00) is positioned above the 30-day DMA (₹2,698.21), 50-day DMA (₹2,687.88), and 200-day DMA (₹2,577.55). The price distance from 200 DMA is +7.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ASIANPAINT. Current Market Price (₹2,760.00) is positioned above the 30-day DMA (₹2,698.21), 50-day DMA (₹2,687.88), and 200-day DMA (₹2,577.55). The price distance from 200 DMA is +7.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[2759.0, 2767.28, 2775.55, 2783.83, 2792.11, 2800.38]</t>
+          <t>[2760.0, 2768.28, 2776.56, 2784.84, 2793.12, 2801.4]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2759.0, 2790.97, 2809.06, 2824.87, 2839.5, 2853.37]</t>
+          <t>[2760.0, 2791.97, 2810.07, 2825.88, 2840.51, 2854.38]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2759.0, 2749.51, 2750.42, 2753.05, 2756.57, 2760.65]</t>
-        </is>
+          <t>[2760.0, 2750.51, 2751.43, 2754.06, 2757.58, 2761.66]</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>2760.99</v>
       </c>
     </row>
     <row r="8">
@@ -1649,7 +1672,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>104899.84</v>
+        <v>105483.44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1657,15 +1680,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>737.6</v>
+        <v>741.05</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹734.61 - ₹742.09</t>
+          <t>₹738.06 - ₹745.54</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>749.58</v>
+        <v>753.03</v>
       </c>
       <c r="I8" t="n">
         <v>731.6799999999999</v>
@@ -1692,10 +1715,10 @@
         <v>14.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.55</v>
+        <v>12.06</v>
       </c>
       <c r="R8" t="n">
-        <v>43.8</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
         <v>0.26</v>
@@ -1707,31 +1730,31 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>6.3</v>
+        <v>6.32</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>719.63</v>
+        <v>728.89</v>
       </c>
       <c r="Y8" t="n">
-        <v>729.87</v>
+        <v>744.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>743.5</v>
+        <v>744.51</v>
       </c>
       <c r="AA8" t="n">
-        <v>715.14</v>
+        <v>718.59</v>
       </c>
       <c r="AB8" t="n">
-        <v>742.4299999999999</v>
+        <v>742.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>748.0599999999999</v>
+        <v>751.3099999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>758.53</v>
+        <v>761.58</v>
       </c>
       <c r="AE8" t="n">
         <v>54.1</v>
@@ -1741,14 +1764,14 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.55) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.06) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>49.1</v>
+        <v>48.3</v>
       </c>
       <c r="AJ8" t="n">
         <v>15.1</v>
@@ -1760,14 +1783,14 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>755.92</v>
+        <v>759.89</v>
       </c>
       <c r="AN8" t="n">
-        <v>720</v>
+        <v>722.96</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹104,899.84 Cr., a P/E ratio of 49.13, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹105,483.44 Cr., a P/E ratio of 48.31, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1777,23 +1800,26 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹737.60) is positioned above the 30-day DMA (₹731.68), 50-day DMA (₹709.25), and 200-day DMA (₹686.46). The price distance from 200 DMA is +9.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.05) is positioned above the 30-day DMA (₹731.68), 50-day DMA (₹709.25), and 200-day DMA (₹686.46). The price distance from 200 DMA is +9.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[737.6, 739.81, 742.03, 744.24, 746.45, 748.66]</t>
+          <t>[741.05, 743.27, 745.5, 747.72, 749.94, 752.17]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[737.6, 745.8, 750.49, 754.61, 758.43, 762.05]</t>
+          <t>[741.05, 749.26, 753.97, 758.09, 761.92, 765.56]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[737.6, 735.32, 735.67, 736.46, 737.47, 738.62]</t>
-        </is>
+          <t>[741.05, 738.78, 739.14, 739.94, 740.96, 742.12]</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>744.51</v>
       </c>
     </row>
     <row r="9">
@@ -1813,7 +1839,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>95902.02</v>
+        <v>96376</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1821,98 +1847,98 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>364.2</v>
+        <v>366</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹362.64 - ₹366.55</t>
+          <t>₹364.46 - ₹368.31</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>370.46</v>
+        <v>372.16</v>
       </c>
       <c r="I9" t="n">
-        <v>358.01</v>
+        <v>358.35</v>
       </c>
       <c r="J9" t="n">
-        <v>351.17</v>
+        <v>351.85</v>
       </c>
       <c r="K9" t="n">
-        <v>347.72</v>
+        <v>347.77</v>
       </c>
       <c r="L9" t="n">
-        <v>5.86</v>
+        <v>5.82</v>
       </c>
       <c r="M9" t="n">
         <v>4.82</v>
       </c>
       <c r="N9" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1.59</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>7.83</v>
+        <v>7.69</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.55</v>
+        <v>12.06</v>
       </c>
       <c r="R9" t="n">
-        <v>43</v>
+        <v>44.2</v>
       </c>
       <c r="S9" t="n">
         <v>0.25</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.49</v>
+        <v>-1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="V9" t="n">
-        <v>2.99</v>
+        <v>3.33</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>356.16</v>
+        <v>359.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>368.91</v>
+        <v>367.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>367.11</v>
+        <v>367.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>352.46</v>
+        <v>354.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>366.87</v>
+        <v>367.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>369.64</v>
+        <v>371</v>
       </c>
       <c r="AD9" t="n">
-        <v>375.07</v>
+        <v>376</v>
       </c>
       <c r="AE9" t="n">
-        <v>71.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.55) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.06) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AJ9" t="n">
         <v>25.2</v>
@@ -1924,40 +1950,43 @@
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>373.9</v>
+        <v>375.86</v>
       </c>
       <c r="AN9" t="n">
-        <v>354.41</v>
+        <v>356.74</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹95,902.02 Cr., a P/E ratio of 5.99, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
+          <t>RECLTD operates in the Financial Services sector. With an estimated Market Cap of ₹96,376.00 Cr., a P/E ratio of 6.10, and YoY Revenue Growth of +25.2%, the company demonstrates strong institutional backing, solid operating profit margins (68.89%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 71.84 (Bullish Momentum Zone), while MACD Line (4.82) trades above Signal (3.23) with an expanding histogram (+1.59). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.86% above the 200-day DMA (₹347.72). Daily volatility envelope is bounded by ATR(14) of ₹7.83.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.88 (Bullish Momentum Zone), while MACD Line (4.82) trades above Signal (3.55) with an expanding histogram (+1.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.82% above the 200-day DMA (₹347.77). Daily volatility envelope is bounded by ATR(14) of ₹7.69.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹364.20) is positioned above the 30-day DMA (₹358.01), 50-day DMA (₹351.17), and 200-day DMA (₹347.72). The price distance from 200 DMA is +5.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for RECLTD. Current Market Price (₹366.00) is positioned above the 30-day DMA (₹358.35), 50-day DMA (₹351.85), and 200-day DMA (₹347.77). The price distance from 200 DMA is +5.82%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[364.2, 365.29, 366.39, 367.48, 368.57, 369.66]</t>
+          <t>[366.0, 367.1, 368.2, 369.29, 370.39, 371.49]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[364.2, 368.42, 370.81, 372.9, 374.83, 376.66]</t>
+          <t>[366.0, 370.18, 372.55, 374.62, 376.55, 378.37]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[364.2, 362.95, 363.07, 363.41, 363.88, 364.41]</t>
-        </is>
+          <t>[366.0, 364.79, 364.93, 365.3, 365.78, 366.33]</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>367.82</v>
       </c>
     </row>
     <row r="10">
@@ -1977,7 +2006,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>117478.01</v>
+        <v>117849.63</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1985,15 +2014,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1454.2</v>
+        <v>1458.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹1447.37 - ₹1464.44</t>
+          <t>₹1451.97 - ₹1469.04</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1481.51</v>
+        <v>1486.11</v>
       </c>
       <c r="I10" t="n">
         <v>1443.04</v>
@@ -2020,16 +2049,16 @@
         <v>34.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.55</v>
+        <v>12.06</v>
       </c>
       <c r="R10" t="n">
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="S10" t="n">
         <v>0.23</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.69</v>
+        <v>-1.68</v>
       </c>
       <c r="U10" t="n">
         <v>45</v>
@@ -2041,25 +2070,25 @@
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>1413.23</v>
+        <v>1429.22</v>
       </c>
       <c r="Y10" t="n">
-        <v>1416.3</v>
+        <v>1463.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>1465.83</v>
+        <v>1463.41</v>
       </c>
       <c r="AA10" t="n">
-        <v>1402.99</v>
+        <v>1407.59</v>
       </c>
       <c r="AB10" t="n">
-        <v>1452.57</v>
+        <v>1455.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1461.64</v>
+        <v>1466.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1469.07</v>
+        <v>1474.6</v>
       </c>
       <c r="AE10" t="n">
         <v>55.4</v>
@@ -2069,14 +2098,14 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.55) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.06) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="AJ10" t="n">
         <v>3.5</v>
@@ -2088,14 +2117,14 @@
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>1486.32</v>
+        <v>1489.77</v>
       </c>
       <c r="AN10" t="n">
-        <v>1423.91</v>
+        <v>1427.07</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,478.01 Cr., a P/E ratio of 35.19, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
+          <t>CIPLA operates in the Healthcare sector. With an estimated Market Cap of ₹117,849.63 Cr., a P/E ratio of 35.30, and YoY Revenue Growth of +3.5%, the company demonstrates strong institutional backing, solid operating profit margins (12.01%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2105,23 +2134,26 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,454.20) is positioned above the 30-day DMA (₹1,443.04), 50-day DMA (₹1,419.16), and 200-day DMA (₹1,394.98). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for CIPLA. Current Market Price (₹1,458.80) is positioned above the 30-day DMA (₹1,443.04), 50-day DMA (₹1,419.16), and 200-day DMA (₹1,394.98). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[1454.2, 1458.56, 1462.93, 1467.29, 1471.65, 1476.01]</t>
+          <t>[1458.8, 1463.18, 1467.55, 1471.93, 1476.31, 1480.68]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[1454.2, 1472.22, 1482.24, 1490.94, 1498.96, 1506.55]</t>
+          <t>[1458.8, 1476.83, 1486.87, 1495.58, 1503.62, 1511.22]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[1454.2, 1448.32, 1448.44, 1449.55, 1451.16, 1453.11]</t>
-        </is>
+          <t>[1458.8, 1452.93, 1453.07, 1454.19, 1455.82, 1457.78]</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>1463.41</v>
       </c>
     </row>
     <row r="11">
@@ -2141,106 +2173,106 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>147121.83</v>
+        <v>146165.11</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1660.8</v>
+        <v>1650</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹1651.69 - ₹1674.47</t>
+          <t>₹1641.39 - ₹1662.92</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1697.26</v>
+        <v>1684.45</v>
       </c>
       <c r="I11" t="n">
-        <v>1496.08</v>
+        <v>1505.04</v>
       </c>
       <c r="J11" t="n">
-        <v>1470.74</v>
+        <v>1475.27</v>
       </c>
       <c r="K11" t="n">
-        <v>1461.21</v>
+        <v>1462.42</v>
       </c>
       <c r="L11" t="n">
-        <v>12.85</v>
+        <v>12.72</v>
       </c>
       <c r="M11" t="n">
-        <v>58.14</v>
+        <v>57.73</v>
       </c>
       <c r="N11" t="n">
-        <v>48.29</v>
+        <v>50.18</v>
       </c>
       <c r="O11" t="n">
-        <v>9.85</v>
+        <v>7.55</v>
       </c>
       <c r="P11" t="n">
-        <v>45.57</v>
+        <v>43.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.55</v>
+        <v>12.06</v>
       </c>
       <c r="R11" t="n">
-        <v>48.3</v>
+        <v>47.1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.74</v>
+        <v>-1.69</v>
       </c>
       <c r="U11" t="n">
         <v>50</v>
       </c>
       <c r="V11" t="n">
-        <v>7.95</v>
+        <v>7.72</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>1632.32</v>
+        <v>1647.94</v>
       </c>
       <c r="Y11" t="n">
-        <v>1690.45</v>
+        <v>1678.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>1674.09</v>
+        <v>1639.27</v>
       </c>
       <c r="AA11" t="n">
-        <v>1592.44</v>
+        <v>1585.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1657.77</v>
+        <v>1651.27</v>
       </c>
       <c r="AC11" t="n">
-        <v>1667.84</v>
+        <v>1663.54</v>
       </c>
       <c r="AD11" t="n">
-        <v>1674.87</v>
+        <v>1677.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>83.5</v>
+        <v>82.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Low VIX (12.55) | LSTM Deep Net</t>
+          <t>Low VIX (12.06) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="AJ11" t="n">
         <v>17.7</v>
@@ -2252,40 +2284,43 @@
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>1703.67</v>
+        <v>1695.57</v>
       </c>
       <c r="AN11" t="n">
-        <v>1616.56</v>
+        <v>1603.07</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹147,121.83 Cr., a P/E ratio of 28.73, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹146,165.11 Cr., a P/E ratio of 28.51, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 83.49 (Bullish Momentum Zone), while MACD Line (58.14) trades above Signal (48.29) with an expanding histogram (+9.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.85% above the 200-day DMA (₹1461.21). Daily volatility envelope is bounded by ATR(14) of ₹45.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 82.28 (Bullish Momentum Zone), while MACD Line (57.73) trades above Signal (50.18) with an expanding histogram (+7.55). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.72% above the 200-day DMA (₹1462.42). Daily volatility envelope is bounded by ATR(14) of ₹43.06.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,660.80) is positioned above the 30-day DMA (₹1,496.08), 50-day DMA (₹1,470.74), and 200-day DMA (₹1,461.21). The price distance from 200 DMA is +12.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,650.00) is positioned above the 30-day DMA (₹1,505.04), 50-day DMA (₹1,475.27), and 200-day DMA (₹1,462.42). The price distance from 200 DMA is +12.72%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[1660.8, 1665.78, 1670.76, 1675.75, 1680.73, 1685.71]</t>
+          <t>[1650.0, 1659.56, 1669.12, 1678.67, 1688.23, 1697.79]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[1660.8, 1684.01, 1696.54, 1707.32, 1717.19, 1726.47]</t>
+          <t>[1650.0, 1676.78, 1693.48, 1708.51, 1722.68, 1736.31]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[1660.8, 1652.11, 1651.43, 1652.07, 1653.39, 1655.14]</t>
-        </is>
+          <t>[1650.0, 1646.64, 1650.85, 1656.3, 1662.39, 1668.9]</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>1639.27</v>
       </c>
     </row>
     <